--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD0F70F2-5507-4353-9B30-395B47C7FCEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64939C9F-954F-4DDC-8AEC-A497F09A3B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -2816,7 +2816,7 @@
         <v>83</v>
       </c>
       <c r="D2">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="E2">
         <v>48</v>
@@ -2872,7 +2872,7 @@
         <v>84</v>
       </c>
       <c r="D3">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="E3">
         <v>32</v>
@@ -2928,7 +2928,7 @@
         <v>85</v>
       </c>
       <c r="D4">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="E4">
         <v>34</v>
@@ -2984,7 +2984,7 @@
         <v>86</v>
       </c>
       <c r="D5">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="E5">
         <v>41</v>
@@ -3040,7 +3040,7 @@
         <v>87</v>
       </c>
       <c r="D6">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="E6">
         <v>35</v>
@@ -3096,7 +3096,7 @@
         <v>88</v>
       </c>
       <c r="D7">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="E7">
         <v>46</v>
@@ -3152,7 +3152,7 @@
         <v>89</v>
       </c>
       <c r="D8">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="E8">
         <v>38</v>
@@ -3208,7 +3208,7 @@
         <v>90</v>
       </c>
       <c r="D9">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="E9">
         <v>51</v>
@@ -3264,7 +3264,7 @@
         <v>91</v>
       </c>
       <c r="D10">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="E10">
         <v>47</v>
@@ -3320,7 +3320,7 @@
         <v>21</v>
       </c>
       <c r="D11">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="E11">
         <v>32</v>
@@ -3376,7 +3376,7 @@
         <v>92</v>
       </c>
       <c r="D12">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="E12">
         <v>43</v>
@@ -3432,7 +3432,7 @@
         <v>93</v>
       </c>
       <c r="D13">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="E13">
         <v>45</v>
@@ -3488,7 +3488,7 @@
         <v>23</v>
       </c>
       <c r="D14">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="E14">
         <v>48</v>
@@ -3544,7 +3544,7 @@
         <v>94</v>
       </c>
       <c r="D15">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="E15">
         <v>45</v>
@@ -3600,7 +3600,7 @@
         <v>95</v>
       </c>
       <c r="D16">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="E16">
         <v>41</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64939C9F-954F-4DDC-8AEC-A497F09A3B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF0C547-2C98-4E2E-9AAE-CC7FF2C1F261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   <externalReferences>
     <externalReference r:id="rId6"/>
   </externalReferences>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="122">
   <si>
     <t>Id</t>
   </si>
@@ -401,13 +401,17 @@
   </si>
   <si>
     <t>ビヤーキー</t>
+  </si>
+  <si>
+    <t>Mov</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -417,6 +421,14 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -445,11 +457,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2740,7 +2755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:T33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="7.6328125" customWidth="1"/>
@@ -2749,10 +2764,10 @@
     <col min="5" max="5" width="3.81640625" customWidth="1"/>
     <col min="6" max="6" width="4" customWidth="1"/>
     <col min="7" max="8" width="4.453125" customWidth="1"/>
-    <col min="9" max="9" width="4.7265625" customWidth="1"/>
+    <col min="9" max="10" width="4.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2780,32 +2795,35 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2834,34 +2852,37 @@
         <v>19</v>
       </c>
       <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
         <v>4</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>11</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
       <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
         <v>90</v>
       </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
       <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
         <v>50</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>70</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>50</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2890,34 +2911,37 @@
         <v>13</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
         <v>11</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
       <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
         <v>50</v>
       </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
       <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
         <v>90</v>
-      </c>
-      <c r="P3">
-        <v>30</v>
       </c>
       <c r="Q3">
         <v>30</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R3">
+        <v>30</v>
+      </c>
+      <c r="S3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2949,31 +2973,34 @@
         <v>2</v>
       </c>
       <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
         <v>11</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
       <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
         <v>60</v>
       </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
       <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
         <v>60</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>10</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>90</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3002,34 +3029,37 @@
         <v>18</v>
       </c>
       <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
         <v>5</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>11</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
       <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
         <v>80</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
       <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
         <v>75</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>35</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>50</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3061,31 +3091,34 @@
         <v>2</v>
       </c>
       <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
         <v>11</v>
       </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
       <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
         <v>60</v>
       </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
       <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
         <v>60</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>10</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <v>70</v>
       </c>
-      <c r="R6" t="s">
+      <c r="S6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3114,34 +3147,37 @@
         <v>12</v>
       </c>
       <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7">
         <v>6</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>11</v>
       </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
       <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
         <v>90</v>
       </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
       <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
         <v>55</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>40</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>30</v>
       </c>
-      <c r="R7" t="s">
+      <c r="S7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3173,31 +3209,34 @@
         <v>2</v>
       </c>
       <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
         <v>11</v>
       </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
       <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
         <v>60</v>
       </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
       <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
         <v>80</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>20</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>60</v>
       </c>
-      <c r="R8" t="s">
+      <c r="S8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3226,34 +3265,37 @@
         <v>14</v>
       </c>
       <c r="J9">
+        <v>2</v>
+      </c>
+      <c r="K9">
         <v>6</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>11</v>
       </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
       <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
         <v>100</v>
       </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
       <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
         <v>50</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>75</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <v>40</v>
       </c>
-      <c r="R9" t="s">
+      <c r="S9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3282,34 +3324,37 @@
         <v>12</v>
       </c>
       <c r="J10">
+        <v>2</v>
+      </c>
+      <c r="K10">
         <v>4</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>11</v>
       </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
       <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
         <v>90</v>
       </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
       <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
         <v>80</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>20</v>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <v>40</v>
       </c>
-      <c r="R10" t="s">
+      <c r="S10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3338,34 +3383,37 @@
         <v>31</v>
       </c>
       <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11">
         <v>5</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>11</v>
       </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
       <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
         <v>50</v>
       </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
       <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
         <v>60</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>20</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>70</v>
       </c>
-      <c r="R11" t="s">
+      <c r="S11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3394,22 +3442,22 @@
         <v>23</v>
       </c>
       <c r="J12">
+        <v>2</v>
+      </c>
+      <c r="K12">
         <v>5</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>11</v>
       </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
       <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
         <v>70</v>
       </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
       <c r="O12">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="P12">
         <v>60</v>
@@ -3417,11 +3465,14 @@
       <c r="Q12">
         <v>60</v>
       </c>
-      <c r="R12" t="s">
+      <c r="R12">
+        <v>60</v>
+      </c>
+      <c r="S12" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3450,34 +3501,37 @@
         <v>17</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
         <v>11</v>
       </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
       <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
         <v>80</v>
       </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
       <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
         <v>80</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>30</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <v>50</v>
       </c>
-      <c r="R13" t="s">
+      <c r="S13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3506,34 +3560,37 @@
         <v>18</v>
       </c>
       <c r="J14">
+        <v>2</v>
+      </c>
+      <c r="K14">
         <v>4</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>11</v>
       </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
       <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
         <v>100</v>
       </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
       <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
         <v>70</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>40</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <v>50</v>
       </c>
-      <c r="R14" t="s">
+      <c r="S14" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3562,34 +3619,37 @@
         <v>11</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
         <v>11</v>
       </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
       <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
         <v>110</v>
       </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
       <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
         <v>60</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>25</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <v>40</v>
       </c>
-      <c r="R15" t="s">
+      <c r="S15" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3618,34 +3678,37 @@
         <v>25</v>
       </c>
       <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="K16">
         <v>6</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>11</v>
       </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
       <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
         <v>70</v>
       </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
       <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
         <v>85</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>20</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <v>70</v>
       </c>
-      <c r="R16" t="s">
+      <c r="S16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>101</v>
       </c>
@@ -3674,34 +3737,37 @@
         <v>18</v>
       </c>
       <c r="J17">
+        <v>2</v>
+      </c>
+      <c r="K17">
         <v>5</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>12</v>
       </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
       <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
         <v>80</v>
       </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
       <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
         <v>70</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>40</v>
       </c>
-      <c r="Q17">
+      <c r="R17">
         <v>20</v>
       </c>
-      <c r="R17" t="s">
+      <c r="S17" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>102</v>
       </c>
@@ -3730,34 +3796,37 @@
         <v>18</v>
       </c>
       <c r="J18">
+        <v>2</v>
+      </c>
+      <c r="K18">
         <v>4</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>12</v>
       </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
       <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
         <v>100</v>
       </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
       <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
         <v>60</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>35</v>
       </c>
-      <c r="Q18">
+      <c r="R18">
         <v>40</v>
       </c>
-      <c r="R18" t="s">
+      <c r="S18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>103</v>
       </c>
@@ -3786,34 +3855,37 @@
         <v>22</v>
       </c>
       <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19">
         <v>6</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>12</v>
       </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
       <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
         <v>100</v>
       </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
       <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
         <v>50</v>
-      </c>
-      <c r="P19">
-        <v>30</v>
       </c>
       <c r="Q19">
         <v>30</v>
       </c>
-      <c r="R19" t="s">
+      <c r="R19">
+        <v>30</v>
+      </c>
+      <c r="S19" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>104</v>
       </c>
@@ -3845,31 +3917,34 @@
         <v>2</v>
       </c>
       <c r="K20">
+        <v>2</v>
+      </c>
+      <c r="L20">
         <v>12</v>
       </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
       <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
         <v>100</v>
       </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
       <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
         <v>50</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>25</v>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <v>50</v>
       </c>
-      <c r="R20" t="s">
+      <c r="S20" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>105</v>
       </c>
@@ -3898,34 +3973,37 @@
         <v>13</v>
       </c>
       <c r="J21">
+        <v>2</v>
+      </c>
+      <c r="K21">
         <v>6</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>12</v>
       </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
       <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
         <v>100</v>
       </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
       <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
         <v>70</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>50</v>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <v>15</v>
       </c>
-      <c r="R21" t="s">
+      <c r="S21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>201</v>
       </c>
@@ -3954,31 +4032,34 @@
         <v>20</v>
       </c>
       <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22">
         <v>5</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>12</v>
       </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
       <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
         <v>120</v>
       </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
       <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
         <v>80</v>
-      </c>
-      <c r="P22">
-        <v>60</v>
       </c>
       <c r="Q22">
         <v>60</v>
       </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="R22">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>1001</v>
       </c>
@@ -4007,7 +4088,7 @@
         <v>15</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -4016,22 +4097,25 @@
         <v>0</v>
       </c>
       <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
         <v>55</v>
       </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
       <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
         <v>60</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>30</v>
       </c>
-      <c r="Q23">
+      <c r="R23">
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>1002</v>
       </c>
@@ -4060,7 +4144,7 @@
         <v>28</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -4069,25 +4153,28 @@
         <v>0</v>
       </c>
       <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
         <v>60</v>
       </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
       <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
         <v>40</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <v>25</v>
       </c>
-      <c r="Q24">
+      <c r="R24">
         <v>70</v>
       </c>
-      <c r="S24" t="s">
+      <c r="T24" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>1003</v>
       </c>
@@ -4116,7 +4203,7 @@
         <v>9</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -4125,25 +4212,28 @@
         <v>0</v>
       </c>
       <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
         <v>85</v>
       </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
       <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
         <v>25</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <v>40</v>
       </c>
-      <c r="Q25">
+      <c r="R25">
         <v>25</v>
       </c>
-      <c r="S25" t="s">
+      <c r="T25" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>1004</v>
       </c>
@@ -4172,7 +4262,7 @@
         <v>21</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -4181,25 +4271,28 @@
         <v>0</v>
       </c>
       <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
         <v>85</v>
       </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
       <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
         <v>35</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>15</v>
       </c>
-      <c r="Q26">
+      <c r="R26">
         <v>30</v>
       </c>
-      <c r="S26" t="s">
+      <c r="T26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>1005</v>
       </c>
@@ -4228,7 +4321,7 @@
         <v>12</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -4237,25 +4330,28 @@
         <v>0</v>
       </c>
       <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
         <v>70</v>
       </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
       <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
         <v>30</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
         <v>40</v>
       </c>
-      <c r="Q27">
+      <c r="R27">
         <v>45</v>
       </c>
-      <c r="S27" t="s">
+      <c r="T27" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>1006</v>
       </c>
@@ -4284,7 +4380,7 @@
         <v>20</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -4293,13 +4389,13 @@
         <v>0</v>
       </c>
       <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
         <v>40</v>
       </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
       <c r="O28">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P28">
         <v>50</v>
@@ -4307,11 +4403,14 @@
       <c r="Q28">
         <v>50</v>
       </c>
-      <c r="S28" t="s">
+      <c r="R28">
+        <v>50</v>
+      </c>
+      <c r="T28" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>1007</v>
       </c>
@@ -4340,7 +4439,7 @@
         <v>16</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -4349,25 +4448,28 @@
         <v>0</v>
       </c>
       <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
         <v>65</v>
       </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
       <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
         <v>45</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <v>40</v>
       </c>
-      <c r="Q29">
+      <c r="R29">
         <v>30</v>
       </c>
-      <c r="S29" t="s">
+      <c r="T29" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>1008</v>
       </c>
@@ -4396,7 +4498,7 @@
         <v>16</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -4405,25 +4507,28 @@
         <v>0</v>
       </c>
       <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
         <v>80</v>
       </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
       <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
         <v>40</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>60</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>35</v>
       </c>
-      <c r="S30" t="s">
+      <c r="T30" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>1009</v>
       </c>
@@ -4452,7 +4557,7 @@
         <v>24</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -4461,25 +4566,28 @@
         <v>0</v>
       </c>
       <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
         <v>25</v>
       </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
       <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
         <v>65</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <v>30</v>
       </c>
-      <c r="Q31">
+      <c r="R31">
         <v>50</v>
       </c>
-      <c r="S31" t="s">
+      <c r="T31" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>1010</v>
       </c>
@@ -4508,7 +4616,7 @@
         <v>31</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -4517,25 +4625,28 @@
         <v>0</v>
       </c>
       <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
         <v>45</v>
       </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
       <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
         <v>30</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
         <v>20</v>
       </c>
-      <c r="Q32">
+      <c r="R32">
         <v>75</v>
       </c>
-      <c r="S32" t="s">
+      <c r="T32" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>1011</v>
       </c>
@@ -4564,7 +4675,7 @@
         <v>18</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -4573,21 +4684,24 @@
         <v>0</v>
       </c>
       <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
         <v>65</v>
       </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
       <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
         <v>40</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <v>25</v>
       </c>
-      <c r="Q33">
+      <c r="R33">
         <v>30</v>
       </c>
-      <c r="S33" t="s">
+      <c r="T33" t="s">
         <v>28</v>
       </c>
     </row>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF0C547-2C98-4E2E-9AAE-CC7FF2C1F261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0DD2E6-B160-4EDC-AD42-3616A36B93E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   <externalReferences>
     <externalReference r:id="rId6"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -2852,7 +2852,7 @@
         <v>19</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <v>4</v>
@@ -2911,7 +2911,7 @@
         <v>13</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -2970,7 +2970,7 @@
         <v>31</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4">
         <v>2</v>
@@ -3029,7 +3029,7 @@
         <v>18</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <v>5</v>
@@ -3088,7 +3088,7 @@
         <v>32</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6">
         <v>2</v>
@@ -3147,7 +3147,7 @@
         <v>12</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7">
         <v>6</v>
@@ -3206,7 +3206,7 @@
         <v>20</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8">
         <v>2</v>
@@ -3265,7 +3265,7 @@
         <v>14</v>
       </c>
       <c r="J9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9">
         <v>6</v>
@@ -3324,7 +3324,7 @@
         <v>12</v>
       </c>
       <c r="J10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10">
         <v>4</v>
@@ -3383,7 +3383,7 @@
         <v>31</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11">
         <v>5</v>
@@ -3442,7 +3442,7 @@
         <v>23</v>
       </c>
       <c r="J12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K12">
         <v>5</v>
@@ -3501,7 +3501,7 @@
         <v>17</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -3560,7 +3560,7 @@
         <v>18</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14">
         <v>4</v>
@@ -3619,7 +3619,7 @@
         <v>11</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -3678,7 +3678,7 @@
         <v>25</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16">
         <v>6</v>
@@ -3737,7 +3737,7 @@
         <v>18</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17">
         <v>5</v>
@@ -3796,7 +3796,7 @@
         <v>18</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18">
         <v>4</v>
@@ -3855,7 +3855,7 @@
         <v>22</v>
       </c>
       <c r="J19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K19">
         <v>6</v>
@@ -3914,7 +3914,7 @@
         <v>16</v>
       </c>
       <c r="J20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20">
         <v>2</v>
@@ -3973,7 +3973,7 @@
         <v>13</v>
       </c>
       <c r="J21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21">
         <v>6</v>
@@ -4032,7 +4032,7 @@
         <v>20</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22">
         <v>5</v>
@@ -4088,7 +4088,7 @@
         <v>15</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -4144,7 +4144,7 @@
         <v>28</v>
       </c>
       <c r="J24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -4203,7 +4203,7 @@
         <v>9</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -4262,7 +4262,7 @@
         <v>21</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -4321,7 +4321,7 @@
         <v>12</v>
       </c>
       <c r="J27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -4380,7 +4380,7 @@
         <v>20</v>
       </c>
       <c r="J28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -4439,7 +4439,7 @@
         <v>16</v>
       </c>
       <c r="J29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -4498,7 +4498,7 @@
         <v>16</v>
       </c>
       <c r="J30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -4557,7 +4557,7 @@
         <v>24</v>
       </c>
       <c r="J31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -4616,7 +4616,7 @@
         <v>31</v>
       </c>
       <c r="J32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -4675,7 +4675,7 @@
         <v>18</v>
       </c>
       <c r="J33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K33">
         <v>0</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0DD2E6-B160-4EDC-AD42-3616A36B93E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{423A6C05-079C-416B-A56D-CA4ECB7D07C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2834,22 +2834,22 @@
         <v>83</v>
       </c>
       <c r="D2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2">
         <v>3</v>
@@ -2893,7 +2893,7 @@
         <v>84</v>
       </c>
       <c r="D3">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>32</v>
@@ -2902,10 +2902,10 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3">
         <v>13</v>
@@ -2952,22 +2952,22 @@
         <v>85</v>
       </c>
       <c r="D4">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J4">
         <v>3</v>
@@ -3011,22 +3011,22 @@
         <v>86</v>
       </c>
       <c r="D5">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -3070,22 +3070,22 @@
         <v>87</v>
       </c>
       <c r="D6">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J6">
         <v>3</v>
@@ -3129,22 +3129,22 @@
         <v>88</v>
       </c>
       <c r="D7">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J7">
         <v>3</v>
@@ -3188,22 +3188,22 @@
         <v>89</v>
       </c>
       <c r="D8">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J8">
         <v>3</v>
@@ -3247,19 +3247,19 @@
         <v>90</v>
       </c>
       <c r="D9">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I9">
         <v>14</v>
@@ -3306,19 +3306,19 @@
         <v>91</v>
       </c>
       <c r="D10">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I10">
         <v>12</v>
@@ -3365,22 +3365,22 @@
         <v>21</v>
       </c>
       <c r="D11">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I11">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J11">
         <v>3</v>
@@ -3424,22 +3424,22 @@
         <v>92</v>
       </c>
       <c r="D12">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H12">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I12">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J12">
         <v>3</v>
@@ -3483,22 +3483,22 @@
         <v>93</v>
       </c>
       <c r="D13">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E13">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H13">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I13">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J13">
         <v>3</v>
@@ -3542,22 +3542,22 @@
         <v>23</v>
       </c>
       <c r="D14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E14">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I14">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J14">
         <v>3</v>
@@ -3601,19 +3601,19 @@
         <v>94</v>
       </c>
       <c r="D15">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H15">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I15">
         <v>11</v>
@@ -3660,22 +3660,22 @@
         <v>95</v>
       </c>
       <c r="D16">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J16">
         <v>3</v>
@@ -3719,22 +3719,22 @@
         <v>96</v>
       </c>
       <c r="D17">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="E17">
+        <v>100</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
         <v>40</v>
       </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>12</v>
-      </c>
       <c r="H17">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I17">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J17">
         <v>3</v>
@@ -3778,22 +3778,22 @@
         <v>97</v>
       </c>
       <c r="D18">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="H18">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I18">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J18">
         <v>3</v>
@@ -3837,22 +3837,22 @@
         <v>98</v>
       </c>
       <c r="D19">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="H19">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I19">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J19">
         <v>3</v>
@@ -3896,22 +3896,22 @@
         <v>99</v>
       </c>
       <c r="D20">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H20">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I20">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J20">
         <v>3</v>
@@ -3955,7 +3955,7 @@
         <v>100</v>
       </c>
       <c r="D21">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="E21">
         <v>100</v>
@@ -3964,13 +3964,13 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="H21">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I21">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="J21">
         <v>3</v>
@@ -4014,7 +4014,7 @@
         <v>29</v>
       </c>
       <c r="D22">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E22">
         <v>100</v>
@@ -4023,13 +4023,13 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H22">
         <v>20</v>
       </c>
       <c r="I22">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J22">
         <v>3</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{423A6C05-079C-416B-A56D-CA4ECB7D07C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -22,18 +16,7 @@
   <externalReferences>
     <externalReference r:id="rId6"/>
   </externalReferences>
-  <calcPr calcId="191029" concurrentCalc="0"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
@@ -67,6 +50,9 @@
     <t>Spd</t>
   </si>
   <si>
+    <t>Mov</t>
+  </si>
+  <si>
     <t>Kind1</t>
   </si>
   <si>
@@ -91,63 +77,117 @@
     <t>SpdGrowth</t>
   </si>
   <si>
+    <t>Jelslime</t>
+  </si>
+  <si>
     <t>氷</t>
   </si>
   <si>
+    <t>Cursed</t>
+  </si>
+  <si>
     <t>闇</t>
   </si>
   <si>
+    <t>Bee</t>
+  </si>
+  <si>
     <t>雷</t>
   </si>
   <si>
+    <t>Wolf</t>
+  </si>
+  <si>
     <t>炎</t>
   </si>
   <si>
+    <t>Crow</t>
+  </si>
+  <si>
+    <t>Nameless</t>
+  </si>
+  <si>
+    <t>Seacher</t>
+  </si>
+  <si>
+    <t>Shiled</t>
+  </si>
+  <si>
+    <t>Dryad</t>
+  </si>
+  <si>
     <t>Scorpion</t>
   </si>
   <si>
+    <t>Squid</t>
+  </si>
+  <si>
+    <t>Creeper</t>
+  </si>
+  <si>
+    <t>Imp</t>
+  </si>
+  <si>
     <t>白</t>
   </si>
   <si>
-    <t>Imp</t>
+    <t>Armor</t>
+  </si>
+  <si>
+    <t>Sword</t>
+  </si>
+  <si>
+    <t>Ammon</t>
+  </si>
+  <si>
+    <t>Berith</t>
+  </si>
+  <si>
+    <t>Paimon</t>
+  </si>
+  <si>
+    <t>Andras</t>
+  </si>
+  <si>
+    <t>Bifrons</t>
+  </si>
+  <si>
+    <t>Cyaegha</t>
+  </si>
+  <si>
+    <t>Actor0001</t>
+  </si>
+  <si>
+    <t>Actor0002</t>
   </si>
   <si>
     <t>3ボス</t>
   </si>
   <si>
+    <t>Actor0003</t>
+  </si>
+  <si>
     <t>4ボス</t>
   </si>
   <si>
+    <t>Actor0004</t>
+  </si>
+  <si>
     <t>6ボス</t>
   </si>
   <si>
+    <t>Actor0005</t>
+  </si>
+  <si>
     <t>2ボス</t>
   </si>
   <si>
+    <t>Actor0006</t>
+  </si>
+  <si>
     <t>5ボス</t>
   </si>
   <si>
-    <t>Cyaegha</t>
-  </si>
-  <si>
-    <t>Actor0001</t>
-  </si>
-  <si>
-    <t>Actor0002</t>
-  </si>
-  <si>
-    <t>Actor0003</t>
-  </si>
-  <si>
-    <t>Actor0004</t>
-  </si>
-  <si>
-    <t>Actor0005</t>
-  </si>
-  <si>
-    <t>Actor0006</t>
-  </si>
-  <si>
     <t>Actor0007</t>
   </si>
   <si>
@@ -202,12 +242,72 @@
     <t>Text</t>
   </si>
   <si>
+    <t>ネレイドジェム</t>
+  </si>
+  <si>
+    <t>カースド</t>
+  </si>
+  <si>
+    <t>ビー</t>
+  </si>
+  <si>
+    <t>ウルフ</t>
+  </si>
+  <si>
+    <t>クロウ</t>
+  </si>
+  <si>
+    <t>ネームレス</t>
+  </si>
+  <si>
+    <t>サーチャー</t>
+  </si>
+  <si>
+    <t>シールド</t>
+  </si>
+  <si>
+    <t>ドライアド</t>
+  </si>
+  <si>
     <t>スコーピオン</t>
   </si>
   <si>
+    <t>スクイッド</t>
+  </si>
+  <si>
+    <t>クリーパー</t>
+  </si>
+  <si>
     <t>インプ</t>
   </si>
   <si>
+    <t>ゴーストアーマー</t>
+  </si>
+  <si>
+    <t>ソード</t>
+  </si>
+  <si>
+    <t>アモン</t>
+  </si>
+  <si>
+    <t>ベリト</t>
+  </si>
+  <si>
+    <t>パイモン</t>
+  </si>
+  <si>
+    <t>アンドラス</t>
+  </si>
+  <si>
+    <t>ビフロンス</t>
+  </si>
+  <si>
+    <t>アイホート</t>
+  </si>
+  <si>
+    <t>ビヤーキー</t>
+  </si>
+  <si>
     <t>アンリマユ</t>
   </si>
   <si>
@@ -287,131 +387,19 @@
   </si>
   <si>
     <t>ボス</t>
-  </si>
-  <si>
-    <t>Jelslime</t>
-  </si>
-  <si>
-    <t>Cursed</t>
-  </si>
-  <si>
-    <t>Bee</t>
-  </si>
-  <si>
-    <t>Wolf</t>
-  </si>
-  <si>
-    <t>Crow</t>
-  </si>
-  <si>
-    <t>Nameless</t>
-  </si>
-  <si>
-    <t>Seacher</t>
-  </si>
-  <si>
-    <t>Shiled</t>
-  </si>
-  <si>
-    <t>Dryad</t>
-  </si>
-  <si>
-    <t>Squid</t>
-  </si>
-  <si>
-    <t>Creeper</t>
-  </si>
-  <si>
-    <t>Armor</t>
-  </si>
-  <si>
-    <t>Sword</t>
-  </si>
-  <si>
-    <t>Ammon</t>
-  </si>
-  <si>
-    <t>Berith</t>
-  </si>
-  <si>
-    <t>Paimon</t>
-  </si>
-  <si>
-    <t>Andras</t>
-  </si>
-  <si>
-    <t>Bifrons</t>
-  </si>
-  <si>
-    <t>ネレイドジェム</t>
-  </si>
-  <si>
-    <t>カースド</t>
-  </si>
-  <si>
-    <t>ビー</t>
-  </si>
-  <si>
-    <t>ウルフ</t>
-  </si>
-  <si>
-    <t>クロウ</t>
-  </si>
-  <si>
-    <t>ネームレス</t>
-  </si>
-  <si>
-    <t>サーチャー</t>
-  </si>
-  <si>
-    <t>シールド</t>
-  </si>
-  <si>
-    <t>ドライアド</t>
-  </si>
-  <si>
-    <t>スクイッド</t>
-  </si>
-  <si>
-    <t>クリーパー</t>
-  </si>
-  <si>
-    <t>ゴーストアーマー</t>
-  </si>
-  <si>
-    <t>ソード</t>
-  </si>
-  <si>
-    <t>アモン</t>
-  </si>
-  <si>
-    <t>ベリト</t>
-  </si>
-  <si>
-    <t>パイモン</t>
-  </si>
-  <si>
-    <t>アンドラス</t>
-  </si>
-  <si>
-    <t>ビフロンス</t>
-  </si>
-  <si>
-    <t>アイホート</t>
-  </si>
-  <si>
-    <t>ビヤーキー</t>
-  </si>
-  <si>
-    <t>Mov</t>
-    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -420,30 +408,352 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="6"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -451,9 +761,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -464,28 +1016,72 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
+    <cellStyle name="入力" xfId="2" builtinId="20"/>
+    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
+    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
+    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
+    <cellStyle name="通貨" xfId="6" builtinId="4"/>
+    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
+    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
+    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="良い" xfId="13" builtinId="26"/>
+    <cellStyle name="警告文" xfId="14" builtinId="11"/>
+    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
+    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
+    <cellStyle name="説明文" xfId="17" builtinId="53"/>
+    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
+    <cellStyle name="出力" xfId="19" builtinId="21"/>
+    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
+    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
+    <cellStyle name="計算" xfId="22" builtinId="22"/>
+    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
+    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
+    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
+    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
+    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
+    <cellStyle name="集計" xfId="28" builtinId="25"/>
+    <cellStyle name="悪い" xfId="29" builtinId="27"/>
+    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
+    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
+    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
+    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
+    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
+    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
+    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
+    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
+    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
+    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
+    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
+    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
+    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
+    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
+    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
+    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
+    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
+    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Skills"/>
@@ -522,7 +1118,7 @@
             <v>1</v>
           </cell>
           <cell r="B3" t="str">
-            <v>攻撃</v>
+            <v>はずす</v>
           </cell>
         </row>
         <row r="4">
@@ -887,559 +1483,559 @@
         </row>
         <row r="49">
           <cell r="A49">
-            <v>10010</v>
+            <v>6010</v>
           </cell>
           <cell r="B49" t="str">
-            <v>アンデッド</v>
+            <v>何もしない</v>
           </cell>
         </row>
         <row r="50">
           <cell r="A50">
-            <v>10020</v>
+            <v>10010</v>
           </cell>
           <cell r="B50" t="str">
-            <v>エアリアル</v>
+            <v>アンデッド</v>
           </cell>
         </row>
         <row r="51">
           <cell r="A51">
-            <v>10030</v>
+            <v>10020</v>
           </cell>
           <cell r="B51" t="str">
-            <v>悪魔</v>
+            <v>エアリアル</v>
           </cell>
         </row>
         <row r="52">
           <cell r="A52">
-            <v>10040</v>
+            <v>10030</v>
           </cell>
           <cell r="B52" t="str">
-            <v>クリーチャー</v>
+            <v>悪魔</v>
           </cell>
         </row>
         <row r="53">
           <cell r="A53">
-            <v>10050</v>
+            <v>10040</v>
           </cell>
           <cell r="B53" t="str">
-            <v>野生の記憶</v>
+            <v>クリーチャー</v>
           </cell>
         </row>
         <row r="54">
           <cell r="A54">
-            <v>10060</v>
+            <v>10050</v>
           </cell>
           <cell r="B54" t="str">
-            <v>変異生物</v>
+            <v>野生の記憶</v>
           </cell>
         </row>
         <row r="55">
           <cell r="A55">
-            <v>11010</v>
+            <v>10060</v>
           </cell>
           <cell r="B55" t="str">
-            <v>ウルフソウル</v>
+            <v>変異生物</v>
           </cell>
         </row>
         <row r="56">
           <cell r="A56">
-            <v>11020</v>
+            <v>11010</v>
           </cell>
           <cell r="B56" t="str">
-            <v>プリディカメント</v>
+            <v>ウルフソウル</v>
           </cell>
         </row>
         <row r="57">
           <cell r="A57">
-            <v>11030</v>
+            <v>11020</v>
           </cell>
           <cell r="B57" t="str">
-            <v>アサルトシフト</v>
+            <v>プリディカメント</v>
           </cell>
         </row>
         <row r="58">
           <cell r="A58">
-            <v>11040</v>
+            <v>11030</v>
           </cell>
           <cell r="B58" t="str">
-            <v>アクティブギフト</v>
+            <v>アサルトシフト</v>
           </cell>
         </row>
         <row r="59">
           <cell r="A59">
-            <v>11050</v>
+            <v>11040</v>
           </cell>
           <cell r="B59" t="str">
-            <v>イグナイテッド</v>
+            <v>アクティブギフト</v>
           </cell>
         </row>
         <row r="60">
           <cell r="A60">
-            <v>11060</v>
+            <v>11050</v>
           </cell>
           <cell r="B60" t="str">
-            <v>ライジングファイア</v>
+            <v>イグナイテッド</v>
           </cell>
         </row>
         <row r="61">
           <cell r="A61">
-            <v>11070</v>
+            <v>11060</v>
           </cell>
           <cell r="B61" t="str">
-            <v>ルージュバック</v>
+            <v>ライジングファイア</v>
           </cell>
         </row>
         <row r="62">
           <cell r="A62">
-            <v>11080</v>
+            <v>11070</v>
           </cell>
           <cell r="B62" t="str">
-            <v>パワーエール</v>
+            <v>ルージュバック</v>
           </cell>
         </row>
         <row r="63">
           <cell r="A63">
-            <v>11090</v>
+            <v>11080</v>
           </cell>
           <cell r="B63" t="str">
-            <v>スレイプニル</v>
+            <v>パワーエール</v>
           </cell>
         </row>
         <row r="64">
           <cell r="A64">
-            <v>12010</v>
+            <v>11090</v>
           </cell>
           <cell r="B64" t="str">
-            <v>エクステンション</v>
+            <v>スレイプニル</v>
           </cell>
         </row>
         <row r="65">
           <cell r="A65">
-            <v>12020</v>
+            <v>12010</v>
           </cell>
           <cell r="B65" t="str">
-            <v>ヘブンリーラック</v>
+            <v>エクステンション</v>
           </cell>
         </row>
         <row r="66">
           <cell r="A66">
-            <v>12030</v>
+            <v>12020</v>
           </cell>
           <cell r="B66" t="str">
-            <v>スウィフトカレント</v>
+            <v>ヘブンリーラック</v>
           </cell>
         </row>
         <row r="67">
           <cell r="A67">
-            <v>12040</v>
+            <v>12030</v>
           </cell>
           <cell r="B67" t="str">
-            <v>イヴェイドオール</v>
+            <v>スウィフトカレント</v>
           </cell>
         </row>
         <row r="68">
           <cell r="A68">
-            <v>12050</v>
+            <v>12040</v>
           </cell>
           <cell r="B68" t="str">
-            <v>クイックムーブ</v>
+            <v>イヴェイドオール</v>
           </cell>
         </row>
         <row r="69">
           <cell r="A69">
-            <v>12060</v>
+            <v>12050</v>
           </cell>
           <cell r="B69" t="str">
-            <v>チェイスマジック</v>
+            <v>クイックムーブ</v>
           </cell>
         </row>
         <row r="70">
           <cell r="A70">
-            <v>12070</v>
+            <v>12060</v>
           </cell>
           <cell r="B70" t="str">
-            <v>ソーサリーコネクト</v>
+            <v>チェイスマジック</v>
           </cell>
         </row>
         <row r="71">
           <cell r="A71">
-            <v>12080</v>
+            <v>12070</v>
           </cell>
           <cell r="B71" t="str">
-            <v>ウィンドライズ</v>
+            <v>ソーサリーコネクト</v>
           </cell>
         </row>
         <row r="72">
           <cell r="A72">
-            <v>12090</v>
+            <v>12080</v>
           </cell>
           <cell r="B72" t="str">
-            <v>アウトオブオーダー</v>
+            <v>ウィンドライズ</v>
           </cell>
         </row>
         <row r="73">
           <cell r="A73">
-            <v>13010</v>
+            <v>12090</v>
           </cell>
           <cell r="B73" t="str">
-            <v>アーマーコード</v>
+            <v>アウトオブオーダー</v>
           </cell>
         </row>
         <row r="74">
           <cell r="A74">
-            <v>13020</v>
+            <v>13010</v>
           </cell>
           <cell r="B74" t="str">
-            <v>クイックバリア</v>
+            <v>アーマーコード</v>
           </cell>
         </row>
         <row r="75">
           <cell r="A75">
-            <v>13030</v>
+            <v>13020</v>
           </cell>
           <cell r="B75" t="str">
-            <v>クイックキュア</v>
+            <v>クイックバリア</v>
           </cell>
         </row>
         <row r="76">
           <cell r="A76">
-            <v>13040</v>
+            <v>13030</v>
           </cell>
           <cell r="B76" t="str">
-            <v>セルフシールド</v>
+            <v>クイックキュア</v>
           </cell>
         </row>
         <row r="77">
           <cell r="A77">
-            <v>13050</v>
+            <v>13040</v>
           </cell>
           <cell r="B77" t="str">
-            <v>パッシブジャミング</v>
+            <v>セルフシールド</v>
           </cell>
         </row>
         <row r="78">
           <cell r="A78">
-            <v>13060</v>
+            <v>13050</v>
           </cell>
           <cell r="B78" t="str">
-            <v>サプライカバー</v>
+            <v>パッシブジャミング</v>
           </cell>
         </row>
         <row r="79">
           <cell r="A79">
-            <v>13070</v>
+            <v>13060</v>
           </cell>
           <cell r="B79" t="str">
-            <v>アシッドラッシュ</v>
+            <v>サプライカバー</v>
           </cell>
         </row>
         <row r="80">
           <cell r="A80">
-            <v>13080</v>
+            <v>13070</v>
           </cell>
           <cell r="B80" t="str">
-            <v>ライフスティール</v>
+            <v>アシッドラッシュ</v>
           </cell>
         </row>
         <row r="81">
           <cell r="A81">
-            <v>13090</v>
+            <v>13080</v>
           </cell>
           <cell r="B81" t="str">
-            <v>アイスセイバー</v>
+            <v>ライフスティール</v>
           </cell>
         </row>
         <row r="82">
           <cell r="A82">
-            <v>14010</v>
+            <v>13090</v>
           </cell>
           <cell r="B82" t="str">
-            <v>ディバインシールド</v>
+            <v>アイスセイバー</v>
           </cell>
         </row>
         <row r="83">
           <cell r="A83">
-            <v>14020</v>
+            <v>14010</v>
           </cell>
           <cell r="B83" t="str">
-            <v>ライフディバイド</v>
+            <v>ディバインシールド</v>
           </cell>
         </row>
         <row r="84">
           <cell r="A84">
-            <v>14030</v>
+            <v>14020</v>
           </cell>
           <cell r="B84" t="str">
-            <v>エイミングスコープ</v>
+            <v>ライフディバイド</v>
           </cell>
         </row>
         <row r="85">
           <cell r="A85">
-            <v>14040</v>
+            <v>14030</v>
           </cell>
           <cell r="B85" t="str">
-            <v>リジェネレーション</v>
+            <v>エイミングスコープ</v>
           </cell>
         </row>
         <row r="86">
           <cell r="A86">
-            <v>14050</v>
+            <v>14040</v>
           </cell>
           <cell r="B86" t="str">
-            <v>ホープフルアイリス</v>
+            <v>リジェネレーション</v>
           </cell>
         </row>
         <row r="87">
           <cell r="A87">
-            <v>14060</v>
+            <v>14050</v>
           </cell>
           <cell r="B87" t="str">
-            <v>パッシブサプライ</v>
+            <v>ホープフルアイリス</v>
           </cell>
         </row>
         <row r="88">
           <cell r="A88">
-            <v>14070</v>
+            <v>14060</v>
           </cell>
           <cell r="B88" t="str">
-            <v>ホーミングクルセイド</v>
+            <v>パッシブサプライ</v>
           </cell>
         </row>
         <row r="89">
           <cell r="A89">
-            <v>14080</v>
+            <v>14070</v>
           </cell>
           <cell r="B89" t="str">
-            <v>クイックヒール</v>
+            <v>ホーミングクルセイド</v>
           </cell>
         </row>
         <row r="90">
           <cell r="A90">
-            <v>14090</v>
+            <v>14080</v>
           </cell>
           <cell r="B90" t="str">
-            <v>リレイズ</v>
+            <v>クイックヒール</v>
           </cell>
         </row>
         <row r="91">
           <cell r="A91">
-            <v>15010</v>
+            <v>14090</v>
           </cell>
           <cell r="B91" t="str">
-            <v>イーグルアイ</v>
+            <v>リレイズ</v>
           </cell>
         </row>
         <row r="92">
           <cell r="A92">
-            <v>15020</v>
+            <v>15010</v>
           </cell>
           <cell r="B92" t="str">
-            <v>ネヴァーエンド</v>
+            <v>イーグルアイ</v>
           </cell>
         </row>
         <row r="93">
           <cell r="A93">
-            <v>15030</v>
+            <v>15020</v>
           </cell>
           <cell r="B93" t="str">
-            <v>グレイブアクト</v>
+            <v>ネヴァーエンド</v>
           </cell>
         </row>
         <row r="94">
           <cell r="A94">
-            <v>15040</v>
+            <v>15030</v>
           </cell>
           <cell r="B94" t="str">
-            <v>スカルグラッジ</v>
+            <v>グレイブアクト</v>
           </cell>
         </row>
         <row r="95">
           <cell r="A95">
-            <v>15050</v>
+            <v>15040</v>
           </cell>
           <cell r="B95" t="str">
-            <v>ネガティブドレイン</v>
+            <v>スカルグラッジ</v>
           </cell>
         </row>
         <row r="96">
           <cell r="A96">
-            <v>15060</v>
+            <v>15050</v>
           </cell>
           <cell r="B96" t="str">
-            <v>アンデッドペイン</v>
+            <v>ネガティブドレイン</v>
           </cell>
         </row>
         <row r="97">
           <cell r="A97">
-            <v>15070</v>
+            <v>15060</v>
           </cell>
           <cell r="B97" t="str">
-            <v>ジャックポッド</v>
+            <v>アンデッドペイン</v>
           </cell>
         </row>
         <row r="98">
           <cell r="A98">
-            <v>15080</v>
+            <v>15070</v>
           </cell>
           <cell r="B98" t="str">
-            <v>ヒールハント</v>
+            <v>ジャックポッド</v>
           </cell>
         </row>
         <row r="99">
           <cell r="A99">
-            <v>15090</v>
+            <v>15080</v>
           </cell>
           <cell r="B99" t="str">
-            <v>クイックカース</v>
+            <v>ヒールハント</v>
           </cell>
         </row>
         <row r="100">
           <cell r="A100">
-            <v>20010</v>
+            <v>15090</v>
           </cell>
           <cell r="B100" t="str">
-            <v>ウェイトユニゾン</v>
+            <v>クイックカース</v>
           </cell>
         </row>
         <row r="101">
           <cell r="A101">
-            <v>100110</v>
+            <v>20010</v>
           </cell>
           <cell r="B101" t="str">
-            <v>ソーイングアームド</v>
+            <v>ウェイトユニゾン</v>
           </cell>
         </row>
         <row r="102">
           <cell r="A102">
-            <v>100120</v>
+            <v>100110</v>
           </cell>
           <cell r="B102" t="str">
-            <v>エターナルロンド</v>
+            <v>ソーイングアームド</v>
           </cell>
         </row>
         <row r="103">
           <cell r="A103">
-            <v>100210</v>
+            <v>100120</v>
           </cell>
           <cell r="B103" t="str">
-            <v>アブソリュートパリィ</v>
+            <v>エターナルロンド</v>
           </cell>
         </row>
         <row r="104">
           <cell r="A104">
-            <v>100220</v>
+            <v>100210</v>
           </cell>
           <cell r="B104" t="str">
-            <v>レヴェリー</v>
+            <v>アブソリュートパリィ</v>
           </cell>
         </row>
         <row r="105">
           <cell r="A105">
-            <v>100310</v>
+            <v>100220</v>
           </cell>
           <cell r="B105" t="str">
-            <v>セイクリッドバリア</v>
+            <v>レヴェリー</v>
           </cell>
         </row>
         <row r="106">
           <cell r="A106">
-            <v>100320</v>
+            <v>100310</v>
           </cell>
           <cell r="B106" t="str">
-            <v>リベンジニードル</v>
+            <v>セイクリッドバリア</v>
           </cell>
         </row>
         <row r="107">
           <cell r="A107">
-            <v>100410</v>
+            <v>100320</v>
           </cell>
           <cell r="B107" t="str">
-            <v>アバンデンス</v>
+            <v>リベンジニードル</v>
           </cell>
         </row>
         <row r="108">
           <cell r="A108">
-            <v>100420</v>
+            <v>100410</v>
           </cell>
           <cell r="B108" t="str">
-            <v>ハーヴェスト</v>
+            <v>アバンデンス</v>
           </cell>
         </row>
         <row r="109">
           <cell r="A109">
-            <v>100510</v>
+            <v>100420</v>
           </cell>
           <cell r="B109" t="str">
-            <v>カースドブレイク</v>
+            <v>ハーヴェスト</v>
           </cell>
         </row>
         <row r="110">
           <cell r="A110">
-            <v>100520</v>
+            <v>100510</v>
           </cell>
           <cell r="B110" t="str">
-            <v>ムーンライトレイ</v>
+            <v>カースドブレイク</v>
           </cell>
         </row>
         <row r="111">
           <cell r="A111">
-            <v>100610</v>
+            <v>100520</v>
           </cell>
           <cell r="B111" t="str">
-            <v>サンフレイム</v>
+            <v>ムーンライトレイ</v>
           </cell>
         </row>
         <row r="112">
           <cell r="A112">
-            <v>100620</v>
+            <v>100610</v>
           </cell>
           <cell r="B112" t="str">
-            <v>フレイムタン</v>
+            <v>サンフレイム</v>
           </cell>
         </row>
         <row r="113">
           <cell r="A113">
-            <v>100710</v>
+            <v>100620</v>
           </cell>
           <cell r="B113" t="str">
-            <v>ライズザフラッグ</v>
+            <v>フレイムタン</v>
           </cell>
         </row>
         <row r="114">
           <cell r="A114">
-            <v>100720</v>
+            <v>100710</v>
           </cell>
           <cell r="B114" t="str">
-            <v>オーバーリミット</v>
+            <v>ライズザフラッグ</v>
           </cell>
         </row>
         <row r="115">
           <cell r="A115">
-            <v>100810</v>
+            <v>100720</v>
           </cell>
           <cell r="B115" t="str">
-            <v>テンパランス</v>
+            <v>オーバーリミット</v>
           </cell>
         </row>
         <row r="116">
           <cell r="A116">
-            <v>100820</v>
+            <v>100810</v>
           </cell>
           <cell r="B116" t="str">
-            <v>シエルクルセイダー</v>
+            <v>テンパランス</v>
           </cell>
         </row>
         <row r="117">
           <cell r="A117">
-            <v>100910</v>
+            <v>100820</v>
           </cell>
           <cell r="B117" t="str">
-            <v>バーニングカウンター</v>
+            <v>シエルクルセイダー</v>
           </cell>
         </row>
         <row r="118">
           <cell r="A118">
-            <v>100911</v>
+            <v>100910</v>
           </cell>
           <cell r="B118" t="str">
             <v>バーニングカウンター</v>
@@ -1447,15 +2043,15 @@
         </row>
         <row r="119">
           <cell r="A119">
-            <v>100920</v>
+            <v>100911</v>
           </cell>
           <cell r="B119" t="str">
-            <v>プロミネンス</v>
+            <v>バーニングカウンター</v>
           </cell>
         </row>
         <row r="120">
           <cell r="A120">
-            <v>100921</v>
+            <v>100920</v>
           </cell>
           <cell r="B120" t="str">
             <v>プロミネンス</v>
@@ -1463,95 +2059,95 @@
         </row>
         <row r="121">
           <cell r="A121">
-            <v>101010</v>
+            <v>100921</v>
           </cell>
           <cell r="B121" t="str">
-            <v>エウロス</v>
+            <v>プロミネンス</v>
           </cell>
         </row>
         <row r="122">
           <cell r="A122">
-            <v>101020</v>
+            <v>101010</v>
           </cell>
           <cell r="B122" t="str">
-            <v>ボレアス</v>
+            <v>エウロス</v>
           </cell>
         </row>
         <row r="123">
           <cell r="A123">
-            <v>101110</v>
+            <v>101020</v>
           </cell>
           <cell r="B123" t="str">
-            <v>アバランシュ</v>
+            <v>ボレアス</v>
           </cell>
         </row>
         <row r="124">
           <cell r="A124">
-            <v>101120</v>
+            <v>101110</v>
           </cell>
           <cell r="B124" t="str">
-            <v>ブリザードコフィン</v>
+            <v>アバランシュ</v>
           </cell>
         </row>
         <row r="125">
           <cell r="A125">
-            <v>200210</v>
+            <v>101120</v>
           </cell>
           <cell r="B125" t="str">
-            <v>マイトレインフォース</v>
+            <v>ブリザードコフィン</v>
           </cell>
         </row>
         <row r="126">
           <cell r="A126">
-            <v>200220</v>
+            <v>200210</v>
           </cell>
           <cell r="B126" t="str">
-            <v>カタストロフィ</v>
+            <v>マイトレインフォース</v>
           </cell>
         </row>
         <row r="127">
           <cell r="A127">
-            <v>200230</v>
+            <v>200220</v>
           </cell>
           <cell r="B127" t="str">
-            <v>悪魔(ベリト)</v>
+            <v>カタストロフィ</v>
           </cell>
         </row>
         <row r="128">
           <cell r="A128">
-            <v>200310</v>
+            <v>200230</v>
           </cell>
           <cell r="B128" t="str">
-            <v>プルガシオン</v>
+            <v>悪魔(ベリト)</v>
           </cell>
         </row>
         <row r="129">
           <cell r="A129">
-            <v>200320</v>
+            <v>200310</v>
           </cell>
           <cell r="B129" t="str">
-            <v>プリエステス</v>
+            <v>プルガシオン</v>
           </cell>
         </row>
         <row r="130">
           <cell r="A130">
-            <v>200330</v>
+            <v>200320</v>
           </cell>
           <cell r="B130" t="str">
-            <v>悪魔(パイモン)</v>
+            <v>プリエステス</v>
           </cell>
         </row>
         <row r="131">
           <cell r="A131">
-            <v>200410</v>
+            <v>200330</v>
           </cell>
           <cell r="B131" t="str">
-            <v>コウソクテンショウ</v>
+            <v>悪魔(パイモン)</v>
           </cell>
         </row>
         <row r="132">
           <cell r="A132">
-            <v>200411</v>
+            <v>200410</v>
           </cell>
           <cell r="B132" t="str">
             <v>コウソクテンショウ</v>
@@ -1559,905 +2155,913 @@
         </row>
         <row r="133">
           <cell r="A133">
-            <v>200420</v>
+            <v>200411</v>
           </cell>
           <cell r="B133" t="str">
-            <v>アンチバフ</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="134">
           <cell r="A134">
-            <v>200430</v>
+            <v>200420</v>
           </cell>
           <cell r="B134" t="str">
-            <v>悪魔(アンドラス)</v>
+            <v>アンチバフ</v>
           </cell>
         </row>
         <row r="135">
           <cell r="A135">
-            <v>200510</v>
+            <v>200430</v>
           </cell>
           <cell r="B135" t="str">
-            <v>カウントダウン</v>
+            <v>悪魔(アンドラス)</v>
           </cell>
         </row>
         <row r="136">
           <cell r="A136">
-            <v>200520</v>
+            <v>200510</v>
           </cell>
           <cell r="B136" t="str">
-            <v>グラウンドゼロ</v>
+            <v>カウントダウン</v>
           </cell>
         </row>
         <row r="137">
           <cell r="A137">
-            <v>200530</v>
+            <v>200520</v>
           </cell>
           <cell r="B137" t="str">
-            <v>悪魔(ビフロンス)</v>
+            <v>グラウンドゼロ</v>
           </cell>
         </row>
         <row r="138">
           <cell r="A138">
-            <v>201010</v>
+            <v>200530</v>
           </cell>
           <cell r="B138" t="str">
-            <v>カオスペイン</v>
+            <v>悪魔(ビフロンス)</v>
           </cell>
         </row>
         <row r="139">
           <cell r="A139">
-            <v>201020</v>
+            <v>201010</v>
           </cell>
           <cell r="B139" t="str">
-            <v>フォールンワン</v>
+            <v>カオスペイン</v>
           </cell>
         </row>
         <row r="140">
           <cell r="A140">
-            <v>201030</v>
+            <v>201020</v>
           </cell>
           <cell r="B140" t="str">
-            <v>アンリマユ</v>
+            <v>フォールンワン</v>
           </cell>
         </row>
         <row r="141">
           <cell r="A141">
-            <v>300010</v>
+            <v>201030</v>
           </cell>
           <cell r="B141" t="str">
-            <v>ライフブースト</v>
+            <v>アンリマユ</v>
           </cell>
         </row>
         <row r="142">
           <cell r="A142">
-            <v>300020</v>
+            <v>300010</v>
           </cell>
           <cell r="B142" t="str">
-            <v>スピリットチャージ</v>
+            <v>ライフブースト</v>
           </cell>
         </row>
         <row r="143">
           <cell r="A143">
-            <v>300030</v>
+            <v>300020</v>
           </cell>
           <cell r="B143" t="str">
-            <v>フォースライズ</v>
+            <v>スピリットチャージ</v>
           </cell>
         </row>
         <row r="144">
           <cell r="A144">
-            <v>300040</v>
+            <v>300030</v>
           </cell>
           <cell r="B144" t="str">
-            <v>ディフェンスオーラ</v>
+            <v>フォースライズ</v>
           </cell>
         </row>
         <row r="145">
           <cell r="A145">
-            <v>300050</v>
+            <v>300040</v>
           </cell>
           <cell r="B145" t="str">
-            <v>ラピッドムーブ</v>
+            <v>ディフェンスオーラ</v>
           </cell>
         </row>
         <row r="146">
           <cell r="A146">
-            <v>300130</v>
+            <v>300050</v>
           </cell>
           <cell r="B146" t="str">
-            <v>アタックブレイク</v>
+            <v>ラピッドムーブ</v>
           </cell>
         </row>
         <row r="147">
           <cell r="A147">
-            <v>300140</v>
+            <v>300130</v>
           </cell>
           <cell r="B147" t="str">
-            <v>シールドバニッシュ</v>
+            <v>アタックブレイク</v>
           </cell>
         </row>
         <row r="148">
           <cell r="A148">
-            <v>300210</v>
+            <v>300140</v>
           </cell>
           <cell r="B148" t="str">
-            <v>エーテルリチャージ</v>
+            <v>シールドバニッシュ</v>
           </cell>
         </row>
         <row r="149">
           <cell r="A149">
-            <v>300220</v>
+            <v>300210</v>
           </cell>
           <cell r="B149" t="str">
-            <v>リカバリーエンハンス</v>
+            <v>エーテルリチャージ</v>
           </cell>
         </row>
         <row r="150">
           <cell r="A150">
-            <v>300230</v>
+            <v>300220</v>
           </cell>
           <cell r="B150" t="str">
-            <v>ヴェンジェンス</v>
+            <v>リカバリーエンハンス</v>
           </cell>
         </row>
         <row r="151">
           <cell r="A151">
-            <v>301010</v>
+            <v>300230</v>
           </cell>
           <cell r="B151" t="str">
-            <v>ディケイドリセット</v>
+            <v>ヴェンジェンス</v>
           </cell>
         </row>
         <row r="152">
           <cell r="A152">
-            <v>301020</v>
+            <v>301010</v>
           </cell>
           <cell r="B152" t="str">
-            <v>ウォーリアーブラッド</v>
+            <v>ディケイドリセット</v>
           </cell>
         </row>
         <row r="153">
           <cell r="A153">
-            <v>301030</v>
+            <v>301020</v>
           </cell>
           <cell r="B153" t="str">
-            <v>トライアングルガード</v>
+            <v>ウォーリアーブラッド</v>
           </cell>
         </row>
         <row r="154">
           <cell r="A154">
-            <v>301040</v>
+            <v>301030</v>
           </cell>
           <cell r="B154" t="str">
-            <v>セーフティバリア</v>
+            <v>トライアングルガード</v>
           </cell>
         </row>
         <row r="155">
           <cell r="A155">
-            <v>301050</v>
+            <v>301040</v>
           </cell>
           <cell r="B155" t="str">
-            <v>ヒロインズハイ</v>
+            <v>セーフティバリア</v>
           </cell>
         </row>
         <row r="156">
           <cell r="A156">
-            <v>301060</v>
+            <v>301050</v>
           </cell>
           <cell r="B156" t="str">
-            <v>セカンドステージ</v>
+            <v>ヒロインズハイ</v>
           </cell>
         </row>
         <row r="157">
           <cell r="A157">
-            <v>301070</v>
+            <v>301060</v>
           </cell>
           <cell r="B157" t="str">
-            <v>ハイヒットポイント</v>
+            <v>セカンドステージ</v>
           </cell>
         </row>
         <row r="158">
           <cell r="A158">
-            <v>301080</v>
+            <v>301070</v>
           </cell>
           <cell r="B158" t="str">
-            <v>セプタブラスト</v>
+            <v>ハイヒットポイント</v>
           </cell>
         </row>
         <row r="159">
           <cell r="A159">
-            <v>301090</v>
+            <v>301080</v>
           </cell>
           <cell r="B159" t="str">
-            <v>イニシャルブロッカー</v>
+            <v>セプタブラスト</v>
           </cell>
         </row>
         <row r="160">
           <cell r="A160">
-            <v>301100</v>
+            <v>301090</v>
           </cell>
           <cell r="B160" t="str">
-            <v>ファーストテイク</v>
+            <v>イニシャルブロッカー</v>
           </cell>
         </row>
         <row r="161">
           <cell r="A161">
-            <v>401010</v>
+            <v>301100</v>
           </cell>
           <cell r="B161" t="str">
-            <v>ファイアボール+</v>
+            <v>ファーストテイク</v>
           </cell>
         </row>
         <row r="162">
           <cell r="A162">
-            <v>401020</v>
+            <v>401010</v>
           </cell>
           <cell r="B162" t="str">
-            <v>バーンストーム+</v>
+            <v>ファイアボール+</v>
           </cell>
         </row>
         <row r="163">
           <cell r="A163">
-            <v>401030</v>
+            <v>401020</v>
           </cell>
           <cell r="B163" t="str">
-            <v>ヒートスタンプ+</v>
+            <v>バーンストーム+</v>
           </cell>
         </row>
         <row r="164">
           <cell r="A164">
-            <v>401040</v>
+            <v>401030</v>
           </cell>
           <cell r="B164" t="str">
-            <v>ソードアダプト+</v>
+            <v>ヒートスタンプ+</v>
           </cell>
         </row>
         <row r="165">
           <cell r="A165">
-            <v>401050</v>
+            <v>401040</v>
           </cell>
           <cell r="B165" t="str">
-            <v>フレイムレイン+</v>
+            <v>ソードアダプト+</v>
           </cell>
         </row>
         <row r="166">
           <cell r="A166">
-            <v>401060</v>
+            <v>401050</v>
           </cell>
           <cell r="B166" t="str">
-            <v>イクスティンクション+</v>
+            <v>フレイムレイン+</v>
           </cell>
         </row>
         <row r="167">
           <cell r="A167">
-            <v>401070</v>
+            <v>401060</v>
           </cell>
           <cell r="B167" t="str">
-            <v>バーニングソウル+</v>
+            <v>イクスティンクション+</v>
           </cell>
         </row>
         <row r="168">
           <cell r="A168">
-            <v>401080</v>
+            <v>401070</v>
           </cell>
           <cell r="B168" t="str">
-            <v>レイジングバウンサー+</v>
+            <v>バーニングソウル+</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169">
-            <v>402010</v>
+            <v>401080</v>
           </cell>
           <cell r="B169" t="str">
-            <v>ディスチャージ+</v>
+            <v>レイジングバウンサー+</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170">
-            <v>402020</v>
+            <v>402010</v>
           </cell>
           <cell r="B170" t="str">
-            <v>イベイドコード+</v>
+            <v>ディスチャージ+</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171">
-            <v>402030</v>
+            <v>402020</v>
           </cell>
           <cell r="B171" t="str">
-            <v>ショックインパルス+</v>
+            <v>イベイドコード+</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172">
-            <v>402040</v>
+            <v>402030</v>
           </cell>
           <cell r="B172" t="str">
-            <v>トラストチェイン+</v>
+            <v>ショックインパルス+</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173">
-            <v>402050</v>
+            <v>402040</v>
           </cell>
           <cell r="B173" t="str">
-            <v>スペルバニシング+</v>
+            <v>トラストチェイン+</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174">
-            <v>402060</v>
+            <v>402050</v>
           </cell>
           <cell r="B174" t="str">
-            <v>アーテニーストライク+</v>
+            <v>スペルバニシング+</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175">
-            <v>402070</v>
+            <v>402060</v>
           </cell>
           <cell r="B175" t="str">
-            <v>コンセントレイト+</v>
+            <v>アーテニーストライク+</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176">
-            <v>402080</v>
+            <v>402070</v>
           </cell>
           <cell r="B176" t="str">
-            <v>ディレイマジック+</v>
+            <v>コンセントレイト+</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177">
-            <v>403010</v>
+            <v>402080</v>
           </cell>
           <cell r="B177" t="str">
-            <v>アイスブレイド+</v>
+            <v>ディレイマジック+</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178">
-            <v>403020</v>
+            <v>403010</v>
           </cell>
           <cell r="B178" t="str">
-            <v>カウンターオーラ+</v>
+            <v>アイスブレイド+</v>
           </cell>
         </row>
         <row r="179">
           <cell r="A179">
-            <v>403030</v>
+            <v>403020</v>
           </cell>
           <cell r="B179" t="str">
-            <v>ラインプロテクト+</v>
+            <v>カウンターオーラ+</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180">
-            <v>403040</v>
+            <v>403030</v>
           </cell>
           <cell r="B180" t="str">
-            <v>エスコートソール+</v>
+            <v>ラインプロテクト+</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181">
-            <v>403050</v>
+            <v>403040</v>
           </cell>
           <cell r="B181" t="str">
-            <v>ディープフリーズ+</v>
+            <v>エスコートソール+</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182">
-            <v>403060</v>
+            <v>403050</v>
           </cell>
           <cell r="B182" t="str">
-            <v>バブルブロウ+</v>
+            <v>ディープフリーズ+</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183">
-            <v>403070</v>
+            <v>403060</v>
           </cell>
           <cell r="B183" t="str">
-            <v>アクアミラージュ+</v>
+            <v>バブルブロウ+</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184">
-            <v>403080</v>
+            <v>403070</v>
           </cell>
           <cell r="B184" t="str">
-            <v>フロストシールド+</v>
+            <v>アクアミラージュ+</v>
           </cell>
         </row>
         <row r="185">
           <cell r="A185">
-            <v>404010</v>
+            <v>403080</v>
           </cell>
           <cell r="B185" t="str">
-            <v>セイントレーザー+</v>
+            <v>フロストシールド+</v>
           </cell>
         </row>
         <row r="186">
           <cell r="A186">
-            <v>404020</v>
+            <v>404010</v>
           </cell>
           <cell r="B186" t="str">
-            <v>ペネトレイト+</v>
+            <v>セイントレーザー+</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187">
-            <v>404030</v>
+            <v>404020</v>
           </cell>
           <cell r="B187" t="str">
-            <v>ヒーリング+</v>
+            <v>ペネトレイト+</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188">
-            <v>404040</v>
+            <v>404030</v>
           </cell>
           <cell r="B188" t="str">
-            <v>リザイアフォトン+</v>
+            <v>ヒーリング+</v>
           </cell>
         </row>
         <row r="189">
           <cell r="A189">
-            <v>404050</v>
+            <v>404040</v>
           </cell>
           <cell r="B189" t="str">
-            <v>べネディクション+</v>
+            <v>リザイアフォトン+</v>
           </cell>
         </row>
         <row r="190">
           <cell r="A190">
-            <v>404060</v>
+            <v>404050</v>
           </cell>
           <cell r="B190" t="str">
-            <v>ホーリーグレイス+</v>
+            <v>べネディクション+</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191">
-            <v>404070</v>
+            <v>404060</v>
           </cell>
           <cell r="B191" t="str">
-            <v>キュアエール+</v>
+            <v>ホーリーグレイス+</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192">
-            <v>404080</v>
+            <v>404070</v>
           </cell>
           <cell r="B192" t="str">
-            <v>ラインバリア+</v>
+            <v>キュアエール+</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193">
-            <v>405010</v>
+            <v>404080</v>
           </cell>
           <cell r="B193" t="str">
-            <v>ダークプリズン+</v>
+            <v>ラインバリア+</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194">
-            <v>405020</v>
+            <v>405010</v>
           </cell>
           <cell r="B194" t="str">
-            <v>ユーサネイジア+</v>
+            <v>ダークプリズン+</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195">
-            <v>405030</v>
+            <v>405020</v>
           </cell>
           <cell r="B195" t="str">
-            <v>ドレインヒール+</v>
+            <v>ユーサネイジア+</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196">
-            <v>405040</v>
+            <v>405030</v>
           </cell>
           <cell r="B196" t="str">
-            <v>アビサルデスペア+</v>
+            <v>ドレインヒール+</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197">
-            <v>405050</v>
+            <v>405040</v>
           </cell>
           <cell r="B197" t="str">
-            <v>ディプラヴィティ+</v>
+            <v>アビサルデスペア+</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198">
-            <v>405060</v>
+            <v>405050</v>
           </cell>
           <cell r="B198" t="str">
-            <v>ダークネス+</v>
+            <v>ディプラヴィティ+</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199">
-            <v>405070</v>
+            <v>405060</v>
           </cell>
           <cell r="B199" t="str">
-            <v>シェイディークラウド+</v>
+            <v>ダークネス+</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200">
-            <v>405080</v>
+            <v>405070</v>
           </cell>
           <cell r="B200" t="str">
-            <v>ポイズンブロウ+</v>
+            <v>シェイディークラウド+</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201">
-            <v>411010</v>
+            <v>405080</v>
           </cell>
           <cell r="B201" t="str">
-            <v>ウルフソウル+</v>
+            <v>ポイズンブロウ+</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202">
-            <v>411020</v>
+            <v>411010</v>
           </cell>
           <cell r="B202" t="str">
-            <v>プリディカメント+</v>
+            <v>ウルフソウル+</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203">
-            <v>411030</v>
+            <v>411020</v>
           </cell>
           <cell r="B203" t="str">
-            <v>アサルトシフト+</v>
+            <v>プリディカメント+</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204">
-            <v>411040</v>
+            <v>411030</v>
           </cell>
           <cell r="B204" t="str">
-            <v>アクティブギフト+</v>
+            <v>アサルトシフト+</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205">
-            <v>411050</v>
+            <v>411040</v>
           </cell>
           <cell r="B205" t="str">
-            <v>イグナイテッド+</v>
+            <v>アクティブギフト+</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206">
-            <v>411060</v>
+            <v>411050</v>
           </cell>
           <cell r="B206" t="str">
-            <v>ライジングファイア+</v>
+            <v>イグナイテッド+</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207">
-            <v>411070</v>
+            <v>411060</v>
           </cell>
           <cell r="B207" t="str">
-            <v>ルージュバック+</v>
+            <v>ライジングファイア+</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208">
-            <v>411080</v>
+            <v>411070</v>
           </cell>
           <cell r="B208" t="str">
-            <v>パワーエール+</v>
+            <v>ルージュバック+</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209">
-            <v>411090</v>
+            <v>411080</v>
           </cell>
           <cell r="B209" t="str">
-            <v>スレイプニル+</v>
+            <v>パワーエール+</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210">
-            <v>412010</v>
+            <v>411090</v>
           </cell>
           <cell r="B210" t="str">
-            <v>エクステンション+</v>
+            <v>スレイプニル+</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211">
-            <v>412020</v>
+            <v>412010</v>
           </cell>
           <cell r="B211" t="str">
-            <v>ヘブンリーラック+</v>
+            <v>エクステンション+</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212">
-            <v>412030</v>
+            <v>412020</v>
           </cell>
           <cell r="B212" t="str">
-            <v>スウィフトカレント+</v>
+            <v>ヘブンリーラック+</v>
           </cell>
         </row>
         <row r="213">
           <cell r="A213">
-            <v>412040</v>
+            <v>412030</v>
           </cell>
           <cell r="B213" t="str">
-            <v>イヴェイドオール+</v>
+            <v>スウィフトカレント+</v>
           </cell>
         </row>
         <row r="214">
           <cell r="A214">
-            <v>412050</v>
+            <v>412040</v>
           </cell>
           <cell r="B214" t="str">
-            <v>クイックムーブ+</v>
+            <v>イヴェイドオール+</v>
           </cell>
         </row>
         <row r="215">
           <cell r="A215">
-            <v>412060</v>
+            <v>412050</v>
           </cell>
           <cell r="B215" t="str">
-            <v>チェイスマジック+</v>
+            <v>クイックムーブ+</v>
           </cell>
         </row>
         <row r="216">
           <cell r="A216">
-            <v>412070</v>
+            <v>412060</v>
           </cell>
           <cell r="B216" t="str">
-            <v>ソーサリーコネクト+</v>
+            <v>チェイスマジック+</v>
           </cell>
         </row>
         <row r="217">
           <cell r="A217">
-            <v>412080</v>
+            <v>412070</v>
           </cell>
           <cell r="B217" t="str">
-            <v>ウィンドライズ+</v>
+            <v>ソーサリーコネクト+</v>
           </cell>
         </row>
         <row r="218">
           <cell r="A218">
-            <v>412090</v>
+            <v>412080</v>
           </cell>
           <cell r="B218" t="str">
-            <v>アウトオブオーダー+</v>
+            <v>ウィンドライズ+</v>
           </cell>
         </row>
         <row r="219">
           <cell r="A219">
-            <v>413010</v>
+            <v>412090</v>
           </cell>
           <cell r="B219" t="str">
-            <v>アーマーコード+</v>
+            <v>アウトオブオーダー+</v>
           </cell>
         </row>
         <row r="220">
           <cell r="A220">
-            <v>413020</v>
+            <v>413010</v>
           </cell>
           <cell r="B220" t="str">
-            <v>クイックバリア+</v>
+            <v>アーマーコード+</v>
           </cell>
         </row>
         <row r="221">
           <cell r="A221">
-            <v>413030</v>
+            <v>413020</v>
           </cell>
           <cell r="B221" t="str">
-            <v>クイックキュア+</v>
+            <v>クイックバリア+</v>
           </cell>
         </row>
         <row r="222">
           <cell r="A222">
-            <v>413040</v>
+            <v>413030</v>
           </cell>
           <cell r="B222" t="str">
-            <v>セルフシールド+</v>
+            <v>クイックキュア+</v>
           </cell>
         </row>
         <row r="223">
           <cell r="A223">
-            <v>413050</v>
+            <v>413040</v>
           </cell>
           <cell r="B223" t="str">
-            <v>パッシブジャミング+</v>
+            <v>セルフシールド+</v>
           </cell>
         </row>
         <row r="224">
           <cell r="A224">
-            <v>413060</v>
+            <v>413050</v>
           </cell>
           <cell r="B224" t="str">
-            <v>サプライカバー+</v>
+            <v>パッシブジャミング+</v>
           </cell>
         </row>
         <row r="225">
           <cell r="A225">
-            <v>413070</v>
+            <v>413060</v>
           </cell>
           <cell r="B225" t="str">
-            <v>アシッドラッシュ+</v>
+            <v>サプライカバー+</v>
           </cell>
         </row>
         <row r="226">
           <cell r="A226">
-            <v>413080</v>
+            <v>413070</v>
           </cell>
           <cell r="B226" t="str">
-            <v>ライフスティール+</v>
+            <v>アシッドラッシュ+</v>
           </cell>
         </row>
         <row r="227">
           <cell r="A227">
-            <v>413090</v>
+            <v>413080</v>
           </cell>
           <cell r="B227" t="str">
-            <v>アイスセイバー+</v>
+            <v>ライフスティール+</v>
           </cell>
         </row>
         <row r="228">
           <cell r="A228">
-            <v>414010</v>
+            <v>413090</v>
           </cell>
           <cell r="B228" t="str">
-            <v>ディバインシールド+</v>
+            <v>アイスセイバー+</v>
           </cell>
         </row>
         <row r="229">
           <cell r="A229">
-            <v>414020</v>
+            <v>414010</v>
           </cell>
           <cell r="B229" t="str">
-            <v>ライフディバイド+</v>
+            <v>ディバインシールド+</v>
           </cell>
         </row>
         <row r="230">
           <cell r="A230">
-            <v>414030</v>
+            <v>414020</v>
           </cell>
           <cell r="B230" t="str">
-            <v>エイミングスコープ+</v>
+            <v>ライフディバイド+</v>
           </cell>
         </row>
         <row r="231">
           <cell r="A231">
-            <v>414040</v>
+            <v>414030</v>
           </cell>
           <cell r="B231" t="str">
-            <v>リジェネレーション+</v>
+            <v>エイミングスコープ+</v>
           </cell>
         </row>
         <row r="232">
           <cell r="A232">
-            <v>414050</v>
+            <v>414040</v>
           </cell>
           <cell r="B232" t="str">
-            <v>ホープフルアイリス+</v>
+            <v>リジェネレーション+</v>
           </cell>
         </row>
         <row r="233">
           <cell r="A233">
-            <v>414060</v>
+            <v>414050</v>
           </cell>
           <cell r="B233" t="str">
-            <v>パッシブサプライ+</v>
+            <v>ホープフルアイリス+</v>
           </cell>
         </row>
         <row r="234">
           <cell r="A234">
-            <v>414070</v>
+            <v>414060</v>
           </cell>
           <cell r="B234" t="str">
-            <v>ホーミングクルセイド+</v>
+            <v>パッシブサプライ+</v>
           </cell>
         </row>
         <row r="235">
           <cell r="A235">
-            <v>414080</v>
+            <v>414070</v>
           </cell>
           <cell r="B235" t="str">
-            <v>クイックヒール+</v>
+            <v>ホーミングクルセイド+</v>
           </cell>
         </row>
         <row r="236">
           <cell r="A236">
-            <v>414090</v>
+            <v>414080</v>
           </cell>
           <cell r="B236" t="str">
-            <v>リレイズ+</v>
+            <v>クイックヒール+</v>
           </cell>
         </row>
         <row r="237">
           <cell r="A237">
-            <v>415010</v>
+            <v>414090</v>
           </cell>
           <cell r="B237" t="str">
-            <v>イーグルアイ+</v>
+            <v>リレイズ+</v>
           </cell>
         </row>
         <row r="238">
           <cell r="A238">
-            <v>415020</v>
+            <v>415010</v>
           </cell>
           <cell r="B238" t="str">
-            <v>ネヴァーエンド+</v>
+            <v>イーグルアイ+</v>
           </cell>
         </row>
         <row r="239">
           <cell r="A239">
-            <v>415030</v>
+            <v>415020</v>
           </cell>
           <cell r="B239" t="str">
-            <v>グレイブアクト+</v>
+            <v>ネヴァーエンド+</v>
           </cell>
         </row>
         <row r="240">
           <cell r="A240">
-            <v>415040</v>
+            <v>415030</v>
           </cell>
           <cell r="B240" t="str">
-            <v>スカルグラッジ+</v>
+            <v>グレイブアクト+</v>
           </cell>
         </row>
         <row r="241">
           <cell r="A241">
-            <v>415050</v>
+            <v>415040</v>
           </cell>
           <cell r="B241" t="str">
-            <v>ネガティブドレイン+</v>
+            <v>スカルグラッジ+</v>
           </cell>
         </row>
         <row r="242">
           <cell r="A242">
-            <v>415060</v>
+            <v>415050</v>
           </cell>
           <cell r="B242" t="str">
-            <v>アンデッドペイン+</v>
+            <v>ネガティブドレイン+</v>
           </cell>
         </row>
         <row r="243">
           <cell r="A243">
-            <v>415070</v>
+            <v>415060</v>
           </cell>
           <cell r="B243" t="str">
-            <v>ジャックポッド+</v>
+            <v>アンデッドペイン+</v>
           </cell>
         </row>
         <row r="244">
           <cell r="A244">
-            <v>415080</v>
+            <v>415070</v>
           </cell>
           <cell r="B244" t="str">
-            <v>ヒールハント+</v>
+            <v>ジャックポッド+</v>
           </cell>
         </row>
         <row r="245">
           <cell r="A245">
+            <v>415080</v>
+          </cell>
+          <cell r="B245" t="str">
+            <v>ヒールハント+</v>
+          </cell>
+        </row>
+        <row r="246">
+          <cell r="A246">
             <v>415090</v>
           </cell>
-          <cell r="B245" t="str">
+          <cell r="B246" t="str">
             <v>クイックカース+</v>
           </cell>
         </row>
@@ -2749,25 +3353,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:T33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="7.6328125" customWidth="1"/>
-    <col min="3" max="3" width="21.08984375" customWidth="1"/>
+    <col min="2" max="2" width="7.63636363636364" customWidth="1"/>
+    <col min="3" max="3" width="21.0909090909091" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="3.81640625" customWidth="1"/>
+    <col min="5" max="5" width="3.81818181818182" customWidth="1"/>
     <col min="6" max="6" width="4" customWidth="1"/>
-    <col min="7" max="8" width="4.453125" customWidth="1"/>
-    <col min="9" max="10" width="4.7265625" customWidth="1"/>
+    <col min="7" max="8" width="4.45454545454545" customWidth="1"/>
+    <col min="9" max="10" width="4.72727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2796,34 +3400,34 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>121</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2831,7 +3435,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -2879,10 +3483,10 @@
         <v>50</v>
       </c>
       <c r="S2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2890,7 +3494,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -2938,10 +3542,10 @@
         <v>30</v>
       </c>
       <c r="S3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2949,7 +3553,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -2997,10 +3601,10 @@
         <v>90</v>
       </c>
       <c r="S4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3008,7 +3612,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -3056,10 +3660,10 @@
         <v>50</v>
       </c>
       <c r="S5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3067,7 +3671,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -3115,10 +3719,10 @@
         <v>70</v>
       </c>
       <c r="S6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3126,7 +3730,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -3174,10 +3778,10 @@
         <v>30</v>
       </c>
       <c r="S7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3185,7 +3789,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -3233,10 +3837,10 @@
         <v>60</v>
       </c>
       <c r="S8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3244,7 +3848,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -3292,10 +3896,10 @@
         <v>40</v>
       </c>
       <c r="S9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3303,7 +3907,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -3351,10 +3955,10 @@
         <v>40</v>
       </c>
       <c r="S10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3362,7 +3966,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -3410,10 +4014,10 @@
         <v>70</v>
       </c>
       <c r="S11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3421,7 +4025,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -3469,10 +4073,10 @@
         <v>60</v>
       </c>
       <c r="S12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3480,7 +4084,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -3528,10 +4132,10 @@
         <v>50</v>
       </c>
       <c r="S13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3539,7 +4143,7 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -3587,10 +4191,10 @@
         <v>50</v>
       </c>
       <c r="S14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3598,7 +4202,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -3646,10 +4250,10 @@
         <v>40</v>
       </c>
       <c r="S15" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3657,7 +4261,7 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -3705,10 +4309,10 @@
         <v>70</v>
       </c>
       <c r="S16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17">
         <v>101</v>
       </c>
@@ -3716,7 +4320,7 @@
         <v>101</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -3764,10 +4368,10 @@
         <v>20</v>
       </c>
       <c r="S17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18">
         <v>102</v>
       </c>
@@ -3775,7 +4379,7 @@
         <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -3823,10 +4427,10 @@
         <v>40</v>
       </c>
       <c r="S18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19">
         <v>103</v>
       </c>
@@ -3834,7 +4438,7 @@
         <v>103</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -3882,10 +4486,10 @@
         <v>30</v>
       </c>
       <c r="S19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
       <c r="A20">
         <v>104</v>
       </c>
@@ -3893,7 +4497,7 @@
         <v>104</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -3941,10 +4545,10 @@
         <v>50</v>
       </c>
       <c r="S20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21">
         <v>105</v>
       </c>
@@ -3952,7 +4556,7 @@
         <v>105</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -4000,10 +4604,10 @@
         <v>15</v>
       </c>
       <c r="S21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22">
         <v>201</v>
       </c>
@@ -4011,7 +4615,7 @@
         <v>201</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -4059,7 +4663,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18">
       <c r="A23">
         <v>1001</v>
       </c>
@@ -4067,7 +4671,7 @@
         <v>1001</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D23">
         <v>1.5</v>
@@ -4115,7 +4719,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20">
       <c r="A24">
         <v>1002</v>
       </c>
@@ -4123,7 +4727,7 @@
         <v>1002</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -4171,10 +4775,10 @@
         <v>70</v>
       </c>
       <c r="T24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20">
       <c r="A25">
         <v>1003</v>
       </c>
@@ -4182,7 +4786,7 @@
         <v>1003</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -4230,10 +4834,10 @@
         <v>25</v>
       </c>
       <c r="T25" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20">
       <c r="A26">
         <v>1004</v>
       </c>
@@ -4241,7 +4845,7 @@
         <v>1004</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -4289,10 +4893,10 @@
         <v>30</v>
       </c>
       <c r="T26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20">
       <c r="A27">
         <v>1005</v>
       </c>
@@ -4300,7 +4904,7 @@
         <v>1005</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -4348,10 +4952,10 @@
         <v>45</v>
       </c>
       <c r="T27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20">
       <c r="A28">
         <v>1006</v>
       </c>
@@ -4359,7 +4963,7 @@
         <v>1006</v>
       </c>
       <c r="C28" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -4407,10 +5011,10 @@
         <v>50</v>
       </c>
       <c r="T28" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20">
       <c r="A29">
         <v>1007</v>
       </c>
@@ -4418,7 +5022,7 @@
         <v>1007</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -4466,10 +5070,10 @@
         <v>30</v>
       </c>
       <c r="T29" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20">
       <c r="A30">
         <v>1008</v>
       </c>
@@ -4477,7 +5081,7 @@
         <v>1008</v>
       </c>
       <c r="C30" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -4525,10 +5129,10 @@
         <v>35</v>
       </c>
       <c r="T30" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20">
       <c r="A31">
         <v>1009</v>
       </c>
@@ -4536,7 +5140,7 @@
         <v>1009</v>
       </c>
       <c r="C31" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -4584,10 +5188,10 @@
         <v>50</v>
       </c>
       <c r="T31" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20">
       <c r="A32">
         <v>1010</v>
       </c>
@@ -4595,7 +5199,7 @@
         <v>1010</v>
       </c>
       <c r="C32" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -4643,10 +5247,10 @@
         <v>75</v>
       </c>
       <c r="T32" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20">
       <c r="A33">
         <v>1011</v>
       </c>
@@ -4654,7 +5258,7 @@
         <v>1011</v>
       </c>
       <c r="C33" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -4702,48 +5306,49 @@
         <v>30</v>
       </c>
       <c r="T33" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G206"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
-    <col min="3" max="3" width="16.7265625" customWidth="1"/>
+    <col min="3" max="3" width="16.7272727272727" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C1" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D1" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E1" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="F1" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="G1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4767,7 +5372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4791,7 +5396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -4815,7 +5420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -4839,7 +5444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -4863,7 +5468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>2</v>
       </c>
@@ -4887,7 +5492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>2</v>
       </c>
@@ -4911,7 +5516,7 @@
         <v>14211</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -4935,7 +5540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -4959,7 +5564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -4983,7 +5588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>3</v>
       </c>
@@ -5007,7 +5612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>3</v>
       </c>
@@ -5031,7 +5636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>3</v>
       </c>
@@ -5055,7 +5660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>3</v>
       </c>
@@ -5079,7 +5684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>3</v>
       </c>
@@ -5103,7 +5708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>4</v>
       </c>
@@ -5127,7 +5732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>4</v>
       </c>
@@ -5151,7 +5756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>4</v>
       </c>
@@ -5175,7 +5780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>4</v>
       </c>
@@ -5199,7 +5804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>4</v>
       </c>
@@ -5223,7 +5828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>5</v>
       </c>
@@ -5247,7 +5852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>5</v>
       </c>
@@ -5271,7 +5876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>5</v>
       </c>
@@ -5295,7 +5900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>5</v>
       </c>
@@ -5319,7 +5924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>5</v>
       </c>
@@ -5343,7 +5948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>6</v>
       </c>
@@ -5367,7 +5972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>6</v>
       </c>
@@ -5391,7 +5996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>6</v>
       </c>
@@ -5415,7 +6020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>6</v>
       </c>
@@ -5439,7 +6044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>6</v>
       </c>
@@ -5463,7 +6068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>7</v>
       </c>
@@ -5487,7 +6092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>7</v>
       </c>
@@ -5511,7 +6116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>7</v>
       </c>
@@ -5535,7 +6140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>7</v>
       </c>
@@ -5559,7 +6164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>7</v>
       </c>
@@ -5583,7 +6188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>8</v>
       </c>
@@ -5607,7 +6212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>8</v>
       </c>
@@ -5631,7 +6236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>8</v>
       </c>
@@ -5655,7 +6260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>8</v>
       </c>
@@ -5679,7 +6284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>8</v>
       </c>
@@ -5703,7 +6308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>9</v>
       </c>
@@ -5727,7 +6332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>9</v>
       </c>
@@ -5751,7 +6356,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>9</v>
       </c>
@@ -5775,7 +6380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>9</v>
       </c>
@@ -5799,7 +6404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>9</v>
       </c>
@@ -5823,7 +6428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>10</v>
       </c>
@@ -5847,7 +6452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>10</v>
       </c>
@@ -5871,7 +6476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>10</v>
       </c>
@@ -5895,7 +6500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7">
       <c r="A50">
         <v>10</v>
       </c>
@@ -5919,7 +6524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7">
       <c r="A51">
         <v>10</v>
       </c>
@@ -5943,7 +6548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7">
       <c r="A52">
         <v>11</v>
       </c>
@@ -5967,7 +6572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7">
       <c r="A53">
         <v>11</v>
       </c>
@@ -5991,7 +6596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7">
       <c r="A54">
         <v>11</v>
       </c>
@@ -6015,7 +6620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7">
       <c r="A55">
         <v>11</v>
       </c>
@@ -6039,7 +6644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7">
       <c r="A56">
         <v>11</v>
       </c>
@@ -6063,7 +6668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7">
       <c r="A57">
         <v>12</v>
       </c>
@@ -6087,7 +6692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7">
       <c r="A58">
         <v>12</v>
       </c>
@@ -6111,7 +6716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7">
       <c r="A59">
         <v>12</v>
       </c>
@@ -6135,7 +6740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7">
       <c r="A60">
         <v>12</v>
       </c>
@@ -6159,7 +6764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7">
       <c r="A61">
         <v>12</v>
       </c>
@@ -6183,7 +6788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7">
       <c r="A62">
         <v>13</v>
       </c>
@@ -6207,7 +6812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7">
       <c r="A63">
         <v>13</v>
       </c>
@@ -6231,7 +6836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7">
       <c r="A64">
         <v>13</v>
       </c>
@@ -6255,7 +6860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7">
       <c r="A65">
         <v>13</v>
       </c>
@@ -6279,7 +6884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7">
       <c r="A66">
         <v>13</v>
       </c>
@@ -6303,7 +6908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7">
       <c r="A67">
         <v>14</v>
       </c>
@@ -6327,7 +6932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7">
       <c r="A68">
         <v>14</v>
       </c>
@@ -6351,7 +6956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7">
       <c r="A69">
         <v>14</v>
       </c>
@@ -6375,7 +6980,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7">
       <c r="A70">
         <v>14</v>
       </c>
@@ -6399,7 +7004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7">
       <c r="A71">
         <v>14</v>
       </c>
@@ -6423,7 +7028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7">
       <c r="A72">
         <v>15</v>
       </c>
@@ -6447,7 +7052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7">
       <c r="A73">
         <v>15</v>
       </c>
@@ -6471,7 +7076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7">
       <c r="A74">
         <v>15</v>
       </c>
@@ -6495,7 +7100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7">
       <c r="A75">
         <v>15</v>
       </c>
@@ -6519,7 +7124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7">
       <c r="A76">
         <v>15</v>
       </c>
@@ -6543,7 +7148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7">
       <c r="A77">
         <v>101</v>
       </c>
@@ -6567,7 +7172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7">
       <c r="A78">
         <v>102</v>
       </c>
@@ -6591,7 +7196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7">
       <c r="A79">
         <v>102</v>
       </c>
@@ -6615,7 +7220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7">
       <c r="A80">
         <v>102</v>
       </c>
@@ -6639,7 +7244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7">
       <c r="A81">
         <v>102</v>
       </c>
@@ -6663,7 +7268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7">
       <c r="A82">
         <v>102</v>
       </c>
@@ -6687,7 +7292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7">
       <c r="A83">
         <v>103</v>
       </c>
@@ -6711,7 +7316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7">
       <c r="A84">
         <v>103</v>
       </c>
@@ -6735,7 +7340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7">
       <c r="A85">
         <v>103</v>
       </c>
@@ -6759,7 +7364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7">
       <c r="A86">
         <v>103</v>
       </c>
@@ -6783,7 +7388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7">
       <c r="A87">
         <v>103</v>
       </c>
@@ -6807,7 +7412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7">
       <c r="A88">
         <v>103</v>
       </c>
@@ -6831,7 +7436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7">
       <c r="A89">
         <v>104</v>
       </c>
@@ -6855,7 +7460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7">
       <c r="A90">
         <v>104</v>
       </c>
@@ -6879,7 +7484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7">
       <c r="A91">
         <v>104</v>
       </c>
@@ -6903,7 +7508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7">
       <c r="A92">
         <v>104</v>
       </c>
@@ -6927,7 +7532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7">
       <c r="A93">
         <v>105</v>
       </c>
@@ -6951,7 +7556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7">
       <c r="A94">
         <v>105</v>
       </c>
@@ -6975,7 +7580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7">
       <c r="A95">
         <v>105</v>
       </c>
@@ -6999,7 +7604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7">
       <c r="A96">
         <v>105</v>
       </c>
@@ -7023,7 +7628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7">
       <c r="A97">
         <v>105</v>
       </c>
@@ -7047,7 +7652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7">
       <c r="A98">
         <v>105</v>
       </c>
@@ -7071,7 +7676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7">
       <c r="A99">
         <v>201</v>
       </c>
@@ -7095,7 +7700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7">
       <c r="A100">
         <v>201</v>
       </c>
@@ -7119,7 +7724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7">
       <c r="A101">
         <v>201</v>
       </c>
@@ -7143,7 +7748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7">
       <c r="A102">
         <v>201</v>
       </c>
@@ -7167,7 +7772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7">
       <c r="A103">
         <v>201</v>
       </c>
@@ -7191,7 +7796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7">
       <c r="A104">
         <v>201</v>
       </c>
@@ -7215,7 +7820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7">
       <c r="A105">
         <v>201</v>
       </c>
@@ -7239,7 +7844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7">
       <c r="A106">
         <v>201</v>
       </c>
@@ -7263,7 +7868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7">
       <c r="A107">
         <v>201</v>
       </c>
@@ -7287,7 +7892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7">
       <c r="A108">
         <v>201</v>
       </c>
@@ -7311,7 +7916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7">
       <c r="A109">
         <v>1001</v>
       </c>
@@ -7335,7 +7940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7">
       <c r="A110">
         <v>1001</v>
       </c>
@@ -7359,7 +7964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7">
       <c r="A111">
         <v>1001</v>
       </c>
@@ -7383,7 +7988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7">
       <c r="A112">
         <v>1001</v>
       </c>
@@ -7407,7 +8012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7">
       <c r="A113">
         <v>1001</v>
       </c>
@@ -7431,7 +8036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7">
       <c r="A114">
         <v>1001</v>
       </c>
@@ -7455,7 +8060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7">
       <c r="A115">
         <v>1001</v>
       </c>
@@ -7479,7 +8084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7">
       <c r="A116">
         <v>1001</v>
       </c>
@@ -7503,7 +8108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7">
       <c r="A117">
         <v>1002</v>
       </c>
@@ -7527,7 +8132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7">
       <c r="A118">
         <v>1002</v>
       </c>
@@ -7551,7 +8156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7">
       <c r="A119">
         <v>1002</v>
       </c>
@@ -7575,7 +8180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7">
       <c r="A120">
         <v>1002</v>
       </c>
@@ -7599,7 +8204,7 @@
         <v>5060</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7">
       <c r="A121">
         <v>1002</v>
       </c>
@@ -7623,7 +8228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7">
       <c r="A122">
         <v>1002</v>
       </c>
@@ -7647,7 +8252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7">
       <c r="A123">
         <v>1002</v>
       </c>
@@ -7671,7 +8276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7">
       <c r="A124">
         <v>1002</v>
       </c>
@@ -7695,7 +8300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7">
       <c r="A125">
         <v>1002</v>
       </c>
@@ -7719,7 +8324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7">
       <c r="A126">
         <v>1003</v>
       </c>
@@ -7743,7 +8348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7">
       <c r="A127">
         <v>1003</v>
       </c>
@@ -7767,7 +8372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7">
       <c r="A128">
         <v>1003</v>
       </c>
@@ -7791,7 +8396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7">
       <c r="A129">
         <v>1003</v>
       </c>
@@ -7815,7 +8420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7">
       <c r="A130">
         <v>1003</v>
       </c>
@@ -7839,7 +8444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7">
       <c r="A131">
         <v>1003</v>
       </c>
@@ -7863,7 +8468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7">
       <c r="A132">
         <v>1003</v>
       </c>
@@ -7887,7 +8492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7">
       <c r="A133">
         <v>1003</v>
       </c>
@@ -7911,7 +8516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7">
       <c r="A134">
         <v>1003</v>
       </c>
@@ -7935,7 +8540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7">
       <c r="A135">
         <v>1004</v>
       </c>
@@ -7959,7 +8564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7">
       <c r="A136">
         <v>1004</v>
       </c>
@@ -7983,7 +8588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7">
       <c r="A137">
         <v>1004</v>
       </c>
@@ -8007,7 +8612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7">
       <c r="A138">
         <v>1004</v>
       </c>
@@ -8031,7 +8636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7">
       <c r="A139">
         <v>1004</v>
       </c>
@@ -8055,7 +8660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7">
       <c r="A140">
         <v>1004</v>
       </c>
@@ -8079,7 +8684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7">
       <c r="A141">
         <v>1004</v>
       </c>
@@ -8103,7 +8708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7">
       <c r="A142">
         <v>1004</v>
       </c>
@@ -8127,7 +8732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7">
       <c r="A143">
         <v>1004</v>
       </c>
@@ -8151,7 +8756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7">
       <c r="A144">
         <v>1005</v>
       </c>
@@ -8175,7 +8780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7">
       <c r="A145">
         <v>1005</v>
       </c>
@@ -8199,7 +8804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7">
       <c r="A146">
         <v>1005</v>
       </c>
@@ -8223,7 +8828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7">
       <c r="A147">
         <v>1005</v>
       </c>
@@ -8247,7 +8852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7">
       <c r="A148">
         <v>1005</v>
       </c>
@@ -8271,7 +8876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7">
       <c r="A149">
         <v>1005</v>
       </c>
@@ -8295,7 +8900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7">
       <c r="A150">
         <v>1005</v>
       </c>
@@ -8319,7 +8924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7">
       <c r="A151">
         <v>1005</v>
       </c>
@@ -8343,7 +8948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7">
       <c r="A152">
         <v>1005</v>
       </c>
@@ -8367,7 +8972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7">
       <c r="A153">
         <v>1006</v>
       </c>
@@ -8391,7 +8996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7">
       <c r="A154">
         <v>1006</v>
       </c>
@@ -8415,7 +9020,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7">
       <c r="A155">
         <v>1006</v>
       </c>
@@ -8439,7 +9044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7">
       <c r="A156">
         <v>1006</v>
       </c>
@@ -8463,7 +9068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7">
       <c r="A157">
         <v>1006</v>
       </c>
@@ -8487,7 +9092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7">
       <c r="A158">
         <v>1006</v>
       </c>
@@ -8511,7 +9116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7">
       <c r="A159">
         <v>1006</v>
       </c>
@@ -8535,7 +9140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7">
       <c r="A160">
         <v>1006</v>
       </c>
@@ -8559,7 +9164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7">
       <c r="A161">
         <v>1006</v>
       </c>
@@ -8583,7 +9188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7">
       <c r="A162">
         <v>1007</v>
       </c>
@@ -8607,7 +9212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7">
       <c r="A163">
         <v>1007</v>
       </c>
@@ -8631,7 +9236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7">
       <c r="A164">
         <v>1007</v>
       </c>
@@ -8655,7 +9260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7">
       <c r="A165">
         <v>1007</v>
       </c>
@@ -8679,7 +9284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7">
       <c r="A166">
         <v>1007</v>
       </c>
@@ -8703,7 +9308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7">
       <c r="A167">
         <v>1007</v>
       </c>
@@ -8727,7 +9332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7">
       <c r="A168">
         <v>1007</v>
       </c>
@@ -8751,7 +9356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7">
       <c r="A169">
         <v>1007</v>
       </c>
@@ -8775,7 +9380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7">
       <c r="A170">
         <v>1007</v>
       </c>
@@ -8799,7 +9404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7">
       <c r="A171">
         <v>1008</v>
       </c>
@@ -8823,7 +9428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7">
       <c r="A172">
         <v>1008</v>
       </c>
@@ -8847,7 +9452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7">
       <c r="A173">
         <v>1008</v>
       </c>
@@ -8871,7 +9476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7">
       <c r="A174">
         <v>1008</v>
       </c>
@@ -8895,7 +9500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7">
       <c r="A175">
         <v>1008</v>
       </c>
@@ -8919,7 +9524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7">
       <c r="A176">
         <v>1008</v>
       </c>
@@ -8943,7 +9548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:7">
       <c r="A177">
         <v>1008</v>
       </c>
@@ -8967,7 +9572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:7">
       <c r="A178">
         <v>1008</v>
       </c>
@@ -8991,7 +9596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:7">
       <c r="A179">
         <v>1008</v>
       </c>
@@ -9015,7 +9620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:7">
       <c r="A180">
         <v>1009</v>
       </c>
@@ -9039,7 +9644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:7">
       <c r="A181">
         <v>1009</v>
       </c>
@@ -9063,7 +9668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:7">
       <c r="A182">
         <v>1009</v>
       </c>
@@ -9087,7 +9692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:7">
       <c r="A183">
         <v>1009</v>
       </c>
@@ -9111,7 +9716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:7">
       <c r="A184">
         <v>1009</v>
       </c>
@@ -9135,7 +9740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:7">
       <c r="A185">
         <v>1009</v>
       </c>
@@ -9159,7 +9764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:7">
       <c r="A186">
         <v>1009</v>
       </c>
@@ -9183,7 +9788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:7">
       <c r="A187">
         <v>1009</v>
       </c>
@@ -9207,7 +9812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:7">
       <c r="A188">
         <v>1009</v>
       </c>
@@ -9231,7 +9836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:7">
       <c r="A189">
         <v>1010</v>
       </c>
@@ -9255,7 +9860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:7">
       <c r="A190">
         <v>1010</v>
       </c>
@@ -9279,7 +9884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:7">
       <c r="A191">
         <v>1010</v>
       </c>
@@ -9303,7 +9908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:7">
       <c r="A192">
         <v>1010</v>
       </c>
@@ -9327,7 +9932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:7">
       <c r="A193">
         <v>1010</v>
       </c>
@@ -9351,7 +9956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:7">
       <c r="A194">
         <v>1010</v>
       </c>
@@ -9375,7 +9980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:7">
       <c r="A195">
         <v>1010</v>
       </c>
@@ -9399,7 +10004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:7">
       <c r="A196">
         <v>1010</v>
       </c>
@@ -9423,7 +10028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7">
       <c r="A197">
         <v>1010</v>
       </c>
@@ -9447,7 +10052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:7">
       <c r="A198">
         <v>1011</v>
       </c>
@@ -9471,7 +10076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:7">
       <c r="A199">
         <v>1011</v>
       </c>
@@ -9495,7 +10100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:7">
       <c r="A200">
         <v>1011</v>
       </c>
@@ -9519,7 +10124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:7">
       <c r="A201">
         <v>1011</v>
       </c>
@@ -9543,7 +10148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:7">
       <c r="A202">
         <v>1011</v>
       </c>
@@ -9567,7 +10172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:7">
       <c r="A203">
         <v>1011</v>
       </c>
@@ -9591,7 +10196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:7">
       <c r="A204">
         <v>1011</v>
       </c>
@@ -9615,7 +10220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:7">
       <c r="A205">
         <v>1011</v>
       </c>
@@ -9639,7 +10244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7">
       <c r="A206">
         <v>1011</v>
       </c>
@@ -9664,40 +10269,41 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C1" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="D1" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="E1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F1" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="G1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>6</v>
       </c>
@@ -9720,7 +10326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>6</v>
       </c>
@@ -9743,7 +10349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>9</v>
       </c>
@@ -9766,7 +10372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>13</v>
       </c>
@@ -9789,7 +10395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>14</v>
       </c>
@@ -9812,7 +10418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>15</v>
       </c>
@@ -9835,7 +10441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>15</v>
       </c>
@@ -9858,7 +10464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>101</v>
       </c>
@@ -9881,7 +10487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>103</v>
       </c>
@@ -9904,7 +10510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>104</v>
       </c>
@@ -9927,7 +10533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>104</v>
       </c>
@@ -9950,7 +10556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>105</v>
       </c>
@@ -9974,437 +10580,439 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B42"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="1"/>
   <cols>
-    <col min="2" max="2" width="13.54296875" customWidth="1"/>
+    <col min="2" max="2" width="13.5454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>101</v>
       </c>
       <c r="B17" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18">
         <v>102</v>
       </c>
       <c r="B18" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19">
         <v>103</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20">
         <v>104</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21">
         <v>105</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22">
         <v>106</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23">
         <v>107</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24">
         <v>201</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25">
         <v>202</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26">
         <v>203</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27">
         <v>204</v>
       </c>
       <c r="B27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28">
         <v>205</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29">
         <v>206</v>
       </c>
       <c r="B29" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30">
         <v>207</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31">
         <v>301</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32">
         <v>1001</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33">
         <v>1002</v>
       </c>
       <c r="B33" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34">
         <v>1003</v>
       </c>
       <c r="B34" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35">
         <v>1004</v>
       </c>
       <c r="B35" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36">
         <v>1005</v>
       </c>
       <c r="B36" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37">
         <v>1006</v>
       </c>
       <c r="B37" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38">
         <v>1007</v>
       </c>
       <c r="B38" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39">
         <v>1008</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40">
         <v>1009</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41">
         <v>1010</v>
       </c>
       <c r="B41" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42">
         <v>1011</v>
       </c>
       <c r="B42" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="B1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:2">
       <c r="B1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="2:3">
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3">
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
       <c r="B7">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
       <c r="B8">
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
       <c r="B9">
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -394,10 +394,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -415,6 +415,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -424,7 +431,15 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -438,24 +453,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -470,6 +493,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -477,7 +522,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -491,62 +536,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -568,6 +568,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -580,7 +586,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -592,19 +622,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -616,139 +742,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -786,6 +786,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -797,39 +806,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -859,6 +835,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -867,145 +867,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,559 +1491,559 @@
         </row>
         <row r="50">
           <cell r="A50">
-            <v>10010</v>
+            <v>6020</v>
           </cell>
           <cell r="B50" t="str">
-            <v>アンデッド</v>
+            <v>交代</v>
           </cell>
         </row>
         <row r="51">
           <cell r="A51">
-            <v>10020</v>
+            <v>10010</v>
           </cell>
           <cell r="B51" t="str">
-            <v>エアリアル</v>
+            <v>アンデッド</v>
           </cell>
         </row>
         <row r="52">
           <cell r="A52">
-            <v>10030</v>
+            <v>10020</v>
           </cell>
           <cell r="B52" t="str">
-            <v>悪魔</v>
+            <v>エアリアル</v>
           </cell>
         </row>
         <row r="53">
           <cell r="A53">
-            <v>10040</v>
+            <v>10030</v>
           </cell>
           <cell r="B53" t="str">
-            <v>クリーチャー</v>
+            <v>悪魔</v>
           </cell>
         </row>
         <row r="54">
           <cell r="A54">
-            <v>10050</v>
+            <v>10040</v>
           </cell>
           <cell r="B54" t="str">
-            <v>野生の記憶</v>
+            <v>クリーチャー</v>
           </cell>
         </row>
         <row r="55">
           <cell r="A55">
-            <v>10060</v>
+            <v>10050</v>
           </cell>
           <cell r="B55" t="str">
-            <v>変異生物</v>
+            <v>野生の記憶</v>
           </cell>
         </row>
         <row r="56">
           <cell r="A56">
-            <v>11010</v>
+            <v>10060</v>
           </cell>
           <cell r="B56" t="str">
-            <v>ウルフソウル</v>
+            <v>変異生物</v>
           </cell>
         </row>
         <row r="57">
           <cell r="A57">
-            <v>11020</v>
+            <v>11010</v>
           </cell>
           <cell r="B57" t="str">
-            <v>プリディカメント</v>
+            <v>ウルフソウル</v>
           </cell>
         </row>
         <row r="58">
           <cell r="A58">
-            <v>11030</v>
+            <v>11020</v>
           </cell>
           <cell r="B58" t="str">
-            <v>アサルトシフト</v>
+            <v>プリディカメント</v>
           </cell>
         </row>
         <row r="59">
           <cell r="A59">
-            <v>11040</v>
+            <v>11030</v>
           </cell>
           <cell r="B59" t="str">
-            <v>アクティブギフト</v>
+            <v>アサルトシフト</v>
           </cell>
         </row>
         <row r="60">
           <cell r="A60">
-            <v>11050</v>
+            <v>11040</v>
           </cell>
           <cell r="B60" t="str">
-            <v>イグナイテッド</v>
+            <v>アクティブギフト</v>
           </cell>
         </row>
         <row r="61">
           <cell r="A61">
-            <v>11060</v>
+            <v>11050</v>
           </cell>
           <cell r="B61" t="str">
-            <v>ライジングファイア</v>
+            <v>イグナイテッド</v>
           </cell>
         </row>
         <row r="62">
           <cell r="A62">
-            <v>11070</v>
+            <v>11060</v>
           </cell>
           <cell r="B62" t="str">
-            <v>ルージュバック</v>
+            <v>ライジングファイア</v>
           </cell>
         </row>
         <row r="63">
           <cell r="A63">
-            <v>11080</v>
+            <v>11070</v>
           </cell>
           <cell r="B63" t="str">
-            <v>パワーエール</v>
+            <v>ルージュバック</v>
           </cell>
         </row>
         <row r="64">
           <cell r="A64">
-            <v>11090</v>
+            <v>11080</v>
           </cell>
           <cell r="B64" t="str">
-            <v>スレイプニル</v>
+            <v>パワーエール</v>
           </cell>
         </row>
         <row r="65">
           <cell r="A65">
-            <v>12010</v>
+            <v>11090</v>
           </cell>
           <cell r="B65" t="str">
-            <v>エクステンション</v>
+            <v>スレイプニル</v>
           </cell>
         </row>
         <row r="66">
           <cell r="A66">
-            <v>12020</v>
+            <v>12010</v>
           </cell>
           <cell r="B66" t="str">
-            <v>ヘブンリーラック</v>
+            <v>エクステンション</v>
           </cell>
         </row>
         <row r="67">
           <cell r="A67">
-            <v>12030</v>
+            <v>12020</v>
           </cell>
           <cell r="B67" t="str">
-            <v>スウィフトカレント</v>
+            <v>ヘブンリーラック</v>
           </cell>
         </row>
         <row r="68">
           <cell r="A68">
-            <v>12040</v>
+            <v>12030</v>
           </cell>
           <cell r="B68" t="str">
-            <v>イヴェイドオール</v>
+            <v>スウィフトカレント</v>
           </cell>
         </row>
         <row r="69">
           <cell r="A69">
-            <v>12050</v>
+            <v>12040</v>
           </cell>
           <cell r="B69" t="str">
-            <v>クイックムーブ</v>
+            <v>イヴェイドオール</v>
           </cell>
         </row>
         <row r="70">
           <cell r="A70">
-            <v>12060</v>
+            <v>12050</v>
           </cell>
           <cell r="B70" t="str">
-            <v>チェイスマジック</v>
+            <v>クイックムーブ</v>
           </cell>
         </row>
         <row r="71">
           <cell r="A71">
-            <v>12070</v>
+            <v>12060</v>
           </cell>
           <cell r="B71" t="str">
-            <v>ソーサリーコネクト</v>
+            <v>チェイスマジック</v>
           </cell>
         </row>
         <row r="72">
           <cell r="A72">
-            <v>12080</v>
+            <v>12070</v>
           </cell>
           <cell r="B72" t="str">
-            <v>ウィンドライズ</v>
+            <v>ソーサリーコネクト</v>
           </cell>
         </row>
         <row r="73">
           <cell r="A73">
-            <v>12090</v>
+            <v>12080</v>
           </cell>
           <cell r="B73" t="str">
-            <v>アウトオブオーダー</v>
+            <v>ウィンドライズ</v>
           </cell>
         </row>
         <row r="74">
           <cell r="A74">
-            <v>13010</v>
+            <v>12090</v>
           </cell>
           <cell r="B74" t="str">
-            <v>アーマーコード</v>
+            <v>アウトオブオーダー</v>
           </cell>
         </row>
         <row r="75">
           <cell r="A75">
-            <v>13020</v>
+            <v>13010</v>
           </cell>
           <cell r="B75" t="str">
-            <v>クイックバリア</v>
+            <v>アーマーコード</v>
           </cell>
         </row>
         <row r="76">
           <cell r="A76">
-            <v>13030</v>
+            <v>13020</v>
           </cell>
           <cell r="B76" t="str">
-            <v>クイックキュア</v>
+            <v>クイックバリア</v>
           </cell>
         </row>
         <row r="77">
           <cell r="A77">
-            <v>13040</v>
+            <v>13030</v>
           </cell>
           <cell r="B77" t="str">
-            <v>セルフシールド</v>
+            <v>クイックキュア</v>
           </cell>
         </row>
         <row r="78">
           <cell r="A78">
-            <v>13050</v>
+            <v>13040</v>
           </cell>
           <cell r="B78" t="str">
-            <v>パッシブジャミング</v>
+            <v>セルフシールド</v>
           </cell>
         </row>
         <row r="79">
           <cell r="A79">
-            <v>13060</v>
+            <v>13050</v>
           </cell>
           <cell r="B79" t="str">
-            <v>サプライカバー</v>
+            <v>パッシブジャミング</v>
           </cell>
         </row>
         <row r="80">
           <cell r="A80">
-            <v>13070</v>
+            <v>13060</v>
           </cell>
           <cell r="B80" t="str">
-            <v>アシッドラッシュ</v>
+            <v>サプライカバー</v>
           </cell>
         </row>
         <row r="81">
           <cell r="A81">
-            <v>13080</v>
+            <v>13070</v>
           </cell>
           <cell r="B81" t="str">
-            <v>ライフスティール</v>
+            <v>アシッドラッシュ</v>
           </cell>
         </row>
         <row r="82">
           <cell r="A82">
-            <v>13090</v>
+            <v>13080</v>
           </cell>
           <cell r="B82" t="str">
-            <v>アイスセイバー</v>
+            <v>ライフスティール</v>
           </cell>
         </row>
         <row r="83">
           <cell r="A83">
-            <v>14010</v>
+            <v>13090</v>
           </cell>
           <cell r="B83" t="str">
-            <v>ディバインシールド</v>
+            <v>アイスセイバー</v>
           </cell>
         </row>
         <row r="84">
           <cell r="A84">
-            <v>14020</v>
+            <v>14010</v>
           </cell>
           <cell r="B84" t="str">
-            <v>ライフディバイド</v>
+            <v>ディバインシールド</v>
           </cell>
         </row>
         <row r="85">
           <cell r="A85">
-            <v>14030</v>
+            <v>14020</v>
           </cell>
           <cell r="B85" t="str">
-            <v>エイミングスコープ</v>
+            <v>ライフディバイド</v>
           </cell>
         </row>
         <row r="86">
           <cell r="A86">
-            <v>14040</v>
+            <v>14030</v>
           </cell>
           <cell r="B86" t="str">
-            <v>リジェネレーション</v>
+            <v>エイミングスコープ</v>
           </cell>
         </row>
         <row r="87">
           <cell r="A87">
-            <v>14050</v>
+            <v>14040</v>
           </cell>
           <cell r="B87" t="str">
-            <v>ホープフルアイリス</v>
+            <v>リジェネレーション</v>
           </cell>
         </row>
         <row r="88">
           <cell r="A88">
-            <v>14060</v>
+            <v>14050</v>
           </cell>
           <cell r="B88" t="str">
-            <v>パッシブサプライ</v>
+            <v>ホープフルアイリス</v>
           </cell>
         </row>
         <row r="89">
           <cell r="A89">
-            <v>14070</v>
+            <v>14060</v>
           </cell>
           <cell r="B89" t="str">
-            <v>ホーミングクルセイド</v>
+            <v>パッシブサプライ</v>
           </cell>
         </row>
         <row r="90">
           <cell r="A90">
-            <v>14080</v>
+            <v>14070</v>
           </cell>
           <cell r="B90" t="str">
-            <v>クイックヒール</v>
+            <v>ホーミングクルセイド</v>
           </cell>
         </row>
         <row r="91">
           <cell r="A91">
-            <v>14090</v>
+            <v>14080</v>
           </cell>
           <cell r="B91" t="str">
-            <v>リレイズ</v>
+            <v>クイックヒール</v>
           </cell>
         </row>
         <row r="92">
           <cell r="A92">
-            <v>15010</v>
+            <v>14090</v>
           </cell>
           <cell r="B92" t="str">
-            <v>イーグルアイ</v>
+            <v>リレイズ</v>
           </cell>
         </row>
         <row r="93">
           <cell r="A93">
-            <v>15020</v>
+            <v>15010</v>
           </cell>
           <cell r="B93" t="str">
-            <v>ネヴァーエンド</v>
+            <v>イーグルアイ</v>
           </cell>
         </row>
         <row r="94">
           <cell r="A94">
-            <v>15030</v>
+            <v>15020</v>
           </cell>
           <cell r="B94" t="str">
-            <v>グレイブアクト</v>
+            <v>ネヴァーエンド</v>
           </cell>
         </row>
         <row r="95">
           <cell r="A95">
-            <v>15040</v>
+            <v>15030</v>
           </cell>
           <cell r="B95" t="str">
-            <v>スカルグラッジ</v>
+            <v>グレイブアクト</v>
           </cell>
         </row>
         <row r="96">
           <cell r="A96">
-            <v>15050</v>
+            <v>15040</v>
           </cell>
           <cell r="B96" t="str">
-            <v>ネガティブドレイン</v>
+            <v>スカルグラッジ</v>
           </cell>
         </row>
         <row r="97">
           <cell r="A97">
-            <v>15060</v>
+            <v>15050</v>
           </cell>
           <cell r="B97" t="str">
-            <v>アンデッドペイン</v>
+            <v>ネガティブドレイン</v>
           </cell>
         </row>
         <row r="98">
           <cell r="A98">
-            <v>15070</v>
+            <v>15060</v>
           </cell>
           <cell r="B98" t="str">
-            <v>ジャックポッド</v>
+            <v>アンデッドペイン</v>
           </cell>
         </row>
         <row r="99">
           <cell r="A99">
-            <v>15080</v>
+            <v>15070</v>
           </cell>
           <cell r="B99" t="str">
-            <v>ヒールハント</v>
+            <v>ジャックポッド</v>
           </cell>
         </row>
         <row r="100">
           <cell r="A100">
-            <v>15090</v>
+            <v>15080</v>
           </cell>
           <cell r="B100" t="str">
-            <v>クイックカース</v>
+            <v>ヒールハント</v>
           </cell>
         </row>
         <row r="101">
           <cell r="A101">
-            <v>20010</v>
+            <v>15090</v>
           </cell>
           <cell r="B101" t="str">
-            <v>ウェイトユニゾン</v>
+            <v>クイックカース</v>
           </cell>
         </row>
         <row r="102">
           <cell r="A102">
-            <v>100110</v>
+            <v>20010</v>
           </cell>
           <cell r="B102" t="str">
-            <v>ソーイングアームド</v>
+            <v>ウェイトユニゾン</v>
           </cell>
         </row>
         <row r="103">
           <cell r="A103">
-            <v>100120</v>
+            <v>100110</v>
           </cell>
           <cell r="B103" t="str">
-            <v>エターナルロンド</v>
+            <v>ソーイングアームド</v>
           </cell>
         </row>
         <row r="104">
           <cell r="A104">
-            <v>100210</v>
+            <v>100120</v>
           </cell>
           <cell r="B104" t="str">
-            <v>アブソリュートパリィ</v>
+            <v>エターナルロンド</v>
           </cell>
         </row>
         <row r="105">
           <cell r="A105">
-            <v>100220</v>
+            <v>100210</v>
           </cell>
           <cell r="B105" t="str">
-            <v>レヴェリー</v>
+            <v>アブソリュートパリィ</v>
           </cell>
         </row>
         <row r="106">
           <cell r="A106">
-            <v>100310</v>
+            <v>100220</v>
           </cell>
           <cell r="B106" t="str">
-            <v>セイクリッドバリア</v>
+            <v>レヴェリー</v>
           </cell>
         </row>
         <row r="107">
           <cell r="A107">
-            <v>100320</v>
+            <v>100310</v>
           </cell>
           <cell r="B107" t="str">
-            <v>リベンジニードル</v>
+            <v>セイクリッドバリア</v>
           </cell>
         </row>
         <row r="108">
           <cell r="A108">
-            <v>100410</v>
+            <v>100320</v>
           </cell>
           <cell r="B108" t="str">
-            <v>アバンデンス</v>
+            <v>リベンジニードル</v>
           </cell>
         </row>
         <row r="109">
           <cell r="A109">
-            <v>100420</v>
+            <v>100410</v>
           </cell>
           <cell r="B109" t="str">
-            <v>ハーヴェスト</v>
+            <v>アバンデンス</v>
           </cell>
         </row>
         <row r="110">
           <cell r="A110">
-            <v>100510</v>
+            <v>100420</v>
           </cell>
           <cell r="B110" t="str">
-            <v>カースドブレイク</v>
+            <v>ハーヴェスト</v>
           </cell>
         </row>
         <row r="111">
           <cell r="A111">
-            <v>100520</v>
+            <v>100510</v>
           </cell>
           <cell r="B111" t="str">
-            <v>ムーンライトレイ</v>
+            <v>カースドブレイク</v>
           </cell>
         </row>
         <row r="112">
           <cell r="A112">
-            <v>100610</v>
+            <v>100520</v>
           </cell>
           <cell r="B112" t="str">
-            <v>サンフレイム</v>
+            <v>ムーンライトレイ</v>
           </cell>
         </row>
         <row r="113">
           <cell r="A113">
-            <v>100620</v>
+            <v>100610</v>
           </cell>
           <cell r="B113" t="str">
-            <v>フレイムタン</v>
+            <v>サンフレイム</v>
           </cell>
         </row>
         <row r="114">
           <cell r="A114">
-            <v>100710</v>
+            <v>100620</v>
           </cell>
           <cell r="B114" t="str">
-            <v>ライズザフラッグ</v>
+            <v>フレイムタン</v>
           </cell>
         </row>
         <row r="115">
           <cell r="A115">
-            <v>100720</v>
+            <v>100710</v>
           </cell>
           <cell r="B115" t="str">
-            <v>オーバーリミット</v>
+            <v>ライズザフラッグ</v>
           </cell>
         </row>
         <row r="116">
           <cell r="A116">
-            <v>100810</v>
+            <v>100720</v>
           </cell>
           <cell r="B116" t="str">
-            <v>テンパランス</v>
+            <v>オーバーリミット</v>
           </cell>
         </row>
         <row r="117">
           <cell r="A117">
-            <v>100820</v>
+            <v>100810</v>
           </cell>
           <cell r="B117" t="str">
-            <v>シエルクルセイダー</v>
+            <v>テンパランス</v>
           </cell>
         </row>
         <row r="118">
           <cell r="A118">
-            <v>100910</v>
+            <v>100820</v>
           </cell>
           <cell r="B118" t="str">
-            <v>バーニングカウンター</v>
+            <v>シエルクルセイダー</v>
           </cell>
         </row>
         <row r="119">
           <cell r="A119">
-            <v>100911</v>
+            <v>100910</v>
           </cell>
           <cell r="B119" t="str">
             <v>バーニングカウンター</v>
@@ -2051,15 +2051,15 @@
         </row>
         <row r="120">
           <cell r="A120">
-            <v>100920</v>
+            <v>100911</v>
           </cell>
           <cell r="B120" t="str">
-            <v>プロミネンス</v>
+            <v>バーニングカウンター</v>
           </cell>
         </row>
         <row r="121">
           <cell r="A121">
-            <v>100921</v>
+            <v>100920</v>
           </cell>
           <cell r="B121" t="str">
             <v>プロミネンス</v>
@@ -2067,95 +2067,95 @@
         </row>
         <row r="122">
           <cell r="A122">
-            <v>101010</v>
+            <v>100921</v>
           </cell>
           <cell r="B122" t="str">
-            <v>エウロス</v>
+            <v>プロミネンス</v>
           </cell>
         </row>
         <row r="123">
           <cell r="A123">
-            <v>101020</v>
+            <v>101010</v>
           </cell>
           <cell r="B123" t="str">
-            <v>ボレアス</v>
+            <v>エウロス</v>
           </cell>
         </row>
         <row r="124">
           <cell r="A124">
-            <v>101110</v>
+            <v>101020</v>
           </cell>
           <cell r="B124" t="str">
-            <v>アバランシュ</v>
+            <v>ボレアス</v>
           </cell>
         </row>
         <row r="125">
           <cell r="A125">
-            <v>101120</v>
+            <v>101110</v>
           </cell>
           <cell r="B125" t="str">
-            <v>ブリザードコフィン</v>
+            <v>アバランシュ</v>
           </cell>
         </row>
         <row r="126">
           <cell r="A126">
-            <v>200210</v>
+            <v>101120</v>
           </cell>
           <cell r="B126" t="str">
-            <v>マイトレインフォース</v>
+            <v>ブリザードコフィン</v>
           </cell>
         </row>
         <row r="127">
           <cell r="A127">
-            <v>200220</v>
+            <v>200210</v>
           </cell>
           <cell r="B127" t="str">
-            <v>カタストロフィ</v>
+            <v>マイトレインフォース</v>
           </cell>
         </row>
         <row r="128">
           <cell r="A128">
-            <v>200230</v>
+            <v>200220</v>
           </cell>
           <cell r="B128" t="str">
-            <v>悪魔(ベリト)</v>
+            <v>カタストロフィ</v>
           </cell>
         </row>
         <row r="129">
           <cell r="A129">
-            <v>200310</v>
+            <v>200230</v>
           </cell>
           <cell r="B129" t="str">
-            <v>プルガシオン</v>
+            <v>悪魔(ベリト)</v>
           </cell>
         </row>
         <row r="130">
           <cell r="A130">
-            <v>200320</v>
+            <v>200310</v>
           </cell>
           <cell r="B130" t="str">
-            <v>プリエステス</v>
+            <v>プルガシオン</v>
           </cell>
         </row>
         <row r="131">
           <cell r="A131">
-            <v>200330</v>
+            <v>200320</v>
           </cell>
           <cell r="B131" t="str">
-            <v>悪魔(パイモン)</v>
+            <v>プリエステス</v>
           </cell>
         </row>
         <row r="132">
           <cell r="A132">
-            <v>200410</v>
+            <v>200330</v>
           </cell>
           <cell r="B132" t="str">
-            <v>コウソクテンショウ</v>
+            <v>悪魔(パイモン)</v>
           </cell>
         </row>
         <row r="133">
           <cell r="A133">
-            <v>200411</v>
+            <v>200410</v>
           </cell>
           <cell r="B133" t="str">
             <v>コウソクテンショウ</v>
@@ -2163,905 +2163,913 @@
         </row>
         <row r="134">
           <cell r="A134">
-            <v>200420</v>
+            <v>200411</v>
           </cell>
           <cell r="B134" t="str">
-            <v>アンチバフ</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="135">
           <cell r="A135">
-            <v>200430</v>
+            <v>200420</v>
           </cell>
           <cell r="B135" t="str">
-            <v>悪魔(アンドラス)</v>
+            <v>アンチバフ</v>
           </cell>
         </row>
         <row r="136">
           <cell r="A136">
-            <v>200510</v>
+            <v>200430</v>
           </cell>
           <cell r="B136" t="str">
-            <v>カウントダウン</v>
+            <v>悪魔(アンドラス)</v>
           </cell>
         </row>
         <row r="137">
           <cell r="A137">
-            <v>200520</v>
+            <v>200510</v>
           </cell>
           <cell r="B137" t="str">
-            <v>グラウンドゼロ</v>
+            <v>カウントダウン</v>
           </cell>
         </row>
         <row r="138">
           <cell r="A138">
-            <v>200530</v>
+            <v>200520</v>
           </cell>
           <cell r="B138" t="str">
-            <v>悪魔(ビフロンス)</v>
+            <v>グラウンドゼロ</v>
           </cell>
         </row>
         <row r="139">
           <cell r="A139">
-            <v>201010</v>
+            <v>200530</v>
           </cell>
           <cell r="B139" t="str">
-            <v>カオスペイン</v>
+            <v>悪魔(ビフロンス)</v>
           </cell>
         </row>
         <row r="140">
           <cell r="A140">
-            <v>201020</v>
+            <v>201010</v>
           </cell>
           <cell r="B140" t="str">
-            <v>フォールンワン</v>
+            <v>カオスペイン</v>
           </cell>
         </row>
         <row r="141">
           <cell r="A141">
-            <v>201030</v>
+            <v>201020</v>
           </cell>
           <cell r="B141" t="str">
-            <v>アンリマユ</v>
+            <v>フォールンワン</v>
           </cell>
         </row>
         <row r="142">
           <cell r="A142">
-            <v>300010</v>
+            <v>201030</v>
           </cell>
           <cell r="B142" t="str">
-            <v>ライフブースト</v>
+            <v>アンリマユ</v>
           </cell>
         </row>
         <row r="143">
           <cell r="A143">
-            <v>300020</v>
+            <v>300010</v>
           </cell>
           <cell r="B143" t="str">
-            <v>スピリットチャージ</v>
+            <v>ライフブースト</v>
           </cell>
         </row>
         <row r="144">
           <cell r="A144">
-            <v>300030</v>
+            <v>300020</v>
           </cell>
           <cell r="B144" t="str">
-            <v>フォースライズ</v>
+            <v>スピリットチャージ</v>
           </cell>
         </row>
         <row r="145">
           <cell r="A145">
-            <v>300040</v>
+            <v>300030</v>
           </cell>
           <cell r="B145" t="str">
-            <v>ディフェンスオーラ</v>
+            <v>フォースライズ</v>
           </cell>
         </row>
         <row r="146">
           <cell r="A146">
-            <v>300050</v>
+            <v>300040</v>
           </cell>
           <cell r="B146" t="str">
-            <v>ラピッドムーブ</v>
+            <v>ディフェンスオーラ</v>
           </cell>
         </row>
         <row r="147">
           <cell r="A147">
-            <v>300130</v>
+            <v>300050</v>
           </cell>
           <cell r="B147" t="str">
-            <v>アタックブレイク</v>
+            <v>ラピッドムーブ</v>
           </cell>
         </row>
         <row r="148">
           <cell r="A148">
-            <v>300140</v>
+            <v>300130</v>
           </cell>
           <cell r="B148" t="str">
-            <v>シールドバニッシュ</v>
+            <v>アタックブレイク</v>
           </cell>
         </row>
         <row r="149">
           <cell r="A149">
-            <v>300210</v>
+            <v>300140</v>
           </cell>
           <cell r="B149" t="str">
-            <v>エーテルリチャージ</v>
+            <v>シールドバニッシュ</v>
           </cell>
         </row>
         <row r="150">
           <cell r="A150">
-            <v>300220</v>
+            <v>300210</v>
           </cell>
           <cell r="B150" t="str">
-            <v>リカバリーエンハンス</v>
+            <v>エーテルリチャージ</v>
           </cell>
         </row>
         <row r="151">
           <cell r="A151">
-            <v>300230</v>
+            <v>300220</v>
           </cell>
           <cell r="B151" t="str">
-            <v>ヴェンジェンス</v>
+            <v>リカバリーエンハンス</v>
           </cell>
         </row>
         <row r="152">
           <cell r="A152">
-            <v>301010</v>
+            <v>300230</v>
           </cell>
           <cell r="B152" t="str">
-            <v>ディケイドリセット</v>
+            <v>ヴェンジェンス</v>
           </cell>
         </row>
         <row r="153">
           <cell r="A153">
-            <v>301020</v>
+            <v>301010</v>
           </cell>
           <cell r="B153" t="str">
-            <v>ウォーリアーブラッド</v>
+            <v>ディケイドリセット</v>
           </cell>
         </row>
         <row r="154">
           <cell r="A154">
-            <v>301030</v>
+            <v>301020</v>
           </cell>
           <cell r="B154" t="str">
-            <v>トライアングルガード</v>
+            <v>ウォーリアーブラッド</v>
           </cell>
         </row>
         <row r="155">
           <cell r="A155">
-            <v>301040</v>
+            <v>301030</v>
           </cell>
           <cell r="B155" t="str">
-            <v>セーフティバリア</v>
+            <v>トライアングルガード</v>
           </cell>
         </row>
         <row r="156">
           <cell r="A156">
-            <v>301050</v>
+            <v>301040</v>
           </cell>
           <cell r="B156" t="str">
-            <v>ヒロインズハイ</v>
+            <v>セーフティバリア</v>
           </cell>
         </row>
         <row r="157">
           <cell r="A157">
-            <v>301060</v>
+            <v>301050</v>
           </cell>
           <cell r="B157" t="str">
-            <v>セカンドステージ</v>
+            <v>ヒロインズハイ</v>
           </cell>
         </row>
         <row r="158">
           <cell r="A158">
-            <v>301070</v>
+            <v>301060</v>
           </cell>
           <cell r="B158" t="str">
-            <v>ハイヒットポイント</v>
+            <v>セカンドステージ</v>
           </cell>
         </row>
         <row r="159">
           <cell r="A159">
-            <v>301080</v>
+            <v>301070</v>
           </cell>
           <cell r="B159" t="str">
-            <v>セプタブラスト</v>
+            <v>ハイヒットポイント</v>
           </cell>
         </row>
         <row r="160">
           <cell r="A160">
-            <v>301090</v>
+            <v>301080</v>
           </cell>
           <cell r="B160" t="str">
-            <v>イニシャルブロッカー</v>
+            <v>セプタブラスト</v>
           </cell>
         </row>
         <row r="161">
           <cell r="A161">
-            <v>301100</v>
+            <v>301090</v>
           </cell>
           <cell r="B161" t="str">
-            <v>ファーストテイク</v>
+            <v>イニシャルブロッカー</v>
           </cell>
         </row>
         <row r="162">
           <cell r="A162">
-            <v>401010</v>
+            <v>301100</v>
           </cell>
           <cell r="B162" t="str">
-            <v>ファイアボール+</v>
+            <v>ファーストテイク</v>
           </cell>
         </row>
         <row r="163">
           <cell r="A163">
-            <v>401020</v>
+            <v>401010</v>
           </cell>
           <cell r="B163" t="str">
-            <v>バーンストーム+</v>
+            <v>ファイアボール+</v>
           </cell>
         </row>
         <row r="164">
           <cell r="A164">
-            <v>401030</v>
+            <v>401020</v>
           </cell>
           <cell r="B164" t="str">
-            <v>ヒートスタンプ+</v>
+            <v>バーンストーム+</v>
           </cell>
         </row>
         <row r="165">
           <cell r="A165">
-            <v>401040</v>
+            <v>401030</v>
           </cell>
           <cell r="B165" t="str">
-            <v>ソードアダプト+</v>
+            <v>ヒートスタンプ+</v>
           </cell>
         </row>
         <row r="166">
           <cell r="A166">
-            <v>401050</v>
+            <v>401040</v>
           </cell>
           <cell r="B166" t="str">
-            <v>フレイムレイン+</v>
+            <v>ソードアダプト+</v>
           </cell>
         </row>
         <row r="167">
           <cell r="A167">
-            <v>401060</v>
+            <v>401050</v>
           </cell>
           <cell r="B167" t="str">
-            <v>イクスティンクション+</v>
+            <v>フレイムレイン+</v>
           </cell>
         </row>
         <row r="168">
           <cell r="A168">
-            <v>401070</v>
+            <v>401060</v>
           </cell>
           <cell r="B168" t="str">
-            <v>バーニングソウル+</v>
+            <v>イクスティンクション+</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169">
-            <v>401080</v>
+            <v>401070</v>
           </cell>
           <cell r="B169" t="str">
-            <v>レイジングバウンサー+</v>
+            <v>バーニングソウル+</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170">
-            <v>402010</v>
+            <v>401080</v>
           </cell>
           <cell r="B170" t="str">
-            <v>ディスチャージ+</v>
+            <v>レイジングバウンサー+</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171">
-            <v>402020</v>
+            <v>402010</v>
           </cell>
           <cell r="B171" t="str">
-            <v>イベイドコード+</v>
+            <v>ディスチャージ+</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172">
-            <v>402030</v>
+            <v>402020</v>
           </cell>
           <cell r="B172" t="str">
-            <v>ショックインパルス+</v>
+            <v>イベイドコード+</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173">
-            <v>402040</v>
+            <v>402030</v>
           </cell>
           <cell r="B173" t="str">
-            <v>トラストチェイン+</v>
+            <v>ショックインパルス+</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174">
-            <v>402050</v>
+            <v>402040</v>
           </cell>
           <cell r="B174" t="str">
-            <v>スペルバニシング+</v>
+            <v>トラストチェイン+</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175">
-            <v>402060</v>
+            <v>402050</v>
           </cell>
           <cell r="B175" t="str">
-            <v>アーテニーストライク+</v>
+            <v>スペルバニシング+</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176">
-            <v>402070</v>
+            <v>402060</v>
           </cell>
           <cell r="B176" t="str">
-            <v>コンセントレイト+</v>
+            <v>アーテニーストライク+</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177">
-            <v>402080</v>
+            <v>402070</v>
           </cell>
           <cell r="B177" t="str">
-            <v>ディレイマジック+</v>
+            <v>コンセントレイト+</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178">
-            <v>403010</v>
+            <v>402080</v>
           </cell>
           <cell r="B178" t="str">
-            <v>アイスブレイド+</v>
+            <v>ディレイマジック+</v>
           </cell>
         </row>
         <row r="179">
           <cell r="A179">
-            <v>403020</v>
+            <v>403010</v>
           </cell>
           <cell r="B179" t="str">
-            <v>カウンターオーラ+</v>
+            <v>アイスブレイド+</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180">
-            <v>403030</v>
+            <v>403020</v>
           </cell>
           <cell r="B180" t="str">
-            <v>ラインプロテクト+</v>
+            <v>カウンターオーラ+</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181">
-            <v>403040</v>
+            <v>403030</v>
           </cell>
           <cell r="B181" t="str">
-            <v>エスコートソール+</v>
+            <v>ラインプロテクト+</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182">
-            <v>403050</v>
+            <v>403040</v>
           </cell>
           <cell r="B182" t="str">
-            <v>ディープフリーズ+</v>
+            <v>エスコートソール+</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183">
-            <v>403060</v>
+            <v>403050</v>
           </cell>
           <cell r="B183" t="str">
-            <v>バブルブロウ+</v>
+            <v>ディープフリーズ+</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184">
-            <v>403070</v>
+            <v>403060</v>
           </cell>
           <cell r="B184" t="str">
-            <v>アクアミラージュ+</v>
+            <v>バブルブロウ+</v>
           </cell>
         </row>
         <row r="185">
           <cell r="A185">
-            <v>403080</v>
+            <v>403070</v>
           </cell>
           <cell r="B185" t="str">
-            <v>フロストシールド+</v>
+            <v>アクアミラージュ+</v>
           </cell>
         </row>
         <row r="186">
           <cell r="A186">
-            <v>404010</v>
+            <v>403080</v>
           </cell>
           <cell r="B186" t="str">
-            <v>セイントレーザー+</v>
+            <v>フロストシールド+</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187">
-            <v>404020</v>
+            <v>404010</v>
           </cell>
           <cell r="B187" t="str">
-            <v>ペネトレイト+</v>
+            <v>セイントレーザー+</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188">
-            <v>404030</v>
+            <v>404020</v>
           </cell>
           <cell r="B188" t="str">
-            <v>ヒーリング+</v>
+            <v>ペネトレイト+</v>
           </cell>
         </row>
         <row r="189">
           <cell r="A189">
-            <v>404040</v>
+            <v>404030</v>
           </cell>
           <cell r="B189" t="str">
-            <v>リザイアフォトン+</v>
+            <v>ヒーリング+</v>
           </cell>
         </row>
         <row r="190">
           <cell r="A190">
-            <v>404050</v>
+            <v>404040</v>
           </cell>
           <cell r="B190" t="str">
-            <v>べネディクション+</v>
+            <v>リザイアフォトン+</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191">
-            <v>404060</v>
+            <v>404050</v>
           </cell>
           <cell r="B191" t="str">
-            <v>ホーリーグレイス+</v>
+            <v>べネディクション+</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192">
-            <v>404070</v>
+            <v>404060</v>
           </cell>
           <cell r="B192" t="str">
-            <v>キュアエール+</v>
+            <v>ホーリーグレイス+</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193">
-            <v>404080</v>
+            <v>404070</v>
           </cell>
           <cell r="B193" t="str">
-            <v>ラインバリア+</v>
+            <v>キュアエール+</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194">
-            <v>405010</v>
+            <v>404080</v>
           </cell>
           <cell r="B194" t="str">
-            <v>ダークプリズン+</v>
+            <v>ラインバリア+</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195">
-            <v>405020</v>
+            <v>405010</v>
           </cell>
           <cell r="B195" t="str">
-            <v>ユーサネイジア+</v>
+            <v>ダークプリズン+</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196">
-            <v>405030</v>
+            <v>405020</v>
           </cell>
           <cell r="B196" t="str">
-            <v>ドレインヒール+</v>
+            <v>ユーサネイジア+</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197">
-            <v>405040</v>
+            <v>405030</v>
           </cell>
           <cell r="B197" t="str">
-            <v>アビサルデスペア+</v>
+            <v>ドレインヒール+</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198">
-            <v>405050</v>
+            <v>405040</v>
           </cell>
           <cell r="B198" t="str">
-            <v>ディプラヴィティ+</v>
+            <v>アビサルデスペア+</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199">
-            <v>405060</v>
+            <v>405050</v>
           </cell>
           <cell r="B199" t="str">
-            <v>ダークネス+</v>
+            <v>ディプラヴィティ+</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200">
-            <v>405070</v>
+            <v>405060</v>
           </cell>
           <cell r="B200" t="str">
-            <v>シェイディークラウド+</v>
+            <v>ダークネス+</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201">
-            <v>405080</v>
+            <v>405070</v>
           </cell>
           <cell r="B201" t="str">
-            <v>ポイズンブロウ+</v>
+            <v>シェイディークラウド+</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202">
-            <v>411010</v>
+            <v>405080</v>
           </cell>
           <cell r="B202" t="str">
-            <v>ウルフソウル+</v>
+            <v>ポイズンブロウ+</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203">
-            <v>411020</v>
+            <v>411010</v>
           </cell>
           <cell r="B203" t="str">
-            <v>プリディカメント+</v>
+            <v>ウルフソウル+</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204">
-            <v>411030</v>
+            <v>411020</v>
           </cell>
           <cell r="B204" t="str">
-            <v>アサルトシフト+</v>
+            <v>プリディカメント+</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205">
-            <v>411040</v>
+            <v>411030</v>
           </cell>
           <cell r="B205" t="str">
-            <v>アクティブギフト+</v>
+            <v>アサルトシフト+</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206">
-            <v>411050</v>
+            <v>411040</v>
           </cell>
           <cell r="B206" t="str">
-            <v>イグナイテッド+</v>
+            <v>アクティブギフト+</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207">
-            <v>411060</v>
+            <v>411050</v>
           </cell>
           <cell r="B207" t="str">
-            <v>ライジングファイア+</v>
+            <v>イグナイテッド+</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208">
-            <v>411070</v>
+            <v>411060</v>
           </cell>
           <cell r="B208" t="str">
-            <v>ルージュバック+</v>
+            <v>ライジングファイア+</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209">
-            <v>411080</v>
+            <v>411070</v>
           </cell>
           <cell r="B209" t="str">
-            <v>パワーエール+</v>
+            <v>ルージュバック+</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210">
-            <v>411090</v>
+            <v>411080</v>
           </cell>
           <cell r="B210" t="str">
-            <v>スレイプニル+</v>
+            <v>パワーエール+</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211">
-            <v>412010</v>
+            <v>411090</v>
           </cell>
           <cell r="B211" t="str">
-            <v>エクステンション+</v>
+            <v>スレイプニル+</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212">
-            <v>412020</v>
+            <v>412010</v>
           </cell>
           <cell r="B212" t="str">
-            <v>ヘブンリーラック+</v>
+            <v>エクステンション+</v>
           </cell>
         </row>
         <row r="213">
           <cell r="A213">
-            <v>412030</v>
+            <v>412020</v>
           </cell>
           <cell r="B213" t="str">
-            <v>スウィフトカレント+</v>
+            <v>ヘブンリーラック+</v>
           </cell>
         </row>
         <row r="214">
           <cell r="A214">
-            <v>412040</v>
+            <v>412030</v>
           </cell>
           <cell r="B214" t="str">
-            <v>イヴェイドオール+</v>
+            <v>スウィフトカレント+</v>
           </cell>
         </row>
         <row r="215">
           <cell r="A215">
-            <v>412050</v>
+            <v>412040</v>
           </cell>
           <cell r="B215" t="str">
-            <v>クイックムーブ+</v>
+            <v>イヴェイドオール+</v>
           </cell>
         </row>
         <row r="216">
           <cell r="A216">
-            <v>412060</v>
+            <v>412050</v>
           </cell>
           <cell r="B216" t="str">
-            <v>チェイスマジック+</v>
+            <v>クイックムーブ+</v>
           </cell>
         </row>
         <row r="217">
           <cell r="A217">
-            <v>412070</v>
+            <v>412060</v>
           </cell>
           <cell r="B217" t="str">
-            <v>ソーサリーコネクト+</v>
+            <v>チェイスマジック+</v>
           </cell>
         </row>
         <row r="218">
           <cell r="A218">
-            <v>412080</v>
+            <v>412070</v>
           </cell>
           <cell r="B218" t="str">
-            <v>ウィンドライズ+</v>
+            <v>ソーサリーコネクト+</v>
           </cell>
         </row>
         <row r="219">
           <cell r="A219">
-            <v>412090</v>
+            <v>412080</v>
           </cell>
           <cell r="B219" t="str">
-            <v>アウトオブオーダー+</v>
+            <v>ウィンドライズ+</v>
           </cell>
         </row>
         <row r="220">
           <cell r="A220">
-            <v>413010</v>
+            <v>412090</v>
           </cell>
           <cell r="B220" t="str">
-            <v>アーマーコード+</v>
+            <v>アウトオブオーダー+</v>
           </cell>
         </row>
         <row r="221">
           <cell r="A221">
-            <v>413020</v>
+            <v>413010</v>
           </cell>
           <cell r="B221" t="str">
-            <v>クイックバリア+</v>
+            <v>アーマーコード+</v>
           </cell>
         </row>
         <row r="222">
           <cell r="A222">
-            <v>413030</v>
+            <v>413020</v>
           </cell>
           <cell r="B222" t="str">
-            <v>クイックキュア+</v>
+            <v>クイックバリア+</v>
           </cell>
         </row>
         <row r="223">
           <cell r="A223">
-            <v>413040</v>
+            <v>413030</v>
           </cell>
           <cell r="B223" t="str">
-            <v>セルフシールド+</v>
+            <v>クイックキュア+</v>
           </cell>
         </row>
         <row r="224">
           <cell r="A224">
-            <v>413050</v>
+            <v>413040</v>
           </cell>
           <cell r="B224" t="str">
-            <v>パッシブジャミング+</v>
+            <v>セルフシールド+</v>
           </cell>
         </row>
         <row r="225">
           <cell r="A225">
-            <v>413060</v>
+            <v>413050</v>
           </cell>
           <cell r="B225" t="str">
-            <v>サプライカバー+</v>
+            <v>パッシブジャミング+</v>
           </cell>
         </row>
         <row r="226">
           <cell r="A226">
-            <v>413070</v>
+            <v>413060</v>
           </cell>
           <cell r="B226" t="str">
-            <v>アシッドラッシュ+</v>
+            <v>サプライカバー+</v>
           </cell>
         </row>
         <row r="227">
           <cell r="A227">
-            <v>413080</v>
+            <v>413070</v>
           </cell>
           <cell r="B227" t="str">
-            <v>ライフスティール+</v>
+            <v>アシッドラッシュ+</v>
           </cell>
         </row>
         <row r="228">
           <cell r="A228">
-            <v>413090</v>
+            <v>413080</v>
           </cell>
           <cell r="B228" t="str">
-            <v>アイスセイバー+</v>
+            <v>ライフスティール+</v>
           </cell>
         </row>
         <row r="229">
           <cell r="A229">
-            <v>414010</v>
+            <v>413090</v>
           </cell>
           <cell r="B229" t="str">
-            <v>ディバインシールド+</v>
+            <v>アイスセイバー+</v>
           </cell>
         </row>
         <row r="230">
           <cell r="A230">
-            <v>414020</v>
+            <v>414010</v>
           </cell>
           <cell r="B230" t="str">
-            <v>ライフディバイド+</v>
+            <v>ディバインシールド+</v>
           </cell>
         </row>
         <row r="231">
           <cell r="A231">
-            <v>414030</v>
+            <v>414020</v>
           </cell>
           <cell r="B231" t="str">
-            <v>エイミングスコープ+</v>
+            <v>ライフディバイド+</v>
           </cell>
         </row>
         <row r="232">
           <cell r="A232">
-            <v>414040</v>
+            <v>414030</v>
           </cell>
           <cell r="B232" t="str">
-            <v>リジェネレーション+</v>
+            <v>エイミングスコープ+</v>
           </cell>
         </row>
         <row r="233">
           <cell r="A233">
-            <v>414050</v>
+            <v>414040</v>
           </cell>
           <cell r="B233" t="str">
-            <v>ホープフルアイリス+</v>
+            <v>リジェネレーション+</v>
           </cell>
         </row>
         <row r="234">
           <cell r="A234">
-            <v>414060</v>
+            <v>414050</v>
           </cell>
           <cell r="B234" t="str">
-            <v>パッシブサプライ+</v>
+            <v>ホープフルアイリス+</v>
           </cell>
         </row>
         <row r="235">
           <cell r="A235">
-            <v>414070</v>
+            <v>414060</v>
           </cell>
           <cell r="B235" t="str">
-            <v>ホーミングクルセイド+</v>
+            <v>パッシブサプライ+</v>
           </cell>
         </row>
         <row r="236">
           <cell r="A236">
-            <v>414080</v>
+            <v>414070</v>
           </cell>
           <cell r="B236" t="str">
-            <v>クイックヒール+</v>
+            <v>ホーミングクルセイド+</v>
           </cell>
         </row>
         <row r="237">
           <cell r="A237">
-            <v>414090</v>
+            <v>414080</v>
           </cell>
           <cell r="B237" t="str">
-            <v>リレイズ+</v>
+            <v>クイックヒール+</v>
           </cell>
         </row>
         <row r="238">
           <cell r="A238">
-            <v>415010</v>
+            <v>414090</v>
           </cell>
           <cell r="B238" t="str">
-            <v>イーグルアイ+</v>
+            <v>リレイズ+</v>
           </cell>
         </row>
         <row r="239">
           <cell r="A239">
-            <v>415020</v>
+            <v>415010</v>
           </cell>
           <cell r="B239" t="str">
-            <v>ネヴァーエンド+</v>
+            <v>イーグルアイ+</v>
           </cell>
         </row>
         <row r="240">
           <cell r="A240">
-            <v>415030</v>
+            <v>415020</v>
           </cell>
           <cell r="B240" t="str">
-            <v>グレイブアクト+</v>
+            <v>ネヴァーエンド+</v>
           </cell>
         </row>
         <row r="241">
           <cell r="A241">
-            <v>415040</v>
+            <v>415030</v>
           </cell>
           <cell r="B241" t="str">
-            <v>スカルグラッジ+</v>
+            <v>グレイブアクト+</v>
           </cell>
         </row>
         <row r="242">
           <cell r="A242">
-            <v>415050</v>
+            <v>415040</v>
           </cell>
           <cell r="B242" t="str">
-            <v>ネガティブドレイン+</v>
+            <v>スカルグラッジ+</v>
           </cell>
         </row>
         <row r="243">
           <cell r="A243">
-            <v>415060</v>
+            <v>415050</v>
           </cell>
           <cell r="B243" t="str">
-            <v>アンデッドペイン+</v>
+            <v>ネガティブドレイン+</v>
           </cell>
         </row>
         <row r="244">
           <cell r="A244">
-            <v>415070</v>
+            <v>415060</v>
           </cell>
           <cell r="B244" t="str">
-            <v>ジャックポッド+</v>
+            <v>アンデッドペイン+</v>
           </cell>
         </row>
         <row r="245">
           <cell r="A245">
-            <v>415080</v>
+            <v>415070</v>
           </cell>
           <cell r="B245" t="str">
-            <v>ヒールハント+</v>
+            <v>ジャックポッド+</v>
           </cell>
         </row>
         <row r="246">
           <cell r="A246">
+            <v>415080</v>
+          </cell>
+          <cell r="B246" t="str">
+            <v>ヒールハント+</v>
+          </cell>
+        </row>
+        <row r="247">
+          <cell r="A247">
             <v>415090</v>
           </cell>
-          <cell r="B246" t="str">
+          <cell r="B247" t="str">
             <v>クイックカース+</v>
           </cell>
         </row>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="7820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -396,8 +396,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -415,8 +415,68 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -438,39 +498,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -485,32 +522,18 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -530,32 +553,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -568,13 +568,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,25 +598,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -622,25 +616,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -658,7 +664,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -670,19 +682,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -700,19 +706,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -724,31 +724,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -759,6 +759,51 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -788,45 +833,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -845,17 +851,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -867,145 +867,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5374,7 +5374,7 @@
         <v>50</v>
       </c>
       <c r="F2">
-        <v>14215</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -6094,7 +6094,7 @@
         <v>50</v>
       </c>
       <c r="F32">
-        <v>14213</v>
+        <v>0</v>
       </c>
       <c r="G32">
         <v>0</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7820"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -415,17 +415,39 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -440,36 +462,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -491,31 +484,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -530,10 +500,10 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -541,6 +511,22 @@
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -553,9 +539,23 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -565,6 +565,60 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -580,7 +634,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -592,19 +688,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -616,31 +712,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -652,43 +736,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -700,55 +748,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -759,6 +759,36 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -777,17 +807,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -807,37 +831,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -853,9 +851,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -867,7 +867,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -876,7 +876,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -885,127 +885,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3467,7 +3467,7 @@
         <v>3</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <v>11</v>
@@ -3526,7 +3526,7 @@
         <v>3</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L3">
         <v>11</v>
@@ -3585,7 +3585,7 @@
         <v>3</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>11</v>
@@ -3644,7 +3644,7 @@
         <v>3</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L5">
         <v>11</v>
@@ -3703,7 +3703,7 @@
         <v>3</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>11</v>
@@ -3762,7 +3762,7 @@
         <v>3</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <v>11</v>
@@ -3880,7 +3880,7 @@
         <v>3</v>
       </c>
       <c r="K9">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L9">
         <v>11</v>
@@ -3939,7 +3939,7 @@
         <v>3</v>
       </c>
       <c r="K10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L10">
         <v>11</v>
@@ -3998,7 +3998,7 @@
         <v>3</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L11">
         <v>11</v>
@@ -4116,7 +4116,7 @@
         <v>3</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L13">
         <v>11</v>
@@ -4175,7 +4175,7 @@
         <v>3</v>
       </c>
       <c r="K14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L14">
         <v>11</v>
@@ -4234,7 +4234,7 @@
         <v>3</v>
       </c>
       <c r="K15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L15">
         <v>11</v>
@@ -4293,7 +4293,7 @@
         <v>3</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L16">
         <v>11</v>
@@ -4340,19 +4340,19 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H17">
+        <v>10</v>
+      </c>
+      <c r="I17">
         <v>20</v>
-      </c>
-      <c r="I17">
-        <v>30</v>
       </c>
       <c r="J17">
         <v>3</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L17">
         <v>12</v>
@@ -4376,7 +4376,7 @@
         <v>20</v>
       </c>
       <c r="S17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4399,13 +4399,13 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H18">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I18">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J18">
         <v>3</v>
@@ -4435,7 +4435,7 @@
         <v>40</v>
       </c>
       <c r="S18" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4458,19 +4458,19 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H19">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I19">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J19">
         <v>3</v>
       </c>
       <c r="K19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>12</v>
@@ -4494,7 +4494,7 @@
         <v>30</v>
       </c>
       <c r="S19" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4517,19 +4517,19 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="H20">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I20">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J20">
         <v>3</v>
       </c>
       <c r="K20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20">
         <v>12</v>
@@ -4553,7 +4553,7 @@
         <v>50</v>
       </c>
       <c r="S20" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4576,19 +4576,19 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H21">
         <v>20</v>
       </c>
       <c r="I21">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J21">
         <v>3</v>
       </c>
       <c r="K21">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L21">
         <v>12</v>
@@ -4612,7 +4612,7 @@
         <v>15</v>
       </c>
       <c r="S21" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -4635,7 +4635,7 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H22">
         <v>20</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -394,10 +394,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -415,15 +415,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -437,17 +431,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -468,6 +453,66 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -477,9 +522,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -499,59 +552,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -568,7 +568,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,102 +724,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -694,61 +736,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -759,21 +759,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -793,40 +778,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -859,6 +820,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -867,16 +867,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -885,127 +885,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3567,7 +3567,7 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -3579,7 +3579,7 @@
         <v>6</v>
       </c>
       <c r="I4">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="J4">
         <v>3</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -394,9 +394,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -415,9 +415,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -432,37 +438,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -470,14 +453,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -491,8 +467,16 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -506,8 +490,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -521,15 +506,15 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -545,10 +530,25 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -568,7 +568,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,7 +586,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -598,7 +604,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -610,7 +622,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -622,13 +634,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -640,19 +652,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -670,7 +670,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -682,7 +682,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -694,31 +736,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -730,25 +748,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -762,17 +762,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -788,35 +791,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -855,6 +829,32 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -867,145 +867,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1622,7 +1622,7 @@
             <v>12010</v>
           </cell>
           <cell r="B66" t="str">
-            <v>エクステンション</v>
+            <v>コンセントレイト</v>
           </cell>
         </row>
         <row r="67">
@@ -2395,681 +2395,713 @@
         </row>
         <row r="163">
           <cell r="A163">
-            <v>401010</v>
+            <v>310010</v>
           </cell>
           <cell r="B163" t="str">
-            <v>ファイアボール+</v>
+            <v>妖精の祈り</v>
           </cell>
         </row>
         <row r="164">
           <cell r="A164">
-            <v>401020</v>
+            <v>310020</v>
           </cell>
           <cell r="B164" t="str">
-            <v>バーンストーム+</v>
+            <v>月のかけら</v>
           </cell>
         </row>
         <row r="165">
           <cell r="A165">
-            <v>401030</v>
+            <v>310030</v>
           </cell>
           <cell r="B165" t="str">
-            <v>ヒートスタンプ+</v>
+            <v>錬金術師の遺稿</v>
           </cell>
         </row>
         <row r="166">
           <cell r="A166">
-            <v>401040</v>
+            <v>310130</v>
           </cell>
           <cell r="B166" t="str">
-            <v>ソードアダプト+</v>
+            <v>ヒールユニット</v>
           </cell>
         </row>
         <row r="167">
           <cell r="A167">
-            <v>401050</v>
+            <v>401010</v>
           </cell>
           <cell r="B167" t="str">
-            <v>フレイムレイン+</v>
+            <v>ファイアボール+</v>
           </cell>
         </row>
         <row r="168">
           <cell r="A168">
-            <v>401060</v>
+            <v>401020</v>
           </cell>
           <cell r="B168" t="str">
-            <v>イクスティンクション+</v>
+            <v>バーンストーム+</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169">
-            <v>401070</v>
+            <v>401030</v>
           </cell>
           <cell r="B169" t="str">
-            <v>バーニングソウル+</v>
+            <v>ヒートスタンプ+</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170">
-            <v>401080</v>
+            <v>401040</v>
           </cell>
           <cell r="B170" t="str">
-            <v>レイジングバウンサー+</v>
+            <v>ソードアダプト+</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171">
-            <v>402010</v>
+            <v>401050</v>
           </cell>
           <cell r="B171" t="str">
-            <v>ディスチャージ+</v>
+            <v>フレイムレイン+</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172">
-            <v>402020</v>
+            <v>401060</v>
           </cell>
           <cell r="B172" t="str">
-            <v>イベイドコード+</v>
+            <v>イクスティンクション+</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173">
-            <v>402030</v>
+            <v>401070</v>
           </cell>
           <cell r="B173" t="str">
-            <v>ショックインパルス+</v>
+            <v>バーニングソウル+</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174">
-            <v>402040</v>
+            <v>401080</v>
           </cell>
           <cell r="B174" t="str">
-            <v>トラストチェイン+</v>
+            <v>レイジングバウンサー+</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175">
-            <v>402050</v>
+            <v>402010</v>
           </cell>
           <cell r="B175" t="str">
-            <v>スペルバニシング+</v>
+            <v>ディスチャージ+</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176">
-            <v>402060</v>
+            <v>402020</v>
           </cell>
           <cell r="B176" t="str">
-            <v>アーテニーストライク+</v>
+            <v>イベイドコード+</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177">
-            <v>402070</v>
+            <v>402030</v>
           </cell>
           <cell r="B177" t="str">
-            <v>コンセントレイト+</v>
+            <v>ショックインパルス+</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178">
-            <v>402080</v>
+            <v>402040</v>
           </cell>
           <cell r="B178" t="str">
-            <v>ディレイマジック+</v>
+            <v>トラストチェイン+</v>
           </cell>
         </row>
         <row r="179">
           <cell r="A179">
-            <v>403010</v>
+            <v>402050</v>
           </cell>
           <cell r="B179" t="str">
-            <v>アイスブレイド+</v>
+            <v>スペルバニシング+</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180">
-            <v>403020</v>
+            <v>402060</v>
           </cell>
           <cell r="B180" t="str">
-            <v>カウンターオーラ+</v>
+            <v>アーテニーストライク+</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181">
-            <v>403030</v>
+            <v>402070</v>
           </cell>
           <cell r="B181" t="str">
-            <v>ラインプロテクト+</v>
+            <v>コンセントレイト+</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182">
-            <v>403040</v>
+            <v>402080</v>
           </cell>
           <cell r="B182" t="str">
-            <v>エスコートソール+</v>
+            <v>ディレイマジック+</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183">
-            <v>403050</v>
+            <v>403010</v>
           </cell>
           <cell r="B183" t="str">
-            <v>ディープフリーズ+</v>
+            <v>アイスブレイド+</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184">
-            <v>403060</v>
+            <v>403020</v>
           </cell>
           <cell r="B184" t="str">
-            <v>バブルブロウ+</v>
+            <v>カウンターオーラ+</v>
           </cell>
         </row>
         <row r="185">
           <cell r="A185">
-            <v>403070</v>
+            <v>403030</v>
           </cell>
           <cell r="B185" t="str">
-            <v>アクアミラージュ+</v>
+            <v>ラインプロテクト+</v>
           </cell>
         </row>
         <row r="186">
           <cell r="A186">
-            <v>403080</v>
+            <v>403040</v>
           </cell>
           <cell r="B186" t="str">
-            <v>フロストシールド+</v>
+            <v>エスコートソール+</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187">
-            <v>404010</v>
+            <v>403050</v>
           </cell>
           <cell r="B187" t="str">
-            <v>セイントレーザー+</v>
+            <v>ディープフリーズ+</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188">
-            <v>404020</v>
+            <v>403060</v>
           </cell>
           <cell r="B188" t="str">
-            <v>ペネトレイト+</v>
+            <v>バブルブロウ+</v>
           </cell>
         </row>
         <row r="189">
           <cell r="A189">
-            <v>404030</v>
+            <v>403070</v>
           </cell>
           <cell r="B189" t="str">
-            <v>ヒーリング+</v>
+            <v>アクアミラージュ+</v>
           </cell>
         </row>
         <row r="190">
           <cell r="A190">
-            <v>404040</v>
+            <v>403080</v>
           </cell>
           <cell r="B190" t="str">
-            <v>リザイアフォトン+</v>
+            <v>フロストシールド+</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191">
-            <v>404050</v>
+            <v>404010</v>
           </cell>
           <cell r="B191" t="str">
-            <v>べネディクション+</v>
+            <v>セイントレーザー+</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192">
-            <v>404060</v>
+            <v>404020</v>
           </cell>
           <cell r="B192" t="str">
-            <v>ホーリーグレイス+</v>
+            <v>ペネトレイト+</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193">
-            <v>404070</v>
+            <v>404030</v>
           </cell>
           <cell r="B193" t="str">
-            <v>キュアエール+</v>
+            <v>ヒーリング+</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194">
-            <v>404080</v>
+            <v>404040</v>
           </cell>
           <cell r="B194" t="str">
-            <v>ラインバリア+</v>
+            <v>リザイアフォトン+</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195">
-            <v>405010</v>
+            <v>404050</v>
           </cell>
           <cell r="B195" t="str">
-            <v>ダークプリズン+</v>
+            <v>べネディクション+</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196">
-            <v>405020</v>
+            <v>404060</v>
           </cell>
           <cell r="B196" t="str">
-            <v>ユーサネイジア+</v>
+            <v>ホーリーグレイス+</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197">
-            <v>405030</v>
+            <v>404070</v>
           </cell>
           <cell r="B197" t="str">
-            <v>ドレインヒール+</v>
+            <v>キュアエール+</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198">
-            <v>405040</v>
+            <v>404080</v>
           </cell>
           <cell r="B198" t="str">
-            <v>アビサルデスペア+</v>
+            <v>ラインバリア+</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199">
-            <v>405050</v>
+            <v>405010</v>
           </cell>
           <cell r="B199" t="str">
-            <v>ディプラヴィティ+</v>
+            <v>ダークプリズン+</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200">
-            <v>405060</v>
+            <v>405020</v>
           </cell>
           <cell r="B200" t="str">
-            <v>ダークネス+</v>
+            <v>ユーサネイジア+</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201">
-            <v>405070</v>
+            <v>405030</v>
           </cell>
           <cell r="B201" t="str">
-            <v>シェイディークラウド+</v>
+            <v>ドレインヒール+</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202">
-            <v>405080</v>
+            <v>405040</v>
           </cell>
           <cell r="B202" t="str">
-            <v>ポイズンブロウ+</v>
+            <v>アビサルデスペア+</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203">
-            <v>411010</v>
+            <v>405050</v>
           </cell>
           <cell r="B203" t="str">
-            <v>ウルフソウル+</v>
+            <v>ディプラヴィティ+</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204">
-            <v>411020</v>
+            <v>405060</v>
           </cell>
           <cell r="B204" t="str">
-            <v>プリディカメント+</v>
+            <v>ダークネス+</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205">
-            <v>411030</v>
+            <v>405070</v>
           </cell>
           <cell r="B205" t="str">
-            <v>アサルトシフト+</v>
+            <v>シェイディークラウド+</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206">
-            <v>411040</v>
+            <v>405080</v>
           </cell>
           <cell r="B206" t="str">
-            <v>アクティブギフト+</v>
+            <v>ポイズンブロウ+</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207">
-            <v>411050</v>
+            <v>411010</v>
           </cell>
           <cell r="B207" t="str">
-            <v>イグナイテッド+</v>
+            <v>ウルフソウル+</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208">
-            <v>411060</v>
+            <v>411020</v>
           </cell>
           <cell r="B208" t="str">
-            <v>ライジングファイア+</v>
+            <v>プリディカメント+</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209">
-            <v>411070</v>
+            <v>411030</v>
           </cell>
           <cell r="B209" t="str">
-            <v>ルージュバック+</v>
+            <v>アサルトシフト+</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210">
-            <v>411080</v>
+            <v>411040</v>
           </cell>
           <cell r="B210" t="str">
-            <v>パワーエール+</v>
+            <v>アクティブギフト+</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211">
-            <v>411090</v>
+            <v>411050</v>
           </cell>
           <cell r="B211" t="str">
-            <v>スレイプニル+</v>
+            <v>イグナイテッド+</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212">
-            <v>412010</v>
+            <v>411060</v>
           </cell>
           <cell r="B212" t="str">
-            <v>エクステンション+</v>
+            <v>ライジングファイア+</v>
           </cell>
         </row>
         <row r="213">
           <cell r="A213">
-            <v>412020</v>
+            <v>411070</v>
           </cell>
           <cell r="B213" t="str">
-            <v>ヘブンリーラック+</v>
+            <v>ルージュバック+</v>
           </cell>
         </row>
         <row r="214">
           <cell r="A214">
-            <v>412030</v>
+            <v>411080</v>
           </cell>
           <cell r="B214" t="str">
-            <v>スウィフトカレント+</v>
+            <v>パワーエール+</v>
           </cell>
         </row>
         <row r="215">
           <cell r="A215">
-            <v>412040</v>
+            <v>411090</v>
           </cell>
           <cell r="B215" t="str">
-            <v>イヴェイドオール+</v>
+            <v>スレイプニル+</v>
           </cell>
         </row>
         <row r="216">
           <cell r="A216">
-            <v>412050</v>
+            <v>412010</v>
           </cell>
           <cell r="B216" t="str">
-            <v>クイックムーブ+</v>
+            <v>エクステンション+</v>
           </cell>
         </row>
         <row r="217">
           <cell r="A217">
-            <v>412060</v>
+            <v>412020</v>
           </cell>
           <cell r="B217" t="str">
-            <v>チェイスマジック+</v>
+            <v>ヘブンリーラック+</v>
           </cell>
         </row>
         <row r="218">
           <cell r="A218">
-            <v>412070</v>
+            <v>412030</v>
           </cell>
           <cell r="B218" t="str">
-            <v>ソーサリーコネクト+</v>
+            <v>スウィフトカレント+</v>
           </cell>
         </row>
         <row r="219">
           <cell r="A219">
-            <v>412080</v>
+            <v>412040</v>
           </cell>
           <cell r="B219" t="str">
-            <v>ウィンドライズ+</v>
+            <v>イヴェイドオール+</v>
           </cell>
         </row>
         <row r="220">
           <cell r="A220">
-            <v>412090</v>
+            <v>412050</v>
           </cell>
           <cell r="B220" t="str">
-            <v>アウトオブオーダー+</v>
+            <v>クイックムーブ+</v>
           </cell>
         </row>
         <row r="221">
           <cell r="A221">
-            <v>413010</v>
+            <v>412060</v>
           </cell>
           <cell r="B221" t="str">
-            <v>アーマーコード+</v>
+            <v>チェイスマジック+</v>
           </cell>
         </row>
         <row r="222">
           <cell r="A222">
-            <v>413020</v>
+            <v>412070</v>
           </cell>
           <cell r="B222" t="str">
-            <v>クイックバリア+</v>
+            <v>ソーサリーコネクト+</v>
           </cell>
         </row>
         <row r="223">
           <cell r="A223">
-            <v>413030</v>
+            <v>412080</v>
           </cell>
           <cell r="B223" t="str">
-            <v>クイックキュア+</v>
+            <v>ウィンドライズ+</v>
           </cell>
         </row>
         <row r="224">
           <cell r="A224">
-            <v>413040</v>
+            <v>412090</v>
           </cell>
           <cell r="B224" t="str">
-            <v>セルフシールド+</v>
+            <v>アウトオブオーダー+</v>
           </cell>
         </row>
         <row r="225">
           <cell r="A225">
-            <v>413050</v>
+            <v>413010</v>
           </cell>
           <cell r="B225" t="str">
-            <v>パッシブジャミング+</v>
+            <v>アーマーコード+</v>
           </cell>
         </row>
         <row r="226">
           <cell r="A226">
-            <v>413060</v>
+            <v>413020</v>
           </cell>
           <cell r="B226" t="str">
-            <v>サプライカバー+</v>
+            <v>クイックバリア+</v>
           </cell>
         </row>
         <row r="227">
           <cell r="A227">
-            <v>413070</v>
+            <v>413030</v>
           </cell>
           <cell r="B227" t="str">
-            <v>アシッドラッシュ+</v>
+            <v>クイックキュア+</v>
           </cell>
         </row>
         <row r="228">
           <cell r="A228">
-            <v>413080</v>
+            <v>413040</v>
           </cell>
           <cell r="B228" t="str">
-            <v>ライフスティール+</v>
+            <v>セルフシールド+</v>
           </cell>
         </row>
         <row r="229">
           <cell r="A229">
-            <v>413090</v>
+            <v>413050</v>
           </cell>
           <cell r="B229" t="str">
-            <v>アイスセイバー+</v>
+            <v>パッシブジャミング+</v>
           </cell>
         </row>
         <row r="230">
           <cell r="A230">
-            <v>414010</v>
+            <v>413060</v>
           </cell>
           <cell r="B230" t="str">
-            <v>ディバインシールド+</v>
+            <v>サプライカバー+</v>
           </cell>
         </row>
         <row r="231">
           <cell r="A231">
-            <v>414020</v>
+            <v>413070</v>
           </cell>
           <cell r="B231" t="str">
-            <v>ライフディバイド+</v>
+            <v>アシッドラッシュ+</v>
           </cell>
         </row>
         <row r="232">
           <cell r="A232">
-            <v>414030</v>
+            <v>413080</v>
           </cell>
           <cell r="B232" t="str">
-            <v>エイミングスコープ+</v>
+            <v>ライフスティール+</v>
           </cell>
         </row>
         <row r="233">
           <cell r="A233">
-            <v>414040</v>
+            <v>413090</v>
           </cell>
           <cell r="B233" t="str">
-            <v>リジェネレーション+</v>
+            <v>アイスセイバー+</v>
           </cell>
         </row>
         <row r="234">
           <cell r="A234">
-            <v>414050</v>
+            <v>414010</v>
           </cell>
           <cell r="B234" t="str">
-            <v>ホープフルアイリス+</v>
+            <v>ディバインシールド+</v>
           </cell>
         </row>
         <row r="235">
           <cell r="A235">
-            <v>414060</v>
+            <v>414020</v>
           </cell>
           <cell r="B235" t="str">
-            <v>パッシブサプライ+</v>
+            <v>ライフディバイド+</v>
           </cell>
         </row>
         <row r="236">
           <cell r="A236">
-            <v>414070</v>
+            <v>414030</v>
           </cell>
           <cell r="B236" t="str">
-            <v>ホーミングクルセイド+</v>
+            <v>エイミングスコープ+</v>
           </cell>
         </row>
         <row r="237">
           <cell r="A237">
-            <v>414080</v>
+            <v>414040</v>
           </cell>
           <cell r="B237" t="str">
-            <v>クイックヒール+</v>
+            <v>リジェネレーション+</v>
           </cell>
         </row>
         <row r="238">
           <cell r="A238">
-            <v>414090</v>
+            <v>414050</v>
           </cell>
           <cell r="B238" t="str">
-            <v>リレイズ+</v>
+            <v>ホープフルアイリス+</v>
           </cell>
         </row>
         <row r="239">
           <cell r="A239">
-            <v>415010</v>
+            <v>414060</v>
           </cell>
           <cell r="B239" t="str">
-            <v>イーグルアイ+</v>
+            <v>パッシブサプライ+</v>
           </cell>
         </row>
         <row r="240">
           <cell r="A240">
-            <v>415020</v>
+            <v>414070</v>
           </cell>
           <cell r="B240" t="str">
-            <v>ネヴァーエンド+</v>
+            <v>ホーミングクルセイド+</v>
           </cell>
         </row>
         <row r="241">
           <cell r="A241">
-            <v>415030</v>
+            <v>414080</v>
           </cell>
           <cell r="B241" t="str">
-            <v>グレイブアクト+</v>
+            <v>クイックヒール+</v>
           </cell>
         </row>
         <row r="242">
           <cell r="A242">
-            <v>415040</v>
+            <v>414090</v>
           </cell>
           <cell r="B242" t="str">
-            <v>スカルグラッジ+</v>
+            <v>リレイズ+</v>
           </cell>
         </row>
         <row r="243">
           <cell r="A243">
-            <v>415050</v>
+            <v>415010</v>
           </cell>
           <cell r="B243" t="str">
-            <v>ネガティブドレイン+</v>
+            <v>イーグルアイ+</v>
           </cell>
         </row>
         <row r="244">
           <cell r="A244">
-            <v>415060</v>
+            <v>415020</v>
           </cell>
           <cell r="B244" t="str">
-            <v>アンデッドペイン+</v>
+            <v>ネヴァーエンド+</v>
           </cell>
         </row>
         <row r="245">
           <cell r="A245">
-            <v>415070</v>
+            <v>415030</v>
           </cell>
           <cell r="B245" t="str">
-            <v>ジャックポッド+</v>
+            <v>グレイブアクト+</v>
           </cell>
         </row>
         <row r="246">
           <cell r="A246">
-            <v>415080</v>
+            <v>415040</v>
           </cell>
           <cell r="B246" t="str">
-            <v>ヒールハント+</v>
+            <v>スカルグラッジ+</v>
           </cell>
         </row>
         <row r="247">
           <cell r="A247">
+            <v>415050</v>
+          </cell>
+          <cell r="B247" t="str">
+            <v>ネガティブドレイン+</v>
+          </cell>
+        </row>
+        <row r="248">
+          <cell r="A248">
+            <v>415060</v>
+          </cell>
+          <cell r="B248" t="str">
+            <v>アンデッドペイン+</v>
+          </cell>
+        </row>
+        <row r="249">
+          <cell r="A249">
+            <v>415070</v>
+          </cell>
+          <cell r="B249" t="str">
+            <v>ジャックポッド+</v>
+          </cell>
+        </row>
+        <row r="250">
+          <cell r="A250">
+            <v>415080</v>
+          </cell>
+          <cell r="B250" t="str">
+            <v>ヒールハント+</v>
+          </cell>
+        </row>
+        <row r="251">
+          <cell r="A251">
             <v>415090</v>
           </cell>
-          <cell r="B247" t="str">
+          <cell r="B251" t="str">
             <v>クイックカース+</v>
           </cell>
         </row>
@@ -3449,7 +3481,7 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -3626,7 +3658,7 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -3685,7 +3717,7 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -3744,7 +3776,7 @@
         <v>1</v>
       </c>
       <c r="E7">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -7909,7 +7941,7 @@
       </c>
       <c r="C108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B108,[1]TextData!A:A))</f>
-        <v>エクステンション</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -8077,7 +8109,7 @@
       </c>
       <c r="C115" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B115,[1]TextData!A:A))</f>
-        <v>エクステンション</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -8317,7 +8349,7 @@
       </c>
       <c r="C125" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B125,[1]TextData!A:A))</f>
-        <v>エクステンション</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -9949,7 +9981,7 @@
       </c>
       <c r="C193" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B193,[1]TextData!A:A))</f>
-        <v>エクステンション</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D193">
         <v>1</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="7820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -394,10 +394,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -423,20 +423,36 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -444,23 +460,37 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -474,17 +504,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -492,38 +513,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -538,24 +536,26 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -568,7 +568,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,13 +658,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -598,25 +682,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -634,121 +730,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -762,20 +762,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -795,32 +792,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -828,8 +804,19 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -851,11 +838,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -867,145 +867,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5526,7 +5526,7 @@
         <v>50</v>
       </c>
       <c r="F7">
-        <v>1161</v>
+        <v>0</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -5766,7 +5766,7 @@
         <v>50</v>
       </c>
       <c r="F17">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -6006,7 +6006,7 @@
         <v>100</v>
       </c>
       <c r="F27">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -6366,7 +6366,7 @@
         <v>50</v>
       </c>
       <c r="F42">
-        <v>5062</v>
+        <v>0</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -6726,7 +6726,7 @@
         <v>50</v>
       </c>
       <c r="F57">
-        <v>14211</v>
+        <v>0</v>
       </c>
       <c r="G57">
         <v>0</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -394,10 +394,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -415,8 +415,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -429,19 +445,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -453,8 +476,16 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -469,13 +500,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -483,7 +507,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -497,31 +521,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -536,26 +537,25 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -568,7 +568,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,79 +736,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -664,91 +748,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -762,17 +762,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -792,11 +795,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -810,13 +819,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -838,24 +851,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -867,145 +867,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1915,1193 +1915,1209 @@
         </row>
         <row r="103">
           <cell r="A103">
-            <v>100110</v>
+            <v>30010</v>
           </cell>
           <cell r="B103" t="str">
-            <v>ソーイングアームド</v>
+            <v>ラーニングピアス</v>
           </cell>
         </row>
         <row r="104">
           <cell r="A104">
-            <v>100120</v>
+            <v>30020</v>
           </cell>
           <cell r="B104" t="str">
-            <v>エターナルロンド</v>
+            <v>スティールヒール</v>
           </cell>
         </row>
         <row r="105">
           <cell r="A105">
-            <v>100210</v>
+            <v>100110</v>
           </cell>
           <cell r="B105" t="str">
-            <v>アブソリュートパリィ</v>
+            <v>ソーイングアームド</v>
           </cell>
         </row>
         <row r="106">
           <cell r="A106">
-            <v>100220</v>
+            <v>100120</v>
           </cell>
           <cell r="B106" t="str">
-            <v>レヴェリー</v>
+            <v>エターナルロンド</v>
           </cell>
         </row>
         <row r="107">
           <cell r="A107">
-            <v>100310</v>
+            <v>100210</v>
           </cell>
           <cell r="B107" t="str">
-            <v>セイクリッドバリア</v>
+            <v>アブソリュートパリィ</v>
           </cell>
         </row>
         <row r="108">
           <cell r="A108">
-            <v>100320</v>
+            <v>100220</v>
           </cell>
           <cell r="B108" t="str">
-            <v>リベンジニードル</v>
+            <v>レヴェリー</v>
           </cell>
         </row>
         <row r="109">
           <cell r="A109">
-            <v>100410</v>
+            <v>100310</v>
           </cell>
           <cell r="B109" t="str">
-            <v>アバンデンス</v>
+            <v>セイクリッドバリア</v>
           </cell>
         </row>
         <row r="110">
           <cell r="A110">
-            <v>100420</v>
+            <v>100320</v>
           </cell>
           <cell r="B110" t="str">
-            <v>ハーヴェスト</v>
+            <v>リベンジニードル</v>
           </cell>
         </row>
         <row r="111">
           <cell r="A111">
-            <v>100510</v>
+            <v>100410</v>
           </cell>
           <cell r="B111" t="str">
-            <v>カースドブレイク</v>
+            <v>アバンデンス</v>
           </cell>
         </row>
         <row r="112">
           <cell r="A112">
-            <v>100520</v>
+            <v>100420</v>
           </cell>
           <cell r="B112" t="str">
-            <v>ムーンライトレイ</v>
+            <v>ハーヴェスト</v>
           </cell>
         </row>
         <row r="113">
           <cell r="A113">
-            <v>100610</v>
+            <v>100510</v>
           </cell>
           <cell r="B113" t="str">
-            <v>サンフレイム</v>
+            <v>カースドブレイク</v>
           </cell>
         </row>
         <row r="114">
           <cell r="A114">
-            <v>100620</v>
+            <v>100520</v>
           </cell>
           <cell r="B114" t="str">
-            <v>フレイムタン</v>
+            <v>ムーンライトレイ</v>
           </cell>
         </row>
         <row r="115">
           <cell r="A115">
-            <v>100710</v>
+            <v>100610</v>
           </cell>
           <cell r="B115" t="str">
-            <v>ライズザフラッグ</v>
+            <v>サンフレイム</v>
           </cell>
         </row>
         <row r="116">
           <cell r="A116">
-            <v>100720</v>
+            <v>100620</v>
           </cell>
           <cell r="B116" t="str">
-            <v>オーバーリミット</v>
+            <v>フレイムタン</v>
           </cell>
         </row>
         <row r="117">
           <cell r="A117">
-            <v>100810</v>
+            <v>100710</v>
           </cell>
           <cell r="B117" t="str">
-            <v>テンパランス</v>
+            <v>ライズザフラッグ</v>
           </cell>
         </row>
         <row r="118">
           <cell r="A118">
-            <v>100820</v>
+            <v>100720</v>
           </cell>
           <cell r="B118" t="str">
-            <v>シエルクルセイダー</v>
+            <v>オーバーリミット</v>
           </cell>
         </row>
         <row r="119">
           <cell r="A119">
-            <v>100910</v>
+            <v>100810</v>
           </cell>
           <cell r="B119" t="str">
-            <v>バーニングカウンター</v>
+            <v>テンパランス</v>
           </cell>
         </row>
         <row r="120">
           <cell r="A120">
-            <v>100911</v>
+            <v>100820</v>
           </cell>
           <cell r="B120" t="str">
-            <v>バーニングカウンター</v>
+            <v>シエルクルセイダー</v>
           </cell>
         </row>
         <row r="121">
           <cell r="A121">
-            <v>100920</v>
+            <v>100910</v>
           </cell>
           <cell r="B121" t="str">
-            <v>プロミネンス</v>
+            <v>バーニングカウンター</v>
           </cell>
         </row>
         <row r="122">
           <cell r="A122">
-            <v>100921</v>
+            <v>100911</v>
           </cell>
           <cell r="B122" t="str">
-            <v>プロミネンス</v>
+            <v>バーニングカウンター</v>
           </cell>
         </row>
         <row r="123">
           <cell r="A123">
-            <v>101010</v>
+            <v>100920</v>
           </cell>
           <cell r="B123" t="str">
-            <v>エウロス</v>
+            <v>プロミネンス</v>
           </cell>
         </row>
         <row r="124">
           <cell r="A124">
-            <v>101020</v>
+            <v>100921</v>
           </cell>
           <cell r="B124" t="str">
-            <v>ボレアス</v>
+            <v>プロミネンス</v>
           </cell>
         </row>
         <row r="125">
           <cell r="A125">
-            <v>101110</v>
+            <v>101010</v>
           </cell>
           <cell r="B125" t="str">
-            <v>アバランシュ</v>
+            <v>エウロス</v>
           </cell>
         </row>
         <row r="126">
           <cell r="A126">
-            <v>101120</v>
+            <v>101020</v>
           </cell>
           <cell r="B126" t="str">
-            <v>ブリザードコフィン</v>
+            <v>ボレアス</v>
           </cell>
         </row>
         <row r="127">
           <cell r="A127">
-            <v>200210</v>
+            <v>101110</v>
           </cell>
           <cell r="B127" t="str">
-            <v>マイトレインフォース</v>
+            <v>アバランシュ</v>
           </cell>
         </row>
         <row r="128">
           <cell r="A128">
-            <v>200220</v>
+            <v>101120</v>
           </cell>
           <cell r="B128" t="str">
-            <v>カタストロフィ</v>
+            <v>ブリザードコフィン</v>
           </cell>
         </row>
         <row r="129">
           <cell r="A129">
-            <v>200230</v>
+            <v>200210</v>
           </cell>
           <cell r="B129" t="str">
-            <v>悪魔(ベリト)</v>
+            <v>マイトレインフォース</v>
           </cell>
         </row>
         <row r="130">
           <cell r="A130">
-            <v>200310</v>
+            <v>200220</v>
           </cell>
           <cell r="B130" t="str">
-            <v>プルガシオン</v>
+            <v>カタストロフィ</v>
           </cell>
         </row>
         <row r="131">
           <cell r="A131">
-            <v>200320</v>
+            <v>200230</v>
           </cell>
           <cell r="B131" t="str">
-            <v>プリエステス</v>
+            <v>悪魔(ベリト)</v>
           </cell>
         </row>
         <row r="132">
           <cell r="A132">
-            <v>200330</v>
+            <v>200310</v>
           </cell>
           <cell r="B132" t="str">
-            <v>悪魔(パイモン)</v>
+            <v>プルガシオン</v>
           </cell>
         </row>
         <row r="133">
           <cell r="A133">
-            <v>200410</v>
+            <v>200320</v>
           </cell>
           <cell r="B133" t="str">
-            <v>コウソクテンショウ</v>
+            <v>プリエステス</v>
           </cell>
         </row>
         <row r="134">
           <cell r="A134">
-            <v>200411</v>
+            <v>200330</v>
           </cell>
           <cell r="B134" t="str">
-            <v>コウソクテンショウ</v>
+            <v>悪魔(パイモン)</v>
           </cell>
         </row>
         <row r="135">
           <cell r="A135">
-            <v>200420</v>
+            <v>200410</v>
           </cell>
           <cell r="B135" t="str">
-            <v>アンチバフ</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="136">
           <cell r="A136">
-            <v>200430</v>
+            <v>200411</v>
           </cell>
           <cell r="B136" t="str">
-            <v>悪魔(アンドラス)</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="137">
           <cell r="A137">
-            <v>200510</v>
+            <v>200420</v>
           </cell>
           <cell r="B137" t="str">
-            <v>カウントダウン</v>
+            <v>アンチバフ</v>
           </cell>
         </row>
         <row r="138">
           <cell r="A138">
-            <v>200520</v>
+            <v>200430</v>
           </cell>
           <cell r="B138" t="str">
-            <v>グラウンドゼロ</v>
+            <v>悪魔(アンドラス)</v>
           </cell>
         </row>
         <row r="139">
           <cell r="A139">
-            <v>200530</v>
+            <v>200510</v>
           </cell>
           <cell r="B139" t="str">
-            <v>悪魔(ビフロンス)</v>
+            <v>カウントダウン</v>
           </cell>
         </row>
         <row r="140">
           <cell r="A140">
-            <v>201010</v>
+            <v>200520</v>
           </cell>
           <cell r="B140" t="str">
-            <v>カオスペイン</v>
+            <v>グラウンドゼロ</v>
           </cell>
         </row>
         <row r="141">
           <cell r="A141">
-            <v>201020</v>
+            <v>200530</v>
           </cell>
           <cell r="B141" t="str">
-            <v>フォールンワン</v>
+            <v>悪魔(ビフロンス)</v>
           </cell>
         </row>
         <row r="142">
           <cell r="A142">
-            <v>201030</v>
+            <v>201010</v>
           </cell>
           <cell r="B142" t="str">
-            <v>アンリマユ</v>
+            <v>カオスペイン</v>
           </cell>
         </row>
         <row r="143">
           <cell r="A143">
-            <v>300010</v>
+            <v>201020</v>
           </cell>
           <cell r="B143" t="str">
-            <v>ライフブースト</v>
+            <v>フォールンワン</v>
           </cell>
         </row>
         <row r="144">
           <cell r="A144">
-            <v>300020</v>
+            <v>201030</v>
           </cell>
           <cell r="B144" t="str">
-            <v>スピリットチャージ</v>
+            <v>アンリマユ</v>
           </cell>
         </row>
         <row r="145">
           <cell r="A145">
-            <v>300030</v>
+            <v>300010</v>
           </cell>
           <cell r="B145" t="str">
-            <v>フォースライズ</v>
+            <v>ライフブースト</v>
           </cell>
         </row>
         <row r="146">
           <cell r="A146">
-            <v>300040</v>
+            <v>300020</v>
           </cell>
           <cell r="B146" t="str">
-            <v>ディフェンスオーラ</v>
+            <v>スピリットチャージ</v>
           </cell>
         </row>
         <row r="147">
           <cell r="A147">
-            <v>300050</v>
+            <v>300030</v>
           </cell>
           <cell r="B147" t="str">
-            <v>ラピッドムーブ</v>
+            <v>フォースライズ</v>
           </cell>
         </row>
         <row r="148">
           <cell r="A148">
-            <v>300130</v>
+            <v>300040</v>
           </cell>
           <cell r="B148" t="str">
-            <v>アタックブレイク</v>
+            <v>ディフェンスオーラ</v>
           </cell>
         </row>
         <row r="149">
           <cell r="A149">
-            <v>300140</v>
+            <v>300050</v>
           </cell>
           <cell r="B149" t="str">
-            <v>シールドバニッシュ</v>
+            <v>ラピッドムーブ</v>
           </cell>
         </row>
         <row r="150">
           <cell r="A150">
-            <v>300210</v>
+            <v>300130</v>
           </cell>
           <cell r="B150" t="str">
-            <v>エーテルリチャージ</v>
+            <v>アタックブレイク</v>
           </cell>
         </row>
         <row r="151">
           <cell r="A151">
-            <v>300220</v>
+            <v>300140</v>
           </cell>
           <cell r="B151" t="str">
-            <v>リカバリーエンハンス</v>
+            <v>シールドバニッシュ</v>
           </cell>
         </row>
         <row r="152">
           <cell r="A152">
-            <v>300230</v>
+            <v>300210</v>
           </cell>
           <cell r="B152" t="str">
-            <v>ヴェンジェンス</v>
+            <v>エーテルリチャージ</v>
           </cell>
         </row>
         <row r="153">
           <cell r="A153">
-            <v>301010</v>
+            <v>300220</v>
           </cell>
           <cell r="B153" t="str">
-            <v>ディケイドリセット</v>
+            <v>リカバリーエンハンス</v>
           </cell>
         </row>
         <row r="154">
           <cell r="A154">
-            <v>301020</v>
+            <v>300230</v>
           </cell>
           <cell r="B154" t="str">
-            <v>ウォーリアーブラッド</v>
+            <v>ヴェンジェンス</v>
           </cell>
         </row>
         <row r="155">
           <cell r="A155">
-            <v>301030</v>
+            <v>301010</v>
           </cell>
           <cell r="B155" t="str">
-            <v>トライアングルガード</v>
+            <v>ディケイドリセット</v>
           </cell>
         </row>
         <row r="156">
           <cell r="A156">
-            <v>301040</v>
+            <v>301020</v>
           </cell>
           <cell r="B156" t="str">
-            <v>セーフティバリア</v>
+            <v>ウォーリアーブラッド</v>
           </cell>
         </row>
         <row r="157">
           <cell r="A157">
-            <v>301050</v>
+            <v>301030</v>
           </cell>
           <cell r="B157" t="str">
-            <v>ヒロインズハイ</v>
+            <v>トライアングルガード</v>
           </cell>
         </row>
         <row r="158">
           <cell r="A158">
-            <v>301060</v>
+            <v>301040</v>
           </cell>
           <cell r="B158" t="str">
-            <v>セカンドステージ</v>
+            <v>セーフティバリア</v>
           </cell>
         </row>
         <row r="159">
           <cell r="A159">
-            <v>301070</v>
+            <v>301050</v>
           </cell>
           <cell r="B159" t="str">
-            <v>ハイヒットポイント</v>
+            <v>ヒロインズハイ</v>
           </cell>
         </row>
         <row r="160">
           <cell r="A160">
-            <v>301080</v>
+            <v>301060</v>
           </cell>
           <cell r="B160" t="str">
-            <v>セプタブラスト</v>
+            <v>セカンドステージ</v>
           </cell>
         </row>
         <row r="161">
           <cell r="A161">
-            <v>301090</v>
+            <v>301070</v>
           </cell>
           <cell r="B161" t="str">
-            <v>イニシャルブロッカー</v>
+            <v>ハイヒットポイント</v>
           </cell>
         </row>
         <row r="162">
           <cell r="A162">
-            <v>301100</v>
+            <v>301080</v>
           </cell>
           <cell r="B162" t="str">
-            <v>ファーストテイク</v>
+            <v>セプタブラスト</v>
           </cell>
         </row>
         <row r="163">
           <cell r="A163">
-            <v>310010</v>
+            <v>301090</v>
           </cell>
           <cell r="B163" t="str">
-            <v>妖精の祈り</v>
+            <v>イニシャルブロッカー</v>
           </cell>
         </row>
         <row r="164">
           <cell r="A164">
-            <v>310020</v>
+            <v>301100</v>
           </cell>
           <cell r="B164" t="str">
-            <v>月のかけら</v>
+            <v>ファーストテイク</v>
           </cell>
         </row>
         <row r="165">
           <cell r="A165">
-            <v>310030</v>
+            <v>310010</v>
           </cell>
           <cell r="B165" t="str">
-            <v>錬金術師の遺稿</v>
+            <v>妖精の祈り</v>
           </cell>
         </row>
         <row r="166">
           <cell r="A166">
-            <v>310130</v>
+            <v>310020</v>
           </cell>
           <cell r="B166" t="str">
-            <v>ヒールユニット</v>
+            <v>月のかけら</v>
           </cell>
         </row>
         <row r="167">
           <cell r="A167">
-            <v>401010</v>
+            <v>310030</v>
           </cell>
           <cell r="B167" t="str">
-            <v>ファイアボール+</v>
+            <v>錬金術師の遺稿</v>
           </cell>
         </row>
         <row r="168">
           <cell r="A168">
-            <v>401020</v>
+            <v>310130</v>
           </cell>
           <cell r="B168" t="str">
-            <v>バーンストーム+</v>
+            <v>ヒールユニット</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169">
-            <v>401030</v>
+            <v>401010</v>
           </cell>
           <cell r="B169" t="str">
-            <v>ヒートスタンプ+</v>
+            <v>ファイアボール+</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170">
-            <v>401040</v>
+            <v>401020</v>
           </cell>
           <cell r="B170" t="str">
-            <v>ソードアダプト+</v>
+            <v>バーンストーム+</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171">
-            <v>401050</v>
+            <v>401030</v>
           </cell>
           <cell r="B171" t="str">
-            <v>フレイムレイン+</v>
+            <v>ヒートスタンプ+</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172">
-            <v>401060</v>
+            <v>401040</v>
           </cell>
           <cell r="B172" t="str">
-            <v>イクスティンクション+</v>
+            <v>ソードアダプト+</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173">
-            <v>401070</v>
+            <v>401050</v>
           </cell>
           <cell r="B173" t="str">
-            <v>バーニングソウル+</v>
+            <v>フレイムレイン+</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174">
-            <v>401080</v>
+            <v>401060</v>
           </cell>
           <cell r="B174" t="str">
-            <v>レイジングバウンサー+</v>
+            <v>イクスティンクション+</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175">
-            <v>402010</v>
+            <v>401070</v>
           </cell>
           <cell r="B175" t="str">
-            <v>ディスチャージ+</v>
+            <v>バーニングソウル+</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176">
-            <v>402020</v>
+            <v>401080</v>
           </cell>
           <cell r="B176" t="str">
-            <v>イベイドコード+</v>
+            <v>レイジングバウンサー+</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177">
-            <v>402030</v>
+            <v>402010</v>
           </cell>
           <cell r="B177" t="str">
-            <v>ショックインパルス+</v>
+            <v>ディスチャージ+</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178">
-            <v>402040</v>
+            <v>402020</v>
           </cell>
           <cell r="B178" t="str">
-            <v>トラストチェイン+</v>
+            <v>イベイドコード+</v>
           </cell>
         </row>
         <row r="179">
           <cell r="A179">
-            <v>402050</v>
+            <v>402030</v>
           </cell>
           <cell r="B179" t="str">
-            <v>スペルバニシング+</v>
+            <v>ショックインパルス+</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180">
-            <v>402060</v>
+            <v>402040</v>
           </cell>
           <cell r="B180" t="str">
-            <v>アーテニーストライク+</v>
+            <v>トラストチェイン+</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181">
-            <v>402070</v>
+            <v>402050</v>
           </cell>
           <cell r="B181" t="str">
-            <v>コンセントレイト+</v>
+            <v>スペルバニシング+</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182">
-            <v>402080</v>
+            <v>402060</v>
           </cell>
           <cell r="B182" t="str">
-            <v>ディレイマジック+</v>
+            <v>アーテニーストライク+</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183">
-            <v>403010</v>
+            <v>402070</v>
           </cell>
           <cell r="B183" t="str">
-            <v>アイスブレイド+</v>
+            <v>コンセントレイト+</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184">
-            <v>403020</v>
+            <v>402080</v>
           </cell>
           <cell r="B184" t="str">
-            <v>カウンターオーラ+</v>
+            <v>ディレイマジック+</v>
           </cell>
         </row>
         <row r="185">
           <cell r="A185">
-            <v>403030</v>
+            <v>403010</v>
           </cell>
           <cell r="B185" t="str">
-            <v>ラインプロテクト+</v>
+            <v>アイスブレイド+</v>
           </cell>
         </row>
         <row r="186">
           <cell r="A186">
-            <v>403040</v>
+            <v>403020</v>
           </cell>
           <cell r="B186" t="str">
-            <v>エスコートソール+</v>
+            <v>カウンターオーラ+</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187">
-            <v>403050</v>
+            <v>403030</v>
           </cell>
           <cell r="B187" t="str">
-            <v>ディープフリーズ+</v>
+            <v>ラインプロテクト+</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188">
-            <v>403060</v>
+            <v>403040</v>
           </cell>
           <cell r="B188" t="str">
-            <v>バブルブロウ+</v>
+            <v>エスコートソール+</v>
           </cell>
         </row>
         <row r="189">
           <cell r="A189">
-            <v>403070</v>
+            <v>403050</v>
           </cell>
           <cell r="B189" t="str">
-            <v>アクアミラージュ+</v>
+            <v>ディープフリーズ+</v>
           </cell>
         </row>
         <row r="190">
           <cell r="A190">
-            <v>403080</v>
+            <v>403060</v>
           </cell>
           <cell r="B190" t="str">
-            <v>フロストシールド+</v>
+            <v>バブルブロウ+</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191">
-            <v>404010</v>
+            <v>403070</v>
           </cell>
           <cell r="B191" t="str">
-            <v>セイントレーザー+</v>
+            <v>アクアミラージュ+</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192">
-            <v>404020</v>
+            <v>403080</v>
           </cell>
           <cell r="B192" t="str">
-            <v>ペネトレイト+</v>
+            <v>フロストシールド+</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193">
-            <v>404030</v>
+            <v>404010</v>
           </cell>
           <cell r="B193" t="str">
-            <v>ヒーリング+</v>
+            <v>セイントレーザー+</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194">
-            <v>404040</v>
+            <v>404020</v>
           </cell>
           <cell r="B194" t="str">
-            <v>リザイアフォトン+</v>
+            <v>ペネトレイト+</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195">
-            <v>404050</v>
+            <v>404030</v>
           </cell>
           <cell r="B195" t="str">
-            <v>べネディクション+</v>
+            <v>ヒーリング+</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196">
-            <v>404060</v>
+            <v>404040</v>
           </cell>
           <cell r="B196" t="str">
-            <v>ホーリーグレイス+</v>
+            <v>リザイアフォトン+</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197">
-            <v>404070</v>
+            <v>404050</v>
           </cell>
           <cell r="B197" t="str">
-            <v>キュアエール+</v>
+            <v>べネディクション+</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198">
-            <v>404080</v>
+            <v>404060</v>
           </cell>
           <cell r="B198" t="str">
-            <v>ラインバリア+</v>
+            <v>ホーリーグレイス+</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199">
-            <v>405010</v>
+            <v>404070</v>
           </cell>
           <cell r="B199" t="str">
-            <v>ダークプリズン+</v>
+            <v>キュアエール+</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200">
-            <v>405020</v>
+            <v>404080</v>
           </cell>
           <cell r="B200" t="str">
-            <v>ユーサネイジア+</v>
+            <v>ラインバリア+</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201">
-            <v>405030</v>
+            <v>405010</v>
           </cell>
           <cell r="B201" t="str">
-            <v>ドレインヒール+</v>
+            <v>ダークプリズン+</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202">
-            <v>405040</v>
+            <v>405020</v>
           </cell>
           <cell r="B202" t="str">
-            <v>アビサルデスペア+</v>
+            <v>ユーサネイジア+</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203">
-            <v>405050</v>
+            <v>405030</v>
           </cell>
           <cell r="B203" t="str">
-            <v>ディプラヴィティ+</v>
+            <v>ドレインヒール+</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204">
-            <v>405060</v>
+            <v>405040</v>
           </cell>
           <cell r="B204" t="str">
-            <v>ダークネス+</v>
+            <v>アビサルデスペア+</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205">
-            <v>405070</v>
+            <v>405050</v>
           </cell>
           <cell r="B205" t="str">
-            <v>シェイディークラウド+</v>
+            <v>ディプラヴィティ+</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206">
-            <v>405080</v>
+            <v>405060</v>
           </cell>
           <cell r="B206" t="str">
-            <v>ポイズンブロウ+</v>
+            <v>ダークネス+</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207">
-            <v>411010</v>
+            <v>405070</v>
           </cell>
           <cell r="B207" t="str">
-            <v>ウルフソウル+</v>
+            <v>シェイディークラウド+</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208">
-            <v>411020</v>
+            <v>405080</v>
           </cell>
           <cell r="B208" t="str">
-            <v>プリディカメント+</v>
+            <v>ポイズンブロウ+</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209">
-            <v>411030</v>
+            <v>411010</v>
           </cell>
           <cell r="B209" t="str">
-            <v>アサルトシフト+</v>
+            <v>ウルフソウル+</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210">
-            <v>411040</v>
+            <v>411020</v>
           </cell>
           <cell r="B210" t="str">
-            <v>アクティブギフト+</v>
+            <v>プリディカメント+</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211">
-            <v>411050</v>
+            <v>411030</v>
           </cell>
           <cell r="B211" t="str">
-            <v>イグナイテッド+</v>
+            <v>アサルトシフト+</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212">
-            <v>411060</v>
+            <v>411040</v>
           </cell>
           <cell r="B212" t="str">
-            <v>ライジングファイア+</v>
+            <v>アクティブギフト+</v>
           </cell>
         </row>
         <row r="213">
           <cell r="A213">
-            <v>411070</v>
+            <v>411050</v>
           </cell>
           <cell r="B213" t="str">
-            <v>ルージュバック+</v>
+            <v>イグナイテッド+</v>
           </cell>
         </row>
         <row r="214">
           <cell r="A214">
-            <v>411080</v>
+            <v>411060</v>
           </cell>
           <cell r="B214" t="str">
-            <v>パワーエール+</v>
+            <v>ライジングファイア+</v>
           </cell>
         </row>
         <row r="215">
           <cell r="A215">
-            <v>411090</v>
+            <v>411070</v>
           </cell>
           <cell r="B215" t="str">
-            <v>スレイプニル+</v>
+            <v>ルージュバック+</v>
           </cell>
         </row>
         <row r="216">
           <cell r="A216">
-            <v>412010</v>
+            <v>411080</v>
           </cell>
           <cell r="B216" t="str">
-            <v>エクステンション+</v>
+            <v>パワーエール+</v>
           </cell>
         </row>
         <row r="217">
           <cell r="A217">
-            <v>412020</v>
+            <v>411090</v>
           </cell>
           <cell r="B217" t="str">
-            <v>ヘブンリーラック+</v>
+            <v>スレイプニル+</v>
           </cell>
         </row>
         <row r="218">
           <cell r="A218">
-            <v>412030</v>
+            <v>412010</v>
           </cell>
           <cell r="B218" t="str">
-            <v>スウィフトカレント+</v>
+            <v>エクステンション+</v>
           </cell>
         </row>
         <row r="219">
           <cell r="A219">
-            <v>412040</v>
+            <v>412020</v>
           </cell>
           <cell r="B219" t="str">
-            <v>イヴェイドオール+</v>
+            <v>ヘブンリーラック+</v>
           </cell>
         </row>
         <row r="220">
           <cell r="A220">
-            <v>412050</v>
+            <v>412030</v>
           </cell>
           <cell r="B220" t="str">
-            <v>クイックムーブ+</v>
+            <v>スウィフトカレント+</v>
           </cell>
         </row>
         <row r="221">
           <cell r="A221">
-            <v>412060</v>
+            <v>412040</v>
           </cell>
           <cell r="B221" t="str">
-            <v>チェイスマジック+</v>
+            <v>イヴェイドオール+</v>
           </cell>
         </row>
         <row r="222">
           <cell r="A222">
-            <v>412070</v>
+            <v>412050</v>
           </cell>
           <cell r="B222" t="str">
-            <v>ソーサリーコネクト+</v>
+            <v>クイックムーブ+</v>
           </cell>
         </row>
         <row r="223">
           <cell r="A223">
-            <v>412080</v>
+            <v>412060</v>
           </cell>
           <cell r="B223" t="str">
-            <v>ウィンドライズ+</v>
+            <v>チェイスマジック+</v>
           </cell>
         </row>
         <row r="224">
           <cell r="A224">
-            <v>412090</v>
+            <v>412070</v>
           </cell>
           <cell r="B224" t="str">
-            <v>アウトオブオーダー+</v>
+            <v>ソーサリーコネクト+</v>
           </cell>
         </row>
         <row r="225">
           <cell r="A225">
-            <v>413010</v>
+            <v>412080</v>
           </cell>
           <cell r="B225" t="str">
-            <v>アーマーコード+</v>
+            <v>ウィンドライズ+</v>
           </cell>
         </row>
         <row r="226">
           <cell r="A226">
-            <v>413020</v>
+            <v>412090</v>
           </cell>
           <cell r="B226" t="str">
-            <v>クイックバリア+</v>
+            <v>アウトオブオーダー+</v>
           </cell>
         </row>
         <row r="227">
           <cell r="A227">
-            <v>413030</v>
+            <v>413010</v>
           </cell>
           <cell r="B227" t="str">
-            <v>クイックキュア+</v>
+            <v>アーマーコード+</v>
           </cell>
         </row>
         <row r="228">
           <cell r="A228">
-            <v>413040</v>
+            <v>413020</v>
           </cell>
           <cell r="B228" t="str">
-            <v>セルフシールド+</v>
+            <v>クイックバリア+</v>
           </cell>
         </row>
         <row r="229">
           <cell r="A229">
-            <v>413050</v>
+            <v>413030</v>
           </cell>
           <cell r="B229" t="str">
-            <v>パッシブジャミング+</v>
+            <v>クイックキュア+</v>
           </cell>
         </row>
         <row r="230">
           <cell r="A230">
-            <v>413060</v>
+            <v>413040</v>
           </cell>
           <cell r="B230" t="str">
-            <v>サプライカバー+</v>
+            <v>セルフシールド+</v>
           </cell>
         </row>
         <row r="231">
           <cell r="A231">
-            <v>413070</v>
+            <v>413050</v>
           </cell>
           <cell r="B231" t="str">
-            <v>アシッドラッシュ+</v>
+            <v>パッシブジャミング+</v>
           </cell>
         </row>
         <row r="232">
           <cell r="A232">
-            <v>413080</v>
+            <v>413060</v>
           </cell>
           <cell r="B232" t="str">
-            <v>ライフスティール+</v>
+            <v>サプライカバー+</v>
           </cell>
         </row>
         <row r="233">
           <cell r="A233">
-            <v>413090</v>
+            <v>413070</v>
           </cell>
           <cell r="B233" t="str">
-            <v>アイスセイバー+</v>
+            <v>アシッドラッシュ+</v>
           </cell>
         </row>
         <row r="234">
           <cell r="A234">
-            <v>414010</v>
+            <v>413080</v>
           </cell>
           <cell r="B234" t="str">
-            <v>ディバインシールド+</v>
+            <v>ライフスティール+</v>
           </cell>
         </row>
         <row r="235">
           <cell r="A235">
-            <v>414020</v>
+            <v>413090</v>
           </cell>
           <cell r="B235" t="str">
-            <v>ライフディバイド+</v>
+            <v>アイスセイバー+</v>
           </cell>
         </row>
         <row r="236">
           <cell r="A236">
-            <v>414030</v>
+            <v>414010</v>
           </cell>
           <cell r="B236" t="str">
-            <v>エイミングスコープ+</v>
+            <v>ディバインシールド+</v>
           </cell>
         </row>
         <row r="237">
           <cell r="A237">
-            <v>414040</v>
+            <v>414020</v>
           </cell>
           <cell r="B237" t="str">
-            <v>リジェネレーション+</v>
+            <v>ライフディバイド+</v>
           </cell>
         </row>
         <row r="238">
           <cell r="A238">
-            <v>414050</v>
+            <v>414030</v>
           </cell>
           <cell r="B238" t="str">
-            <v>ホープフルアイリス+</v>
+            <v>エイミングスコープ+</v>
           </cell>
         </row>
         <row r="239">
           <cell r="A239">
-            <v>414060</v>
+            <v>414040</v>
           </cell>
           <cell r="B239" t="str">
-            <v>パッシブサプライ+</v>
+            <v>リジェネレーション+</v>
           </cell>
         </row>
         <row r="240">
           <cell r="A240">
-            <v>414070</v>
+            <v>414050</v>
           </cell>
           <cell r="B240" t="str">
-            <v>ホーミングクルセイド+</v>
+            <v>ホープフルアイリス+</v>
           </cell>
         </row>
         <row r="241">
           <cell r="A241">
-            <v>414080</v>
+            <v>414060</v>
           </cell>
           <cell r="B241" t="str">
-            <v>クイックヒール+</v>
+            <v>パッシブサプライ+</v>
           </cell>
         </row>
         <row r="242">
           <cell r="A242">
-            <v>414090</v>
+            <v>414070</v>
           </cell>
           <cell r="B242" t="str">
-            <v>リレイズ+</v>
+            <v>ホーミングクルセイド+</v>
           </cell>
         </row>
         <row r="243">
           <cell r="A243">
-            <v>415010</v>
+            <v>414080</v>
           </cell>
           <cell r="B243" t="str">
-            <v>イーグルアイ+</v>
+            <v>クイックヒール+</v>
           </cell>
         </row>
         <row r="244">
           <cell r="A244">
-            <v>415020</v>
+            <v>414090</v>
           </cell>
           <cell r="B244" t="str">
-            <v>ネヴァーエンド+</v>
+            <v>リレイズ+</v>
           </cell>
         </row>
         <row r="245">
           <cell r="A245">
-            <v>415030</v>
+            <v>415010</v>
           </cell>
           <cell r="B245" t="str">
-            <v>グレイブアクト+</v>
+            <v>イーグルアイ+</v>
           </cell>
         </row>
         <row r="246">
           <cell r="A246">
-            <v>415040</v>
+            <v>415020</v>
           </cell>
           <cell r="B246" t="str">
-            <v>スカルグラッジ+</v>
+            <v>ネヴァーエンド+</v>
           </cell>
         </row>
         <row r="247">
           <cell r="A247">
-            <v>415050</v>
+            <v>415030</v>
           </cell>
           <cell r="B247" t="str">
-            <v>ネガティブドレイン+</v>
+            <v>グレイブアクト+</v>
           </cell>
         </row>
         <row r="248">
           <cell r="A248">
-            <v>415060</v>
+            <v>415040</v>
           </cell>
           <cell r="B248" t="str">
-            <v>アンデッドペイン+</v>
+            <v>スカルグラッジ+</v>
           </cell>
         </row>
         <row r="249">
           <cell r="A249">
-            <v>415070</v>
+            <v>415050</v>
           </cell>
           <cell r="B249" t="str">
-            <v>ジャックポッド+</v>
+            <v>ネガティブドレイン+</v>
           </cell>
         </row>
         <row r="250">
           <cell r="A250">
-            <v>415080</v>
+            <v>415060</v>
           </cell>
           <cell r="B250" t="str">
-            <v>ヒールハント+</v>
+            <v>アンデッドペイン+</v>
           </cell>
         </row>
         <row r="251">
           <cell r="A251">
+            <v>415070</v>
+          </cell>
+          <cell r="B251" t="str">
+            <v>ジャックポッド+</v>
+          </cell>
+        </row>
+        <row r="252">
+          <cell r="A252">
+            <v>415080</v>
+          </cell>
+          <cell r="B252" t="str">
+            <v>ヒールハント+</v>
+          </cell>
+        </row>
+        <row r="253">
+          <cell r="A253">
             <v>415090</v>
           </cell>
-          <cell r="B251" t="str">
+          <cell r="B253" t="str">
             <v>クイックカース+</v>
           </cell>
         </row>
@@ -3567,7 +3583,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -4136,7 +4152,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H13">
         <v>9</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="7820"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -394,10 +394,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -415,24 +415,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -445,41 +429,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -488,6 +441,14 @@
       <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -507,7 +468,38 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -529,10 +521,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -541,6 +533,14 @@
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -568,13 +568,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,37 +622,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -634,7 +640,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -646,97 +736,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -748,7 +748,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -759,24 +759,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -795,6 +777,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -806,6 +797,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -834,17 +840,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -867,145 +867,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4152,7 +4152,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H13">
         <v>9</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -396,8 +396,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -416,7 +416,77 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -430,25 +500,16 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -467,54 +528,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -522,22 +538,6 @@
     <font>
       <b/>
       <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -553,7 +553,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -568,7 +568,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,7 +592,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -592,13 +712,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -610,37 +724,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -652,91 +736,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -748,7 +748,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -762,56 +762,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -849,6 +804,36 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -856,6 +841,21 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -867,145 +867,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2435,689 +2435,705 @@
         </row>
         <row r="168">
           <cell r="A168">
-            <v>310130</v>
+            <v>310040</v>
           </cell>
           <cell r="B168" t="str">
-            <v>ヒールユニット</v>
+            <v>レイヴンバナー</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169">
-            <v>401010</v>
+            <v>310041</v>
           </cell>
           <cell r="B169" t="str">
-            <v>ファイアボール+</v>
+            <v>レイヴンバナー</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170">
-            <v>401020</v>
+            <v>310130</v>
           </cell>
           <cell r="B170" t="str">
-            <v>バーンストーム+</v>
+            <v>ヒールユニット</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171">
-            <v>401030</v>
+            <v>401010</v>
           </cell>
           <cell r="B171" t="str">
-            <v>ヒートスタンプ+</v>
+            <v>ファイアボール+</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172">
-            <v>401040</v>
+            <v>401020</v>
           </cell>
           <cell r="B172" t="str">
-            <v>ソードアダプト+</v>
+            <v>バーンストーム+</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173">
-            <v>401050</v>
+            <v>401030</v>
           </cell>
           <cell r="B173" t="str">
-            <v>フレイムレイン+</v>
+            <v>ヒートスタンプ+</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174">
-            <v>401060</v>
+            <v>401040</v>
           </cell>
           <cell r="B174" t="str">
-            <v>イクスティンクション+</v>
+            <v>ソードアダプト+</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175">
-            <v>401070</v>
+            <v>401050</v>
           </cell>
           <cell r="B175" t="str">
-            <v>バーニングソウル+</v>
+            <v>フレイムレイン+</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176">
-            <v>401080</v>
+            <v>401060</v>
           </cell>
           <cell r="B176" t="str">
-            <v>レイジングバウンサー+</v>
+            <v>イクスティンクション+</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177">
-            <v>402010</v>
+            <v>401070</v>
           </cell>
           <cell r="B177" t="str">
-            <v>ディスチャージ+</v>
+            <v>バーニングソウル+</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178">
-            <v>402020</v>
+            <v>401080</v>
           </cell>
           <cell r="B178" t="str">
-            <v>イベイドコード+</v>
+            <v>レイジングバウンサー+</v>
           </cell>
         </row>
         <row r="179">
           <cell r="A179">
-            <v>402030</v>
+            <v>402010</v>
           </cell>
           <cell r="B179" t="str">
-            <v>ショックインパルス+</v>
+            <v>ディスチャージ+</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180">
-            <v>402040</v>
+            <v>402020</v>
           </cell>
           <cell r="B180" t="str">
-            <v>トラストチェイン+</v>
+            <v>イベイドコード+</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181">
-            <v>402050</v>
+            <v>402030</v>
           </cell>
           <cell r="B181" t="str">
-            <v>スペルバニシング+</v>
+            <v>ショックインパルス+</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182">
-            <v>402060</v>
+            <v>402040</v>
           </cell>
           <cell r="B182" t="str">
-            <v>アーテニーストライク+</v>
+            <v>トラストチェイン+</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183">
-            <v>402070</v>
+            <v>402050</v>
           </cell>
           <cell r="B183" t="str">
-            <v>コンセントレイト+</v>
+            <v>スペルバニシング+</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184">
-            <v>402080</v>
+            <v>402060</v>
           </cell>
           <cell r="B184" t="str">
-            <v>ディレイマジック+</v>
+            <v>アーテニーストライク+</v>
           </cell>
         </row>
         <row r="185">
           <cell r="A185">
-            <v>403010</v>
+            <v>402070</v>
           </cell>
           <cell r="B185" t="str">
-            <v>アイスブレイド+</v>
+            <v>コンセントレイト+</v>
           </cell>
         </row>
         <row r="186">
           <cell r="A186">
-            <v>403020</v>
+            <v>402080</v>
           </cell>
           <cell r="B186" t="str">
-            <v>カウンターオーラ+</v>
+            <v>ディレイマジック+</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187">
-            <v>403030</v>
+            <v>403010</v>
           </cell>
           <cell r="B187" t="str">
-            <v>ラインプロテクト+</v>
+            <v>アイスブレイド+</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188">
-            <v>403040</v>
+            <v>403020</v>
           </cell>
           <cell r="B188" t="str">
-            <v>エスコートソール+</v>
+            <v>カウンターオーラ+</v>
           </cell>
         </row>
         <row r="189">
           <cell r="A189">
-            <v>403050</v>
+            <v>403030</v>
           </cell>
           <cell r="B189" t="str">
-            <v>ディープフリーズ+</v>
+            <v>ラインプロテクト+</v>
           </cell>
         </row>
         <row r="190">
           <cell r="A190">
-            <v>403060</v>
+            <v>403040</v>
           </cell>
           <cell r="B190" t="str">
-            <v>バブルブロウ+</v>
+            <v>エスコートソール+</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191">
-            <v>403070</v>
+            <v>403050</v>
           </cell>
           <cell r="B191" t="str">
-            <v>アクアミラージュ+</v>
+            <v>ディープフリーズ+</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192">
-            <v>403080</v>
+            <v>403060</v>
           </cell>
           <cell r="B192" t="str">
-            <v>フロストシールド+</v>
+            <v>バブルブロウ+</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193">
-            <v>404010</v>
+            <v>403070</v>
           </cell>
           <cell r="B193" t="str">
-            <v>セイントレーザー+</v>
+            <v>アクアミラージュ+</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194">
-            <v>404020</v>
+            <v>403080</v>
           </cell>
           <cell r="B194" t="str">
-            <v>ペネトレイト+</v>
+            <v>フロストシールド+</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195">
-            <v>404030</v>
+            <v>404010</v>
           </cell>
           <cell r="B195" t="str">
-            <v>ヒーリング+</v>
+            <v>セイントレーザー+</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196">
-            <v>404040</v>
+            <v>404020</v>
           </cell>
           <cell r="B196" t="str">
-            <v>リザイアフォトン+</v>
+            <v>ペネトレイト+</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197">
-            <v>404050</v>
+            <v>404030</v>
           </cell>
           <cell r="B197" t="str">
-            <v>べネディクション+</v>
+            <v>ヒーリング+</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198">
-            <v>404060</v>
+            <v>404040</v>
           </cell>
           <cell r="B198" t="str">
-            <v>ホーリーグレイス+</v>
+            <v>リザイアフォトン+</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199">
-            <v>404070</v>
+            <v>404050</v>
           </cell>
           <cell r="B199" t="str">
-            <v>キュアエール+</v>
+            <v>べネディクション+</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200">
-            <v>404080</v>
+            <v>404060</v>
           </cell>
           <cell r="B200" t="str">
-            <v>ラインバリア+</v>
+            <v>ホーリーグレイス+</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201">
-            <v>405010</v>
+            <v>404070</v>
           </cell>
           <cell r="B201" t="str">
-            <v>ダークプリズン+</v>
+            <v>キュアエール+</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202">
-            <v>405020</v>
+            <v>404080</v>
           </cell>
           <cell r="B202" t="str">
-            <v>ユーサネイジア+</v>
+            <v>ラインバリア+</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203">
-            <v>405030</v>
+            <v>405010</v>
           </cell>
           <cell r="B203" t="str">
-            <v>ドレインヒール+</v>
+            <v>ダークプリズン+</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204">
-            <v>405040</v>
+            <v>405020</v>
           </cell>
           <cell r="B204" t="str">
-            <v>アビサルデスペア+</v>
+            <v>ユーサネイジア+</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205">
-            <v>405050</v>
+            <v>405030</v>
           </cell>
           <cell r="B205" t="str">
-            <v>ディプラヴィティ+</v>
+            <v>ドレインヒール+</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206">
-            <v>405060</v>
+            <v>405040</v>
           </cell>
           <cell r="B206" t="str">
-            <v>ダークネス+</v>
+            <v>アビサルデスペア+</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207">
-            <v>405070</v>
+            <v>405050</v>
           </cell>
           <cell r="B207" t="str">
-            <v>シェイディークラウド+</v>
+            <v>ディプラヴィティ+</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208">
-            <v>405080</v>
+            <v>405060</v>
           </cell>
           <cell r="B208" t="str">
-            <v>ポイズンブロウ+</v>
+            <v>ダークネス+</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209">
-            <v>411010</v>
+            <v>405070</v>
           </cell>
           <cell r="B209" t="str">
-            <v>ウルフソウル+</v>
+            <v>シェイディークラウド+</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210">
-            <v>411020</v>
+            <v>405080</v>
           </cell>
           <cell r="B210" t="str">
-            <v>プリディカメント+</v>
+            <v>ポイズンブロウ+</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211">
-            <v>411030</v>
+            <v>411010</v>
           </cell>
           <cell r="B211" t="str">
-            <v>アサルトシフト+</v>
+            <v>ウルフソウル+</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212">
-            <v>411040</v>
+            <v>411020</v>
           </cell>
           <cell r="B212" t="str">
-            <v>アクティブギフト+</v>
+            <v>プリディカメント+</v>
           </cell>
         </row>
         <row r="213">
           <cell r="A213">
-            <v>411050</v>
+            <v>411030</v>
           </cell>
           <cell r="B213" t="str">
-            <v>イグナイテッド+</v>
+            <v>アサルトシフト+</v>
           </cell>
         </row>
         <row r="214">
           <cell r="A214">
-            <v>411060</v>
+            <v>411040</v>
           </cell>
           <cell r="B214" t="str">
-            <v>ライジングファイア+</v>
+            <v>アクティブギフト+</v>
           </cell>
         </row>
         <row r="215">
           <cell r="A215">
-            <v>411070</v>
+            <v>411050</v>
           </cell>
           <cell r="B215" t="str">
-            <v>ルージュバック+</v>
+            <v>イグナイテッド+</v>
           </cell>
         </row>
         <row r="216">
           <cell r="A216">
-            <v>411080</v>
+            <v>411060</v>
           </cell>
           <cell r="B216" t="str">
-            <v>パワーエール+</v>
+            <v>ライジングファイア+</v>
           </cell>
         </row>
         <row r="217">
           <cell r="A217">
-            <v>411090</v>
+            <v>411070</v>
           </cell>
           <cell r="B217" t="str">
-            <v>スレイプニル+</v>
+            <v>ルージュバック+</v>
           </cell>
         </row>
         <row r="218">
           <cell r="A218">
-            <v>412010</v>
+            <v>411080</v>
           </cell>
           <cell r="B218" t="str">
-            <v>エクステンション+</v>
+            <v>パワーエール+</v>
           </cell>
         </row>
         <row r="219">
           <cell r="A219">
-            <v>412020</v>
+            <v>411090</v>
           </cell>
           <cell r="B219" t="str">
-            <v>ヘブンリーラック+</v>
+            <v>スレイプニル+</v>
           </cell>
         </row>
         <row r="220">
           <cell r="A220">
-            <v>412030</v>
+            <v>412010</v>
           </cell>
           <cell r="B220" t="str">
-            <v>スウィフトカレント+</v>
+            <v>エクステンション+</v>
           </cell>
         </row>
         <row r="221">
           <cell r="A221">
-            <v>412040</v>
+            <v>412020</v>
           </cell>
           <cell r="B221" t="str">
-            <v>イヴェイドオール+</v>
+            <v>ヘブンリーラック+</v>
           </cell>
         </row>
         <row r="222">
           <cell r="A222">
-            <v>412050</v>
+            <v>412030</v>
           </cell>
           <cell r="B222" t="str">
-            <v>クイックムーブ+</v>
+            <v>スウィフトカレント+</v>
           </cell>
         </row>
         <row r="223">
           <cell r="A223">
-            <v>412060</v>
+            <v>412040</v>
           </cell>
           <cell r="B223" t="str">
-            <v>チェイスマジック+</v>
+            <v>イヴェイドオール+</v>
           </cell>
         </row>
         <row r="224">
           <cell r="A224">
-            <v>412070</v>
+            <v>412050</v>
           </cell>
           <cell r="B224" t="str">
-            <v>ソーサリーコネクト+</v>
+            <v>クイックムーブ+</v>
           </cell>
         </row>
         <row r="225">
           <cell r="A225">
-            <v>412080</v>
+            <v>412060</v>
           </cell>
           <cell r="B225" t="str">
-            <v>ウィンドライズ+</v>
+            <v>チェイスマジック+</v>
           </cell>
         </row>
         <row r="226">
           <cell r="A226">
-            <v>412090</v>
+            <v>412070</v>
           </cell>
           <cell r="B226" t="str">
-            <v>アウトオブオーダー+</v>
+            <v>ソーサリーコネクト+</v>
           </cell>
         </row>
         <row r="227">
           <cell r="A227">
-            <v>413010</v>
+            <v>412080</v>
           </cell>
           <cell r="B227" t="str">
-            <v>アーマーコード+</v>
+            <v>ウィンドライズ+</v>
           </cell>
         </row>
         <row r="228">
           <cell r="A228">
-            <v>413020</v>
+            <v>412090</v>
           </cell>
           <cell r="B228" t="str">
-            <v>クイックバリア+</v>
+            <v>アウトオブオーダー+</v>
           </cell>
         </row>
         <row r="229">
           <cell r="A229">
-            <v>413030</v>
+            <v>413010</v>
           </cell>
           <cell r="B229" t="str">
-            <v>クイックキュア+</v>
+            <v>アーマーコード+</v>
           </cell>
         </row>
         <row r="230">
           <cell r="A230">
-            <v>413040</v>
+            <v>413020</v>
           </cell>
           <cell r="B230" t="str">
-            <v>セルフシールド+</v>
+            <v>クイックバリア+</v>
           </cell>
         </row>
         <row r="231">
           <cell r="A231">
-            <v>413050</v>
+            <v>413030</v>
           </cell>
           <cell r="B231" t="str">
-            <v>パッシブジャミング+</v>
+            <v>クイックキュア+</v>
           </cell>
         </row>
         <row r="232">
           <cell r="A232">
-            <v>413060</v>
+            <v>413040</v>
           </cell>
           <cell r="B232" t="str">
-            <v>サプライカバー+</v>
+            <v>セルフシールド+</v>
           </cell>
         </row>
         <row r="233">
           <cell r="A233">
-            <v>413070</v>
+            <v>413050</v>
           </cell>
           <cell r="B233" t="str">
-            <v>アシッドラッシュ+</v>
+            <v>パッシブジャミング+</v>
           </cell>
         </row>
         <row r="234">
           <cell r="A234">
-            <v>413080</v>
+            <v>413060</v>
           </cell>
           <cell r="B234" t="str">
-            <v>ライフスティール+</v>
+            <v>サプライカバー+</v>
           </cell>
         </row>
         <row r="235">
           <cell r="A235">
-            <v>413090</v>
+            <v>413070</v>
           </cell>
           <cell r="B235" t="str">
-            <v>アイスセイバー+</v>
+            <v>アシッドラッシュ+</v>
           </cell>
         </row>
         <row r="236">
           <cell r="A236">
-            <v>414010</v>
+            <v>413080</v>
           </cell>
           <cell r="B236" t="str">
-            <v>ディバインシールド+</v>
+            <v>ライフスティール+</v>
           </cell>
         </row>
         <row r="237">
           <cell r="A237">
-            <v>414020</v>
+            <v>413090</v>
           </cell>
           <cell r="B237" t="str">
-            <v>ライフディバイド+</v>
+            <v>アイスセイバー+</v>
           </cell>
         </row>
         <row r="238">
           <cell r="A238">
-            <v>414030</v>
+            <v>414010</v>
           </cell>
           <cell r="B238" t="str">
-            <v>エイミングスコープ+</v>
+            <v>ディバインシールド+</v>
           </cell>
         </row>
         <row r="239">
           <cell r="A239">
-            <v>414040</v>
+            <v>414020</v>
           </cell>
           <cell r="B239" t="str">
-            <v>リジェネレーション+</v>
+            <v>ライフディバイド+</v>
           </cell>
         </row>
         <row r="240">
           <cell r="A240">
-            <v>414050</v>
+            <v>414030</v>
           </cell>
           <cell r="B240" t="str">
-            <v>ホープフルアイリス+</v>
+            <v>エイミングスコープ+</v>
           </cell>
         </row>
         <row r="241">
           <cell r="A241">
-            <v>414060</v>
+            <v>414040</v>
           </cell>
           <cell r="B241" t="str">
-            <v>パッシブサプライ+</v>
+            <v>リジェネレーション+</v>
           </cell>
         </row>
         <row r="242">
           <cell r="A242">
-            <v>414070</v>
+            <v>414050</v>
           </cell>
           <cell r="B242" t="str">
-            <v>ホーミングクルセイド+</v>
+            <v>ホープフルアイリス+</v>
           </cell>
         </row>
         <row r="243">
           <cell r="A243">
-            <v>414080</v>
+            <v>414060</v>
           </cell>
           <cell r="B243" t="str">
-            <v>クイックヒール+</v>
+            <v>パッシブサプライ+</v>
           </cell>
         </row>
         <row r="244">
           <cell r="A244">
-            <v>414090</v>
+            <v>414070</v>
           </cell>
           <cell r="B244" t="str">
-            <v>リレイズ+</v>
+            <v>ホーミングクルセイド+</v>
           </cell>
         </row>
         <row r="245">
           <cell r="A245">
-            <v>415010</v>
+            <v>414080</v>
           </cell>
           <cell r="B245" t="str">
-            <v>イーグルアイ+</v>
+            <v>クイックヒール+</v>
           </cell>
         </row>
         <row r="246">
           <cell r="A246">
-            <v>415020</v>
+            <v>414090</v>
           </cell>
           <cell r="B246" t="str">
-            <v>ネヴァーエンド+</v>
+            <v>リレイズ+</v>
           </cell>
         </row>
         <row r="247">
           <cell r="A247">
-            <v>415030</v>
+            <v>415010</v>
           </cell>
           <cell r="B247" t="str">
-            <v>グレイブアクト+</v>
+            <v>イーグルアイ+</v>
           </cell>
         </row>
         <row r="248">
           <cell r="A248">
-            <v>415040</v>
+            <v>415020</v>
           </cell>
           <cell r="B248" t="str">
-            <v>スカルグラッジ+</v>
+            <v>ネヴァーエンド+</v>
           </cell>
         </row>
         <row r="249">
           <cell r="A249">
-            <v>415050</v>
+            <v>415030</v>
           </cell>
           <cell r="B249" t="str">
-            <v>ネガティブドレイン+</v>
+            <v>グレイブアクト+</v>
           </cell>
         </row>
         <row r="250">
           <cell r="A250">
-            <v>415060</v>
+            <v>415040</v>
           </cell>
           <cell r="B250" t="str">
-            <v>アンデッドペイン+</v>
+            <v>スカルグラッジ+</v>
           </cell>
         </row>
         <row r="251">
           <cell r="A251">
-            <v>415070</v>
+            <v>415050</v>
           </cell>
           <cell r="B251" t="str">
-            <v>ジャックポッド+</v>
+            <v>ネガティブドレイン+</v>
           </cell>
         </row>
         <row r="252">
           <cell r="A252">
-            <v>415080</v>
+            <v>415060</v>
           </cell>
           <cell r="B252" t="str">
-            <v>ヒールハント+</v>
+            <v>アンデッドペイン+</v>
           </cell>
         </row>
         <row r="253">
           <cell r="A253">
+            <v>415070</v>
+          </cell>
+          <cell r="B253" t="str">
+            <v>ジャックポッド+</v>
+          </cell>
+        </row>
+        <row r="254">
+          <cell r="A254">
+            <v>415080</v>
+          </cell>
+          <cell r="B254" t="str">
+            <v>ヒールハント+</v>
+          </cell>
+        </row>
+        <row r="255">
+          <cell r="A255">
             <v>415090</v>
           </cell>
-          <cell r="B253" t="str">
+          <cell r="B255" t="str">
             <v>クイックカース+</v>
           </cell>
         </row>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="7820"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -394,10 +394,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -422,6 +422,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -431,6 +438,37 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -438,7 +476,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -470,13 +508,20 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -484,30 +529,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -521,41 +551,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -569,6 +569,72 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -592,13 +658,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -610,37 +670,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -658,7 +706,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -670,37 +736,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -712,43 +748,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -773,33 +773,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -834,13 +812,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -859,6 +841,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -867,16 +867,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -885,127 +885,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3540,19 +3540,19 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="Q2">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="R2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="S2" t="s">
         <v>19</v>
@@ -3599,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -3658,19 +3658,19 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="Q4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R4">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="S4" t="s">
         <v>23</v>
@@ -3717,16 +3717,16 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Q5">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="R5">
         <v>50</v>
@@ -3782,10 +3782,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q6">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R6">
         <v>70</v>
@@ -3835,13 +3835,13 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Q7">
         <v>40</v>
@@ -3894,19 +3894,19 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="R8">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="S8" t="s">
         <v>19</v>
@@ -3953,19 +3953,19 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="R9">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="S9" t="s">
         <v>19</v>
@@ -4012,16 +4012,16 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="Q10">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="R10">
         <v>40</v>
@@ -4077,13 +4077,13 @@
         <v>0</v>
       </c>
       <c r="P11">
+        <v>50</v>
+      </c>
+      <c r="Q11">
+        <v>40</v>
+      </c>
+      <c r="R11">
         <v>60</v>
-      </c>
-      <c r="Q11">
-        <v>20</v>
-      </c>
-      <c r="R11">
-        <v>70</v>
       </c>
       <c r="S11" t="s">
         <v>23</v>
@@ -4130,19 +4130,19 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q12">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="R12">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="S12" t="s">
         <v>19</v>
@@ -4189,19 +4189,19 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="Q13">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R13">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="S13" t="s">
         <v>21</v>
@@ -4248,19 +4248,19 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="Q14">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="R14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="S14" t="s">
         <v>35</v>
@@ -4307,16 +4307,16 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Q15">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="R15">
         <v>40</v>
@@ -4366,19 +4366,19 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="Q16">
         <v>20</v>
       </c>
       <c r="R16">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="S16" t="s">
         <v>25</v>
@@ -4484,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="N18">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="N20">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -4614,7 +4614,7 @@
         <v>25</v>
       </c>
       <c r="R20">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="S20" t="s">
         <v>23</v>
@@ -4661,19 +4661,19 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="Q21">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="R21">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="S21" t="s">
         <v>19</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -394,10 +394,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -416,14 +416,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -437,16 +445,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -461,30 +484,37 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -498,9 +528,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -513,51 +558,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -568,55 +568,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -634,37 +616,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -676,25 +652,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -706,13 +694,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -724,25 +706,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -762,11 +762,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -782,17 +797,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -827,6 +836,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -841,24 +859,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -867,145 +867,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3540,19 +3540,19 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="Q2">
         <v>60</v>
       </c>
       <c r="R2">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="S2" t="s">
         <v>19</v>
@@ -3599,19 +3599,19 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="Q3">
         <v>30</v>
       </c>
       <c r="R3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="S3" t="s">
         <v>21</v>
@@ -3658,19 +3658,19 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="Q4">
         <v>20</v>
       </c>
       <c r="R4">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="S4" t="s">
         <v>23</v>
@@ -3717,19 +3717,19 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="Q5">
         <v>30</v>
       </c>
       <c r="R5">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="S5" t="s">
         <v>25</v>
@@ -3776,19 +3776,19 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="Q6">
         <v>20</v>
       </c>
       <c r="R6">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="S6" t="s">
         <v>23</v>
@@ -3835,19 +3835,19 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="Q7">
         <v>40</v>
       </c>
       <c r="R7">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="S7" t="s">
         <v>23</v>
@@ -3894,19 +3894,19 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="Q8">
         <v>40</v>
       </c>
       <c r="R8">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="S8" t="s">
         <v>19</v>
@@ -3953,19 +3953,19 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="Q9">
         <v>70</v>
       </c>
       <c r="R9">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="S9" t="s">
         <v>19</v>
@@ -4012,19 +4012,19 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="Q10">
         <v>40</v>
       </c>
       <c r="R10">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="S10" t="s">
         <v>25</v>
@@ -4071,19 +4071,19 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="Q11">
         <v>40</v>
       </c>
       <c r="R11">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="S11" t="s">
         <v>23</v>
@@ -4130,19 +4130,19 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="Q12">
         <v>50</v>
       </c>
       <c r="R12">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="S12" t="s">
         <v>19</v>
@@ -4189,19 +4189,19 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="Q13">
         <v>40</v>
       </c>
       <c r="R13">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="S13" t="s">
         <v>21</v>
@@ -4248,19 +4248,19 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="Q14">
         <v>60</v>
       </c>
       <c r="R14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="S14" t="s">
         <v>35</v>
@@ -4307,19 +4307,19 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="Q15">
         <v>70</v>
       </c>
       <c r="R15">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="S15" t="s">
         <v>25</v>
@@ -4366,19 +4366,19 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="Q16">
         <v>20</v>
       </c>
       <c r="R16">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="S16" t="s">
         <v>25</v>
@@ -4425,19 +4425,19 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="Q17">
         <v>40</v>
       </c>
       <c r="R17">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="S17" t="s">
         <v>25</v>
@@ -4484,19 +4484,19 @@
         <v>0</v>
       </c>
       <c r="N18">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="Q18">
         <v>35</v>
       </c>
       <c r="R18">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="S18" t="s">
         <v>21</v>
@@ -4543,19 +4543,19 @@
         <v>0</v>
       </c>
       <c r="N19">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="Q19">
         <v>30</v>
       </c>
       <c r="R19">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="S19" t="s">
         <v>35</v>
@@ -4602,19 +4602,19 @@
         <v>0</v>
       </c>
       <c r="N20">
+        <v>160</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
         <v>80</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>50</v>
       </c>
       <c r="Q20">
         <v>25</v>
       </c>
       <c r="R20">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="S20" t="s">
         <v>23</v>
@@ -4661,19 +4661,19 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="Q21">
         <v>60</v>
       </c>
       <c r="R21">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="S21" t="s">
         <v>19</v>
@@ -4720,19 +4720,19 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="Q22">
         <v>60</v>
       </c>
       <c r="R22">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:18">

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -394,10 +394,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -415,41 +415,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -467,24 +460,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -500,39 +477,9 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -558,6 +505,59 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -574,25 +574,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -604,13 +604,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -622,31 +628,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -664,7 +646,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -676,7 +664,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -688,19 +700,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -724,31 +742,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -759,6 +759,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -773,35 +782,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -836,15 +816,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -859,6 +830,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -867,16 +867,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -885,94 +885,88 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -981,31 +975,37 @@
     <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1931,143 +1931,143 @@
         </row>
         <row r="105">
           <cell r="A105">
-            <v>100110</v>
+            <v>30030</v>
           </cell>
           <cell r="B105" t="str">
-            <v>ソーイングアームド</v>
+            <v>ガッツ</v>
           </cell>
         </row>
         <row r="106">
           <cell r="A106">
-            <v>100120</v>
+            <v>100110</v>
           </cell>
           <cell r="B106" t="str">
-            <v>エターナルロンド</v>
+            <v>ソーイングアームド</v>
           </cell>
         </row>
         <row r="107">
           <cell r="A107">
-            <v>100210</v>
+            <v>100120</v>
           </cell>
           <cell r="B107" t="str">
-            <v>アブソリュートパリィ</v>
+            <v>エターナルロンド</v>
           </cell>
         </row>
         <row r="108">
           <cell r="A108">
-            <v>100220</v>
+            <v>100210</v>
           </cell>
           <cell r="B108" t="str">
-            <v>レヴェリー</v>
+            <v>アブソリュートパリィ</v>
           </cell>
         </row>
         <row r="109">
           <cell r="A109">
-            <v>100310</v>
+            <v>100220</v>
           </cell>
           <cell r="B109" t="str">
-            <v>セイクリッドバリア</v>
+            <v>レヴェリー</v>
           </cell>
         </row>
         <row r="110">
           <cell r="A110">
-            <v>100320</v>
+            <v>100310</v>
           </cell>
           <cell r="B110" t="str">
-            <v>リベンジニードル</v>
+            <v>セイクリッドバリア</v>
           </cell>
         </row>
         <row r="111">
           <cell r="A111">
-            <v>100410</v>
+            <v>100320</v>
           </cell>
           <cell r="B111" t="str">
-            <v>アバンデンス</v>
+            <v>リベンジニードル</v>
           </cell>
         </row>
         <row r="112">
           <cell r="A112">
-            <v>100420</v>
+            <v>100410</v>
           </cell>
           <cell r="B112" t="str">
-            <v>ハーヴェスト</v>
+            <v>アバンデンス</v>
           </cell>
         </row>
         <row r="113">
           <cell r="A113">
-            <v>100510</v>
+            <v>100420</v>
           </cell>
           <cell r="B113" t="str">
-            <v>カースドブレイク</v>
+            <v>ハーヴェスト</v>
           </cell>
         </row>
         <row r="114">
           <cell r="A114">
-            <v>100520</v>
+            <v>100510</v>
           </cell>
           <cell r="B114" t="str">
-            <v>ムーンライトレイ</v>
+            <v>カースドブレイク</v>
           </cell>
         </row>
         <row r="115">
           <cell r="A115">
-            <v>100610</v>
+            <v>100520</v>
           </cell>
           <cell r="B115" t="str">
-            <v>サンフレイム</v>
+            <v>ムーンライトレイ</v>
           </cell>
         </row>
         <row r="116">
           <cell r="A116">
-            <v>100620</v>
+            <v>100610</v>
           </cell>
           <cell r="B116" t="str">
-            <v>フレイムタン</v>
+            <v>サンフレイム</v>
           </cell>
         </row>
         <row r="117">
           <cell r="A117">
-            <v>100710</v>
+            <v>100620</v>
           </cell>
           <cell r="B117" t="str">
-            <v>ライズザフラッグ</v>
+            <v>フレイムタン</v>
           </cell>
         </row>
         <row r="118">
           <cell r="A118">
-            <v>100720</v>
+            <v>100710</v>
           </cell>
           <cell r="B118" t="str">
-            <v>オーバーリミット</v>
+            <v>ライズザフラッグ</v>
           </cell>
         </row>
         <row r="119">
           <cell r="A119">
-            <v>100810</v>
+            <v>100720</v>
           </cell>
           <cell r="B119" t="str">
-            <v>テンパランス</v>
+            <v>オーバーリミット</v>
           </cell>
         </row>
         <row r="120">
           <cell r="A120">
-            <v>100820</v>
+            <v>100810</v>
           </cell>
           <cell r="B120" t="str">
-            <v>シエルクルセイダー</v>
+            <v>テンパランス</v>
           </cell>
         </row>
         <row r="121">
           <cell r="A121">
-            <v>100910</v>
+            <v>100820</v>
           </cell>
           <cell r="B121" t="str">
-            <v>バーニングカウンター</v>
+            <v>シエルクルセイダー</v>
           </cell>
         </row>
         <row r="122">
           <cell r="A122">
-            <v>100911</v>
+            <v>100910</v>
           </cell>
           <cell r="B122" t="str">
             <v>バーニングカウンター</v>
@@ -2075,15 +2075,15 @@
         </row>
         <row r="123">
           <cell r="A123">
-            <v>100920</v>
+            <v>100911</v>
           </cell>
           <cell r="B123" t="str">
-            <v>プロミネンス</v>
+            <v>バーニングカウンター</v>
           </cell>
         </row>
         <row r="124">
           <cell r="A124">
-            <v>100921</v>
+            <v>100920</v>
           </cell>
           <cell r="B124" t="str">
             <v>プロミネンス</v>
@@ -2091,1049 +2091,1233 @@
         </row>
         <row r="125">
           <cell r="A125">
-            <v>101010</v>
+            <v>100921</v>
           </cell>
           <cell r="B125" t="str">
-            <v>エウロス</v>
+            <v>プロミネンス</v>
           </cell>
         </row>
         <row r="126">
           <cell r="A126">
-            <v>101020</v>
+            <v>101010</v>
           </cell>
           <cell r="B126" t="str">
-            <v>ボレアス</v>
+            <v>エウロス</v>
           </cell>
         </row>
         <row r="127">
           <cell r="A127">
-            <v>101110</v>
+            <v>101020</v>
           </cell>
           <cell r="B127" t="str">
-            <v>アバランシュ</v>
+            <v>ボレアス</v>
           </cell>
         </row>
         <row r="128">
           <cell r="A128">
-            <v>101120</v>
+            <v>101110</v>
           </cell>
           <cell r="B128" t="str">
-            <v>ブリザードコフィン</v>
+            <v>アバランシュ</v>
           </cell>
         </row>
         <row r="129">
           <cell r="A129">
-            <v>200210</v>
+            <v>101120</v>
           </cell>
           <cell r="B129" t="str">
-            <v>マイトレインフォース</v>
+            <v>ブリザードコフィン</v>
           </cell>
         </row>
         <row r="130">
           <cell r="A130">
-            <v>200220</v>
+            <v>200110</v>
           </cell>
           <cell r="B130" t="str">
-            <v>カタストロフィ</v>
+            <v>スリータイムス</v>
           </cell>
         </row>
         <row r="131">
           <cell r="A131">
-            <v>200230</v>
+            <v>200120</v>
           </cell>
           <cell r="B131" t="str">
-            <v>悪魔(ベリト)</v>
+            <v>アングリークライ</v>
           </cell>
         </row>
         <row r="132">
           <cell r="A132">
-            <v>200310</v>
+            <v>200210</v>
           </cell>
           <cell r="B132" t="str">
-            <v>プルガシオン</v>
+            <v>マイトレインフォース</v>
           </cell>
         </row>
         <row r="133">
           <cell r="A133">
-            <v>200320</v>
+            <v>200220</v>
           </cell>
           <cell r="B133" t="str">
-            <v>プリエステス</v>
+            <v>カタストロフィ</v>
           </cell>
         </row>
         <row r="134">
           <cell r="A134">
-            <v>200330</v>
+            <v>200230</v>
           </cell>
           <cell r="B134" t="str">
-            <v>悪魔(パイモン)</v>
+            <v>悪魔(ベリト)</v>
           </cell>
         </row>
         <row r="135">
           <cell r="A135">
-            <v>200410</v>
+            <v>200310</v>
           </cell>
           <cell r="B135" t="str">
-            <v>コウソクテンショウ</v>
+            <v>プルガシオン</v>
           </cell>
         </row>
         <row r="136">
           <cell r="A136">
-            <v>200411</v>
+            <v>200320</v>
           </cell>
           <cell r="B136" t="str">
-            <v>コウソクテンショウ</v>
+            <v>プリエステス</v>
           </cell>
         </row>
         <row r="137">
           <cell r="A137">
-            <v>200420</v>
+            <v>200330</v>
           </cell>
           <cell r="B137" t="str">
-            <v>アンチバフ</v>
+            <v>悪魔(パイモン)</v>
           </cell>
         </row>
         <row r="138">
           <cell r="A138">
-            <v>200430</v>
+            <v>200410</v>
           </cell>
           <cell r="B138" t="str">
-            <v>悪魔(アンドラス)</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="139">
           <cell r="A139">
-            <v>200510</v>
+            <v>200411</v>
           </cell>
           <cell r="B139" t="str">
-            <v>カウントダウン</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="140">
           <cell r="A140">
-            <v>200520</v>
+            <v>200420</v>
           </cell>
           <cell r="B140" t="str">
-            <v>グラウンドゼロ</v>
+            <v>アンチバフ</v>
           </cell>
         </row>
         <row r="141">
           <cell r="A141">
-            <v>200530</v>
+            <v>200430</v>
           </cell>
           <cell r="B141" t="str">
-            <v>悪魔(ビフロンス)</v>
+            <v>悪魔(アンドラス)</v>
           </cell>
         </row>
         <row r="142">
           <cell r="A142">
-            <v>201010</v>
+            <v>200510</v>
           </cell>
           <cell r="B142" t="str">
-            <v>カオスペイン</v>
+            <v>カウントダウン</v>
           </cell>
         </row>
         <row r="143">
           <cell r="A143">
-            <v>201020</v>
+            <v>200520</v>
           </cell>
           <cell r="B143" t="str">
-            <v>フォールンワン</v>
+            <v>グラウンドゼロ</v>
           </cell>
         </row>
         <row r="144">
           <cell r="A144">
-            <v>201030</v>
+            <v>200530</v>
           </cell>
           <cell r="B144" t="str">
-            <v>アンリマユ</v>
+            <v>悪魔(ビフロンス)</v>
           </cell>
         </row>
         <row r="145">
           <cell r="A145">
-            <v>300010</v>
+            <v>201010</v>
           </cell>
           <cell r="B145" t="str">
-            <v>ライフブースト</v>
+            <v>カオスペイン</v>
           </cell>
         </row>
         <row r="146">
           <cell r="A146">
-            <v>300020</v>
+            <v>201020</v>
           </cell>
           <cell r="B146" t="str">
-            <v>スピリットチャージ</v>
+            <v>フォールンワン</v>
           </cell>
         </row>
         <row r="147">
           <cell r="A147">
-            <v>300030</v>
+            <v>201030</v>
           </cell>
           <cell r="B147" t="str">
-            <v>フォースライズ</v>
+            <v>アンリマユ</v>
           </cell>
         </row>
         <row r="148">
           <cell r="A148">
-            <v>300040</v>
+            <v>300010</v>
           </cell>
           <cell r="B148" t="str">
-            <v>ディフェンスオーラ</v>
+            <v>ライフブースト</v>
           </cell>
         </row>
         <row r="149">
           <cell r="A149">
-            <v>300050</v>
+            <v>300020</v>
           </cell>
           <cell r="B149" t="str">
-            <v>ラピッドムーブ</v>
+            <v>スピリットチャージ</v>
           </cell>
         </row>
         <row r="150">
           <cell r="A150">
-            <v>300130</v>
+            <v>300030</v>
           </cell>
           <cell r="B150" t="str">
-            <v>アタックブレイク</v>
+            <v>フォースライズ</v>
           </cell>
         </row>
         <row r="151">
           <cell r="A151">
-            <v>300140</v>
+            <v>300040</v>
           </cell>
           <cell r="B151" t="str">
-            <v>シールドバニッシュ</v>
+            <v>ディフェンスオーラ</v>
           </cell>
         </row>
         <row r="152">
           <cell r="A152">
-            <v>300210</v>
+            <v>300050</v>
           </cell>
           <cell r="B152" t="str">
-            <v>エーテルリチャージ</v>
+            <v>ラピッドムーブ</v>
           </cell>
         </row>
         <row r="153">
           <cell r="A153">
-            <v>300220</v>
+            <v>300130</v>
           </cell>
           <cell r="B153" t="str">
-            <v>リカバリーエンハンス</v>
+            <v>アタックブレイク</v>
           </cell>
         </row>
         <row r="154">
           <cell r="A154">
-            <v>300230</v>
+            <v>300140</v>
           </cell>
           <cell r="B154" t="str">
-            <v>ヴェンジェンス</v>
+            <v>シールドバニッシュ</v>
           </cell>
         </row>
         <row r="155">
           <cell r="A155">
-            <v>301010</v>
+            <v>300210</v>
           </cell>
           <cell r="B155" t="str">
-            <v>ディケイドリセット</v>
+            <v>エーテルリチャージ</v>
           </cell>
         </row>
         <row r="156">
           <cell r="A156">
-            <v>301020</v>
+            <v>300220</v>
           </cell>
           <cell r="B156" t="str">
-            <v>ウォーリアーブラッド</v>
+            <v>リカバリーエンハンス</v>
           </cell>
         </row>
         <row r="157">
           <cell r="A157">
-            <v>301030</v>
+            <v>300230</v>
           </cell>
           <cell r="B157" t="str">
-            <v>トライアングルガード</v>
+            <v>ヴェンジェンス</v>
           </cell>
         </row>
         <row r="158">
           <cell r="A158">
-            <v>301040</v>
+            <v>301010</v>
           </cell>
           <cell r="B158" t="str">
-            <v>セーフティバリア</v>
+            <v>ディケイドリセット</v>
           </cell>
         </row>
         <row r="159">
           <cell r="A159">
-            <v>301050</v>
+            <v>301020</v>
           </cell>
           <cell r="B159" t="str">
-            <v>ヒロインズハイ</v>
+            <v>ウォーリアーブラッド</v>
           </cell>
         </row>
         <row r="160">
           <cell r="A160">
-            <v>301060</v>
+            <v>301030</v>
           </cell>
           <cell r="B160" t="str">
-            <v>セカンドステージ</v>
+            <v>トライアングルガード</v>
           </cell>
         </row>
         <row r="161">
           <cell r="A161">
-            <v>301070</v>
+            <v>301040</v>
           </cell>
           <cell r="B161" t="str">
-            <v>ハイヒットポイント</v>
+            <v>セーフティバリア</v>
           </cell>
         </row>
         <row r="162">
           <cell r="A162">
-            <v>301080</v>
+            <v>301050</v>
           </cell>
           <cell r="B162" t="str">
-            <v>セプタブラスト</v>
+            <v>ヒロインズハイ</v>
           </cell>
         </row>
         <row r="163">
           <cell r="A163">
-            <v>301090</v>
+            <v>301060</v>
           </cell>
           <cell r="B163" t="str">
-            <v>イニシャルブロッカー</v>
+            <v>セカンドステージ</v>
           </cell>
         </row>
         <row r="164">
           <cell r="A164">
-            <v>301100</v>
+            <v>301070</v>
           </cell>
           <cell r="B164" t="str">
-            <v>ファーストテイク</v>
+            <v>ハイヒットポイント</v>
           </cell>
         </row>
         <row r="165">
           <cell r="A165">
-            <v>310010</v>
+            <v>301080</v>
           </cell>
           <cell r="B165" t="str">
-            <v>妖精の祈り</v>
+            <v>セプタブラスト</v>
           </cell>
         </row>
         <row r="166">
           <cell r="A166">
-            <v>310020</v>
+            <v>301090</v>
           </cell>
           <cell r="B166" t="str">
-            <v>月のかけら</v>
+            <v>イニシャルブロッカー</v>
           </cell>
         </row>
         <row r="167">
           <cell r="A167">
-            <v>310030</v>
+            <v>301100</v>
           </cell>
           <cell r="B167" t="str">
-            <v>錬金術師の遺稿</v>
+            <v>ファーストテイク</v>
           </cell>
         </row>
         <row r="168">
           <cell r="A168">
-            <v>310040</v>
+            <v>310010</v>
           </cell>
           <cell r="B168" t="str">
-            <v>レイヴンバナー</v>
+            <v>妖精の祈り</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169">
-            <v>310041</v>
+            <v>310020</v>
           </cell>
           <cell r="B169" t="str">
-            <v>レイヴンバナー</v>
+            <v>月のかけら</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170">
-            <v>310130</v>
+            <v>310030</v>
           </cell>
           <cell r="B170" t="str">
-            <v>ヒールユニット</v>
+            <v>商売の才覚書</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171">
-            <v>401010</v>
+            <v>310040</v>
           </cell>
           <cell r="B171" t="str">
-            <v>ファイアボール+</v>
+            <v>レイヴンバナー</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172">
-            <v>401020</v>
+            <v>310041</v>
           </cell>
           <cell r="B172" t="str">
-            <v>バーンストーム+</v>
+            <v>レイヴンバナー</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173">
-            <v>401030</v>
+            <v>310050</v>
           </cell>
           <cell r="B173" t="str">
-            <v>ヒートスタンプ+</v>
+            <v>先陣の心得</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174">
-            <v>401040</v>
+            <v>310130</v>
           </cell>
           <cell r="B174" t="str">
-            <v>ソードアダプト+</v>
+            <v>ヒールユニット</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175">
-            <v>401050</v>
+            <v>320010</v>
           </cell>
           <cell r="B175" t="str">
-            <v>フレイムレイン+</v>
+            <v>訓練所Lv1</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176">
-            <v>401060</v>
+            <v>320011</v>
           </cell>
           <cell r="B176" t="str">
-            <v>イクスティンクション+</v>
+            <v>訓練所Lv2</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177">
-            <v>401070</v>
+            <v>320012</v>
           </cell>
           <cell r="B177" t="str">
-            <v>バーニングソウル+</v>
+            <v>訓練所Lv3</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178">
-            <v>401080</v>
+            <v>320020</v>
           </cell>
           <cell r="B178" t="str">
-            <v>レイジングバウンサー+</v>
+            <v>研究施設Lv1</v>
           </cell>
         </row>
         <row r="179">
           <cell r="A179">
-            <v>402010</v>
+            <v>320021</v>
           </cell>
           <cell r="B179" t="str">
-            <v>ディスチャージ+</v>
+            <v>研究施設Lv2</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180">
-            <v>402020</v>
+            <v>320022</v>
           </cell>
           <cell r="B180" t="str">
-            <v>イベイドコード+</v>
+            <v>研究施設Lv3</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181">
-            <v>402030</v>
+            <v>320030</v>
           </cell>
           <cell r="B181" t="str">
-            <v>ショックインパルス+</v>
+            <v>資料館Lv1</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182">
-            <v>402040</v>
+            <v>320031</v>
           </cell>
           <cell r="B182" t="str">
-            <v>トラストチェイン+</v>
+            <v>資料館Lv2</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183">
-            <v>402050</v>
+            <v>320032</v>
           </cell>
           <cell r="B183" t="str">
-            <v>スペルバニシング+</v>
+            <v>資料館Lv3</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184">
-            <v>402060</v>
+            <v>320040</v>
           </cell>
           <cell r="B184" t="str">
-            <v>アーテニーストライク+</v>
+            <v>潜伏技術Lv1</v>
           </cell>
         </row>
         <row r="185">
           <cell r="A185">
-            <v>402070</v>
+            <v>321010</v>
           </cell>
           <cell r="B185" t="str">
-            <v>コンセントレイト+</v>
+            <v>炎の祭壇</v>
           </cell>
         </row>
         <row r="186">
           <cell r="A186">
-            <v>402080</v>
+            <v>321020</v>
           </cell>
           <cell r="B186" t="str">
-            <v>ディレイマジック+</v>
+            <v>稲妻の祭壇</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187">
-            <v>403010</v>
+            <v>321030</v>
           </cell>
           <cell r="B187" t="str">
-            <v>アイスブレイド+</v>
+            <v>蒼の祭壇</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188">
-            <v>403020</v>
+            <v>321040</v>
           </cell>
           <cell r="B188" t="str">
-            <v>カウンターオーラ+</v>
+            <v>光の祭壇</v>
           </cell>
         </row>
         <row r="189">
           <cell r="A189">
-            <v>403030</v>
+            <v>321050</v>
           </cell>
           <cell r="B189" t="str">
-            <v>ラインプロテクト+</v>
+            <v>月の祭壇</v>
           </cell>
         </row>
         <row r="190">
           <cell r="A190">
-            <v>403040</v>
+            <v>322010</v>
           </cell>
           <cell r="B190" t="str">
-            <v>エスコートソール+</v>
+            <v>食糧庫Lv1</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191">
-            <v>403050</v>
+            <v>322020</v>
           </cell>
           <cell r="B191" t="str">
-            <v>ディープフリーズ+</v>
+            <v>攻撃技術Lv1</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192">
-            <v>403060</v>
+            <v>322030</v>
           </cell>
           <cell r="B192" t="str">
-            <v>バブルブロウ+</v>
+            <v>防御技術Lv1</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193">
-            <v>403070</v>
+            <v>322040</v>
           </cell>
           <cell r="B193" t="str">
-            <v>アクアミラージュ+</v>
+            <v>詠唱技術Lv1</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194">
-            <v>403080</v>
+            <v>401010</v>
           </cell>
           <cell r="B194" t="str">
-            <v>フロストシールド+</v>
+            <v>ファイアボール+</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195">
-            <v>404010</v>
+            <v>401020</v>
           </cell>
           <cell r="B195" t="str">
-            <v>セイントレーザー+</v>
+            <v>バーンストーム+</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196">
-            <v>404020</v>
+            <v>401030</v>
           </cell>
           <cell r="B196" t="str">
-            <v>ペネトレイト+</v>
+            <v>ヒートスタンプ+</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197">
-            <v>404030</v>
+            <v>401040</v>
           </cell>
           <cell r="B197" t="str">
-            <v>ヒーリング+</v>
+            <v>ソードアダプト+</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198">
-            <v>404040</v>
+            <v>401050</v>
           </cell>
           <cell r="B198" t="str">
-            <v>リザイアフォトン+</v>
+            <v>フレイムレイン+</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199">
-            <v>404050</v>
+            <v>401060</v>
           </cell>
           <cell r="B199" t="str">
-            <v>べネディクション+</v>
+            <v>イクスティンクション+</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200">
-            <v>404060</v>
+            <v>401070</v>
           </cell>
           <cell r="B200" t="str">
-            <v>ホーリーグレイス+</v>
+            <v>バーニングソウル+</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201">
-            <v>404070</v>
+            <v>401080</v>
           </cell>
           <cell r="B201" t="str">
-            <v>キュアエール+</v>
+            <v>レイジングバウンサー+</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202">
-            <v>404080</v>
+            <v>402010</v>
           </cell>
           <cell r="B202" t="str">
-            <v>ラインバリア+</v>
+            <v>ディスチャージ+</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203">
-            <v>405010</v>
+            <v>402020</v>
           </cell>
           <cell r="B203" t="str">
-            <v>ダークプリズン+</v>
+            <v>イベイドコード+</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204">
-            <v>405020</v>
+            <v>402030</v>
           </cell>
           <cell r="B204" t="str">
-            <v>ユーサネイジア+</v>
+            <v>ショックインパルス+</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205">
-            <v>405030</v>
+            <v>402040</v>
           </cell>
           <cell r="B205" t="str">
-            <v>ドレインヒール+</v>
+            <v>トラストチェイン+</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206">
-            <v>405040</v>
+            <v>402050</v>
           </cell>
           <cell r="B206" t="str">
-            <v>アビサルデスペア+</v>
+            <v>スペルバニシング+</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207">
-            <v>405050</v>
+            <v>402060</v>
           </cell>
           <cell r="B207" t="str">
-            <v>ディプラヴィティ+</v>
+            <v>アーテニーストライク+</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208">
-            <v>405060</v>
+            <v>402070</v>
           </cell>
           <cell r="B208" t="str">
-            <v>ダークネス+</v>
+            <v>コンセントレイト+</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209">
-            <v>405070</v>
+            <v>402080</v>
           </cell>
           <cell r="B209" t="str">
-            <v>シェイディークラウド+</v>
+            <v>ディレイマジック+</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210">
-            <v>405080</v>
+            <v>403010</v>
           </cell>
           <cell r="B210" t="str">
-            <v>ポイズンブロウ+</v>
+            <v>アイスブレイド+</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211">
-            <v>411010</v>
+            <v>403020</v>
           </cell>
           <cell r="B211" t="str">
-            <v>ウルフソウル+</v>
+            <v>カウンターオーラ+</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212">
-            <v>411020</v>
+            <v>403030</v>
           </cell>
           <cell r="B212" t="str">
-            <v>プリディカメント+</v>
+            <v>ラインプロテクト+</v>
           </cell>
         </row>
         <row r="213">
           <cell r="A213">
-            <v>411030</v>
+            <v>403040</v>
           </cell>
           <cell r="B213" t="str">
-            <v>アサルトシフト+</v>
+            <v>エスコートソール+</v>
           </cell>
         </row>
         <row r="214">
           <cell r="A214">
-            <v>411040</v>
+            <v>403050</v>
           </cell>
           <cell r="B214" t="str">
-            <v>アクティブギフト+</v>
+            <v>ディープフリーズ+</v>
           </cell>
         </row>
         <row r="215">
           <cell r="A215">
-            <v>411050</v>
+            <v>403060</v>
           </cell>
           <cell r="B215" t="str">
-            <v>イグナイテッド+</v>
+            <v>バブルブロウ+</v>
           </cell>
         </row>
         <row r="216">
           <cell r="A216">
-            <v>411060</v>
+            <v>403070</v>
           </cell>
           <cell r="B216" t="str">
-            <v>ライジングファイア+</v>
+            <v>アクアミラージュ+</v>
           </cell>
         </row>
         <row r="217">
           <cell r="A217">
-            <v>411070</v>
+            <v>403080</v>
           </cell>
           <cell r="B217" t="str">
-            <v>ルージュバック+</v>
+            <v>フロストシールド+</v>
           </cell>
         </row>
         <row r="218">
           <cell r="A218">
-            <v>411080</v>
+            <v>404010</v>
           </cell>
           <cell r="B218" t="str">
-            <v>パワーエール+</v>
+            <v>セイントレーザー+</v>
           </cell>
         </row>
         <row r="219">
           <cell r="A219">
-            <v>411090</v>
+            <v>404020</v>
           </cell>
           <cell r="B219" t="str">
-            <v>スレイプニル+</v>
+            <v>ペネトレイト+</v>
           </cell>
         </row>
         <row r="220">
           <cell r="A220">
-            <v>412010</v>
+            <v>404030</v>
           </cell>
           <cell r="B220" t="str">
-            <v>エクステンション+</v>
+            <v>ヒーリング+</v>
           </cell>
         </row>
         <row r="221">
           <cell r="A221">
-            <v>412020</v>
+            <v>404040</v>
           </cell>
           <cell r="B221" t="str">
-            <v>ヘブンリーラック+</v>
+            <v>リザイアフォトン+</v>
           </cell>
         </row>
         <row r="222">
           <cell r="A222">
-            <v>412030</v>
+            <v>404050</v>
           </cell>
           <cell r="B222" t="str">
-            <v>スウィフトカレント+</v>
+            <v>べネディクション+</v>
           </cell>
         </row>
         <row r="223">
           <cell r="A223">
-            <v>412040</v>
+            <v>404060</v>
           </cell>
           <cell r="B223" t="str">
-            <v>イヴェイドオール+</v>
+            <v>ホーリーグレイス+</v>
           </cell>
         </row>
         <row r="224">
           <cell r="A224">
-            <v>412050</v>
+            <v>404070</v>
           </cell>
           <cell r="B224" t="str">
-            <v>クイックムーブ+</v>
+            <v>キュアエール+</v>
           </cell>
         </row>
         <row r="225">
           <cell r="A225">
-            <v>412060</v>
+            <v>404080</v>
           </cell>
           <cell r="B225" t="str">
-            <v>チェイスマジック+</v>
+            <v>ラインバリア+</v>
           </cell>
         </row>
         <row r="226">
           <cell r="A226">
-            <v>412070</v>
+            <v>405010</v>
           </cell>
           <cell r="B226" t="str">
-            <v>ソーサリーコネクト+</v>
+            <v>ダークプリズン+</v>
           </cell>
         </row>
         <row r="227">
           <cell r="A227">
-            <v>412080</v>
+            <v>405020</v>
           </cell>
           <cell r="B227" t="str">
-            <v>ウィンドライズ+</v>
+            <v>ユーサネイジア+</v>
           </cell>
         </row>
         <row r="228">
           <cell r="A228">
-            <v>412090</v>
+            <v>405030</v>
           </cell>
           <cell r="B228" t="str">
-            <v>アウトオブオーダー+</v>
+            <v>ドレインヒール+</v>
           </cell>
         </row>
         <row r="229">
           <cell r="A229">
-            <v>413010</v>
+            <v>405040</v>
           </cell>
           <cell r="B229" t="str">
-            <v>アーマーコード+</v>
+            <v>アビサルデスペア+</v>
           </cell>
         </row>
         <row r="230">
           <cell r="A230">
-            <v>413020</v>
+            <v>405050</v>
           </cell>
           <cell r="B230" t="str">
-            <v>クイックバリア+</v>
+            <v>ディプラヴィティ+</v>
           </cell>
         </row>
         <row r="231">
           <cell r="A231">
-            <v>413030</v>
+            <v>405060</v>
           </cell>
           <cell r="B231" t="str">
-            <v>クイックキュア+</v>
+            <v>ダークネス+</v>
           </cell>
         </row>
         <row r="232">
           <cell r="A232">
-            <v>413040</v>
+            <v>405070</v>
           </cell>
           <cell r="B232" t="str">
-            <v>セルフシールド+</v>
+            <v>シェイディークラウド+</v>
           </cell>
         </row>
         <row r="233">
           <cell r="A233">
-            <v>413050</v>
+            <v>405080</v>
           </cell>
           <cell r="B233" t="str">
-            <v>パッシブジャミング+</v>
+            <v>ポイズンブロウ+</v>
           </cell>
         </row>
         <row r="234">
           <cell r="A234">
-            <v>413060</v>
+            <v>411010</v>
           </cell>
           <cell r="B234" t="str">
-            <v>サプライカバー+</v>
+            <v>ウルフソウル+</v>
           </cell>
         </row>
         <row r="235">
           <cell r="A235">
-            <v>413070</v>
+            <v>411020</v>
           </cell>
           <cell r="B235" t="str">
-            <v>アシッドラッシュ+</v>
+            <v>プリディカメント+</v>
           </cell>
         </row>
         <row r="236">
           <cell r="A236">
-            <v>413080</v>
+            <v>411030</v>
           </cell>
           <cell r="B236" t="str">
-            <v>ライフスティール+</v>
+            <v>アサルトシフト+</v>
           </cell>
         </row>
         <row r="237">
           <cell r="A237">
-            <v>413090</v>
+            <v>411040</v>
           </cell>
           <cell r="B237" t="str">
-            <v>アイスセイバー+</v>
+            <v>アクティブギフト+</v>
           </cell>
         </row>
         <row r="238">
           <cell r="A238">
-            <v>414010</v>
+            <v>411050</v>
           </cell>
           <cell r="B238" t="str">
-            <v>ディバインシールド+</v>
+            <v>イグナイテッド+</v>
           </cell>
         </row>
         <row r="239">
           <cell r="A239">
-            <v>414020</v>
+            <v>411060</v>
           </cell>
           <cell r="B239" t="str">
-            <v>ライフディバイド+</v>
+            <v>ライジングファイア+</v>
           </cell>
         </row>
         <row r="240">
           <cell r="A240">
-            <v>414030</v>
+            <v>411070</v>
           </cell>
           <cell r="B240" t="str">
-            <v>エイミングスコープ+</v>
+            <v>ルージュバック+</v>
           </cell>
         </row>
         <row r="241">
           <cell r="A241">
-            <v>414040</v>
+            <v>411080</v>
           </cell>
           <cell r="B241" t="str">
-            <v>リジェネレーション+</v>
+            <v>パワーエール+</v>
           </cell>
         </row>
         <row r="242">
           <cell r="A242">
-            <v>414050</v>
+            <v>411090</v>
           </cell>
           <cell r="B242" t="str">
-            <v>ホープフルアイリス+</v>
+            <v>スレイプニル+</v>
           </cell>
         </row>
         <row r="243">
           <cell r="A243">
-            <v>414060</v>
+            <v>412010</v>
           </cell>
           <cell r="B243" t="str">
-            <v>パッシブサプライ+</v>
+            <v>エクステンション+</v>
           </cell>
         </row>
         <row r="244">
           <cell r="A244">
-            <v>414070</v>
+            <v>412020</v>
           </cell>
           <cell r="B244" t="str">
-            <v>ホーミングクルセイド+</v>
+            <v>ヘブンリーラック+</v>
           </cell>
         </row>
         <row r="245">
           <cell r="A245">
-            <v>414080</v>
+            <v>412030</v>
           </cell>
           <cell r="B245" t="str">
-            <v>クイックヒール+</v>
+            <v>スウィフトカレント+</v>
           </cell>
         </row>
         <row r="246">
           <cell r="A246">
-            <v>414090</v>
+            <v>412040</v>
           </cell>
           <cell r="B246" t="str">
-            <v>リレイズ+</v>
+            <v>イヴェイドオール+</v>
           </cell>
         </row>
         <row r="247">
           <cell r="A247">
-            <v>415010</v>
+            <v>412050</v>
           </cell>
           <cell r="B247" t="str">
-            <v>イーグルアイ+</v>
+            <v>クイックムーブ+</v>
           </cell>
         </row>
         <row r="248">
           <cell r="A248">
-            <v>415020</v>
+            <v>412060</v>
           </cell>
           <cell r="B248" t="str">
-            <v>ネヴァーエンド+</v>
+            <v>チェイスマジック+</v>
           </cell>
         </row>
         <row r="249">
           <cell r="A249">
-            <v>415030</v>
+            <v>412070</v>
           </cell>
           <cell r="B249" t="str">
-            <v>グレイブアクト+</v>
+            <v>ソーサリーコネクト+</v>
           </cell>
         </row>
         <row r="250">
           <cell r="A250">
-            <v>415040</v>
+            <v>412080</v>
           </cell>
           <cell r="B250" t="str">
-            <v>スカルグラッジ+</v>
+            <v>ウィンドライズ+</v>
           </cell>
         </row>
         <row r="251">
           <cell r="A251">
-            <v>415050</v>
+            <v>412090</v>
           </cell>
           <cell r="B251" t="str">
-            <v>ネガティブドレイン+</v>
+            <v>アウトオブオーダー+</v>
           </cell>
         </row>
         <row r="252">
           <cell r="A252">
-            <v>415060</v>
+            <v>413010</v>
           </cell>
           <cell r="B252" t="str">
-            <v>アンデッドペイン+</v>
+            <v>アーマーコード+</v>
           </cell>
         </row>
         <row r="253">
           <cell r="A253">
-            <v>415070</v>
+            <v>413020</v>
           </cell>
           <cell r="B253" t="str">
-            <v>ジャックポッド+</v>
+            <v>クイックバリア+</v>
           </cell>
         </row>
         <row r="254">
           <cell r="A254">
-            <v>415080</v>
+            <v>413030</v>
           </cell>
           <cell r="B254" t="str">
-            <v>ヒールハント+</v>
+            <v>クイックキュア+</v>
           </cell>
         </row>
         <row r="255">
           <cell r="A255">
+            <v>413040</v>
+          </cell>
+          <cell r="B255" t="str">
+            <v>セルフシールド+</v>
+          </cell>
+        </row>
+        <row r="256">
+          <cell r="A256">
+            <v>413050</v>
+          </cell>
+          <cell r="B256" t="str">
+            <v>パッシブジャミング+</v>
+          </cell>
+        </row>
+        <row r="257">
+          <cell r="A257">
+            <v>413060</v>
+          </cell>
+          <cell r="B257" t="str">
+            <v>サプライカバー+</v>
+          </cell>
+        </row>
+        <row r="258">
+          <cell r="A258">
+            <v>413070</v>
+          </cell>
+          <cell r="B258" t="str">
+            <v>アシッドラッシュ+</v>
+          </cell>
+        </row>
+        <row r="259">
+          <cell r="A259">
+            <v>413080</v>
+          </cell>
+          <cell r="B259" t="str">
+            <v>ライフスティール+</v>
+          </cell>
+        </row>
+        <row r="260">
+          <cell r="A260">
+            <v>413090</v>
+          </cell>
+          <cell r="B260" t="str">
+            <v>アイスセイバー+</v>
+          </cell>
+        </row>
+        <row r="261">
+          <cell r="A261">
+            <v>414010</v>
+          </cell>
+          <cell r="B261" t="str">
+            <v>ディバインシールド+</v>
+          </cell>
+        </row>
+        <row r="262">
+          <cell r="A262">
+            <v>414020</v>
+          </cell>
+          <cell r="B262" t="str">
+            <v>ライフディバイド+</v>
+          </cell>
+        </row>
+        <row r="263">
+          <cell r="A263">
+            <v>414030</v>
+          </cell>
+          <cell r="B263" t="str">
+            <v>エイミングスコープ+</v>
+          </cell>
+        </row>
+        <row r="264">
+          <cell r="A264">
+            <v>414040</v>
+          </cell>
+          <cell r="B264" t="str">
+            <v>リジェネレーション+</v>
+          </cell>
+        </row>
+        <row r="265">
+          <cell r="A265">
+            <v>414050</v>
+          </cell>
+          <cell r="B265" t="str">
+            <v>ホープフルアイリス+</v>
+          </cell>
+        </row>
+        <row r="266">
+          <cell r="A266">
+            <v>414060</v>
+          </cell>
+          <cell r="B266" t="str">
+            <v>パッシブサプライ+</v>
+          </cell>
+        </row>
+        <row r="267">
+          <cell r="A267">
+            <v>414070</v>
+          </cell>
+          <cell r="B267" t="str">
+            <v>ホーミングクルセイド+</v>
+          </cell>
+        </row>
+        <row r="268">
+          <cell r="A268">
+            <v>414080</v>
+          </cell>
+          <cell r="B268" t="str">
+            <v>クイックヒール+</v>
+          </cell>
+        </row>
+        <row r="269">
+          <cell r="A269">
+            <v>414090</v>
+          </cell>
+          <cell r="B269" t="str">
+            <v>リレイズ+</v>
+          </cell>
+        </row>
+        <row r="270">
+          <cell r="A270">
+            <v>415010</v>
+          </cell>
+          <cell r="B270" t="str">
+            <v>イーグルアイ+</v>
+          </cell>
+        </row>
+        <row r="271">
+          <cell r="A271">
+            <v>415020</v>
+          </cell>
+          <cell r="B271" t="str">
+            <v>ネヴァーエンド+</v>
+          </cell>
+        </row>
+        <row r="272">
+          <cell r="A272">
+            <v>415030</v>
+          </cell>
+          <cell r="B272" t="str">
+            <v>グレイブアクト+</v>
+          </cell>
+        </row>
+        <row r="273">
+          <cell r="A273">
+            <v>415040</v>
+          </cell>
+          <cell r="B273" t="str">
+            <v>スカルグラッジ+</v>
+          </cell>
+        </row>
+        <row r="274">
+          <cell r="A274">
+            <v>415050</v>
+          </cell>
+          <cell r="B274" t="str">
+            <v>ネガティブドレイン+</v>
+          </cell>
+        </row>
+        <row r="275">
+          <cell r="A275">
+            <v>415060</v>
+          </cell>
+          <cell r="B275" t="str">
+            <v>アンデッドペイン+</v>
+          </cell>
+        </row>
+        <row r="276">
+          <cell r="A276">
+            <v>415070</v>
+          </cell>
+          <cell r="B276" t="str">
+            <v>ジャックポッド+</v>
+          </cell>
+        </row>
+        <row r="277">
+          <cell r="A277">
+            <v>415080</v>
+          </cell>
+          <cell r="B277" t="str">
+            <v>ヒールハント+</v>
+          </cell>
+        </row>
+        <row r="278">
+          <cell r="A278">
             <v>415090</v>
           </cell>
-          <cell r="B255" t="str">
+          <cell r="B278" t="str">
             <v>クイックカース+</v>
           </cell>
         </row>
@@ -5391,7 +5575,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G206"/>
+  <dimension ref="A1:G208"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="16.7272727272727" customWidth="1"/>
@@ -7246,20 +7430,20 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B78">
-        <v>5010</v>
+        <v>200110</v>
       </c>
       <c r="C78" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B78,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>スリータイムス</v>
       </c>
       <c r="D78">
         <v>1</v>
       </c>
       <c r="E78">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -7270,20 +7454,20 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B79">
-        <v>15050</v>
+        <v>200120</v>
       </c>
       <c r="C79" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B79,[1]TextData!A:A))</f>
-        <v>ネガティブドレイン</v>
+        <v>アングリークライ</v>
       </c>
       <c r="D79">
         <v>1</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -7297,17 +7481,17 @@
         <v>102</v>
       </c>
       <c r="B80">
-        <v>200210</v>
+        <v>5010</v>
       </c>
       <c r="C80" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B80,[1]TextData!A:A))</f>
-        <v>マイトレインフォース</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="D80">
         <v>1</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -7321,17 +7505,17 @@
         <v>102</v>
       </c>
       <c r="B81">
-        <v>200220</v>
+        <v>15050</v>
       </c>
       <c r="C81" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B81,[1]TextData!A:A))</f>
-        <v>カタストロフィ</v>
+        <v>ネガティブドレイン</v>
       </c>
       <c r="D81">
         <v>1</v>
       </c>
       <c r="E81">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -7345,11 +7529,11 @@
         <v>102</v>
       </c>
       <c r="B82">
-        <v>200230</v>
+        <v>200210</v>
       </c>
       <c r="C82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B82,[1]TextData!A:A))</f>
-        <v>悪魔(ベリト)</v>
+        <v>マイトレインフォース</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -7366,20 +7550,20 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B83">
-        <v>4010</v>
+        <v>200220</v>
       </c>
       <c r="C83" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B83,[1]TextData!A:A))</f>
-        <v>セイントレーザー</v>
+        <v>カタストロフィ</v>
       </c>
       <c r="D83">
         <v>1</v>
       </c>
       <c r="E83">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -7390,23 +7574,23 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B84">
-        <v>4030</v>
+        <v>200230</v>
       </c>
       <c r="C84" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B84,[1]TextData!A:A))</f>
-        <v>ヒーリング</v>
+        <v>悪魔(ベリト)</v>
       </c>
       <c r="D84">
         <v>1</v>
       </c>
       <c r="E84">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F84">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -7417,20 +7601,20 @@
         <v>103</v>
       </c>
       <c r="B85">
-        <v>14080</v>
+        <v>4010</v>
       </c>
       <c r="C85" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B85,[1]TextData!A:A))</f>
-        <v>クイックヒール</v>
+        <v>セイントレーザー</v>
       </c>
       <c r="D85">
         <v>1</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F85">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -7441,20 +7625,20 @@
         <v>103</v>
       </c>
       <c r="B86">
-        <v>200310</v>
+        <v>4030</v>
       </c>
       <c r="C86" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B86,[1]TextData!A:A))</f>
-        <v>プルガシオン</v>
+        <v>ヒーリング</v>
       </c>
       <c r="D86">
         <v>1</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -7465,20 +7649,20 @@
         <v>103</v>
       </c>
       <c r="B87">
-        <v>200320</v>
+        <v>14080</v>
       </c>
       <c r="C87" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B87,[1]TextData!A:A))</f>
-        <v>プリエステス</v>
+        <v>クイックヒール</v>
       </c>
       <c r="D87">
         <v>1</v>
       </c>
       <c r="E87">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -7489,11 +7673,11 @@
         <v>103</v>
       </c>
       <c r="B88">
-        <v>200330</v>
+        <v>200310</v>
       </c>
       <c r="C88" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B88,[1]TextData!A:A))</f>
-        <v>悪魔(パイモン)</v>
+        <v>プルガシオン</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -7510,20 +7694,20 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B89">
-        <v>2010</v>
+        <v>200320</v>
       </c>
       <c r="C89" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B89,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>プリエステス</v>
       </c>
       <c r="D89">
         <v>1</v>
       </c>
       <c r="E89">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -7534,14 +7718,14 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B90">
-        <v>200410</v>
+        <v>200330</v>
       </c>
       <c r="C90" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B90,[1]TextData!A:A))</f>
-        <v>コウソクテンショウ</v>
+        <v>悪魔(パイモン)</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -7561,20 +7745,20 @@
         <v>104</v>
       </c>
       <c r="B91">
-        <v>200420</v>
+        <v>2010</v>
       </c>
       <c r="C91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B91,[1]TextData!A:A))</f>
-        <v>アンチバフ</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D91">
         <v>1</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F91">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -7585,11 +7769,11 @@
         <v>104</v>
       </c>
       <c r="B92">
-        <v>200430</v>
+        <v>200410</v>
       </c>
       <c r="C92" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B92,[1]TextData!A:A))</f>
-        <v>悪魔(アンドラス)</v>
+        <v>コウソクテンショウ</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -7606,23 +7790,23 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B93">
-        <v>3010</v>
+        <v>200420</v>
       </c>
       <c r="C93" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B93,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>アンチバフ</v>
       </c>
       <c r="D93">
         <v>1</v>
       </c>
       <c r="E93">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -7630,20 +7814,20 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B94">
-        <v>3070</v>
+        <v>200430</v>
       </c>
       <c r="C94" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B94,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>悪魔(アンドラス)</v>
       </c>
       <c r="D94">
         <v>1</v>
       </c>
       <c r="E94">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -7657,17 +7841,17 @@
         <v>105</v>
       </c>
       <c r="B95">
-        <v>200510</v>
+        <v>3010</v>
       </c>
       <c r="C95" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B95,[1]TextData!A:A))</f>
-        <v>カウントダウン</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D95">
         <v>1</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -7681,17 +7865,17 @@
         <v>105</v>
       </c>
       <c r="B96">
-        <v>200520</v>
+        <v>3070</v>
       </c>
       <c r="C96" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B96,[1]TextData!A:A))</f>
-        <v>グラウンドゼロ</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D96">
         <v>1</v>
       </c>
       <c r="E96">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -7705,11 +7889,11 @@
         <v>105</v>
       </c>
       <c r="B97">
-        <v>200530</v>
+        <v>200510</v>
       </c>
       <c r="C97" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B97,[1]TextData!A:A))</f>
-        <v>悪魔(ビフロンス)</v>
+        <v>カウントダウン</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -7729,17 +7913,17 @@
         <v>105</v>
       </c>
       <c r="B98">
-        <v>403070</v>
+        <v>200520</v>
       </c>
       <c r="C98" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B98,[1]TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>グラウンドゼロ</v>
       </c>
       <c r="D98">
         <v>1</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -7750,20 +7934,20 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="B99">
-        <v>5010</v>
+        <v>200530</v>
       </c>
       <c r="C99" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B99,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>悪魔(ビフロンス)</v>
       </c>
       <c r="D99">
         <v>1</v>
       </c>
       <c r="E99">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F99">
         <v>0</v>
@@ -7774,20 +7958,20 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="B100">
-        <v>5020</v>
+        <v>403070</v>
       </c>
       <c r="C100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B100,[1]TextData!A:A))</f>
-        <v>ユーサネイジア</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="D100">
         <v>1</v>
       </c>
       <c r="E100">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -7801,20 +7985,20 @@
         <v>201</v>
       </c>
       <c r="B101">
-        <v>3070</v>
+        <v>5010</v>
       </c>
       <c r="C101" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B101,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="D101">
         <v>1</v>
       </c>
       <c r="E101">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F101">
-        <v>9110</v>
+        <v>0</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -7825,17 +8009,17 @@
         <v>201</v>
       </c>
       <c r="B102">
-        <v>403070</v>
+        <v>5020</v>
       </c>
       <c r="C102" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B102,[1]TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>ユーサネイジア</v>
       </c>
       <c r="D102">
         <v>1</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -7849,20 +8033,20 @@
         <v>201</v>
       </c>
       <c r="B103">
-        <v>201010</v>
+        <v>3070</v>
       </c>
       <c r="C103" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B103,[1]TextData!A:A))</f>
-        <v>カオスペイン</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D103">
         <v>1</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F103">
-        <v>5080</v>
+        <v>9110</v>
       </c>
       <c r="G103">
         <v>0</v>
@@ -7873,17 +8057,17 @@
         <v>201</v>
       </c>
       <c r="B104">
-        <v>201020</v>
+        <v>403070</v>
       </c>
       <c r="C104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B104,[1]TextData!A:A))</f>
-        <v>フォールンワン</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="D104">
         <v>1</v>
       </c>
       <c r="E104">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -7897,11 +8081,11 @@
         <v>201</v>
       </c>
       <c r="B105">
-        <v>201030</v>
+        <v>201010</v>
       </c>
       <c r="C105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B105,[1]TextData!A:A))</f>
-        <v>アンリマユ</v>
+        <v>カオスペイン</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -7910,7 +8094,7 @@
         <v>0</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>5080</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -7921,17 +8105,17 @@
         <v>201</v>
       </c>
       <c r="B106">
-        <v>405010</v>
+        <v>201020</v>
       </c>
       <c r="C106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B106,[1]TextData!A:A))</f>
-        <v>ダークプリズン+</v>
+        <v>フォールンワン</v>
       </c>
       <c r="D106">
         <v>1</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -7945,11 +8129,11 @@
         <v>201</v>
       </c>
       <c r="B107">
-        <v>405020</v>
+        <v>201030</v>
       </c>
       <c r="C107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B107,[1]TextData!A:A))</f>
-        <v>ユーサネイジア+</v>
+        <v>アンリマユ</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -7969,11 +8153,11 @@
         <v>201</v>
       </c>
       <c r="B108">
-        <v>12010</v>
+        <v>405010</v>
       </c>
       <c r="C108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B108,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>ダークプリズン+</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -7990,23 +8174,23 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="B109">
-        <v>1010</v>
+        <v>405020</v>
       </c>
       <c r="C109" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B109,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>ユーサネイジア+</v>
       </c>
       <c r="D109">
         <v>1</v>
       </c>
       <c r="E109">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F109">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -8014,23 +8198,23 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="B110">
-        <v>1060</v>
+        <v>12010</v>
       </c>
       <c r="C110" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B110,[1]TextData!A:A))</f>
-        <v>イクスティンクション</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D110">
         <v>1</v>
       </c>
       <c r="E110">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F110">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -8041,20 +8225,20 @@
         <v>1001</v>
       </c>
       <c r="B111">
-        <v>100110</v>
+        <v>1010</v>
       </c>
       <c r="C111" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B111,[1]TextData!A:A))</f>
-        <v>ソーイングアームド</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D111">
         <v>1</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F111">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -8065,20 +8249,20 @@
         <v>1001</v>
       </c>
       <c r="B112">
-        <v>100120</v>
+        <v>1060</v>
       </c>
       <c r="C112" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B112,[1]TextData!A:A))</f>
-        <v>エターナルロンド</v>
+        <v>イクスティンクション</v>
       </c>
       <c r="D112">
         <v>1</v>
       </c>
       <c r="E112">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F112">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G112">
         <v>0</v>
@@ -8089,11 +8273,11 @@
         <v>1001</v>
       </c>
       <c r="B113">
-        <v>11060</v>
+        <v>100110</v>
       </c>
       <c r="C113" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B113,[1]TextData!A:A))</f>
-        <v>ライジングファイア</v>
+        <v>ソーイングアームド</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -8113,17 +8297,17 @@
         <v>1001</v>
       </c>
       <c r="B114">
-        <v>14010</v>
+        <v>100120</v>
       </c>
       <c r="C114" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B114,[1]TextData!A:A))</f>
-        <v>ディバインシールド</v>
+        <v>エターナルロンド</v>
       </c>
       <c r="D114">
         <v>1</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -8137,11 +8321,11 @@
         <v>1001</v>
       </c>
       <c r="B115">
-        <v>12010</v>
+        <v>11060</v>
       </c>
       <c r="C115" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B115,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>ライジングファイア</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -8161,11 +8345,11 @@
         <v>1001</v>
       </c>
       <c r="B116">
-        <v>12060</v>
+        <v>14010</v>
       </c>
       <c r="C116" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B116,[1]TextData!A:A))</f>
-        <v>チェイスマジック</v>
+        <v>ディバインシールド</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -8182,23 +8366,23 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B117">
-        <v>2010</v>
+        <v>12010</v>
       </c>
       <c r="C117" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B117,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D117">
         <v>1</v>
       </c>
       <c r="E117">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F117">
-        <v>5060</v>
+        <v>0</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -8206,20 +8390,20 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B118">
-        <v>2070</v>
+        <v>12060</v>
       </c>
       <c r="C118" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B118,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>チェイスマジック</v>
       </c>
       <c r="D118">
         <v>1</v>
       </c>
       <c r="E118">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F118">
         <v>0</v>
@@ -8233,20 +8417,20 @@
         <v>1002</v>
       </c>
       <c r="B119">
-        <v>100210</v>
+        <v>2010</v>
       </c>
       <c r="C119" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B119,[1]TextData!A:A))</f>
-        <v>アブソリュートパリィ</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D119">
         <v>1</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>5060</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -8257,23 +8441,23 @@
         <v>1002</v>
       </c>
       <c r="B120">
-        <v>100220</v>
+        <v>2070</v>
       </c>
       <c r="C120" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B120,[1]TextData!A:A))</f>
-        <v>レヴェリー</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D120">
         <v>1</v>
       </c>
       <c r="E120">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F120">
-        <v>14211</v>
+        <v>0</v>
       </c>
       <c r="G120">
-        <v>5060</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -8281,11 +8465,11 @@
         <v>1002</v>
       </c>
       <c r="B121">
-        <v>402070</v>
+        <v>100210</v>
       </c>
       <c r="C121" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B121,[1]TextData!A:A))</f>
-        <v>コンセントレイト+</v>
+        <v>アブソリュートパリィ</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -8305,23 +8489,23 @@
         <v>1002</v>
       </c>
       <c r="B122">
-        <v>12080</v>
+        <v>100220</v>
       </c>
       <c r="C122" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B122,[1]TextData!A:A))</f>
-        <v>ウィンドライズ</v>
+        <v>レヴェリー</v>
       </c>
       <c r="D122">
         <v>1</v>
       </c>
       <c r="E122">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F122">
-        <v>0</v>
+        <v>14211</v>
       </c>
       <c r="G122">
-        <v>0</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -8329,11 +8513,11 @@
         <v>1002</v>
       </c>
       <c r="B123">
-        <v>12040</v>
+        <v>402070</v>
       </c>
       <c r="C123" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B123,[1]TextData!A:A))</f>
-        <v>イヴェイドオール</v>
+        <v>コンセントレイト+</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -8353,11 +8537,11 @@
         <v>1002</v>
       </c>
       <c r="B124">
-        <v>12050</v>
+        <v>12080</v>
       </c>
       <c r="C124" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B124,[1]TextData!A:A))</f>
-        <v>クイックムーブ</v>
+        <v>ウィンドライズ</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -8377,11 +8561,11 @@
         <v>1002</v>
       </c>
       <c r="B125">
-        <v>12010</v>
+        <v>12040</v>
       </c>
       <c r="C125" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B125,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>イヴェイドオール</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -8398,20 +8582,20 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B126">
-        <v>3010</v>
+        <v>12050</v>
       </c>
       <c r="C126" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B126,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>クイックムーブ</v>
       </c>
       <c r="D126">
         <v>1</v>
       </c>
       <c r="E126">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F126">
         <v>0</v>
@@ -8422,23 +8606,23 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B127">
-        <v>3020</v>
+        <v>12010</v>
       </c>
       <c r="C127" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B127,[1]TextData!A:A))</f>
-        <v>カウンターオーラ</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D127">
         <v>1</v>
       </c>
       <c r="E127">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F127">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G127">
         <v>0</v>
@@ -8449,17 +8633,17 @@
         <v>1003</v>
       </c>
       <c r="B128">
-        <v>100310</v>
+        <v>3010</v>
       </c>
       <c r="C128" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B128,[1]TextData!A:A))</f>
-        <v>セイクリッドバリア</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D128">
         <v>1</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F128">
         <v>0</v>
@@ -8473,20 +8657,20 @@
         <v>1003</v>
       </c>
       <c r="B129">
-        <v>100320</v>
+        <v>3020</v>
       </c>
       <c r="C129" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B129,[1]TextData!A:A))</f>
-        <v>リベンジニードル</v>
+        <v>カウンターオーラ</v>
       </c>
       <c r="D129">
         <v>1</v>
       </c>
       <c r="E129">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F129">
-        <v>14214</v>
+        <v>1023</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -8497,11 +8681,11 @@
         <v>1003</v>
       </c>
       <c r="B130">
-        <v>403020</v>
+        <v>100310</v>
       </c>
       <c r="C130" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B130,[1]TextData!A:A))</f>
-        <v>カウンターオーラ+</v>
+        <v>セイクリッドバリア</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -8521,20 +8705,20 @@
         <v>1003</v>
       </c>
       <c r="B131">
-        <v>403010</v>
+        <v>100320</v>
       </c>
       <c r="C131" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B131,[1]TextData!A:A))</f>
-        <v>アイスブレイド+</v>
+        <v>リベンジニードル</v>
       </c>
       <c r="D131">
         <v>1</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F131">
-        <v>0</v>
+        <v>14214</v>
       </c>
       <c r="G131">
         <v>0</v>
@@ -8545,11 +8729,11 @@
         <v>1003</v>
       </c>
       <c r="B132">
-        <v>13020</v>
+        <v>403020</v>
       </c>
       <c r="C132" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B132,[1]TextData!A:A))</f>
-        <v>クイックバリア</v>
+        <v>カウンターオーラ+</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -8569,11 +8753,11 @@
         <v>1003</v>
       </c>
       <c r="B133">
-        <v>13080</v>
+        <v>403010</v>
       </c>
       <c r="C133" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B133,[1]TextData!A:A))</f>
-        <v>ライフスティール</v>
+        <v>アイスブレイド+</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -8593,11 +8777,11 @@
         <v>1003</v>
       </c>
       <c r="B134">
-        <v>14050</v>
+        <v>13020</v>
       </c>
       <c r="C134" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B134,[1]TextData!A:A))</f>
-        <v>ホープフルアイリス</v>
+        <v>クイックバリア</v>
       </c>
       <c r="D134">
         <v>1</v>
@@ -8614,20 +8798,20 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B135">
-        <v>4010</v>
+        <v>13080</v>
       </c>
       <c r="C135" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B135,[1]TextData!A:A))</f>
-        <v>セイントレーザー</v>
+        <v>ライフスティール</v>
       </c>
       <c r="D135">
         <v>1</v>
       </c>
       <c r="E135">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F135">
         <v>0</v>
@@ -8638,23 +8822,23 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B136">
-        <v>4030</v>
+        <v>14050</v>
       </c>
       <c r="C136" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B136,[1]TextData!A:A))</f>
-        <v>ヒーリング</v>
+        <v>ホープフルアイリス</v>
       </c>
       <c r="D136">
         <v>1</v>
       </c>
       <c r="E136">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F136">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="G136">
         <v>0</v>
@@ -8665,17 +8849,17 @@
         <v>1004</v>
       </c>
       <c r="B137">
-        <v>100410</v>
+        <v>4010</v>
       </c>
       <c r="C137" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B137,[1]TextData!A:A))</f>
-        <v>アバンデンス</v>
+        <v>セイントレーザー</v>
       </c>
       <c r="D137">
         <v>1</v>
       </c>
       <c r="E137">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -8689,20 +8873,20 @@
         <v>1004</v>
       </c>
       <c r="B138">
-        <v>100420</v>
+        <v>4030</v>
       </c>
       <c r="C138" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B138,[1]TextData!A:A))</f>
-        <v>ハーヴェスト</v>
+        <v>ヒーリング</v>
       </c>
       <c r="D138">
         <v>1</v>
       </c>
       <c r="E138">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F138">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="G138">
         <v>0</v>
@@ -8713,11 +8897,11 @@
         <v>1004</v>
       </c>
       <c r="B139">
-        <v>404030</v>
+        <v>100410</v>
       </c>
       <c r="C139" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B139,[1]TextData!A:A))</f>
-        <v>ヒーリング+</v>
+        <v>アバンデンス</v>
       </c>
       <c r="D139">
         <v>1</v>
@@ -8737,17 +8921,17 @@
         <v>1004</v>
       </c>
       <c r="B140">
-        <v>14080</v>
+        <v>100420</v>
       </c>
       <c r="C140" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B140,[1]TextData!A:A))</f>
-        <v>クイックヒール</v>
+        <v>ハーヴェスト</v>
       </c>
       <c r="D140">
         <v>1</v>
       </c>
       <c r="E140">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F140">
         <v>0</v>
@@ -8761,11 +8945,11 @@
         <v>1004</v>
       </c>
       <c r="B141">
-        <v>14010</v>
+        <v>404030</v>
       </c>
       <c r="C141" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B141,[1]TextData!A:A))</f>
-        <v>ディバインシールド</v>
+        <v>ヒーリング+</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -8774,7 +8958,7 @@
         <v>0</v>
       </c>
       <c r="F141">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -8785,11 +8969,11 @@
         <v>1004</v>
       </c>
       <c r="B142">
-        <v>14040</v>
+        <v>14080</v>
       </c>
       <c r="C142" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B142,[1]TextData!A:A))</f>
-        <v>リジェネレーション</v>
+        <v>クイックヒール</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -8809,11 +8993,11 @@
         <v>1004</v>
       </c>
       <c r="B143">
-        <v>14090</v>
+        <v>14010</v>
       </c>
       <c r="C143" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B143,[1]TextData!A:A))</f>
-        <v>リレイズ</v>
+        <v>ディバインシールド</v>
       </c>
       <c r="D143">
         <v>1</v>
@@ -8822,7 +9006,7 @@
         <v>0</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G143">
         <v>0</v>
@@ -8830,20 +9014,20 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B144">
-        <v>5010</v>
+        <v>14040</v>
       </c>
       <c r="C144" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B144,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>リジェネレーション</v>
       </c>
       <c r="D144">
         <v>1</v>
       </c>
       <c r="E144">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F144">
         <v>0</v>
@@ -8854,23 +9038,23 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B145">
-        <v>5070</v>
+        <v>14090</v>
       </c>
       <c r="C145" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B145,[1]TextData!A:A))</f>
-        <v>シェイディークラウド</v>
+        <v>リレイズ</v>
       </c>
       <c r="D145">
         <v>1</v>
       </c>
       <c r="E145">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F145">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G145">
         <v>0</v>
@@ -8881,17 +9065,17 @@
         <v>1005</v>
       </c>
       <c r="B146">
-        <v>100510</v>
+        <v>5010</v>
       </c>
       <c r="C146" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B146,[1]TextData!A:A))</f>
-        <v>カースドブレイク</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="D146">
         <v>1</v>
       </c>
       <c r="E146">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F146">
         <v>0</v>
@@ -8905,20 +9089,20 @@
         <v>1005</v>
       </c>
       <c r="B147">
-        <v>100520</v>
+        <v>5070</v>
       </c>
       <c r="C147" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B147,[1]TextData!A:A))</f>
-        <v>ムーンライトレイ</v>
+        <v>シェイディークラウド</v>
       </c>
       <c r="D147">
         <v>1</v>
       </c>
       <c r="E147">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F147">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G147">
         <v>0</v>
@@ -8929,11 +9113,11 @@
         <v>1005</v>
       </c>
       <c r="B148">
-        <v>15090</v>
+        <v>100510</v>
       </c>
       <c r="C148" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B148,[1]TextData!A:A))</f>
-        <v>クイックカース</v>
+        <v>カースドブレイク</v>
       </c>
       <c r="D148">
         <v>1</v>
@@ -8953,17 +9137,17 @@
         <v>1005</v>
       </c>
       <c r="B149">
-        <v>405070</v>
+        <v>100520</v>
       </c>
       <c r="C149" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B149,[1]TextData!A:A))</f>
-        <v>シェイディークラウド+</v>
+        <v>ムーンライトレイ</v>
       </c>
       <c r="D149">
         <v>1</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F149">
         <v>0</v>
@@ -8977,11 +9161,11 @@
         <v>1005</v>
       </c>
       <c r="B150">
-        <v>15080</v>
+        <v>15090</v>
       </c>
       <c r="C150" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B150,[1]TextData!A:A))</f>
-        <v>ヒールハント</v>
+        <v>クイックカース</v>
       </c>
       <c r="D150">
         <v>1</v>
@@ -9001,11 +9185,11 @@
         <v>1005</v>
       </c>
       <c r="B151">
-        <v>405010</v>
+        <v>405070</v>
       </c>
       <c r="C151" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B151,[1]TextData!A:A))</f>
-        <v>ダークプリズン+</v>
+        <v>シェイディークラウド+</v>
       </c>
       <c r="D151">
         <v>1</v>
@@ -9025,11 +9209,11 @@
         <v>1005</v>
       </c>
       <c r="B152">
-        <v>415090</v>
+        <v>15080</v>
       </c>
       <c r="C152" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B152,[1]TextData!A:A))</f>
-        <v>クイックカース+</v>
+        <v>ヒールハント</v>
       </c>
       <c r="D152">
         <v>1</v>
@@ -9046,20 +9230,20 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B153">
-        <v>1010</v>
+        <v>405010</v>
       </c>
       <c r="C153" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B153,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>ダークプリズン+</v>
       </c>
       <c r="D153">
         <v>1</v>
       </c>
       <c r="E153">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F153">
         <v>0</v>
@@ -9070,26 +9254,26 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B154">
-        <v>1030</v>
+        <v>415090</v>
       </c>
       <c r="C154" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B154,[1]TextData!A:A))</f>
-        <v>ヒートスタンプ</v>
+        <v>クイックカース+</v>
       </c>
       <c r="D154">
         <v>1</v>
       </c>
       <c r="E154">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F154">
-        <v>9120</v>
+        <v>0</v>
       </c>
       <c r="G154">
-        <v>1023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -9097,20 +9281,20 @@
         <v>1006</v>
       </c>
       <c r="B155">
-        <v>1070</v>
+        <v>1010</v>
       </c>
       <c r="C155" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B155,[1]TextData!A:A))</f>
-        <v>バーニングソウル</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D155">
         <v>1</v>
       </c>
       <c r="E155">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F155">
-        <v>6322</v>
+        <v>0</v>
       </c>
       <c r="G155">
         <v>0</v>
@@ -9121,23 +9305,23 @@
         <v>1006</v>
       </c>
       <c r="B156">
-        <v>100610</v>
+        <v>1030</v>
       </c>
       <c r="C156" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B156,[1]TextData!A:A))</f>
-        <v>サンフレイム</v>
+        <v>ヒートスタンプ</v>
       </c>
       <c r="D156">
         <v>1</v>
       </c>
       <c r="E156">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F156">
-        <v>0</v>
+        <v>9120</v>
       </c>
       <c r="G156">
-        <v>0</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -9145,20 +9329,20 @@
         <v>1006</v>
       </c>
       <c r="B157">
-        <v>100620</v>
+        <v>1070</v>
       </c>
       <c r="C157" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B157,[1]TextData!A:A))</f>
-        <v>フレイムタン</v>
+        <v>バーニングソウル</v>
       </c>
       <c r="D157">
         <v>1</v>
       </c>
       <c r="E157">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F157">
-        <v>0</v>
+        <v>6322</v>
       </c>
       <c r="G157">
         <v>0</v>
@@ -9169,11 +9353,11 @@
         <v>1006</v>
       </c>
       <c r="B158">
-        <v>11040</v>
+        <v>100610</v>
       </c>
       <c r="C158" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B158,[1]TextData!A:A))</f>
-        <v>アクティブギフト</v>
+        <v>サンフレイム</v>
       </c>
       <c r="D158">
         <v>1</v>
@@ -9182,7 +9366,7 @@
         <v>0</v>
       </c>
       <c r="F158">
-        <v>5042</v>
+        <v>0</v>
       </c>
       <c r="G158">
         <v>0</v>
@@ -9193,17 +9377,17 @@
         <v>1006</v>
       </c>
       <c r="B159">
-        <v>401030</v>
+        <v>100620</v>
       </c>
       <c r="C159" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B159,[1]TextData!A:A))</f>
-        <v>ヒートスタンプ+</v>
+        <v>フレイムタン</v>
       </c>
       <c r="D159">
         <v>1</v>
       </c>
       <c r="E159">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -9217,11 +9401,11 @@
         <v>1006</v>
       </c>
       <c r="B160">
-        <v>411040</v>
+        <v>11040</v>
       </c>
       <c r="C160" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B160,[1]TextData!A:A))</f>
-        <v>アクティブギフト+</v>
+        <v>アクティブギフト</v>
       </c>
       <c r="D160">
         <v>1</v>
@@ -9230,7 +9414,7 @@
         <v>0</v>
       </c>
       <c r="F160">
-        <v>0</v>
+        <v>5042</v>
       </c>
       <c r="G160">
         <v>0</v>
@@ -9241,11 +9425,11 @@
         <v>1006</v>
       </c>
       <c r="B161">
-        <v>13040</v>
+        <v>401030</v>
       </c>
       <c r="C161" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B161,[1]TextData!A:A))</f>
-        <v>セルフシールド</v>
+        <v>ヒートスタンプ+</v>
       </c>
       <c r="D161">
         <v>1</v>
@@ -9262,20 +9446,20 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B162">
-        <v>2010</v>
+        <v>411040</v>
       </c>
       <c r="C162" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B162,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>アクティブギフト+</v>
       </c>
       <c r="D162">
         <v>1</v>
       </c>
       <c r="E162">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F162">
         <v>0</v>
@@ -9286,23 +9470,23 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B163">
-        <v>2040</v>
+        <v>13040</v>
       </c>
       <c r="C163" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B163,[1]TextData!A:A))</f>
-        <v>トラストチェイン</v>
+        <v>セルフシールド</v>
       </c>
       <c r="D163">
         <v>1</v>
       </c>
       <c r="E163">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F163">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G163">
         <v>0</v>
@@ -9313,17 +9497,17 @@
         <v>1007</v>
       </c>
       <c r="B164">
-        <v>100710</v>
+        <v>2010</v>
       </c>
       <c r="C164" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B164,[1]TextData!A:A))</f>
-        <v>ライズザフラッグ</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D164">
         <v>1</v>
       </c>
       <c r="E164">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F164">
         <v>0</v>
@@ -9337,20 +9521,20 @@
         <v>1007</v>
       </c>
       <c r="B165">
-        <v>100720</v>
+        <v>2040</v>
       </c>
       <c r="C165" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B165,[1]TextData!A:A))</f>
-        <v>オーバーリミット</v>
+        <v>トラストチェイン</v>
       </c>
       <c r="D165">
         <v>1</v>
       </c>
       <c r="E165">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F165">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G165">
         <v>0</v>
@@ -9361,11 +9545,11 @@
         <v>1007</v>
       </c>
       <c r="B166">
-        <v>12090</v>
+        <v>100710</v>
       </c>
       <c r="C166" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B166,[1]TextData!A:A))</f>
-        <v>アウトオブオーダー</v>
+        <v>ライズザフラッグ</v>
       </c>
       <c r="D166">
         <v>1</v>
@@ -9374,7 +9558,7 @@
         <v>0</v>
       </c>
       <c r="F166">
-        <v>5042</v>
+        <v>0</v>
       </c>
       <c r="G166">
         <v>0</v>
@@ -9385,17 +9569,17 @@
         <v>1007</v>
       </c>
       <c r="B167">
-        <v>412090</v>
+        <v>100720</v>
       </c>
       <c r="C167" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B167,[1]TextData!A:A))</f>
-        <v>アウトオブオーダー+</v>
+        <v>オーバーリミット</v>
       </c>
       <c r="D167">
         <v>1</v>
       </c>
       <c r="E167">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F167">
         <v>0</v>
@@ -9409,11 +9593,11 @@
         <v>1007</v>
       </c>
       <c r="B168">
-        <v>12050</v>
+        <v>12090</v>
       </c>
       <c r="C168" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B168,[1]TextData!A:A))</f>
-        <v>クイックムーブ</v>
+        <v>アウトオブオーダー</v>
       </c>
       <c r="D168">
         <v>1</v>
@@ -9422,7 +9606,7 @@
         <v>0</v>
       </c>
       <c r="F168">
-        <v>0</v>
+        <v>5042</v>
       </c>
       <c r="G168">
         <v>0</v>
@@ -9433,11 +9617,11 @@
         <v>1007</v>
       </c>
       <c r="B169">
-        <v>12070</v>
+        <v>412090</v>
       </c>
       <c r="C169" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B169,[1]TextData!A:A))</f>
-        <v>ソーサリーコネクト</v>
+        <v>アウトオブオーダー+</v>
       </c>
       <c r="D169">
         <v>1</v>
@@ -9457,11 +9641,11 @@
         <v>1007</v>
       </c>
       <c r="B170">
-        <v>14030</v>
+        <v>12050</v>
       </c>
       <c r="C170" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B170,[1]TextData!A:A))</f>
-        <v>エイミングスコープ</v>
+        <v>クイックムーブ</v>
       </c>
       <c r="D170">
         <v>1</v>
@@ -9478,20 +9662,20 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B171">
-        <v>3010</v>
+        <v>12070</v>
       </c>
       <c r="C171" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B171,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>ソーサリーコネクト</v>
       </c>
       <c r="D171">
         <v>1</v>
       </c>
       <c r="E171">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F171">
         <v>0</v>
@@ -9502,20 +9686,20 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B172">
-        <v>3070</v>
+        <v>14030</v>
       </c>
       <c r="C172" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B172,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>エイミングスコープ</v>
       </c>
       <c r="D172">
         <v>1</v>
       </c>
       <c r="E172">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F172">
         <v>0</v>
@@ -9529,17 +9713,17 @@
         <v>1008</v>
       </c>
       <c r="B173">
-        <v>100810</v>
+        <v>3010</v>
       </c>
       <c r="C173" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B173,[1]TextData!A:A))</f>
-        <v>テンパランス</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D173">
         <v>1</v>
       </c>
       <c r="E173">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F173">
         <v>0</v>
@@ -9553,17 +9737,17 @@
         <v>1008</v>
       </c>
       <c r="B174">
-        <v>100820</v>
+        <v>3070</v>
       </c>
       <c r="C174" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B174,[1]TextData!A:A))</f>
-        <v>シエルクルセイダー</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D174">
         <v>1</v>
       </c>
       <c r="E174">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F174">
         <v>0</v>
@@ -9577,11 +9761,11 @@
         <v>1008</v>
       </c>
       <c r="B175">
-        <v>13060</v>
+        <v>100810</v>
       </c>
       <c r="C175" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B175,[1]TextData!A:A))</f>
-        <v>サプライカバー</v>
+        <v>テンパランス</v>
       </c>
       <c r="D175">
         <v>1</v>
@@ -9590,7 +9774,7 @@
         <v>0</v>
       </c>
       <c r="F175">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G175">
         <v>0</v>
@@ -9601,17 +9785,17 @@
         <v>1008</v>
       </c>
       <c r="B176">
-        <v>403070</v>
+        <v>100820</v>
       </c>
       <c r="C176" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B176,[1]TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>シエルクルセイダー</v>
       </c>
       <c r="D176">
         <v>1</v>
       </c>
       <c r="E176">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F176">
         <v>0</v>
@@ -9625,11 +9809,11 @@
         <v>1008</v>
       </c>
       <c r="B177">
-        <v>13010</v>
+        <v>13060</v>
       </c>
       <c r="C177" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B177,[1]TextData!A:A))</f>
-        <v>アーマーコード</v>
+        <v>サプライカバー</v>
       </c>
       <c r="D177">
         <v>1</v>
@@ -9638,7 +9822,7 @@
         <v>0</v>
       </c>
       <c r="F177">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G177">
         <v>0</v>
@@ -9649,11 +9833,11 @@
         <v>1008</v>
       </c>
       <c r="B178">
-        <v>13020</v>
+        <v>403070</v>
       </c>
       <c r="C178" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B178,[1]TextData!A:A))</f>
-        <v>クイックバリア</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="D178">
         <v>1</v>
@@ -9673,11 +9857,11 @@
         <v>1008</v>
       </c>
       <c r="B179">
-        <v>13040</v>
+        <v>13010</v>
       </c>
       <c r="C179" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B179,[1]TextData!A:A))</f>
-        <v>セルフシールド</v>
+        <v>アーマーコード</v>
       </c>
       <c r="D179">
         <v>1</v>
@@ -9694,20 +9878,20 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B180">
-        <v>1010</v>
+        <v>13020</v>
       </c>
       <c r="C180" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B180,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>クイックバリア</v>
       </c>
       <c r="D180">
         <v>1</v>
       </c>
       <c r="E180">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F180">
         <v>0</v>
@@ -9718,23 +9902,23 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B181">
-        <v>1050</v>
+        <v>13040</v>
       </c>
       <c r="C181" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B181,[1]TextData!A:A))</f>
-        <v>フレイムレイン</v>
+        <v>セルフシールド</v>
       </c>
       <c r="D181">
         <v>1</v>
       </c>
       <c r="E181">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F181">
-        <v>1151</v>
+        <v>0</v>
       </c>
       <c r="G181">
         <v>0</v>
@@ -9745,17 +9929,17 @@
         <v>1009</v>
       </c>
       <c r="B182">
-        <v>100910</v>
+        <v>1010</v>
       </c>
       <c r="C182" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B182,[1]TextData!A:A))</f>
-        <v>バーニングカウンター</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D182">
         <v>1</v>
       </c>
       <c r="E182">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F182">
         <v>0</v>
@@ -9769,20 +9953,20 @@
         <v>1009</v>
       </c>
       <c r="B183">
-        <v>100920</v>
+        <v>1050</v>
       </c>
       <c r="C183" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B183,[1]TextData!A:A))</f>
-        <v>プロミネンス</v>
+        <v>フレイムレイン</v>
       </c>
       <c r="D183">
         <v>1</v>
       </c>
       <c r="E183">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F183">
-        <v>0</v>
+        <v>1151</v>
       </c>
       <c r="G183">
         <v>0</v>
@@ -9793,11 +9977,11 @@
         <v>1009</v>
       </c>
       <c r="B184">
-        <v>11070</v>
+        <v>100910</v>
       </c>
       <c r="C184" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B184,[1]TextData!A:A))</f>
-        <v>ルージュバック</v>
+        <v>バーニングカウンター</v>
       </c>
       <c r="D184">
         <v>1</v>
@@ -9817,17 +10001,17 @@
         <v>1009</v>
       </c>
       <c r="B185">
-        <v>401050</v>
+        <v>100920</v>
       </c>
       <c r="C185" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B185,[1]TextData!A:A))</f>
-        <v>フレイムレイン+</v>
+        <v>プロミネンス</v>
       </c>
       <c r="D185">
         <v>1</v>
       </c>
       <c r="E185">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F185">
         <v>0</v>
@@ -9841,11 +10025,11 @@
         <v>1009</v>
       </c>
       <c r="B186">
-        <v>11030</v>
+        <v>11070</v>
       </c>
       <c r="C186" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B186,[1]TextData!A:A))</f>
-        <v>アサルトシフト</v>
+        <v>ルージュバック</v>
       </c>
       <c r="D186">
         <v>1</v>
@@ -9865,11 +10049,11 @@
         <v>1009</v>
       </c>
       <c r="B187">
-        <v>11020</v>
+        <v>401050</v>
       </c>
       <c r="C187" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B187,[1]TextData!A:A))</f>
-        <v>プリディカメント</v>
+        <v>フレイムレイン+</v>
       </c>
       <c r="D187">
         <v>1</v>
@@ -9889,11 +10073,11 @@
         <v>1009</v>
       </c>
       <c r="B188">
-        <v>15040</v>
+        <v>11030</v>
       </c>
       <c r="C188" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B188,[1]TextData!A:A))</f>
-        <v>スカルグラッジ</v>
+        <v>アサルトシフト</v>
       </c>
       <c r="D188">
         <v>1</v>
@@ -9910,20 +10094,20 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B189">
-        <v>2010</v>
+        <v>11020</v>
       </c>
       <c r="C189" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B189,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>プリディカメント</v>
       </c>
       <c r="D189">
         <v>1</v>
       </c>
       <c r="E189">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F189">
         <v>0</v>
@@ -9934,23 +10118,23 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B190">
-        <v>2030</v>
+        <v>15040</v>
       </c>
       <c r="C190" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B190,[1]TextData!A:A))</f>
-        <v>ショックインパルス</v>
+        <v>スカルグラッジ</v>
       </c>
       <c r="D190">
         <v>1</v>
       </c>
       <c r="E190">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F190">
-        <v>14215</v>
+        <v>0</v>
       </c>
       <c r="G190">
         <v>0</v>
@@ -9961,17 +10145,17 @@
         <v>1010</v>
       </c>
       <c r="B191">
-        <v>101010</v>
+        <v>2010</v>
       </c>
       <c r="C191" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B191,[1]TextData!A:A))</f>
-        <v>エウロス</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D191">
         <v>1</v>
       </c>
       <c r="E191">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F191">
         <v>0</v>
@@ -9985,20 +10169,20 @@
         <v>1010</v>
       </c>
       <c r="B192">
-        <v>101020</v>
+        <v>2030</v>
       </c>
       <c r="C192" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B192,[1]TextData!A:A))</f>
-        <v>ボレアス</v>
+        <v>ショックインパルス</v>
       </c>
       <c r="D192">
         <v>1</v>
       </c>
       <c r="E192">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F192">
-        <v>0</v>
+        <v>14215</v>
       </c>
       <c r="G192">
         <v>0</v>
@@ -10009,11 +10193,11 @@
         <v>1010</v>
       </c>
       <c r="B193">
-        <v>12010</v>
+        <v>101010</v>
       </c>
       <c r="C193" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B193,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>エウロス</v>
       </c>
       <c r="D193">
         <v>1</v>
@@ -10033,17 +10217,17 @@
         <v>1010</v>
       </c>
       <c r="B194">
-        <v>402030</v>
+        <v>101020</v>
       </c>
       <c r="C194" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B194,[1]TextData!A:A))</f>
-        <v>ショックインパルス+</v>
+        <v>ボレアス</v>
       </c>
       <c r="D194">
         <v>1</v>
       </c>
       <c r="E194">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F194">
         <v>0</v>
@@ -10057,11 +10241,11 @@
         <v>1010</v>
       </c>
       <c r="B195">
-        <v>12020</v>
+        <v>12010</v>
       </c>
       <c r="C195" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B195,[1]TextData!A:A))</f>
-        <v>ヘブンリーラック</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D195">
         <v>1</v>
@@ -10081,11 +10265,11 @@
         <v>1010</v>
       </c>
       <c r="B196">
-        <v>12030</v>
+        <v>402030</v>
       </c>
       <c r="C196" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B196,[1]TextData!A:A))</f>
-        <v>スウィフトカレント</v>
+        <v>ショックインパルス+</v>
       </c>
       <c r="D196">
         <v>1</v>
@@ -10105,11 +10289,11 @@
         <v>1010</v>
       </c>
       <c r="B197">
-        <v>15070</v>
+        <v>12020</v>
       </c>
       <c r="C197" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B197,[1]TextData!A:A))</f>
-        <v>ジャックポッド</v>
+        <v>ヘブンリーラック</v>
       </c>
       <c r="D197">
         <v>1</v>
@@ -10126,20 +10310,20 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B198">
-        <v>3010</v>
+        <v>12030</v>
       </c>
       <c r="C198" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B198,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>スウィフトカレント</v>
       </c>
       <c r="D198">
         <v>1</v>
       </c>
       <c r="E198">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F198">
         <v>0</v>
@@ -10150,20 +10334,20 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B199">
-        <v>3050</v>
+        <v>15070</v>
       </c>
       <c r="C199" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B199,[1]TextData!A:A))</f>
-        <v>ディープフリーズ</v>
+        <v>ジャックポッド</v>
       </c>
       <c r="D199">
         <v>1</v>
       </c>
       <c r="E199">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F199">
         <v>0</v>
@@ -10177,17 +10361,17 @@
         <v>1011</v>
       </c>
       <c r="B200">
-        <v>101110</v>
+        <v>3010</v>
       </c>
       <c r="C200" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B200,[1]TextData!A:A))</f>
-        <v>アバランシュ</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D200">
         <v>1</v>
       </c>
       <c r="E200">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F200">
         <v>0</v>
@@ -10201,17 +10385,17 @@
         <v>1011</v>
       </c>
       <c r="B201">
-        <v>101120</v>
+        <v>3050</v>
       </c>
       <c r="C201" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B201,[1]TextData!A:A))</f>
-        <v>ブリザードコフィン</v>
+        <v>ディープフリーズ</v>
       </c>
       <c r="D201">
         <v>1</v>
       </c>
       <c r="E201">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F201">
         <v>0</v>
@@ -10225,11 +10409,11 @@
         <v>1011</v>
       </c>
       <c r="B202">
-        <v>13090</v>
+        <v>101110</v>
       </c>
       <c r="C202" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B202,[1]TextData!A:A))</f>
-        <v>アイスセイバー</v>
+        <v>アバランシュ</v>
       </c>
       <c r="D202">
         <v>1</v>
@@ -10249,17 +10433,17 @@
         <v>1011</v>
       </c>
       <c r="B203">
-        <v>403050</v>
+        <v>101120</v>
       </c>
       <c r="C203" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B203,[1]TextData!A:A))</f>
-        <v>ディープフリーズ+</v>
+        <v>ブリザードコフィン</v>
       </c>
       <c r="D203">
         <v>1</v>
       </c>
       <c r="E203">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F203">
         <v>0</v>
@@ -10273,11 +10457,11 @@
         <v>1011</v>
       </c>
       <c r="B204">
-        <v>13050</v>
+        <v>13090</v>
       </c>
       <c r="C204" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B204,[1]TextData!A:A))</f>
-        <v>パッシブジャミング</v>
+        <v>アイスセイバー</v>
       </c>
       <c r="D204">
         <v>1</v>
@@ -10297,11 +10481,11 @@
         <v>1011</v>
       </c>
       <c r="B205">
-        <v>13070</v>
+        <v>403050</v>
       </c>
       <c r="C205" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B205,[1]TextData!A:A))</f>
-        <v>アシッドラッシュ</v>
+        <v>ディープフリーズ+</v>
       </c>
       <c r="D205">
         <v>1</v>
@@ -10321,22 +10505,70 @@
         <v>1011</v>
       </c>
       <c r="B206">
-        <v>14070</v>
+        <v>13050</v>
       </c>
       <c r="C206" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B206,[1]TextData!A:A))</f>
+        <v>パッシブジャミング</v>
+      </c>
+      <c r="D206">
+        <v>1</v>
+      </c>
+      <c r="E206">
+        <v>0</v>
+      </c>
+      <c r="F206">
+        <v>0</v>
+      </c>
+      <c r="G206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7">
+      <c r="A207">
+        <v>1011</v>
+      </c>
+      <c r="B207">
+        <v>13070</v>
+      </c>
+      <c r="C207" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B207,[1]TextData!A:A))</f>
+        <v>アシッドラッシュ</v>
+      </c>
+      <c r="D207">
+        <v>1</v>
+      </c>
+      <c r="E207">
+        <v>0</v>
+      </c>
+      <c r="F207">
+        <v>0</v>
+      </c>
+      <c r="G207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7">
+      <c r="A208">
+        <v>1011</v>
+      </c>
+      <c r="B208">
+        <v>14070</v>
+      </c>
+      <c r="C208" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B208,[1]TextData!A:A))</f>
         <v>ホーミングクルセイド</v>
       </c>
-      <c r="D206">
-        <v>1</v>
-      </c>
-      <c r="E206">
-        <v>0</v>
-      </c>
-      <c r="F206">
-        <v>0</v>
-      </c>
-      <c r="G206">
+      <c r="D208">
+        <v>1</v>
+      </c>
+      <c r="E208">
+        <v>0</v>
+      </c>
+      <c r="F208">
+        <v>0</v>
+      </c>
+      <c r="G208">
         <v>0</v>
       </c>
     </row>
@@ -10349,7 +10581,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -10538,19 +10770,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B9">
-        <v>1040</v>
+        <v>2050</v>
       </c>
       <c r="C9">
-        <v>4020</v>
+        <v>1020</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -10561,25 +10793,25 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B10">
-        <v>2050</v>
+        <v>1040</v>
       </c>
       <c r="C10">
-        <v>1020</v>
+        <v>4020</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -10590,64 +10822,41 @@
         <v>1040</v>
       </c>
       <c r="C11">
-        <v>4020</v>
+        <v>1020</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B12">
-        <v>1040</v>
+        <v>4050</v>
       </c>
       <c r="C12">
-        <v>1020</v>
+        <v>4020</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>105</v>
-      </c>
-      <c r="B13">
-        <v>4050</v>
-      </c>
-      <c r="C13">
-        <v>4020</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7820"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -394,10 +394,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -415,17 +415,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -440,14 +446,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -460,8 +466,54 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -475,14 +527,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -491,52 +535,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -568,7 +568,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,31 +640,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -616,43 +682,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -670,85 +742,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -762,11 +762,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -786,17 +801,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -816,26 +840,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -844,18 +855,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -867,145 +867,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3736,7 +3736,7 @@
         <v>60</v>
       </c>
       <c r="R2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="S2" t="s">
         <v>19</v>
@@ -3795,7 +3795,7 @@
         <v>30</v>
       </c>
       <c r="R3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="S3" t="s">
         <v>21</v>
@@ -3854,7 +3854,7 @@
         <v>20</v>
       </c>
       <c r="R4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="S4" t="s">
         <v>23</v>
@@ -3913,7 +3913,7 @@
         <v>30</v>
       </c>
       <c r="R5">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="S5" t="s">
         <v>25</v>
@@ -3972,7 +3972,7 @@
         <v>20</v>
       </c>
       <c r="R6">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="S6" t="s">
         <v>23</v>
@@ -4031,7 +4031,7 @@
         <v>40</v>
       </c>
       <c r="R7">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="S7" t="s">
         <v>23</v>
@@ -4090,7 +4090,7 @@
         <v>40</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="S8" t="s">
         <v>19</v>
@@ -4149,7 +4149,7 @@
         <v>70</v>
       </c>
       <c r="R9">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="S9" t="s">
         <v>19</v>
@@ -4208,7 +4208,7 @@
         <v>40</v>
       </c>
       <c r="R10">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="S10" t="s">
         <v>25</v>
@@ -4267,7 +4267,7 @@
         <v>40</v>
       </c>
       <c r="R11">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="S11" t="s">
         <v>23</v>
@@ -4326,7 +4326,7 @@
         <v>50</v>
       </c>
       <c r="R12">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="S12" t="s">
         <v>19</v>
@@ -4385,7 +4385,7 @@
         <v>40</v>
       </c>
       <c r="R13">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="S13" t="s">
         <v>21</v>
@@ -4444,7 +4444,7 @@
         <v>60</v>
       </c>
       <c r="R14">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="S14" t="s">
         <v>35</v>
@@ -4503,7 +4503,7 @@
         <v>70</v>
       </c>
       <c r="R15">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="S15" t="s">
         <v>25</v>
@@ -4562,7 +4562,7 @@
         <v>20</v>
       </c>
       <c r="R16">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="S16" t="s">
         <v>25</v>
@@ -4621,7 +4621,7 @@
         <v>40</v>
       </c>
       <c r="R17">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="S17" t="s">
         <v>25</v>
@@ -4680,7 +4680,7 @@
         <v>35</v>
       </c>
       <c r="R18">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="S18" t="s">
         <v>21</v>
@@ -4739,7 +4739,7 @@
         <v>30</v>
       </c>
       <c r="R19">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="S19" t="s">
         <v>35</v>
@@ -4798,7 +4798,7 @@
         <v>25</v>
       </c>
       <c r="R20">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="S20" t="s">
         <v>23</v>
@@ -4857,7 +4857,7 @@
         <v>60</v>
       </c>
       <c r="R21">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="S21" t="s">
         <v>19</v>
@@ -4916,7 +4916,7 @@
         <v>60</v>
       </c>
       <c r="R22">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -4972,7 +4972,7 @@
         <v>30</v>
       </c>
       <c r="R23">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:20">
@@ -5028,7 +5028,7 @@
         <v>25</v>
       </c>
       <c r="R24">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="T24" t="s">
         <v>46</v>
@@ -5087,7 +5087,7 @@
         <v>40</v>
       </c>
       <c r="R25">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T25" t="s">
         <v>48</v>
@@ -5146,7 +5146,7 @@
         <v>15</v>
       </c>
       <c r="R26">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T26" t="s">
         <v>50</v>
@@ -5205,7 +5205,7 @@
         <v>40</v>
       </c>
       <c r="R27">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="T27" t="s">
         <v>52</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -394,8 +394,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -416,22 +416,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -445,15 +438,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -466,24 +460,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -498,6 +485,37 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -505,7 +523,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -519,41 +552,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -580,7 +580,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -592,7 +622,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -604,115 +718,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -724,31 +742,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -777,15 +777,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -804,23 +795,28 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -842,20 +838,24 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -867,7 +867,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -876,7 +876,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -885,127 +885,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1619,1705 +1619,1761 @@
         </row>
         <row r="66">
           <cell r="A66">
-            <v>12010</v>
+            <v>11100</v>
           </cell>
           <cell r="B66" t="str">
-            <v>コンセントレイト</v>
+            <v>レストア</v>
           </cell>
         </row>
         <row r="67">
           <cell r="A67">
-            <v>12020</v>
+            <v>12010</v>
           </cell>
           <cell r="B67" t="str">
-            <v>ヘブンリーラック</v>
+            <v>コンセントレイト</v>
           </cell>
         </row>
         <row r="68">
           <cell r="A68">
-            <v>12030</v>
+            <v>12020</v>
           </cell>
           <cell r="B68" t="str">
-            <v>スウィフトカレント</v>
+            <v>ヘブンリーラック</v>
           </cell>
         </row>
         <row r="69">
           <cell r="A69">
-            <v>12040</v>
+            <v>12030</v>
           </cell>
           <cell r="B69" t="str">
-            <v>イヴェイドオール</v>
+            <v>スウィフトカレント</v>
           </cell>
         </row>
         <row r="70">
           <cell r="A70">
-            <v>12050</v>
+            <v>12040</v>
           </cell>
           <cell r="B70" t="str">
-            <v>クイックムーブ</v>
+            <v>イヴェイドオール</v>
           </cell>
         </row>
         <row r="71">
           <cell r="A71">
-            <v>12060</v>
+            <v>12050</v>
           </cell>
           <cell r="B71" t="str">
-            <v>チェイスマジック</v>
+            <v>クイックムーブ</v>
           </cell>
         </row>
         <row r="72">
           <cell r="A72">
-            <v>12070</v>
+            <v>12060</v>
           </cell>
           <cell r="B72" t="str">
-            <v>ソーサリーコネクト</v>
+            <v>チェイスマジック</v>
           </cell>
         </row>
         <row r="73">
           <cell r="A73">
-            <v>12080</v>
+            <v>12070</v>
           </cell>
           <cell r="B73" t="str">
-            <v>ウィンドライズ</v>
+            <v>ソーサリーコネクト</v>
           </cell>
         </row>
         <row r="74">
           <cell r="A74">
-            <v>12090</v>
+            <v>12080</v>
           </cell>
           <cell r="B74" t="str">
-            <v>アウトオブオーダー</v>
+            <v>ウィンドライズ</v>
           </cell>
         </row>
         <row r="75">
           <cell r="A75">
-            <v>13010</v>
+            <v>12090</v>
           </cell>
           <cell r="B75" t="str">
-            <v>アーマーコード</v>
+            <v>アウトオブオーダー</v>
           </cell>
         </row>
         <row r="76">
           <cell r="A76">
-            <v>13020</v>
+            <v>12100</v>
           </cell>
           <cell r="B76" t="str">
-            <v>クイックバリア</v>
+            <v>ワンスパニッシュ</v>
           </cell>
         </row>
         <row r="77">
           <cell r="A77">
-            <v>13030</v>
+            <v>13010</v>
           </cell>
           <cell r="B77" t="str">
-            <v>クイックキュア</v>
+            <v>アーマーコード</v>
           </cell>
         </row>
         <row r="78">
           <cell r="A78">
-            <v>13040</v>
+            <v>13020</v>
           </cell>
           <cell r="B78" t="str">
-            <v>セルフシールド</v>
+            <v>クイックバリア</v>
           </cell>
         </row>
         <row r="79">
           <cell r="A79">
-            <v>13050</v>
+            <v>13030</v>
           </cell>
           <cell r="B79" t="str">
-            <v>パッシブジャミング</v>
+            <v>クイックキュア</v>
           </cell>
         </row>
         <row r="80">
           <cell r="A80">
-            <v>13060</v>
+            <v>13040</v>
           </cell>
           <cell r="B80" t="str">
-            <v>サプライカバー</v>
+            <v>セルフシールド</v>
           </cell>
         </row>
         <row r="81">
           <cell r="A81">
-            <v>13070</v>
+            <v>13050</v>
           </cell>
           <cell r="B81" t="str">
-            <v>アシッドラッシュ</v>
+            <v>パッシブジャミング</v>
           </cell>
         </row>
         <row r="82">
           <cell r="A82">
-            <v>13080</v>
+            <v>13060</v>
           </cell>
           <cell r="B82" t="str">
-            <v>ライフスティール</v>
+            <v>サプライカバー</v>
           </cell>
         </row>
         <row r="83">
           <cell r="A83">
-            <v>13090</v>
+            <v>13070</v>
           </cell>
           <cell r="B83" t="str">
-            <v>アイスセイバー</v>
+            <v>アシッドラッシュ</v>
           </cell>
         </row>
         <row r="84">
           <cell r="A84">
-            <v>14010</v>
+            <v>13080</v>
           </cell>
           <cell r="B84" t="str">
-            <v>ディバインシールド</v>
+            <v>ライフスティール</v>
           </cell>
         </row>
         <row r="85">
           <cell r="A85">
-            <v>14020</v>
+            <v>13090</v>
           </cell>
           <cell r="B85" t="str">
-            <v>ライフディバイド</v>
+            <v>アイスセイバー</v>
           </cell>
         </row>
         <row r="86">
           <cell r="A86">
-            <v>14030</v>
+            <v>13100</v>
           </cell>
           <cell r="B86" t="str">
-            <v>エイミングスコープ</v>
+            <v>ルミナスカバー</v>
           </cell>
         </row>
         <row r="87">
           <cell r="A87">
-            <v>14040</v>
+            <v>14010</v>
           </cell>
           <cell r="B87" t="str">
-            <v>リジェネレーション</v>
+            <v>ディバインシールド</v>
           </cell>
         </row>
         <row r="88">
           <cell r="A88">
-            <v>14050</v>
+            <v>14020</v>
           </cell>
           <cell r="B88" t="str">
-            <v>ホープフルアイリス</v>
+            <v>ライフディバイド</v>
           </cell>
         </row>
         <row r="89">
           <cell r="A89">
-            <v>14060</v>
+            <v>14030</v>
           </cell>
           <cell r="B89" t="str">
-            <v>パッシブサプライ</v>
+            <v>エイミングスコープ</v>
           </cell>
         </row>
         <row r="90">
           <cell r="A90">
-            <v>14070</v>
+            <v>14040</v>
           </cell>
           <cell r="B90" t="str">
-            <v>ホーミングクルセイド</v>
+            <v>リジェネレーション</v>
           </cell>
         </row>
         <row r="91">
           <cell r="A91">
-            <v>14080</v>
+            <v>14050</v>
           </cell>
           <cell r="B91" t="str">
-            <v>クイックヒール</v>
+            <v>ホープフルアイリス</v>
           </cell>
         </row>
         <row r="92">
           <cell r="A92">
-            <v>14090</v>
+            <v>14060</v>
           </cell>
           <cell r="B92" t="str">
-            <v>リレイズ</v>
+            <v>パッシブサプライ</v>
           </cell>
         </row>
         <row r="93">
           <cell r="A93">
-            <v>15010</v>
+            <v>14070</v>
           </cell>
           <cell r="B93" t="str">
-            <v>イーグルアイ</v>
+            <v>ホーミングクルセイド</v>
           </cell>
         </row>
         <row r="94">
           <cell r="A94">
-            <v>15020</v>
+            <v>14080</v>
           </cell>
           <cell r="B94" t="str">
-            <v>ネヴァーエンド</v>
+            <v>クイックヒール</v>
           </cell>
         </row>
         <row r="95">
           <cell r="A95">
-            <v>15030</v>
+            <v>14090</v>
           </cell>
           <cell r="B95" t="str">
-            <v>グレイブアクト</v>
+            <v>リレイズ</v>
           </cell>
         </row>
         <row r="96">
           <cell r="A96">
-            <v>15040</v>
+            <v>14100</v>
           </cell>
           <cell r="B96" t="str">
-            <v>スカルグラッジ</v>
+            <v>ファストヒール</v>
           </cell>
         </row>
         <row r="97">
           <cell r="A97">
-            <v>15050</v>
+            <v>15010</v>
           </cell>
           <cell r="B97" t="str">
-            <v>ネガティブドレイン</v>
+            <v>イーグルアイ</v>
           </cell>
         </row>
         <row r="98">
           <cell r="A98">
-            <v>15060</v>
+            <v>15020</v>
           </cell>
           <cell r="B98" t="str">
-            <v>アンデッドペイン</v>
+            <v>ネヴァーエンド</v>
           </cell>
         </row>
         <row r="99">
           <cell r="A99">
-            <v>15070</v>
+            <v>15030</v>
           </cell>
           <cell r="B99" t="str">
-            <v>ジャックポッド</v>
+            <v>グレイブアクト</v>
           </cell>
         </row>
         <row r="100">
           <cell r="A100">
-            <v>15080</v>
+            <v>15040</v>
           </cell>
           <cell r="B100" t="str">
-            <v>ヒールハント</v>
+            <v>スカルグラッジ</v>
           </cell>
         </row>
         <row r="101">
           <cell r="A101">
-            <v>15090</v>
+            <v>15050</v>
           </cell>
           <cell r="B101" t="str">
-            <v>クイックカース</v>
+            <v>ネガティブドレイン</v>
           </cell>
         </row>
         <row r="102">
           <cell r="A102">
-            <v>20010</v>
+            <v>15060</v>
           </cell>
           <cell r="B102" t="str">
-            <v>ウェイトユニゾン</v>
+            <v>アンデッドペイン</v>
           </cell>
         </row>
         <row r="103">
           <cell r="A103">
-            <v>30010</v>
+            <v>15070</v>
           </cell>
           <cell r="B103" t="str">
-            <v>ラーニングピアス</v>
+            <v>ジャックポッド</v>
           </cell>
         </row>
         <row r="104">
           <cell r="A104">
-            <v>30020</v>
+            <v>15080</v>
           </cell>
           <cell r="B104" t="str">
-            <v>スティールヒール</v>
+            <v>ヒールハント</v>
           </cell>
         </row>
         <row r="105">
           <cell r="A105">
-            <v>30030</v>
+            <v>15090</v>
           </cell>
           <cell r="B105" t="str">
-            <v>ガッツ</v>
+            <v>クイックカース</v>
           </cell>
         </row>
         <row r="106">
           <cell r="A106">
-            <v>100110</v>
+            <v>15100</v>
           </cell>
           <cell r="B106" t="str">
-            <v>ソーイングアームド</v>
+            <v>リヴェンジャー</v>
           </cell>
         </row>
         <row r="107">
           <cell r="A107">
-            <v>100120</v>
+            <v>20010</v>
           </cell>
           <cell r="B107" t="str">
-            <v>エターナルロンド</v>
+            <v>ウェイトユニゾン</v>
           </cell>
         </row>
         <row r="108">
           <cell r="A108">
-            <v>100210</v>
+            <v>30010</v>
           </cell>
           <cell r="B108" t="str">
-            <v>アブソリュートパリィ</v>
+            <v>ラーニングピアス</v>
           </cell>
         </row>
         <row r="109">
           <cell r="A109">
-            <v>100220</v>
+            <v>30020</v>
           </cell>
           <cell r="B109" t="str">
-            <v>レヴェリー</v>
+            <v>スティールヒール</v>
           </cell>
         </row>
         <row r="110">
           <cell r="A110">
-            <v>100310</v>
+            <v>30030</v>
           </cell>
           <cell r="B110" t="str">
-            <v>セイクリッドバリア</v>
+            <v>ガッツ</v>
           </cell>
         </row>
         <row r="111">
           <cell r="A111">
-            <v>100320</v>
+            <v>100110</v>
           </cell>
           <cell r="B111" t="str">
-            <v>リベンジニードル</v>
+            <v>ソーイングアームド</v>
           </cell>
         </row>
         <row r="112">
           <cell r="A112">
-            <v>100410</v>
+            <v>100120</v>
           </cell>
           <cell r="B112" t="str">
-            <v>アバンデンス</v>
+            <v>エターナルロンド</v>
           </cell>
         </row>
         <row r="113">
           <cell r="A113">
-            <v>100420</v>
+            <v>100210</v>
           </cell>
           <cell r="B113" t="str">
-            <v>ハーヴェスト</v>
+            <v>アブソリュートパリィ</v>
           </cell>
         </row>
         <row r="114">
           <cell r="A114">
-            <v>100510</v>
+            <v>100220</v>
           </cell>
           <cell r="B114" t="str">
-            <v>カースドブレイク</v>
+            <v>レヴェリー</v>
           </cell>
         </row>
         <row r="115">
           <cell r="A115">
-            <v>100520</v>
+            <v>100310</v>
           </cell>
           <cell r="B115" t="str">
-            <v>ムーンライトレイ</v>
+            <v>セイクリッドバリア</v>
           </cell>
         </row>
         <row r="116">
           <cell r="A116">
-            <v>100610</v>
+            <v>100320</v>
           </cell>
           <cell r="B116" t="str">
-            <v>サンフレイム</v>
+            <v>リベンジニードル</v>
           </cell>
         </row>
         <row r="117">
           <cell r="A117">
-            <v>100620</v>
+            <v>100410</v>
           </cell>
           <cell r="B117" t="str">
-            <v>フレイムタン</v>
+            <v>アバンデンス</v>
           </cell>
         </row>
         <row r="118">
           <cell r="A118">
-            <v>100710</v>
+            <v>100420</v>
           </cell>
           <cell r="B118" t="str">
-            <v>ライズザフラッグ</v>
+            <v>ハーヴェスト</v>
           </cell>
         </row>
         <row r="119">
           <cell r="A119">
-            <v>100720</v>
+            <v>100510</v>
           </cell>
           <cell r="B119" t="str">
-            <v>オーバーリミット</v>
+            <v>カースドブレイク</v>
           </cell>
         </row>
         <row r="120">
           <cell r="A120">
-            <v>100810</v>
+            <v>100520</v>
           </cell>
           <cell r="B120" t="str">
-            <v>テンパランス</v>
+            <v>ムーンライトレイ</v>
           </cell>
         </row>
         <row r="121">
           <cell r="A121">
-            <v>100820</v>
+            <v>100610</v>
           </cell>
           <cell r="B121" t="str">
-            <v>シエルクルセイダー</v>
+            <v>サンフレイム</v>
           </cell>
         </row>
         <row r="122">
           <cell r="A122">
-            <v>100910</v>
+            <v>100620</v>
           </cell>
           <cell r="B122" t="str">
-            <v>バーニングカウンター</v>
+            <v>フレイムタン</v>
           </cell>
         </row>
         <row r="123">
           <cell r="A123">
-            <v>100911</v>
+            <v>100710</v>
           </cell>
           <cell r="B123" t="str">
-            <v>バーニングカウンター</v>
+            <v>ライズザフラッグ</v>
           </cell>
         </row>
         <row r="124">
           <cell r="A124">
-            <v>100920</v>
+            <v>100720</v>
           </cell>
           <cell r="B124" t="str">
-            <v>プロミネンス</v>
+            <v>オーバーリミット</v>
           </cell>
         </row>
         <row r="125">
           <cell r="A125">
-            <v>100921</v>
+            <v>100810</v>
           </cell>
           <cell r="B125" t="str">
-            <v>プロミネンス</v>
+            <v>テンパランス</v>
           </cell>
         </row>
         <row r="126">
           <cell r="A126">
-            <v>101010</v>
+            <v>100820</v>
           </cell>
           <cell r="B126" t="str">
-            <v>エウロス</v>
+            <v>シエルクルセイダー</v>
           </cell>
         </row>
         <row r="127">
           <cell r="A127">
-            <v>101020</v>
+            <v>100910</v>
           </cell>
           <cell r="B127" t="str">
-            <v>ボレアス</v>
+            <v>バーニングカウンター</v>
           </cell>
         </row>
         <row r="128">
           <cell r="A128">
-            <v>101110</v>
+            <v>100911</v>
           </cell>
           <cell r="B128" t="str">
-            <v>アバランシュ</v>
+            <v>バーニングカウンター</v>
           </cell>
         </row>
         <row r="129">
           <cell r="A129">
-            <v>101120</v>
+            <v>100920</v>
           </cell>
           <cell r="B129" t="str">
-            <v>ブリザードコフィン</v>
+            <v>プロミネンス</v>
           </cell>
         </row>
         <row r="130">
           <cell r="A130">
-            <v>200110</v>
+            <v>100921</v>
           </cell>
           <cell r="B130" t="str">
-            <v>スリータイムス</v>
+            <v>プロミネンス</v>
           </cell>
         </row>
         <row r="131">
           <cell r="A131">
-            <v>200120</v>
+            <v>101010</v>
           </cell>
           <cell r="B131" t="str">
-            <v>アングリークライ</v>
+            <v>エウロス</v>
           </cell>
         </row>
         <row r="132">
           <cell r="A132">
-            <v>200210</v>
+            <v>101020</v>
           </cell>
           <cell r="B132" t="str">
-            <v>マイトレインフォース</v>
+            <v>ボレアス</v>
           </cell>
         </row>
         <row r="133">
           <cell r="A133">
-            <v>200220</v>
+            <v>101110</v>
           </cell>
           <cell r="B133" t="str">
-            <v>カタストロフィ</v>
+            <v>アバランシュ</v>
           </cell>
         </row>
         <row r="134">
           <cell r="A134">
-            <v>200230</v>
+            <v>101120</v>
           </cell>
           <cell r="B134" t="str">
-            <v>悪魔(ベリト)</v>
+            <v>ブリザードコフィン</v>
           </cell>
         </row>
         <row r="135">
           <cell r="A135">
-            <v>200310</v>
+            <v>200110</v>
           </cell>
           <cell r="B135" t="str">
-            <v>プルガシオン</v>
+            <v>スリータイムス</v>
           </cell>
         </row>
         <row r="136">
           <cell r="A136">
-            <v>200320</v>
+            <v>200120</v>
           </cell>
           <cell r="B136" t="str">
-            <v>プリエステス</v>
+            <v>アングリークライ</v>
           </cell>
         </row>
         <row r="137">
           <cell r="A137">
-            <v>200330</v>
+            <v>200210</v>
           </cell>
           <cell r="B137" t="str">
-            <v>悪魔(パイモン)</v>
+            <v>マイトレインフォース</v>
           </cell>
         </row>
         <row r="138">
           <cell r="A138">
-            <v>200410</v>
+            <v>200220</v>
           </cell>
           <cell r="B138" t="str">
-            <v>コウソクテンショウ</v>
+            <v>カタストロフィ</v>
           </cell>
         </row>
         <row r="139">
           <cell r="A139">
-            <v>200411</v>
+            <v>200230</v>
           </cell>
           <cell r="B139" t="str">
-            <v>コウソクテンショウ</v>
+            <v>悪魔(ベリト)</v>
           </cell>
         </row>
         <row r="140">
           <cell r="A140">
-            <v>200420</v>
+            <v>200310</v>
           </cell>
           <cell r="B140" t="str">
-            <v>アンチバフ</v>
+            <v>プルガシオン</v>
           </cell>
         </row>
         <row r="141">
           <cell r="A141">
-            <v>200430</v>
+            <v>200320</v>
           </cell>
           <cell r="B141" t="str">
-            <v>悪魔(アンドラス)</v>
+            <v>プリエステス</v>
           </cell>
         </row>
         <row r="142">
           <cell r="A142">
-            <v>200510</v>
+            <v>200330</v>
           </cell>
           <cell r="B142" t="str">
-            <v>カウントダウン</v>
+            <v>悪魔(パイモン)</v>
           </cell>
         </row>
         <row r="143">
           <cell r="A143">
-            <v>200520</v>
+            <v>200410</v>
           </cell>
           <cell r="B143" t="str">
-            <v>グラウンドゼロ</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="144">
           <cell r="A144">
-            <v>200530</v>
+            <v>200411</v>
           </cell>
           <cell r="B144" t="str">
-            <v>悪魔(ビフロンス)</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="145">
           <cell r="A145">
-            <v>201010</v>
+            <v>200420</v>
           </cell>
           <cell r="B145" t="str">
-            <v>カオスペイン</v>
+            <v>アンチバフ</v>
           </cell>
         </row>
         <row r="146">
           <cell r="A146">
-            <v>201020</v>
+            <v>200430</v>
           </cell>
           <cell r="B146" t="str">
-            <v>フォールンワン</v>
+            <v>悪魔(アンドラス)</v>
           </cell>
         </row>
         <row r="147">
           <cell r="A147">
-            <v>201030</v>
+            <v>200510</v>
           </cell>
           <cell r="B147" t="str">
-            <v>アンリマユ</v>
+            <v>カウントダウン</v>
           </cell>
         </row>
         <row r="148">
           <cell r="A148">
-            <v>300010</v>
+            <v>200520</v>
           </cell>
           <cell r="B148" t="str">
-            <v>ライフブースト</v>
+            <v>グラウンドゼロ</v>
           </cell>
         </row>
         <row r="149">
           <cell r="A149">
-            <v>300020</v>
+            <v>200530</v>
           </cell>
           <cell r="B149" t="str">
-            <v>スピリットチャージ</v>
+            <v>悪魔(ビフロンス)</v>
           </cell>
         </row>
         <row r="150">
           <cell r="A150">
-            <v>300030</v>
+            <v>201010</v>
           </cell>
           <cell r="B150" t="str">
-            <v>フォースライズ</v>
+            <v>カオスペイン</v>
           </cell>
         </row>
         <row r="151">
           <cell r="A151">
-            <v>300040</v>
+            <v>201020</v>
           </cell>
           <cell r="B151" t="str">
-            <v>ディフェンスオーラ</v>
+            <v>フォールンワン</v>
           </cell>
         </row>
         <row r="152">
           <cell r="A152">
-            <v>300050</v>
+            <v>201030</v>
           </cell>
           <cell r="B152" t="str">
-            <v>ラピッドムーブ</v>
+            <v>アンリマユ</v>
           </cell>
         </row>
         <row r="153">
           <cell r="A153">
-            <v>300130</v>
+            <v>300010</v>
           </cell>
           <cell r="B153" t="str">
-            <v>アタックブレイク</v>
+            <v>ライフブースト</v>
           </cell>
         </row>
         <row r="154">
           <cell r="A154">
-            <v>300140</v>
+            <v>300020</v>
           </cell>
           <cell r="B154" t="str">
-            <v>シールドバニッシュ</v>
+            <v>スピリットチャージ</v>
           </cell>
         </row>
         <row r="155">
           <cell r="A155">
-            <v>300210</v>
+            <v>300030</v>
           </cell>
           <cell r="B155" t="str">
-            <v>エーテルリチャージ</v>
+            <v>フォースライズ</v>
           </cell>
         </row>
         <row r="156">
           <cell r="A156">
-            <v>300220</v>
+            <v>300040</v>
           </cell>
           <cell r="B156" t="str">
-            <v>リカバリーエンハンス</v>
+            <v>ディフェンスオーラ</v>
           </cell>
         </row>
         <row r="157">
           <cell r="A157">
-            <v>300230</v>
+            <v>300050</v>
           </cell>
           <cell r="B157" t="str">
-            <v>ヴェンジェンス</v>
+            <v>ラピッドムーブ</v>
           </cell>
         </row>
         <row r="158">
           <cell r="A158">
-            <v>301010</v>
+            <v>300130</v>
           </cell>
           <cell r="B158" t="str">
-            <v>ディケイドリセット</v>
+            <v>アタックブレイク</v>
           </cell>
         </row>
         <row r="159">
           <cell r="A159">
-            <v>301020</v>
+            <v>300140</v>
           </cell>
           <cell r="B159" t="str">
-            <v>ウォーリアーブラッド</v>
+            <v>シールドバニッシュ</v>
           </cell>
         </row>
         <row r="160">
           <cell r="A160">
-            <v>301030</v>
+            <v>300210</v>
           </cell>
           <cell r="B160" t="str">
-            <v>トライアングルガード</v>
+            <v>エーテルリチャージ</v>
           </cell>
         </row>
         <row r="161">
           <cell r="A161">
-            <v>301040</v>
+            <v>300220</v>
           </cell>
           <cell r="B161" t="str">
-            <v>セーフティバリア</v>
+            <v>リカバリーエンハンス</v>
           </cell>
         </row>
         <row r="162">
           <cell r="A162">
-            <v>301050</v>
+            <v>300230</v>
           </cell>
           <cell r="B162" t="str">
-            <v>ヒロインズハイ</v>
+            <v>ヴェンジェンス</v>
           </cell>
         </row>
         <row r="163">
           <cell r="A163">
-            <v>301060</v>
+            <v>301010</v>
           </cell>
           <cell r="B163" t="str">
-            <v>セカンドステージ</v>
+            <v>ディケイドリセット</v>
           </cell>
         </row>
         <row r="164">
           <cell r="A164">
-            <v>301070</v>
+            <v>301020</v>
           </cell>
           <cell r="B164" t="str">
-            <v>ハイヒットポイント</v>
+            <v>ウォーリアーブラッド</v>
           </cell>
         </row>
         <row r="165">
           <cell r="A165">
-            <v>301080</v>
+            <v>301030</v>
           </cell>
           <cell r="B165" t="str">
-            <v>セプタブラスト</v>
+            <v>トライアングルガード</v>
           </cell>
         </row>
         <row r="166">
           <cell r="A166">
-            <v>301090</v>
+            <v>301040</v>
           </cell>
           <cell r="B166" t="str">
-            <v>イニシャルブロッカー</v>
+            <v>セーフティバリア</v>
           </cell>
         </row>
         <row r="167">
           <cell r="A167">
-            <v>301100</v>
+            <v>301050</v>
           </cell>
           <cell r="B167" t="str">
-            <v>ファーストテイク</v>
+            <v>ヒロインズハイ</v>
           </cell>
         </row>
         <row r="168">
           <cell r="A168">
-            <v>310010</v>
+            <v>301060</v>
           </cell>
           <cell r="B168" t="str">
-            <v>妖精の祈り</v>
+            <v>セカンドステージ</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169">
-            <v>310020</v>
+            <v>301070</v>
           </cell>
           <cell r="B169" t="str">
-            <v>月のかけら</v>
+            <v>ハイヒットポイント</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170">
-            <v>310030</v>
+            <v>301080</v>
           </cell>
           <cell r="B170" t="str">
-            <v>商売の才覚書</v>
+            <v>セプタブラスト</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171">
-            <v>310040</v>
+            <v>301090</v>
           </cell>
           <cell r="B171" t="str">
-            <v>レイヴンバナー</v>
+            <v>イニシャルブロッカー</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172">
-            <v>310041</v>
+            <v>301100</v>
           </cell>
           <cell r="B172" t="str">
-            <v>レイヴンバナー</v>
+            <v>ファーストテイク</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173">
-            <v>310050</v>
+            <v>310010</v>
           </cell>
           <cell r="B173" t="str">
-            <v>先陣の心得</v>
+            <v>妖精の祈り</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174">
-            <v>310130</v>
+            <v>310020</v>
           </cell>
           <cell r="B174" t="str">
-            <v>ヒールユニット</v>
+            <v>月のかけら</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175">
-            <v>320010</v>
+            <v>310030</v>
           </cell>
           <cell r="B175" t="str">
-            <v>訓練所Lv1</v>
+            <v>商売の才覚書</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176">
-            <v>320011</v>
+            <v>310040</v>
           </cell>
           <cell r="B176" t="str">
-            <v>訓練所Lv2</v>
+            <v>メビウスの砂時計</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177">
-            <v>320012</v>
+            <v>310050</v>
           </cell>
           <cell r="B177" t="str">
-            <v>訓練所Lv3</v>
+            <v>先陣の心得</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178">
-            <v>320020</v>
+            <v>310060</v>
           </cell>
           <cell r="B178" t="str">
-            <v>研究施設Lv1</v>
+            <v>ヒスイの勾玉</v>
           </cell>
         </row>
         <row r="179">
           <cell r="A179">
-            <v>320021</v>
+            <v>310070</v>
           </cell>
           <cell r="B179" t="str">
-            <v>研究施設Lv2</v>
+            <v>英傑の盾</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180">
-            <v>320022</v>
+            <v>310080</v>
           </cell>
           <cell r="B180" t="str">
-            <v>研究施設Lv3</v>
+            <v>鷹の目</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181">
-            <v>320030</v>
+            <v>310130</v>
           </cell>
           <cell r="B181" t="str">
-            <v>資料館Lv1</v>
+            <v>ヒールユニット</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182">
-            <v>320031</v>
+            <v>320010</v>
           </cell>
           <cell r="B182" t="str">
-            <v>資料館Lv2</v>
+            <v>訓練所Lv1</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183">
-            <v>320032</v>
+            <v>320011</v>
           </cell>
           <cell r="B183" t="str">
-            <v>資料館Lv3</v>
+            <v>訓練所Lv2</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184">
-            <v>320040</v>
+            <v>320012</v>
           </cell>
           <cell r="B184" t="str">
-            <v>潜伏技術Lv1</v>
+            <v>訓練所Lv3</v>
           </cell>
         </row>
         <row r="185">
           <cell r="A185">
-            <v>321010</v>
+            <v>320020</v>
           </cell>
           <cell r="B185" t="str">
-            <v>炎の祭壇</v>
+            <v>研究施設Lv1</v>
           </cell>
         </row>
         <row r="186">
           <cell r="A186">
-            <v>321020</v>
+            <v>320021</v>
           </cell>
           <cell r="B186" t="str">
-            <v>稲妻の祭壇</v>
+            <v>研究施設Lv2</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187">
-            <v>321030</v>
+            <v>320022</v>
           </cell>
           <cell r="B187" t="str">
-            <v>蒼の祭壇</v>
+            <v>研究施設Lv3</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188">
-            <v>321040</v>
+            <v>320030</v>
           </cell>
           <cell r="B188" t="str">
-            <v>光の祭壇</v>
+            <v>資料館Lv1</v>
           </cell>
         </row>
         <row r="189">
           <cell r="A189">
-            <v>321050</v>
+            <v>320031</v>
           </cell>
           <cell r="B189" t="str">
-            <v>月の祭壇</v>
+            <v>資料館Lv2</v>
           </cell>
         </row>
         <row r="190">
           <cell r="A190">
-            <v>322010</v>
+            <v>320032</v>
           </cell>
           <cell r="B190" t="str">
-            <v>食糧庫Lv1</v>
+            <v>資料館Lv3</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191">
-            <v>322020</v>
+            <v>320040</v>
           </cell>
           <cell r="B191" t="str">
-            <v>攻撃技術Lv1</v>
+            <v>潜伏技術Lv1</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192">
-            <v>322030</v>
+            <v>321010</v>
           </cell>
           <cell r="B192" t="str">
-            <v>防御技術Lv1</v>
+            <v>炎の祭壇</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193">
-            <v>322040</v>
+            <v>321020</v>
           </cell>
           <cell r="B193" t="str">
-            <v>詠唱技術Lv1</v>
+            <v>稲妻の祭壇</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194">
-            <v>401010</v>
+            <v>321030</v>
           </cell>
           <cell r="B194" t="str">
-            <v>ファイアボール+</v>
+            <v>蒼の祭壇</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195">
-            <v>401020</v>
+            <v>321040</v>
           </cell>
           <cell r="B195" t="str">
-            <v>バーンストーム+</v>
+            <v>光の祭壇</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196">
-            <v>401030</v>
+            <v>321050</v>
           </cell>
           <cell r="B196" t="str">
-            <v>ヒートスタンプ+</v>
+            <v>月の祭壇</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197">
-            <v>401040</v>
+            <v>322010</v>
           </cell>
           <cell r="B197" t="str">
-            <v>ソードアダプト+</v>
+            <v>食糧庫Lv1</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198">
-            <v>401050</v>
+            <v>322020</v>
           </cell>
           <cell r="B198" t="str">
-            <v>フレイムレイン+</v>
+            <v>攻撃技術Lv1</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199">
-            <v>401060</v>
+            <v>322030</v>
           </cell>
           <cell r="B199" t="str">
-            <v>イクスティンクション+</v>
+            <v>防御技術Lv1</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200">
-            <v>401070</v>
+            <v>322040</v>
           </cell>
           <cell r="B200" t="str">
-            <v>バーニングソウル+</v>
+            <v>詠唱技術Lv1</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201">
-            <v>401080</v>
+            <v>401010</v>
           </cell>
           <cell r="B201" t="str">
-            <v>レイジングバウンサー+</v>
+            <v>ファイアボール+</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202">
-            <v>402010</v>
+            <v>401020</v>
           </cell>
           <cell r="B202" t="str">
-            <v>ディスチャージ+</v>
+            <v>バーンストーム+</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203">
-            <v>402020</v>
+            <v>401030</v>
           </cell>
           <cell r="B203" t="str">
-            <v>イベイドコード+</v>
+            <v>ヒートスタンプ+</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204">
-            <v>402030</v>
+            <v>401040</v>
           </cell>
           <cell r="B204" t="str">
-            <v>ショックインパルス+</v>
+            <v>ソードアダプト+</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205">
-            <v>402040</v>
+            <v>401050</v>
           </cell>
           <cell r="B205" t="str">
-            <v>トラストチェイン+</v>
+            <v>フレイムレイン+</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206">
-            <v>402050</v>
+            <v>401060</v>
           </cell>
           <cell r="B206" t="str">
-            <v>スペルバニシング+</v>
+            <v>イクスティンクション+</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207">
-            <v>402060</v>
+            <v>401070</v>
           </cell>
           <cell r="B207" t="str">
-            <v>アーテニーストライク+</v>
+            <v>バーニングソウル+</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208">
-            <v>402070</v>
+            <v>401080</v>
           </cell>
           <cell r="B208" t="str">
-            <v>コンセントレイト+</v>
+            <v>レイジングバウンサー+</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209">
-            <v>402080</v>
+            <v>402010</v>
           </cell>
           <cell r="B209" t="str">
-            <v>ディレイマジック+</v>
+            <v>ディスチャージ+</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210">
-            <v>403010</v>
+            <v>402020</v>
           </cell>
           <cell r="B210" t="str">
-            <v>アイスブレイド+</v>
+            <v>イベイドコード+</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211">
-            <v>403020</v>
+            <v>402030</v>
           </cell>
           <cell r="B211" t="str">
-            <v>カウンターオーラ+</v>
+            <v>ショックインパルス+</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212">
-            <v>403030</v>
+            <v>402040</v>
           </cell>
           <cell r="B212" t="str">
-            <v>ラインプロテクト+</v>
+            <v>トラストチェイン+</v>
           </cell>
         </row>
         <row r="213">
           <cell r="A213">
-            <v>403040</v>
+            <v>402050</v>
           </cell>
           <cell r="B213" t="str">
-            <v>エスコートソール+</v>
+            <v>スペルバニシング+</v>
           </cell>
         </row>
         <row r="214">
           <cell r="A214">
-            <v>403050</v>
+            <v>402060</v>
           </cell>
           <cell r="B214" t="str">
-            <v>ディープフリーズ+</v>
+            <v>アーテニーストライク+</v>
           </cell>
         </row>
         <row r="215">
           <cell r="A215">
-            <v>403060</v>
+            <v>402070</v>
           </cell>
           <cell r="B215" t="str">
-            <v>バブルブロウ+</v>
+            <v>コンセントレイト+</v>
           </cell>
         </row>
         <row r="216">
           <cell r="A216">
-            <v>403070</v>
+            <v>402080</v>
           </cell>
           <cell r="B216" t="str">
-            <v>アクアミラージュ+</v>
+            <v>ディレイマジック+</v>
           </cell>
         </row>
         <row r="217">
           <cell r="A217">
-            <v>403080</v>
+            <v>403010</v>
           </cell>
           <cell r="B217" t="str">
-            <v>フロストシールド+</v>
+            <v>アイスブレイド+</v>
           </cell>
         </row>
         <row r="218">
           <cell r="A218">
-            <v>404010</v>
+            <v>403020</v>
           </cell>
           <cell r="B218" t="str">
-            <v>セイントレーザー+</v>
+            <v>カウンターオーラ+</v>
           </cell>
         </row>
         <row r="219">
           <cell r="A219">
-            <v>404020</v>
+            <v>403030</v>
           </cell>
           <cell r="B219" t="str">
-            <v>ペネトレイト+</v>
+            <v>ラインプロテクト+</v>
           </cell>
         </row>
         <row r="220">
           <cell r="A220">
-            <v>404030</v>
+            <v>403040</v>
           </cell>
           <cell r="B220" t="str">
-            <v>ヒーリング+</v>
+            <v>エスコートソール+</v>
           </cell>
         </row>
         <row r="221">
           <cell r="A221">
-            <v>404040</v>
+            <v>403050</v>
           </cell>
           <cell r="B221" t="str">
-            <v>リザイアフォトン+</v>
+            <v>ディープフリーズ+</v>
           </cell>
         </row>
         <row r="222">
           <cell r="A222">
-            <v>404050</v>
+            <v>403060</v>
           </cell>
           <cell r="B222" t="str">
-            <v>べネディクション+</v>
+            <v>バブルブロウ+</v>
           </cell>
         </row>
         <row r="223">
           <cell r="A223">
-            <v>404060</v>
+            <v>403070</v>
           </cell>
           <cell r="B223" t="str">
-            <v>ホーリーグレイス+</v>
+            <v>アクアミラージュ+</v>
           </cell>
         </row>
         <row r="224">
           <cell r="A224">
-            <v>404070</v>
+            <v>403080</v>
           </cell>
           <cell r="B224" t="str">
-            <v>キュアエール+</v>
+            <v>フロストシールド+</v>
           </cell>
         </row>
         <row r="225">
           <cell r="A225">
-            <v>404080</v>
+            <v>404010</v>
           </cell>
           <cell r="B225" t="str">
-            <v>ラインバリア+</v>
+            <v>セイントレーザー+</v>
           </cell>
         </row>
         <row r="226">
           <cell r="A226">
-            <v>405010</v>
+            <v>404020</v>
           </cell>
           <cell r="B226" t="str">
-            <v>ダークプリズン+</v>
+            <v>ペネトレイト+</v>
           </cell>
         </row>
         <row r="227">
           <cell r="A227">
-            <v>405020</v>
+            <v>404030</v>
           </cell>
           <cell r="B227" t="str">
-            <v>ユーサネイジア+</v>
+            <v>ヒーリング+</v>
           </cell>
         </row>
         <row r="228">
           <cell r="A228">
-            <v>405030</v>
+            <v>404040</v>
           </cell>
           <cell r="B228" t="str">
-            <v>ドレインヒール+</v>
+            <v>リザイアフォトン+</v>
           </cell>
         </row>
         <row r="229">
           <cell r="A229">
-            <v>405040</v>
+            <v>404050</v>
           </cell>
           <cell r="B229" t="str">
-            <v>アビサルデスペア+</v>
+            <v>べネディクション+</v>
           </cell>
         </row>
         <row r="230">
           <cell r="A230">
-            <v>405050</v>
+            <v>404060</v>
           </cell>
           <cell r="B230" t="str">
-            <v>ディプラヴィティ+</v>
+            <v>ホーリーグレイス+</v>
           </cell>
         </row>
         <row r="231">
           <cell r="A231">
-            <v>405060</v>
+            <v>404070</v>
           </cell>
           <cell r="B231" t="str">
-            <v>ダークネス+</v>
+            <v>キュアエール+</v>
           </cell>
         </row>
         <row r="232">
           <cell r="A232">
-            <v>405070</v>
+            <v>404080</v>
           </cell>
           <cell r="B232" t="str">
-            <v>シェイディークラウド+</v>
+            <v>ラインバリア+</v>
           </cell>
         </row>
         <row r="233">
           <cell r="A233">
-            <v>405080</v>
+            <v>405010</v>
           </cell>
           <cell r="B233" t="str">
-            <v>ポイズンブロウ+</v>
+            <v>ダークプリズン+</v>
           </cell>
         </row>
         <row r="234">
           <cell r="A234">
-            <v>411010</v>
+            <v>405020</v>
           </cell>
           <cell r="B234" t="str">
-            <v>ウルフソウル+</v>
+            <v>ユーサネイジア+</v>
           </cell>
         </row>
         <row r="235">
           <cell r="A235">
-            <v>411020</v>
+            <v>405030</v>
           </cell>
           <cell r="B235" t="str">
-            <v>プリディカメント+</v>
+            <v>ドレインヒール+</v>
           </cell>
         </row>
         <row r="236">
           <cell r="A236">
-            <v>411030</v>
+            <v>405040</v>
           </cell>
           <cell r="B236" t="str">
-            <v>アサルトシフト+</v>
+            <v>アビサルデスペア+</v>
           </cell>
         </row>
         <row r="237">
           <cell r="A237">
-            <v>411040</v>
+            <v>405050</v>
           </cell>
           <cell r="B237" t="str">
-            <v>アクティブギフト+</v>
+            <v>ディプラヴィティ+</v>
           </cell>
         </row>
         <row r="238">
           <cell r="A238">
-            <v>411050</v>
+            <v>405060</v>
           </cell>
           <cell r="B238" t="str">
-            <v>イグナイテッド+</v>
+            <v>ダークネス+</v>
           </cell>
         </row>
         <row r="239">
           <cell r="A239">
-            <v>411060</v>
+            <v>405070</v>
           </cell>
           <cell r="B239" t="str">
-            <v>ライジングファイア+</v>
+            <v>シェイディークラウド+</v>
           </cell>
         </row>
         <row r="240">
           <cell r="A240">
-            <v>411070</v>
+            <v>405080</v>
           </cell>
           <cell r="B240" t="str">
-            <v>ルージュバック+</v>
+            <v>ポイズンブロウ+</v>
           </cell>
         </row>
         <row r="241">
           <cell r="A241">
-            <v>411080</v>
+            <v>411010</v>
           </cell>
           <cell r="B241" t="str">
-            <v>パワーエール+</v>
+            <v>ウルフソウル+</v>
           </cell>
         </row>
         <row r="242">
           <cell r="A242">
-            <v>411090</v>
+            <v>411020</v>
           </cell>
           <cell r="B242" t="str">
-            <v>スレイプニル+</v>
+            <v>プリディカメント+</v>
           </cell>
         </row>
         <row r="243">
           <cell r="A243">
-            <v>412010</v>
+            <v>411030</v>
           </cell>
           <cell r="B243" t="str">
-            <v>エクステンション+</v>
+            <v>アサルトシフト+</v>
           </cell>
         </row>
         <row r="244">
           <cell r="A244">
-            <v>412020</v>
+            <v>411040</v>
           </cell>
           <cell r="B244" t="str">
-            <v>ヘブンリーラック+</v>
+            <v>アクティブギフト+</v>
           </cell>
         </row>
         <row r="245">
           <cell r="A245">
-            <v>412030</v>
+            <v>411050</v>
           </cell>
           <cell r="B245" t="str">
-            <v>スウィフトカレント+</v>
+            <v>イグナイテッド+</v>
           </cell>
         </row>
         <row r="246">
           <cell r="A246">
-            <v>412040</v>
+            <v>411060</v>
           </cell>
           <cell r="B246" t="str">
-            <v>イヴェイドオール+</v>
+            <v>ライジングファイア+</v>
           </cell>
         </row>
         <row r="247">
           <cell r="A247">
-            <v>412050</v>
+            <v>411070</v>
           </cell>
           <cell r="B247" t="str">
-            <v>クイックムーブ+</v>
+            <v>ルージュバック+</v>
           </cell>
         </row>
         <row r="248">
           <cell r="A248">
-            <v>412060</v>
+            <v>411080</v>
           </cell>
           <cell r="B248" t="str">
-            <v>チェイスマジック+</v>
+            <v>パワーエール+</v>
           </cell>
         </row>
         <row r="249">
           <cell r="A249">
-            <v>412070</v>
+            <v>411090</v>
           </cell>
           <cell r="B249" t="str">
-            <v>ソーサリーコネクト+</v>
+            <v>スレイプニル+</v>
           </cell>
         </row>
         <row r="250">
           <cell r="A250">
-            <v>412080</v>
+            <v>412010</v>
           </cell>
           <cell r="B250" t="str">
-            <v>ウィンドライズ+</v>
+            <v>エクステンション+</v>
           </cell>
         </row>
         <row r="251">
           <cell r="A251">
-            <v>412090</v>
+            <v>412020</v>
           </cell>
           <cell r="B251" t="str">
-            <v>アウトオブオーダー+</v>
+            <v>ヘブンリーラック+</v>
           </cell>
         </row>
         <row r="252">
           <cell r="A252">
-            <v>413010</v>
+            <v>412030</v>
           </cell>
           <cell r="B252" t="str">
-            <v>アーマーコード+</v>
+            <v>スウィフトカレント+</v>
           </cell>
         </row>
         <row r="253">
           <cell r="A253">
-            <v>413020</v>
+            <v>412040</v>
           </cell>
           <cell r="B253" t="str">
-            <v>クイックバリア+</v>
+            <v>イヴェイドオール+</v>
           </cell>
         </row>
         <row r="254">
           <cell r="A254">
-            <v>413030</v>
+            <v>412050</v>
           </cell>
           <cell r="B254" t="str">
-            <v>クイックキュア+</v>
+            <v>クイックムーブ+</v>
           </cell>
         </row>
         <row r="255">
           <cell r="A255">
-            <v>413040</v>
+            <v>412060</v>
           </cell>
           <cell r="B255" t="str">
-            <v>セルフシールド+</v>
+            <v>チェイスマジック+</v>
           </cell>
         </row>
         <row r="256">
           <cell r="A256">
-            <v>413050</v>
+            <v>412070</v>
           </cell>
           <cell r="B256" t="str">
-            <v>パッシブジャミング+</v>
+            <v>ソーサリーコネクト+</v>
           </cell>
         </row>
         <row r="257">
           <cell r="A257">
-            <v>413060</v>
+            <v>412080</v>
           </cell>
           <cell r="B257" t="str">
-            <v>サプライカバー+</v>
+            <v>ウィンドライズ+</v>
           </cell>
         </row>
         <row r="258">
           <cell r="A258">
-            <v>413070</v>
+            <v>412090</v>
           </cell>
           <cell r="B258" t="str">
-            <v>アシッドラッシュ+</v>
+            <v>アウトオブオーダー+</v>
           </cell>
         </row>
         <row r="259">
           <cell r="A259">
-            <v>413080</v>
+            <v>413010</v>
           </cell>
           <cell r="B259" t="str">
-            <v>ライフスティール+</v>
+            <v>アーマーコード+</v>
           </cell>
         </row>
         <row r="260">
           <cell r="A260">
-            <v>413090</v>
+            <v>413020</v>
           </cell>
           <cell r="B260" t="str">
-            <v>アイスセイバー+</v>
+            <v>クイックバリア+</v>
           </cell>
         </row>
         <row r="261">
           <cell r="A261">
-            <v>414010</v>
+            <v>413030</v>
           </cell>
           <cell r="B261" t="str">
-            <v>ディバインシールド+</v>
+            <v>クイックキュア+</v>
           </cell>
         </row>
         <row r="262">
           <cell r="A262">
-            <v>414020</v>
+            <v>413040</v>
           </cell>
           <cell r="B262" t="str">
-            <v>ライフディバイド+</v>
+            <v>セルフシールド+</v>
           </cell>
         </row>
         <row r="263">
           <cell r="A263">
-            <v>414030</v>
+            <v>413050</v>
           </cell>
           <cell r="B263" t="str">
-            <v>エイミングスコープ+</v>
+            <v>パッシブジャミング+</v>
           </cell>
         </row>
         <row r="264">
           <cell r="A264">
-            <v>414040</v>
+            <v>413060</v>
           </cell>
           <cell r="B264" t="str">
-            <v>リジェネレーション+</v>
+            <v>サプライカバー+</v>
           </cell>
         </row>
         <row r="265">
           <cell r="A265">
-            <v>414050</v>
+            <v>413070</v>
           </cell>
           <cell r="B265" t="str">
-            <v>ホープフルアイリス+</v>
+            <v>アシッドラッシュ+</v>
           </cell>
         </row>
         <row r="266">
           <cell r="A266">
-            <v>414060</v>
+            <v>413080</v>
           </cell>
           <cell r="B266" t="str">
-            <v>パッシブサプライ+</v>
+            <v>ライフスティール+</v>
           </cell>
         </row>
         <row r="267">
           <cell r="A267">
-            <v>414070</v>
+            <v>413090</v>
           </cell>
           <cell r="B267" t="str">
-            <v>ホーミングクルセイド+</v>
+            <v>アイスセイバー+</v>
           </cell>
         </row>
         <row r="268">
           <cell r="A268">
-            <v>414080</v>
+            <v>414010</v>
           </cell>
           <cell r="B268" t="str">
-            <v>クイックヒール+</v>
+            <v>ディバインシールド+</v>
           </cell>
         </row>
         <row r="269">
           <cell r="A269">
-            <v>414090</v>
+            <v>414020</v>
           </cell>
           <cell r="B269" t="str">
-            <v>リレイズ+</v>
+            <v>ライフディバイド+</v>
           </cell>
         </row>
         <row r="270">
           <cell r="A270">
-            <v>415010</v>
+            <v>414030</v>
           </cell>
           <cell r="B270" t="str">
-            <v>イーグルアイ+</v>
+            <v>エイミングスコープ+</v>
           </cell>
         </row>
         <row r="271">
           <cell r="A271">
-            <v>415020</v>
+            <v>414040</v>
           </cell>
           <cell r="B271" t="str">
-            <v>ネヴァーエンド+</v>
+            <v>リジェネレーション+</v>
           </cell>
         </row>
         <row r="272">
           <cell r="A272">
-            <v>415030</v>
+            <v>414050</v>
           </cell>
           <cell r="B272" t="str">
-            <v>グレイブアクト+</v>
+            <v>ホープフルアイリス+</v>
           </cell>
         </row>
         <row r="273">
           <cell r="A273">
-            <v>415040</v>
+            <v>414060</v>
           </cell>
           <cell r="B273" t="str">
-            <v>スカルグラッジ+</v>
+            <v>パッシブサプライ+</v>
           </cell>
         </row>
         <row r="274">
           <cell r="A274">
-            <v>415050</v>
+            <v>414070</v>
           </cell>
           <cell r="B274" t="str">
-            <v>ネガティブドレイン+</v>
+            <v>ホーミングクルセイド+</v>
           </cell>
         </row>
         <row r="275">
           <cell r="A275">
-            <v>415060</v>
+            <v>414080</v>
           </cell>
           <cell r="B275" t="str">
-            <v>アンデッドペイン+</v>
+            <v>クイックヒール+</v>
           </cell>
         </row>
         <row r="276">
           <cell r="A276">
-            <v>415070</v>
+            <v>414090</v>
           </cell>
           <cell r="B276" t="str">
-            <v>ジャックポッド+</v>
+            <v>リレイズ+</v>
           </cell>
         </row>
         <row r="277">
           <cell r="A277">
-            <v>415080</v>
+            <v>415010</v>
           </cell>
           <cell r="B277" t="str">
-            <v>ヒールハント+</v>
+            <v>イーグルアイ+</v>
           </cell>
         </row>
         <row r="278">
           <cell r="A278">
+            <v>415020</v>
+          </cell>
+          <cell r="B278" t="str">
+            <v>ネヴァーエンド+</v>
+          </cell>
+        </row>
+        <row r="279">
+          <cell r="A279">
+            <v>415030</v>
+          </cell>
+          <cell r="B279" t="str">
+            <v>グレイブアクト+</v>
+          </cell>
+        </row>
+        <row r="280">
+          <cell r="A280">
+            <v>415040</v>
+          </cell>
+          <cell r="B280" t="str">
+            <v>スカルグラッジ+</v>
+          </cell>
+        </row>
+        <row r="281">
+          <cell r="A281">
+            <v>415050</v>
+          </cell>
+          <cell r="B281" t="str">
+            <v>ネガティブドレイン+</v>
+          </cell>
+        </row>
+        <row r="282">
+          <cell r="A282">
+            <v>415060</v>
+          </cell>
+          <cell r="B282" t="str">
+            <v>アンデッドペイン+</v>
+          </cell>
+        </row>
+        <row r="283">
+          <cell r="A283">
+            <v>415070</v>
+          </cell>
+          <cell r="B283" t="str">
+            <v>ジャックポッド+</v>
+          </cell>
+        </row>
+        <row r="284">
+          <cell r="A284">
+            <v>415080</v>
+          </cell>
+          <cell r="B284" t="str">
+            <v>ヒールハント+</v>
+          </cell>
+        </row>
+        <row r="285">
+          <cell r="A285">
             <v>415090</v>
           </cell>
-          <cell r="B278" t="str">
+          <cell r="B285" t="str">
             <v>クイックカース+</v>
           </cell>
         </row>
@@ -5575,7 +5631,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G208"/>
+  <dimension ref="A1:G209"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="16.7272727272727" customWidth="1"/>
@@ -7505,20 +7561,20 @@
         <v>102</v>
       </c>
       <c r="B81">
-        <v>15050</v>
+        <v>5020</v>
       </c>
       <c r="C81" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B81,[1]TextData!A:A))</f>
-        <v>ネガティブドレイン</v>
+        <v>ユーサネイジア</v>
       </c>
       <c r="D81">
         <v>1</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>1013</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7529,11 +7585,11 @@
         <v>102</v>
       </c>
       <c r="B82">
-        <v>200210</v>
+        <v>15050</v>
       </c>
       <c r="C82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B82,[1]TextData!A:A))</f>
-        <v>マイトレインフォース</v>
+        <v>ネガティブドレイン</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -7553,17 +7609,17 @@
         <v>102</v>
       </c>
       <c r="B83">
-        <v>200220</v>
+        <v>200210</v>
       </c>
       <c r="C83" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B83,[1]TextData!A:A))</f>
-        <v>カタストロフィ</v>
+        <v>マイトレインフォース</v>
       </c>
       <c r="D83">
         <v>1</v>
       </c>
       <c r="E83">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -7577,17 +7633,17 @@
         <v>102</v>
       </c>
       <c r="B84">
-        <v>200230</v>
+        <v>200220</v>
       </c>
       <c r="C84" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B84,[1]TextData!A:A))</f>
-        <v>悪魔(ベリト)</v>
+        <v>カタストロフィ</v>
       </c>
       <c r="D84">
         <v>1</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -7598,20 +7654,20 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B85">
-        <v>4010</v>
+        <v>200230</v>
       </c>
       <c r="C85" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B85,[1]TextData!A:A))</f>
-        <v>セイントレーザー</v>
+        <v>悪魔(ベリト)</v>
       </c>
       <c r="D85">
         <v>1</v>
       </c>
       <c r="E85">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -7625,20 +7681,20 @@
         <v>103</v>
       </c>
       <c r="B86">
-        <v>4030</v>
+        <v>4010</v>
       </c>
       <c r="C86" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B86,[1]TextData!A:A))</f>
-        <v>ヒーリング</v>
+        <v>セイントレーザー</v>
       </c>
       <c r="D86">
         <v>1</v>
       </c>
       <c r="E86">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F86">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -7649,17 +7705,17 @@
         <v>103</v>
       </c>
       <c r="B87">
-        <v>14080</v>
+        <v>4030</v>
       </c>
       <c r="C87" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B87,[1]TextData!A:A))</f>
-        <v>クイックヒール</v>
+        <v>ヒーリング</v>
       </c>
       <c r="D87">
         <v>1</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F87">
         <v>1033</v>
@@ -7673,11 +7729,11 @@
         <v>103</v>
       </c>
       <c r="B88">
-        <v>200310</v>
+        <v>14080</v>
       </c>
       <c r="C88" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B88,[1]TextData!A:A))</f>
-        <v>プルガシオン</v>
+        <v>クイックヒール</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -7686,7 +7742,7 @@
         <v>0</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -7697,17 +7753,17 @@
         <v>103</v>
       </c>
       <c r="B89">
-        <v>200320</v>
+        <v>200310</v>
       </c>
       <c r="C89" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B89,[1]TextData!A:A))</f>
-        <v>プリエステス</v>
+        <v>プルガシオン</v>
       </c>
       <c r="D89">
         <v>1</v>
       </c>
       <c r="E89">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -7721,17 +7777,17 @@
         <v>103</v>
       </c>
       <c r="B90">
-        <v>200330</v>
+        <v>200320</v>
       </c>
       <c r="C90" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B90,[1]TextData!A:A))</f>
-        <v>悪魔(パイモン)</v>
+        <v>プリエステス</v>
       </c>
       <c r="D90">
         <v>1</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F90">
         <v>0</v>
@@ -7742,20 +7798,20 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B91">
-        <v>2010</v>
+        <v>200330</v>
       </c>
       <c r="C91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B91,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>悪魔(パイモン)</v>
       </c>
       <c r="D91">
         <v>1</v>
       </c>
       <c r="E91">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -7769,17 +7825,17 @@
         <v>104</v>
       </c>
       <c r="B92">
-        <v>200410</v>
+        <v>2010</v>
       </c>
       <c r="C92" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B92,[1]TextData!A:A))</f>
-        <v>コウソクテンショウ</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D92">
         <v>1</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -7793,11 +7849,11 @@
         <v>104</v>
       </c>
       <c r="B93">
-        <v>200420</v>
+        <v>200410</v>
       </c>
       <c r="C93" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B93,[1]TextData!A:A))</f>
-        <v>アンチバフ</v>
+        <v>コウソクテンショウ</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -7806,7 +7862,7 @@
         <v>0</v>
       </c>
       <c r="F93">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -7817,11 +7873,11 @@
         <v>104</v>
       </c>
       <c r="B94">
-        <v>200430</v>
+        <v>200420</v>
       </c>
       <c r="C94" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B94,[1]TextData!A:A))</f>
-        <v>悪魔(アンドラス)</v>
+        <v>アンチバフ</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -7830,7 +7886,7 @@
         <v>0</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -7838,20 +7894,20 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B95">
-        <v>3010</v>
+        <v>200430</v>
       </c>
       <c r="C95" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B95,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>悪魔(アンドラス)</v>
       </c>
       <c r="D95">
         <v>1</v>
       </c>
       <c r="E95">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -7865,17 +7921,17 @@
         <v>105</v>
       </c>
       <c r="B96">
-        <v>3070</v>
+        <v>3010</v>
       </c>
       <c r="C96" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B96,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D96">
         <v>1</v>
       </c>
       <c r="E96">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -7889,17 +7945,17 @@
         <v>105</v>
       </c>
       <c r="B97">
-        <v>200510</v>
+        <v>3070</v>
       </c>
       <c r="C97" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B97,[1]TextData!A:A))</f>
-        <v>カウントダウン</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D97">
         <v>1</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -7913,17 +7969,17 @@
         <v>105</v>
       </c>
       <c r="B98">
-        <v>200520</v>
+        <v>200510</v>
       </c>
       <c r="C98" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B98,[1]TextData!A:A))</f>
-        <v>グラウンドゼロ</v>
+        <v>カウントダウン</v>
       </c>
       <c r="D98">
         <v>1</v>
       </c>
       <c r="E98">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -7937,17 +7993,17 @@
         <v>105</v>
       </c>
       <c r="B99">
-        <v>200530</v>
+        <v>200520</v>
       </c>
       <c r="C99" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B99,[1]TextData!A:A))</f>
-        <v>悪魔(ビフロンス)</v>
+        <v>グラウンドゼロ</v>
       </c>
       <c r="D99">
         <v>1</v>
       </c>
       <c r="E99">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F99">
         <v>0</v>
@@ -7961,11 +8017,11 @@
         <v>105</v>
       </c>
       <c r="B100">
-        <v>403070</v>
+        <v>200530</v>
       </c>
       <c r="C100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B100,[1]TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>悪魔(ビフロンス)</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -7982,20 +8038,20 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="B101">
-        <v>5010</v>
+        <v>403070</v>
       </c>
       <c r="C101" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B101,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="D101">
         <v>1</v>
       </c>
       <c r="E101">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -8009,17 +8065,17 @@
         <v>201</v>
       </c>
       <c r="B102">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="C102" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B102,[1]TextData!A:A))</f>
-        <v>ユーサネイジア</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="D102">
         <v>1</v>
       </c>
       <c r="E102">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -8033,20 +8089,20 @@
         <v>201</v>
       </c>
       <c r="B103">
-        <v>3070</v>
+        <v>5020</v>
       </c>
       <c r="C103" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B103,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>ユーサネイジア</v>
       </c>
       <c r="D103">
         <v>1</v>
       </c>
       <c r="E103">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F103">
-        <v>9110</v>
+        <v>0</v>
       </c>
       <c r="G103">
         <v>0</v>
@@ -8057,20 +8113,20 @@
         <v>201</v>
       </c>
       <c r="B104">
-        <v>403070</v>
+        <v>3070</v>
       </c>
       <c r="C104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B104,[1]TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D104">
         <v>1</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F104">
-        <v>0</v>
+        <v>9110</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -8081,11 +8137,11 @@
         <v>201</v>
       </c>
       <c r="B105">
-        <v>201010</v>
+        <v>403070</v>
       </c>
       <c r="C105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B105,[1]TextData!A:A))</f>
-        <v>カオスペイン</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -8094,7 +8150,7 @@
         <v>0</v>
       </c>
       <c r="F105">
-        <v>5080</v>
+        <v>0</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -8105,20 +8161,20 @@
         <v>201</v>
       </c>
       <c r="B106">
-        <v>201020</v>
+        <v>201010</v>
       </c>
       <c r="C106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B106,[1]TextData!A:A))</f>
-        <v>フォールンワン</v>
+        <v>カオスペイン</v>
       </c>
       <c r="D106">
         <v>1</v>
       </c>
       <c r="E106">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="F106">
-        <v>0</v>
+        <v>5080</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -8129,17 +8185,17 @@
         <v>201</v>
       </c>
       <c r="B107">
-        <v>201030</v>
+        <v>201020</v>
       </c>
       <c r="C107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B107,[1]TextData!A:A))</f>
-        <v>アンリマユ</v>
+        <v>フォールンワン</v>
       </c>
       <c r="D107">
         <v>1</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -8153,11 +8209,11 @@
         <v>201</v>
       </c>
       <c r="B108">
-        <v>405010</v>
+        <v>201030</v>
       </c>
       <c r="C108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B108,[1]TextData!A:A))</f>
-        <v>ダークプリズン+</v>
+        <v>アンリマユ</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -8177,11 +8233,11 @@
         <v>201</v>
       </c>
       <c r="B109">
-        <v>405020</v>
+        <v>405010</v>
       </c>
       <c r="C109" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B109,[1]TextData!A:A))</f>
-        <v>ユーサネイジア+</v>
+        <v>ダークプリズン+</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -8201,11 +8257,11 @@
         <v>201</v>
       </c>
       <c r="B110">
-        <v>12010</v>
+        <v>405020</v>
       </c>
       <c r="C110" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B110,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>ユーサネイジア+</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -8222,23 +8278,23 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="B111">
-        <v>1010</v>
+        <v>12010</v>
       </c>
       <c r="C111" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B111,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D111">
         <v>1</v>
       </c>
       <c r="E111">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F111">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -8249,17 +8305,17 @@
         <v>1001</v>
       </c>
       <c r="B112">
-        <v>1060</v>
+        <v>1010</v>
       </c>
       <c r="C112" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B112,[1]TextData!A:A))</f>
-        <v>イクスティンクション</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D112">
         <v>1</v>
       </c>
       <c r="E112">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F112">
         <v>5061</v>
@@ -8273,20 +8329,20 @@
         <v>1001</v>
       </c>
       <c r="B113">
-        <v>100110</v>
+        <v>1060</v>
       </c>
       <c r="C113" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B113,[1]TextData!A:A))</f>
-        <v>ソーイングアームド</v>
+        <v>イクスティンクション</v>
       </c>
       <c r="D113">
         <v>1</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F113">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -8297,17 +8353,17 @@
         <v>1001</v>
       </c>
       <c r="B114">
-        <v>100120</v>
+        <v>100110</v>
       </c>
       <c r="C114" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B114,[1]TextData!A:A))</f>
-        <v>エターナルロンド</v>
+        <v>ソーイングアームド</v>
       </c>
       <c r="D114">
         <v>1</v>
       </c>
       <c r="E114">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -8321,17 +8377,17 @@
         <v>1001</v>
       </c>
       <c r="B115">
-        <v>11060</v>
+        <v>100120</v>
       </c>
       <c r="C115" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B115,[1]TextData!A:A))</f>
-        <v>ライジングファイア</v>
+        <v>エターナルロンド</v>
       </c>
       <c r="D115">
         <v>1</v>
       </c>
       <c r="E115">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F115">
         <v>0</v>
@@ -8345,11 +8401,11 @@
         <v>1001</v>
       </c>
       <c r="B116">
-        <v>14010</v>
+        <v>11060</v>
       </c>
       <c r="C116" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B116,[1]TextData!A:A))</f>
-        <v>ディバインシールド</v>
+        <v>ライジングファイア</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -8369,11 +8425,11 @@
         <v>1001</v>
       </c>
       <c r="B117">
-        <v>12010</v>
+        <v>14010</v>
       </c>
       <c r="C117" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B117,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>ディバインシールド</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -8393,11 +8449,11 @@
         <v>1001</v>
       </c>
       <c r="B118">
-        <v>12060</v>
+        <v>12010</v>
       </c>
       <c r="C118" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B118,[1]TextData!A:A))</f>
-        <v>チェイスマジック</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -8414,23 +8470,23 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B119">
-        <v>2010</v>
+        <v>12060</v>
       </c>
       <c r="C119" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B119,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>チェイスマジック</v>
       </c>
       <c r="D119">
         <v>1</v>
       </c>
       <c r="E119">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F119">
-        <v>5060</v>
+        <v>0</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -8441,20 +8497,20 @@
         <v>1002</v>
       </c>
       <c r="B120">
-        <v>2070</v>
+        <v>2010</v>
       </c>
       <c r="C120" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B120,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D120">
         <v>1</v>
       </c>
       <c r="E120">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F120">
-        <v>0</v>
+        <v>5060</v>
       </c>
       <c r="G120">
         <v>0</v>
@@ -8465,17 +8521,17 @@
         <v>1002</v>
       </c>
       <c r="B121">
-        <v>100210</v>
+        <v>2070</v>
       </c>
       <c r="C121" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B121,[1]TextData!A:A))</f>
-        <v>アブソリュートパリィ</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D121">
         <v>1</v>
       </c>
       <c r="E121">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F121">
         <v>0</v>
@@ -8489,23 +8545,23 @@
         <v>1002</v>
       </c>
       <c r="B122">
-        <v>100220</v>
+        <v>100210</v>
       </c>
       <c r="C122" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B122,[1]TextData!A:A))</f>
-        <v>レヴェリー</v>
+        <v>アブソリュートパリィ</v>
       </c>
       <c r="D122">
         <v>1</v>
       </c>
       <c r="E122">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F122">
-        <v>14211</v>
+        <v>0</v>
       </c>
       <c r="G122">
-        <v>5060</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -8513,23 +8569,23 @@
         <v>1002</v>
       </c>
       <c r="B123">
-        <v>402070</v>
+        <v>100220</v>
       </c>
       <c r="C123" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B123,[1]TextData!A:A))</f>
-        <v>コンセントレイト+</v>
+        <v>レヴェリー</v>
       </c>
       <c r="D123">
         <v>1</v>
       </c>
       <c r="E123">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F123">
-        <v>0</v>
+        <v>14211</v>
       </c>
       <c r="G123">
-        <v>0</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -8537,11 +8593,11 @@
         <v>1002</v>
       </c>
       <c r="B124">
-        <v>12080</v>
+        <v>402070</v>
       </c>
       <c r="C124" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B124,[1]TextData!A:A))</f>
-        <v>ウィンドライズ</v>
+        <v>コンセントレイト+</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -8561,11 +8617,11 @@
         <v>1002</v>
       </c>
       <c r="B125">
-        <v>12040</v>
+        <v>12080</v>
       </c>
       <c r="C125" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B125,[1]TextData!A:A))</f>
-        <v>イヴェイドオール</v>
+        <v>ウィンドライズ</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -8585,11 +8641,11 @@
         <v>1002</v>
       </c>
       <c r="B126">
-        <v>12050</v>
+        <v>12040</v>
       </c>
       <c r="C126" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B126,[1]TextData!A:A))</f>
-        <v>クイックムーブ</v>
+        <v>イヴェイドオール</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -8609,11 +8665,11 @@
         <v>1002</v>
       </c>
       <c r="B127">
-        <v>12010</v>
+        <v>12050</v>
       </c>
       <c r="C127" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B127,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>クイックムーブ</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -8630,20 +8686,20 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B128">
-        <v>3010</v>
+        <v>12010</v>
       </c>
       <c r="C128" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B128,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D128">
         <v>1</v>
       </c>
       <c r="E128">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F128">
         <v>0</v>
@@ -8657,20 +8713,20 @@
         <v>1003</v>
       </c>
       <c r="B129">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="C129" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B129,[1]TextData!A:A))</f>
-        <v>カウンターオーラ</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D129">
         <v>1</v>
       </c>
       <c r="E129">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F129">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -8681,20 +8737,20 @@
         <v>1003</v>
       </c>
       <c r="B130">
-        <v>100310</v>
+        <v>3020</v>
       </c>
       <c r="C130" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B130,[1]TextData!A:A))</f>
-        <v>セイクリッドバリア</v>
+        <v>カウンターオーラ</v>
       </c>
       <c r="D130">
         <v>1</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F130">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G130">
         <v>0</v>
@@ -8705,20 +8761,20 @@
         <v>1003</v>
       </c>
       <c r="B131">
-        <v>100320</v>
+        <v>100310</v>
       </c>
       <c r="C131" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B131,[1]TextData!A:A))</f>
-        <v>リベンジニードル</v>
+        <v>セイクリッドバリア</v>
       </c>
       <c r="D131">
         <v>1</v>
       </c>
       <c r="E131">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F131">
-        <v>14214</v>
+        <v>0</v>
       </c>
       <c r="G131">
         <v>0</v>
@@ -8729,20 +8785,20 @@
         <v>1003</v>
       </c>
       <c r="B132">
-        <v>403020</v>
+        <v>100320</v>
       </c>
       <c r="C132" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B132,[1]TextData!A:A))</f>
-        <v>カウンターオーラ+</v>
+        <v>リベンジニードル</v>
       </c>
       <c r="D132">
         <v>1</v>
       </c>
       <c r="E132">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F132">
-        <v>0</v>
+        <v>14214</v>
       </c>
       <c r="G132">
         <v>0</v>
@@ -8753,11 +8809,11 @@
         <v>1003</v>
       </c>
       <c r="B133">
-        <v>403010</v>
+        <v>403020</v>
       </c>
       <c r="C133" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B133,[1]TextData!A:A))</f>
-        <v>アイスブレイド+</v>
+        <v>カウンターオーラ+</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -8777,11 +8833,11 @@
         <v>1003</v>
       </c>
       <c r="B134">
-        <v>13020</v>
+        <v>403010</v>
       </c>
       <c r="C134" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B134,[1]TextData!A:A))</f>
-        <v>クイックバリア</v>
+        <v>アイスブレイド+</v>
       </c>
       <c r="D134">
         <v>1</v>
@@ -8801,11 +8857,11 @@
         <v>1003</v>
       </c>
       <c r="B135">
-        <v>13080</v>
+        <v>13020</v>
       </c>
       <c r="C135" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B135,[1]TextData!A:A))</f>
-        <v>ライフスティール</v>
+        <v>クイックバリア</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -8825,11 +8881,11 @@
         <v>1003</v>
       </c>
       <c r="B136">
-        <v>14050</v>
+        <v>13080</v>
       </c>
       <c r="C136" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B136,[1]TextData!A:A))</f>
-        <v>ホープフルアイリス</v>
+        <v>ライフスティール</v>
       </c>
       <c r="D136">
         <v>1</v>
@@ -8846,20 +8902,20 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B137">
-        <v>4010</v>
+        <v>14050</v>
       </c>
       <c r="C137" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B137,[1]TextData!A:A))</f>
-        <v>セイントレーザー</v>
+        <v>ホープフルアイリス</v>
       </c>
       <c r="D137">
         <v>1</v>
       </c>
       <c r="E137">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -8873,20 +8929,20 @@
         <v>1004</v>
       </c>
       <c r="B138">
-        <v>4030</v>
+        <v>4010</v>
       </c>
       <c r="C138" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B138,[1]TextData!A:A))</f>
-        <v>ヒーリング</v>
+        <v>セイントレーザー</v>
       </c>
       <c r="D138">
         <v>1</v>
       </c>
       <c r="E138">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F138">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="G138">
         <v>0</v>
@@ -8897,20 +8953,20 @@
         <v>1004</v>
       </c>
       <c r="B139">
-        <v>100410</v>
+        <v>4030</v>
       </c>
       <c r="C139" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B139,[1]TextData!A:A))</f>
-        <v>アバンデンス</v>
+        <v>ヒーリング</v>
       </c>
       <c r="D139">
         <v>1</v>
       </c>
       <c r="E139">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F139">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="G139">
         <v>0</v>
@@ -8921,17 +8977,17 @@
         <v>1004</v>
       </c>
       <c r="B140">
-        <v>100420</v>
+        <v>100410</v>
       </c>
       <c r="C140" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B140,[1]TextData!A:A))</f>
-        <v>ハーヴェスト</v>
+        <v>アバンデンス</v>
       </c>
       <c r="D140">
         <v>1</v>
       </c>
       <c r="E140">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F140">
         <v>0</v>
@@ -8945,17 +9001,17 @@
         <v>1004</v>
       </c>
       <c r="B141">
-        <v>404030</v>
+        <v>100420</v>
       </c>
       <c r="C141" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B141,[1]TextData!A:A))</f>
-        <v>ヒーリング+</v>
+        <v>ハーヴェスト</v>
       </c>
       <c r="D141">
         <v>1</v>
       </c>
       <c r="E141">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F141">
         <v>0</v>
@@ -8969,11 +9025,11 @@
         <v>1004</v>
       </c>
       <c r="B142">
-        <v>14080</v>
+        <v>404030</v>
       </c>
       <c r="C142" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B142,[1]TextData!A:A))</f>
-        <v>クイックヒール</v>
+        <v>ヒーリング+</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -8993,11 +9049,11 @@
         <v>1004</v>
       </c>
       <c r="B143">
-        <v>14010</v>
+        <v>14080</v>
       </c>
       <c r="C143" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B143,[1]TextData!A:A))</f>
-        <v>ディバインシールド</v>
+        <v>クイックヒール</v>
       </c>
       <c r="D143">
         <v>1</v>
@@ -9006,7 +9062,7 @@
         <v>0</v>
       </c>
       <c r="F143">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G143">
         <v>0</v>
@@ -9017,11 +9073,11 @@
         <v>1004</v>
       </c>
       <c r="B144">
-        <v>14040</v>
+        <v>14010</v>
       </c>
       <c r="C144" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B144,[1]TextData!A:A))</f>
-        <v>リジェネレーション</v>
+        <v>ディバインシールド</v>
       </c>
       <c r="D144">
         <v>1</v>
@@ -9030,7 +9086,7 @@
         <v>0</v>
       </c>
       <c r="F144">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G144">
         <v>0</v>
@@ -9041,11 +9097,11 @@
         <v>1004</v>
       </c>
       <c r="B145">
-        <v>14090</v>
+        <v>14040</v>
       </c>
       <c r="C145" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B145,[1]TextData!A:A))</f>
-        <v>リレイズ</v>
+        <v>リジェネレーション</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -9062,20 +9118,20 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B146">
-        <v>5010</v>
+        <v>14090</v>
       </c>
       <c r="C146" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B146,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>リレイズ</v>
       </c>
       <c r="D146">
         <v>1</v>
       </c>
       <c r="E146">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F146">
         <v>0</v>
@@ -9089,20 +9145,20 @@
         <v>1005</v>
       </c>
       <c r="B147">
-        <v>5070</v>
+        <v>5010</v>
       </c>
       <c r="C147" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B147,[1]TextData!A:A))</f>
-        <v>シェイディークラウド</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="D147">
         <v>1</v>
       </c>
       <c r="E147">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F147">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G147">
         <v>0</v>
@@ -9113,20 +9169,20 @@
         <v>1005</v>
       </c>
       <c r="B148">
-        <v>100510</v>
+        <v>5070</v>
       </c>
       <c r="C148" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B148,[1]TextData!A:A))</f>
-        <v>カースドブレイク</v>
+        <v>シェイディークラウド</v>
       </c>
       <c r="D148">
         <v>1</v>
       </c>
       <c r="E148">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F148">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -9137,17 +9193,17 @@
         <v>1005</v>
       </c>
       <c r="B149">
-        <v>100520</v>
+        <v>100510</v>
       </c>
       <c r="C149" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B149,[1]TextData!A:A))</f>
-        <v>ムーンライトレイ</v>
+        <v>カースドブレイク</v>
       </c>
       <c r="D149">
         <v>1</v>
       </c>
       <c r="E149">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F149">
         <v>0</v>
@@ -9161,17 +9217,17 @@
         <v>1005</v>
       </c>
       <c r="B150">
-        <v>15090</v>
+        <v>100520</v>
       </c>
       <c r="C150" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B150,[1]TextData!A:A))</f>
-        <v>クイックカース</v>
+        <v>ムーンライトレイ</v>
       </c>
       <c r="D150">
         <v>1</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F150">
         <v>0</v>
@@ -9185,11 +9241,11 @@
         <v>1005</v>
       </c>
       <c r="B151">
-        <v>405070</v>
+        <v>15090</v>
       </c>
       <c r="C151" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B151,[1]TextData!A:A))</f>
-        <v>シェイディークラウド+</v>
+        <v>クイックカース</v>
       </c>
       <c r="D151">
         <v>1</v>
@@ -9209,11 +9265,11 @@
         <v>1005</v>
       </c>
       <c r="B152">
-        <v>15080</v>
+        <v>405070</v>
       </c>
       <c r="C152" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B152,[1]TextData!A:A))</f>
-        <v>ヒールハント</v>
+        <v>シェイディークラウド+</v>
       </c>
       <c r="D152">
         <v>1</v>
@@ -9233,11 +9289,11 @@
         <v>1005</v>
       </c>
       <c r="B153">
-        <v>405010</v>
+        <v>15080</v>
       </c>
       <c r="C153" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B153,[1]TextData!A:A))</f>
-        <v>ダークプリズン+</v>
+        <v>ヒールハント</v>
       </c>
       <c r="D153">
         <v>1</v>
@@ -9257,11 +9313,11 @@
         <v>1005</v>
       </c>
       <c r="B154">
-        <v>415090</v>
+        <v>405010</v>
       </c>
       <c r="C154" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B154,[1]TextData!A:A))</f>
-        <v>クイックカース+</v>
+        <v>ダークプリズン+</v>
       </c>
       <c r="D154">
         <v>1</v>
@@ -9278,20 +9334,20 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B155">
-        <v>1010</v>
+        <v>415090</v>
       </c>
       <c r="C155" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B155,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>クイックカース+</v>
       </c>
       <c r="D155">
         <v>1</v>
       </c>
       <c r="E155">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F155">
         <v>0</v>
@@ -9305,23 +9361,23 @@
         <v>1006</v>
       </c>
       <c r="B156">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="C156" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B156,[1]TextData!A:A))</f>
-        <v>ヒートスタンプ</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D156">
         <v>1</v>
       </c>
       <c r="E156">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F156">
-        <v>9120</v>
+        <v>0</v>
       </c>
       <c r="G156">
-        <v>1023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -9329,23 +9385,23 @@
         <v>1006</v>
       </c>
       <c r="B157">
-        <v>1070</v>
+        <v>1030</v>
       </c>
       <c r="C157" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B157,[1]TextData!A:A))</f>
-        <v>バーニングソウル</v>
+        <v>ヒートスタンプ</v>
       </c>
       <c r="D157">
         <v>1</v>
       </c>
       <c r="E157">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F157">
-        <v>6322</v>
+        <v>9120</v>
       </c>
       <c r="G157">
-        <v>0</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -9353,20 +9409,20 @@
         <v>1006</v>
       </c>
       <c r="B158">
-        <v>100610</v>
+        <v>1070</v>
       </c>
       <c r="C158" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B158,[1]TextData!A:A))</f>
-        <v>サンフレイム</v>
+        <v>バーニングソウル</v>
       </c>
       <c r="D158">
         <v>1</v>
       </c>
       <c r="E158">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F158">
-        <v>0</v>
+        <v>6322</v>
       </c>
       <c r="G158">
         <v>0</v>
@@ -9377,17 +9433,17 @@
         <v>1006</v>
       </c>
       <c r="B159">
-        <v>100620</v>
+        <v>100610</v>
       </c>
       <c r="C159" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B159,[1]TextData!A:A))</f>
-        <v>フレイムタン</v>
+        <v>サンフレイム</v>
       </c>
       <c r="D159">
         <v>1</v>
       </c>
       <c r="E159">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -9401,20 +9457,20 @@
         <v>1006</v>
       </c>
       <c r="B160">
-        <v>11040</v>
+        <v>100620</v>
       </c>
       <c r="C160" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B160,[1]TextData!A:A))</f>
-        <v>アクティブギフト</v>
+        <v>フレイムタン</v>
       </c>
       <c r="D160">
         <v>1</v>
       </c>
       <c r="E160">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F160">
-        <v>5042</v>
+        <v>0</v>
       </c>
       <c r="G160">
         <v>0</v>
@@ -9425,11 +9481,11 @@
         <v>1006</v>
       </c>
       <c r="B161">
-        <v>401030</v>
+        <v>11040</v>
       </c>
       <c r="C161" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B161,[1]TextData!A:A))</f>
-        <v>ヒートスタンプ+</v>
+        <v>アクティブギフト</v>
       </c>
       <c r="D161">
         <v>1</v>
@@ -9438,7 +9494,7 @@
         <v>0</v>
       </c>
       <c r="F161">
-        <v>0</v>
+        <v>5042</v>
       </c>
       <c r="G161">
         <v>0</v>
@@ -9449,11 +9505,11 @@
         <v>1006</v>
       </c>
       <c r="B162">
-        <v>411040</v>
+        <v>401030</v>
       </c>
       <c r="C162" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B162,[1]TextData!A:A))</f>
-        <v>アクティブギフト+</v>
+        <v>ヒートスタンプ+</v>
       </c>
       <c r="D162">
         <v>1</v>
@@ -9473,11 +9529,11 @@
         <v>1006</v>
       </c>
       <c r="B163">
-        <v>13040</v>
+        <v>411040</v>
       </c>
       <c r="C163" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B163,[1]TextData!A:A))</f>
-        <v>セルフシールド</v>
+        <v>アクティブギフト+</v>
       </c>
       <c r="D163">
         <v>1</v>
@@ -9494,20 +9550,20 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B164">
-        <v>2010</v>
+        <v>13040</v>
       </c>
       <c r="C164" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B164,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>セルフシールド</v>
       </c>
       <c r="D164">
         <v>1</v>
       </c>
       <c r="E164">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F164">
         <v>0</v>
@@ -9521,20 +9577,20 @@
         <v>1007</v>
       </c>
       <c r="B165">
-        <v>2040</v>
+        <v>2010</v>
       </c>
       <c r="C165" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B165,[1]TextData!A:A))</f>
-        <v>トラストチェイン</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D165">
         <v>1</v>
       </c>
       <c r="E165">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F165">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G165">
         <v>0</v>
@@ -9545,20 +9601,20 @@
         <v>1007</v>
       </c>
       <c r="B166">
-        <v>100710</v>
+        <v>2040</v>
       </c>
       <c r="C166" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B166,[1]TextData!A:A))</f>
-        <v>ライズザフラッグ</v>
+        <v>トラストチェイン</v>
       </c>
       <c r="D166">
         <v>1</v>
       </c>
       <c r="E166">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F166">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G166">
         <v>0</v>
@@ -9569,17 +9625,17 @@
         <v>1007</v>
       </c>
       <c r="B167">
-        <v>100720</v>
+        <v>100710</v>
       </c>
       <c r="C167" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B167,[1]TextData!A:A))</f>
-        <v>オーバーリミット</v>
+        <v>ライズザフラッグ</v>
       </c>
       <c r="D167">
         <v>1</v>
       </c>
       <c r="E167">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F167">
         <v>0</v>
@@ -9593,20 +9649,20 @@
         <v>1007</v>
       </c>
       <c r="B168">
-        <v>12090</v>
+        <v>100720</v>
       </c>
       <c r="C168" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B168,[1]TextData!A:A))</f>
-        <v>アウトオブオーダー</v>
+        <v>オーバーリミット</v>
       </c>
       <c r="D168">
         <v>1</v>
       </c>
       <c r="E168">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F168">
-        <v>5042</v>
+        <v>0</v>
       </c>
       <c r="G168">
         <v>0</v>
@@ -9617,11 +9673,11 @@
         <v>1007</v>
       </c>
       <c r="B169">
-        <v>412090</v>
+        <v>12090</v>
       </c>
       <c r="C169" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B169,[1]TextData!A:A))</f>
-        <v>アウトオブオーダー+</v>
+        <v>アウトオブオーダー</v>
       </c>
       <c r="D169">
         <v>1</v>
@@ -9630,7 +9686,7 @@
         <v>0</v>
       </c>
       <c r="F169">
-        <v>0</v>
+        <v>5042</v>
       </c>
       <c r="G169">
         <v>0</v>
@@ -9641,11 +9697,11 @@
         <v>1007</v>
       </c>
       <c r="B170">
-        <v>12050</v>
+        <v>412090</v>
       </c>
       <c r="C170" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B170,[1]TextData!A:A))</f>
-        <v>クイックムーブ</v>
+        <v>アウトオブオーダー+</v>
       </c>
       <c r="D170">
         <v>1</v>
@@ -9665,11 +9721,11 @@
         <v>1007</v>
       </c>
       <c r="B171">
-        <v>12070</v>
+        <v>12050</v>
       </c>
       <c r="C171" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B171,[1]TextData!A:A))</f>
-        <v>ソーサリーコネクト</v>
+        <v>クイックムーブ</v>
       </c>
       <c r="D171">
         <v>1</v>
@@ -9689,11 +9745,11 @@
         <v>1007</v>
       </c>
       <c r="B172">
-        <v>14030</v>
+        <v>12070</v>
       </c>
       <c r="C172" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B172,[1]TextData!A:A))</f>
-        <v>エイミングスコープ</v>
+        <v>ソーサリーコネクト</v>
       </c>
       <c r="D172">
         <v>1</v>
@@ -9710,20 +9766,20 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B173">
-        <v>3010</v>
+        <v>14030</v>
       </c>
       <c r="C173" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B173,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>エイミングスコープ</v>
       </c>
       <c r="D173">
         <v>1</v>
       </c>
       <c r="E173">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F173">
         <v>0</v>
@@ -9737,17 +9793,17 @@
         <v>1008</v>
       </c>
       <c r="B174">
-        <v>3070</v>
+        <v>3010</v>
       </c>
       <c r="C174" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B174,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D174">
         <v>1</v>
       </c>
       <c r="E174">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F174">
         <v>0</v>
@@ -9761,17 +9817,17 @@
         <v>1008</v>
       </c>
       <c r="B175">
-        <v>100810</v>
+        <v>3070</v>
       </c>
       <c r="C175" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B175,[1]TextData!A:A))</f>
-        <v>テンパランス</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D175">
         <v>1</v>
       </c>
       <c r="E175">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -9785,17 +9841,17 @@
         <v>1008</v>
       </c>
       <c r="B176">
-        <v>100820</v>
+        <v>100810</v>
       </c>
       <c r="C176" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B176,[1]TextData!A:A))</f>
-        <v>シエルクルセイダー</v>
+        <v>テンパランス</v>
       </c>
       <c r="D176">
         <v>1</v>
       </c>
       <c r="E176">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F176">
         <v>0</v>
@@ -9809,20 +9865,20 @@
         <v>1008</v>
       </c>
       <c r="B177">
-        <v>13060</v>
+        <v>100820</v>
       </c>
       <c r="C177" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B177,[1]TextData!A:A))</f>
-        <v>サプライカバー</v>
+        <v>シエルクルセイダー</v>
       </c>
       <c r="D177">
         <v>1</v>
       </c>
       <c r="E177">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F177">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G177">
         <v>0</v>
@@ -9833,11 +9889,11 @@
         <v>1008</v>
       </c>
       <c r="B178">
-        <v>403070</v>
+        <v>13060</v>
       </c>
       <c r="C178" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B178,[1]TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>サプライカバー</v>
       </c>
       <c r="D178">
         <v>1</v>
@@ -9846,7 +9902,7 @@
         <v>0</v>
       </c>
       <c r="F178">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G178">
         <v>0</v>
@@ -9857,11 +9913,11 @@
         <v>1008</v>
       </c>
       <c r="B179">
-        <v>13010</v>
+        <v>403070</v>
       </c>
       <c r="C179" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B179,[1]TextData!A:A))</f>
-        <v>アーマーコード</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="D179">
         <v>1</v>
@@ -9881,11 +9937,11 @@
         <v>1008</v>
       </c>
       <c r="B180">
-        <v>13020</v>
+        <v>13010</v>
       </c>
       <c r="C180" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B180,[1]TextData!A:A))</f>
-        <v>クイックバリア</v>
+        <v>アーマーコード</v>
       </c>
       <c r="D180">
         <v>1</v>
@@ -9905,11 +9961,11 @@
         <v>1008</v>
       </c>
       <c r="B181">
-        <v>13040</v>
+        <v>13020</v>
       </c>
       <c r="C181" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B181,[1]TextData!A:A))</f>
-        <v>セルフシールド</v>
+        <v>クイックバリア</v>
       </c>
       <c r="D181">
         <v>1</v>
@@ -9926,20 +9982,20 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B182">
-        <v>1010</v>
+        <v>13040</v>
       </c>
       <c r="C182" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B182,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>セルフシールド</v>
       </c>
       <c r="D182">
         <v>1</v>
       </c>
       <c r="E182">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F182">
         <v>0</v>
@@ -9953,20 +10009,20 @@
         <v>1009</v>
       </c>
       <c r="B183">
-        <v>1050</v>
+        <v>1010</v>
       </c>
       <c r="C183" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B183,[1]TextData!A:A))</f>
-        <v>フレイムレイン</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D183">
         <v>1</v>
       </c>
       <c r="E183">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F183">
-        <v>1151</v>
+        <v>0</v>
       </c>
       <c r="G183">
         <v>0</v>
@@ -9977,20 +10033,20 @@
         <v>1009</v>
       </c>
       <c r="B184">
-        <v>100910</v>
+        <v>1050</v>
       </c>
       <c r="C184" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B184,[1]TextData!A:A))</f>
-        <v>バーニングカウンター</v>
+        <v>フレイムレイン</v>
       </c>
       <c r="D184">
         <v>1</v>
       </c>
       <c r="E184">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F184">
-        <v>0</v>
+        <v>1151</v>
       </c>
       <c r="G184">
         <v>0</v>
@@ -10001,17 +10057,17 @@
         <v>1009</v>
       </c>
       <c r="B185">
-        <v>100920</v>
+        <v>100910</v>
       </c>
       <c r="C185" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B185,[1]TextData!A:A))</f>
-        <v>プロミネンス</v>
+        <v>バーニングカウンター</v>
       </c>
       <c r="D185">
         <v>1</v>
       </c>
       <c r="E185">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F185">
         <v>0</v>
@@ -10025,17 +10081,17 @@
         <v>1009</v>
       </c>
       <c r="B186">
-        <v>11070</v>
+        <v>100920</v>
       </c>
       <c r="C186" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B186,[1]TextData!A:A))</f>
-        <v>ルージュバック</v>
+        <v>プロミネンス</v>
       </c>
       <c r="D186">
         <v>1</v>
       </c>
       <c r="E186">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F186">
         <v>0</v>
@@ -10049,11 +10105,11 @@
         <v>1009</v>
       </c>
       <c r="B187">
-        <v>401050</v>
+        <v>11070</v>
       </c>
       <c r="C187" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B187,[1]TextData!A:A))</f>
-        <v>フレイムレイン+</v>
+        <v>ルージュバック</v>
       </c>
       <c r="D187">
         <v>1</v>
@@ -10073,11 +10129,11 @@
         <v>1009</v>
       </c>
       <c r="B188">
-        <v>11030</v>
+        <v>401050</v>
       </c>
       <c r="C188" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B188,[1]TextData!A:A))</f>
-        <v>アサルトシフト</v>
+        <v>フレイムレイン+</v>
       </c>
       <c r="D188">
         <v>1</v>
@@ -10097,11 +10153,11 @@
         <v>1009</v>
       </c>
       <c r="B189">
-        <v>11020</v>
+        <v>11030</v>
       </c>
       <c r="C189" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B189,[1]TextData!A:A))</f>
-        <v>プリディカメント</v>
+        <v>アサルトシフト</v>
       </c>
       <c r="D189">
         <v>1</v>
@@ -10121,11 +10177,11 @@
         <v>1009</v>
       </c>
       <c r="B190">
-        <v>15040</v>
+        <v>11020</v>
       </c>
       <c r="C190" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B190,[1]TextData!A:A))</f>
-        <v>スカルグラッジ</v>
+        <v>プリディカメント</v>
       </c>
       <c r="D190">
         <v>1</v>
@@ -10142,20 +10198,20 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B191">
-        <v>2010</v>
+        <v>15040</v>
       </c>
       <c r="C191" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B191,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>スカルグラッジ</v>
       </c>
       <c r="D191">
         <v>1</v>
       </c>
       <c r="E191">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F191">
         <v>0</v>
@@ -10169,20 +10225,20 @@
         <v>1010</v>
       </c>
       <c r="B192">
-        <v>2030</v>
+        <v>2010</v>
       </c>
       <c r="C192" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B192,[1]TextData!A:A))</f>
-        <v>ショックインパルス</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D192">
         <v>1</v>
       </c>
       <c r="E192">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F192">
-        <v>14215</v>
+        <v>0</v>
       </c>
       <c r="G192">
         <v>0</v>
@@ -10193,20 +10249,20 @@
         <v>1010</v>
       </c>
       <c r="B193">
-        <v>101010</v>
+        <v>2030</v>
       </c>
       <c r="C193" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B193,[1]TextData!A:A))</f>
-        <v>エウロス</v>
+        <v>ショックインパルス</v>
       </c>
       <c r="D193">
         <v>1</v>
       </c>
       <c r="E193">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F193">
-        <v>0</v>
+        <v>14215</v>
       </c>
       <c r="G193">
         <v>0</v>
@@ -10217,17 +10273,17 @@
         <v>1010</v>
       </c>
       <c r="B194">
-        <v>101020</v>
+        <v>101010</v>
       </c>
       <c r="C194" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B194,[1]TextData!A:A))</f>
-        <v>ボレアス</v>
+        <v>エウロス</v>
       </c>
       <c r="D194">
         <v>1</v>
       </c>
       <c r="E194">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F194">
         <v>0</v>
@@ -10241,17 +10297,17 @@
         <v>1010</v>
       </c>
       <c r="B195">
-        <v>12010</v>
+        <v>101020</v>
       </c>
       <c r="C195" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B195,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>ボレアス</v>
       </c>
       <c r="D195">
         <v>1</v>
       </c>
       <c r="E195">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F195">
         <v>0</v>
@@ -10265,11 +10321,11 @@
         <v>1010</v>
       </c>
       <c r="B196">
-        <v>402030</v>
+        <v>12010</v>
       </c>
       <c r="C196" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B196,[1]TextData!A:A))</f>
-        <v>ショックインパルス+</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D196">
         <v>1</v>
@@ -10289,11 +10345,11 @@
         <v>1010</v>
       </c>
       <c r="B197">
-        <v>12020</v>
+        <v>402030</v>
       </c>
       <c r="C197" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B197,[1]TextData!A:A))</f>
-        <v>ヘブンリーラック</v>
+        <v>ショックインパルス+</v>
       </c>
       <c r="D197">
         <v>1</v>
@@ -10313,11 +10369,11 @@
         <v>1010</v>
       </c>
       <c r="B198">
-        <v>12030</v>
+        <v>12020</v>
       </c>
       <c r="C198" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B198,[1]TextData!A:A))</f>
-        <v>スウィフトカレント</v>
+        <v>ヘブンリーラック</v>
       </c>
       <c r="D198">
         <v>1</v>
@@ -10337,11 +10393,11 @@
         <v>1010</v>
       </c>
       <c r="B199">
-        <v>15070</v>
+        <v>12030</v>
       </c>
       <c r="C199" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B199,[1]TextData!A:A))</f>
-        <v>ジャックポッド</v>
+        <v>スウィフトカレント</v>
       </c>
       <c r="D199">
         <v>1</v>
@@ -10358,20 +10414,20 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B200">
-        <v>3010</v>
+        <v>15070</v>
       </c>
       <c r="C200" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B200,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>ジャックポッド</v>
       </c>
       <c r="D200">
         <v>1</v>
       </c>
       <c r="E200">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F200">
         <v>0</v>
@@ -10385,17 +10441,17 @@
         <v>1011</v>
       </c>
       <c r="B201">
-        <v>3050</v>
+        <v>3010</v>
       </c>
       <c r="C201" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B201,[1]TextData!A:A))</f>
-        <v>ディープフリーズ</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D201">
         <v>1</v>
       </c>
       <c r="E201">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F201">
         <v>0</v>
@@ -10409,17 +10465,17 @@
         <v>1011</v>
       </c>
       <c r="B202">
-        <v>101110</v>
+        <v>3050</v>
       </c>
       <c r="C202" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B202,[1]TextData!A:A))</f>
-        <v>アバランシュ</v>
+        <v>ディープフリーズ</v>
       </c>
       <c r="D202">
         <v>1</v>
       </c>
       <c r="E202">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F202">
         <v>0</v>
@@ -10433,17 +10489,17 @@
         <v>1011</v>
       </c>
       <c r="B203">
-        <v>101120</v>
+        <v>101110</v>
       </c>
       <c r="C203" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B203,[1]TextData!A:A))</f>
-        <v>ブリザードコフィン</v>
+        <v>アバランシュ</v>
       </c>
       <c r="D203">
         <v>1</v>
       </c>
       <c r="E203">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F203">
         <v>0</v>
@@ -10457,17 +10513,17 @@
         <v>1011</v>
       </c>
       <c r="B204">
-        <v>13090</v>
+        <v>101120</v>
       </c>
       <c r="C204" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B204,[1]TextData!A:A))</f>
-        <v>アイスセイバー</v>
+        <v>ブリザードコフィン</v>
       </c>
       <c r="D204">
         <v>1</v>
       </c>
       <c r="E204">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F204">
         <v>0</v>
@@ -10481,11 +10537,11 @@
         <v>1011</v>
       </c>
       <c r="B205">
-        <v>403050</v>
+        <v>13090</v>
       </c>
       <c r="C205" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B205,[1]TextData!A:A))</f>
-        <v>ディープフリーズ+</v>
+        <v>アイスセイバー</v>
       </c>
       <c r="D205">
         <v>1</v>
@@ -10505,11 +10561,11 @@
         <v>1011</v>
       </c>
       <c r="B206">
-        <v>13050</v>
+        <v>403050</v>
       </c>
       <c r="C206" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B206,[1]TextData!A:A))</f>
-        <v>パッシブジャミング</v>
+        <v>ディープフリーズ+</v>
       </c>
       <c r="D206">
         <v>1</v>
@@ -10529,11 +10585,11 @@
         <v>1011</v>
       </c>
       <c r="B207">
-        <v>13070</v>
+        <v>13050</v>
       </c>
       <c r="C207" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B207,[1]TextData!A:A))</f>
-        <v>アシッドラッシュ</v>
+        <v>パッシブジャミング</v>
       </c>
       <c r="D207">
         <v>1</v>
@@ -10553,22 +10609,46 @@
         <v>1011</v>
       </c>
       <c r="B208">
-        <v>14070</v>
+        <v>13070</v>
       </c>
       <c r="C208" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B208,[1]TextData!A:A))</f>
+        <v>アシッドラッシュ</v>
+      </c>
+      <c r="D208">
+        <v>1</v>
+      </c>
+      <c r="E208">
+        <v>0</v>
+      </c>
+      <c r="F208">
+        <v>0</v>
+      </c>
+      <c r="G208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7">
+      <c r="A209">
+        <v>1011</v>
+      </c>
+      <c r="B209">
+        <v>14070</v>
+      </c>
+      <c r="C209" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B209,[1]TextData!A:A))</f>
         <v>ホーミングクルセイド</v>
       </c>
-      <c r="D208">
-        <v>1</v>
-      </c>
-      <c r="E208">
-        <v>0</v>
-      </c>
-      <c r="F208">
-        <v>0</v>
-      </c>
-      <c r="G208">
+      <c r="D209">
+        <v>1</v>
+      </c>
+      <c r="E209">
+        <v>0</v>
+      </c>
+      <c r="F209">
+        <v>0</v>
+      </c>
+      <c r="G209">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -395,9 +395,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -416,15 +416,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -438,11 +437,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -461,38 +468,31 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -508,22 +508,36 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -537,25 +551,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -568,7 +568,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,13 +580,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -598,31 +706,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -634,13 +718,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -652,103 +748,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -759,21 +759,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -794,15 +779,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -815,8 +791,56 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -835,30 +859,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -867,16 +867,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -885,127 +885,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1555,1825 +1555,1985 @@
         </row>
         <row r="58">
           <cell r="A58">
-            <v>11020</v>
+            <v>11011</v>
           </cell>
           <cell r="B58" t="str">
-            <v>プリディカメント</v>
+            <v>ウルフソウル+</v>
           </cell>
         </row>
         <row r="59">
           <cell r="A59">
-            <v>11030</v>
+            <v>11020</v>
           </cell>
           <cell r="B59" t="str">
-            <v>アサルトシフト</v>
+            <v>プリディカメント</v>
           </cell>
         </row>
         <row r="60">
           <cell r="A60">
-            <v>11040</v>
+            <v>11021</v>
           </cell>
           <cell r="B60" t="str">
-            <v>アクティブギフト</v>
+            <v>プリディカメント+</v>
           </cell>
         </row>
         <row r="61">
           <cell r="A61">
-            <v>11050</v>
+            <v>11030</v>
           </cell>
           <cell r="B61" t="str">
-            <v>イグナイテッド</v>
+            <v>アサルトシフト</v>
           </cell>
         </row>
         <row r="62">
           <cell r="A62">
-            <v>11060</v>
+            <v>11031</v>
           </cell>
           <cell r="B62" t="str">
-            <v>ライジングファイア</v>
+            <v>アサルトシフト+</v>
           </cell>
         </row>
         <row r="63">
           <cell r="A63">
-            <v>11070</v>
+            <v>11040</v>
           </cell>
           <cell r="B63" t="str">
-            <v>ルージュバック</v>
+            <v>アクティブギフト</v>
           </cell>
         </row>
         <row r="64">
           <cell r="A64">
-            <v>11080</v>
+            <v>11050</v>
           </cell>
           <cell r="B64" t="str">
-            <v>パワーエール</v>
+            <v>イグナイテッド</v>
           </cell>
         </row>
         <row r="65">
           <cell r="A65">
-            <v>11090</v>
+            <v>11060</v>
           </cell>
           <cell r="B65" t="str">
-            <v>スレイプニル</v>
+            <v>ライジングファイア</v>
           </cell>
         </row>
         <row r="66">
           <cell r="A66">
-            <v>11100</v>
+            <v>11070</v>
           </cell>
           <cell r="B66" t="str">
-            <v>レストア</v>
+            <v>ルージュバック</v>
           </cell>
         </row>
         <row r="67">
           <cell r="A67">
-            <v>12010</v>
+            <v>11080</v>
           </cell>
           <cell r="B67" t="str">
-            <v>コンセントレイト</v>
+            <v>パワーエール</v>
           </cell>
         </row>
         <row r="68">
           <cell r="A68">
-            <v>12020</v>
+            <v>11090</v>
           </cell>
           <cell r="B68" t="str">
-            <v>ヘブンリーラック</v>
+            <v>スレイプニル</v>
           </cell>
         </row>
         <row r="69">
           <cell r="A69">
-            <v>12030</v>
+            <v>11100</v>
           </cell>
           <cell r="B69" t="str">
-            <v>スウィフトカレント</v>
+            <v>レストア</v>
           </cell>
         </row>
         <row r="70">
           <cell r="A70">
-            <v>12040</v>
+            <v>11101</v>
           </cell>
           <cell r="B70" t="str">
-            <v>イヴェイドオール</v>
+            <v>レストア+</v>
           </cell>
         </row>
         <row r="71">
           <cell r="A71">
-            <v>12050</v>
+            <v>12010</v>
           </cell>
           <cell r="B71" t="str">
-            <v>クイックムーブ</v>
+            <v>コンセントレイト</v>
           </cell>
         </row>
         <row r="72">
           <cell r="A72">
-            <v>12060</v>
+            <v>12020</v>
           </cell>
           <cell r="B72" t="str">
-            <v>チェイスマジック</v>
+            <v>ヘブンリーラック</v>
           </cell>
         </row>
         <row r="73">
           <cell r="A73">
-            <v>12070</v>
+            <v>12021</v>
           </cell>
           <cell r="B73" t="str">
-            <v>ソーサリーコネクト</v>
+            <v>ヘブンリーラック+</v>
           </cell>
         </row>
         <row r="74">
           <cell r="A74">
-            <v>12080</v>
+            <v>12030</v>
           </cell>
           <cell r="B74" t="str">
-            <v>ウィンドライズ</v>
+            <v>スウィフトカレント</v>
           </cell>
         </row>
         <row r="75">
           <cell r="A75">
-            <v>12090</v>
+            <v>12031</v>
           </cell>
           <cell r="B75" t="str">
-            <v>アウトオブオーダー</v>
+            <v>スウィフトカレント+</v>
           </cell>
         </row>
         <row r="76">
           <cell r="A76">
-            <v>12100</v>
+            <v>12040</v>
           </cell>
           <cell r="B76" t="str">
-            <v>ワンスパニッシュ</v>
+            <v>イヴェイドオール</v>
           </cell>
         </row>
         <row r="77">
           <cell r="A77">
-            <v>13010</v>
+            <v>12041</v>
           </cell>
           <cell r="B77" t="str">
-            <v>アーマーコード</v>
+            <v>イヴェイドオール+</v>
           </cell>
         </row>
         <row r="78">
           <cell r="A78">
-            <v>13020</v>
+            <v>12050</v>
           </cell>
           <cell r="B78" t="str">
-            <v>クイックバリア</v>
+            <v>クイックムーブ</v>
           </cell>
         </row>
         <row r="79">
           <cell r="A79">
-            <v>13030</v>
+            <v>12051</v>
           </cell>
           <cell r="B79" t="str">
-            <v>クイックキュア</v>
+            <v>クイックムーブ+</v>
           </cell>
         </row>
         <row r="80">
           <cell r="A80">
-            <v>13040</v>
+            <v>12060</v>
           </cell>
           <cell r="B80" t="str">
-            <v>セルフシールド</v>
+            <v>チェイスマジック</v>
           </cell>
         </row>
         <row r="81">
           <cell r="A81">
-            <v>13050</v>
+            <v>12070</v>
           </cell>
           <cell r="B81" t="str">
-            <v>パッシブジャミング</v>
+            <v>ソーサリーコネクト</v>
           </cell>
         </row>
         <row r="82">
           <cell r="A82">
-            <v>13060</v>
+            <v>12080</v>
           </cell>
           <cell r="B82" t="str">
-            <v>サプライカバー</v>
+            <v>ウィンドライズ</v>
           </cell>
         </row>
         <row r="83">
           <cell r="A83">
-            <v>13070</v>
+            <v>12090</v>
           </cell>
           <cell r="B83" t="str">
-            <v>アシッドラッシュ</v>
+            <v>アウトオブオーダー</v>
           </cell>
         </row>
         <row r="84">
           <cell r="A84">
-            <v>13080</v>
+            <v>12100</v>
           </cell>
           <cell r="B84" t="str">
-            <v>ライフスティール</v>
+            <v>ワンスパニッシュ</v>
           </cell>
         </row>
         <row r="85">
           <cell r="A85">
-            <v>13090</v>
+            <v>13010</v>
           </cell>
           <cell r="B85" t="str">
-            <v>アイスセイバー</v>
+            <v>アーマーコード</v>
           </cell>
         </row>
         <row r="86">
           <cell r="A86">
-            <v>13100</v>
+            <v>13011</v>
           </cell>
           <cell r="B86" t="str">
-            <v>ルミナスカバー</v>
+            <v>アーマーコード+</v>
           </cell>
         </row>
         <row r="87">
           <cell r="A87">
-            <v>14010</v>
+            <v>13020</v>
           </cell>
           <cell r="B87" t="str">
-            <v>ディバインシールド</v>
+            <v>クイックバリア</v>
           </cell>
         </row>
         <row r="88">
           <cell r="A88">
-            <v>14020</v>
+            <v>13030</v>
           </cell>
           <cell r="B88" t="str">
-            <v>ライフディバイド</v>
+            <v>クイックキュア</v>
           </cell>
         </row>
         <row r="89">
           <cell r="A89">
-            <v>14030</v>
+            <v>13040</v>
           </cell>
           <cell r="B89" t="str">
-            <v>エイミングスコープ</v>
+            <v>セルフシールド</v>
           </cell>
         </row>
         <row r="90">
           <cell r="A90">
-            <v>14040</v>
+            <v>13041</v>
           </cell>
           <cell r="B90" t="str">
-            <v>リジェネレーション</v>
+            <v>セルフシールド+</v>
           </cell>
         </row>
         <row r="91">
           <cell r="A91">
-            <v>14050</v>
+            <v>13050</v>
           </cell>
           <cell r="B91" t="str">
-            <v>ホープフルアイリス</v>
+            <v>パッシブジャミング</v>
           </cell>
         </row>
         <row r="92">
           <cell r="A92">
-            <v>14060</v>
+            <v>13060</v>
           </cell>
           <cell r="B92" t="str">
-            <v>パッシブサプライ</v>
+            <v>サプライカバー</v>
           </cell>
         </row>
         <row r="93">
           <cell r="A93">
-            <v>14070</v>
+            <v>13070</v>
           </cell>
           <cell r="B93" t="str">
-            <v>ホーミングクルセイド</v>
+            <v>アシッドラッシュ</v>
           </cell>
         </row>
         <row r="94">
           <cell r="A94">
-            <v>14080</v>
+            <v>13071</v>
           </cell>
           <cell r="B94" t="str">
-            <v>クイックヒール</v>
+            <v>アシッドラッシュ+</v>
           </cell>
         </row>
         <row r="95">
           <cell r="A95">
-            <v>14090</v>
+            <v>13080</v>
           </cell>
           <cell r="B95" t="str">
-            <v>リレイズ</v>
+            <v>ライフスティール</v>
           </cell>
         </row>
         <row r="96">
           <cell r="A96">
-            <v>14100</v>
+            <v>13081</v>
           </cell>
           <cell r="B96" t="str">
-            <v>ファストヒール</v>
+            <v>ライフスティール+</v>
           </cell>
         </row>
         <row r="97">
           <cell r="A97">
-            <v>15010</v>
+            <v>13090</v>
           </cell>
           <cell r="B97" t="str">
-            <v>イーグルアイ</v>
+            <v>アイスセイバー</v>
           </cell>
         </row>
         <row r="98">
           <cell r="A98">
-            <v>15020</v>
+            <v>13100</v>
           </cell>
           <cell r="B98" t="str">
-            <v>ネヴァーエンド</v>
+            <v>ルミナスカバー</v>
           </cell>
         </row>
         <row r="99">
           <cell r="A99">
-            <v>15030</v>
+            <v>14010</v>
           </cell>
           <cell r="B99" t="str">
-            <v>グレイブアクト</v>
+            <v>ディバインシールド</v>
           </cell>
         </row>
         <row r="100">
           <cell r="A100">
-            <v>15040</v>
+            <v>14011</v>
           </cell>
           <cell r="B100" t="str">
-            <v>スカルグラッジ</v>
+            <v>ディバインシールド+</v>
           </cell>
         </row>
         <row r="101">
           <cell r="A101">
-            <v>15050</v>
+            <v>14020</v>
           </cell>
           <cell r="B101" t="str">
-            <v>ネガティブドレイン</v>
+            <v>ライフディバイド</v>
           </cell>
         </row>
         <row r="102">
           <cell r="A102">
-            <v>15060</v>
+            <v>14030</v>
           </cell>
           <cell r="B102" t="str">
-            <v>アンデッドペイン</v>
+            <v>エイミングスコープ</v>
           </cell>
         </row>
         <row r="103">
           <cell r="A103">
-            <v>15070</v>
+            <v>14031</v>
           </cell>
           <cell r="B103" t="str">
-            <v>ジャックポッド</v>
+            <v>エイミングスコープ+</v>
           </cell>
         </row>
         <row r="104">
           <cell r="A104">
-            <v>15080</v>
+            <v>14040</v>
           </cell>
           <cell r="B104" t="str">
-            <v>ヒールハント</v>
+            <v>リジェネレーション</v>
           </cell>
         </row>
         <row r="105">
           <cell r="A105">
-            <v>15090</v>
+            <v>14050</v>
           </cell>
           <cell r="B105" t="str">
-            <v>クイックカース</v>
+            <v>ホープフルアイリス</v>
           </cell>
         </row>
         <row r="106">
           <cell r="A106">
-            <v>15100</v>
+            <v>14051</v>
           </cell>
           <cell r="B106" t="str">
-            <v>リヴェンジャー</v>
+            <v>ホープフルアイリス+</v>
           </cell>
         </row>
         <row r="107">
           <cell r="A107">
-            <v>20010</v>
+            <v>14060</v>
           </cell>
           <cell r="B107" t="str">
-            <v>ウェイトユニゾン</v>
+            <v>パッシブサプライ</v>
           </cell>
         </row>
         <row r="108">
           <cell r="A108">
-            <v>30010</v>
+            <v>14070</v>
           </cell>
           <cell r="B108" t="str">
-            <v>ラーニングピアス</v>
+            <v>ホーミングクルセイド</v>
           </cell>
         </row>
         <row r="109">
           <cell r="A109">
-            <v>30020</v>
+            <v>14080</v>
           </cell>
           <cell r="B109" t="str">
-            <v>スティールヒール</v>
+            <v>クイックヒール</v>
           </cell>
         </row>
         <row r="110">
           <cell r="A110">
-            <v>30030</v>
+            <v>14081</v>
           </cell>
           <cell r="B110" t="str">
-            <v>ガッツ</v>
+            <v>クイックヒール+</v>
           </cell>
         </row>
         <row r="111">
           <cell r="A111">
-            <v>100110</v>
+            <v>14090</v>
           </cell>
           <cell r="B111" t="str">
-            <v>ソーイングアームド</v>
+            <v>リレイズ</v>
           </cell>
         </row>
         <row r="112">
           <cell r="A112">
-            <v>100120</v>
+            <v>14100</v>
           </cell>
           <cell r="B112" t="str">
-            <v>エターナルロンド</v>
+            <v>ファストヒール</v>
           </cell>
         </row>
         <row r="113">
           <cell r="A113">
-            <v>100210</v>
+            <v>15010</v>
           </cell>
           <cell r="B113" t="str">
-            <v>アブソリュートパリィ</v>
+            <v>イーグルアイ</v>
           </cell>
         </row>
         <row r="114">
           <cell r="A114">
-            <v>100220</v>
+            <v>15011</v>
           </cell>
           <cell r="B114" t="str">
-            <v>レヴェリー</v>
+            <v>イーグルアイ+</v>
           </cell>
         </row>
         <row r="115">
           <cell r="A115">
-            <v>100310</v>
+            <v>15020</v>
           </cell>
           <cell r="B115" t="str">
-            <v>セイクリッドバリア</v>
+            <v>ネヴァーエンド</v>
           </cell>
         </row>
         <row r="116">
           <cell r="A116">
-            <v>100320</v>
+            <v>15021</v>
           </cell>
           <cell r="B116" t="str">
-            <v>リベンジニードル</v>
+            <v>ネヴァーエンド+</v>
           </cell>
         </row>
         <row r="117">
           <cell r="A117">
-            <v>100410</v>
+            <v>15030</v>
           </cell>
           <cell r="B117" t="str">
-            <v>アバンデンス</v>
+            <v>グレイブアクト</v>
           </cell>
         </row>
         <row r="118">
           <cell r="A118">
-            <v>100420</v>
+            <v>15040</v>
           </cell>
           <cell r="B118" t="str">
-            <v>ハーヴェスト</v>
+            <v>スカルグラッジ</v>
           </cell>
         </row>
         <row r="119">
           <cell r="A119">
-            <v>100510</v>
+            <v>15050</v>
           </cell>
           <cell r="B119" t="str">
-            <v>カースドブレイク</v>
+            <v>ネガティブドレイン</v>
           </cell>
         </row>
         <row r="120">
           <cell r="A120">
-            <v>100520</v>
+            <v>15051</v>
           </cell>
           <cell r="B120" t="str">
-            <v>ムーンライトレイ</v>
+            <v>ネガティブドレイン+</v>
           </cell>
         </row>
         <row r="121">
           <cell r="A121">
-            <v>100610</v>
+            <v>15060</v>
           </cell>
           <cell r="B121" t="str">
-            <v>サンフレイム</v>
+            <v>アンデッドペイン</v>
           </cell>
         </row>
         <row r="122">
           <cell r="A122">
-            <v>100620</v>
+            <v>15070</v>
           </cell>
           <cell r="B122" t="str">
-            <v>フレイムタン</v>
+            <v>ジャックポッド</v>
           </cell>
         </row>
         <row r="123">
           <cell r="A123">
-            <v>100710</v>
+            <v>15080</v>
           </cell>
           <cell r="B123" t="str">
-            <v>ライズザフラッグ</v>
+            <v>ヒールハント</v>
           </cell>
         </row>
         <row r="124">
           <cell r="A124">
-            <v>100720</v>
+            <v>15090</v>
           </cell>
           <cell r="B124" t="str">
-            <v>オーバーリミット</v>
+            <v>クイックカース</v>
           </cell>
         </row>
         <row r="125">
           <cell r="A125">
-            <v>100810</v>
+            <v>15100</v>
           </cell>
           <cell r="B125" t="str">
-            <v>テンパランス</v>
+            <v>リヴェンジャー</v>
           </cell>
         </row>
         <row r="126">
           <cell r="A126">
-            <v>100820</v>
+            <v>15101</v>
           </cell>
           <cell r="B126" t="str">
-            <v>シエルクルセイダー</v>
+            <v>リヴェンジャー+</v>
           </cell>
         </row>
         <row r="127">
           <cell r="A127">
-            <v>100910</v>
+            <v>20010</v>
           </cell>
           <cell r="B127" t="str">
-            <v>バーニングカウンター</v>
+            <v>ウェイトユニゾン</v>
           </cell>
         </row>
         <row r="128">
           <cell r="A128">
-            <v>100911</v>
+            <v>30010</v>
           </cell>
           <cell r="B128" t="str">
-            <v>バーニングカウンター</v>
+            <v>ラーニングピアス</v>
           </cell>
         </row>
         <row r="129">
           <cell r="A129">
-            <v>100920</v>
+            <v>30020</v>
           </cell>
           <cell r="B129" t="str">
-            <v>プロミネンス</v>
+            <v>スティールヒール</v>
           </cell>
         </row>
         <row r="130">
           <cell r="A130">
-            <v>100921</v>
+            <v>30030</v>
           </cell>
           <cell r="B130" t="str">
-            <v>プロミネンス</v>
+            <v>ガッツ</v>
           </cell>
         </row>
         <row r="131">
           <cell r="A131">
-            <v>101010</v>
+            <v>100110</v>
           </cell>
           <cell r="B131" t="str">
-            <v>エウロス</v>
+            <v>ソーイングアームド</v>
           </cell>
         </row>
         <row r="132">
           <cell r="A132">
-            <v>101020</v>
+            <v>100120</v>
           </cell>
           <cell r="B132" t="str">
-            <v>ボレアス</v>
+            <v>エターナルロンド</v>
           </cell>
         </row>
         <row r="133">
           <cell r="A133">
-            <v>101110</v>
+            <v>100210</v>
           </cell>
           <cell r="B133" t="str">
-            <v>アバランシュ</v>
+            <v>アブソリュートパリィ</v>
           </cell>
         </row>
         <row r="134">
           <cell r="A134">
-            <v>101120</v>
+            <v>100220</v>
           </cell>
           <cell r="B134" t="str">
-            <v>ブリザードコフィン</v>
+            <v>レヴェリー</v>
           </cell>
         </row>
         <row r="135">
           <cell r="A135">
-            <v>200110</v>
+            <v>100310</v>
           </cell>
           <cell r="B135" t="str">
-            <v>スリータイムス</v>
+            <v>セイクリッドバリア</v>
           </cell>
         </row>
         <row r="136">
           <cell r="A136">
-            <v>200120</v>
+            <v>100320</v>
           </cell>
           <cell r="B136" t="str">
-            <v>アングリークライ</v>
+            <v>リベンジニードル</v>
           </cell>
         </row>
         <row r="137">
           <cell r="A137">
-            <v>200210</v>
+            <v>100410</v>
           </cell>
           <cell r="B137" t="str">
-            <v>マイトレインフォース</v>
+            <v>アバンデンス</v>
           </cell>
         </row>
         <row r="138">
           <cell r="A138">
-            <v>200220</v>
+            <v>100420</v>
           </cell>
           <cell r="B138" t="str">
-            <v>カタストロフィ</v>
+            <v>ハーヴェスト</v>
           </cell>
         </row>
         <row r="139">
           <cell r="A139">
-            <v>200230</v>
+            <v>100510</v>
           </cell>
           <cell r="B139" t="str">
-            <v>悪魔(ベリト)</v>
+            <v>カースドブレイク</v>
           </cell>
         </row>
         <row r="140">
           <cell r="A140">
-            <v>200310</v>
+            <v>100520</v>
           </cell>
           <cell r="B140" t="str">
-            <v>プルガシオン</v>
+            <v>ムーンライトレイ</v>
           </cell>
         </row>
         <row r="141">
           <cell r="A141">
-            <v>200320</v>
+            <v>100610</v>
           </cell>
           <cell r="B141" t="str">
-            <v>プリエステス</v>
+            <v>サンフレイム</v>
           </cell>
         </row>
         <row r="142">
           <cell r="A142">
-            <v>200330</v>
+            <v>100620</v>
           </cell>
           <cell r="B142" t="str">
-            <v>悪魔(パイモン)</v>
+            <v>フレイムタン</v>
           </cell>
         </row>
         <row r="143">
           <cell r="A143">
-            <v>200410</v>
+            <v>100710</v>
           </cell>
           <cell r="B143" t="str">
-            <v>コウソクテンショウ</v>
+            <v>ライズザフラッグ</v>
           </cell>
         </row>
         <row r="144">
           <cell r="A144">
-            <v>200411</v>
+            <v>100720</v>
           </cell>
           <cell r="B144" t="str">
-            <v>コウソクテンショウ</v>
+            <v>オーバーリミット</v>
           </cell>
         </row>
         <row r="145">
           <cell r="A145">
-            <v>200420</v>
+            <v>100810</v>
           </cell>
           <cell r="B145" t="str">
-            <v>アンチバフ</v>
+            <v>テンパランス</v>
           </cell>
         </row>
         <row r="146">
           <cell r="A146">
-            <v>200430</v>
+            <v>100820</v>
           </cell>
           <cell r="B146" t="str">
-            <v>悪魔(アンドラス)</v>
+            <v>シエルクルセイダー</v>
           </cell>
         </row>
         <row r="147">
           <cell r="A147">
-            <v>200510</v>
+            <v>100910</v>
           </cell>
           <cell r="B147" t="str">
-            <v>カウントダウン</v>
+            <v>バーニングカウンター</v>
           </cell>
         </row>
         <row r="148">
           <cell r="A148">
-            <v>200520</v>
+            <v>100911</v>
           </cell>
           <cell r="B148" t="str">
-            <v>グラウンドゼロ</v>
+            <v>バーニングカウンター</v>
           </cell>
         </row>
         <row r="149">
           <cell r="A149">
-            <v>200530</v>
+            <v>100920</v>
           </cell>
           <cell r="B149" t="str">
-            <v>悪魔(ビフロンス)</v>
+            <v>プロミネンス</v>
           </cell>
         </row>
         <row r="150">
           <cell r="A150">
-            <v>201010</v>
+            <v>100921</v>
           </cell>
           <cell r="B150" t="str">
-            <v>カオスペイン</v>
+            <v>プロミネンス</v>
           </cell>
         </row>
         <row r="151">
           <cell r="A151">
-            <v>201020</v>
+            <v>101010</v>
           </cell>
           <cell r="B151" t="str">
-            <v>フォールンワン</v>
+            <v>エウロス</v>
           </cell>
         </row>
         <row r="152">
           <cell r="A152">
-            <v>201030</v>
+            <v>101020</v>
           </cell>
           <cell r="B152" t="str">
-            <v>アンリマユ</v>
+            <v>ボレアス</v>
           </cell>
         </row>
         <row r="153">
           <cell r="A153">
-            <v>300010</v>
+            <v>101110</v>
           </cell>
           <cell r="B153" t="str">
-            <v>ライフブースト</v>
+            <v>アバランシュ</v>
           </cell>
         </row>
         <row r="154">
           <cell r="A154">
-            <v>300020</v>
+            <v>101120</v>
           </cell>
           <cell r="B154" t="str">
-            <v>スピリットチャージ</v>
+            <v>ブリザードコフィン</v>
           </cell>
         </row>
         <row r="155">
           <cell r="A155">
-            <v>300030</v>
+            <v>200110</v>
           </cell>
           <cell r="B155" t="str">
-            <v>フォースライズ</v>
+            <v>スリータイムス</v>
           </cell>
         </row>
         <row r="156">
           <cell r="A156">
-            <v>300040</v>
+            <v>200120</v>
           </cell>
           <cell r="B156" t="str">
-            <v>ディフェンスオーラ</v>
+            <v>アングリークライ</v>
           </cell>
         </row>
         <row r="157">
           <cell r="A157">
-            <v>300050</v>
+            <v>200210</v>
           </cell>
           <cell r="B157" t="str">
-            <v>ラピッドムーブ</v>
+            <v>マイトレインフォース</v>
           </cell>
         </row>
         <row r="158">
           <cell r="A158">
-            <v>300130</v>
+            <v>200220</v>
           </cell>
           <cell r="B158" t="str">
-            <v>アタックブレイク</v>
+            <v>カタストロフィ</v>
           </cell>
         </row>
         <row r="159">
           <cell r="A159">
-            <v>300140</v>
+            <v>200230</v>
           </cell>
           <cell r="B159" t="str">
-            <v>シールドバニッシュ</v>
+            <v>悪魔(ベリト)</v>
           </cell>
         </row>
         <row r="160">
           <cell r="A160">
-            <v>300210</v>
+            <v>200310</v>
           </cell>
           <cell r="B160" t="str">
-            <v>エーテルリチャージ</v>
+            <v>プルガシオン</v>
           </cell>
         </row>
         <row r="161">
           <cell r="A161">
-            <v>300220</v>
+            <v>200320</v>
           </cell>
           <cell r="B161" t="str">
-            <v>リカバリーエンハンス</v>
+            <v>プリエステス</v>
           </cell>
         </row>
         <row r="162">
           <cell r="A162">
-            <v>300230</v>
+            <v>200330</v>
           </cell>
           <cell r="B162" t="str">
-            <v>ヴェンジェンス</v>
+            <v>悪魔(パイモン)</v>
           </cell>
         </row>
         <row r="163">
           <cell r="A163">
-            <v>301010</v>
+            <v>200410</v>
           </cell>
           <cell r="B163" t="str">
-            <v>ディケイドリセット</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="164">
           <cell r="A164">
-            <v>301020</v>
+            <v>200411</v>
           </cell>
           <cell r="B164" t="str">
-            <v>ウォーリアーブラッド</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="165">
           <cell r="A165">
-            <v>301030</v>
+            <v>200420</v>
           </cell>
           <cell r="B165" t="str">
-            <v>トライアングルガード</v>
+            <v>アンチバフ</v>
           </cell>
         </row>
         <row r="166">
           <cell r="A166">
-            <v>301040</v>
+            <v>200430</v>
           </cell>
           <cell r="B166" t="str">
-            <v>セーフティバリア</v>
+            <v>悪魔(アンドラス)</v>
           </cell>
         </row>
         <row r="167">
           <cell r="A167">
-            <v>301050</v>
+            <v>200510</v>
           </cell>
           <cell r="B167" t="str">
-            <v>ヒロインズハイ</v>
+            <v>カウントダウン</v>
           </cell>
         </row>
         <row r="168">
           <cell r="A168">
-            <v>301060</v>
+            <v>200520</v>
           </cell>
           <cell r="B168" t="str">
-            <v>セカンドステージ</v>
+            <v>グラウンドゼロ</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169">
-            <v>301070</v>
+            <v>200530</v>
           </cell>
           <cell r="B169" t="str">
-            <v>ハイヒットポイント</v>
+            <v>悪魔(ビフロンス)</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170">
-            <v>301080</v>
+            <v>201010</v>
           </cell>
           <cell r="B170" t="str">
-            <v>セプタブラスト</v>
+            <v>カオスペイン</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171">
-            <v>301090</v>
+            <v>201020</v>
           </cell>
           <cell r="B171" t="str">
-            <v>イニシャルブロッカー</v>
+            <v>フォールンワン</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172">
-            <v>301100</v>
+            <v>201030</v>
           </cell>
           <cell r="B172" t="str">
-            <v>ファーストテイク</v>
+            <v>アンリマユ</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173">
-            <v>310010</v>
+            <v>300010</v>
           </cell>
           <cell r="B173" t="str">
-            <v>妖精の祈り</v>
+            <v>ライフブースト</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174">
-            <v>310020</v>
+            <v>300020</v>
           </cell>
           <cell r="B174" t="str">
-            <v>月のかけら</v>
+            <v>スピリットチャージ</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175">
-            <v>310030</v>
+            <v>300030</v>
           </cell>
           <cell r="B175" t="str">
-            <v>商売の才覚書</v>
+            <v>フォースライズ</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176">
-            <v>310040</v>
+            <v>300040</v>
           </cell>
           <cell r="B176" t="str">
-            <v>メビウスの砂時計</v>
+            <v>ディフェンスオーラ</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177">
-            <v>310050</v>
+            <v>300050</v>
           </cell>
           <cell r="B177" t="str">
-            <v>先陣の心得</v>
+            <v>ラピッドムーブ</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178">
-            <v>310060</v>
+            <v>300130</v>
           </cell>
           <cell r="B178" t="str">
-            <v>ヒスイの勾玉</v>
+            <v>アタックブレイク</v>
           </cell>
         </row>
         <row r="179">
           <cell r="A179">
-            <v>310070</v>
+            <v>300140</v>
           </cell>
           <cell r="B179" t="str">
-            <v>英傑の盾</v>
+            <v>シールドバニッシュ</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180">
-            <v>310080</v>
+            <v>300210</v>
           </cell>
           <cell r="B180" t="str">
-            <v>鷹の目</v>
+            <v>エーテルリチャージ</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181">
-            <v>310130</v>
+            <v>300220</v>
           </cell>
           <cell r="B181" t="str">
-            <v>ヒールユニット</v>
+            <v>リカバリーエンハンス</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182">
-            <v>320010</v>
+            <v>300230</v>
           </cell>
           <cell r="B182" t="str">
-            <v>訓練所Lv1</v>
+            <v>ヴェンジェンス</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183">
-            <v>320011</v>
+            <v>301010</v>
           </cell>
           <cell r="B183" t="str">
-            <v>訓練所Lv2</v>
+            <v>ディケイドリセット</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184">
-            <v>320012</v>
+            <v>301020</v>
           </cell>
           <cell r="B184" t="str">
-            <v>訓練所Lv3</v>
+            <v>ウォーリアーブラッド</v>
           </cell>
         </row>
         <row r="185">
           <cell r="A185">
-            <v>320020</v>
+            <v>301030</v>
           </cell>
           <cell r="B185" t="str">
-            <v>研究施設Lv1</v>
+            <v>トライアングルガード</v>
           </cell>
         </row>
         <row r="186">
           <cell r="A186">
-            <v>320021</v>
+            <v>301040</v>
           </cell>
           <cell r="B186" t="str">
-            <v>研究施設Lv2</v>
+            <v>セーフティバリア</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187">
-            <v>320022</v>
+            <v>301050</v>
           </cell>
           <cell r="B187" t="str">
-            <v>研究施設Lv3</v>
+            <v>ヒロインズハイ</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188">
-            <v>320030</v>
+            <v>301060</v>
           </cell>
           <cell r="B188" t="str">
-            <v>資料館Lv1</v>
+            <v>セカンドステージ</v>
           </cell>
         </row>
         <row r="189">
           <cell r="A189">
-            <v>320031</v>
+            <v>301070</v>
           </cell>
           <cell r="B189" t="str">
-            <v>資料館Lv2</v>
+            <v>ハイヒットポイント</v>
           </cell>
         </row>
         <row r="190">
           <cell r="A190">
-            <v>320032</v>
+            <v>301080</v>
           </cell>
           <cell r="B190" t="str">
-            <v>資料館Lv3</v>
+            <v>セプタブラスト</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191">
-            <v>320040</v>
+            <v>301090</v>
           </cell>
           <cell r="B191" t="str">
-            <v>潜伏技術Lv1</v>
+            <v>イニシャルブロッカー</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192">
-            <v>321010</v>
+            <v>301100</v>
           </cell>
           <cell r="B192" t="str">
-            <v>炎の祭壇</v>
+            <v>ファーストテイク</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193">
-            <v>321020</v>
+            <v>310010</v>
           </cell>
           <cell r="B193" t="str">
-            <v>稲妻の祭壇</v>
+            <v>妖精の祈り</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194">
-            <v>321030</v>
+            <v>310020</v>
           </cell>
           <cell r="B194" t="str">
-            <v>蒼の祭壇</v>
+            <v>月のかけら</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195">
-            <v>321040</v>
+            <v>310030</v>
           </cell>
           <cell r="B195" t="str">
-            <v>光の祭壇</v>
+            <v>商売の才覚書</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196">
-            <v>321050</v>
+            <v>310040</v>
           </cell>
           <cell r="B196" t="str">
-            <v>月の祭壇</v>
+            <v>メビウスの砂時計</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197">
-            <v>322010</v>
+            <v>310050</v>
           </cell>
           <cell r="B197" t="str">
-            <v>食糧庫Lv1</v>
+            <v>先陣の心得</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198">
-            <v>322020</v>
+            <v>310060</v>
           </cell>
           <cell r="B198" t="str">
-            <v>攻撃技術Lv1</v>
+            <v>ヒスイの勾玉</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199">
-            <v>322030</v>
+            <v>310070</v>
           </cell>
           <cell r="B199" t="str">
-            <v>防御技術Lv1</v>
+            <v>英傑の盾</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200">
-            <v>322040</v>
+            <v>310080</v>
           </cell>
           <cell r="B200" t="str">
-            <v>詠唱技術Lv1</v>
+            <v>鷹の目</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201">
-            <v>401010</v>
+            <v>310130</v>
           </cell>
           <cell r="B201" t="str">
-            <v>ファイアボール+</v>
+            <v>ヒールユニット</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202">
-            <v>401020</v>
+            <v>320010</v>
           </cell>
           <cell r="B202" t="str">
-            <v>バーンストーム+</v>
+            <v>訓練所Lv1</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203">
-            <v>401030</v>
+            <v>320011</v>
           </cell>
           <cell r="B203" t="str">
-            <v>ヒートスタンプ+</v>
+            <v>訓練所Lv2</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204">
-            <v>401040</v>
+            <v>320012</v>
           </cell>
           <cell r="B204" t="str">
-            <v>ソードアダプト+</v>
+            <v>訓練所Lv3</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205">
-            <v>401050</v>
+            <v>320020</v>
           </cell>
           <cell r="B205" t="str">
-            <v>フレイムレイン+</v>
+            <v>研究施設Lv1</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206">
-            <v>401060</v>
+            <v>320021</v>
           </cell>
           <cell r="B206" t="str">
-            <v>イクスティンクション+</v>
+            <v>研究施設Lv2</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207">
-            <v>401070</v>
+            <v>320022</v>
           </cell>
           <cell r="B207" t="str">
-            <v>バーニングソウル+</v>
+            <v>研究施設Lv3</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208">
-            <v>401080</v>
+            <v>320030</v>
           </cell>
           <cell r="B208" t="str">
-            <v>レイジングバウンサー+</v>
+            <v>資料館Lv1</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209">
-            <v>402010</v>
+            <v>320031</v>
           </cell>
           <cell r="B209" t="str">
-            <v>ディスチャージ+</v>
+            <v>資料館Lv2</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210">
-            <v>402020</v>
+            <v>320032</v>
           </cell>
           <cell r="B210" t="str">
-            <v>イベイドコード+</v>
+            <v>資料館Lv3</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211">
-            <v>402030</v>
+            <v>320040</v>
           </cell>
           <cell r="B211" t="str">
-            <v>ショックインパルス+</v>
+            <v>潜伏技術Lv1</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212">
-            <v>402040</v>
+            <v>321010</v>
           </cell>
           <cell r="B212" t="str">
-            <v>トラストチェイン+</v>
+            <v>炎の祭壇</v>
           </cell>
         </row>
         <row r="213">
           <cell r="A213">
-            <v>402050</v>
+            <v>321020</v>
           </cell>
           <cell r="B213" t="str">
-            <v>スペルバニシング+</v>
+            <v>稲妻の祭壇</v>
           </cell>
         </row>
         <row r="214">
           <cell r="A214">
-            <v>402060</v>
+            <v>321030</v>
           </cell>
           <cell r="B214" t="str">
-            <v>アーテニーストライク+</v>
+            <v>蒼の祭壇</v>
           </cell>
         </row>
         <row r="215">
           <cell r="A215">
-            <v>402070</v>
+            <v>321040</v>
           </cell>
           <cell r="B215" t="str">
-            <v>コンセントレイト+</v>
+            <v>光の祭壇</v>
           </cell>
         </row>
         <row r="216">
           <cell r="A216">
-            <v>402080</v>
+            <v>321050</v>
           </cell>
           <cell r="B216" t="str">
-            <v>ディレイマジック+</v>
+            <v>月の祭壇</v>
           </cell>
         </row>
         <row r="217">
           <cell r="A217">
-            <v>403010</v>
+            <v>322010</v>
           </cell>
           <cell r="B217" t="str">
-            <v>アイスブレイド+</v>
+            <v>食糧庫Lv1</v>
           </cell>
         </row>
         <row r="218">
           <cell r="A218">
-            <v>403020</v>
+            <v>322020</v>
           </cell>
           <cell r="B218" t="str">
-            <v>カウンターオーラ+</v>
+            <v>攻撃技術Lv1</v>
           </cell>
         </row>
         <row r="219">
           <cell r="A219">
-            <v>403030</v>
+            <v>322030</v>
           </cell>
           <cell r="B219" t="str">
-            <v>ラインプロテクト+</v>
+            <v>防御技術Lv1</v>
           </cell>
         </row>
         <row r="220">
           <cell r="A220">
-            <v>403040</v>
+            <v>322040</v>
           </cell>
           <cell r="B220" t="str">
-            <v>エスコートソール+</v>
+            <v>詠唱技術Lv1</v>
           </cell>
         </row>
         <row r="221">
           <cell r="A221">
-            <v>403050</v>
+            <v>401010</v>
           </cell>
           <cell r="B221" t="str">
-            <v>ディープフリーズ+</v>
+            <v>ファイアボール+</v>
           </cell>
         </row>
         <row r="222">
           <cell r="A222">
-            <v>403060</v>
+            <v>401020</v>
           </cell>
           <cell r="B222" t="str">
-            <v>バブルブロウ+</v>
+            <v>バーンストーム+</v>
           </cell>
         </row>
         <row r="223">
           <cell r="A223">
-            <v>403070</v>
+            <v>401030</v>
           </cell>
           <cell r="B223" t="str">
-            <v>アクアミラージュ+</v>
+            <v>ヒートスタンプ+</v>
           </cell>
         </row>
         <row r="224">
           <cell r="A224">
-            <v>403080</v>
+            <v>401040</v>
           </cell>
           <cell r="B224" t="str">
-            <v>フロストシールド+</v>
+            <v>ソードアダプト+</v>
           </cell>
         </row>
         <row r="225">
           <cell r="A225">
-            <v>404010</v>
+            <v>401050</v>
           </cell>
           <cell r="B225" t="str">
-            <v>セイントレーザー+</v>
+            <v>フレイムレイン+</v>
           </cell>
         </row>
         <row r="226">
           <cell r="A226">
-            <v>404020</v>
+            <v>401060</v>
           </cell>
           <cell r="B226" t="str">
-            <v>ペネトレイト+</v>
+            <v>イクスティンクション+</v>
           </cell>
         </row>
         <row r="227">
           <cell r="A227">
-            <v>404030</v>
+            <v>401070</v>
           </cell>
           <cell r="B227" t="str">
-            <v>ヒーリング+</v>
+            <v>バーニングソウル+</v>
           </cell>
         </row>
         <row r="228">
           <cell r="A228">
-            <v>404040</v>
+            <v>401080</v>
           </cell>
           <cell r="B228" t="str">
-            <v>リザイアフォトン+</v>
+            <v>レイジングバウンサー+</v>
           </cell>
         </row>
         <row r="229">
           <cell r="A229">
-            <v>404050</v>
+            <v>402010</v>
           </cell>
           <cell r="B229" t="str">
-            <v>べネディクション+</v>
+            <v>ディスチャージ+</v>
           </cell>
         </row>
         <row r="230">
           <cell r="A230">
-            <v>404060</v>
+            <v>402020</v>
           </cell>
           <cell r="B230" t="str">
-            <v>ホーリーグレイス+</v>
+            <v>イベイドコード+</v>
           </cell>
         </row>
         <row r="231">
           <cell r="A231">
-            <v>404070</v>
+            <v>402030</v>
           </cell>
           <cell r="B231" t="str">
-            <v>キュアエール+</v>
+            <v>ショックインパルス+</v>
           </cell>
         </row>
         <row r="232">
           <cell r="A232">
-            <v>404080</v>
+            <v>402040</v>
           </cell>
           <cell r="B232" t="str">
-            <v>ラインバリア+</v>
+            <v>トラストチェイン+</v>
           </cell>
         </row>
         <row r="233">
           <cell r="A233">
-            <v>405010</v>
+            <v>402050</v>
           </cell>
           <cell r="B233" t="str">
-            <v>ダークプリズン+</v>
+            <v>スペルバニシング+</v>
           </cell>
         </row>
         <row r="234">
           <cell r="A234">
-            <v>405020</v>
+            <v>402060</v>
           </cell>
           <cell r="B234" t="str">
-            <v>ユーサネイジア+</v>
+            <v>アーテニーストライク+</v>
           </cell>
         </row>
         <row r="235">
           <cell r="A235">
-            <v>405030</v>
+            <v>402070</v>
           </cell>
           <cell r="B235" t="str">
-            <v>ドレインヒール+</v>
+            <v>コンセントレイト+</v>
           </cell>
         </row>
         <row r="236">
           <cell r="A236">
-            <v>405040</v>
+            <v>402080</v>
           </cell>
           <cell r="B236" t="str">
-            <v>アビサルデスペア+</v>
+            <v>ディレイマジック+</v>
           </cell>
         </row>
         <row r="237">
           <cell r="A237">
-            <v>405050</v>
+            <v>403010</v>
           </cell>
           <cell r="B237" t="str">
-            <v>ディプラヴィティ+</v>
+            <v>アイスブレイド+</v>
           </cell>
         </row>
         <row r="238">
           <cell r="A238">
-            <v>405060</v>
+            <v>403020</v>
           </cell>
           <cell r="B238" t="str">
-            <v>ダークネス+</v>
+            <v>カウンターオーラ+</v>
           </cell>
         </row>
         <row r="239">
           <cell r="A239">
-            <v>405070</v>
+            <v>403030</v>
           </cell>
           <cell r="B239" t="str">
-            <v>シェイディークラウド+</v>
+            <v>ラインプロテクト+</v>
           </cell>
         </row>
         <row r="240">
           <cell r="A240">
-            <v>405080</v>
+            <v>403040</v>
           </cell>
           <cell r="B240" t="str">
-            <v>ポイズンブロウ+</v>
+            <v>エスコートソール+</v>
           </cell>
         </row>
         <row r="241">
           <cell r="A241">
-            <v>411010</v>
+            <v>403050</v>
           </cell>
           <cell r="B241" t="str">
-            <v>ウルフソウル+</v>
+            <v>ディープフリーズ+</v>
           </cell>
         </row>
         <row r="242">
           <cell r="A242">
-            <v>411020</v>
+            <v>403060</v>
           </cell>
           <cell r="B242" t="str">
-            <v>プリディカメント+</v>
+            <v>バブルブロウ+</v>
           </cell>
         </row>
         <row r="243">
           <cell r="A243">
-            <v>411030</v>
+            <v>403070</v>
           </cell>
           <cell r="B243" t="str">
-            <v>アサルトシフト+</v>
+            <v>アクアミラージュ+</v>
           </cell>
         </row>
         <row r="244">
           <cell r="A244">
-            <v>411040</v>
+            <v>403080</v>
           </cell>
           <cell r="B244" t="str">
-            <v>アクティブギフト+</v>
+            <v>フロストシールド+</v>
           </cell>
         </row>
         <row r="245">
           <cell r="A245">
-            <v>411050</v>
+            <v>404010</v>
           </cell>
           <cell r="B245" t="str">
-            <v>イグナイテッド+</v>
+            <v>セイントレーザー+</v>
           </cell>
         </row>
         <row r="246">
           <cell r="A246">
-            <v>411060</v>
+            <v>404020</v>
           </cell>
           <cell r="B246" t="str">
-            <v>ライジングファイア+</v>
+            <v>ペネトレイト+</v>
           </cell>
         </row>
         <row r="247">
           <cell r="A247">
-            <v>411070</v>
+            <v>404030</v>
           </cell>
           <cell r="B247" t="str">
-            <v>ルージュバック+</v>
+            <v>ヒーリング+</v>
           </cell>
         </row>
         <row r="248">
           <cell r="A248">
-            <v>411080</v>
+            <v>404040</v>
           </cell>
           <cell r="B248" t="str">
-            <v>パワーエール+</v>
+            <v>リザイアフォトン+</v>
           </cell>
         </row>
         <row r="249">
           <cell r="A249">
-            <v>411090</v>
+            <v>404050</v>
           </cell>
           <cell r="B249" t="str">
-            <v>スレイプニル+</v>
+            <v>べネディクション+</v>
           </cell>
         </row>
         <row r="250">
           <cell r="A250">
-            <v>412010</v>
+            <v>404060</v>
           </cell>
           <cell r="B250" t="str">
-            <v>エクステンション+</v>
+            <v>ホーリーグレイス+</v>
           </cell>
         </row>
         <row r="251">
           <cell r="A251">
-            <v>412020</v>
+            <v>404070</v>
           </cell>
           <cell r="B251" t="str">
-            <v>ヘブンリーラック+</v>
+            <v>キュアエール+</v>
           </cell>
         </row>
         <row r="252">
           <cell r="A252">
-            <v>412030</v>
+            <v>404080</v>
           </cell>
           <cell r="B252" t="str">
-            <v>スウィフトカレント+</v>
+            <v>ラインバリア+</v>
           </cell>
         </row>
         <row r="253">
           <cell r="A253">
-            <v>412040</v>
+            <v>405010</v>
           </cell>
           <cell r="B253" t="str">
-            <v>イヴェイドオール+</v>
+            <v>ダークプリズン+</v>
           </cell>
         </row>
         <row r="254">
           <cell r="A254">
-            <v>412050</v>
+            <v>405020</v>
           </cell>
           <cell r="B254" t="str">
-            <v>クイックムーブ+</v>
+            <v>ユーサネイジア+</v>
           </cell>
         </row>
         <row r="255">
           <cell r="A255">
-            <v>412060</v>
+            <v>405030</v>
           </cell>
           <cell r="B255" t="str">
-            <v>チェイスマジック+</v>
+            <v>ドレインヒール+</v>
           </cell>
         </row>
         <row r="256">
           <cell r="A256">
-            <v>412070</v>
+            <v>405040</v>
           </cell>
           <cell r="B256" t="str">
-            <v>ソーサリーコネクト+</v>
+            <v>アビサルデスペア+</v>
           </cell>
         </row>
         <row r="257">
           <cell r="A257">
-            <v>412080</v>
+            <v>405050</v>
           </cell>
           <cell r="B257" t="str">
-            <v>ウィンドライズ+</v>
+            <v>ディプラヴィティ+</v>
           </cell>
         </row>
         <row r="258">
           <cell r="A258">
-            <v>412090</v>
+            <v>405060</v>
           </cell>
           <cell r="B258" t="str">
-            <v>アウトオブオーダー+</v>
+            <v>ダークネス+</v>
           </cell>
         </row>
         <row r="259">
           <cell r="A259">
-            <v>413010</v>
+            <v>405070</v>
           </cell>
           <cell r="B259" t="str">
-            <v>アーマーコード+</v>
+            <v>シェイディークラウド+</v>
           </cell>
         </row>
         <row r="260">
           <cell r="A260">
-            <v>413020</v>
+            <v>405080</v>
           </cell>
           <cell r="B260" t="str">
-            <v>クイックバリア+</v>
+            <v>ポイズンブロウ+</v>
           </cell>
         </row>
         <row r="261">
           <cell r="A261">
-            <v>413030</v>
+            <v>411010</v>
           </cell>
           <cell r="B261" t="str">
-            <v>クイックキュア+</v>
+            <v>ウルフソウル+</v>
           </cell>
         </row>
         <row r="262">
           <cell r="A262">
-            <v>413040</v>
+            <v>411020</v>
           </cell>
           <cell r="B262" t="str">
-            <v>セルフシールド+</v>
+            <v>プリディカメント+</v>
           </cell>
         </row>
         <row r="263">
           <cell r="A263">
-            <v>413050</v>
+            <v>411030</v>
           </cell>
           <cell r="B263" t="str">
-            <v>パッシブジャミング+</v>
+            <v>アサルトシフト+</v>
           </cell>
         </row>
         <row r="264">
           <cell r="A264">
-            <v>413060</v>
+            <v>411040</v>
           </cell>
           <cell r="B264" t="str">
-            <v>サプライカバー+</v>
+            <v>アクティブギフト+</v>
           </cell>
         </row>
         <row r="265">
           <cell r="A265">
-            <v>413070</v>
+            <v>411050</v>
           </cell>
           <cell r="B265" t="str">
-            <v>アシッドラッシュ+</v>
+            <v>イグナイテッド+</v>
           </cell>
         </row>
         <row r="266">
           <cell r="A266">
-            <v>413080</v>
+            <v>411060</v>
           </cell>
           <cell r="B266" t="str">
-            <v>ライフスティール+</v>
+            <v>ライジングファイア+</v>
           </cell>
         </row>
         <row r="267">
           <cell r="A267">
-            <v>413090</v>
+            <v>411070</v>
           </cell>
           <cell r="B267" t="str">
-            <v>アイスセイバー+</v>
+            <v>ルージュバック+</v>
           </cell>
         </row>
         <row r="268">
           <cell r="A268">
-            <v>414010</v>
+            <v>411080</v>
           </cell>
           <cell r="B268" t="str">
-            <v>ディバインシールド+</v>
+            <v>パワーエール+</v>
           </cell>
         </row>
         <row r="269">
           <cell r="A269">
-            <v>414020</v>
+            <v>411090</v>
           </cell>
           <cell r="B269" t="str">
-            <v>ライフディバイド+</v>
+            <v>スレイプニル+</v>
           </cell>
         </row>
         <row r="270">
           <cell r="A270">
-            <v>414030</v>
+            <v>412010</v>
           </cell>
           <cell r="B270" t="str">
-            <v>エイミングスコープ+</v>
+            <v>エクステンション+</v>
           </cell>
         </row>
         <row r="271">
           <cell r="A271">
-            <v>414040</v>
+            <v>412020</v>
           </cell>
           <cell r="B271" t="str">
-            <v>リジェネレーション+</v>
+            <v>ヘブンリーラック+</v>
           </cell>
         </row>
         <row r="272">
           <cell r="A272">
-            <v>414050</v>
+            <v>412030</v>
           </cell>
           <cell r="B272" t="str">
-            <v>ホープフルアイリス+</v>
+            <v>スウィフトカレント+</v>
           </cell>
         </row>
         <row r="273">
           <cell r="A273">
-            <v>414060</v>
+            <v>412040</v>
           </cell>
           <cell r="B273" t="str">
-            <v>パッシブサプライ+</v>
+            <v>イヴェイドオール+</v>
           </cell>
         </row>
         <row r="274">
           <cell r="A274">
-            <v>414070</v>
+            <v>412050</v>
           </cell>
           <cell r="B274" t="str">
-            <v>ホーミングクルセイド+</v>
+            <v>クイックムーブ+</v>
           </cell>
         </row>
         <row r="275">
           <cell r="A275">
-            <v>414080</v>
+            <v>412060</v>
           </cell>
           <cell r="B275" t="str">
-            <v>クイックヒール+</v>
+            <v>チェイスマジック+</v>
           </cell>
         </row>
         <row r="276">
           <cell r="A276">
-            <v>414090</v>
+            <v>412070</v>
           </cell>
           <cell r="B276" t="str">
-            <v>リレイズ+</v>
+            <v>ソーサリーコネクト+</v>
           </cell>
         </row>
         <row r="277">
           <cell r="A277">
-            <v>415010</v>
+            <v>412080</v>
           </cell>
           <cell r="B277" t="str">
-            <v>イーグルアイ+</v>
+            <v>ウィンドライズ+</v>
           </cell>
         </row>
         <row r="278">
           <cell r="A278">
-            <v>415020</v>
+            <v>412090</v>
           </cell>
           <cell r="B278" t="str">
-            <v>ネヴァーエンド+</v>
+            <v>アウトオブオーダー+</v>
           </cell>
         </row>
         <row r="279">
           <cell r="A279">
-            <v>415030</v>
+            <v>413010</v>
           </cell>
           <cell r="B279" t="str">
-            <v>グレイブアクト+</v>
+            <v>アーマーコード+</v>
           </cell>
         </row>
         <row r="280">
           <cell r="A280">
-            <v>415040</v>
+            <v>413020</v>
           </cell>
           <cell r="B280" t="str">
-            <v>スカルグラッジ+</v>
+            <v>クイックバリア+</v>
           </cell>
         </row>
         <row r="281">
           <cell r="A281">
-            <v>415050</v>
+            <v>413030</v>
           </cell>
           <cell r="B281" t="str">
-            <v>ネガティブドレイン+</v>
+            <v>クイックキュア+</v>
           </cell>
         </row>
         <row r="282">
           <cell r="A282">
-            <v>415060</v>
+            <v>413040</v>
           </cell>
           <cell r="B282" t="str">
-            <v>アンデッドペイン+</v>
+            <v>セルフシールド+</v>
           </cell>
         </row>
         <row r="283">
           <cell r="A283">
-            <v>415070</v>
+            <v>413050</v>
           </cell>
           <cell r="B283" t="str">
-            <v>ジャックポッド+</v>
+            <v>パッシブジャミング+</v>
           </cell>
         </row>
         <row r="284">
           <cell r="A284">
-            <v>415080</v>
+            <v>413060</v>
           </cell>
           <cell r="B284" t="str">
-            <v>ヒールハント+</v>
+            <v>サプライカバー+</v>
           </cell>
         </row>
         <row r="285">
           <cell r="A285">
+            <v>413070</v>
+          </cell>
+          <cell r="B285" t="str">
+            <v>アシッドラッシュ+</v>
+          </cell>
+        </row>
+        <row r="286">
+          <cell r="A286">
+            <v>413080</v>
+          </cell>
+          <cell r="B286" t="str">
+            <v>ライフスティール+</v>
+          </cell>
+        </row>
+        <row r="287">
+          <cell r="A287">
+            <v>413090</v>
+          </cell>
+          <cell r="B287" t="str">
+            <v>アイスセイバー+</v>
+          </cell>
+        </row>
+        <row r="288">
+          <cell r="A288">
+            <v>414010</v>
+          </cell>
+          <cell r="B288" t="str">
+            <v>ディバインシールド+</v>
+          </cell>
+        </row>
+        <row r="289">
+          <cell r="A289">
+            <v>414020</v>
+          </cell>
+          <cell r="B289" t="str">
+            <v>ライフディバイド+</v>
+          </cell>
+        </row>
+        <row r="290">
+          <cell r="A290">
+            <v>414030</v>
+          </cell>
+          <cell r="B290" t="str">
+            <v>エイミングスコープ+</v>
+          </cell>
+        </row>
+        <row r="291">
+          <cell r="A291">
+            <v>414040</v>
+          </cell>
+          <cell r="B291" t="str">
+            <v>リジェネレーション+</v>
+          </cell>
+        </row>
+        <row r="292">
+          <cell r="A292">
+            <v>414050</v>
+          </cell>
+          <cell r="B292" t="str">
+            <v>ホープフルアイリス+</v>
+          </cell>
+        </row>
+        <row r="293">
+          <cell r="A293">
+            <v>414060</v>
+          </cell>
+          <cell r="B293" t="str">
+            <v>パッシブサプライ+</v>
+          </cell>
+        </row>
+        <row r="294">
+          <cell r="A294">
+            <v>414070</v>
+          </cell>
+          <cell r="B294" t="str">
+            <v>ホーミングクルセイド+</v>
+          </cell>
+        </row>
+        <row r="295">
+          <cell r="A295">
+            <v>414080</v>
+          </cell>
+          <cell r="B295" t="str">
+            <v>クイックヒール+</v>
+          </cell>
+        </row>
+        <row r="296">
+          <cell r="A296">
+            <v>414090</v>
+          </cell>
+          <cell r="B296" t="str">
+            <v>リレイズ+</v>
+          </cell>
+        </row>
+        <row r="297">
+          <cell r="A297">
+            <v>415010</v>
+          </cell>
+          <cell r="B297" t="str">
+            <v>イーグルアイ+</v>
+          </cell>
+        </row>
+        <row r="298">
+          <cell r="A298">
+            <v>415020</v>
+          </cell>
+          <cell r="B298" t="str">
+            <v>ネヴァーエンド+</v>
+          </cell>
+        </row>
+        <row r="299">
+          <cell r="A299">
+            <v>415030</v>
+          </cell>
+          <cell r="B299" t="str">
+            <v>グレイブアクト+</v>
+          </cell>
+        </row>
+        <row r="300">
+          <cell r="A300">
+            <v>415040</v>
+          </cell>
+          <cell r="B300" t="str">
+            <v>スカルグラッジ+</v>
+          </cell>
+        </row>
+        <row r="301">
+          <cell r="A301">
+            <v>415050</v>
+          </cell>
+          <cell r="B301" t="str">
+            <v>ネガティブドレイン+</v>
+          </cell>
+        </row>
+        <row r="302">
+          <cell r="A302">
+            <v>415060</v>
+          </cell>
+          <cell r="B302" t="str">
+            <v>アンデッドペイン+</v>
+          </cell>
+        </row>
+        <row r="303">
+          <cell r="A303">
+            <v>415070</v>
+          </cell>
+          <cell r="B303" t="str">
+            <v>ジャックポッド+</v>
+          </cell>
+        </row>
+        <row r="304">
+          <cell r="A304">
+            <v>415080</v>
+          </cell>
+          <cell r="B304" t="str">
+            <v>ヒールハント+</v>
+          </cell>
+        </row>
+        <row r="305">
+          <cell r="A305">
             <v>415090</v>
           </cell>
-          <cell r="B285" t="str">
+          <cell r="B305" t="str">
             <v>クイックカース+</v>
           </cell>
         </row>
@@ -3759,13 +3919,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J2">
         <v>3</v>
@@ -3818,13 +3978,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J3">
         <v>3</v>
@@ -3877,13 +4037,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J4">
         <v>3</v>
@@ -3936,10 +4096,10 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>22</v>
@@ -3995,13 +4155,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J6">
         <v>3</v>
@@ -4054,13 +4214,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I7">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J7">
         <v>3</v>
@@ -4113,13 +4273,13 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J8">
         <v>3</v>
@@ -4172,13 +4332,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H9">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J9">
         <v>3</v>
@@ -4231,13 +4391,13 @@
         <v>0</v>
       </c>
       <c r="G10">
+        <v>18</v>
+      </c>
+      <c r="H10">
+        <v>12</v>
+      </c>
+      <c r="I10">
         <v>15</v>
-      </c>
-      <c r="H10">
-        <v>10</v>
-      </c>
-      <c r="I10">
-        <v>12</v>
       </c>
       <c r="J10">
         <v>3</v>
@@ -4290,13 +4450,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J11">
         <v>3</v>
@@ -4349,13 +4509,13 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H12">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I12">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J12">
         <v>3</v>
@@ -4408,10 +4568,10 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I13">
         <v>23</v>
@@ -4467,13 +4627,13 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J14">
         <v>3</v>
@@ -4526,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J15">
         <v>3</v>
@@ -4585,13 +4745,13 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I16">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J16">
         <v>3</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="7820"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -394,9 +394,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -416,7 +416,37 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -430,7 +460,15 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -439,7 +477,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -453,15 +491,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -475,24 +514,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -515,13 +546,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -529,33 +553,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -568,7 +568,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,13 +592,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -604,7 +664,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -616,31 +676,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -652,19 +694,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -676,79 +742,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -759,6 +759,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -792,15 +816,6 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -821,15 +836,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -845,17 +851,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -867,7 +867,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -876,7 +876,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -885,127 +885,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -394,10 +394,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -415,6 +415,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -424,7 +432,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -432,6 +448,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -452,39 +475,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -499,8 +491,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -514,24 +537,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -546,14 +553,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -568,7 +568,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,19 +646,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -604,31 +688,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -640,79 +724,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -730,25 +742,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -762,16 +762,27 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -803,17 +814,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
@@ -836,26 +836,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -867,145 +867,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1659,1881 +1659,1977 @@
         </row>
         <row r="71">
           <cell r="A71">
-            <v>12010</v>
+            <v>11110</v>
           </cell>
           <cell r="B71" t="str">
-            <v>コンセントレイト</v>
+            <v>フレイムセイバー</v>
           </cell>
         </row>
         <row r="72">
           <cell r="A72">
-            <v>12020</v>
+            <v>11111</v>
           </cell>
           <cell r="B72" t="str">
-            <v>ヘブンリーラック</v>
+            <v>フレイムセイバー+</v>
           </cell>
         </row>
         <row r="73">
           <cell r="A73">
-            <v>12021</v>
+            <v>12010</v>
           </cell>
           <cell r="B73" t="str">
-            <v>ヘブンリーラック+</v>
+            <v>コンセントレイト</v>
           </cell>
         </row>
         <row r="74">
           <cell r="A74">
-            <v>12030</v>
+            <v>12020</v>
           </cell>
           <cell r="B74" t="str">
-            <v>スウィフトカレント</v>
+            <v>ヘブンリーラック</v>
           </cell>
         </row>
         <row r="75">
           <cell r="A75">
-            <v>12031</v>
+            <v>12021</v>
           </cell>
           <cell r="B75" t="str">
-            <v>スウィフトカレント+</v>
+            <v>ヘブンリーラック+</v>
           </cell>
         </row>
         <row r="76">
           <cell r="A76">
-            <v>12040</v>
+            <v>12030</v>
           </cell>
           <cell r="B76" t="str">
-            <v>イヴェイドオール</v>
+            <v>スウィフトカレント</v>
           </cell>
         </row>
         <row r="77">
           <cell r="A77">
-            <v>12041</v>
+            <v>12031</v>
           </cell>
           <cell r="B77" t="str">
-            <v>イヴェイドオール+</v>
+            <v>スウィフトカレント+</v>
           </cell>
         </row>
         <row r="78">
           <cell r="A78">
-            <v>12050</v>
+            <v>12040</v>
           </cell>
           <cell r="B78" t="str">
-            <v>クイックムーブ</v>
+            <v>イヴェイドオール</v>
           </cell>
         </row>
         <row r="79">
           <cell r="A79">
-            <v>12051</v>
+            <v>12041</v>
           </cell>
           <cell r="B79" t="str">
-            <v>クイックムーブ+</v>
+            <v>イヴェイドオール+</v>
           </cell>
         </row>
         <row r="80">
           <cell r="A80">
-            <v>12060</v>
+            <v>12050</v>
           </cell>
           <cell r="B80" t="str">
-            <v>チェイスマジック</v>
+            <v>クイックムーブ</v>
           </cell>
         </row>
         <row r="81">
           <cell r="A81">
-            <v>12070</v>
+            <v>12051</v>
           </cell>
           <cell r="B81" t="str">
-            <v>ソーサリーコネクト</v>
+            <v>クイックムーブ+</v>
           </cell>
         </row>
         <row r="82">
           <cell r="A82">
-            <v>12080</v>
+            <v>12060</v>
           </cell>
           <cell r="B82" t="str">
-            <v>ウィンドライズ</v>
+            <v>チェイスマジック</v>
           </cell>
         </row>
         <row r="83">
           <cell r="A83">
-            <v>12090</v>
+            <v>12070</v>
           </cell>
           <cell r="B83" t="str">
-            <v>アウトオブオーダー</v>
+            <v>ソーサリーコネクト</v>
           </cell>
         </row>
         <row r="84">
           <cell r="A84">
-            <v>12100</v>
+            <v>12080</v>
           </cell>
           <cell r="B84" t="str">
-            <v>ワンスパニッシュ</v>
+            <v>ウィンドライズ</v>
           </cell>
         </row>
         <row r="85">
           <cell r="A85">
-            <v>13010</v>
+            <v>12090</v>
           </cell>
           <cell r="B85" t="str">
-            <v>アーマーコード</v>
+            <v>アウトオブオーダー</v>
           </cell>
         </row>
         <row r="86">
           <cell r="A86">
-            <v>13011</v>
+            <v>12100</v>
           </cell>
           <cell r="B86" t="str">
-            <v>アーマーコード+</v>
+            <v>ワンスパニッシュ</v>
           </cell>
         </row>
         <row r="87">
           <cell r="A87">
-            <v>13020</v>
+            <v>12110</v>
           </cell>
           <cell r="B87" t="str">
-            <v>クイックバリア</v>
+            <v>アクトスタンス</v>
           </cell>
         </row>
         <row r="88">
           <cell r="A88">
-            <v>13030</v>
+            <v>12111</v>
           </cell>
           <cell r="B88" t="str">
-            <v>クイックキュア</v>
+            <v>アクトスタンス+</v>
           </cell>
         </row>
         <row r="89">
           <cell r="A89">
-            <v>13040</v>
+            <v>13010</v>
           </cell>
           <cell r="B89" t="str">
-            <v>セルフシールド</v>
+            <v>アーマーコード</v>
           </cell>
         </row>
         <row r="90">
           <cell r="A90">
-            <v>13041</v>
+            <v>13011</v>
           </cell>
           <cell r="B90" t="str">
-            <v>セルフシールド+</v>
+            <v>アーマーコード+</v>
           </cell>
         </row>
         <row r="91">
           <cell r="A91">
-            <v>13050</v>
+            <v>13020</v>
           </cell>
           <cell r="B91" t="str">
-            <v>パッシブジャミング</v>
+            <v>クイックバリア</v>
           </cell>
         </row>
         <row r="92">
           <cell r="A92">
-            <v>13060</v>
+            <v>13030</v>
           </cell>
           <cell r="B92" t="str">
-            <v>サプライカバー</v>
+            <v>クイックキュア</v>
           </cell>
         </row>
         <row r="93">
           <cell r="A93">
-            <v>13070</v>
+            <v>13040</v>
           </cell>
           <cell r="B93" t="str">
-            <v>アシッドラッシュ</v>
+            <v>セルフシールド</v>
           </cell>
         </row>
         <row r="94">
           <cell r="A94">
-            <v>13071</v>
+            <v>13041</v>
           </cell>
           <cell r="B94" t="str">
-            <v>アシッドラッシュ+</v>
+            <v>セルフシールド+</v>
           </cell>
         </row>
         <row r="95">
           <cell r="A95">
-            <v>13080</v>
+            <v>13050</v>
           </cell>
           <cell r="B95" t="str">
-            <v>ライフスティール</v>
+            <v>パッシブジャミング</v>
           </cell>
         </row>
         <row r="96">
           <cell r="A96">
-            <v>13081</v>
+            <v>13060</v>
           </cell>
           <cell r="B96" t="str">
-            <v>ライフスティール+</v>
+            <v>サプライカバー</v>
           </cell>
         </row>
         <row r="97">
           <cell r="A97">
-            <v>13090</v>
+            <v>13070</v>
           </cell>
           <cell r="B97" t="str">
-            <v>アイスセイバー</v>
+            <v>アシッドラッシュ</v>
           </cell>
         </row>
         <row r="98">
           <cell r="A98">
-            <v>13100</v>
+            <v>13071</v>
           </cell>
           <cell r="B98" t="str">
-            <v>ルミナスカバー</v>
+            <v>アシッドラッシュ+</v>
           </cell>
         </row>
         <row r="99">
           <cell r="A99">
-            <v>14010</v>
+            <v>13080</v>
           </cell>
           <cell r="B99" t="str">
-            <v>ディバインシールド</v>
+            <v>ライフスティール</v>
           </cell>
         </row>
         <row r="100">
           <cell r="A100">
-            <v>14011</v>
+            <v>13081</v>
           </cell>
           <cell r="B100" t="str">
-            <v>ディバインシールド+</v>
+            <v>ライフスティール+</v>
           </cell>
         </row>
         <row r="101">
           <cell r="A101">
-            <v>14020</v>
+            <v>13090</v>
           </cell>
           <cell r="B101" t="str">
-            <v>ライフディバイド</v>
+            <v>アイスセイバー</v>
           </cell>
         </row>
         <row r="102">
           <cell r="A102">
-            <v>14030</v>
+            <v>13100</v>
           </cell>
           <cell r="B102" t="str">
-            <v>エイミングスコープ</v>
+            <v>ルミナスカバー</v>
           </cell>
         </row>
         <row r="103">
           <cell r="A103">
-            <v>14031</v>
+            <v>13110</v>
           </cell>
           <cell r="B103" t="str">
-            <v>エイミングスコープ+</v>
+            <v>デコイプラス</v>
           </cell>
         </row>
         <row r="104">
           <cell r="A104">
-            <v>14040</v>
+            <v>13111</v>
           </cell>
           <cell r="B104" t="str">
-            <v>リジェネレーション</v>
+            <v>デコイプラス+</v>
           </cell>
         </row>
         <row r="105">
           <cell r="A105">
-            <v>14050</v>
+            <v>13112</v>
           </cell>
           <cell r="B105" t="str">
-            <v>ホープフルアイリス</v>
+            <v>デコイプラス</v>
           </cell>
         </row>
         <row r="106">
           <cell r="A106">
-            <v>14051</v>
+            <v>13113</v>
           </cell>
           <cell r="B106" t="str">
-            <v>ホープフルアイリス+</v>
+            <v>デコイプラス+</v>
           </cell>
         </row>
         <row r="107">
           <cell r="A107">
-            <v>14060</v>
+            <v>14010</v>
           </cell>
           <cell r="B107" t="str">
-            <v>パッシブサプライ</v>
+            <v>ディバインシールド</v>
           </cell>
         </row>
         <row r="108">
           <cell r="A108">
-            <v>14070</v>
+            <v>14011</v>
           </cell>
           <cell r="B108" t="str">
-            <v>ホーミングクルセイド</v>
+            <v>ディバインシールド+</v>
           </cell>
         </row>
         <row r="109">
           <cell r="A109">
-            <v>14080</v>
+            <v>14020</v>
           </cell>
           <cell r="B109" t="str">
-            <v>クイックヒール</v>
+            <v>ライフディバイド</v>
           </cell>
         </row>
         <row r="110">
           <cell r="A110">
-            <v>14081</v>
+            <v>14030</v>
           </cell>
           <cell r="B110" t="str">
-            <v>クイックヒール+</v>
+            <v>エイミングスコープ</v>
           </cell>
         </row>
         <row r="111">
           <cell r="A111">
-            <v>14090</v>
+            <v>14031</v>
           </cell>
           <cell r="B111" t="str">
-            <v>リレイズ</v>
+            <v>エイミングスコープ+</v>
           </cell>
         </row>
         <row r="112">
           <cell r="A112">
-            <v>14100</v>
+            <v>14040</v>
           </cell>
           <cell r="B112" t="str">
-            <v>ファストヒール</v>
+            <v>リジェネレーション</v>
           </cell>
         </row>
         <row r="113">
           <cell r="A113">
-            <v>15010</v>
+            <v>14050</v>
           </cell>
           <cell r="B113" t="str">
-            <v>イーグルアイ</v>
+            <v>ホープフルアイリス</v>
           </cell>
         </row>
         <row r="114">
           <cell r="A114">
-            <v>15011</v>
+            <v>14051</v>
           </cell>
           <cell r="B114" t="str">
-            <v>イーグルアイ+</v>
+            <v>ホープフルアイリス+</v>
           </cell>
         </row>
         <row r="115">
           <cell r="A115">
-            <v>15020</v>
+            <v>14060</v>
           </cell>
           <cell r="B115" t="str">
-            <v>ネヴァーエンド</v>
+            <v>パッシブサプライ</v>
           </cell>
         </row>
         <row r="116">
           <cell r="A116">
-            <v>15021</v>
+            <v>14070</v>
           </cell>
           <cell r="B116" t="str">
-            <v>ネヴァーエンド+</v>
+            <v>ホーミングクルセイド</v>
           </cell>
         </row>
         <row r="117">
           <cell r="A117">
-            <v>15030</v>
+            <v>14080</v>
           </cell>
           <cell r="B117" t="str">
-            <v>グレイブアクト</v>
+            <v>クイックヒール</v>
           </cell>
         </row>
         <row r="118">
           <cell r="A118">
-            <v>15040</v>
+            <v>14081</v>
           </cell>
           <cell r="B118" t="str">
-            <v>スカルグラッジ</v>
+            <v>クイックヒール+</v>
           </cell>
         </row>
         <row r="119">
           <cell r="A119">
-            <v>15050</v>
+            <v>14090</v>
           </cell>
           <cell r="B119" t="str">
-            <v>ネガティブドレイン</v>
+            <v>リレイズ</v>
           </cell>
         </row>
         <row r="120">
           <cell r="A120">
-            <v>15051</v>
+            <v>14100</v>
           </cell>
           <cell r="B120" t="str">
-            <v>ネガティブドレイン+</v>
+            <v>ファストヒール</v>
           </cell>
         </row>
         <row r="121">
           <cell r="A121">
-            <v>15060</v>
+            <v>14110</v>
           </cell>
           <cell r="B121" t="str">
-            <v>アンデッドペイン</v>
+            <v>セルフケア</v>
           </cell>
         </row>
         <row r="122">
           <cell r="A122">
-            <v>15070</v>
+            <v>14111</v>
           </cell>
           <cell r="B122" t="str">
-            <v>ジャックポッド</v>
+            <v>セルフケア+</v>
           </cell>
         </row>
         <row r="123">
           <cell r="A123">
-            <v>15080</v>
+            <v>15010</v>
           </cell>
           <cell r="B123" t="str">
-            <v>ヒールハント</v>
+            <v>イーグルアイ</v>
           </cell>
         </row>
         <row r="124">
           <cell r="A124">
-            <v>15090</v>
+            <v>15011</v>
           </cell>
           <cell r="B124" t="str">
-            <v>クイックカース</v>
+            <v>イーグルアイ+</v>
           </cell>
         </row>
         <row r="125">
           <cell r="A125">
-            <v>15100</v>
+            <v>15020</v>
           </cell>
           <cell r="B125" t="str">
-            <v>リヴェンジャー</v>
+            <v>ネヴァーエンド</v>
           </cell>
         </row>
         <row r="126">
           <cell r="A126">
-            <v>15101</v>
+            <v>15021</v>
           </cell>
           <cell r="B126" t="str">
-            <v>リヴェンジャー+</v>
+            <v>ネヴァーエンド+</v>
           </cell>
         </row>
         <row r="127">
           <cell r="A127">
-            <v>20010</v>
+            <v>15030</v>
           </cell>
           <cell r="B127" t="str">
-            <v>ウェイトユニゾン</v>
+            <v>グレイブアクト</v>
           </cell>
         </row>
         <row r="128">
           <cell r="A128">
-            <v>30010</v>
+            <v>15040</v>
           </cell>
           <cell r="B128" t="str">
-            <v>ラーニングピアス</v>
+            <v>スカルグラッジ</v>
           </cell>
         </row>
         <row r="129">
           <cell r="A129">
-            <v>30020</v>
+            <v>15050</v>
           </cell>
           <cell r="B129" t="str">
-            <v>スティールヒール</v>
+            <v>ネガティブドレイン</v>
           </cell>
         </row>
         <row r="130">
           <cell r="A130">
-            <v>30030</v>
+            <v>15051</v>
           </cell>
           <cell r="B130" t="str">
-            <v>ガッツ</v>
+            <v>ネガティブドレイン+</v>
           </cell>
         </row>
         <row r="131">
           <cell r="A131">
-            <v>100110</v>
+            <v>15060</v>
           </cell>
           <cell r="B131" t="str">
-            <v>ソーイングアームド</v>
+            <v>アンデッドペイン</v>
           </cell>
         </row>
         <row r="132">
           <cell r="A132">
-            <v>100120</v>
+            <v>15070</v>
           </cell>
           <cell r="B132" t="str">
-            <v>エターナルロンド</v>
+            <v>ジャックポッド</v>
           </cell>
         </row>
         <row r="133">
           <cell r="A133">
-            <v>100210</v>
+            <v>15080</v>
           </cell>
           <cell r="B133" t="str">
-            <v>アブソリュートパリィ</v>
+            <v>ヒールハント</v>
           </cell>
         </row>
         <row r="134">
           <cell r="A134">
-            <v>100220</v>
+            <v>15090</v>
           </cell>
           <cell r="B134" t="str">
-            <v>レヴェリー</v>
+            <v>クイックカース</v>
           </cell>
         </row>
         <row r="135">
           <cell r="A135">
-            <v>100310</v>
+            <v>15100</v>
           </cell>
           <cell r="B135" t="str">
-            <v>セイクリッドバリア</v>
+            <v>リヴェンジャー</v>
           </cell>
         </row>
         <row r="136">
           <cell r="A136">
-            <v>100320</v>
+            <v>15101</v>
           </cell>
           <cell r="B136" t="str">
-            <v>リベンジニードル</v>
+            <v>リヴェンジャー+</v>
           </cell>
         </row>
         <row r="137">
           <cell r="A137">
-            <v>100410</v>
+            <v>15110</v>
           </cell>
           <cell r="B137" t="str">
-            <v>アバンデンス</v>
+            <v>リープリアクト</v>
           </cell>
         </row>
         <row r="138">
           <cell r="A138">
-            <v>100420</v>
+            <v>15111</v>
           </cell>
           <cell r="B138" t="str">
-            <v>ハーヴェスト</v>
+            <v>リープリアクト+</v>
           </cell>
         </row>
         <row r="139">
           <cell r="A139">
-            <v>100510</v>
+            <v>20010</v>
           </cell>
           <cell r="B139" t="str">
-            <v>カースドブレイク</v>
+            <v>ウェイトユニゾン</v>
           </cell>
         </row>
         <row r="140">
           <cell r="A140">
-            <v>100520</v>
+            <v>30010</v>
           </cell>
           <cell r="B140" t="str">
-            <v>ムーンライトレイ</v>
+            <v>ラーニングピアス</v>
           </cell>
         </row>
         <row r="141">
           <cell r="A141">
-            <v>100610</v>
+            <v>30020</v>
           </cell>
           <cell r="B141" t="str">
-            <v>サンフレイム</v>
+            <v>スティールヒール</v>
           </cell>
         </row>
         <row r="142">
           <cell r="A142">
-            <v>100620</v>
+            <v>30030</v>
           </cell>
           <cell r="B142" t="str">
-            <v>フレイムタン</v>
+            <v>ガッツ</v>
           </cell>
         </row>
         <row r="143">
           <cell r="A143">
-            <v>100710</v>
+            <v>100110</v>
           </cell>
           <cell r="B143" t="str">
-            <v>ライズザフラッグ</v>
+            <v>ソーイングアームド</v>
           </cell>
         </row>
         <row r="144">
           <cell r="A144">
-            <v>100720</v>
+            <v>100120</v>
           </cell>
           <cell r="B144" t="str">
-            <v>オーバーリミット</v>
+            <v>エターナルロンド</v>
           </cell>
         </row>
         <row r="145">
           <cell r="A145">
-            <v>100810</v>
+            <v>100210</v>
           </cell>
           <cell r="B145" t="str">
-            <v>テンパランス</v>
+            <v>アブソリュートパリィ</v>
           </cell>
         </row>
         <row r="146">
           <cell r="A146">
-            <v>100820</v>
+            <v>100220</v>
           </cell>
           <cell r="B146" t="str">
-            <v>シエルクルセイダー</v>
+            <v>レヴェリー</v>
           </cell>
         </row>
         <row r="147">
           <cell r="A147">
-            <v>100910</v>
+            <v>100310</v>
           </cell>
           <cell r="B147" t="str">
-            <v>バーニングカウンター</v>
+            <v>セイクリッドバリア</v>
           </cell>
         </row>
         <row r="148">
           <cell r="A148">
-            <v>100911</v>
+            <v>100320</v>
           </cell>
           <cell r="B148" t="str">
-            <v>バーニングカウンター</v>
+            <v>リベンジニードル</v>
           </cell>
         </row>
         <row r="149">
           <cell r="A149">
-            <v>100920</v>
+            <v>100410</v>
           </cell>
           <cell r="B149" t="str">
-            <v>プロミネンス</v>
+            <v>アバンデンス</v>
           </cell>
         </row>
         <row r="150">
           <cell r="A150">
-            <v>100921</v>
+            <v>100420</v>
           </cell>
           <cell r="B150" t="str">
-            <v>プロミネンス</v>
+            <v>ハーヴェスト</v>
           </cell>
         </row>
         <row r="151">
           <cell r="A151">
-            <v>101010</v>
+            <v>100510</v>
           </cell>
           <cell r="B151" t="str">
-            <v>エウロス</v>
+            <v>カースドブレイク</v>
           </cell>
         </row>
         <row r="152">
           <cell r="A152">
-            <v>101020</v>
+            <v>100520</v>
           </cell>
           <cell r="B152" t="str">
-            <v>ボレアス</v>
+            <v>ムーンライトレイ</v>
           </cell>
         </row>
         <row r="153">
           <cell r="A153">
-            <v>101110</v>
+            <v>100610</v>
           </cell>
           <cell r="B153" t="str">
-            <v>アバランシュ</v>
+            <v>サンフレイム</v>
           </cell>
         </row>
         <row r="154">
           <cell r="A154">
-            <v>101120</v>
+            <v>100620</v>
           </cell>
           <cell r="B154" t="str">
-            <v>ブリザードコフィン</v>
+            <v>フレイムタン</v>
           </cell>
         </row>
         <row r="155">
           <cell r="A155">
-            <v>200110</v>
+            <v>100710</v>
           </cell>
           <cell r="B155" t="str">
-            <v>スリータイムス</v>
+            <v>ライズザフラッグ</v>
           </cell>
         </row>
         <row r="156">
           <cell r="A156">
-            <v>200120</v>
+            <v>100720</v>
           </cell>
           <cell r="B156" t="str">
-            <v>アングリークライ</v>
+            <v>オーバーリミット</v>
           </cell>
         </row>
         <row r="157">
           <cell r="A157">
-            <v>200210</v>
+            <v>100810</v>
           </cell>
           <cell r="B157" t="str">
-            <v>マイトレインフォース</v>
+            <v>テンパランス</v>
           </cell>
         </row>
         <row r="158">
           <cell r="A158">
-            <v>200220</v>
+            <v>100820</v>
           </cell>
           <cell r="B158" t="str">
-            <v>カタストロフィ</v>
+            <v>シエルクルセイダー</v>
           </cell>
         </row>
         <row r="159">
           <cell r="A159">
-            <v>200230</v>
+            <v>100910</v>
           </cell>
           <cell r="B159" t="str">
-            <v>悪魔(ベリト)</v>
+            <v>バーニングカウンター</v>
           </cell>
         </row>
         <row r="160">
           <cell r="A160">
-            <v>200310</v>
+            <v>100911</v>
           </cell>
           <cell r="B160" t="str">
-            <v>プルガシオン</v>
+            <v>バーニングカウンター</v>
           </cell>
         </row>
         <row r="161">
           <cell r="A161">
-            <v>200320</v>
+            <v>100920</v>
           </cell>
           <cell r="B161" t="str">
-            <v>プリエステス</v>
+            <v>プロミネンス</v>
           </cell>
         </row>
         <row r="162">
           <cell r="A162">
-            <v>200330</v>
+            <v>100921</v>
           </cell>
           <cell r="B162" t="str">
-            <v>悪魔(パイモン)</v>
+            <v>プロミネンス</v>
           </cell>
         </row>
         <row r="163">
           <cell r="A163">
-            <v>200410</v>
+            <v>101010</v>
           </cell>
           <cell r="B163" t="str">
-            <v>コウソクテンショウ</v>
+            <v>エウロス</v>
           </cell>
         </row>
         <row r="164">
           <cell r="A164">
-            <v>200411</v>
+            <v>101020</v>
           </cell>
           <cell r="B164" t="str">
-            <v>コウソクテンショウ</v>
+            <v>ボレアス</v>
           </cell>
         </row>
         <row r="165">
           <cell r="A165">
-            <v>200420</v>
+            <v>101110</v>
           </cell>
           <cell r="B165" t="str">
-            <v>アンチバフ</v>
+            <v>アバランシュ</v>
           </cell>
         </row>
         <row r="166">
           <cell r="A166">
-            <v>200430</v>
+            <v>101120</v>
           </cell>
           <cell r="B166" t="str">
-            <v>悪魔(アンドラス)</v>
+            <v>ブリザードコフィン</v>
           </cell>
         </row>
         <row r="167">
           <cell r="A167">
-            <v>200510</v>
+            <v>200110</v>
           </cell>
           <cell r="B167" t="str">
-            <v>カウントダウン</v>
+            <v>スリータイムス</v>
           </cell>
         </row>
         <row r="168">
           <cell r="A168">
-            <v>200520</v>
+            <v>200120</v>
           </cell>
           <cell r="B168" t="str">
-            <v>グラウンドゼロ</v>
+            <v>アングリークライ</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169">
-            <v>200530</v>
+            <v>200210</v>
           </cell>
           <cell r="B169" t="str">
-            <v>悪魔(ビフロンス)</v>
+            <v>マイトレインフォース</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170">
-            <v>201010</v>
+            <v>200220</v>
           </cell>
           <cell r="B170" t="str">
-            <v>カオスペイン</v>
+            <v>カタストロフィ</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171">
-            <v>201020</v>
+            <v>200230</v>
           </cell>
           <cell r="B171" t="str">
-            <v>フォールンワン</v>
+            <v>悪魔(ベリト)</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172">
-            <v>201030</v>
+            <v>200310</v>
           </cell>
           <cell r="B172" t="str">
-            <v>アンリマユ</v>
+            <v>プルガシオン</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173">
-            <v>300010</v>
+            <v>200320</v>
           </cell>
           <cell r="B173" t="str">
-            <v>ライフブースト</v>
+            <v>プリエステス</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174">
-            <v>300020</v>
+            <v>200330</v>
           </cell>
           <cell r="B174" t="str">
-            <v>スピリットチャージ</v>
+            <v>悪魔(パイモン)</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175">
-            <v>300030</v>
+            <v>200410</v>
           </cell>
           <cell r="B175" t="str">
-            <v>フォースライズ</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176">
-            <v>300040</v>
+            <v>200411</v>
           </cell>
           <cell r="B176" t="str">
-            <v>ディフェンスオーラ</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177">
-            <v>300050</v>
+            <v>200420</v>
           </cell>
           <cell r="B177" t="str">
-            <v>ラピッドムーブ</v>
+            <v>アンチバフ</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178">
-            <v>300130</v>
+            <v>200430</v>
           </cell>
           <cell r="B178" t="str">
-            <v>アタックブレイク</v>
+            <v>悪魔(アンドラス)</v>
           </cell>
         </row>
         <row r="179">
           <cell r="A179">
-            <v>300140</v>
+            <v>200510</v>
           </cell>
           <cell r="B179" t="str">
-            <v>シールドバニッシュ</v>
+            <v>カウントダウン</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180">
-            <v>300210</v>
+            <v>200520</v>
           </cell>
           <cell r="B180" t="str">
-            <v>エーテルリチャージ</v>
+            <v>グラウンドゼロ</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181">
-            <v>300220</v>
+            <v>200530</v>
           </cell>
           <cell r="B181" t="str">
-            <v>リカバリーエンハンス</v>
+            <v>悪魔(ビフロンス)</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182">
-            <v>300230</v>
+            <v>201010</v>
           </cell>
           <cell r="B182" t="str">
-            <v>ヴェンジェンス</v>
+            <v>カオスペイン</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183">
-            <v>301010</v>
+            <v>201020</v>
           </cell>
           <cell r="B183" t="str">
-            <v>ディケイドリセット</v>
+            <v>フォールンワン</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184">
-            <v>301020</v>
+            <v>201030</v>
           </cell>
           <cell r="B184" t="str">
-            <v>ウォーリアーブラッド</v>
+            <v>アンリマユ</v>
           </cell>
         </row>
         <row r="185">
           <cell r="A185">
-            <v>301030</v>
+            <v>300010</v>
           </cell>
           <cell r="B185" t="str">
-            <v>トライアングルガード</v>
+            <v>ライフブースト</v>
           </cell>
         </row>
         <row r="186">
           <cell r="A186">
-            <v>301040</v>
+            <v>300020</v>
           </cell>
           <cell r="B186" t="str">
-            <v>セーフティバリア</v>
+            <v>スピリットチャージ</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187">
-            <v>301050</v>
+            <v>300030</v>
           </cell>
           <cell r="B187" t="str">
-            <v>ヒロインズハイ</v>
+            <v>フォースライズ</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188">
-            <v>301060</v>
+            <v>300040</v>
           </cell>
           <cell r="B188" t="str">
-            <v>セカンドステージ</v>
+            <v>ディフェンスオーラ</v>
           </cell>
         </row>
         <row r="189">
           <cell r="A189">
-            <v>301070</v>
+            <v>300050</v>
           </cell>
           <cell r="B189" t="str">
-            <v>ハイヒットポイント</v>
+            <v>ラピッドムーブ</v>
           </cell>
         </row>
         <row r="190">
           <cell r="A190">
-            <v>301080</v>
+            <v>300130</v>
           </cell>
           <cell r="B190" t="str">
-            <v>セプタブラスト</v>
+            <v>アタックブレイク</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191">
-            <v>301090</v>
+            <v>300140</v>
           </cell>
           <cell r="B191" t="str">
-            <v>イニシャルブロッカー</v>
+            <v>シールドバニッシュ</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192">
-            <v>301100</v>
+            <v>300210</v>
           </cell>
           <cell r="B192" t="str">
-            <v>ファーストテイク</v>
+            <v>エーテルリチャージ</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193">
-            <v>310010</v>
+            <v>300220</v>
           </cell>
           <cell r="B193" t="str">
-            <v>妖精の祈り</v>
+            <v>リカバリーエンハンス</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194">
-            <v>310020</v>
+            <v>300230</v>
           </cell>
           <cell r="B194" t="str">
-            <v>月のかけら</v>
+            <v>ヴェンジェンス</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195">
-            <v>310030</v>
+            <v>301010</v>
           </cell>
           <cell r="B195" t="str">
-            <v>商売の才覚書</v>
+            <v>ディケイドリセット</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196">
-            <v>310040</v>
+            <v>301020</v>
           </cell>
           <cell r="B196" t="str">
-            <v>メビウスの砂時計</v>
+            <v>ウォーリアーブラッド</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197">
-            <v>310050</v>
+            <v>301030</v>
           </cell>
           <cell r="B197" t="str">
-            <v>先陣の心得</v>
+            <v>トライアングルガード</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198">
-            <v>310060</v>
+            <v>301040</v>
           </cell>
           <cell r="B198" t="str">
-            <v>ヒスイの勾玉</v>
+            <v>セーフティバリア</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199">
-            <v>310070</v>
+            <v>301050</v>
           </cell>
           <cell r="B199" t="str">
-            <v>英傑の盾</v>
+            <v>ヒロインズハイ</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200">
-            <v>310080</v>
+            <v>301060</v>
           </cell>
           <cell r="B200" t="str">
-            <v>鷹の目</v>
+            <v>セカンドステージ</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201">
-            <v>310130</v>
+            <v>301070</v>
           </cell>
           <cell r="B201" t="str">
-            <v>ヒールユニット</v>
+            <v>ハイヒットポイント</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202">
-            <v>320010</v>
+            <v>301080</v>
           </cell>
           <cell r="B202" t="str">
-            <v>訓練所Lv1</v>
+            <v>セプタブラスト</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203">
-            <v>320011</v>
+            <v>301090</v>
           </cell>
           <cell r="B203" t="str">
-            <v>訓練所Lv2</v>
+            <v>イニシャルブロッカー</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204">
-            <v>320012</v>
+            <v>301100</v>
           </cell>
           <cell r="B204" t="str">
-            <v>訓練所Lv3</v>
+            <v>ファーストテイク</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205">
-            <v>320020</v>
+            <v>310010</v>
           </cell>
           <cell r="B205" t="str">
-            <v>研究施設Lv1</v>
+            <v>妖精の祈り</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206">
-            <v>320021</v>
+            <v>310020</v>
           </cell>
           <cell r="B206" t="str">
-            <v>研究施設Lv2</v>
+            <v>月のかけら</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207">
-            <v>320022</v>
+            <v>310030</v>
           </cell>
           <cell r="B207" t="str">
-            <v>研究施設Lv3</v>
+            <v>商売の才覚書</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208">
-            <v>320030</v>
+            <v>310040</v>
           </cell>
           <cell r="B208" t="str">
-            <v>資料館Lv1</v>
+            <v>メビウスの砂時計</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209">
-            <v>320031</v>
+            <v>310050</v>
           </cell>
           <cell r="B209" t="str">
-            <v>資料館Lv2</v>
+            <v>先陣の心得</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210">
-            <v>320032</v>
+            <v>310060</v>
           </cell>
           <cell r="B210" t="str">
-            <v>資料館Lv3</v>
+            <v>ヒスイの勾玉</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211">
-            <v>320040</v>
+            <v>310070</v>
           </cell>
           <cell r="B211" t="str">
-            <v>潜伏技術Lv1</v>
+            <v>英傑の盾</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212">
-            <v>321010</v>
+            <v>310080</v>
           </cell>
           <cell r="B212" t="str">
-            <v>炎の祭壇</v>
+            <v>鷹の目</v>
           </cell>
         </row>
         <row r="213">
           <cell r="A213">
-            <v>321020</v>
+            <v>310130</v>
           </cell>
           <cell r="B213" t="str">
-            <v>稲妻の祭壇</v>
+            <v>ヒールユニット</v>
           </cell>
         </row>
         <row r="214">
           <cell r="A214">
-            <v>321030</v>
+            <v>320010</v>
           </cell>
           <cell r="B214" t="str">
-            <v>蒼の祭壇</v>
+            <v>訓練所Lv1</v>
           </cell>
         </row>
         <row r="215">
           <cell r="A215">
-            <v>321040</v>
+            <v>320011</v>
           </cell>
           <cell r="B215" t="str">
-            <v>光の祭壇</v>
+            <v>訓練所Lv2</v>
           </cell>
         </row>
         <row r="216">
           <cell r="A216">
-            <v>321050</v>
+            <v>320012</v>
           </cell>
           <cell r="B216" t="str">
-            <v>月の祭壇</v>
+            <v>訓練所Lv3</v>
           </cell>
         </row>
         <row r="217">
           <cell r="A217">
-            <v>322010</v>
+            <v>320020</v>
           </cell>
           <cell r="B217" t="str">
-            <v>食糧庫Lv1</v>
+            <v>研究施設Lv1</v>
           </cell>
         </row>
         <row r="218">
           <cell r="A218">
-            <v>322020</v>
+            <v>320021</v>
           </cell>
           <cell r="B218" t="str">
-            <v>攻撃技術Lv1</v>
+            <v>研究施設Lv2</v>
           </cell>
         </row>
         <row r="219">
           <cell r="A219">
-            <v>322030</v>
+            <v>320022</v>
           </cell>
           <cell r="B219" t="str">
-            <v>防御技術Lv1</v>
+            <v>研究施設Lv3</v>
           </cell>
         </row>
         <row r="220">
           <cell r="A220">
-            <v>322040</v>
+            <v>320030</v>
           </cell>
           <cell r="B220" t="str">
-            <v>詠唱技術Lv1</v>
+            <v>資料館Lv1</v>
           </cell>
         </row>
         <row r="221">
           <cell r="A221">
-            <v>401010</v>
+            <v>320031</v>
           </cell>
           <cell r="B221" t="str">
-            <v>ファイアボール+</v>
+            <v>資料館Lv2</v>
           </cell>
         </row>
         <row r="222">
           <cell r="A222">
-            <v>401020</v>
+            <v>320032</v>
           </cell>
           <cell r="B222" t="str">
-            <v>バーンストーム+</v>
+            <v>資料館Lv3</v>
           </cell>
         </row>
         <row r="223">
           <cell r="A223">
-            <v>401030</v>
+            <v>320040</v>
           </cell>
           <cell r="B223" t="str">
-            <v>ヒートスタンプ+</v>
+            <v>潜伏技術Lv1</v>
           </cell>
         </row>
         <row r="224">
           <cell r="A224">
-            <v>401040</v>
+            <v>321010</v>
           </cell>
           <cell r="B224" t="str">
-            <v>ソードアダプト+</v>
+            <v>炎の祭壇</v>
           </cell>
         </row>
         <row r="225">
           <cell r="A225">
-            <v>401050</v>
+            <v>321020</v>
           </cell>
           <cell r="B225" t="str">
-            <v>フレイムレイン+</v>
+            <v>稲妻の祭壇</v>
           </cell>
         </row>
         <row r="226">
           <cell r="A226">
-            <v>401060</v>
+            <v>321030</v>
           </cell>
           <cell r="B226" t="str">
-            <v>イクスティンクション+</v>
+            <v>蒼の祭壇</v>
           </cell>
         </row>
         <row r="227">
           <cell r="A227">
-            <v>401070</v>
+            <v>321040</v>
           </cell>
           <cell r="B227" t="str">
-            <v>バーニングソウル+</v>
+            <v>光の祭壇</v>
           </cell>
         </row>
         <row r="228">
           <cell r="A228">
-            <v>401080</v>
+            <v>321050</v>
           </cell>
           <cell r="B228" t="str">
-            <v>レイジングバウンサー+</v>
+            <v>月の祭壇</v>
           </cell>
         </row>
         <row r="229">
           <cell r="A229">
-            <v>402010</v>
+            <v>322010</v>
           </cell>
           <cell r="B229" t="str">
-            <v>ディスチャージ+</v>
+            <v>食糧庫Lv1</v>
           </cell>
         </row>
         <row r="230">
           <cell r="A230">
-            <v>402020</v>
+            <v>322020</v>
           </cell>
           <cell r="B230" t="str">
-            <v>イベイドコード+</v>
+            <v>攻撃技術Lv1</v>
           </cell>
         </row>
         <row r="231">
           <cell r="A231">
-            <v>402030</v>
+            <v>322030</v>
           </cell>
           <cell r="B231" t="str">
-            <v>ショックインパルス+</v>
+            <v>防御技術Lv1</v>
           </cell>
         </row>
         <row r="232">
           <cell r="A232">
-            <v>402040</v>
+            <v>322040</v>
           </cell>
           <cell r="B232" t="str">
-            <v>トラストチェイン+</v>
+            <v>詠唱技術Lv1</v>
           </cell>
         </row>
         <row r="233">
           <cell r="A233">
-            <v>402050</v>
+            <v>401010</v>
           </cell>
           <cell r="B233" t="str">
-            <v>スペルバニシング+</v>
+            <v>ファイアボール+</v>
           </cell>
         </row>
         <row r="234">
           <cell r="A234">
-            <v>402060</v>
+            <v>401020</v>
           </cell>
           <cell r="B234" t="str">
-            <v>アーテニーストライク+</v>
+            <v>バーンストーム+</v>
           </cell>
         </row>
         <row r="235">
           <cell r="A235">
-            <v>402070</v>
+            <v>401030</v>
           </cell>
           <cell r="B235" t="str">
-            <v>コンセントレイト+</v>
+            <v>ヒートスタンプ+</v>
           </cell>
         </row>
         <row r="236">
           <cell r="A236">
-            <v>402080</v>
+            <v>401040</v>
           </cell>
           <cell r="B236" t="str">
-            <v>ディレイマジック+</v>
+            <v>ソードアダプト+</v>
           </cell>
         </row>
         <row r="237">
           <cell r="A237">
-            <v>403010</v>
+            <v>401050</v>
           </cell>
           <cell r="B237" t="str">
-            <v>アイスブレイド+</v>
+            <v>フレイムレイン+</v>
           </cell>
         </row>
         <row r="238">
           <cell r="A238">
-            <v>403020</v>
+            <v>401060</v>
           </cell>
           <cell r="B238" t="str">
-            <v>カウンターオーラ+</v>
+            <v>イクスティンクション+</v>
           </cell>
         </row>
         <row r="239">
           <cell r="A239">
-            <v>403030</v>
+            <v>401070</v>
           </cell>
           <cell r="B239" t="str">
-            <v>ラインプロテクト+</v>
+            <v>バーニングソウル+</v>
           </cell>
         </row>
         <row r="240">
           <cell r="A240">
-            <v>403040</v>
+            <v>401080</v>
           </cell>
           <cell r="B240" t="str">
-            <v>エスコートソール+</v>
+            <v>レイジングバウンサー+</v>
           </cell>
         </row>
         <row r="241">
           <cell r="A241">
-            <v>403050</v>
+            <v>402010</v>
           </cell>
           <cell r="B241" t="str">
-            <v>ディープフリーズ+</v>
+            <v>ディスチャージ+</v>
           </cell>
         </row>
         <row r="242">
           <cell r="A242">
-            <v>403060</v>
+            <v>402020</v>
           </cell>
           <cell r="B242" t="str">
-            <v>バブルブロウ+</v>
+            <v>イベイドコード+</v>
           </cell>
         </row>
         <row r="243">
           <cell r="A243">
-            <v>403070</v>
+            <v>402030</v>
           </cell>
           <cell r="B243" t="str">
-            <v>アクアミラージュ+</v>
+            <v>ショックインパルス+</v>
           </cell>
         </row>
         <row r="244">
           <cell r="A244">
-            <v>403080</v>
+            <v>402040</v>
           </cell>
           <cell r="B244" t="str">
-            <v>フロストシールド+</v>
+            <v>トラストチェイン+</v>
           </cell>
         </row>
         <row r="245">
           <cell r="A245">
-            <v>404010</v>
+            <v>402050</v>
           </cell>
           <cell r="B245" t="str">
-            <v>セイントレーザー+</v>
+            <v>スペルバニシング+</v>
           </cell>
         </row>
         <row r="246">
           <cell r="A246">
-            <v>404020</v>
+            <v>402060</v>
           </cell>
           <cell r="B246" t="str">
-            <v>ペネトレイト+</v>
+            <v>アーテニーストライク+</v>
           </cell>
         </row>
         <row r="247">
           <cell r="A247">
-            <v>404030</v>
+            <v>402070</v>
           </cell>
           <cell r="B247" t="str">
-            <v>ヒーリング+</v>
+            <v>コンセントレイト+</v>
           </cell>
         </row>
         <row r="248">
           <cell r="A248">
-            <v>404040</v>
+            <v>402080</v>
           </cell>
           <cell r="B248" t="str">
-            <v>リザイアフォトン+</v>
+            <v>ディレイマジック+</v>
           </cell>
         </row>
         <row r="249">
           <cell r="A249">
-            <v>404050</v>
+            <v>403010</v>
           </cell>
           <cell r="B249" t="str">
-            <v>べネディクション+</v>
+            <v>アイスブレイド+</v>
           </cell>
         </row>
         <row r="250">
           <cell r="A250">
-            <v>404060</v>
+            <v>403020</v>
           </cell>
           <cell r="B250" t="str">
-            <v>ホーリーグレイス+</v>
+            <v>カウンターオーラ+</v>
           </cell>
         </row>
         <row r="251">
           <cell r="A251">
-            <v>404070</v>
+            <v>403030</v>
           </cell>
           <cell r="B251" t="str">
-            <v>キュアエール+</v>
+            <v>ラインプロテクト+</v>
           </cell>
         </row>
         <row r="252">
           <cell r="A252">
-            <v>404080</v>
+            <v>403040</v>
           </cell>
           <cell r="B252" t="str">
-            <v>ラインバリア+</v>
+            <v>エスコートソール+</v>
           </cell>
         </row>
         <row r="253">
           <cell r="A253">
-            <v>405010</v>
+            <v>403050</v>
           </cell>
           <cell r="B253" t="str">
-            <v>ダークプリズン+</v>
+            <v>ディープフリーズ+</v>
           </cell>
         </row>
         <row r="254">
           <cell r="A254">
-            <v>405020</v>
+            <v>403060</v>
           </cell>
           <cell r="B254" t="str">
-            <v>ユーサネイジア+</v>
+            <v>バブルブロウ+</v>
           </cell>
         </row>
         <row r="255">
           <cell r="A255">
-            <v>405030</v>
+            <v>403070</v>
           </cell>
           <cell r="B255" t="str">
-            <v>ドレインヒール+</v>
+            <v>アクアミラージュ+</v>
           </cell>
         </row>
         <row r="256">
           <cell r="A256">
-            <v>405040</v>
+            <v>403080</v>
           </cell>
           <cell r="B256" t="str">
-            <v>アビサルデスペア+</v>
+            <v>フロストシールド+</v>
           </cell>
         </row>
         <row r="257">
           <cell r="A257">
-            <v>405050</v>
+            <v>404010</v>
           </cell>
           <cell r="B257" t="str">
-            <v>ディプラヴィティ+</v>
+            <v>セイントレーザー+</v>
           </cell>
         </row>
         <row r="258">
           <cell r="A258">
-            <v>405060</v>
+            <v>404020</v>
           </cell>
           <cell r="B258" t="str">
-            <v>ダークネス+</v>
+            <v>ペネトレイト+</v>
           </cell>
         </row>
         <row r="259">
           <cell r="A259">
-            <v>405070</v>
+            <v>404030</v>
           </cell>
           <cell r="B259" t="str">
-            <v>シェイディークラウド+</v>
+            <v>ヒーリング+</v>
           </cell>
         </row>
         <row r="260">
           <cell r="A260">
-            <v>405080</v>
+            <v>404040</v>
           </cell>
           <cell r="B260" t="str">
-            <v>ポイズンブロウ+</v>
+            <v>リザイアフォトン+</v>
           </cell>
         </row>
         <row r="261">
           <cell r="A261">
-            <v>411010</v>
+            <v>404050</v>
           </cell>
           <cell r="B261" t="str">
-            <v>ウルフソウル+</v>
+            <v>べネディクション+</v>
           </cell>
         </row>
         <row r="262">
           <cell r="A262">
-            <v>411020</v>
+            <v>404060</v>
           </cell>
           <cell r="B262" t="str">
-            <v>プリディカメント+</v>
+            <v>ホーリーグレイス+</v>
           </cell>
         </row>
         <row r="263">
           <cell r="A263">
-            <v>411030</v>
+            <v>404070</v>
           </cell>
           <cell r="B263" t="str">
-            <v>アサルトシフト+</v>
+            <v>キュアエール+</v>
           </cell>
         </row>
         <row r="264">
           <cell r="A264">
-            <v>411040</v>
+            <v>404080</v>
           </cell>
           <cell r="B264" t="str">
-            <v>アクティブギフト+</v>
+            <v>ラインバリア+</v>
           </cell>
         </row>
         <row r="265">
           <cell r="A265">
-            <v>411050</v>
+            <v>405010</v>
           </cell>
           <cell r="B265" t="str">
-            <v>イグナイテッド+</v>
+            <v>ダークプリズン+</v>
           </cell>
         </row>
         <row r="266">
           <cell r="A266">
-            <v>411060</v>
+            <v>405020</v>
           </cell>
           <cell r="B266" t="str">
-            <v>ライジングファイア+</v>
+            <v>ユーサネイジア+</v>
           </cell>
         </row>
         <row r="267">
           <cell r="A267">
-            <v>411070</v>
+            <v>405030</v>
           </cell>
           <cell r="B267" t="str">
-            <v>ルージュバック+</v>
+            <v>ドレインヒール+</v>
           </cell>
         </row>
         <row r="268">
           <cell r="A268">
-            <v>411080</v>
+            <v>405040</v>
           </cell>
           <cell r="B268" t="str">
-            <v>パワーエール+</v>
+            <v>アビサルデスペア+</v>
           </cell>
         </row>
         <row r="269">
           <cell r="A269">
-            <v>411090</v>
+            <v>405050</v>
           </cell>
           <cell r="B269" t="str">
-            <v>スレイプニル+</v>
+            <v>ディプラヴィティ+</v>
           </cell>
         </row>
         <row r="270">
           <cell r="A270">
-            <v>412010</v>
+            <v>405060</v>
           </cell>
           <cell r="B270" t="str">
-            <v>エクステンション+</v>
+            <v>ダークネス+</v>
           </cell>
         </row>
         <row r="271">
           <cell r="A271">
-            <v>412020</v>
+            <v>405070</v>
           </cell>
           <cell r="B271" t="str">
-            <v>ヘブンリーラック+</v>
+            <v>シェイディークラウド+</v>
           </cell>
         </row>
         <row r="272">
           <cell r="A272">
-            <v>412030</v>
+            <v>405080</v>
           </cell>
           <cell r="B272" t="str">
-            <v>スウィフトカレント+</v>
+            <v>ポイズンブロウ+</v>
           </cell>
         </row>
         <row r="273">
           <cell r="A273">
-            <v>412040</v>
+            <v>411010</v>
           </cell>
           <cell r="B273" t="str">
-            <v>イヴェイドオール+</v>
+            <v>ウルフソウル+</v>
           </cell>
         </row>
         <row r="274">
           <cell r="A274">
-            <v>412050</v>
+            <v>411020</v>
           </cell>
           <cell r="B274" t="str">
-            <v>クイックムーブ+</v>
+            <v>プリディカメント+</v>
           </cell>
         </row>
         <row r="275">
           <cell r="A275">
-            <v>412060</v>
+            <v>411030</v>
           </cell>
           <cell r="B275" t="str">
-            <v>チェイスマジック+</v>
+            <v>アサルトシフト+</v>
           </cell>
         </row>
         <row r="276">
           <cell r="A276">
-            <v>412070</v>
+            <v>411040</v>
           </cell>
           <cell r="B276" t="str">
-            <v>ソーサリーコネクト+</v>
+            <v>アクティブギフト+</v>
           </cell>
         </row>
         <row r="277">
           <cell r="A277">
-            <v>412080</v>
+            <v>411050</v>
           </cell>
           <cell r="B277" t="str">
-            <v>ウィンドライズ+</v>
+            <v>イグナイテッド+</v>
           </cell>
         </row>
         <row r="278">
           <cell r="A278">
-            <v>412090</v>
+            <v>411060</v>
           </cell>
           <cell r="B278" t="str">
-            <v>アウトオブオーダー+</v>
+            <v>ライジングファイア+</v>
           </cell>
         </row>
         <row r="279">
           <cell r="A279">
-            <v>413010</v>
+            <v>411070</v>
           </cell>
           <cell r="B279" t="str">
-            <v>アーマーコード+</v>
+            <v>ルージュバック+</v>
           </cell>
         </row>
         <row r="280">
           <cell r="A280">
-            <v>413020</v>
+            <v>411080</v>
           </cell>
           <cell r="B280" t="str">
-            <v>クイックバリア+</v>
+            <v>パワーエール+</v>
           </cell>
         </row>
         <row r="281">
           <cell r="A281">
-            <v>413030</v>
+            <v>411090</v>
           </cell>
           <cell r="B281" t="str">
-            <v>クイックキュア+</v>
+            <v>スレイプニル+</v>
           </cell>
         </row>
         <row r="282">
           <cell r="A282">
-            <v>413040</v>
+            <v>412010</v>
           </cell>
           <cell r="B282" t="str">
-            <v>セルフシールド+</v>
+            <v>エクステンション+</v>
           </cell>
         </row>
         <row r="283">
           <cell r="A283">
-            <v>413050</v>
+            <v>412020</v>
           </cell>
           <cell r="B283" t="str">
-            <v>パッシブジャミング+</v>
+            <v>ヘブンリーラック+</v>
           </cell>
         </row>
         <row r="284">
           <cell r="A284">
-            <v>413060</v>
+            <v>412030</v>
           </cell>
           <cell r="B284" t="str">
-            <v>サプライカバー+</v>
+            <v>スウィフトカレント+</v>
           </cell>
         </row>
         <row r="285">
           <cell r="A285">
-            <v>413070</v>
+            <v>412040</v>
           </cell>
           <cell r="B285" t="str">
-            <v>アシッドラッシュ+</v>
+            <v>イヴェイドオール+</v>
           </cell>
         </row>
         <row r="286">
           <cell r="A286">
-            <v>413080</v>
+            <v>412050</v>
           </cell>
           <cell r="B286" t="str">
-            <v>ライフスティール+</v>
+            <v>クイックムーブ+</v>
           </cell>
         </row>
         <row r="287">
           <cell r="A287">
-            <v>413090</v>
+            <v>412060</v>
           </cell>
           <cell r="B287" t="str">
-            <v>アイスセイバー+</v>
+            <v>チェイスマジック+</v>
           </cell>
         </row>
         <row r="288">
           <cell r="A288">
-            <v>414010</v>
+            <v>412070</v>
           </cell>
           <cell r="B288" t="str">
-            <v>ディバインシールド+</v>
+            <v>ソーサリーコネクト+</v>
           </cell>
         </row>
         <row r="289">
           <cell r="A289">
-            <v>414020</v>
+            <v>412080</v>
           </cell>
           <cell r="B289" t="str">
-            <v>ライフディバイド+</v>
+            <v>ウィンドライズ+</v>
           </cell>
         </row>
         <row r="290">
           <cell r="A290">
-            <v>414030</v>
+            <v>412090</v>
           </cell>
           <cell r="B290" t="str">
-            <v>エイミングスコープ+</v>
+            <v>アウトオブオーダー+</v>
           </cell>
         </row>
         <row r="291">
           <cell r="A291">
-            <v>414040</v>
+            <v>413010</v>
           </cell>
           <cell r="B291" t="str">
-            <v>リジェネレーション+</v>
+            <v>アーマーコード+</v>
           </cell>
         </row>
         <row r="292">
           <cell r="A292">
-            <v>414050</v>
+            <v>413020</v>
           </cell>
           <cell r="B292" t="str">
-            <v>ホープフルアイリス+</v>
+            <v>クイックバリア+</v>
           </cell>
         </row>
         <row r="293">
           <cell r="A293">
-            <v>414060</v>
+            <v>413030</v>
           </cell>
           <cell r="B293" t="str">
-            <v>パッシブサプライ+</v>
+            <v>クイックキュア+</v>
           </cell>
         </row>
         <row r="294">
           <cell r="A294">
-            <v>414070</v>
+            <v>413040</v>
           </cell>
           <cell r="B294" t="str">
-            <v>ホーミングクルセイド+</v>
+            <v>セルフシールド+</v>
           </cell>
         </row>
         <row r="295">
           <cell r="A295">
-            <v>414080</v>
+            <v>413050</v>
           </cell>
           <cell r="B295" t="str">
-            <v>クイックヒール+</v>
+            <v>パッシブジャミング+</v>
           </cell>
         </row>
         <row r="296">
           <cell r="A296">
-            <v>414090</v>
+            <v>413060</v>
           </cell>
           <cell r="B296" t="str">
-            <v>リレイズ+</v>
+            <v>サプライカバー+</v>
           </cell>
         </row>
         <row r="297">
           <cell r="A297">
-            <v>415010</v>
+            <v>413070</v>
           </cell>
           <cell r="B297" t="str">
-            <v>イーグルアイ+</v>
+            <v>アシッドラッシュ+</v>
           </cell>
         </row>
         <row r="298">
           <cell r="A298">
-            <v>415020</v>
+            <v>413080</v>
           </cell>
           <cell r="B298" t="str">
-            <v>ネヴァーエンド+</v>
+            <v>ライフスティール+</v>
           </cell>
         </row>
         <row r="299">
           <cell r="A299">
-            <v>415030</v>
+            <v>413090</v>
           </cell>
           <cell r="B299" t="str">
-            <v>グレイブアクト+</v>
+            <v>アイスセイバー+</v>
           </cell>
         </row>
         <row r="300">
           <cell r="A300">
-            <v>415040</v>
+            <v>414010</v>
           </cell>
           <cell r="B300" t="str">
-            <v>スカルグラッジ+</v>
+            <v>ディバインシールド+</v>
           </cell>
         </row>
         <row r="301">
           <cell r="A301">
-            <v>415050</v>
+            <v>414020</v>
           </cell>
           <cell r="B301" t="str">
-            <v>ネガティブドレイン+</v>
+            <v>ライフディバイド+</v>
           </cell>
         </row>
         <row r="302">
           <cell r="A302">
-            <v>415060</v>
+            <v>414030</v>
           </cell>
           <cell r="B302" t="str">
-            <v>アンデッドペイン+</v>
+            <v>エイミングスコープ+</v>
           </cell>
         </row>
         <row r="303">
           <cell r="A303">
-            <v>415070</v>
+            <v>414040</v>
           </cell>
           <cell r="B303" t="str">
-            <v>ジャックポッド+</v>
+            <v>リジェネレーション+</v>
           </cell>
         </row>
         <row r="304">
           <cell r="A304">
-            <v>415080</v>
+            <v>414050</v>
           </cell>
           <cell r="B304" t="str">
-            <v>ヒールハント+</v>
+            <v>ホープフルアイリス+</v>
           </cell>
         </row>
         <row r="305">
           <cell r="A305">
+            <v>414060</v>
+          </cell>
+          <cell r="B305" t="str">
+            <v>パッシブサプライ+</v>
+          </cell>
+        </row>
+        <row r="306">
+          <cell r="A306">
+            <v>414070</v>
+          </cell>
+          <cell r="B306" t="str">
+            <v>ホーミングクルセイド+</v>
+          </cell>
+        </row>
+        <row r="307">
+          <cell r="A307">
+            <v>414080</v>
+          </cell>
+          <cell r="B307" t="str">
+            <v>クイックヒール+</v>
+          </cell>
+        </row>
+        <row r="308">
+          <cell r="A308">
+            <v>414090</v>
+          </cell>
+          <cell r="B308" t="str">
+            <v>リレイズ+</v>
+          </cell>
+        </row>
+        <row r="309">
+          <cell r="A309">
+            <v>415010</v>
+          </cell>
+          <cell r="B309" t="str">
+            <v>イーグルアイ+</v>
+          </cell>
+        </row>
+        <row r="310">
+          <cell r="A310">
+            <v>415020</v>
+          </cell>
+          <cell r="B310" t="str">
+            <v>ネヴァーエンド+</v>
+          </cell>
+        </row>
+        <row r="311">
+          <cell r="A311">
+            <v>415030</v>
+          </cell>
+          <cell r="B311" t="str">
+            <v>グレイブアクト+</v>
+          </cell>
+        </row>
+        <row r="312">
+          <cell r="A312">
+            <v>415040</v>
+          </cell>
+          <cell r="B312" t="str">
+            <v>スカルグラッジ+</v>
+          </cell>
+        </row>
+        <row r="313">
+          <cell r="A313">
+            <v>415050</v>
+          </cell>
+          <cell r="B313" t="str">
+            <v>ネガティブドレイン+</v>
+          </cell>
+        </row>
+        <row r="314">
+          <cell r="A314">
+            <v>415060</v>
+          </cell>
+          <cell r="B314" t="str">
+            <v>アンデッドペイン+</v>
+          </cell>
+        </row>
+        <row r="315">
+          <cell r="A315">
+            <v>415070</v>
+          </cell>
+          <cell r="B315" t="str">
+            <v>ジャックポッド+</v>
+          </cell>
+        </row>
+        <row r="316">
+          <cell r="A316">
+            <v>415080</v>
+          </cell>
+          <cell r="B316" t="str">
+            <v>ヒールハント+</v>
+          </cell>
+        </row>
+        <row r="317">
+          <cell r="A317">
             <v>415090</v>
           </cell>
-          <cell r="B305" t="str">
+          <cell r="B317" t="str">
             <v>クイックカース+</v>
           </cell>
         </row>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="124">
   <si>
     <t>Id</t>
   </si>
@@ -137,6 +137,9 @@
     <t>Sword</t>
   </si>
   <si>
+    <t>Orga</t>
+  </si>
+  <si>
     <t>Ammon</t>
   </si>
   <si>
@@ -285,6 +288,9 @@
   </si>
   <si>
     <t>ソード</t>
+  </si>
+  <si>
+    <t>オーガ</t>
   </si>
   <si>
     <t>アモン</t>
@@ -394,10 +400,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -415,53 +421,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -483,9 +444,61 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -506,13 +519,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -523,22 +529,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -552,8 +543,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -568,7 +574,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,31 +682,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -616,139 +754,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -764,26 +770,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -812,11 +801,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -836,6 +831,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -845,17 +855,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -867,46 +873,46 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -915,97 +921,97 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1547,130 +1553,130 @@
         </row>
         <row r="57">
           <cell r="A57">
-            <v>11010</v>
+            <v>10110</v>
           </cell>
           <cell r="B57" t="str">
-            <v>ウルフソウル</v>
+            <v>炎の加護</v>
           </cell>
         </row>
         <row r="58">
           <cell r="A58">
-            <v>11011</v>
+            <v>10120</v>
           </cell>
           <cell r="B58" t="str">
-            <v>ウルフソウル+</v>
+            <v>雷の加護</v>
           </cell>
         </row>
         <row r="59">
           <cell r="A59">
-            <v>11020</v>
+            <v>10130</v>
           </cell>
           <cell r="B59" t="str">
-            <v>プリディカメント</v>
+            <v>氷の加護</v>
           </cell>
         </row>
         <row r="60">
           <cell r="A60">
-            <v>11021</v>
+            <v>10140</v>
           </cell>
           <cell r="B60" t="str">
-            <v>プリディカメント+</v>
+            <v>光の加護</v>
           </cell>
         </row>
         <row r="61">
           <cell r="A61">
-            <v>11030</v>
+            <v>10150</v>
           </cell>
           <cell r="B61" t="str">
-            <v>アサルトシフト</v>
+            <v>闇の加護</v>
           </cell>
         </row>
         <row r="62">
           <cell r="A62">
-            <v>11031</v>
+            <v>11010</v>
           </cell>
           <cell r="B62" t="str">
-            <v>アサルトシフト+</v>
+            <v>ウルフソウル</v>
           </cell>
         </row>
         <row r="63">
           <cell r="A63">
-            <v>11040</v>
+            <v>11020</v>
           </cell>
           <cell r="B63" t="str">
-            <v>アクティブギフト</v>
+            <v>プリディカメント</v>
           </cell>
         </row>
         <row r="64">
           <cell r="A64">
-            <v>11050</v>
+            <v>11030</v>
           </cell>
           <cell r="B64" t="str">
-            <v>イグナイテッド</v>
+            <v>アサルトシフト</v>
           </cell>
         </row>
         <row r="65">
           <cell r="A65">
-            <v>11060</v>
+            <v>11040</v>
           </cell>
           <cell r="B65" t="str">
-            <v>ライジングファイア</v>
+            <v>アクティブギフト</v>
           </cell>
         </row>
         <row r="66">
           <cell r="A66">
-            <v>11070</v>
+            <v>11050</v>
           </cell>
           <cell r="B66" t="str">
-            <v>ルージュバック</v>
+            <v>イグナイテッド</v>
           </cell>
         </row>
         <row r="67">
           <cell r="A67">
-            <v>11080</v>
+            <v>11060</v>
           </cell>
           <cell r="B67" t="str">
-            <v>パワーエール</v>
+            <v>ライジングファイア</v>
           </cell>
         </row>
         <row r="68">
           <cell r="A68">
-            <v>11090</v>
+            <v>11070</v>
           </cell>
           <cell r="B68" t="str">
-            <v>スレイプニル</v>
+            <v>ルージュバック</v>
           </cell>
         </row>
         <row r="69">
           <cell r="A69">
-            <v>11100</v>
+            <v>11080</v>
           </cell>
           <cell r="B69" t="str">
-            <v>レストア</v>
+            <v>パワーエール</v>
           </cell>
         </row>
         <row r="70">
           <cell r="A70">
-            <v>11101</v>
+            <v>11090</v>
           </cell>
           <cell r="B70" t="str">
-            <v>レストア+</v>
+            <v>スレイプニル</v>
           </cell>
         </row>
         <row r="71">
           <cell r="A71">
-            <v>11110</v>
+            <v>11100</v>
           </cell>
           <cell r="B71" t="str">
-            <v>フレイムセイバー</v>
+            <v>レストア</v>
           </cell>
         </row>
         <row r="72">
           <cell r="A72">
-            <v>11111</v>
+            <v>11110</v>
           </cell>
           <cell r="B72" t="str">
-            <v>フレイムセイバー+</v>
+            <v>フレイムセイバー</v>
           </cell>
         </row>
         <row r="73">
@@ -1691,1945 +1697,1801 @@
         </row>
         <row r="75">
           <cell r="A75">
-            <v>12021</v>
+            <v>12030</v>
           </cell>
           <cell r="B75" t="str">
-            <v>ヘブンリーラック+</v>
+            <v>スウィフトカレント</v>
           </cell>
         </row>
         <row r="76">
           <cell r="A76">
-            <v>12030</v>
+            <v>12040</v>
           </cell>
           <cell r="B76" t="str">
-            <v>スウィフトカレント</v>
+            <v>イヴェイドオール</v>
           </cell>
         </row>
         <row r="77">
           <cell r="A77">
-            <v>12031</v>
+            <v>12050</v>
           </cell>
           <cell r="B77" t="str">
-            <v>スウィフトカレント+</v>
+            <v>クイックムーブ</v>
           </cell>
         </row>
         <row r="78">
           <cell r="A78">
-            <v>12040</v>
+            <v>12060</v>
           </cell>
           <cell r="B78" t="str">
-            <v>イヴェイドオール</v>
+            <v>チェイスマジック</v>
           </cell>
         </row>
         <row r="79">
           <cell r="A79">
-            <v>12041</v>
+            <v>12070</v>
           </cell>
           <cell r="B79" t="str">
-            <v>イヴェイドオール+</v>
+            <v>ソーサリーコネクト</v>
           </cell>
         </row>
         <row r="80">
           <cell r="A80">
-            <v>12050</v>
+            <v>12080</v>
           </cell>
           <cell r="B80" t="str">
-            <v>クイックムーブ</v>
+            <v>ウィンドライズ</v>
           </cell>
         </row>
         <row r="81">
           <cell r="A81">
-            <v>12051</v>
+            <v>12090</v>
           </cell>
           <cell r="B81" t="str">
-            <v>クイックムーブ+</v>
+            <v>アウトオブオーダー</v>
           </cell>
         </row>
         <row r="82">
           <cell r="A82">
-            <v>12060</v>
+            <v>12100</v>
           </cell>
           <cell r="B82" t="str">
-            <v>チェイスマジック</v>
+            <v>ワンスパニッシュ</v>
           </cell>
         </row>
         <row r="83">
           <cell r="A83">
-            <v>12070</v>
+            <v>12110</v>
           </cell>
           <cell r="B83" t="str">
-            <v>ソーサリーコネクト</v>
+            <v>アクトスタンス</v>
           </cell>
         </row>
         <row r="84">
           <cell r="A84">
-            <v>12080</v>
+            <v>13010</v>
           </cell>
           <cell r="B84" t="str">
-            <v>ウィンドライズ</v>
+            <v>アーマーコード</v>
           </cell>
         </row>
         <row r="85">
           <cell r="A85">
-            <v>12090</v>
+            <v>13020</v>
           </cell>
           <cell r="B85" t="str">
-            <v>アウトオブオーダー</v>
+            <v>クイックバリア</v>
           </cell>
         </row>
         <row r="86">
           <cell r="A86">
-            <v>12100</v>
+            <v>13030</v>
           </cell>
           <cell r="B86" t="str">
-            <v>ワンスパニッシュ</v>
+            <v>クイックキュア</v>
           </cell>
         </row>
         <row r="87">
           <cell r="A87">
-            <v>12110</v>
+            <v>13040</v>
           </cell>
           <cell r="B87" t="str">
-            <v>アクトスタンス</v>
+            <v>セルフシールド</v>
           </cell>
         </row>
         <row r="88">
           <cell r="A88">
-            <v>12111</v>
+            <v>13050</v>
           </cell>
           <cell r="B88" t="str">
-            <v>アクトスタンス+</v>
+            <v>パッシブジャミング</v>
           </cell>
         </row>
         <row r="89">
           <cell r="A89">
-            <v>13010</v>
+            <v>13060</v>
           </cell>
           <cell r="B89" t="str">
-            <v>アーマーコード</v>
+            <v>サプライカバー</v>
           </cell>
         </row>
         <row r="90">
           <cell r="A90">
-            <v>13011</v>
+            <v>13070</v>
           </cell>
           <cell r="B90" t="str">
-            <v>アーマーコード+</v>
+            <v>アシッドラッシュ</v>
           </cell>
         </row>
         <row r="91">
           <cell r="A91">
-            <v>13020</v>
+            <v>13080</v>
           </cell>
           <cell r="B91" t="str">
-            <v>クイックバリア</v>
+            <v>ライフスティール</v>
           </cell>
         </row>
         <row r="92">
           <cell r="A92">
-            <v>13030</v>
+            <v>13090</v>
           </cell>
           <cell r="B92" t="str">
-            <v>クイックキュア</v>
+            <v>アイスセイバー</v>
           </cell>
         </row>
         <row r="93">
           <cell r="A93">
-            <v>13040</v>
+            <v>13100</v>
           </cell>
           <cell r="B93" t="str">
-            <v>セルフシールド</v>
+            <v>ルミナスカバー</v>
           </cell>
         </row>
         <row r="94">
           <cell r="A94">
-            <v>13041</v>
+            <v>13110</v>
           </cell>
           <cell r="B94" t="str">
-            <v>セルフシールド+</v>
+            <v>デコイプラス</v>
           </cell>
         </row>
         <row r="95">
           <cell r="A95">
-            <v>13050</v>
+            <v>13111</v>
           </cell>
           <cell r="B95" t="str">
-            <v>パッシブジャミング</v>
+            <v>デコイプラス</v>
           </cell>
         </row>
         <row r="96">
           <cell r="A96">
-            <v>13060</v>
+            <v>14010</v>
           </cell>
           <cell r="B96" t="str">
-            <v>サプライカバー</v>
+            <v>ディバインシールド</v>
           </cell>
         </row>
         <row r="97">
           <cell r="A97">
-            <v>13070</v>
+            <v>14020</v>
           </cell>
           <cell r="B97" t="str">
-            <v>アシッドラッシュ</v>
+            <v>ライフディバイド</v>
           </cell>
         </row>
         <row r="98">
           <cell r="A98">
-            <v>13071</v>
+            <v>14030</v>
           </cell>
           <cell r="B98" t="str">
-            <v>アシッドラッシュ+</v>
+            <v>エイミングスコープ</v>
           </cell>
         </row>
         <row r="99">
           <cell r="A99">
-            <v>13080</v>
+            <v>14040</v>
           </cell>
           <cell r="B99" t="str">
-            <v>ライフスティール</v>
+            <v>リジェネレーション</v>
           </cell>
         </row>
         <row r="100">
           <cell r="A100">
-            <v>13081</v>
+            <v>14050</v>
           </cell>
           <cell r="B100" t="str">
-            <v>ライフスティール+</v>
+            <v>ホープフルアイリス</v>
           </cell>
         </row>
         <row r="101">
           <cell r="A101">
-            <v>13090</v>
+            <v>14060</v>
           </cell>
           <cell r="B101" t="str">
-            <v>アイスセイバー</v>
+            <v>パッシブサプライ</v>
           </cell>
         </row>
         <row r="102">
           <cell r="A102">
-            <v>13100</v>
+            <v>14070</v>
           </cell>
           <cell r="B102" t="str">
-            <v>ルミナスカバー</v>
+            <v>ホーミングクルセイド</v>
           </cell>
         </row>
         <row r="103">
           <cell r="A103">
-            <v>13110</v>
+            <v>14080</v>
           </cell>
           <cell r="B103" t="str">
-            <v>デコイプラス</v>
+            <v>クイックヒール</v>
           </cell>
         </row>
         <row r="104">
           <cell r="A104">
-            <v>13111</v>
+            <v>14090</v>
           </cell>
           <cell r="B104" t="str">
-            <v>デコイプラス+</v>
+            <v>リレイズ</v>
           </cell>
         </row>
         <row r="105">
           <cell r="A105">
-            <v>13112</v>
+            <v>14100</v>
           </cell>
           <cell r="B105" t="str">
-            <v>デコイプラス</v>
+            <v>ファストヒール</v>
           </cell>
         </row>
         <row r="106">
           <cell r="A106">
-            <v>13113</v>
+            <v>14110</v>
           </cell>
           <cell r="B106" t="str">
-            <v>デコイプラス+</v>
+            <v>セルフケア</v>
           </cell>
         </row>
         <row r="107">
           <cell r="A107">
-            <v>14010</v>
+            <v>15010</v>
           </cell>
           <cell r="B107" t="str">
-            <v>ディバインシールド</v>
+            <v>イーグルアイ</v>
           </cell>
         </row>
         <row r="108">
           <cell r="A108">
-            <v>14011</v>
+            <v>15020</v>
           </cell>
           <cell r="B108" t="str">
-            <v>ディバインシールド+</v>
+            <v>ネヴァーエンド</v>
           </cell>
         </row>
         <row r="109">
           <cell r="A109">
-            <v>14020</v>
+            <v>15030</v>
           </cell>
           <cell r="B109" t="str">
-            <v>ライフディバイド</v>
+            <v>グレイブアクト</v>
           </cell>
         </row>
         <row r="110">
           <cell r="A110">
-            <v>14030</v>
+            <v>15040</v>
           </cell>
           <cell r="B110" t="str">
-            <v>エイミングスコープ</v>
+            <v>スカルグラッジ</v>
           </cell>
         </row>
         <row r="111">
           <cell r="A111">
-            <v>14031</v>
+            <v>15050</v>
           </cell>
           <cell r="B111" t="str">
-            <v>エイミングスコープ+</v>
+            <v>ネガティブドレイン</v>
           </cell>
         </row>
         <row r="112">
           <cell r="A112">
-            <v>14040</v>
+            <v>15060</v>
           </cell>
           <cell r="B112" t="str">
-            <v>リジェネレーション</v>
+            <v>アンデッドペイン</v>
           </cell>
         </row>
         <row r="113">
           <cell r="A113">
-            <v>14050</v>
+            <v>15070</v>
           </cell>
           <cell r="B113" t="str">
-            <v>ホープフルアイリス</v>
+            <v>ジャックポッド</v>
           </cell>
         </row>
         <row r="114">
           <cell r="A114">
-            <v>14051</v>
+            <v>15080</v>
           </cell>
           <cell r="B114" t="str">
-            <v>ホープフルアイリス+</v>
+            <v>ヒールハント</v>
           </cell>
         </row>
         <row r="115">
           <cell r="A115">
-            <v>14060</v>
+            <v>15090</v>
           </cell>
           <cell r="B115" t="str">
-            <v>パッシブサプライ</v>
+            <v>クイックカース</v>
           </cell>
         </row>
         <row r="116">
           <cell r="A116">
-            <v>14070</v>
+            <v>15100</v>
           </cell>
           <cell r="B116" t="str">
-            <v>ホーミングクルセイド</v>
+            <v>リヴェンジャー</v>
           </cell>
         </row>
         <row r="117">
           <cell r="A117">
-            <v>14080</v>
+            <v>15110</v>
           </cell>
           <cell r="B117" t="str">
-            <v>クイックヒール</v>
+            <v>リープリアクト</v>
           </cell>
         </row>
         <row r="118">
           <cell r="A118">
-            <v>14081</v>
+            <v>15112</v>
           </cell>
           <cell r="B118" t="str">
-            <v>クイックヒール+</v>
+            <v>リープリアクト</v>
           </cell>
         </row>
         <row r="119">
           <cell r="A119">
-            <v>14090</v>
+            <v>20010</v>
           </cell>
           <cell r="B119" t="str">
-            <v>リレイズ</v>
+            <v>ウェイトユニゾン</v>
           </cell>
         </row>
         <row r="120">
           <cell r="A120">
-            <v>14100</v>
+            <v>30010</v>
           </cell>
           <cell r="B120" t="str">
-            <v>ファストヒール</v>
+            <v>ラーニングピアス</v>
           </cell>
         </row>
         <row r="121">
           <cell r="A121">
-            <v>14110</v>
+            <v>30020</v>
           </cell>
           <cell r="B121" t="str">
-            <v>セルフケア</v>
+            <v>スティールヒール</v>
           </cell>
         </row>
         <row r="122">
           <cell r="A122">
-            <v>14111</v>
+            <v>30030</v>
           </cell>
           <cell r="B122" t="str">
-            <v>セルフケア+</v>
+            <v>ガッツ</v>
           </cell>
         </row>
         <row r="123">
           <cell r="A123">
-            <v>15010</v>
+            <v>100110</v>
           </cell>
           <cell r="B123" t="str">
-            <v>イーグルアイ</v>
+            <v>ソーイングアームド</v>
           </cell>
         </row>
         <row r="124">
           <cell r="A124">
-            <v>15011</v>
+            <v>100120</v>
           </cell>
           <cell r="B124" t="str">
-            <v>イーグルアイ+</v>
+            <v>エターナルロンド</v>
           </cell>
         </row>
         <row r="125">
           <cell r="A125">
-            <v>15020</v>
+            <v>100210</v>
           </cell>
           <cell r="B125" t="str">
-            <v>ネヴァーエンド</v>
+            <v>アブソリュートパリィ</v>
           </cell>
         </row>
         <row r="126">
           <cell r="A126">
-            <v>15021</v>
+            <v>100220</v>
           </cell>
           <cell r="B126" t="str">
-            <v>ネヴァーエンド+</v>
+            <v>レヴェリー</v>
           </cell>
         </row>
         <row r="127">
           <cell r="A127">
-            <v>15030</v>
+            <v>100310</v>
           </cell>
           <cell r="B127" t="str">
-            <v>グレイブアクト</v>
+            <v>セイクリッドバリア</v>
           </cell>
         </row>
         <row r="128">
           <cell r="A128">
-            <v>15040</v>
+            <v>100320</v>
           </cell>
           <cell r="B128" t="str">
-            <v>スカルグラッジ</v>
+            <v>リベンジニードル</v>
           </cell>
         </row>
         <row r="129">
           <cell r="A129">
-            <v>15050</v>
+            <v>100410</v>
           </cell>
           <cell r="B129" t="str">
-            <v>ネガティブドレイン</v>
+            <v>アバンデンス</v>
           </cell>
         </row>
         <row r="130">
           <cell r="A130">
-            <v>15051</v>
+            <v>100420</v>
           </cell>
           <cell r="B130" t="str">
-            <v>ネガティブドレイン+</v>
+            <v>ハーヴェスト</v>
           </cell>
         </row>
         <row r="131">
           <cell r="A131">
-            <v>15060</v>
+            <v>100510</v>
           </cell>
           <cell r="B131" t="str">
-            <v>アンデッドペイン</v>
+            <v>カースドブレイク</v>
           </cell>
         </row>
         <row r="132">
           <cell r="A132">
-            <v>15070</v>
+            <v>100520</v>
           </cell>
           <cell r="B132" t="str">
-            <v>ジャックポッド</v>
+            <v>ムーンライトレイ</v>
           </cell>
         </row>
         <row r="133">
           <cell r="A133">
-            <v>15080</v>
+            <v>100610</v>
           </cell>
           <cell r="B133" t="str">
-            <v>ヒールハント</v>
+            <v>サンフレイム</v>
           </cell>
         </row>
         <row r="134">
           <cell r="A134">
-            <v>15090</v>
+            <v>100620</v>
           </cell>
           <cell r="B134" t="str">
-            <v>クイックカース</v>
+            <v>フレイムタン</v>
           </cell>
         </row>
         <row r="135">
           <cell r="A135">
-            <v>15100</v>
+            <v>100710</v>
           </cell>
           <cell r="B135" t="str">
-            <v>リヴェンジャー</v>
+            <v>ライズザフラッグ</v>
           </cell>
         </row>
         <row r="136">
           <cell r="A136">
-            <v>15101</v>
+            <v>100720</v>
           </cell>
           <cell r="B136" t="str">
-            <v>リヴェンジャー+</v>
+            <v>オーバーリミット</v>
           </cell>
         </row>
         <row r="137">
           <cell r="A137">
-            <v>15110</v>
+            <v>100810</v>
           </cell>
           <cell r="B137" t="str">
-            <v>リープリアクト</v>
+            <v>テンパランス</v>
           </cell>
         </row>
         <row r="138">
           <cell r="A138">
-            <v>15111</v>
+            <v>100820</v>
           </cell>
           <cell r="B138" t="str">
-            <v>リープリアクト+</v>
+            <v>シエルクルセイダー</v>
           </cell>
         </row>
         <row r="139">
           <cell r="A139">
-            <v>20010</v>
+            <v>100910</v>
           </cell>
           <cell r="B139" t="str">
-            <v>ウェイトユニゾン</v>
+            <v>バーニングカウンター</v>
           </cell>
         </row>
         <row r="140">
           <cell r="A140">
-            <v>30010</v>
+            <v>100911</v>
           </cell>
           <cell r="B140" t="str">
-            <v>ラーニングピアス</v>
+            <v>バーニングカウンター</v>
           </cell>
         </row>
         <row r="141">
           <cell r="A141">
-            <v>30020</v>
+            <v>100920</v>
           </cell>
           <cell r="B141" t="str">
-            <v>スティールヒール</v>
+            <v>プロミネンス</v>
           </cell>
         </row>
         <row r="142">
           <cell r="A142">
-            <v>30030</v>
+            <v>100921</v>
           </cell>
           <cell r="B142" t="str">
-            <v>ガッツ</v>
+            <v>プロミネンス</v>
           </cell>
         </row>
         <row r="143">
           <cell r="A143">
-            <v>100110</v>
+            <v>101010</v>
           </cell>
           <cell r="B143" t="str">
-            <v>ソーイングアームド</v>
+            <v>エウロス</v>
           </cell>
         </row>
         <row r="144">
           <cell r="A144">
-            <v>100120</v>
+            <v>101020</v>
           </cell>
           <cell r="B144" t="str">
-            <v>エターナルロンド</v>
+            <v>ボレアス</v>
           </cell>
         </row>
         <row r="145">
           <cell r="A145">
-            <v>100210</v>
+            <v>101110</v>
           </cell>
           <cell r="B145" t="str">
-            <v>アブソリュートパリィ</v>
+            <v>アバランシュ</v>
           </cell>
         </row>
         <row r="146">
           <cell r="A146">
-            <v>100220</v>
+            <v>101120</v>
           </cell>
           <cell r="B146" t="str">
-            <v>レヴェリー</v>
+            <v>ブリザードコフィン</v>
           </cell>
         </row>
         <row r="147">
           <cell r="A147">
-            <v>100310</v>
+            <v>110110</v>
           </cell>
           <cell r="B147" t="str">
-            <v>セイクリッドバリア</v>
+            <v>ウィビングヒストリー</v>
           </cell>
         </row>
         <row r="148">
           <cell r="A148">
-            <v>100320</v>
+            <v>110120</v>
           </cell>
           <cell r="B148" t="str">
-            <v>リベンジニードル</v>
+            <v>アンライバルド</v>
           </cell>
         </row>
         <row r="149">
           <cell r="A149">
-            <v>100410</v>
+            <v>200110</v>
           </cell>
           <cell r="B149" t="str">
-            <v>アバンデンス</v>
+            <v>スリータイムス</v>
           </cell>
         </row>
         <row r="150">
           <cell r="A150">
-            <v>100420</v>
+            <v>200120</v>
           </cell>
           <cell r="B150" t="str">
-            <v>ハーヴェスト</v>
+            <v>アングリークライ</v>
           </cell>
         </row>
         <row r="151">
           <cell r="A151">
-            <v>100510</v>
+            <v>200210</v>
           </cell>
           <cell r="B151" t="str">
-            <v>カースドブレイク</v>
+            <v>マイトレインフォース</v>
           </cell>
         </row>
         <row r="152">
           <cell r="A152">
-            <v>100520</v>
+            <v>200220</v>
           </cell>
           <cell r="B152" t="str">
-            <v>ムーンライトレイ</v>
+            <v>カタストロフィ</v>
           </cell>
         </row>
         <row r="153">
           <cell r="A153">
-            <v>100610</v>
+            <v>200230</v>
           </cell>
           <cell r="B153" t="str">
-            <v>サンフレイム</v>
+            <v>悪魔(ベリト)</v>
           </cell>
         </row>
         <row r="154">
           <cell r="A154">
-            <v>100620</v>
+            <v>200310</v>
           </cell>
           <cell r="B154" t="str">
-            <v>フレイムタン</v>
+            <v>プルガシオン</v>
           </cell>
         </row>
         <row r="155">
           <cell r="A155">
-            <v>100710</v>
+            <v>200320</v>
           </cell>
           <cell r="B155" t="str">
-            <v>ライズザフラッグ</v>
+            <v>プリエステス</v>
           </cell>
         </row>
         <row r="156">
           <cell r="A156">
-            <v>100720</v>
+            <v>200330</v>
           </cell>
           <cell r="B156" t="str">
-            <v>オーバーリミット</v>
+            <v>悪魔(パイモン)</v>
           </cell>
         </row>
         <row r="157">
           <cell r="A157">
-            <v>100810</v>
+            <v>200410</v>
           </cell>
           <cell r="B157" t="str">
-            <v>テンパランス</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="158">
           <cell r="A158">
-            <v>100820</v>
+            <v>200411</v>
           </cell>
           <cell r="B158" t="str">
-            <v>シエルクルセイダー</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="159">
           <cell r="A159">
-            <v>100910</v>
+            <v>200420</v>
           </cell>
           <cell r="B159" t="str">
-            <v>バーニングカウンター</v>
+            <v>アンチバフ</v>
           </cell>
         </row>
         <row r="160">
           <cell r="A160">
-            <v>100911</v>
+            <v>200430</v>
           </cell>
           <cell r="B160" t="str">
-            <v>バーニングカウンター</v>
+            <v>悪魔(アンドラス)</v>
           </cell>
         </row>
         <row r="161">
           <cell r="A161">
-            <v>100920</v>
+            <v>200510</v>
           </cell>
           <cell r="B161" t="str">
-            <v>プロミネンス</v>
+            <v>カウントダウン</v>
           </cell>
         </row>
         <row r="162">
           <cell r="A162">
-            <v>100921</v>
+            <v>200520</v>
           </cell>
           <cell r="B162" t="str">
-            <v>プロミネンス</v>
+            <v>グラウンドゼロ</v>
           </cell>
         </row>
         <row r="163">
           <cell r="A163">
-            <v>101010</v>
+            <v>200530</v>
           </cell>
           <cell r="B163" t="str">
-            <v>エウロス</v>
+            <v>悪魔(ビフロンス)</v>
           </cell>
         </row>
         <row r="164">
           <cell r="A164">
-            <v>101020</v>
+            <v>201010</v>
           </cell>
           <cell r="B164" t="str">
-            <v>ボレアス</v>
+            <v>カオスペイン</v>
           </cell>
         </row>
         <row r="165">
           <cell r="A165">
-            <v>101110</v>
+            <v>201020</v>
           </cell>
           <cell r="B165" t="str">
-            <v>アバランシュ</v>
+            <v>フォールンワン</v>
           </cell>
         </row>
         <row r="166">
           <cell r="A166">
-            <v>101120</v>
+            <v>201030</v>
           </cell>
           <cell r="B166" t="str">
-            <v>ブリザードコフィン</v>
+            <v>アンリマユ</v>
           </cell>
         </row>
         <row r="167">
           <cell r="A167">
-            <v>200110</v>
+            <v>300010</v>
           </cell>
           <cell r="B167" t="str">
-            <v>スリータイムス</v>
+            <v>ライフブースト</v>
           </cell>
         </row>
         <row r="168">
           <cell r="A168">
-            <v>200120</v>
+            <v>300020</v>
           </cell>
           <cell r="B168" t="str">
-            <v>アングリークライ</v>
+            <v>スピリットチャージ</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169">
-            <v>200210</v>
+            <v>300030</v>
           </cell>
           <cell r="B169" t="str">
-            <v>マイトレインフォース</v>
+            <v>フォースライズ</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170">
-            <v>200220</v>
+            <v>300040</v>
           </cell>
           <cell r="B170" t="str">
-            <v>カタストロフィ</v>
+            <v>ディフェンスオーラ</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171">
-            <v>200230</v>
+            <v>300050</v>
           </cell>
           <cell r="B171" t="str">
-            <v>悪魔(ベリト)</v>
+            <v>ラピッドムーブ</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172">
-            <v>200310</v>
+            <v>300130</v>
           </cell>
           <cell r="B172" t="str">
-            <v>プルガシオン</v>
+            <v>アタックブレイク</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173">
-            <v>200320</v>
+            <v>300140</v>
           </cell>
           <cell r="B173" t="str">
-            <v>プリエステス</v>
+            <v>シールドバニッシュ</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174">
-            <v>200330</v>
+            <v>300210</v>
           </cell>
           <cell r="B174" t="str">
-            <v>悪魔(パイモン)</v>
+            <v>エーテルリチャージ</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175">
-            <v>200410</v>
+            <v>300220</v>
           </cell>
           <cell r="B175" t="str">
-            <v>コウソクテンショウ</v>
+            <v>リカバリーエンハンス</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176">
-            <v>200411</v>
+            <v>300230</v>
           </cell>
           <cell r="B176" t="str">
-            <v>コウソクテンショウ</v>
+            <v>ヴェンジェンス</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177">
-            <v>200420</v>
+            <v>301010</v>
           </cell>
           <cell r="B177" t="str">
-            <v>アンチバフ</v>
+            <v>ディケイドリセット</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178">
-            <v>200430</v>
+            <v>301020</v>
           </cell>
           <cell r="B178" t="str">
-            <v>悪魔(アンドラス)</v>
+            <v>ウォーリアーブラッド</v>
           </cell>
         </row>
         <row r="179">
           <cell r="A179">
-            <v>200510</v>
+            <v>301030</v>
           </cell>
           <cell r="B179" t="str">
-            <v>カウントダウン</v>
+            <v>トライアングルガード</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180">
-            <v>200520</v>
+            <v>301040</v>
           </cell>
           <cell r="B180" t="str">
-            <v>グラウンドゼロ</v>
+            <v>セーフティバリア</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181">
-            <v>200530</v>
+            <v>301050</v>
           </cell>
           <cell r="B181" t="str">
-            <v>悪魔(ビフロンス)</v>
+            <v>ヒロインズハイ</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182">
-            <v>201010</v>
+            <v>301060</v>
           </cell>
           <cell r="B182" t="str">
-            <v>カオスペイン</v>
+            <v>セカンドステージ</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183">
-            <v>201020</v>
+            <v>301070</v>
           </cell>
           <cell r="B183" t="str">
-            <v>フォールンワン</v>
+            <v>ハイヒットポイント</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184">
-            <v>201030</v>
+            <v>301080</v>
           </cell>
           <cell r="B184" t="str">
-            <v>アンリマユ</v>
+            <v>セプタブラスト</v>
           </cell>
         </row>
         <row r="185">
           <cell r="A185">
-            <v>300010</v>
+            <v>301090</v>
           </cell>
           <cell r="B185" t="str">
-            <v>ライフブースト</v>
+            <v>イニシャルブロッカー</v>
           </cell>
         </row>
         <row r="186">
           <cell r="A186">
-            <v>300020</v>
+            <v>301100</v>
           </cell>
           <cell r="B186" t="str">
-            <v>スピリットチャージ</v>
+            <v>ファーストテイク</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187">
-            <v>300030</v>
+            <v>310010</v>
           </cell>
           <cell r="B187" t="str">
-            <v>フォースライズ</v>
+            <v>妖精の祈り</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188">
-            <v>300040</v>
+            <v>310020</v>
           </cell>
           <cell r="B188" t="str">
-            <v>ディフェンスオーラ</v>
+            <v>月のかけら</v>
           </cell>
         </row>
         <row r="189">
           <cell r="A189">
-            <v>300050</v>
+            <v>310030</v>
           </cell>
           <cell r="B189" t="str">
-            <v>ラピッドムーブ</v>
+            <v>商売の才覚書</v>
           </cell>
         </row>
         <row r="190">
           <cell r="A190">
-            <v>300130</v>
+            <v>310040</v>
           </cell>
           <cell r="B190" t="str">
-            <v>アタックブレイク</v>
+            <v>メビウスの砂時計</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191">
-            <v>300140</v>
+            <v>310050</v>
           </cell>
           <cell r="B191" t="str">
-            <v>シールドバニッシュ</v>
+            <v>先陣の心得</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192">
-            <v>300210</v>
+            <v>310060</v>
           </cell>
           <cell r="B192" t="str">
-            <v>エーテルリチャージ</v>
+            <v>ヒスイの勾玉</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193">
-            <v>300220</v>
+            <v>310070</v>
           </cell>
           <cell r="B193" t="str">
-            <v>リカバリーエンハンス</v>
+            <v>英傑の盾</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194">
-            <v>300230</v>
+            <v>310080</v>
           </cell>
           <cell r="B194" t="str">
-            <v>ヴェンジェンス</v>
+            <v>鷹の目</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195">
-            <v>301010</v>
+            <v>310130</v>
           </cell>
           <cell r="B195" t="str">
-            <v>ディケイドリセット</v>
+            <v>ヒールユニット</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196">
-            <v>301020</v>
+            <v>320010</v>
           </cell>
           <cell r="B196" t="str">
-            <v>ウォーリアーブラッド</v>
+            <v>訓練所Lv1</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197">
-            <v>301030</v>
+            <v>320011</v>
           </cell>
           <cell r="B197" t="str">
-            <v>トライアングルガード</v>
+            <v>訓練所Lv2</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198">
-            <v>301040</v>
+            <v>320012</v>
           </cell>
           <cell r="B198" t="str">
-            <v>セーフティバリア</v>
+            <v>訓練所Lv3</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199">
-            <v>301050</v>
+            <v>320020</v>
           </cell>
           <cell r="B199" t="str">
-            <v>ヒロインズハイ</v>
+            <v>研究施設Lv1</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200">
-            <v>301060</v>
+            <v>320021</v>
           </cell>
           <cell r="B200" t="str">
-            <v>セカンドステージ</v>
+            <v>研究施設Lv2</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201">
-            <v>301070</v>
+            <v>320022</v>
           </cell>
           <cell r="B201" t="str">
-            <v>ハイヒットポイント</v>
+            <v>研究施設Lv3</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202">
-            <v>301080</v>
+            <v>320030</v>
           </cell>
           <cell r="B202" t="str">
-            <v>セプタブラスト</v>
+            <v>資料館Lv1</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203">
-            <v>301090</v>
+            <v>320031</v>
           </cell>
           <cell r="B203" t="str">
-            <v>イニシャルブロッカー</v>
+            <v>資料館Lv2</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204">
-            <v>301100</v>
+            <v>320032</v>
           </cell>
           <cell r="B204" t="str">
-            <v>ファーストテイク</v>
+            <v>資料館Lv3</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205">
-            <v>310010</v>
+            <v>320040</v>
           </cell>
           <cell r="B205" t="str">
-            <v>妖精の祈り</v>
+            <v>潜伏技術Lv1</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206">
-            <v>310020</v>
+            <v>321010</v>
           </cell>
           <cell r="B206" t="str">
-            <v>月のかけら</v>
+            <v>炎の祭壇</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207">
-            <v>310030</v>
+            <v>321020</v>
           </cell>
           <cell r="B207" t="str">
-            <v>商売の才覚書</v>
+            <v>稲妻の祭壇</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208">
-            <v>310040</v>
+            <v>321030</v>
           </cell>
           <cell r="B208" t="str">
-            <v>メビウスの砂時計</v>
+            <v>蒼の祭壇</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209">
-            <v>310050</v>
+            <v>321040</v>
           </cell>
           <cell r="B209" t="str">
-            <v>先陣の心得</v>
+            <v>光の祭壇</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210">
-            <v>310060</v>
+            <v>321050</v>
           </cell>
           <cell r="B210" t="str">
-            <v>ヒスイの勾玉</v>
+            <v>月の祭壇</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211">
-            <v>310070</v>
+            <v>322010</v>
           </cell>
           <cell r="B211" t="str">
-            <v>英傑の盾</v>
+            <v>食糧庫Lv1</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212">
-            <v>310080</v>
+            <v>322020</v>
           </cell>
           <cell r="B212" t="str">
-            <v>鷹の目</v>
+            <v>攻撃技術Lv1</v>
           </cell>
         </row>
         <row r="213">
           <cell r="A213">
-            <v>310130</v>
+            <v>322030</v>
           </cell>
           <cell r="B213" t="str">
-            <v>ヒールユニット</v>
+            <v>防御技術Lv1</v>
           </cell>
         </row>
         <row r="214">
           <cell r="A214">
-            <v>320010</v>
+            <v>322040</v>
           </cell>
           <cell r="B214" t="str">
-            <v>訓練所Lv1</v>
+            <v>詠唱技術Lv1</v>
           </cell>
         </row>
         <row r="215">
           <cell r="A215">
-            <v>320011</v>
+            <v>401010</v>
           </cell>
           <cell r="B215" t="str">
-            <v>訓練所Lv2</v>
+            <v>ファイアボール+</v>
           </cell>
         </row>
         <row r="216">
           <cell r="A216">
-            <v>320012</v>
+            <v>401020</v>
           </cell>
           <cell r="B216" t="str">
-            <v>訓練所Lv3</v>
+            <v>バーンストーム+</v>
           </cell>
         </row>
         <row r="217">
           <cell r="A217">
-            <v>320020</v>
+            <v>401030</v>
           </cell>
           <cell r="B217" t="str">
-            <v>研究施設Lv1</v>
+            <v>ヒートスタンプ+</v>
           </cell>
         </row>
         <row r="218">
           <cell r="A218">
-            <v>320021</v>
+            <v>401040</v>
           </cell>
           <cell r="B218" t="str">
-            <v>研究施設Lv2</v>
+            <v>ソードアダプト+</v>
           </cell>
         </row>
         <row r="219">
           <cell r="A219">
-            <v>320022</v>
+            <v>401050</v>
           </cell>
           <cell r="B219" t="str">
-            <v>研究施設Lv3</v>
+            <v>フレイムレイン+</v>
           </cell>
         </row>
         <row r="220">
           <cell r="A220">
-            <v>320030</v>
+            <v>401060</v>
           </cell>
           <cell r="B220" t="str">
-            <v>資料館Lv1</v>
+            <v>イクスティンクション+</v>
           </cell>
         </row>
         <row r="221">
           <cell r="A221">
-            <v>320031</v>
+            <v>401070</v>
           </cell>
           <cell r="B221" t="str">
-            <v>資料館Lv2</v>
+            <v>バーニングソウル+</v>
           </cell>
         </row>
         <row r="222">
           <cell r="A222">
-            <v>320032</v>
+            <v>401080</v>
           </cell>
           <cell r="B222" t="str">
-            <v>資料館Lv3</v>
+            <v>レイジングバウンサー+</v>
           </cell>
         </row>
         <row r="223">
           <cell r="A223">
-            <v>320040</v>
+            <v>402010</v>
           </cell>
           <cell r="B223" t="str">
-            <v>潜伏技術Lv1</v>
+            <v>ディスチャージ+</v>
           </cell>
         </row>
         <row r="224">
           <cell r="A224">
-            <v>321010</v>
+            <v>402020</v>
           </cell>
           <cell r="B224" t="str">
-            <v>炎の祭壇</v>
+            <v>イベイドコード+</v>
           </cell>
         </row>
         <row r="225">
           <cell r="A225">
-            <v>321020</v>
+            <v>402030</v>
           </cell>
           <cell r="B225" t="str">
-            <v>稲妻の祭壇</v>
+            <v>ショックインパルス+</v>
           </cell>
         </row>
         <row r="226">
           <cell r="A226">
-            <v>321030</v>
+            <v>402040</v>
           </cell>
           <cell r="B226" t="str">
-            <v>蒼の祭壇</v>
+            <v>トラストチェイン+</v>
           </cell>
         </row>
         <row r="227">
           <cell r="A227">
-            <v>321040</v>
+            <v>402050</v>
           </cell>
           <cell r="B227" t="str">
-            <v>光の祭壇</v>
+            <v>スペルバニシング+</v>
           </cell>
         </row>
         <row r="228">
           <cell r="A228">
-            <v>321050</v>
+            <v>402060</v>
           </cell>
           <cell r="B228" t="str">
-            <v>月の祭壇</v>
+            <v>アーテニーストライク+</v>
           </cell>
         </row>
         <row r="229">
           <cell r="A229">
-            <v>322010</v>
+            <v>402070</v>
           </cell>
           <cell r="B229" t="str">
-            <v>食糧庫Lv1</v>
+            <v>コンセントレイト+</v>
           </cell>
         </row>
         <row r="230">
           <cell r="A230">
-            <v>322020</v>
+            <v>402080</v>
           </cell>
           <cell r="B230" t="str">
-            <v>攻撃技術Lv1</v>
+            <v>ディレイマジック+</v>
           </cell>
         </row>
         <row r="231">
           <cell r="A231">
-            <v>322030</v>
+            <v>403010</v>
           </cell>
           <cell r="B231" t="str">
-            <v>防御技術Lv1</v>
+            <v>アイスブレイド+</v>
           </cell>
         </row>
         <row r="232">
           <cell r="A232">
-            <v>322040</v>
+            <v>403020</v>
           </cell>
           <cell r="B232" t="str">
-            <v>詠唱技術Lv1</v>
+            <v>カウンターオーラ+</v>
           </cell>
         </row>
         <row r="233">
           <cell r="A233">
-            <v>401010</v>
+            <v>403030</v>
           </cell>
           <cell r="B233" t="str">
-            <v>ファイアボール+</v>
+            <v>ラインプロテクト+</v>
           </cell>
         </row>
         <row r="234">
           <cell r="A234">
-            <v>401020</v>
+            <v>403040</v>
           </cell>
           <cell r="B234" t="str">
-            <v>バーンストーム+</v>
+            <v>エスコートソール+</v>
           </cell>
         </row>
         <row r="235">
           <cell r="A235">
-            <v>401030</v>
+            <v>403050</v>
           </cell>
           <cell r="B235" t="str">
-            <v>ヒートスタンプ+</v>
+            <v>ディープフリーズ+</v>
           </cell>
         </row>
         <row r="236">
           <cell r="A236">
-            <v>401040</v>
+            <v>403060</v>
           </cell>
           <cell r="B236" t="str">
-            <v>ソードアダプト+</v>
+            <v>バブルブロウ+</v>
           </cell>
         </row>
         <row r="237">
           <cell r="A237">
-            <v>401050</v>
+            <v>403070</v>
           </cell>
           <cell r="B237" t="str">
-            <v>フレイムレイン+</v>
+            <v>アクアミラージュ+</v>
           </cell>
         </row>
         <row r="238">
           <cell r="A238">
-            <v>401060</v>
+            <v>403080</v>
           </cell>
           <cell r="B238" t="str">
-            <v>イクスティンクション+</v>
+            <v>フロストシールド+</v>
           </cell>
         </row>
         <row r="239">
           <cell r="A239">
-            <v>401070</v>
+            <v>404010</v>
           </cell>
           <cell r="B239" t="str">
-            <v>バーニングソウル+</v>
+            <v>セイントレーザー+</v>
           </cell>
         </row>
         <row r="240">
           <cell r="A240">
-            <v>401080</v>
+            <v>404020</v>
           </cell>
           <cell r="B240" t="str">
-            <v>レイジングバウンサー+</v>
+            <v>ペネトレイト+</v>
           </cell>
         </row>
         <row r="241">
           <cell r="A241">
-            <v>402010</v>
+            <v>404030</v>
           </cell>
           <cell r="B241" t="str">
-            <v>ディスチャージ+</v>
+            <v>ヒーリング+</v>
           </cell>
         </row>
         <row r="242">
           <cell r="A242">
-            <v>402020</v>
+            <v>404040</v>
           </cell>
           <cell r="B242" t="str">
-            <v>イベイドコード+</v>
+            <v>リザイアフォトン+</v>
           </cell>
         </row>
         <row r="243">
           <cell r="A243">
-            <v>402030</v>
+            <v>404050</v>
           </cell>
           <cell r="B243" t="str">
-            <v>ショックインパルス+</v>
+            <v>べネディクション+</v>
           </cell>
         </row>
         <row r="244">
           <cell r="A244">
-            <v>402040</v>
+            <v>404060</v>
           </cell>
           <cell r="B244" t="str">
-            <v>トラストチェイン+</v>
+            <v>ホーリーグレイス+</v>
           </cell>
         </row>
         <row r="245">
           <cell r="A245">
-            <v>402050</v>
+            <v>404070</v>
           </cell>
           <cell r="B245" t="str">
-            <v>スペルバニシング+</v>
+            <v>キュアエール+</v>
           </cell>
         </row>
         <row r="246">
           <cell r="A246">
-            <v>402060</v>
+            <v>404080</v>
           </cell>
           <cell r="B246" t="str">
-            <v>アーテニーストライク+</v>
+            <v>ラインバリア+</v>
           </cell>
         </row>
         <row r="247">
           <cell r="A247">
-            <v>402070</v>
+            <v>405010</v>
           </cell>
           <cell r="B247" t="str">
-            <v>コンセントレイト+</v>
+            <v>ダークプリズン+</v>
           </cell>
         </row>
         <row r="248">
           <cell r="A248">
-            <v>402080</v>
+            <v>405020</v>
           </cell>
           <cell r="B248" t="str">
-            <v>ディレイマジック+</v>
+            <v>ユーサネイジア+</v>
           </cell>
         </row>
         <row r="249">
           <cell r="A249">
-            <v>403010</v>
+            <v>405030</v>
           </cell>
           <cell r="B249" t="str">
-            <v>アイスブレイド+</v>
+            <v>ドレインヒール+</v>
           </cell>
         </row>
         <row r="250">
           <cell r="A250">
-            <v>403020</v>
+            <v>405040</v>
           </cell>
           <cell r="B250" t="str">
-            <v>カウンターオーラ+</v>
+            <v>アビサルデスペア+</v>
           </cell>
         </row>
         <row r="251">
           <cell r="A251">
-            <v>403030</v>
+            <v>405050</v>
           </cell>
           <cell r="B251" t="str">
-            <v>ラインプロテクト+</v>
+            <v>ディプラヴィティ+</v>
           </cell>
         </row>
         <row r="252">
           <cell r="A252">
-            <v>403040</v>
+            <v>405060</v>
           </cell>
           <cell r="B252" t="str">
-            <v>エスコートソール+</v>
+            <v>ダークネス+</v>
           </cell>
         </row>
         <row r="253">
           <cell r="A253">
-            <v>403050</v>
+            <v>405070</v>
           </cell>
           <cell r="B253" t="str">
-            <v>ディープフリーズ+</v>
+            <v>シェイディークラウド+</v>
           </cell>
         </row>
         <row r="254">
           <cell r="A254">
-            <v>403060</v>
+            <v>405080</v>
           </cell>
           <cell r="B254" t="str">
-            <v>バブルブロウ+</v>
+            <v>ポイズンブロウ+</v>
           </cell>
         </row>
         <row r="255">
           <cell r="A255">
-            <v>403070</v>
+            <v>411010</v>
           </cell>
           <cell r="B255" t="str">
-            <v>アクアミラージュ+</v>
+            <v>ウルフソウル+</v>
           </cell>
         </row>
         <row r="256">
           <cell r="A256">
-            <v>403080</v>
+            <v>411020</v>
           </cell>
           <cell r="B256" t="str">
-            <v>フロストシールド+</v>
+            <v>プリディカメント+</v>
           </cell>
         </row>
         <row r="257">
           <cell r="A257">
-            <v>404010</v>
+            <v>411030</v>
           </cell>
           <cell r="B257" t="str">
-            <v>セイントレーザー+</v>
+            <v>アサルトシフト+</v>
           </cell>
         </row>
         <row r="258">
           <cell r="A258">
-            <v>404020</v>
+            <v>411040</v>
           </cell>
           <cell r="B258" t="str">
-            <v>ペネトレイト+</v>
+            <v>アクティブギフト+</v>
           </cell>
         </row>
         <row r="259">
           <cell r="A259">
-            <v>404030</v>
+            <v>411050</v>
           </cell>
           <cell r="B259" t="str">
-            <v>ヒーリング+</v>
+            <v>イグナイテッド+</v>
           </cell>
         </row>
         <row r="260">
           <cell r="A260">
-            <v>404040</v>
+            <v>411060</v>
           </cell>
           <cell r="B260" t="str">
-            <v>リザイアフォトン+</v>
+            <v>ライジングファイア+</v>
           </cell>
         </row>
         <row r="261">
           <cell r="A261">
-            <v>404050</v>
+            <v>411070</v>
           </cell>
           <cell r="B261" t="str">
-            <v>べネディクション+</v>
+            <v>ルージュバック+</v>
           </cell>
         </row>
         <row r="262">
           <cell r="A262">
-            <v>404060</v>
+            <v>411080</v>
           </cell>
           <cell r="B262" t="str">
-            <v>ホーリーグレイス+</v>
+            <v>パワーエール+</v>
           </cell>
         </row>
         <row r="263">
           <cell r="A263">
-            <v>404070</v>
+            <v>411090</v>
           </cell>
           <cell r="B263" t="str">
-            <v>キュアエール+</v>
+            <v>スレイプニル+</v>
           </cell>
         </row>
         <row r="264">
           <cell r="A264">
-            <v>404080</v>
+            <v>412010</v>
           </cell>
           <cell r="B264" t="str">
-            <v>ラインバリア+</v>
+            <v>エクステンション+</v>
           </cell>
         </row>
         <row r="265">
           <cell r="A265">
-            <v>405010</v>
+            <v>412020</v>
           </cell>
           <cell r="B265" t="str">
-            <v>ダークプリズン+</v>
+            <v>ヘブンリーラック+</v>
           </cell>
         </row>
         <row r="266">
           <cell r="A266">
-            <v>405020</v>
+            <v>412030</v>
           </cell>
           <cell r="B266" t="str">
-            <v>ユーサネイジア+</v>
+            <v>スウィフトカレント+</v>
           </cell>
         </row>
         <row r="267">
           <cell r="A267">
-            <v>405030</v>
+            <v>412040</v>
           </cell>
           <cell r="B267" t="str">
-            <v>ドレインヒール+</v>
+            <v>イヴェイドオール+</v>
           </cell>
         </row>
         <row r="268">
           <cell r="A268">
-            <v>405040</v>
+            <v>412050</v>
           </cell>
           <cell r="B268" t="str">
-            <v>アビサルデスペア+</v>
+            <v>クイックムーブ+</v>
           </cell>
         </row>
         <row r="269">
           <cell r="A269">
-            <v>405050</v>
+            <v>412060</v>
           </cell>
           <cell r="B269" t="str">
-            <v>ディプラヴィティ+</v>
+            <v>チェイスマジック+</v>
           </cell>
         </row>
         <row r="270">
           <cell r="A270">
-            <v>405060</v>
+            <v>412070</v>
           </cell>
           <cell r="B270" t="str">
-            <v>ダークネス+</v>
+            <v>ソーサリーコネクト+</v>
           </cell>
         </row>
         <row r="271">
           <cell r="A271">
-            <v>405070</v>
+            <v>412080</v>
           </cell>
           <cell r="B271" t="str">
-            <v>シェイディークラウド+</v>
+            <v>ウィンドライズ+</v>
           </cell>
         </row>
         <row r="272">
           <cell r="A272">
-            <v>405080</v>
+            <v>412090</v>
           </cell>
           <cell r="B272" t="str">
-            <v>ポイズンブロウ+</v>
+            <v>アウトオブオーダー+</v>
           </cell>
         </row>
         <row r="273">
           <cell r="A273">
-            <v>411010</v>
+            <v>413010</v>
           </cell>
           <cell r="B273" t="str">
-            <v>ウルフソウル+</v>
+            <v>アーマーコード+</v>
           </cell>
         </row>
         <row r="274">
           <cell r="A274">
-            <v>411020</v>
+            <v>413020</v>
           </cell>
           <cell r="B274" t="str">
-            <v>プリディカメント+</v>
+            <v>クイックバリア+</v>
           </cell>
         </row>
         <row r="275">
           <cell r="A275">
-            <v>411030</v>
+            <v>413030</v>
           </cell>
           <cell r="B275" t="str">
-            <v>アサルトシフト+</v>
+            <v>クイックキュア+</v>
           </cell>
         </row>
         <row r="276">
           <cell r="A276">
-            <v>411040</v>
+            <v>413040</v>
           </cell>
           <cell r="B276" t="str">
-            <v>アクティブギフト+</v>
+            <v>セルフシールド+</v>
           </cell>
         </row>
         <row r="277">
           <cell r="A277">
-            <v>411050</v>
+            <v>413050</v>
           </cell>
           <cell r="B277" t="str">
-            <v>イグナイテッド+</v>
+            <v>パッシブジャミング+</v>
           </cell>
         </row>
         <row r="278">
           <cell r="A278">
-            <v>411060</v>
+            <v>413060</v>
           </cell>
           <cell r="B278" t="str">
-            <v>ライジングファイア+</v>
+            <v>サプライカバー+</v>
           </cell>
         </row>
         <row r="279">
           <cell r="A279">
-            <v>411070</v>
+            <v>413070</v>
           </cell>
           <cell r="B279" t="str">
-            <v>ルージュバック+</v>
+            <v>アシッドラッシュ+</v>
           </cell>
         </row>
         <row r="280">
           <cell r="A280">
-            <v>411080</v>
+            <v>413080</v>
           </cell>
           <cell r="B280" t="str">
-            <v>パワーエール+</v>
+            <v>ライフスティール+</v>
           </cell>
         </row>
         <row r="281">
           <cell r="A281">
-            <v>411090</v>
+            <v>413090</v>
           </cell>
           <cell r="B281" t="str">
-            <v>スレイプニル+</v>
+            <v>アイスセイバー+</v>
           </cell>
         </row>
         <row r="282">
           <cell r="A282">
-            <v>412010</v>
+            <v>414010</v>
           </cell>
           <cell r="B282" t="str">
-            <v>エクステンション+</v>
+            <v>ディバインシールド+</v>
           </cell>
         </row>
         <row r="283">
           <cell r="A283">
-            <v>412020</v>
+            <v>414020</v>
           </cell>
           <cell r="B283" t="str">
-            <v>ヘブンリーラック+</v>
+            <v>ライフディバイド+</v>
           </cell>
         </row>
         <row r="284">
           <cell r="A284">
-            <v>412030</v>
+            <v>414030</v>
           </cell>
           <cell r="B284" t="str">
-            <v>スウィフトカレント+</v>
+            <v>エイミングスコープ+</v>
           </cell>
         </row>
         <row r="285">
           <cell r="A285">
-            <v>412040</v>
+            <v>414040</v>
           </cell>
           <cell r="B285" t="str">
-            <v>イヴェイドオール+</v>
+            <v>リジェネレーション+</v>
           </cell>
         </row>
         <row r="286">
           <cell r="A286">
-            <v>412050</v>
+            <v>414050</v>
           </cell>
           <cell r="B286" t="str">
-            <v>クイックムーブ+</v>
+            <v>ホープフルアイリス+</v>
           </cell>
         </row>
         <row r="287">
           <cell r="A287">
-            <v>412060</v>
+            <v>414060</v>
           </cell>
           <cell r="B287" t="str">
-            <v>チェイスマジック+</v>
+            <v>パッシブサプライ+</v>
           </cell>
         </row>
         <row r="288">
           <cell r="A288">
-            <v>412070</v>
+            <v>414070</v>
           </cell>
           <cell r="B288" t="str">
-            <v>ソーサリーコネクト+</v>
+            <v>ホーミングクルセイド+</v>
           </cell>
         </row>
         <row r="289">
           <cell r="A289">
-            <v>412080</v>
+            <v>414080</v>
           </cell>
           <cell r="B289" t="str">
-            <v>ウィンドライズ+</v>
+            <v>クイックヒール+</v>
           </cell>
         </row>
         <row r="290">
           <cell r="A290">
-            <v>412090</v>
+            <v>414090</v>
           </cell>
           <cell r="B290" t="str">
-            <v>アウトオブオーダー+</v>
+            <v>リレイズ+</v>
           </cell>
         </row>
         <row r="291">
           <cell r="A291">
-            <v>413010</v>
+            <v>415010</v>
           </cell>
           <cell r="B291" t="str">
-            <v>アーマーコード+</v>
+            <v>イーグルアイ+</v>
           </cell>
         </row>
         <row r="292">
           <cell r="A292">
-            <v>413020</v>
+            <v>415020</v>
           </cell>
           <cell r="B292" t="str">
-            <v>クイックバリア+</v>
+            <v>ネヴァーエンド+</v>
           </cell>
         </row>
         <row r="293">
           <cell r="A293">
-            <v>413030</v>
+            <v>415030</v>
           </cell>
           <cell r="B293" t="str">
-            <v>クイックキュア+</v>
+            <v>グレイブアクト+</v>
           </cell>
         </row>
         <row r="294">
           <cell r="A294">
-            <v>413040</v>
+            <v>415040</v>
           </cell>
           <cell r="B294" t="str">
-            <v>セルフシールド+</v>
+            <v>スカルグラッジ+</v>
           </cell>
         </row>
         <row r="295">
           <cell r="A295">
-            <v>413050</v>
+            <v>415050</v>
           </cell>
           <cell r="B295" t="str">
-            <v>パッシブジャミング+</v>
+            <v>ネガティブドレイン+</v>
           </cell>
         </row>
         <row r="296">
           <cell r="A296">
-            <v>413060</v>
+            <v>415060</v>
           </cell>
           <cell r="B296" t="str">
-            <v>サプライカバー+</v>
+            <v>アンデッドペイン+</v>
           </cell>
         </row>
         <row r="297">
           <cell r="A297">
-            <v>413070</v>
+            <v>415070</v>
           </cell>
           <cell r="B297" t="str">
-            <v>アシッドラッシュ+</v>
+            <v>ジャックポッド+</v>
           </cell>
         </row>
         <row r="298">
           <cell r="A298">
-            <v>413080</v>
+            <v>415080</v>
           </cell>
           <cell r="B298" t="str">
-            <v>ライフスティール+</v>
+            <v>ヒールハント+</v>
           </cell>
         </row>
         <row r="299">
           <cell r="A299">
-            <v>413090</v>
+            <v>415090</v>
           </cell>
           <cell r="B299" t="str">
-            <v>アイスセイバー+</v>
-          </cell>
-        </row>
-        <row r="300">
-          <cell r="A300">
-            <v>414010</v>
-          </cell>
-          <cell r="B300" t="str">
-            <v>ディバインシールド+</v>
-          </cell>
-        </row>
-        <row r="301">
-          <cell r="A301">
-            <v>414020</v>
-          </cell>
-          <cell r="B301" t="str">
-            <v>ライフディバイド+</v>
-          </cell>
-        </row>
-        <row r="302">
-          <cell r="A302">
-            <v>414030</v>
-          </cell>
-          <cell r="B302" t="str">
-            <v>エイミングスコープ+</v>
-          </cell>
-        </row>
-        <row r="303">
-          <cell r="A303">
-            <v>414040</v>
-          </cell>
-          <cell r="B303" t="str">
-            <v>リジェネレーション+</v>
-          </cell>
-        </row>
-        <row r="304">
-          <cell r="A304">
-            <v>414050</v>
-          </cell>
-          <cell r="B304" t="str">
-            <v>ホープフルアイリス+</v>
-          </cell>
-        </row>
-        <row r="305">
-          <cell r="A305">
-            <v>414060</v>
-          </cell>
-          <cell r="B305" t="str">
-            <v>パッシブサプライ+</v>
-          </cell>
-        </row>
-        <row r="306">
-          <cell r="A306">
-            <v>414070</v>
-          </cell>
-          <cell r="B306" t="str">
-            <v>ホーミングクルセイド+</v>
-          </cell>
-        </row>
-        <row r="307">
-          <cell r="A307">
-            <v>414080</v>
-          </cell>
-          <cell r="B307" t="str">
-            <v>クイックヒール+</v>
-          </cell>
-        </row>
-        <row r="308">
-          <cell r="A308">
-            <v>414090</v>
-          </cell>
-          <cell r="B308" t="str">
-            <v>リレイズ+</v>
-          </cell>
-        </row>
-        <row r="309">
-          <cell r="A309">
-            <v>415010</v>
-          </cell>
-          <cell r="B309" t="str">
-            <v>イーグルアイ+</v>
-          </cell>
-        </row>
-        <row r="310">
-          <cell r="A310">
-            <v>415020</v>
-          </cell>
-          <cell r="B310" t="str">
-            <v>ネヴァーエンド+</v>
-          </cell>
-        </row>
-        <row r="311">
-          <cell r="A311">
-            <v>415030</v>
-          </cell>
-          <cell r="B311" t="str">
-            <v>グレイブアクト+</v>
-          </cell>
-        </row>
-        <row r="312">
-          <cell r="A312">
-            <v>415040</v>
-          </cell>
-          <cell r="B312" t="str">
-            <v>スカルグラッジ+</v>
-          </cell>
-        </row>
-        <row r="313">
-          <cell r="A313">
-            <v>415050</v>
-          </cell>
-          <cell r="B313" t="str">
-            <v>ネガティブドレイン+</v>
-          </cell>
-        </row>
-        <row r="314">
-          <cell r="A314">
-            <v>415060</v>
-          </cell>
-          <cell r="B314" t="str">
-            <v>アンデッドペイン+</v>
-          </cell>
-        </row>
-        <row r="315">
-          <cell r="A315">
-            <v>415070</v>
-          </cell>
-          <cell r="B315" t="str">
-            <v>ジャックポッド+</v>
-          </cell>
-        </row>
-        <row r="316">
-          <cell r="A316">
-            <v>415080</v>
-          </cell>
-          <cell r="B316" t="str">
-            <v>ヒールハント+</v>
-          </cell>
-        </row>
-        <row r="317">
-          <cell r="A317">
-            <v>415090</v>
-          </cell>
-          <cell r="B317" t="str">
             <v>クイックカース+</v>
           </cell>
         </row>
@@ -3927,7 +3789,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T33"/>
+  <dimension ref="A1:T34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="7.63636363636364" customWidth="1"/>
@@ -4882,10 +4744,10 @@
     </row>
     <row r="17" spans="1:19">
       <c r="A17">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="B17">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
         <v>38</v>
@@ -4894,19 +4756,19 @@
         <v>1</v>
       </c>
       <c r="E17">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I17">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J17">
         <v>3</v>
@@ -4915,7 +4777,7 @@
         <v>3</v>
       </c>
       <c r="L17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -4927,7 +4789,7 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q17">
         <v>40</v>
@@ -4941,10 +4803,10 @@
     </row>
     <row r="18" spans="1:19">
       <c r="A18">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B18">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C18" t="s">
         <v>39</v>
@@ -4959,19 +4821,19 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H18">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J18">
         <v>3</v>
       </c>
       <c r="K18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L18">
         <v>12</v>
@@ -4986,24 +4848,24 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q18">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="R18">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="S18" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:19">
       <c r="A19">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B19">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C19" t="s">
         <v>40</v>
@@ -5018,19 +4880,19 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H19">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I19">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J19">
         <v>3</v>
       </c>
       <c r="K19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L19">
         <v>12</v>
@@ -5039,30 +4901,30 @@
         <v>0</v>
       </c>
       <c r="N19">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q19">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="R19">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="S19" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:19">
       <c r="A20">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B20">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
         <v>41</v>
@@ -5077,19 +4939,19 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H20">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I20">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="J20">
         <v>3</v>
       </c>
       <c r="K20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>12</v>
@@ -5098,7 +4960,7 @@
         <v>0</v>
       </c>
       <c r="N20">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -5107,21 +4969,21 @@
         <v>80</v>
       </c>
       <c r="Q20">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R20">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="S20" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:19">
       <c r="A21">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B21">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
         <v>42</v>
@@ -5136,19 +4998,19 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H21">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I21">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="J21">
         <v>3</v>
       </c>
       <c r="K21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L21">
         <v>12</v>
@@ -5157,30 +5019,30 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="Q21">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="R21">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="S21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
       <c r="A22">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="B22">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s">
         <v>43</v>
@@ -5195,19 +5057,19 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H22">
         <v>20</v>
       </c>
       <c r="I22">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J22">
         <v>3</v>
       </c>
       <c r="K22">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L22">
         <v>12</v>
@@ -5216,36 +5078,39 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="Q22">
         <v>60</v>
       </c>
       <c r="R22">
-        <v>80</v>
+        <v>40</v>
+      </c>
+      <c r="S22" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:18">
       <c r="A23">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="B23">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="C23" t="s">
         <v>44</v>
       </c>
       <c r="D23">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E23">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -5254,66 +5119,66 @@
         <v>30</v>
       </c>
       <c r="H23">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I23">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J23">
         <v>3</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M23">
         <v>0</v>
       </c>
       <c r="N23">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
+        <v>110</v>
+      </c>
+      <c r="Q23">
         <v>60</v>
       </c>
-      <c r="Q23">
-        <v>30</v>
-      </c>
       <c r="R23">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
       <c r="A24">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B24">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C24" t="s">
         <v>45</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E24">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H24">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I24">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="J24">
         <v>3</v>
@@ -5328,51 +5193,48 @@
         <v>0</v>
       </c>
       <c r="N24">
+        <v>55</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
         <v>60</v>
       </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>40</v>
-      </c>
       <c r="Q24">
+        <v>30</v>
+      </c>
+      <c r="R24">
         <v>25</v>
-      </c>
-      <c r="R24">
-        <v>60</v>
-      </c>
-      <c r="T24" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:20">
       <c r="A25">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B25">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="E25">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H25">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I25">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="J25">
         <v>3</v>
@@ -5387,51 +5249,51 @@
         <v>0</v>
       </c>
       <c r="N25">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
+        <v>40</v>
+      </c>
+      <c r="Q25">
         <v>25</v>
       </c>
-      <c r="Q25">
-        <v>40</v>
-      </c>
       <c r="R25">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="T25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:20">
       <c r="A26">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B26">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H26">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I26">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J26">
         <v>3</v>
@@ -5452,45 +5314,45 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="Q26">
+        <v>40</v>
+      </c>
+      <c r="R26">
         <v>15</v>
       </c>
-      <c r="R26">
-        <v>20</v>
-      </c>
       <c r="T26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:20">
       <c r="A27">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B27">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
       <c r="G27">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I27">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J27">
         <v>3</v>
@@ -5505,51 +5367,51 @@
         <v>0</v>
       </c>
       <c r="N27">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="Q27">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="R27">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="T27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:20">
       <c r="A28">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B28">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
       <c r="G28">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H28">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I28">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J28">
         <v>3</v>
@@ -5564,51 +5426,51 @@
         <v>0</v>
       </c>
       <c r="N28">
+        <v>70</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>30</v>
+      </c>
+      <c r="Q28">
         <v>40</v>
       </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="P28">
-        <v>50</v>
-      </c>
-      <c r="Q28">
-        <v>50</v>
-      </c>
       <c r="R28">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="T28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:20">
       <c r="A29">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B29">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H29">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I29">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J29">
         <v>3</v>
@@ -5623,30 +5485,30 @@
         <v>0</v>
       </c>
       <c r="N29">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Q29">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="R29">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T29" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:20">
       <c r="A30">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B30">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C30" t="s">
         <v>56</v>
@@ -5655,16 +5517,16 @@
         <v>1</v>
       </c>
       <c r="E30">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H30">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I30">
         <v>16</v>
@@ -5682,30 +5544,30 @@
         <v>0</v>
       </c>
       <c r="N30">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
+        <v>45</v>
+      </c>
+      <c r="Q30">
         <v>40</v>
       </c>
-      <c r="Q30">
-        <v>60</v>
-      </c>
       <c r="R30">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="T30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:20">
       <c r="A31">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B31">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C31" t="s">
         <v>57</v>
@@ -5714,19 +5576,19 @@
         <v>1</v>
       </c>
       <c r="E31">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H31">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I31">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J31">
         <v>3</v>
@@ -5741,30 +5603,30 @@
         <v>0</v>
       </c>
       <c r="N31">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="Q31">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="R31">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="T31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:20">
       <c r="A32">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B32">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C32" t="s">
         <v>58</v>
@@ -5773,19 +5635,19 @@
         <v>1</v>
       </c>
       <c r="E32">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
       <c r="G32">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H32">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I32">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J32">
         <v>3</v>
@@ -5800,30 +5662,30 @@
         <v>0</v>
       </c>
       <c r="N32">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
+        <v>65</v>
+      </c>
+      <c r="Q32">
         <v>30</v>
       </c>
-      <c r="Q32">
-        <v>20</v>
-      </c>
       <c r="R32">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:20">
       <c r="A33">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B33">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C33" t="s">
         <v>59</v>
@@ -5832,19 +5694,19 @@
         <v>1</v>
       </c>
       <c r="E33">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="G33">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H33">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I33">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J33">
         <v>3</v>
@@ -5859,22 +5721,81 @@
         <v>0</v>
       </c>
       <c r="N33">
+        <v>45</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>30</v>
+      </c>
+      <c r="Q33">
+        <v>20</v>
+      </c>
+      <c r="R33">
+        <v>75</v>
+      </c>
+      <c r="T33" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20">
+      <c r="A34">
+        <v>1011</v>
+      </c>
+      <c r="B34">
+        <v>1011</v>
+      </c>
+      <c r="C34" t="s">
+        <v>60</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>33</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>18</v>
+      </c>
+      <c r="H34">
+        <v>17</v>
+      </c>
+      <c r="I34">
+        <v>18</v>
+      </c>
+      <c r="J34">
+        <v>3</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
         <v>65</v>
       </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
-      <c r="P33">
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
         <v>40</v>
       </c>
-      <c r="Q33">
+      <c r="Q34">
         <v>25</v>
       </c>
-      <c r="R33">
+      <c r="R34">
         <v>30</v>
       </c>
-      <c r="T33" t="s">
-        <v>54</v>
+      <c r="T34" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -5887,7 +5808,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G209"/>
+  <dimension ref="A1:G211"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="16.7272727272727" customWidth="1"/>
@@ -5895,25 +5816,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -7718,7 +7639,7 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="B77">
         <v>1010</v>
@@ -7734,7 +7655,7 @@
         <v>50</v>
       </c>
       <c r="F77">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7742,20 +7663,20 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="B78">
-        <v>200110</v>
+        <v>1060</v>
       </c>
       <c r="C78" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B78,[1]TextData!A:A))</f>
-        <v>スリータイムス</v>
+        <v>イクスティンクション</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -7769,20 +7690,20 @@
         <v>101</v>
       </c>
       <c r="B79">
-        <v>200120</v>
+        <v>1010</v>
       </c>
       <c r="C79" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B79,[1]TextData!A:A))</f>
-        <v>アングリークライ</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D79">
         <v>1</v>
       </c>
       <c r="E79">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7790,20 +7711,20 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B80">
-        <v>5010</v>
+        <v>200110</v>
       </c>
       <c r="C80" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B80,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>スリータイムス</v>
       </c>
       <c r="D80">
         <v>1</v>
       </c>
       <c r="E80">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -7814,23 +7735,23 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B81">
-        <v>5020</v>
+        <v>200120</v>
       </c>
       <c r="C81" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B81,[1]TextData!A:A))</f>
-        <v>ユーサネイジア</v>
+        <v>アングリークライ</v>
       </c>
       <c r="D81">
         <v>1</v>
       </c>
       <c r="E81">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F81">
-        <v>1013</v>
+        <v>0</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7841,17 +7762,17 @@
         <v>102</v>
       </c>
       <c r="B82">
-        <v>15050</v>
+        <v>5010</v>
       </c>
       <c r="C82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B82,[1]TextData!A:A))</f>
-        <v>ネガティブドレイン</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="D82">
         <v>1</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -7865,20 +7786,20 @@
         <v>102</v>
       </c>
       <c r="B83">
-        <v>200210</v>
+        <v>5020</v>
       </c>
       <c r="C83" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B83,[1]TextData!A:A))</f>
-        <v>マイトレインフォース</v>
+        <v>ユーサネイジア</v>
       </c>
       <c r="D83">
         <v>1</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>1013</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -7889,17 +7810,17 @@
         <v>102</v>
       </c>
       <c r="B84">
-        <v>200220</v>
+        <v>15050</v>
       </c>
       <c r="C84" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B84,[1]TextData!A:A))</f>
-        <v>カタストロフィ</v>
+        <v>ネガティブドレイン</v>
       </c>
       <c r="D84">
         <v>1</v>
       </c>
       <c r="E84">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -7913,11 +7834,11 @@
         <v>102</v>
       </c>
       <c r="B85">
-        <v>200230</v>
+        <v>200210</v>
       </c>
       <c r="C85" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B85,[1]TextData!A:A))</f>
-        <v>悪魔(ベリト)</v>
+        <v>マイトレインフォース</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -7934,20 +7855,20 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B86">
-        <v>4010</v>
+        <v>200220</v>
       </c>
       <c r="C86" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B86,[1]TextData!A:A))</f>
-        <v>セイントレーザー</v>
+        <v>カタストロフィ</v>
       </c>
       <c r="D86">
         <v>1</v>
       </c>
       <c r="E86">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -7958,23 +7879,23 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B87">
-        <v>4030</v>
+        <v>200230</v>
       </c>
       <c r="C87" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B87,[1]TextData!A:A))</f>
-        <v>ヒーリング</v>
+        <v>悪魔(ベリト)</v>
       </c>
       <c r="D87">
         <v>1</v>
       </c>
       <c r="E87">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F87">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -7985,20 +7906,20 @@
         <v>103</v>
       </c>
       <c r="B88">
-        <v>14080</v>
+        <v>4010</v>
       </c>
       <c r="C88" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B88,[1]TextData!A:A))</f>
-        <v>クイックヒール</v>
+        <v>セイントレーザー</v>
       </c>
       <c r="D88">
         <v>1</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F88">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8009,20 +7930,20 @@
         <v>103</v>
       </c>
       <c r="B89">
-        <v>200310</v>
+        <v>4030</v>
       </c>
       <c r="C89" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B89,[1]TextData!A:A))</f>
-        <v>プルガシオン</v>
+        <v>ヒーリング</v>
       </c>
       <c r="D89">
         <v>1</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F89">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8033,20 +7954,20 @@
         <v>103</v>
       </c>
       <c r="B90">
-        <v>200320</v>
+        <v>14080</v>
       </c>
       <c r="C90" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B90,[1]TextData!A:A))</f>
-        <v>プリエステス</v>
+        <v>クイックヒール</v>
       </c>
       <c r="D90">
         <v>1</v>
       </c>
       <c r="E90">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F90">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8057,11 +7978,11 @@
         <v>103</v>
       </c>
       <c r="B91">
-        <v>200330</v>
+        <v>200310</v>
       </c>
       <c r="C91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B91,[1]TextData!A:A))</f>
-        <v>悪魔(パイモン)</v>
+        <v>プルガシオン</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -8078,20 +7999,20 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B92">
-        <v>2010</v>
+        <v>200320</v>
       </c>
       <c r="C92" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B92,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>プリエステス</v>
       </c>
       <c r="D92">
         <v>1</v>
       </c>
       <c r="E92">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -8102,14 +8023,14 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B93">
-        <v>200410</v>
+        <v>200330</v>
       </c>
       <c r="C93" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B93,[1]TextData!A:A))</f>
-        <v>コウソクテンショウ</v>
+        <v>悪魔(パイモン)</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -8129,20 +8050,20 @@
         <v>104</v>
       </c>
       <c r="B94">
-        <v>200420</v>
+        <v>2010</v>
       </c>
       <c r="C94" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B94,[1]TextData!A:A))</f>
-        <v>アンチバフ</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D94">
         <v>1</v>
       </c>
       <c r="E94">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F94">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8153,11 +8074,11 @@
         <v>104</v>
       </c>
       <c r="B95">
-        <v>200430</v>
+        <v>200410</v>
       </c>
       <c r="C95" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B95,[1]TextData!A:A))</f>
-        <v>悪魔(アンドラス)</v>
+        <v>コウソクテンショウ</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -8174,23 +8095,23 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B96">
-        <v>3010</v>
+        <v>200420</v>
       </c>
       <c r="C96" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B96,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>アンチバフ</v>
       </c>
       <c r="D96">
         <v>1</v>
       </c>
       <c r="E96">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -8198,20 +8119,20 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B97">
-        <v>3070</v>
+        <v>200430</v>
       </c>
       <c r="C97" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B97,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>悪魔(アンドラス)</v>
       </c>
       <c r="D97">
         <v>1</v>
       </c>
       <c r="E97">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -8225,17 +8146,17 @@
         <v>105</v>
       </c>
       <c r="B98">
-        <v>200510</v>
+        <v>3010</v>
       </c>
       <c r="C98" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B98,[1]TextData!A:A))</f>
-        <v>カウントダウン</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D98">
         <v>1</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -8249,17 +8170,17 @@
         <v>105</v>
       </c>
       <c r="B99">
-        <v>200520</v>
+        <v>3070</v>
       </c>
       <c r="C99" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B99,[1]TextData!A:A))</f>
-        <v>グラウンドゼロ</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D99">
         <v>1</v>
       </c>
       <c r="E99">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F99">
         <v>0</v>
@@ -8273,11 +8194,11 @@
         <v>105</v>
       </c>
       <c r="B100">
-        <v>200530</v>
+        <v>200510</v>
       </c>
       <c r="C100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B100,[1]TextData!A:A))</f>
-        <v>悪魔(ビフロンス)</v>
+        <v>カウントダウン</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -8297,17 +8218,17 @@
         <v>105</v>
       </c>
       <c r="B101">
-        <v>403070</v>
+        <v>200520</v>
       </c>
       <c r="C101" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B101,[1]TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>グラウンドゼロ</v>
       </c>
       <c r="D101">
         <v>1</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -8318,20 +8239,20 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="B102">
-        <v>5010</v>
+        <v>200530</v>
       </c>
       <c r="C102" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B102,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>悪魔(ビフロンス)</v>
       </c>
       <c r="D102">
         <v>1</v>
       </c>
       <c r="E102">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -8342,20 +8263,20 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="B103">
-        <v>5020</v>
+        <v>403070</v>
       </c>
       <c r="C103" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B103,[1]TextData!A:A))</f>
-        <v>ユーサネイジア</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="D103">
         <v>1</v>
       </c>
       <c r="E103">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -8369,20 +8290,20 @@
         <v>201</v>
       </c>
       <c r="B104">
-        <v>3070</v>
+        <v>5010</v>
       </c>
       <c r="C104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B104,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="D104">
         <v>1</v>
       </c>
       <c r="E104">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F104">
-        <v>9110</v>
+        <v>0</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -8393,17 +8314,17 @@
         <v>201</v>
       </c>
       <c r="B105">
-        <v>403070</v>
+        <v>5020</v>
       </c>
       <c r="C105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B105,[1]TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>ユーサネイジア</v>
       </c>
       <c r="D105">
         <v>1</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -8417,20 +8338,20 @@
         <v>201</v>
       </c>
       <c r="B106">
-        <v>201010</v>
+        <v>3070</v>
       </c>
       <c r="C106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B106,[1]TextData!A:A))</f>
-        <v>カオスペイン</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D106">
         <v>1</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F106">
-        <v>5080</v>
+        <v>9110</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -8441,17 +8362,17 @@
         <v>201</v>
       </c>
       <c r="B107">
-        <v>201020</v>
+        <v>403070</v>
       </c>
       <c r="C107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B107,[1]TextData!A:A))</f>
-        <v>フォールンワン</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="D107">
         <v>1</v>
       </c>
       <c r="E107">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -8465,11 +8386,11 @@
         <v>201</v>
       </c>
       <c r="B108">
-        <v>201030</v>
+        <v>201010</v>
       </c>
       <c r="C108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B108,[1]TextData!A:A))</f>
-        <v>アンリマユ</v>
+        <v>カオスペイン</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -8478,7 +8399,7 @@
         <v>0</v>
       </c>
       <c r="F108">
-        <v>0</v>
+        <v>5080</v>
       </c>
       <c r="G108">
         <v>0</v>
@@ -8489,17 +8410,17 @@
         <v>201</v>
       </c>
       <c r="B109">
-        <v>405010</v>
+        <v>201020</v>
       </c>
       <c r="C109" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B109,[1]TextData!A:A))</f>
-        <v>ダークプリズン+</v>
+        <v>フォールンワン</v>
       </c>
       <c r="D109">
         <v>1</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="F109">
         <v>0</v>
@@ -8513,11 +8434,11 @@
         <v>201</v>
       </c>
       <c r="B110">
-        <v>405020</v>
+        <v>201030</v>
       </c>
       <c r="C110" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B110,[1]TextData!A:A))</f>
-        <v>ユーサネイジア+</v>
+        <v>アンリマユ</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -8537,11 +8458,11 @@
         <v>201</v>
       </c>
       <c r="B111">
-        <v>12010</v>
+        <v>405010</v>
       </c>
       <c r="C111" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B111,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>ダークプリズン+</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -8558,23 +8479,23 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="B112">
-        <v>1010</v>
+        <v>405020</v>
       </c>
       <c r="C112" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B112,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>ユーサネイジア+</v>
       </c>
       <c r="D112">
         <v>1</v>
       </c>
       <c r="E112">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F112">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G112">
         <v>0</v>
@@ -8582,23 +8503,23 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="B113">
-        <v>1060</v>
+        <v>12010</v>
       </c>
       <c r="C113" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B113,[1]TextData!A:A))</f>
-        <v>イクスティンクション</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D113">
         <v>1</v>
       </c>
       <c r="E113">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F113">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -8609,20 +8530,20 @@
         <v>1001</v>
       </c>
       <c r="B114">
-        <v>100110</v>
+        <v>1010</v>
       </c>
       <c r="C114" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B114,[1]TextData!A:A))</f>
-        <v>ソーイングアームド</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D114">
         <v>1</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F114">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G114">
         <v>0</v>
@@ -8633,20 +8554,20 @@
         <v>1001</v>
       </c>
       <c r="B115">
-        <v>100120</v>
+        <v>1060</v>
       </c>
       <c r="C115" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B115,[1]TextData!A:A))</f>
-        <v>エターナルロンド</v>
+        <v>イクスティンクション</v>
       </c>
       <c r="D115">
         <v>1</v>
       </c>
       <c r="E115">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F115">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -8657,11 +8578,11 @@
         <v>1001</v>
       </c>
       <c r="B116">
-        <v>11060</v>
+        <v>100110</v>
       </c>
       <c r="C116" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B116,[1]TextData!A:A))</f>
-        <v>ライジングファイア</v>
+        <v>ソーイングアームド</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -8681,17 +8602,17 @@
         <v>1001</v>
       </c>
       <c r="B117">
-        <v>14010</v>
+        <v>100120</v>
       </c>
       <c r="C117" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B117,[1]TextData!A:A))</f>
-        <v>ディバインシールド</v>
+        <v>エターナルロンド</v>
       </c>
       <c r="D117">
         <v>1</v>
       </c>
       <c r="E117">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F117">
         <v>0</v>
@@ -8705,11 +8626,11 @@
         <v>1001</v>
       </c>
       <c r="B118">
-        <v>12010</v>
+        <v>11060</v>
       </c>
       <c r="C118" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B118,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>ライジングファイア</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -8729,11 +8650,11 @@
         <v>1001</v>
       </c>
       <c r="B119">
-        <v>12060</v>
+        <v>14010</v>
       </c>
       <c r="C119" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B119,[1]TextData!A:A))</f>
-        <v>チェイスマジック</v>
+        <v>ディバインシールド</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -8750,23 +8671,23 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B120">
-        <v>2010</v>
+        <v>12010</v>
       </c>
       <c r="C120" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B120,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D120">
         <v>1</v>
       </c>
       <c r="E120">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F120">
-        <v>5060</v>
+        <v>0</v>
       </c>
       <c r="G120">
         <v>0</v>
@@ -8774,20 +8695,20 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B121">
-        <v>2070</v>
+        <v>12060</v>
       </c>
       <c r="C121" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B121,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>チェイスマジック</v>
       </c>
       <c r="D121">
         <v>1</v>
       </c>
       <c r="E121">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F121">
         <v>0</v>
@@ -8801,20 +8722,20 @@
         <v>1002</v>
       </c>
       <c r="B122">
-        <v>100210</v>
+        <v>2010</v>
       </c>
       <c r="C122" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B122,[1]TextData!A:A))</f>
-        <v>アブソリュートパリィ</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D122">
         <v>1</v>
       </c>
       <c r="E122">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F122">
-        <v>0</v>
+        <v>5060</v>
       </c>
       <c r="G122">
         <v>0</v>
@@ -8825,23 +8746,23 @@
         <v>1002</v>
       </c>
       <c r="B123">
-        <v>100220</v>
+        <v>2070</v>
       </c>
       <c r="C123" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B123,[1]TextData!A:A))</f>
-        <v>レヴェリー</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D123">
         <v>1</v>
       </c>
       <c r="E123">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F123">
-        <v>14211</v>
+        <v>0</v>
       </c>
       <c r="G123">
-        <v>5060</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -8849,11 +8770,11 @@
         <v>1002</v>
       </c>
       <c r="B124">
-        <v>402070</v>
+        <v>100210</v>
       </c>
       <c r="C124" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B124,[1]TextData!A:A))</f>
-        <v>コンセントレイト+</v>
+        <v>アブソリュートパリィ</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -8873,23 +8794,23 @@
         <v>1002</v>
       </c>
       <c r="B125">
-        <v>12080</v>
+        <v>100220</v>
       </c>
       <c r="C125" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B125,[1]TextData!A:A))</f>
-        <v>ウィンドライズ</v>
+        <v>レヴェリー</v>
       </c>
       <c r="D125">
         <v>1</v>
       </c>
       <c r="E125">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F125">
-        <v>0</v>
+        <v>14211</v>
       </c>
       <c r="G125">
-        <v>0</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -8897,11 +8818,11 @@
         <v>1002</v>
       </c>
       <c r="B126">
-        <v>12040</v>
+        <v>402070</v>
       </c>
       <c r="C126" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B126,[1]TextData!A:A))</f>
-        <v>イヴェイドオール</v>
+        <v>コンセントレイト+</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -8921,11 +8842,11 @@
         <v>1002</v>
       </c>
       <c r="B127">
-        <v>12050</v>
+        <v>12080</v>
       </c>
       <c r="C127" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B127,[1]TextData!A:A))</f>
-        <v>クイックムーブ</v>
+        <v>ウィンドライズ</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -8945,11 +8866,11 @@
         <v>1002</v>
       </c>
       <c r="B128">
-        <v>12010</v>
+        <v>12040</v>
       </c>
       <c r="C128" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B128,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>イヴェイドオール</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -8966,20 +8887,20 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B129">
-        <v>3010</v>
+        <v>12050</v>
       </c>
       <c r="C129" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B129,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>クイックムーブ</v>
       </c>
       <c r="D129">
         <v>1</v>
       </c>
       <c r="E129">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -8990,23 +8911,23 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B130">
-        <v>3020</v>
+        <v>12010</v>
       </c>
       <c r="C130" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B130,[1]TextData!A:A))</f>
-        <v>カウンターオーラ</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D130">
         <v>1</v>
       </c>
       <c r="E130">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F130">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G130">
         <v>0</v>
@@ -9017,17 +8938,17 @@
         <v>1003</v>
       </c>
       <c r="B131">
-        <v>100310</v>
+        <v>3010</v>
       </c>
       <c r="C131" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B131,[1]TextData!A:A))</f>
-        <v>セイクリッドバリア</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D131">
         <v>1</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F131">
         <v>0</v>
@@ -9041,20 +8962,20 @@
         <v>1003</v>
       </c>
       <c r="B132">
-        <v>100320</v>
+        <v>3020</v>
       </c>
       <c r="C132" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B132,[1]TextData!A:A))</f>
-        <v>リベンジニードル</v>
+        <v>カウンターオーラ</v>
       </c>
       <c r="D132">
         <v>1</v>
       </c>
       <c r="E132">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F132">
-        <v>14214</v>
+        <v>1023</v>
       </c>
       <c r="G132">
         <v>0</v>
@@ -9065,11 +8986,11 @@
         <v>1003</v>
       </c>
       <c r="B133">
-        <v>403020</v>
+        <v>100310</v>
       </c>
       <c r="C133" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B133,[1]TextData!A:A))</f>
-        <v>カウンターオーラ+</v>
+        <v>セイクリッドバリア</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -9089,20 +9010,20 @@
         <v>1003</v>
       </c>
       <c r="B134">
-        <v>403010</v>
+        <v>100320</v>
       </c>
       <c r="C134" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B134,[1]TextData!A:A))</f>
-        <v>アイスブレイド+</v>
+        <v>リベンジニードル</v>
       </c>
       <c r="D134">
         <v>1</v>
       </c>
       <c r="E134">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F134">
-        <v>0</v>
+        <v>14214</v>
       </c>
       <c r="G134">
         <v>0</v>
@@ -9113,11 +9034,11 @@
         <v>1003</v>
       </c>
       <c r="B135">
-        <v>13020</v>
+        <v>403020</v>
       </c>
       <c r="C135" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B135,[1]TextData!A:A))</f>
-        <v>クイックバリア</v>
+        <v>カウンターオーラ+</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -9137,11 +9058,11 @@
         <v>1003</v>
       </c>
       <c r="B136">
-        <v>13080</v>
+        <v>403010</v>
       </c>
       <c r="C136" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B136,[1]TextData!A:A))</f>
-        <v>ライフスティール</v>
+        <v>アイスブレイド+</v>
       </c>
       <c r="D136">
         <v>1</v>
@@ -9161,11 +9082,11 @@
         <v>1003</v>
       </c>
       <c r="B137">
-        <v>14050</v>
+        <v>13020</v>
       </c>
       <c r="C137" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B137,[1]TextData!A:A))</f>
-        <v>ホープフルアイリス</v>
+        <v>クイックバリア</v>
       </c>
       <c r="D137">
         <v>1</v>
@@ -9182,20 +9103,20 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B138">
-        <v>4010</v>
+        <v>13080</v>
       </c>
       <c r="C138" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B138,[1]TextData!A:A))</f>
-        <v>セイントレーザー</v>
+        <v>ライフスティール</v>
       </c>
       <c r="D138">
         <v>1</v>
       </c>
       <c r="E138">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -9206,23 +9127,23 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B139">
-        <v>4030</v>
+        <v>14050</v>
       </c>
       <c r="C139" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B139,[1]TextData!A:A))</f>
-        <v>ヒーリング</v>
+        <v>ホープフルアイリス</v>
       </c>
       <c r="D139">
         <v>1</v>
       </c>
       <c r="E139">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F139">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="G139">
         <v>0</v>
@@ -9233,17 +9154,17 @@
         <v>1004</v>
       </c>
       <c r="B140">
-        <v>100410</v>
+        <v>4010</v>
       </c>
       <c r="C140" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B140,[1]TextData!A:A))</f>
-        <v>アバンデンス</v>
+        <v>セイントレーザー</v>
       </c>
       <c r="D140">
         <v>1</v>
       </c>
       <c r="E140">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F140">
         <v>0</v>
@@ -9257,20 +9178,20 @@
         <v>1004</v>
       </c>
       <c r="B141">
-        <v>100420</v>
+        <v>4030</v>
       </c>
       <c r="C141" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B141,[1]TextData!A:A))</f>
-        <v>ハーヴェスト</v>
+        <v>ヒーリング</v>
       </c>
       <c r="D141">
         <v>1</v>
       </c>
       <c r="E141">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F141">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -9281,11 +9202,11 @@
         <v>1004</v>
       </c>
       <c r="B142">
-        <v>404030</v>
+        <v>100410</v>
       </c>
       <c r="C142" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B142,[1]TextData!A:A))</f>
-        <v>ヒーリング+</v>
+        <v>アバンデンス</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -9305,17 +9226,17 @@
         <v>1004</v>
       </c>
       <c r="B143">
-        <v>14080</v>
+        <v>100420</v>
       </c>
       <c r="C143" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B143,[1]TextData!A:A))</f>
-        <v>クイックヒール</v>
+        <v>ハーヴェスト</v>
       </c>
       <c r="D143">
         <v>1</v>
       </c>
       <c r="E143">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F143">
         <v>0</v>
@@ -9329,11 +9250,11 @@
         <v>1004</v>
       </c>
       <c r="B144">
-        <v>14010</v>
+        <v>404030</v>
       </c>
       <c r="C144" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B144,[1]TextData!A:A))</f>
-        <v>ディバインシールド</v>
+        <v>ヒーリング+</v>
       </c>
       <c r="D144">
         <v>1</v>
@@ -9342,7 +9263,7 @@
         <v>0</v>
       </c>
       <c r="F144">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G144">
         <v>0</v>
@@ -9353,11 +9274,11 @@
         <v>1004</v>
       </c>
       <c r="B145">
-        <v>14040</v>
+        <v>14080</v>
       </c>
       <c r="C145" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B145,[1]TextData!A:A))</f>
-        <v>リジェネレーション</v>
+        <v>クイックヒール</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -9377,11 +9298,11 @@
         <v>1004</v>
       </c>
       <c r="B146">
-        <v>14090</v>
+        <v>14010</v>
       </c>
       <c r="C146" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B146,[1]TextData!A:A))</f>
-        <v>リレイズ</v>
+        <v>ディバインシールド</v>
       </c>
       <c r="D146">
         <v>1</v>
@@ -9390,7 +9311,7 @@
         <v>0</v>
       </c>
       <c r="F146">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G146">
         <v>0</v>
@@ -9398,20 +9319,20 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B147">
-        <v>5010</v>
+        <v>14040</v>
       </c>
       <c r="C147" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B147,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>リジェネレーション</v>
       </c>
       <c r="D147">
         <v>1</v>
       </c>
       <c r="E147">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F147">
         <v>0</v>
@@ -9422,23 +9343,23 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B148">
-        <v>5070</v>
+        <v>14090</v>
       </c>
       <c r="C148" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B148,[1]TextData!A:A))</f>
-        <v>シェイディークラウド</v>
+        <v>リレイズ</v>
       </c>
       <c r="D148">
         <v>1</v>
       </c>
       <c r="E148">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F148">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -9449,17 +9370,17 @@
         <v>1005</v>
       </c>
       <c r="B149">
-        <v>100510</v>
+        <v>5010</v>
       </c>
       <c r="C149" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B149,[1]TextData!A:A))</f>
-        <v>カースドブレイク</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="D149">
         <v>1</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F149">
         <v>0</v>
@@ -9473,20 +9394,20 @@
         <v>1005</v>
       </c>
       <c r="B150">
-        <v>100520</v>
+        <v>5070</v>
       </c>
       <c r="C150" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B150,[1]TextData!A:A))</f>
-        <v>ムーンライトレイ</v>
+        <v>シェイディークラウド</v>
       </c>
       <c r="D150">
         <v>1</v>
       </c>
       <c r="E150">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F150">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G150">
         <v>0</v>
@@ -9497,11 +9418,11 @@
         <v>1005</v>
       </c>
       <c r="B151">
-        <v>15090</v>
+        <v>100510</v>
       </c>
       <c r="C151" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B151,[1]TextData!A:A))</f>
-        <v>クイックカース</v>
+        <v>カースドブレイク</v>
       </c>
       <c r="D151">
         <v>1</v>
@@ -9521,17 +9442,17 @@
         <v>1005</v>
       </c>
       <c r="B152">
-        <v>405070</v>
+        <v>100520</v>
       </c>
       <c r="C152" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B152,[1]TextData!A:A))</f>
-        <v>シェイディークラウド+</v>
+        <v>ムーンライトレイ</v>
       </c>
       <c r="D152">
         <v>1</v>
       </c>
       <c r="E152">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F152">
         <v>0</v>
@@ -9545,11 +9466,11 @@
         <v>1005</v>
       </c>
       <c r="B153">
-        <v>15080</v>
+        <v>15090</v>
       </c>
       <c r="C153" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B153,[1]TextData!A:A))</f>
-        <v>ヒールハント</v>
+        <v>クイックカース</v>
       </c>
       <c r="D153">
         <v>1</v>
@@ -9569,11 +9490,11 @@
         <v>1005</v>
       </c>
       <c r="B154">
-        <v>405010</v>
+        <v>405070</v>
       </c>
       <c r="C154" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B154,[1]TextData!A:A))</f>
-        <v>ダークプリズン+</v>
+        <v>シェイディークラウド+</v>
       </c>
       <c r="D154">
         <v>1</v>
@@ -9593,11 +9514,11 @@
         <v>1005</v>
       </c>
       <c r="B155">
-        <v>415090</v>
+        <v>15080</v>
       </c>
       <c r="C155" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B155,[1]TextData!A:A))</f>
-        <v>クイックカース+</v>
+        <v>ヒールハント</v>
       </c>
       <c r="D155">
         <v>1</v>
@@ -9614,20 +9535,20 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B156">
-        <v>1010</v>
+        <v>405010</v>
       </c>
       <c r="C156" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B156,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>ダークプリズン+</v>
       </c>
       <c r="D156">
         <v>1</v>
       </c>
       <c r="E156">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -9638,26 +9559,26 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B157">
-        <v>1030</v>
+        <v>415090</v>
       </c>
       <c r="C157" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B157,[1]TextData!A:A))</f>
-        <v>ヒートスタンプ</v>
+        <v>クイックカース+</v>
       </c>
       <c r="D157">
         <v>1</v>
       </c>
       <c r="E157">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F157">
-        <v>9120</v>
+        <v>0</v>
       </c>
       <c r="G157">
-        <v>1023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -9665,20 +9586,20 @@
         <v>1006</v>
       </c>
       <c r="B158">
-        <v>1070</v>
+        <v>1010</v>
       </c>
       <c r="C158" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B158,[1]TextData!A:A))</f>
-        <v>バーニングソウル</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D158">
         <v>1</v>
       </c>
       <c r="E158">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F158">
-        <v>6322</v>
+        <v>0</v>
       </c>
       <c r="G158">
         <v>0</v>
@@ -9689,23 +9610,23 @@
         <v>1006</v>
       </c>
       <c r="B159">
-        <v>100610</v>
+        <v>1030</v>
       </c>
       <c r="C159" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B159,[1]TextData!A:A))</f>
-        <v>サンフレイム</v>
+        <v>ヒートスタンプ</v>
       </c>
       <c r="D159">
         <v>1</v>
       </c>
       <c r="E159">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F159">
-        <v>0</v>
+        <v>9120</v>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -9713,20 +9634,20 @@
         <v>1006</v>
       </c>
       <c r="B160">
-        <v>100620</v>
+        <v>1070</v>
       </c>
       <c r="C160" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B160,[1]TextData!A:A))</f>
-        <v>フレイムタン</v>
+        <v>バーニングソウル</v>
       </c>
       <c r="D160">
         <v>1</v>
       </c>
       <c r="E160">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F160">
-        <v>0</v>
+        <v>6322</v>
       </c>
       <c r="G160">
         <v>0</v>
@@ -9737,11 +9658,11 @@
         <v>1006</v>
       </c>
       <c r="B161">
-        <v>11040</v>
+        <v>100610</v>
       </c>
       <c r="C161" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B161,[1]TextData!A:A))</f>
-        <v>アクティブギフト</v>
+        <v>サンフレイム</v>
       </c>
       <c r="D161">
         <v>1</v>
@@ -9750,7 +9671,7 @@
         <v>0</v>
       </c>
       <c r="F161">
-        <v>5042</v>
+        <v>0</v>
       </c>
       <c r="G161">
         <v>0</v>
@@ -9761,17 +9682,17 @@
         <v>1006</v>
       </c>
       <c r="B162">
-        <v>401030</v>
+        <v>100620</v>
       </c>
       <c r="C162" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B162,[1]TextData!A:A))</f>
-        <v>ヒートスタンプ+</v>
+        <v>フレイムタン</v>
       </c>
       <c r="D162">
         <v>1</v>
       </c>
       <c r="E162">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F162">
         <v>0</v>
@@ -9785,11 +9706,11 @@
         <v>1006</v>
       </c>
       <c r="B163">
-        <v>411040</v>
+        <v>11040</v>
       </c>
       <c r="C163" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B163,[1]TextData!A:A))</f>
-        <v>アクティブギフト+</v>
+        <v>アクティブギフト</v>
       </c>
       <c r="D163">
         <v>1</v>
@@ -9798,7 +9719,7 @@
         <v>0</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>5042</v>
       </c>
       <c r="G163">
         <v>0</v>
@@ -9809,11 +9730,11 @@
         <v>1006</v>
       </c>
       <c r="B164">
-        <v>13040</v>
+        <v>401030</v>
       </c>
       <c r="C164" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B164,[1]TextData!A:A))</f>
-        <v>セルフシールド</v>
+        <v>ヒートスタンプ+</v>
       </c>
       <c r="D164">
         <v>1</v>
@@ -9830,20 +9751,20 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B165">
-        <v>2010</v>
+        <v>411040</v>
       </c>
       <c r="C165" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B165,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>アクティブギフト+</v>
       </c>
       <c r="D165">
         <v>1</v>
       </c>
       <c r="E165">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F165">
         <v>0</v>
@@ -9854,23 +9775,23 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B166">
-        <v>2040</v>
+        <v>13040</v>
       </c>
       <c r="C166" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B166,[1]TextData!A:A))</f>
-        <v>トラストチェイン</v>
+        <v>セルフシールド</v>
       </c>
       <c r="D166">
         <v>1</v>
       </c>
       <c r="E166">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F166">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G166">
         <v>0</v>
@@ -9881,17 +9802,17 @@
         <v>1007</v>
       </c>
       <c r="B167">
-        <v>100710</v>
+        <v>2010</v>
       </c>
       <c r="C167" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B167,[1]TextData!A:A))</f>
-        <v>ライズザフラッグ</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D167">
         <v>1</v>
       </c>
       <c r="E167">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F167">
         <v>0</v>
@@ -9905,20 +9826,20 @@
         <v>1007</v>
       </c>
       <c r="B168">
-        <v>100720</v>
+        <v>2040</v>
       </c>
       <c r="C168" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B168,[1]TextData!A:A))</f>
-        <v>オーバーリミット</v>
+        <v>トラストチェイン</v>
       </c>
       <c r="D168">
         <v>1</v>
       </c>
       <c r="E168">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F168">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G168">
         <v>0</v>
@@ -9929,11 +9850,11 @@
         <v>1007</v>
       </c>
       <c r="B169">
-        <v>12090</v>
+        <v>100710</v>
       </c>
       <c r="C169" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B169,[1]TextData!A:A))</f>
-        <v>アウトオブオーダー</v>
+        <v>ライズザフラッグ</v>
       </c>
       <c r="D169">
         <v>1</v>
@@ -9942,7 +9863,7 @@
         <v>0</v>
       </c>
       <c r="F169">
-        <v>5042</v>
+        <v>0</v>
       </c>
       <c r="G169">
         <v>0</v>
@@ -9953,17 +9874,17 @@
         <v>1007</v>
       </c>
       <c r="B170">
-        <v>412090</v>
+        <v>100720</v>
       </c>
       <c r="C170" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B170,[1]TextData!A:A))</f>
-        <v>アウトオブオーダー+</v>
+        <v>オーバーリミット</v>
       </c>
       <c r="D170">
         <v>1</v>
       </c>
       <c r="E170">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F170">
         <v>0</v>
@@ -9977,11 +9898,11 @@
         <v>1007</v>
       </c>
       <c r="B171">
-        <v>12050</v>
+        <v>12090</v>
       </c>
       <c r="C171" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B171,[1]TextData!A:A))</f>
-        <v>クイックムーブ</v>
+        <v>アウトオブオーダー</v>
       </c>
       <c r="D171">
         <v>1</v>
@@ -9990,7 +9911,7 @@
         <v>0</v>
       </c>
       <c r="F171">
-        <v>0</v>
+        <v>5042</v>
       </c>
       <c r="G171">
         <v>0</v>
@@ -10001,11 +9922,11 @@
         <v>1007</v>
       </c>
       <c r="B172">
-        <v>12070</v>
+        <v>412090</v>
       </c>
       <c r="C172" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B172,[1]TextData!A:A))</f>
-        <v>ソーサリーコネクト</v>
+        <v>アウトオブオーダー+</v>
       </c>
       <c r="D172">
         <v>1</v>
@@ -10025,11 +9946,11 @@
         <v>1007</v>
       </c>
       <c r="B173">
-        <v>14030</v>
+        <v>12050</v>
       </c>
       <c r="C173" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B173,[1]TextData!A:A))</f>
-        <v>エイミングスコープ</v>
+        <v>クイックムーブ</v>
       </c>
       <c r="D173">
         <v>1</v>
@@ -10046,20 +9967,20 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B174">
-        <v>3010</v>
+        <v>12070</v>
       </c>
       <c r="C174" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B174,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>ソーサリーコネクト</v>
       </c>
       <c r="D174">
         <v>1</v>
       </c>
       <c r="E174">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F174">
         <v>0</v>
@@ -10070,20 +9991,20 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B175">
-        <v>3070</v>
+        <v>14030</v>
       </c>
       <c r="C175" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B175,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>エイミングスコープ</v>
       </c>
       <c r="D175">
         <v>1</v>
       </c>
       <c r="E175">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -10097,17 +10018,17 @@
         <v>1008</v>
       </c>
       <c r="B176">
-        <v>100810</v>
+        <v>3010</v>
       </c>
       <c r="C176" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B176,[1]TextData!A:A))</f>
-        <v>テンパランス</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D176">
         <v>1</v>
       </c>
       <c r="E176">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F176">
         <v>0</v>
@@ -10121,17 +10042,17 @@
         <v>1008</v>
       </c>
       <c r="B177">
-        <v>100820</v>
+        <v>3070</v>
       </c>
       <c r="C177" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B177,[1]TextData!A:A))</f>
-        <v>シエルクルセイダー</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D177">
         <v>1</v>
       </c>
       <c r="E177">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F177">
         <v>0</v>
@@ -10145,11 +10066,11 @@
         <v>1008</v>
       </c>
       <c r="B178">
-        <v>13060</v>
+        <v>100810</v>
       </c>
       <c r="C178" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B178,[1]TextData!A:A))</f>
-        <v>サプライカバー</v>
+        <v>テンパランス</v>
       </c>
       <c r="D178">
         <v>1</v>
@@ -10158,7 +10079,7 @@
         <v>0</v>
       </c>
       <c r="F178">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G178">
         <v>0</v>
@@ -10169,17 +10090,17 @@
         <v>1008</v>
       </c>
       <c r="B179">
-        <v>403070</v>
+        <v>100820</v>
       </c>
       <c r="C179" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B179,[1]TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>シエルクルセイダー</v>
       </c>
       <c r="D179">
         <v>1</v>
       </c>
       <c r="E179">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F179">
         <v>0</v>
@@ -10193,11 +10114,11 @@
         <v>1008</v>
       </c>
       <c r="B180">
-        <v>13010</v>
+        <v>13060</v>
       </c>
       <c r="C180" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B180,[1]TextData!A:A))</f>
-        <v>アーマーコード</v>
+        <v>サプライカバー</v>
       </c>
       <c r="D180">
         <v>1</v>
@@ -10206,7 +10127,7 @@
         <v>0</v>
       </c>
       <c r="F180">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G180">
         <v>0</v>
@@ -10217,11 +10138,11 @@
         <v>1008</v>
       </c>
       <c r="B181">
-        <v>13020</v>
+        <v>403070</v>
       </c>
       <c r="C181" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B181,[1]TextData!A:A))</f>
-        <v>クイックバリア</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="D181">
         <v>1</v>
@@ -10241,11 +10162,11 @@
         <v>1008</v>
       </c>
       <c r="B182">
-        <v>13040</v>
+        <v>13010</v>
       </c>
       <c r="C182" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B182,[1]TextData!A:A))</f>
-        <v>セルフシールド</v>
+        <v>アーマーコード</v>
       </c>
       <c r="D182">
         <v>1</v>
@@ -10262,20 +10183,20 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B183">
-        <v>1010</v>
+        <v>13020</v>
       </c>
       <c r="C183" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B183,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>クイックバリア</v>
       </c>
       <c r="D183">
         <v>1</v>
       </c>
       <c r="E183">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F183">
         <v>0</v>
@@ -10286,23 +10207,23 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B184">
-        <v>1050</v>
+        <v>13040</v>
       </c>
       <c r="C184" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B184,[1]TextData!A:A))</f>
-        <v>フレイムレイン</v>
+        <v>セルフシールド</v>
       </c>
       <c r="D184">
         <v>1</v>
       </c>
       <c r="E184">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F184">
-        <v>1151</v>
+        <v>0</v>
       </c>
       <c r="G184">
         <v>0</v>
@@ -10313,17 +10234,17 @@
         <v>1009</v>
       </c>
       <c r="B185">
-        <v>100910</v>
+        <v>1010</v>
       </c>
       <c r="C185" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B185,[1]TextData!A:A))</f>
-        <v>バーニングカウンター</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D185">
         <v>1</v>
       </c>
       <c r="E185">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F185">
         <v>0</v>
@@ -10337,20 +10258,20 @@
         <v>1009</v>
       </c>
       <c r="B186">
-        <v>100920</v>
+        <v>1050</v>
       </c>
       <c r="C186" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B186,[1]TextData!A:A))</f>
-        <v>プロミネンス</v>
+        <v>フレイムレイン</v>
       </c>
       <c r="D186">
         <v>1</v>
       </c>
       <c r="E186">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F186">
-        <v>0</v>
+        <v>1151</v>
       </c>
       <c r="G186">
         <v>0</v>
@@ -10361,11 +10282,11 @@
         <v>1009</v>
       </c>
       <c r="B187">
-        <v>11070</v>
+        <v>100910</v>
       </c>
       <c r="C187" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B187,[1]TextData!A:A))</f>
-        <v>ルージュバック</v>
+        <v>バーニングカウンター</v>
       </c>
       <c r="D187">
         <v>1</v>
@@ -10385,17 +10306,17 @@
         <v>1009</v>
       </c>
       <c r="B188">
-        <v>401050</v>
+        <v>100920</v>
       </c>
       <c r="C188" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B188,[1]TextData!A:A))</f>
-        <v>フレイムレイン+</v>
+        <v>プロミネンス</v>
       </c>
       <c r="D188">
         <v>1</v>
       </c>
       <c r="E188">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F188">
         <v>0</v>
@@ -10409,11 +10330,11 @@
         <v>1009</v>
       </c>
       <c r="B189">
-        <v>11030</v>
+        <v>11070</v>
       </c>
       <c r="C189" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B189,[1]TextData!A:A))</f>
-        <v>アサルトシフト</v>
+        <v>ルージュバック</v>
       </c>
       <c r="D189">
         <v>1</v>
@@ -10433,11 +10354,11 @@
         <v>1009</v>
       </c>
       <c r="B190">
-        <v>11020</v>
+        <v>401050</v>
       </c>
       <c r="C190" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B190,[1]TextData!A:A))</f>
-        <v>プリディカメント</v>
+        <v>フレイムレイン+</v>
       </c>
       <c r="D190">
         <v>1</v>
@@ -10457,11 +10378,11 @@
         <v>1009</v>
       </c>
       <c r="B191">
-        <v>15040</v>
+        <v>11030</v>
       </c>
       <c r="C191" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B191,[1]TextData!A:A))</f>
-        <v>スカルグラッジ</v>
+        <v>アサルトシフト</v>
       </c>
       <c r="D191">
         <v>1</v>
@@ -10478,20 +10399,20 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B192">
-        <v>2010</v>
+        <v>11020</v>
       </c>
       <c r="C192" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B192,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>プリディカメント</v>
       </c>
       <c r="D192">
         <v>1</v>
       </c>
       <c r="E192">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F192">
         <v>0</v>
@@ -10502,23 +10423,23 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B193">
-        <v>2030</v>
+        <v>15040</v>
       </c>
       <c r="C193" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B193,[1]TextData!A:A))</f>
-        <v>ショックインパルス</v>
+        <v>スカルグラッジ</v>
       </c>
       <c r="D193">
         <v>1</v>
       </c>
       <c r="E193">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F193">
-        <v>14215</v>
+        <v>0</v>
       </c>
       <c r="G193">
         <v>0</v>
@@ -10529,17 +10450,17 @@
         <v>1010</v>
       </c>
       <c r="B194">
-        <v>101010</v>
+        <v>2010</v>
       </c>
       <c r="C194" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B194,[1]TextData!A:A))</f>
-        <v>エウロス</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D194">
         <v>1</v>
       </c>
       <c r="E194">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F194">
         <v>0</v>
@@ -10553,20 +10474,20 @@
         <v>1010</v>
       </c>
       <c r="B195">
-        <v>101020</v>
+        <v>2030</v>
       </c>
       <c r="C195" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B195,[1]TextData!A:A))</f>
-        <v>ボレアス</v>
+        <v>ショックインパルス</v>
       </c>
       <c r="D195">
         <v>1</v>
       </c>
       <c r="E195">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F195">
-        <v>0</v>
+        <v>14215</v>
       </c>
       <c r="G195">
         <v>0</v>
@@ -10577,11 +10498,11 @@
         <v>1010</v>
       </c>
       <c r="B196">
-        <v>12010</v>
+        <v>101010</v>
       </c>
       <c r="C196" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B196,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>エウロス</v>
       </c>
       <c r="D196">
         <v>1</v>
@@ -10601,17 +10522,17 @@
         <v>1010</v>
       </c>
       <c r="B197">
-        <v>402030</v>
+        <v>101020</v>
       </c>
       <c r="C197" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B197,[1]TextData!A:A))</f>
-        <v>ショックインパルス+</v>
+        <v>ボレアス</v>
       </c>
       <c r="D197">
         <v>1</v>
       </c>
       <c r="E197">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F197">
         <v>0</v>
@@ -10625,11 +10546,11 @@
         <v>1010</v>
       </c>
       <c r="B198">
-        <v>12020</v>
+        <v>12010</v>
       </c>
       <c r="C198" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B198,[1]TextData!A:A))</f>
-        <v>ヘブンリーラック</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D198">
         <v>1</v>
@@ -10649,11 +10570,11 @@
         <v>1010</v>
       </c>
       <c r="B199">
-        <v>12030</v>
+        <v>402030</v>
       </c>
       <c r="C199" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B199,[1]TextData!A:A))</f>
-        <v>スウィフトカレント</v>
+        <v>ショックインパルス+</v>
       </c>
       <c r="D199">
         <v>1</v>
@@ -10673,11 +10594,11 @@
         <v>1010</v>
       </c>
       <c r="B200">
-        <v>15070</v>
+        <v>12020</v>
       </c>
       <c r="C200" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B200,[1]TextData!A:A))</f>
-        <v>ジャックポッド</v>
+        <v>ヘブンリーラック</v>
       </c>
       <c r="D200">
         <v>1</v>
@@ -10694,20 +10615,20 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B201">
-        <v>3010</v>
+        <v>12030</v>
       </c>
       <c r="C201" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B201,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>スウィフトカレント</v>
       </c>
       <c r="D201">
         <v>1</v>
       </c>
       <c r="E201">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F201">
         <v>0</v>
@@ -10718,20 +10639,20 @@
     </row>
     <row r="202" spans="1:7">
       <c r="A202">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B202">
-        <v>3050</v>
+        <v>15070</v>
       </c>
       <c r="C202" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B202,[1]TextData!A:A))</f>
-        <v>ディープフリーズ</v>
+        <v>ジャックポッド</v>
       </c>
       <c r="D202">
         <v>1</v>
       </c>
       <c r="E202">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F202">
         <v>0</v>
@@ -10745,17 +10666,17 @@
         <v>1011</v>
       </c>
       <c r="B203">
-        <v>101110</v>
+        <v>3010</v>
       </c>
       <c r="C203" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B203,[1]TextData!A:A))</f>
-        <v>アバランシュ</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D203">
         <v>1</v>
       </c>
       <c r="E203">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F203">
         <v>0</v>
@@ -10769,17 +10690,17 @@
         <v>1011</v>
       </c>
       <c r="B204">
-        <v>101120</v>
+        <v>3050</v>
       </c>
       <c r="C204" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B204,[1]TextData!A:A))</f>
-        <v>ブリザードコフィン</v>
+        <v>ディープフリーズ</v>
       </c>
       <c r="D204">
         <v>1</v>
       </c>
       <c r="E204">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F204">
         <v>0</v>
@@ -10793,11 +10714,11 @@
         <v>1011</v>
       </c>
       <c r="B205">
-        <v>13090</v>
+        <v>101110</v>
       </c>
       <c r="C205" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B205,[1]TextData!A:A))</f>
-        <v>アイスセイバー</v>
+        <v>アバランシュ</v>
       </c>
       <c r="D205">
         <v>1</v>
@@ -10817,17 +10738,17 @@
         <v>1011</v>
       </c>
       <c r="B206">
-        <v>403050</v>
+        <v>101120</v>
       </c>
       <c r="C206" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B206,[1]TextData!A:A))</f>
-        <v>ディープフリーズ+</v>
+        <v>ブリザードコフィン</v>
       </c>
       <c r="D206">
         <v>1</v>
       </c>
       <c r="E206">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F206">
         <v>0</v>
@@ -10841,11 +10762,11 @@
         <v>1011</v>
       </c>
       <c r="B207">
-        <v>13050</v>
+        <v>13090</v>
       </c>
       <c r="C207" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B207,[1]TextData!A:A))</f>
-        <v>パッシブジャミング</v>
+        <v>アイスセイバー</v>
       </c>
       <c r="D207">
         <v>1</v>
@@ -10865,11 +10786,11 @@
         <v>1011</v>
       </c>
       <c r="B208">
-        <v>13070</v>
+        <v>403050</v>
       </c>
       <c r="C208" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B208,[1]TextData!A:A))</f>
-        <v>アシッドラッシュ</v>
+        <v>ディープフリーズ+</v>
       </c>
       <c r="D208">
         <v>1</v>
@@ -10889,22 +10810,70 @@
         <v>1011</v>
       </c>
       <c r="B209">
-        <v>14070</v>
+        <v>13050</v>
       </c>
       <c r="C209" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B209,[1]TextData!A:A))</f>
+        <v>パッシブジャミング</v>
+      </c>
+      <c r="D209">
+        <v>1</v>
+      </c>
+      <c r="E209">
+        <v>0</v>
+      </c>
+      <c r="F209">
+        <v>0</v>
+      </c>
+      <c r="G209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7">
+      <c r="A210">
+        <v>1011</v>
+      </c>
+      <c r="B210">
+        <v>13070</v>
+      </c>
+      <c r="C210" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B210,[1]TextData!A:A))</f>
+        <v>アシッドラッシュ</v>
+      </c>
+      <c r="D210">
+        <v>1</v>
+      </c>
+      <c r="E210">
+        <v>0</v>
+      </c>
+      <c r="F210">
+        <v>0</v>
+      </c>
+      <c r="G210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7">
+      <c r="A211">
+        <v>1011</v>
+      </c>
+      <c r="B211">
+        <v>14070</v>
+      </c>
+      <c r="C211" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B211,[1]TextData!A:A))</f>
         <v>ホーミングクルセイド</v>
       </c>
-      <c r="D209">
-        <v>1</v>
-      </c>
-      <c r="E209">
-        <v>0</v>
-      </c>
-      <c r="F209">
-        <v>0</v>
-      </c>
-      <c r="G209">
+      <c r="D211">
+        <v>1</v>
+      </c>
+      <c r="E211">
+        <v>0</v>
+      </c>
+      <c r="F211">
+        <v>0</v>
+      </c>
+      <c r="G211">
         <v>0</v>
       </c>
     </row>
@@ -10922,25 +10891,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -11205,7 +11174,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="1"/>
   <cols>
     <col min="2" max="2" width="13.5454545454545" customWidth="1"/>
@@ -11216,7 +11185,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -11224,7 +11193,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -11232,7 +11201,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -11240,7 +11209,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -11248,7 +11217,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -11256,7 +11225,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -11264,7 +11233,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -11272,7 +11241,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -11280,7 +11249,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -11288,7 +11257,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -11296,7 +11265,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -11304,7 +11273,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -11312,7 +11281,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -11320,7 +11289,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -11328,7 +11297,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -11336,215 +11305,223 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>201</v>
+        <v>107</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>301</v>
+        <v>207</v>
       </c>
       <c r="B31" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>1001</v>
+        <v>301</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B36" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B37" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B39" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B40" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
+        <v>1010</v>
+      </c>
+      <c r="B42" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
         <v>1011</v>
       </c>
-      <c r="B42" t="s">
-        <v>112</v>
+      <c r="B43" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -11561,7 +11538,7 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="2:3">
@@ -11569,7 +11546,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="2:3">
@@ -11577,7 +11554,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="2:3">
@@ -11585,7 +11562,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="2:3">
@@ -11593,7 +11570,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="2:3">
@@ -11601,7 +11578,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="2:3">
@@ -11609,7 +11586,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="2:3">
@@ -11617,7 +11594,7 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="2:3">
@@ -11625,7 +11602,7 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="7960"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
     <t>SpdGrowth</t>
   </si>
   <si>
-    <t>Jelslime</t>
+    <t>basic enemy_084</t>
   </si>
   <si>
     <t>氷</t>
@@ -89,7 +89,7 @@
     <t>闇</t>
   </si>
   <si>
-    <t>Bee</t>
+    <t>basic enemy_097</t>
   </si>
   <si>
     <t>雷</t>
@@ -104,7 +104,7 @@
     <t>Crow</t>
   </si>
   <si>
-    <t>Nameless</t>
+    <t>NY_CJ_monster_010_3</t>
   </si>
   <si>
     <t>Seacher</t>
@@ -125,7 +125,7 @@
     <t>Creeper</t>
   </si>
   <si>
-    <t>Imp</t>
+    <t>NY_CJ_monster_015_1</t>
   </si>
   <si>
     <t>白</t>
@@ -401,8 +401,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -422,7 +422,35 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -437,43 +465,15 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -482,15 +482,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -504,16 +496,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -529,23 +520,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -558,10 +541,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -574,7 +574,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,13 +634,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -604,85 +718,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -694,43 +736,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -742,19 +748,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -765,24 +765,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -801,16 +783,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -831,26 +813,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -865,6 +832,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -873,7 +873,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -882,7 +882,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -891,127 +891,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7960"/>
+    <workbookView windowWidth="19200" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="128">
   <si>
     <t>Id</t>
   </si>
@@ -206,6 +206,12 @@
     <t>Actor0011</t>
   </si>
   <si>
+    <t>Actor0101</t>
+  </si>
+  <si>
+    <t>Actor0102</t>
+  </si>
+  <si>
     <t>EnemyId</t>
   </si>
   <si>
@@ -366,6 +372,12 @@
   </si>
   <si>
     <t>セリナ</t>
+  </si>
+  <si>
+    <t>シグルド</t>
+  </si>
+  <si>
+    <t>ブリュンヒルデ</t>
   </si>
   <si>
     <t>Kind</t>
@@ -400,10 +412,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -422,13 +434,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -436,7 +441,46 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -444,13 +488,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -466,7 +503,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -477,29 +521,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -519,16 +540,31 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -538,30 +574,6 @@
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -574,13 +586,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -592,19 +622,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -616,19 +640,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -646,25 +670,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -676,7 +682,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -688,7 +700,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -700,7 +718,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -712,49 +754,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -765,36 +777,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -816,18 +798,7 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -848,10 +819,27 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -865,6 +853,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -873,145 +885,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1034,12 +1046,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -1556,7 +1568,7 @@
             <v>10110</v>
           </cell>
           <cell r="B57" t="str">
-            <v>炎の加護</v>
+            <v>先天属性・炎</v>
           </cell>
         </row>
         <row r="58">
@@ -1564,7 +1576,7 @@
             <v>10120</v>
           </cell>
           <cell r="B58" t="str">
-            <v>雷の加護</v>
+            <v>先天属性・雷</v>
           </cell>
         </row>
         <row r="59">
@@ -1572,7 +1584,7 @@
             <v>10130</v>
           </cell>
           <cell r="B59" t="str">
-            <v>氷の加護</v>
+            <v>先天属性・氷</v>
           </cell>
         </row>
         <row r="60">
@@ -1580,7 +1592,7 @@
             <v>10140</v>
           </cell>
           <cell r="B60" t="str">
-            <v>光の加護</v>
+            <v>先天属性・光</v>
           </cell>
         </row>
         <row r="61">
@@ -1588,7 +1600,7 @@
             <v>10150</v>
           </cell>
           <cell r="B61" t="str">
-            <v>闇の加護</v>
+            <v>先天属性・闇</v>
           </cell>
         </row>
         <row r="62">
@@ -3789,7 +3801,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T34"/>
+  <dimension ref="A1:T36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="7.63636363636364" customWidth="1"/>
@@ -5798,6 +5810,121 @@
         <v>55</v>
       </c>
     </row>
+    <row r="35" spans="1:18">
+      <c r="A35">
+        <v>1101</v>
+      </c>
+      <c r="B35">
+        <v>1101</v>
+      </c>
+      <c r="C35" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35">
+        <v>1.5</v>
+      </c>
+      <c r="E35">
+        <v>39</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>30</v>
+      </c>
+      <c r="H35">
+        <v>15</v>
+      </c>
+      <c r="I35">
+        <v>15</v>
+      </c>
+      <c r="J35">
+        <v>3</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>55</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>60</v>
+      </c>
+      <c r="Q35">
+        <v>30</v>
+      </c>
+      <c r="R35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20">
+      <c r="A36">
+        <v>1102</v>
+      </c>
+      <c r="B36">
+        <v>1102</v>
+      </c>
+      <c r="C36" t="s">
+        <v>62</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>29</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>21</v>
+      </c>
+      <c r="H36">
+        <v>5</v>
+      </c>
+      <c r="I36">
+        <v>28</v>
+      </c>
+      <c r="J36">
+        <v>3</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>60</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>40</v>
+      </c>
+      <c r="Q36">
+        <v>25</v>
+      </c>
+      <c r="R36">
+        <v>60</v>
+      </c>
+      <c r="T36" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -5808,7 +5935,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G211"/>
+  <dimension ref="A1:G220"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="16.7272727272727" customWidth="1"/>
@@ -5816,25 +5943,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -10874,6 +11001,222 @@
         <v>0</v>
       </c>
       <c r="G211">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7">
+      <c r="A212">
+        <v>1101</v>
+      </c>
+      <c r="B212">
+        <v>3010</v>
+      </c>
+      <c r="C212" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B212,[1]TextData!A:A))</f>
+        <v>アイスブレイド</v>
+      </c>
+      <c r="D212">
+        <v>1</v>
+      </c>
+      <c r="E212">
+        <v>50</v>
+      </c>
+      <c r="F212">
+        <v>0</v>
+      </c>
+      <c r="G212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7">
+      <c r="A213">
+        <v>1101</v>
+      </c>
+      <c r="B213">
+        <v>3070</v>
+      </c>
+      <c r="C213" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B213,[1]TextData!A:A))</f>
+        <v>アクアミラージュ</v>
+      </c>
+      <c r="D213">
+        <v>1</v>
+      </c>
+      <c r="E213">
+        <v>100</v>
+      </c>
+      <c r="F213">
+        <v>0</v>
+      </c>
+      <c r="G213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7">
+      <c r="A214">
+        <v>1101</v>
+      </c>
+      <c r="B214">
+        <v>110110</v>
+      </c>
+      <c r="C214" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B214,[1]TextData!A:A))</f>
+        <v>ウィビングヒストリー</v>
+      </c>
+      <c r="D214">
+        <v>1</v>
+      </c>
+      <c r="E214">
+        <v>0</v>
+      </c>
+      <c r="F214">
+        <v>0</v>
+      </c>
+      <c r="G214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7">
+      <c r="A215">
+        <v>1101</v>
+      </c>
+      <c r="B215">
+        <v>110120</v>
+      </c>
+      <c r="C215" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B215,[1]TextData!A:A))</f>
+        <v>アンライバルド</v>
+      </c>
+      <c r="D215">
+        <v>1</v>
+      </c>
+      <c r="E215">
+        <v>200</v>
+      </c>
+      <c r="F215">
+        <v>0</v>
+      </c>
+      <c r="G215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7">
+      <c r="A216">
+        <v>1101</v>
+      </c>
+      <c r="B216">
+        <v>13100</v>
+      </c>
+      <c r="C216" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B216,[1]TextData!A:A))</f>
+        <v>ルミナスカバー</v>
+      </c>
+      <c r="D216">
+        <v>1</v>
+      </c>
+      <c r="E216">
+        <v>0</v>
+      </c>
+      <c r="F216">
+        <v>0</v>
+      </c>
+      <c r="G216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7">
+      <c r="A217">
+        <v>1101</v>
+      </c>
+      <c r="B217">
+        <v>403050</v>
+      </c>
+      <c r="C217" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B217,[1]TextData!A:A))</f>
+        <v>ディープフリーズ+</v>
+      </c>
+      <c r="D217">
+        <v>1</v>
+      </c>
+      <c r="E217">
+        <v>0</v>
+      </c>
+      <c r="F217">
+        <v>0</v>
+      </c>
+      <c r="G217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7">
+      <c r="A218">
+        <v>1101</v>
+      </c>
+      <c r="B218">
+        <v>13050</v>
+      </c>
+      <c r="C218" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B218,[1]TextData!A:A))</f>
+        <v>パッシブジャミング</v>
+      </c>
+      <c r="D218">
+        <v>1</v>
+      </c>
+      <c r="E218">
+        <v>0</v>
+      </c>
+      <c r="F218">
+        <v>0</v>
+      </c>
+      <c r="G218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7">
+      <c r="A219">
+        <v>1101</v>
+      </c>
+      <c r="B219">
+        <v>13070</v>
+      </c>
+      <c r="C219" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B219,[1]TextData!A:A))</f>
+        <v>アシッドラッシュ</v>
+      </c>
+      <c r="D219">
+        <v>1</v>
+      </c>
+      <c r="E219">
+        <v>0</v>
+      </c>
+      <c r="F219">
+        <v>0</v>
+      </c>
+      <c r="G219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7">
+      <c r="A220">
+        <v>1101</v>
+      </c>
+      <c r="B220">
+        <v>14070</v>
+      </c>
+      <c r="C220" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B220,[1]TextData!A:A))</f>
+        <v>ホーミングクルセイド</v>
+      </c>
+      <c r="D220">
+        <v>1</v>
+      </c>
+      <c r="E220">
+        <v>0</v>
+      </c>
+      <c r="F220">
+        <v>0</v>
+      </c>
+      <c r="G220">
         <v>0</v>
       </c>
     </row>
@@ -10891,25 +11234,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -11174,7 +11517,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="1"/>
   <cols>
     <col min="2" max="2" width="13.5454545454545" customWidth="1"/>
@@ -11185,7 +11528,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -11193,7 +11536,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -11201,7 +11544,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -11209,7 +11552,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -11217,7 +11560,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -11225,7 +11568,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -11233,7 +11576,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -11241,7 +11584,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -11249,7 +11592,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -11257,7 +11600,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -11265,7 +11608,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -11273,7 +11616,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -11281,7 +11624,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -11289,7 +11632,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -11297,7 +11640,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -11305,7 +11648,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -11313,7 +11656,7 @@
         <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -11321,7 +11664,7 @@
         <v>101</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -11329,7 +11672,7 @@
         <v>102</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -11337,7 +11680,7 @@
         <v>103</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -11345,7 +11688,7 @@
         <v>104</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -11353,7 +11696,7 @@
         <v>105</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -11361,7 +11704,7 @@
         <v>106</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -11369,7 +11712,7 @@
         <v>107</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -11377,7 +11720,7 @@
         <v>201</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -11385,7 +11728,7 @@
         <v>202</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -11393,7 +11736,7 @@
         <v>203</v>
       </c>
       <c r="B27" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -11401,7 +11744,7 @@
         <v>204</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -11409,7 +11752,7 @@
         <v>205</v>
       </c>
       <c r="B29" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -11417,7 +11760,7 @@
         <v>206</v>
       </c>
       <c r="B30" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -11425,7 +11768,7 @@
         <v>207</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -11433,7 +11776,7 @@
         <v>301</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -11441,7 +11784,7 @@
         <v>1001</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -11449,7 +11792,7 @@
         <v>1002</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -11457,7 +11800,7 @@
         <v>1003</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -11465,7 +11808,7 @@
         <v>1004</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -11473,7 +11816,7 @@
         <v>1005</v>
       </c>
       <c r="B37" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -11481,7 +11824,7 @@
         <v>1006</v>
       </c>
       <c r="B38" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -11489,7 +11832,7 @@
         <v>1007</v>
       </c>
       <c r="B39" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -11497,7 +11840,7 @@
         <v>1008</v>
       </c>
       <c r="B40" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -11505,7 +11848,7 @@
         <v>1009</v>
       </c>
       <c r="B41" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -11513,7 +11856,7 @@
         <v>1010</v>
       </c>
       <c r="B42" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -11521,7 +11864,23 @@
         <v>1011</v>
       </c>
       <c r="B43" t="s">
-        <v>114</v>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>1101</v>
+      </c>
+      <c r="B44" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>1102</v>
+      </c>
+      <c r="B45" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -11538,7 +11897,7 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="2:3">
@@ -11546,7 +11905,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="2:3">
@@ -11554,7 +11913,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="2:3">
@@ -11562,7 +11921,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="2:3">
@@ -11570,7 +11929,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="2:3">
@@ -11578,7 +11937,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="2:3">
@@ -11586,7 +11945,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="2:3">
@@ -11594,7 +11953,7 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="2:3">
@@ -11602,7 +11961,7 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -412,9 +412,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -434,20 +434,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -462,17 +448,67 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -486,10 +522,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -509,8 +546,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -518,14 +563,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -538,44 +576,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -586,7 +586,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -598,7 +610,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -610,79 +682,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -694,61 +694,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -766,7 +712,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -777,6 +777,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -791,30 +800,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -836,11 +821,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -854,11 +837,28 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -885,145 +885,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1877,1634 +1877,1874 @@
         </row>
         <row r="96">
           <cell r="A96">
-            <v>14010</v>
+            <v>13120</v>
           </cell>
           <cell r="B96" t="str">
-            <v>ディバインシールド</v>
+            <v>アフターシールド</v>
           </cell>
         </row>
         <row r="97">
           <cell r="A97">
-            <v>14020</v>
+            <v>13130</v>
           </cell>
           <cell r="B97" t="str">
-            <v>ライフディバイド</v>
+            <v>カバープラス</v>
           </cell>
         </row>
         <row r="98">
           <cell r="A98">
-            <v>14030</v>
+            <v>14010</v>
           </cell>
           <cell r="B98" t="str">
-            <v>エイミングスコープ</v>
+            <v>ディバインシールド</v>
           </cell>
         </row>
         <row r="99">
           <cell r="A99">
-            <v>14040</v>
+            <v>14020</v>
           </cell>
           <cell r="B99" t="str">
-            <v>リジェネレーション</v>
+            <v>ライフディバイド</v>
           </cell>
         </row>
         <row r="100">
           <cell r="A100">
-            <v>14050</v>
+            <v>14030</v>
           </cell>
           <cell r="B100" t="str">
-            <v>ホープフルアイリス</v>
+            <v>エイミングスコープ</v>
           </cell>
         </row>
         <row r="101">
           <cell r="A101">
-            <v>14060</v>
+            <v>14040</v>
           </cell>
           <cell r="B101" t="str">
-            <v>パッシブサプライ</v>
+            <v>リジェネレーション</v>
           </cell>
         </row>
         <row r="102">
           <cell r="A102">
-            <v>14070</v>
+            <v>14050</v>
           </cell>
           <cell r="B102" t="str">
-            <v>ホーミングクルセイド</v>
+            <v>ホープフルアイリス</v>
           </cell>
         </row>
         <row r="103">
           <cell r="A103">
-            <v>14080</v>
+            <v>14060</v>
           </cell>
           <cell r="B103" t="str">
-            <v>クイックヒール</v>
+            <v>パッシブサプライ</v>
           </cell>
         </row>
         <row r="104">
           <cell r="A104">
-            <v>14090</v>
+            <v>14070</v>
           </cell>
           <cell r="B104" t="str">
-            <v>リレイズ</v>
+            <v>ホーミングクルセイド</v>
           </cell>
         </row>
         <row r="105">
           <cell r="A105">
-            <v>14100</v>
+            <v>14080</v>
           </cell>
           <cell r="B105" t="str">
-            <v>ファストヒール</v>
+            <v>クイックヒール</v>
           </cell>
         </row>
         <row r="106">
           <cell r="A106">
-            <v>14110</v>
+            <v>14090</v>
           </cell>
           <cell r="B106" t="str">
-            <v>セルフケア</v>
+            <v>リレイズ</v>
           </cell>
         </row>
         <row r="107">
           <cell r="A107">
-            <v>15010</v>
+            <v>14100</v>
           </cell>
           <cell r="B107" t="str">
-            <v>イーグルアイ</v>
+            <v>ファストヒール</v>
           </cell>
         </row>
         <row r="108">
           <cell r="A108">
-            <v>15020</v>
+            <v>14110</v>
           </cell>
           <cell r="B108" t="str">
-            <v>ネヴァーエンド</v>
+            <v>セルフケア</v>
           </cell>
         </row>
         <row r="109">
           <cell r="A109">
-            <v>15030</v>
+            <v>14120</v>
           </cell>
           <cell r="B109" t="str">
-            <v>グレイブアクト</v>
+            <v>ファーストエイド</v>
           </cell>
         </row>
         <row r="110">
           <cell r="A110">
-            <v>15040</v>
+            <v>15010</v>
           </cell>
           <cell r="B110" t="str">
-            <v>スカルグラッジ</v>
+            <v>イーグルアイ</v>
           </cell>
         </row>
         <row r="111">
           <cell r="A111">
-            <v>15050</v>
+            <v>15020</v>
           </cell>
           <cell r="B111" t="str">
-            <v>ネガティブドレイン</v>
+            <v>ネヴァーエンド</v>
           </cell>
         </row>
         <row r="112">
           <cell r="A112">
-            <v>15060</v>
+            <v>15030</v>
           </cell>
           <cell r="B112" t="str">
-            <v>アンデッドペイン</v>
+            <v>グレイブアクト</v>
           </cell>
         </row>
         <row r="113">
           <cell r="A113">
-            <v>15070</v>
+            <v>15040</v>
           </cell>
           <cell r="B113" t="str">
-            <v>ジャックポッド</v>
+            <v>スカルグラッジ</v>
           </cell>
         </row>
         <row r="114">
           <cell r="A114">
-            <v>15080</v>
+            <v>15050</v>
           </cell>
           <cell r="B114" t="str">
-            <v>ヒールハント</v>
+            <v>ネガティブドレイン</v>
           </cell>
         </row>
         <row r="115">
           <cell r="A115">
-            <v>15090</v>
+            <v>15060</v>
           </cell>
           <cell r="B115" t="str">
-            <v>クイックカース</v>
+            <v>アンデッドペイン</v>
           </cell>
         </row>
         <row r="116">
           <cell r="A116">
-            <v>15100</v>
+            <v>15070</v>
           </cell>
           <cell r="B116" t="str">
-            <v>リヴェンジャー</v>
+            <v>ジャックポッド</v>
           </cell>
         </row>
         <row r="117">
           <cell r="A117">
-            <v>15110</v>
+            <v>15080</v>
           </cell>
           <cell r="B117" t="str">
-            <v>リープリアクト</v>
+            <v>ヒールハント</v>
           </cell>
         </row>
         <row r="118">
           <cell r="A118">
-            <v>15112</v>
+            <v>15090</v>
           </cell>
           <cell r="B118" t="str">
-            <v>リープリアクト</v>
+            <v>クイックカース</v>
           </cell>
         </row>
         <row r="119">
           <cell r="A119">
-            <v>20010</v>
+            <v>15100</v>
           </cell>
           <cell r="B119" t="str">
-            <v>ウェイトユニゾン</v>
+            <v>リヴェンジャー</v>
           </cell>
         </row>
         <row r="120">
           <cell r="A120">
-            <v>30010</v>
+            <v>15110</v>
           </cell>
           <cell r="B120" t="str">
-            <v>ラーニングピアス</v>
+            <v>リープリアクト</v>
           </cell>
         </row>
         <row r="121">
           <cell r="A121">
-            <v>30020</v>
+            <v>15112</v>
           </cell>
           <cell r="B121" t="str">
-            <v>スティールヒール</v>
+            <v>リープリアクト</v>
           </cell>
         </row>
         <row r="122">
           <cell r="A122">
-            <v>30030</v>
+            <v>15120</v>
           </cell>
           <cell r="B122" t="str">
-            <v>ガッツ</v>
+            <v>ディレイドパッシブ</v>
           </cell>
         </row>
         <row r="123">
           <cell r="A123">
-            <v>100110</v>
+            <v>15130</v>
           </cell>
           <cell r="B123" t="str">
-            <v>ソーイングアームド</v>
+            <v>シャドウケイプ</v>
           </cell>
         </row>
         <row r="124">
           <cell r="A124">
-            <v>100120</v>
+            <v>20010</v>
           </cell>
           <cell r="B124" t="str">
-            <v>エターナルロンド</v>
+            <v>ウェイトユニゾン</v>
           </cell>
         </row>
         <row r="125">
           <cell r="A125">
-            <v>100210</v>
+            <v>30010</v>
           </cell>
           <cell r="B125" t="str">
-            <v>アブソリュートパリィ</v>
+            <v>ラーニングピアス</v>
           </cell>
         </row>
         <row r="126">
           <cell r="A126">
-            <v>100220</v>
+            <v>30020</v>
           </cell>
           <cell r="B126" t="str">
-            <v>レヴェリー</v>
+            <v>スティールヒール</v>
           </cell>
         </row>
         <row r="127">
           <cell r="A127">
-            <v>100310</v>
+            <v>30030</v>
           </cell>
           <cell r="B127" t="str">
-            <v>セイクリッドバリア</v>
+            <v>ガッツ</v>
           </cell>
         </row>
         <row r="128">
           <cell r="A128">
-            <v>100320</v>
+            <v>100110</v>
           </cell>
           <cell r="B128" t="str">
-            <v>リベンジニードル</v>
+            <v>ソーイングアームド</v>
           </cell>
         </row>
         <row r="129">
           <cell r="A129">
-            <v>100410</v>
+            <v>100120</v>
           </cell>
           <cell r="B129" t="str">
-            <v>アバンデンス</v>
+            <v>エターナルロンド</v>
           </cell>
         </row>
         <row r="130">
           <cell r="A130">
-            <v>100420</v>
+            <v>100210</v>
           </cell>
           <cell r="B130" t="str">
-            <v>ハーヴェスト</v>
+            <v>アブソリュートパリィ</v>
           </cell>
         </row>
         <row r="131">
           <cell r="A131">
-            <v>100510</v>
+            <v>100220</v>
           </cell>
           <cell r="B131" t="str">
-            <v>カースドブレイク</v>
+            <v>レヴェリー</v>
           </cell>
         </row>
         <row r="132">
           <cell r="A132">
-            <v>100520</v>
+            <v>100310</v>
           </cell>
           <cell r="B132" t="str">
-            <v>ムーンライトレイ</v>
+            <v>セイクリッドバリア</v>
           </cell>
         </row>
         <row r="133">
           <cell r="A133">
-            <v>100610</v>
+            <v>100320</v>
           </cell>
           <cell r="B133" t="str">
-            <v>サンフレイム</v>
+            <v>リベンジニードル</v>
           </cell>
         </row>
         <row r="134">
           <cell r="A134">
-            <v>100620</v>
+            <v>100410</v>
           </cell>
           <cell r="B134" t="str">
-            <v>フレイムタン</v>
+            <v>アバンデンス</v>
           </cell>
         </row>
         <row r="135">
           <cell r="A135">
-            <v>100710</v>
+            <v>100420</v>
           </cell>
           <cell r="B135" t="str">
-            <v>ライズザフラッグ</v>
+            <v>ハーヴェスト</v>
           </cell>
         </row>
         <row r="136">
           <cell r="A136">
-            <v>100720</v>
+            <v>100510</v>
           </cell>
           <cell r="B136" t="str">
-            <v>オーバーリミット</v>
+            <v>カースドブレイク</v>
           </cell>
         </row>
         <row r="137">
           <cell r="A137">
-            <v>100810</v>
+            <v>100520</v>
           </cell>
           <cell r="B137" t="str">
-            <v>テンパランス</v>
+            <v>ムーンライトレイ</v>
           </cell>
         </row>
         <row r="138">
           <cell r="A138">
-            <v>100820</v>
+            <v>100610</v>
           </cell>
           <cell r="B138" t="str">
-            <v>シエルクルセイダー</v>
+            <v>サンフレイム</v>
           </cell>
         </row>
         <row r="139">
           <cell r="A139">
-            <v>100910</v>
+            <v>100620</v>
           </cell>
           <cell r="B139" t="str">
-            <v>バーニングカウンター</v>
+            <v>フレイムタン</v>
           </cell>
         </row>
         <row r="140">
           <cell r="A140">
-            <v>100911</v>
+            <v>100710</v>
           </cell>
           <cell r="B140" t="str">
-            <v>バーニングカウンター</v>
+            <v>ライズザフラッグ</v>
           </cell>
         </row>
         <row r="141">
           <cell r="A141">
-            <v>100920</v>
+            <v>100720</v>
           </cell>
           <cell r="B141" t="str">
-            <v>プロミネンス</v>
+            <v>オーバーリミット</v>
           </cell>
         </row>
         <row r="142">
           <cell r="A142">
-            <v>100921</v>
+            <v>100810</v>
           </cell>
           <cell r="B142" t="str">
-            <v>プロミネンス</v>
+            <v>テンパランス</v>
           </cell>
         </row>
         <row r="143">
           <cell r="A143">
-            <v>101010</v>
+            <v>100820</v>
           </cell>
           <cell r="B143" t="str">
-            <v>エウロス</v>
+            <v>シエルクルセイダー</v>
           </cell>
         </row>
         <row r="144">
           <cell r="A144">
-            <v>101020</v>
+            <v>100910</v>
           </cell>
           <cell r="B144" t="str">
-            <v>ボレアス</v>
+            <v>バーニングカウンター</v>
           </cell>
         </row>
         <row r="145">
           <cell r="A145">
-            <v>101110</v>
+            <v>100911</v>
           </cell>
           <cell r="B145" t="str">
-            <v>アバランシュ</v>
+            <v>バーニングカウンター</v>
           </cell>
         </row>
         <row r="146">
           <cell r="A146">
-            <v>101120</v>
+            <v>100920</v>
           </cell>
           <cell r="B146" t="str">
-            <v>ブリザードコフィン</v>
+            <v>プロミネンス</v>
           </cell>
         </row>
         <row r="147">
           <cell r="A147">
-            <v>110110</v>
+            <v>100921</v>
           </cell>
           <cell r="B147" t="str">
-            <v>ウィビングヒストリー</v>
+            <v>プロミネンス</v>
           </cell>
         </row>
         <row r="148">
           <cell r="A148">
-            <v>110120</v>
+            <v>101010</v>
           </cell>
           <cell r="B148" t="str">
-            <v>アンライバルド</v>
+            <v>エウロス</v>
           </cell>
         </row>
         <row r="149">
           <cell r="A149">
-            <v>200110</v>
+            <v>101020</v>
           </cell>
           <cell r="B149" t="str">
-            <v>スリータイムス</v>
+            <v>ボレアス</v>
           </cell>
         </row>
         <row r="150">
           <cell r="A150">
-            <v>200120</v>
+            <v>101110</v>
           </cell>
           <cell r="B150" t="str">
-            <v>アングリークライ</v>
+            <v>アバランシュ</v>
           </cell>
         </row>
         <row r="151">
           <cell r="A151">
-            <v>200210</v>
+            <v>101120</v>
           </cell>
           <cell r="B151" t="str">
-            <v>マイトレインフォース</v>
+            <v>ブリザードコフィン</v>
           </cell>
         </row>
         <row r="152">
           <cell r="A152">
-            <v>200220</v>
+            <v>110110</v>
           </cell>
           <cell r="B152" t="str">
-            <v>カタストロフィ</v>
+            <v>ウィビングヒストリー</v>
           </cell>
         </row>
         <row r="153">
           <cell r="A153">
-            <v>200230</v>
+            <v>110120</v>
           </cell>
           <cell r="B153" t="str">
-            <v>悪魔(ベリト)</v>
+            <v>アンライバルド</v>
           </cell>
         </row>
         <row r="154">
           <cell r="A154">
-            <v>200310</v>
+            <v>200110</v>
           </cell>
           <cell r="B154" t="str">
-            <v>プルガシオン</v>
+            <v>スリータイムス</v>
           </cell>
         </row>
         <row r="155">
           <cell r="A155">
-            <v>200320</v>
+            <v>200120</v>
           </cell>
           <cell r="B155" t="str">
-            <v>プリエステス</v>
+            <v>アングリークライ</v>
           </cell>
         </row>
         <row r="156">
           <cell r="A156">
-            <v>200330</v>
+            <v>200210</v>
           </cell>
           <cell r="B156" t="str">
-            <v>悪魔(パイモン)</v>
+            <v>マイトレインフォース</v>
           </cell>
         </row>
         <row r="157">
           <cell r="A157">
-            <v>200410</v>
+            <v>200220</v>
           </cell>
           <cell r="B157" t="str">
-            <v>コウソクテンショウ</v>
+            <v>カタストロフィ</v>
           </cell>
         </row>
         <row r="158">
           <cell r="A158">
-            <v>200411</v>
+            <v>200230</v>
           </cell>
           <cell r="B158" t="str">
-            <v>コウソクテンショウ</v>
+            <v>悪魔(ベリト)</v>
           </cell>
         </row>
         <row r="159">
           <cell r="A159">
-            <v>200420</v>
+            <v>200310</v>
           </cell>
           <cell r="B159" t="str">
-            <v>アンチバフ</v>
+            <v>プルガシオン</v>
           </cell>
         </row>
         <row r="160">
           <cell r="A160">
-            <v>200430</v>
+            <v>200320</v>
           </cell>
           <cell r="B160" t="str">
-            <v>悪魔(アンドラス)</v>
+            <v>プリエステス</v>
           </cell>
         </row>
         <row r="161">
           <cell r="A161">
-            <v>200510</v>
+            <v>200330</v>
           </cell>
           <cell r="B161" t="str">
-            <v>カウントダウン</v>
+            <v>悪魔(パイモン)</v>
           </cell>
         </row>
         <row r="162">
           <cell r="A162">
-            <v>200520</v>
+            <v>200410</v>
           </cell>
           <cell r="B162" t="str">
-            <v>グラウンドゼロ</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="163">
           <cell r="A163">
-            <v>200530</v>
+            <v>200411</v>
           </cell>
           <cell r="B163" t="str">
-            <v>悪魔(ビフロンス)</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="164">
           <cell r="A164">
-            <v>201010</v>
+            <v>200420</v>
           </cell>
           <cell r="B164" t="str">
-            <v>カオスペイン</v>
+            <v>アンチバフ</v>
           </cell>
         </row>
         <row r="165">
           <cell r="A165">
-            <v>201020</v>
+            <v>200430</v>
           </cell>
           <cell r="B165" t="str">
-            <v>フォールンワン</v>
+            <v>悪魔(アンドラス)</v>
           </cell>
         </row>
         <row r="166">
           <cell r="A166">
-            <v>201030</v>
+            <v>200510</v>
           </cell>
           <cell r="B166" t="str">
-            <v>アンリマユ</v>
+            <v>カウントダウン</v>
           </cell>
         </row>
         <row r="167">
           <cell r="A167">
-            <v>300010</v>
+            <v>200520</v>
           </cell>
           <cell r="B167" t="str">
-            <v>ライフブースト</v>
+            <v>グラウンドゼロ</v>
           </cell>
         </row>
         <row r="168">
           <cell r="A168">
-            <v>300020</v>
+            <v>200530</v>
           </cell>
           <cell r="B168" t="str">
-            <v>スピリットチャージ</v>
+            <v>悪魔(ビフロンス)</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169">
-            <v>300030</v>
+            <v>201010</v>
           </cell>
           <cell r="B169" t="str">
-            <v>フォースライズ</v>
+            <v>カオスペイン</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170">
-            <v>300040</v>
+            <v>201020</v>
           </cell>
           <cell r="B170" t="str">
-            <v>ディフェンスオーラ</v>
+            <v>フォールンワン</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171">
-            <v>300050</v>
+            <v>201030</v>
           </cell>
           <cell r="B171" t="str">
-            <v>ラピッドムーブ</v>
+            <v>アンリマユ</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172">
-            <v>300130</v>
+            <v>300010</v>
           </cell>
           <cell r="B172" t="str">
-            <v>アタックブレイク</v>
+            <v>ライフブースト</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173">
-            <v>300140</v>
+            <v>300020</v>
           </cell>
           <cell r="B173" t="str">
-            <v>シールドバニッシュ</v>
+            <v>スピリットチャージ</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174">
-            <v>300210</v>
+            <v>300030</v>
           </cell>
           <cell r="B174" t="str">
-            <v>エーテルリチャージ</v>
+            <v>フォースライズ</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175">
-            <v>300220</v>
+            <v>300040</v>
           </cell>
           <cell r="B175" t="str">
-            <v>リカバリーエンハンス</v>
+            <v>ディフェンスオーラ</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176">
-            <v>300230</v>
+            <v>300050</v>
           </cell>
           <cell r="B176" t="str">
-            <v>ヴェンジェンス</v>
+            <v>ラピッドムーブ</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177">
-            <v>301010</v>
+            <v>300130</v>
           </cell>
           <cell r="B177" t="str">
-            <v>ディケイドリセット</v>
+            <v>アタックブレイク</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178">
-            <v>301020</v>
+            <v>300140</v>
           </cell>
           <cell r="B178" t="str">
-            <v>ウォーリアーブラッド</v>
+            <v>シールドバニッシュ</v>
           </cell>
         </row>
         <row r="179">
           <cell r="A179">
-            <v>301030</v>
+            <v>300210</v>
           </cell>
           <cell r="B179" t="str">
-            <v>トライアングルガード</v>
+            <v>エーテルリチャージ</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180">
-            <v>301040</v>
+            <v>300220</v>
           </cell>
           <cell r="B180" t="str">
-            <v>セーフティバリア</v>
+            <v>リカバリーエンハンス</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181">
-            <v>301050</v>
+            <v>300230</v>
           </cell>
           <cell r="B181" t="str">
-            <v>ヒロインズハイ</v>
+            <v>ヴェンジェンス</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182">
-            <v>301060</v>
+            <v>301010</v>
           </cell>
           <cell r="B182" t="str">
-            <v>セカンドステージ</v>
+            <v>ディケイドリセット</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183">
-            <v>301070</v>
+            <v>301020</v>
           </cell>
           <cell r="B183" t="str">
-            <v>ハイヒットポイント</v>
+            <v>ウォーリアーブラッド</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184">
-            <v>301080</v>
+            <v>301030</v>
           </cell>
           <cell r="B184" t="str">
-            <v>セプタブラスト</v>
+            <v>トライアングルガード</v>
           </cell>
         </row>
         <row r="185">
           <cell r="A185">
-            <v>301090</v>
+            <v>301040</v>
           </cell>
           <cell r="B185" t="str">
-            <v>イニシャルブロッカー</v>
+            <v>セーフティバリア</v>
           </cell>
         </row>
         <row r="186">
           <cell r="A186">
-            <v>301100</v>
+            <v>301050</v>
           </cell>
           <cell r="B186" t="str">
-            <v>ファーストテイク</v>
+            <v>ヒロインズハイ</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187">
-            <v>310010</v>
+            <v>301060</v>
           </cell>
           <cell r="B187" t="str">
-            <v>妖精の祈り</v>
+            <v>セカンドステージ</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188">
-            <v>310020</v>
+            <v>301070</v>
           </cell>
           <cell r="B188" t="str">
-            <v>月のかけら</v>
+            <v>ハイヒットポイント</v>
           </cell>
         </row>
         <row r="189">
           <cell r="A189">
-            <v>310030</v>
+            <v>301080</v>
           </cell>
           <cell r="B189" t="str">
-            <v>商売の才覚書</v>
+            <v>セプタブラスト</v>
           </cell>
         </row>
         <row r="190">
           <cell r="A190">
-            <v>310040</v>
+            <v>301090</v>
           </cell>
           <cell r="B190" t="str">
-            <v>メビウスの砂時計</v>
+            <v>イニシャルブロッカー</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191">
-            <v>310050</v>
+            <v>301100</v>
           </cell>
           <cell r="B191" t="str">
-            <v>先陣の心得</v>
+            <v>ファーストテイク</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192">
-            <v>310060</v>
+            <v>310010</v>
           </cell>
           <cell r="B192" t="str">
-            <v>ヒスイの勾玉</v>
+            <v>妖精の祈り</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193">
-            <v>310070</v>
+            <v>310020</v>
           </cell>
           <cell r="B193" t="str">
-            <v>英傑の盾</v>
+            <v>月のかけら</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194">
-            <v>310080</v>
+            <v>310030</v>
           </cell>
           <cell r="B194" t="str">
-            <v>鷹の目</v>
+            <v>商売の才覚書</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195">
-            <v>310130</v>
+            <v>310040</v>
           </cell>
           <cell r="B195" t="str">
-            <v>ヒールユニット</v>
+            <v>メビウスの砂時計</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196">
-            <v>320010</v>
+            <v>310050</v>
           </cell>
           <cell r="B196" t="str">
-            <v>訓練所Lv1</v>
+            <v>先陣の心得</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197">
-            <v>320011</v>
+            <v>310060</v>
           </cell>
           <cell r="B197" t="str">
-            <v>訓練所Lv2</v>
+            <v>ヒスイの勾玉</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198">
-            <v>320012</v>
+            <v>310070</v>
           </cell>
           <cell r="B198" t="str">
-            <v>訓練所Lv3</v>
+            <v>英傑の盾</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199">
-            <v>320020</v>
+            <v>310080</v>
           </cell>
           <cell r="B199" t="str">
-            <v>研究施設Lv1</v>
+            <v>鷹の目</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200">
-            <v>320021</v>
+            <v>310130</v>
           </cell>
           <cell r="B200" t="str">
-            <v>研究施設Lv2</v>
+            <v>ヒールユニット</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201">
-            <v>320022</v>
+            <v>320010</v>
           </cell>
           <cell r="B201" t="str">
-            <v>研究施設Lv3</v>
+            <v>訓練所Lv1</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202">
-            <v>320030</v>
+            <v>320011</v>
           </cell>
           <cell r="B202" t="str">
-            <v>資料館Lv1</v>
+            <v>訓練所Lv2</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203">
-            <v>320031</v>
+            <v>320012</v>
           </cell>
           <cell r="B203" t="str">
-            <v>資料館Lv2</v>
+            <v>訓練所Lv3</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204">
-            <v>320032</v>
+            <v>320020</v>
           </cell>
           <cell r="B204" t="str">
-            <v>資料館Lv3</v>
+            <v>研究施設Lv1</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205">
-            <v>320040</v>
+            <v>320021</v>
           </cell>
           <cell r="B205" t="str">
-            <v>潜伏技術Lv1</v>
+            <v>研究施設Lv2</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206">
-            <v>321010</v>
+            <v>320022</v>
           </cell>
           <cell r="B206" t="str">
-            <v>炎の祭壇</v>
+            <v>研究施設Lv3</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207">
-            <v>321020</v>
+            <v>320030</v>
           </cell>
           <cell r="B207" t="str">
-            <v>稲妻の祭壇</v>
+            <v>資料館Lv1</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208">
-            <v>321030</v>
+            <v>320031</v>
           </cell>
           <cell r="B208" t="str">
-            <v>蒼の祭壇</v>
+            <v>資料館Lv2</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209">
-            <v>321040</v>
+            <v>320032</v>
           </cell>
           <cell r="B209" t="str">
-            <v>光の祭壇</v>
+            <v>資料館Lv3</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210">
-            <v>321050</v>
+            <v>320040</v>
           </cell>
           <cell r="B210" t="str">
-            <v>月の祭壇</v>
+            <v>潜伏技術Lv1</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211">
-            <v>322010</v>
+            <v>321010</v>
           </cell>
           <cell r="B211" t="str">
-            <v>食糧庫Lv1</v>
+            <v>炎の祭壇</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212">
-            <v>322020</v>
+            <v>321020</v>
           </cell>
           <cell r="B212" t="str">
-            <v>攻撃技術Lv1</v>
+            <v>稲妻の祭壇</v>
           </cell>
         </row>
         <row r="213">
           <cell r="A213">
-            <v>322030</v>
+            <v>321030</v>
           </cell>
           <cell r="B213" t="str">
-            <v>防御技術Lv1</v>
+            <v>蒼の祭壇</v>
           </cell>
         </row>
         <row r="214">
           <cell r="A214">
-            <v>322040</v>
+            <v>321040</v>
           </cell>
           <cell r="B214" t="str">
-            <v>詠唱技術Lv1</v>
+            <v>光の祭壇</v>
           </cell>
         </row>
         <row r="215">
           <cell r="A215">
-            <v>401010</v>
+            <v>321050</v>
           </cell>
           <cell r="B215" t="str">
-            <v>ファイアボール+</v>
+            <v>月の祭壇</v>
           </cell>
         </row>
         <row r="216">
           <cell r="A216">
-            <v>401020</v>
+            <v>322010</v>
           </cell>
           <cell r="B216" t="str">
-            <v>バーンストーム+</v>
+            <v>食糧庫Lv1</v>
           </cell>
         </row>
         <row r="217">
           <cell r="A217">
-            <v>401030</v>
+            <v>322020</v>
           </cell>
           <cell r="B217" t="str">
-            <v>ヒートスタンプ+</v>
+            <v>攻撃技術Lv1</v>
           </cell>
         </row>
         <row r="218">
           <cell r="A218">
-            <v>401040</v>
+            <v>322030</v>
           </cell>
           <cell r="B218" t="str">
-            <v>ソードアダプト+</v>
+            <v>防御技術Lv1</v>
           </cell>
         </row>
         <row r="219">
           <cell r="A219">
-            <v>401050</v>
+            <v>322040</v>
           </cell>
           <cell r="B219" t="str">
-            <v>フレイムレイン+</v>
+            <v>詠唱技術Lv1</v>
           </cell>
         </row>
         <row r="220">
           <cell r="A220">
-            <v>401060</v>
+            <v>401010</v>
           </cell>
           <cell r="B220" t="str">
-            <v>イクスティンクション+</v>
+            <v>ファイアボール+</v>
           </cell>
         </row>
         <row r="221">
           <cell r="A221">
-            <v>401070</v>
+            <v>401020</v>
           </cell>
           <cell r="B221" t="str">
-            <v>バーニングソウル+</v>
+            <v>バーンストーム+</v>
           </cell>
         </row>
         <row r="222">
           <cell r="A222">
-            <v>401080</v>
+            <v>401030</v>
           </cell>
           <cell r="B222" t="str">
-            <v>レイジングバウンサー+</v>
+            <v>ヒートスタンプ+</v>
           </cell>
         </row>
         <row r="223">
           <cell r="A223">
-            <v>402010</v>
+            <v>401040</v>
           </cell>
           <cell r="B223" t="str">
-            <v>ディスチャージ+</v>
+            <v>ソードアダプト+</v>
           </cell>
         </row>
         <row r="224">
           <cell r="A224">
-            <v>402020</v>
+            <v>401050</v>
           </cell>
           <cell r="B224" t="str">
-            <v>イベイドコード+</v>
+            <v>フレイムレイン+</v>
           </cell>
         </row>
         <row r="225">
           <cell r="A225">
-            <v>402030</v>
+            <v>401060</v>
           </cell>
           <cell r="B225" t="str">
-            <v>ショックインパルス+</v>
+            <v>イクスティンクション+</v>
           </cell>
         </row>
         <row r="226">
           <cell r="A226">
-            <v>402040</v>
+            <v>401070</v>
           </cell>
           <cell r="B226" t="str">
-            <v>トラストチェイン+</v>
+            <v>バーニングソウル+</v>
           </cell>
         </row>
         <row r="227">
           <cell r="A227">
-            <v>402050</v>
+            <v>401080</v>
           </cell>
           <cell r="B227" t="str">
-            <v>スペルバニシング+</v>
+            <v>レイジングバウンサー+</v>
           </cell>
         </row>
         <row r="228">
           <cell r="A228">
-            <v>402060</v>
+            <v>402010</v>
           </cell>
           <cell r="B228" t="str">
-            <v>アーテニーストライク+</v>
+            <v>ディスチャージ+</v>
           </cell>
         </row>
         <row r="229">
           <cell r="A229">
-            <v>402070</v>
+            <v>402020</v>
           </cell>
           <cell r="B229" t="str">
-            <v>コンセントレイト+</v>
+            <v>イベイドコード+</v>
           </cell>
         </row>
         <row r="230">
           <cell r="A230">
-            <v>402080</v>
+            <v>402030</v>
           </cell>
           <cell r="B230" t="str">
-            <v>ディレイマジック+</v>
+            <v>ショックインパルス+</v>
           </cell>
         </row>
         <row r="231">
           <cell r="A231">
-            <v>403010</v>
+            <v>402040</v>
           </cell>
           <cell r="B231" t="str">
-            <v>アイスブレイド+</v>
+            <v>トラストチェイン+</v>
           </cell>
         </row>
         <row r="232">
           <cell r="A232">
-            <v>403020</v>
+            <v>402050</v>
           </cell>
           <cell r="B232" t="str">
-            <v>カウンターオーラ+</v>
+            <v>スペルバニシング+</v>
           </cell>
         </row>
         <row r="233">
           <cell r="A233">
-            <v>403030</v>
+            <v>402060</v>
           </cell>
           <cell r="B233" t="str">
-            <v>ラインプロテクト+</v>
+            <v>アーテニーストライク+</v>
           </cell>
         </row>
         <row r="234">
           <cell r="A234">
-            <v>403040</v>
+            <v>402070</v>
           </cell>
           <cell r="B234" t="str">
-            <v>エスコートソール+</v>
+            <v>コンセントレイト+</v>
           </cell>
         </row>
         <row r="235">
           <cell r="A235">
-            <v>403050</v>
+            <v>402080</v>
           </cell>
           <cell r="B235" t="str">
-            <v>ディープフリーズ+</v>
+            <v>ディレイマジック+</v>
           </cell>
         </row>
         <row r="236">
           <cell r="A236">
-            <v>403060</v>
+            <v>403010</v>
           </cell>
           <cell r="B236" t="str">
-            <v>バブルブロウ+</v>
+            <v>アイスブレイド+</v>
           </cell>
         </row>
         <row r="237">
           <cell r="A237">
-            <v>403070</v>
+            <v>403020</v>
           </cell>
           <cell r="B237" t="str">
-            <v>アクアミラージュ+</v>
+            <v>カウンターオーラ+</v>
           </cell>
         </row>
         <row r="238">
           <cell r="A238">
-            <v>403080</v>
+            <v>403030</v>
           </cell>
           <cell r="B238" t="str">
-            <v>フロストシールド+</v>
+            <v>ラインプロテクト+</v>
           </cell>
         </row>
         <row r="239">
           <cell r="A239">
-            <v>404010</v>
+            <v>403040</v>
           </cell>
           <cell r="B239" t="str">
-            <v>セイントレーザー+</v>
+            <v>エスコートソール+</v>
           </cell>
         </row>
         <row r="240">
           <cell r="A240">
-            <v>404020</v>
+            <v>403050</v>
           </cell>
           <cell r="B240" t="str">
-            <v>ペネトレイト+</v>
+            <v>ディープフリーズ+</v>
           </cell>
         </row>
         <row r="241">
           <cell r="A241">
-            <v>404030</v>
+            <v>403060</v>
           </cell>
           <cell r="B241" t="str">
-            <v>ヒーリング+</v>
+            <v>バブルブロウ+</v>
           </cell>
         </row>
         <row r="242">
           <cell r="A242">
-            <v>404040</v>
+            <v>403070</v>
           </cell>
           <cell r="B242" t="str">
-            <v>リザイアフォトン+</v>
+            <v>アクアミラージュ+</v>
           </cell>
         </row>
         <row r="243">
           <cell r="A243">
-            <v>404050</v>
+            <v>403080</v>
           </cell>
           <cell r="B243" t="str">
-            <v>べネディクション+</v>
+            <v>フロストシールド+</v>
           </cell>
         </row>
         <row r="244">
           <cell r="A244">
-            <v>404060</v>
+            <v>404010</v>
           </cell>
           <cell r="B244" t="str">
-            <v>ホーリーグレイス+</v>
+            <v>セイントレーザー+</v>
           </cell>
         </row>
         <row r="245">
           <cell r="A245">
-            <v>404070</v>
+            <v>404020</v>
           </cell>
           <cell r="B245" t="str">
-            <v>キュアエール+</v>
+            <v>ペネトレイト+</v>
           </cell>
         </row>
         <row r="246">
           <cell r="A246">
-            <v>404080</v>
+            <v>404030</v>
           </cell>
           <cell r="B246" t="str">
-            <v>ラインバリア+</v>
+            <v>ヒーリング+</v>
           </cell>
         </row>
         <row r="247">
           <cell r="A247">
-            <v>405010</v>
+            <v>404040</v>
           </cell>
           <cell r="B247" t="str">
-            <v>ダークプリズン+</v>
+            <v>リザイアフォトン+</v>
           </cell>
         </row>
         <row r="248">
           <cell r="A248">
-            <v>405020</v>
+            <v>404050</v>
           </cell>
           <cell r="B248" t="str">
-            <v>ユーサネイジア+</v>
+            <v>べネディクション+</v>
           </cell>
         </row>
         <row r="249">
           <cell r="A249">
-            <v>405030</v>
+            <v>404060</v>
           </cell>
           <cell r="B249" t="str">
-            <v>ドレインヒール+</v>
+            <v>ホーリーグレイス+</v>
           </cell>
         </row>
         <row r="250">
           <cell r="A250">
-            <v>405040</v>
+            <v>404070</v>
           </cell>
           <cell r="B250" t="str">
-            <v>アビサルデスペア+</v>
+            <v>キュアエール+</v>
           </cell>
         </row>
         <row r="251">
           <cell r="A251">
-            <v>405050</v>
+            <v>404080</v>
           </cell>
           <cell r="B251" t="str">
-            <v>ディプラヴィティ+</v>
+            <v>ラインバリア+</v>
           </cell>
         </row>
         <row r="252">
           <cell r="A252">
-            <v>405060</v>
+            <v>405010</v>
           </cell>
           <cell r="B252" t="str">
-            <v>ダークネス+</v>
+            <v>ダークプリズン+</v>
           </cell>
         </row>
         <row r="253">
           <cell r="A253">
-            <v>405070</v>
+            <v>405020</v>
           </cell>
           <cell r="B253" t="str">
-            <v>シェイディークラウド+</v>
+            <v>ユーサネイジア+</v>
           </cell>
         </row>
         <row r="254">
           <cell r="A254">
-            <v>405080</v>
+            <v>405030</v>
           </cell>
           <cell r="B254" t="str">
-            <v>ポイズンブロウ+</v>
+            <v>ドレインヒール+</v>
           </cell>
         </row>
         <row r="255">
           <cell r="A255">
-            <v>411010</v>
+            <v>405040</v>
           </cell>
           <cell r="B255" t="str">
-            <v>ウルフソウル+</v>
+            <v>アビサルデスペア+</v>
           </cell>
         </row>
         <row r="256">
           <cell r="A256">
-            <v>411020</v>
+            <v>405050</v>
           </cell>
           <cell r="B256" t="str">
-            <v>プリディカメント+</v>
+            <v>ディプラヴィティ+</v>
           </cell>
         </row>
         <row r="257">
           <cell r="A257">
-            <v>411030</v>
+            <v>405060</v>
           </cell>
           <cell r="B257" t="str">
-            <v>アサルトシフト+</v>
+            <v>ダークネス+</v>
           </cell>
         </row>
         <row r="258">
           <cell r="A258">
-            <v>411040</v>
+            <v>405070</v>
           </cell>
           <cell r="B258" t="str">
-            <v>アクティブギフト+</v>
+            <v>シェイディークラウド+</v>
           </cell>
         </row>
         <row r="259">
           <cell r="A259">
-            <v>411050</v>
+            <v>405080</v>
           </cell>
           <cell r="B259" t="str">
-            <v>イグナイテッド+</v>
+            <v>ポイズンブロウ+</v>
           </cell>
         </row>
         <row r="260">
           <cell r="A260">
-            <v>411060</v>
+            <v>411010</v>
           </cell>
           <cell r="B260" t="str">
-            <v>ライジングファイア+</v>
+            <v>ウルフソウル+</v>
           </cell>
         </row>
         <row r="261">
           <cell r="A261">
-            <v>411070</v>
+            <v>411020</v>
           </cell>
           <cell r="B261" t="str">
-            <v>ルージュバック+</v>
+            <v>プリディカメント+</v>
           </cell>
         </row>
         <row r="262">
           <cell r="A262">
-            <v>411080</v>
+            <v>411030</v>
           </cell>
           <cell r="B262" t="str">
-            <v>パワーエール+</v>
+            <v>アサルトシフト+</v>
           </cell>
         </row>
         <row r="263">
           <cell r="A263">
-            <v>411090</v>
+            <v>411040</v>
           </cell>
           <cell r="B263" t="str">
-            <v>スレイプニル+</v>
+            <v>アクティブギフト+</v>
           </cell>
         </row>
         <row r="264">
           <cell r="A264">
-            <v>412010</v>
+            <v>411050</v>
           </cell>
           <cell r="B264" t="str">
-            <v>エクステンション+</v>
+            <v>イグナイテッド+</v>
           </cell>
         </row>
         <row r="265">
           <cell r="A265">
-            <v>412020</v>
+            <v>411060</v>
           </cell>
           <cell r="B265" t="str">
-            <v>ヘブンリーラック+</v>
+            <v>ライジングファイア+</v>
           </cell>
         </row>
         <row r="266">
           <cell r="A266">
-            <v>412030</v>
+            <v>411070</v>
           </cell>
           <cell r="B266" t="str">
-            <v>スウィフトカレント+</v>
+            <v>ルージュバック+</v>
           </cell>
         </row>
         <row r="267">
           <cell r="A267">
-            <v>412040</v>
+            <v>411080</v>
           </cell>
           <cell r="B267" t="str">
-            <v>イヴェイドオール+</v>
+            <v>パワーエール+</v>
           </cell>
         </row>
         <row r="268">
           <cell r="A268">
-            <v>412050</v>
+            <v>411090</v>
           </cell>
           <cell r="B268" t="str">
-            <v>クイックムーブ+</v>
+            <v>スレイプニル+</v>
           </cell>
         </row>
         <row r="269">
           <cell r="A269">
-            <v>412060</v>
+            <v>412010</v>
           </cell>
           <cell r="B269" t="str">
-            <v>チェイスマジック+</v>
+            <v>エクステンション+</v>
           </cell>
         </row>
         <row r="270">
           <cell r="A270">
-            <v>412070</v>
+            <v>412020</v>
           </cell>
           <cell r="B270" t="str">
-            <v>ソーサリーコネクト+</v>
+            <v>ヘブンリーラック+</v>
           </cell>
         </row>
         <row r="271">
           <cell r="A271">
-            <v>412080</v>
+            <v>412030</v>
           </cell>
           <cell r="B271" t="str">
-            <v>ウィンドライズ+</v>
+            <v>スウィフトカレント+</v>
           </cell>
         </row>
         <row r="272">
           <cell r="A272">
-            <v>412090</v>
+            <v>412040</v>
           </cell>
           <cell r="B272" t="str">
-            <v>アウトオブオーダー+</v>
+            <v>イヴェイドオール+</v>
           </cell>
         </row>
         <row r="273">
           <cell r="A273">
-            <v>413010</v>
+            <v>412050</v>
           </cell>
           <cell r="B273" t="str">
-            <v>アーマーコード+</v>
+            <v>クイックムーブ+</v>
           </cell>
         </row>
         <row r="274">
           <cell r="A274">
-            <v>413020</v>
+            <v>412060</v>
           </cell>
           <cell r="B274" t="str">
-            <v>クイックバリア+</v>
+            <v>チェイスマジック+</v>
           </cell>
         </row>
         <row r="275">
           <cell r="A275">
-            <v>413030</v>
+            <v>412070</v>
           </cell>
           <cell r="B275" t="str">
-            <v>クイックキュア+</v>
+            <v>ソーサリーコネクト+</v>
           </cell>
         </row>
         <row r="276">
           <cell r="A276">
-            <v>413040</v>
+            <v>412080</v>
           </cell>
           <cell r="B276" t="str">
-            <v>セルフシールド+</v>
+            <v>ウィンドライズ+</v>
           </cell>
         </row>
         <row r="277">
           <cell r="A277">
-            <v>413050</v>
+            <v>412090</v>
           </cell>
           <cell r="B277" t="str">
-            <v>パッシブジャミング+</v>
+            <v>アウトオブオーダー+</v>
           </cell>
         </row>
         <row r="278">
           <cell r="A278">
-            <v>413060</v>
+            <v>413010</v>
           </cell>
           <cell r="B278" t="str">
-            <v>サプライカバー+</v>
+            <v>アーマーコード+</v>
           </cell>
         </row>
         <row r="279">
           <cell r="A279">
-            <v>413070</v>
+            <v>413020</v>
           </cell>
           <cell r="B279" t="str">
-            <v>アシッドラッシュ+</v>
+            <v>クイックバリア+</v>
           </cell>
         </row>
         <row r="280">
           <cell r="A280">
-            <v>413080</v>
+            <v>413030</v>
           </cell>
           <cell r="B280" t="str">
-            <v>ライフスティール+</v>
+            <v>クイックキュア+</v>
           </cell>
         </row>
         <row r="281">
           <cell r="A281">
-            <v>413090</v>
+            <v>413040</v>
           </cell>
           <cell r="B281" t="str">
-            <v>アイスセイバー+</v>
+            <v>セルフシールド+</v>
           </cell>
         </row>
         <row r="282">
           <cell r="A282">
-            <v>414010</v>
+            <v>413050</v>
           </cell>
           <cell r="B282" t="str">
-            <v>ディバインシールド+</v>
+            <v>パッシブジャミング+</v>
           </cell>
         </row>
         <row r="283">
           <cell r="A283">
-            <v>414020</v>
+            <v>413060</v>
           </cell>
           <cell r="B283" t="str">
-            <v>ライフディバイド+</v>
+            <v>サプライカバー+</v>
           </cell>
         </row>
         <row r="284">
           <cell r="A284">
-            <v>414030</v>
+            <v>413070</v>
           </cell>
           <cell r="B284" t="str">
-            <v>エイミングスコープ+</v>
+            <v>アシッドラッシュ+</v>
           </cell>
         </row>
         <row r="285">
           <cell r="A285">
-            <v>414040</v>
+            <v>413080</v>
           </cell>
           <cell r="B285" t="str">
-            <v>リジェネレーション+</v>
+            <v>ライフスティール+</v>
           </cell>
         </row>
         <row r="286">
           <cell r="A286">
-            <v>414050</v>
+            <v>413090</v>
           </cell>
           <cell r="B286" t="str">
-            <v>ホープフルアイリス+</v>
+            <v>アイスセイバー+</v>
           </cell>
         </row>
         <row r="287">
           <cell r="A287">
-            <v>414060</v>
+            <v>414010</v>
           </cell>
           <cell r="B287" t="str">
-            <v>パッシブサプライ+</v>
+            <v>ディバインシールド+</v>
           </cell>
         </row>
         <row r="288">
           <cell r="A288">
-            <v>414070</v>
+            <v>414020</v>
           </cell>
           <cell r="B288" t="str">
-            <v>ホーミングクルセイド+</v>
+            <v>ライフディバイド+</v>
           </cell>
         </row>
         <row r="289">
           <cell r="A289">
-            <v>414080</v>
+            <v>414030</v>
           </cell>
           <cell r="B289" t="str">
-            <v>クイックヒール+</v>
+            <v>エイミングスコープ+</v>
           </cell>
         </row>
         <row r="290">
           <cell r="A290">
-            <v>414090</v>
+            <v>414040</v>
           </cell>
           <cell r="B290" t="str">
-            <v>リレイズ+</v>
+            <v>リジェネレーション+</v>
           </cell>
         </row>
         <row r="291">
           <cell r="A291">
-            <v>415010</v>
+            <v>414050</v>
           </cell>
           <cell r="B291" t="str">
-            <v>イーグルアイ+</v>
+            <v>ホープフルアイリス+</v>
           </cell>
         </row>
         <row r="292">
           <cell r="A292">
-            <v>415020</v>
+            <v>414060</v>
           </cell>
           <cell r="B292" t="str">
-            <v>ネヴァーエンド+</v>
+            <v>パッシブサプライ+</v>
           </cell>
         </row>
         <row r="293">
           <cell r="A293">
-            <v>415030</v>
+            <v>414070</v>
           </cell>
           <cell r="B293" t="str">
-            <v>グレイブアクト+</v>
+            <v>ホーミングクルセイド+</v>
           </cell>
         </row>
         <row r="294">
           <cell r="A294">
-            <v>415040</v>
+            <v>414080</v>
           </cell>
           <cell r="B294" t="str">
-            <v>スカルグラッジ+</v>
+            <v>クイックヒール+</v>
           </cell>
         </row>
         <row r="295">
           <cell r="A295">
-            <v>415050</v>
+            <v>414090</v>
           </cell>
           <cell r="B295" t="str">
-            <v>ネガティブドレイン+</v>
+            <v>リレイズ+</v>
           </cell>
         </row>
         <row r="296">
           <cell r="A296">
-            <v>415060</v>
+            <v>415010</v>
           </cell>
           <cell r="B296" t="str">
-            <v>アンデッドペイン+</v>
+            <v>イーグルアイ+</v>
           </cell>
         </row>
         <row r="297">
           <cell r="A297">
-            <v>415070</v>
+            <v>415020</v>
           </cell>
           <cell r="B297" t="str">
-            <v>ジャックポッド+</v>
+            <v>ネヴァーエンド+</v>
           </cell>
         </row>
         <row r="298">
           <cell r="A298">
-            <v>415080</v>
+            <v>415030</v>
           </cell>
           <cell r="B298" t="str">
-            <v>ヒールハント+</v>
+            <v>グレイブアクト+</v>
           </cell>
         </row>
         <row r="299">
           <cell r="A299">
+            <v>415040</v>
+          </cell>
+          <cell r="B299" t="str">
+            <v>スカルグラッジ+</v>
+          </cell>
+        </row>
+        <row r="300">
+          <cell r="A300">
+            <v>415050</v>
+          </cell>
+          <cell r="B300" t="str">
+            <v>ネガティブドレイン+</v>
+          </cell>
+        </row>
+        <row r="301">
+          <cell r="A301">
+            <v>415060</v>
+          </cell>
+          <cell r="B301" t="str">
+            <v>アンデッドペイン+</v>
+          </cell>
+        </row>
+        <row r="302">
+          <cell r="A302">
+            <v>415070</v>
+          </cell>
+          <cell r="B302" t="str">
+            <v>ジャックポッド+</v>
+          </cell>
+        </row>
+        <row r="303">
+          <cell r="A303">
+            <v>415080</v>
+          </cell>
+          <cell r="B303" t="str">
+            <v>ヒールハント+</v>
+          </cell>
+        </row>
+        <row r="304">
+          <cell r="A304">
             <v>415090</v>
           </cell>
-          <cell r="B299" t="str">
+          <cell r="B304" t="str">
             <v>クイックカース+</v>
+          </cell>
+        </row>
+        <row r="305">
+          <cell r="A305">
+            <v>501010</v>
+          </cell>
+          <cell r="B305" t="str">
+            <v>ATK+2</v>
+          </cell>
+        </row>
+        <row r="306">
+          <cell r="A306">
+            <v>501020</v>
+          </cell>
+          <cell r="B306" t="str">
+            <v>火傷耐性+25%</v>
+          </cell>
+        </row>
+        <row r="307">
+          <cell r="A307">
+            <v>501030</v>
+          </cell>
+          <cell r="B307" t="str">
+            <v>ATK+2</v>
+          </cell>
+        </row>
+        <row r="308">
+          <cell r="A308">
+            <v>501040</v>
+          </cell>
+          <cell r="B308" t="str">
+            <v>ATK+4</v>
+          </cell>
+        </row>
+        <row r="309">
+          <cell r="A309">
+            <v>501041</v>
+          </cell>
+          <cell r="B309" t="str">
+            <v>会心率+10%</v>
+          </cell>
+        </row>
+        <row r="310">
+          <cell r="A310">
+            <v>502010</v>
+          </cell>
+          <cell r="B310" t="str">
+            <v>回避率+5%</v>
+          </cell>
+        </row>
+        <row r="311">
+          <cell r="A311">
+            <v>502020</v>
+          </cell>
+          <cell r="B311" t="str">
+            <v>SPD+1</v>
+          </cell>
+        </row>
+        <row r="312">
+          <cell r="A312">
+            <v>502030</v>
+          </cell>
+          <cell r="B312" t="str">
+            <v>SPD+1</v>
+          </cell>
+        </row>
+        <row r="313">
+          <cell r="A313">
+            <v>502040</v>
+          </cell>
+          <cell r="B313" t="str">
+            <v>SPD+2</v>
+          </cell>
+        </row>
+        <row r="314">
+          <cell r="A314">
+            <v>502041</v>
+          </cell>
+          <cell r="B314" t="str">
+            <v>回避率+15%</v>
+          </cell>
+        </row>
+        <row r="315">
+          <cell r="A315">
+            <v>503010</v>
+          </cell>
+          <cell r="B315" t="str">
+            <v>DEF+2</v>
+          </cell>
+        </row>
+        <row r="316">
+          <cell r="A316">
+            <v>503020</v>
+          </cell>
+          <cell r="B316" t="str">
+            <v>DEF+2</v>
+          </cell>
+        </row>
+        <row r="317">
+          <cell r="A317">
+            <v>503030</v>
+          </cell>
+          <cell r="B317" t="str">
+            <v>DEF+2</v>
+          </cell>
+        </row>
+        <row r="318">
+          <cell r="A318">
+            <v>503040</v>
+          </cell>
+          <cell r="B318" t="str">
+            <v>DEF+4</v>
+          </cell>
+        </row>
+        <row r="319">
+          <cell r="A319">
+            <v>503041</v>
+          </cell>
+          <cell r="B319" t="str">
+            <v>HP回復効果+20%</v>
+          </cell>
+        </row>
+        <row r="320">
+          <cell r="A320">
+            <v>504010</v>
+          </cell>
+          <cell r="B320" t="str">
+            <v>最大HP+4</v>
+          </cell>
+        </row>
+        <row r="321">
+          <cell r="A321">
+            <v>504020</v>
+          </cell>
+          <cell r="B321" t="str">
+            <v>最大HP+4</v>
+          </cell>
+        </row>
+        <row r="322">
+          <cell r="A322">
+            <v>504030</v>
+          </cell>
+          <cell r="B322" t="str">
+            <v>命中率+5%</v>
+          </cell>
+        </row>
+        <row r="323">
+          <cell r="A323">
+            <v>504040</v>
+          </cell>
+          <cell r="B323" t="str">
+            <v>最大HP+10</v>
+          </cell>
+        </row>
+        <row r="324">
+          <cell r="A324">
+            <v>505010</v>
+          </cell>
+          <cell r="B324" t="str">
+            <v>会心率+5%</v>
+          </cell>
+        </row>
+        <row r="325">
+          <cell r="A325">
+            <v>505020</v>
+          </cell>
+          <cell r="B325" t="str">
+            <v>SPD+1</v>
+          </cell>
+        </row>
+        <row r="326">
+          <cell r="A326">
+            <v>505030</v>
+          </cell>
+          <cell r="B326" t="str">
+            <v>回避率+5%</v>
+          </cell>
+        </row>
+        <row r="327">
+          <cell r="A327">
+            <v>505040</v>
+          </cell>
+          <cell r="B327" t="str">
+            <v>暗闇無効</v>
+          </cell>
+        </row>
+        <row r="328">
+          <cell r="A328">
+            <v>506010</v>
+          </cell>
+          <cell r="B328" t="str">
+            <v>獲得Exp+30%</v>
+          </cell>
+        </row>
+        <row r="329">
+          <cell r="A329">
+            <v>506020</v>
+          </cell>
+          <cell r="B329" t="str">
+            <v>ATK⇔DEF交換</v>
           </cell>
         </row>
       </sheetData>
@@ -3883,7 +4123,7 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -3910,7 +4150,7 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -6000,7 +6240,7 @@
         <v>バブルブロウ</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>70</v>
@@ -6120,7 +6360,7 @@
         <v>アビサルデスペア</v>
       </c>
       <c r="D8">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E8">
         <v>100</v>
@@ -6240,7 +6480,7 @@
         <v>コンセントレイト</v>
       </c>
       <c r="D13">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <v>150</v>
@@ -6360,7 +6600,7 @@
         <v>イクスティンクション</v>
       </c>
       <c r="D18">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E18">
         <v>150</v>
@@ -6480,7 +6720,7 @@
         <v>ショックインパルス</v>
       </c>
       <c r="D23">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E23">
         <v>100</v>
@@ -6600,7 +6840,7 @@
         <v>アーテニーストライク</v>
       </c>
       <c r="D28">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E28">
         <v>150</v>
@@ -6720,7 +6960,7 @@
         <v>アクアミラージュ</v>
       </c>
       <c r="D33">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E33">
         <v>100</v>
@@ -6840,7 +7080,7 @@
         <v>カウンターオーラ</v>
       </c>
       <c r="D38">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E38">
         <v>100</v>
@@ -6953,23 +7193,23 @@
         <v>9</v>
       </c>
       <c r="B43">
-        <v>1040</v>
+        <v>11110</v>
       </c>
       <c r="C43" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B43,[1]TextData!A:A))</f>
-        <v>ソードアダプト</v>
+        <v>フレイムセイバー</v>
       </c>
       <c r="D43">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E43">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>14013</v>
+        <v>0</v>
       </c>
       <c r="G43">
-        <v>1023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -7080,7 +7320,7 @@
         <v>スペルバニシング</v>
       </c>
       <c r="D48">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E48">
         <v>100</v>
@@ -7200,7 +7440,7 @@
         <v>エスコートソール</v>
       </c>
       <c r="D53">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E53">
         <v>100</v>
@@ -7320,7 +7560,7 @@
         <v>イーグルアイ</v>
       </c>
       <c r="D58">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -7440,7 +7680,7 @@
         <v>ヒーリング</v>
       </c>
       <c r="D63">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E63">
         <v>100</v>
@@ -7560,7 +7800,7 @@
         <v>リジェネレーション</v>
       </c>
       <c r="D68">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -7680,7 +7920,7 @@
         <v>フレイムレイン</v>
       </c>
       <c r="D73">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E73">
         <v>100</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -89,7 +89,7 @@
     <t>闇</t>
   </si>
   <si>
-    <t>basic enemy_097</t>
+    <t>Bee</t>
   </si>
   <si>
     <t>雷</t>
@@ -125,7 +125,7 @@
     <t>Creeper</t>
   </si>
   <si>
-    <t>NY_CJ_monster_015_1</t>
+    <t>Imp</t>
   </si>
   <si>
     <t>白</t>
@@ -412,9 +412,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -433,8 +433,92 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -448,16 +532,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -472,38 +549,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -514,9 +562,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -524,53 +571,6 @@
     <font>
       <b/>
       <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -586,61 +586,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -658,7 +610,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -670,19 +748,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -694,79 +766,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -784,7 +784,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -804,35 +804,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -852,13 +830,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -877,6 +859,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -885,145 +885,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1605,271 +1605,271 @@
         </row>
         <row r="62">
           <cell r="A62">
-            <v>11010</v>
+            <v>10210</v>
           </cell>
           <cell r="B62" t="str">
-            <v>ウルフソウル</v>
+            <v>装備スロット数+1</v>
           </cell>
         </row>
         <row r="63">
           <cell r="A63">
-            <v>11020</v>
+            <v>11010</v>
           </cell>
           <cell r="B63" t="str">
-            <v>プリディカメント</v>
+            <v>ウルフソウル</v>
           </cell>
         </row>
         <row r="64">
           <cell r="A64">
-            <v>11030</v>
+            <v>11020</v>
           </cell>
           <cell r="B64" t="str">
-            <v>アサルトシフト</v>
+            <v>プリディカメント</v>
           </cell>
         </row>
         <row r="65">
           <cell r="A65">
-            <v>11040</v>
+            <v>11030</v>
           </cell>
           <cell r="B65" t="str">
-            <v>アクティブギフト</v>
+            <v>アサルトシフト</v>
           </cell>
         </row>
         <row r="66">
           <cell r="A66">
-            <v>11050</v>
+            <v>11040</v>
           </cell>
           <cell r="B66" t="str">
-            <v>イグナイテッド</v>
+            <v>アクティブギフト</v>
           </cell>
         </row>
         <row r="67">
           <cell r="A67">
-            <v>11060</v>
+            <v>11050</v>
           </cell>
           <cell r="B67" t="str">
-            <v>ライジングファイア</v>
+            <v>イグナイテッド</v>
           </cell>
         </row>
         <row r="68">
           <cell r="A68">
-            <v>11070</v>
+            <v>11060</v>
           </cell>
           <cell r="B68" t="str">
-            <v>ルージュバック</v>
+            <v>ライジングファイア</v>
           </cell>
         </row>
         <row r="69">
           <cell r="A69">
-            <v>11080</v>
+            <v>11070</v>
           </cell>
           <cell r="B69" t="str">
-            <v>パワーエール</v>
+            <v>ルージュバック</v>
           </cell>
         </row>
         <row r="70">
           <cell r="A70">
-            <v>11090</v>
+            <v>11080</v>
           </cell>
           <cell r="B70" t="str">
-            <v>スレイプニル</v>
+            <v>パワーエール</v>
           </cell>
         </row>
         <row r="71">
           <cell r="A71">
-            <v>11100</v>
+            <v>11090</v>
           </cell>
           <cell r="B71" t="str">
-            <v>レストア</v>
+            <v>スレイプニル</v>
           </cell>
         </row>
         <row r="72">
           <cell r="A72">
-            <v>11110</v>
+            <v>11100</v>
           </cell>
           <cell r="B72" t="str">
-            <v>フレイムセイバー</v>
+            <v>レストア</v>
           </cell>
         </row>
         <row r="73">
           <cell r="A73">
-            <v>12010</v>
+            <v>11110</v>
           </cell>
           <cell r="B73" t="str">
-            <v>コンセントレイト</v>
+            <v>フレイムセイバー</v>
           </cell>
         </row>
         <row r="74">
           <cell r="A74">
-            <v>12020</v>
+            <v>12010</v>
           </cell>
           <cell r="B74" t="str">
-            <v>ヘブンリーラック</v>
+            <v>コンセントレイト</v>
           </cell>
         </row>
         <row r="75">
           <cell r="A75">
-            <v>12030</v>
+            <v>12020</v>
           </cell>
           <cell r="B75" t="str">
-            <v>スウィフトカレント</v>
+            <v>ヘブンリーラック</v>
           </cell>
         </row>
         <row r="76">
           <cell r="A76">
-            <v>12040</v>
+            <v>12030</v>
           </cell>
           <cell r="B76" t="str">
-            <v>イヴェイドオール</v>
+            <v>スウィフトカレント</v>
           </cell>
         </row>
         <row r="77">
           <cell r="A77">
-            <v>12050</v>
+            <v>12040</v>
           </cell>
           <cell r="B77" t="str">
-            <v>クイックムーブ</v>
+            <v>イヴェイドオール</v>
           </cell>
         </row>
         <row r="78">
           <cell r="A78">
-            <v>12060</v>
+            <v>12050</v>
           </cell>
           <cell r="B78" t="str">
-            <v>チェイスマジック</v>
+            <v>クイックムーブ</v>
           </cell>
         </row>
         <row r="79">
           <cell r="A79">
-            <v>12070</v>
+            <v>12060</v>
           </cell>
           <cell r="B79" t="str">
-            <v>ソーサリーコネクト</v>
+            <v>チェイスマジック</v>
           </cell>
         </row>
         <row r="80">
           <cell r="A80">
-            <v>12080</v>
+            <v>12070</v>
           </cell>
           <cell r="B80" t="str">
-            <v>ウィンドライズ</v>
+            <v>ソーサリーコネクト</v>
           </cell>
         </row>
         <row r="81">
           <cell r="A81">
-            <v>12090</v>
+            <v>12080</v>
           </cell>
           <cell r="B81" t="str">
-            <v>アウトオブオーダー</v>
+            <v>ウィンドライズ</v>
           </cell>
         </row>
         <row r="82">
           <cell r="A82">
-            <v>12100</v>
+            <v>12090</v>
           </cell>
           <cell r="B82" t="str">
-            <v>ワンスパニッシュ</v>
+            <v>アウトオブオーダー</v>
           </cell>
         </row>
         <row r="83">
           <cell r="A83">
-            <v>12110</v>
+            <v>12100</v>
           </cell>
           <cell r="B83" t="str">
-            <v>アクトスタンス</v>
+            <v>ワンスパニッシュ</v>
           </cell>
         </row>
         <row r="84">
           <cell r="A84">
-            <v>13010</v>
+            <v>12110</v>
           </cell>
           <cell r="B84" t="str">
-            <v>アーマーコード</v>
+            <v>アクトスタンス</v>
           </cell>
         </row>
         <row r="85">
           <cell r="A85">
-            <v>13020</v>
+            <v>13010</v>
           </cell>
           <cell r="B85" t="str">
-            <v>クイックバリア</v>
+            <v>アーマーコード</v>
           </cell>
         </row>
         <row r="86">
           <cell r="A86">
-            <v>13030</v>
+            <v>13020</v>
           </cell>
           <cell r="B86" t="str">
-            <v>クイックキュア</v>
+            <v>クイックバリア</v>
           </cell>
         </row>
         <row r="87">
           <cell r="A87">
-            <v>13040</v>
+            <v>13030</v>
           </cell>
           <cell r="B87" t="str">
-            <v>セルフシールド</v>
+            <v>クイックキュア</v>
           </cell>
         </row>
         <row r="88">
           <cell r="A88">
-            <v>13050</v>
+            <v>13040</v>
           </cell>
           <cell r="B88" t="str">
-            <v>パッシブジャミング</v>
+            <v>セルフシールド</v>
           </cell>
         </row>
         <row r="89">
           <cell r="A89">
-            <v>13060</v>
+            <v>13050</v>
           </cell>
           <cell r="B89" t="str">
-            <v>サプライカバー</v>
+            <v>パッシブジャミング</v>
           </cell>
         </row>
         <row r="90">
           <cell r="A90">
-            <v>13070</v>
+            <v>13060</v>
           </cell>
           <cell r="B90" t="str">
-            <v>アシッドラッシュ</v>
+            <v>サプライカバー</v>
           </cell>
         </row>
         <row r="91">
           <cell r="A91">
-            <v>13080</v>
+            <v>13070</v>
           </cell>
           <cell r="B91" t="str">
-            <v>ライフスティール</v>
+            <v>アシッドラッシュ</v>
           </cell>
         </row>
         <row r="92">
           <cell r="A92">
-            <v>13090</v>
+            <v>13080</v>
           </cell>
           <cell r="B92" t="str">
-            <v>アイスセイバー</v>
+            <v>ライフスティール</v>
           </cell>
         </row>
         <row r="93">
           <cell r="A93">
-            <v>13100</v>
+            <v>13090</v>
           </cell>
           <cell r="B93" t="str">
-            <v>ルミナスカバー</v>
+            <v>アイスセイバー</v>
           </cell>
         </row>
         <row r="94">
           <cell r="A94">
-            <v>13110</v>
+            <v>13100</v>
           </cell>
           <cell r="B94" t="str">
-            <v>デコイプラス</v>
+            <v>ルミナスカバー</v>
           </cell>
         </row>
         <row r="95">
           <cell r="A95">
-            <v>13111</v>
+            <v>13110</v>
           </cell>
           <cell r="B95" t="str">
             <v>デコイプラス</v>
@@ -1877,207 +1877,207 @@
         </row>
         <row r="96">
           <cell r="A96">
-            <v>13120</v>
+            <v>13111</v>
           </cell>
           <cell r="B96" t="str">
-            <v>アフターシールド</v>
+            <v>デコイプラス</v>
           </cell>
         </row>
         <row r="97">
           <cell r="A97">
-            <v>13130</v>
+            <v>13120</v>
           </cell>
           <cell r="B97" t="str">
-            <v>カバープラス</v>
+            <v>アフターシールド</v>
           </cell>
         </row>
         <row r="98">
           <cell r="A98">
-            <v>14010</v>
+            <v>13130</v>
           </cell>
           <cell r="B98" t="str">
-            <v>ディバインシールド</v>
+            <v>カバープラス</v>
           </cell>
         </row>
         <row r="99">
           <cell r="A99">
-            <v>14020</v>
+            <v>14010</v>
           </cell>
           <cell r="B99" t="str">
-            <v>ライフディバイド</v>
+            <v>ディバインシールド</v>
           </cell>
         </row>
         <row r="100">
           <cell r="A100">
-            <v>14030</v>
+            <v>14020</v>
           </cell>
           <cell r="B100" t="str">
-            <v>エイミングスコープ</v>
+            <v>ライフディバイド</v>
           </cell>
         </row>
         <row r="101">
           <cell r="A101">
-            <v>14040</v>
+            <v>14030</v>
           </cell>
           <cell r="B101" t="str">
-            <v>リジェネレーション</v>
+            <v>エイミングスコープ</v>
           </cell>
         </row>
         <row r="102">
           <cell r="A102">
-            <v>14050</v>
+            <v>14040</v>
           </cell>
           <cell r="B102" t="str">
-            <v>ホープフルアイリス</v>
+            <v>リジェネレーション</v>
           </cell>
         </row>
         <row r="103">
           <cell r="A103">
-            <v>14060</v>
+            <v>14050</v>
           </cell>
           <cell r="B103" t="str">
-            <v>パッシブサプライ</v>
+            <v>ホープフルアイリス</v>
           </cell>
         </row>
         <row r="104">
           <cell r="A104">
-            <v>14070</v>
+            <v>14060</v>
           </cell>
           <cell r="B104" t="str">
-            <v>ホーミングクルセイド</v>
+            <v>パッシブサプライ</v>
           </cell>
         </row>
         <row r="105">
           <cell r="A105">
-            <v>14080</v>
+            <v>14070</v>
           </cell>
           <cell r="B105" t="str">
-            <v>クイックヒール</v>
+            <v>ホーミングクルセイド</v>
           </cell>
         </row>
         <row r="106">
           <cell r="A106">
-            <v>14090</v>
+            <v>14080</v>
           </cell>
           <cell r="B106" t="str">
-            <v>リレイズ</v>
+            <v>クイックヒール</v>
           </cell>
         </row>
         <row r="107">
           <cell r="A107">
-            <v>14100</v>
+            <v>14090</v>
           </cell>
           <cell r="B107" t="str">
-            <v>ファストヒール</v>
+            <v>リレイズ</v>
           </cell>
         </row>
         <row r="108">
           <cell r="A108">
-            <v>14110</v>
+            <v>14100</v>
           </cell>
           <cell r="B108" t="str">
-            <v>セルフケア</v>
+            <v>ファストヒール</v>
           </cell>
         </row>
         <row r="109">
           <cell r="A109">
-            <v>14120</v>
+            <v>14110</v>
           </cell>
           <cell r="B109" t="str">
-            <v>ファーストエイド</v>
+            <v>セルフケア</v>
           </cell>
         </row>
         <row r="110">
           <cell r="A110">
-            <v>15010</v>
+            <v>14120</v>
           </cell>
           <cell r="B110" t="str">
-            <v>イーグルアイ</v>
+            <v>ファーストエイド</v>
           </cell>
         </row>
         <row r="111">
           <cell r="A111">
-            <v>15020</v>
+            <v>15010</v>
           </cell>
           <cell r="B111" t="str">
-            <v>ネヴァーエンド</v>
+            <v>イーグルアイ</v>
           </cell>
         </row>
         <row r="112">
           <cell r="A112">
-            <v>15030</v>
+            <v>15020</v>
           </cell>
           <cell r="B112" t="str">
-            <v>グレイブアクト</v>
+            <v>ネヴァーエンド</v>
           </cell>
         </row>
         <row r="113">
           <cell r="A113">
-            <v>15040</v>
+            <v>15030</v>
           </cell>
           <cell r="B113" t="str">
-            <v>スカルグラッジ</v>
+            <v>グレイブアクト</v>
           </cell>
         </row>
         <row r="114">
           <cell r="A114">
-            <v>15050</v>
+            <v>15040</v>
           </cell>
           <cell r="B114" t="str">
-            <v>ネガティブドレイン</v>
+            <v>スカルグラッジ</v>
           </cell>
         </row>
         <row r="115">
           <cell r="A115">
-            <v>15060</v>
+            <v>15050</v>
           </cell>
           <cell r="B115" t="str">
-            <v>アンデッドペイン</v>
+            <v>ネガティブドレイン</v>
           </cell>
         </row>
         <row r="116">
           <cell r="A116">
-            <v>15070</v>
+            <v>15060</v>
           </cell>
           <cell r="B116" t="str">
-            <v>ジャックポッド</v>
+            <v>アンデッドペイン</v>
           </cell>
         </row>
         <row r="117">
           <cell r="A117">
-            <v>15080</v>
+            <v>15070</v>
           </cell>
           <cell r="B117" t="str">
-            <v>ヒールハント</v>
+            <v>ジャックポッド</v>
           </cell>
         </row>
         <row r="118">
           <cell r="A118">
-            <v>15090</v>
+            <v>15080</v>
           </cell>
           <cell r="B118" t="str">
-            <v>クイックカース</v>
+            <v>ヒールハント</v>
           </cell>
         </row>
         <row r="119">
           <cell r="A119">
-            <v>15100</v>
+            <v>15090</v>
           </cell>
           <cell r="B119" t="str">
-            <v>リヴェンジャー</v>
+            <v>クイックカース</v>
           </cell>
         </row>
         <row r="120">
           <cell r="A120">
-            <v>15110</v>
+            <v>15100</v>
           </cell>
           <cell r="B120" t="str">
-            <v>リープリアクト</v>
+            <v>リヴェンジャー</v>
           </cell>
         </row>
         <row r="121">
           <cell r="A121">
-            <v>15112</v>
+            <v>15110</v>
           </cell>
           <cell r="B121" t="str">
             <v>リープリアクト</v>
@@ -2085,191 +2085,191 @@
         </row>
         <row r="122">
           <cell r="A122">
-            <v>15120</v>
+            <v>15112</v>
           </cell>
           <cell r="B122" t="str">
-            <v>ディレイドパッシブ</v>
+            <v>リープリアクト</v>
           </cell>
         </row>
         <row r="123">
           <cell r="A123">
-            <v>15130</v>
+            <v>15120</v>
           </cell>
           <cell r="B123" t="str">
-            <v>シャドウケイプ</v>
+            <v>ディレイドパッシブ</v>
           </cell>
         </row>
         <row r="124">
           <cell r="A124">
-            <v>20010</v>
+            <v>15130</v>
           </cell>
           <cell r="B124" t="str">
-            <v>ウェイトユニゾン</v>
+            <v>シャドウケイプ</v>
           </cell>
         </row>
         <row r="125">
           <cell r="A125">
-            <v>30010</v>
+            <v>20010</v>
           </cell>
           <cell r="B125" t="str">
-            <v>ラーニングピアス</v>
+            <v>ウェイトユニゾン</v>
           </cell>
         </row>
         <row r="126">
           <cell r="A126">
-            <v>30020</v>
+            <v>30010</v>
           </cell>
           <cell r="B126" t="str">
-            <v>スティールヒール</v>
+            <v>ラーニングピアス</v>
           </cell>
         </row>
         <row r="127">
           <cell r="A127">
-            <v>30030</v>
+            <v>30020</v>
           </cell>
           <cell r="B127" t="str">
-            <v>ガッツ</v>
+            <v>スティールヒール</v>
           </cell>
         </row>
         <row r="128">
           <cell r="A128">
-            <v>100110</v>
+            <v>30030</v>
           </cell>
           <cell r="B128" t="str">
-            <v>ソーイングアームド</v>
+            <v>ガッツ</v>
           </cell>
         </row>
         <row r="129">
           <cell r="A129">
-            <v>100120</v>
+            <v>100110</v>
           </cell>
           <cell r="B129" t="str">
-            <v>エターナルロンド</v>
+            <v>ソーイングアームド</v>
           </cell>
         </row>
         <row r="130">
           <cell r="A130">
-            <v>100210</v>
+            <v>100120</v>
           </cell>
           <cell r="B130" t="str">
-            <v>アブソリュートパリィ</v>
+            <v>エターナルロンド</v>
           </cell>
         </row>
         <row r="131">
           <cell r="A131">
-            <v>100220</v>
+            <v>100210</v>
           </cell>
           <cell r="B131" t="str">
-            <v>レヴェリー</v>
+            <v>アブソリュートパリィ</v>
           </cell>
         </row>
         <row r="132">
           <cell r="A132">
-            <v>100310</v>
+            <v>100220</v>
           </cell>
           <cell r="B132" t="str">
-            <v>セイクリッドバリア</v>
+            <v>レヴェリー</v>
           </cell>
         </row>
         <row r="133">
           <cell r="A133">
-            <v>100320</v>
+            <v>100310</v>
           </cell>
           <cell r="B133" t="str">
-            <v>リベンジニードル</v>
+            <v>セイクリッドバリア</v>
           </cell>
         </row>
         <row r="134">
           <cell r="A134">
-            <v>100410</v>
+            <v>100320</v>
           </cell>
           <cell r="B134" t="str">
-            <v>アバンデンス</v>
+            <v>リベンジニードル</v>
           </cell>
         </row>
         <row r="135">
           <cell r="A135">
-            <v>100420</v>
+            <v>100410</v>
           </cell>
           <cell r="B135" t="str">
-            <v>ハーヴェスト</v>
+            <v>アバンデンス</v>
           </cell>
         </row>
         <row r="136">
           <cell r="A136">
-            <v>100510</v>
+            <v>100420</v>
           </cell>
           <cell r="B136" t="str">
-            <v>カースドブレイク</v>
+            <v>ハーヴェスト</v>
           </cell>
         </row>
         <row r="137">
           <cell r="A137">
-            <v>100520</v>
+            <v>100510</v>
           </cell>
           <cell r="B137" t="str">
-            <v>ムーンライトレイ</v>
+            <v>カースドブレイク</v>
           </cell>
         </row>
         <row r="138">
           <cell r="A138">
-            <v>100610</v>
+            <v>100520</v>
           </cell>
           <cell r="B138" t="str">
-            <v>サンフレイム</v>
+            <v>ムーンライトレイ</v>
           </cell>
         </row>
         <row r="139">
           <cell r="A139">
-            <v>100620</v>
+            <v>100610</v>
           </cell>
           <cell r="B139" t="str">
-            <v>フレイムタン</v>
+            <v>サンフレイム</v>
           </cell>
         </row>
         <row r="140">
           <cell r="A140">
-            <v>100710</v>
+            <v>100620</v>
           </cell>
           <cell r="B140" t="str">
-            <v>ライズザフラッグ</v>
+            <v>フレイムタン</v>
           </cell>
         </row>
         <row r="141">
           <cell r="A141">
-            <v>100720</v>
+            <v>100710</v>
           </cell>
           <cell r="B141" t="str">
-            <v>オーバーリミット</v>
+            <v>ライズザフラッグ</v>
           </cell>
         </row>
         <row r="142">
           <cell r="A142">
-            <v>100810</v>
+            <v>100720</v>
           </cell>
           <cell r="B142" t="str">
-            <v>テンパランス</v>
+            <v>オーバーリミット</v>
           </cell>
         </row>
         <row r="143">
           <cell r="A143">
-            <v>100820</v>
+            <v>100810</v>
           </cell>
           <cell r="B143" t="str">
-            <v>シエルクルセイダー</v>
+            <v>テンパランス</v>
           </cell>
         </row>
         <row r="144">
           <cell r="A144">
-            <v>100910</v>
+            <v>100820</v>
           </cell>
           <cell r="B144" t="str">
-            <v>バーニングカウンター</v>
+            <v>シエルクルセイダー</v>
           </cell>
         </row>
         <row r="145">
           <cell r="A145">
-            <v>100911</v>
+            <v>100910</v>
           </cell>
           <cell r="B145" t="str">
             <v>バーニングカウンター</v>
@@ -2277,15 +2277,15 @@
         </row>
         <row r="146">
           <cell r="A146">
-            <v>100920</v>
+            <v>100911</v>
           </cell>
           <cell r="B146" t="str">
-            <v>プロミネンス</v>
+            <v>バーニングカウンター</v>
           </cell>
         </row>
         <row r="147">
           <cell r="A147">
-            <v>100921</v>
+            <v>100920</v>
           </cell>
           <cell r="B147" t="str">
             <v>プロミネンス</v>
@@ -2293,127 +2293,127 @@
         </row>
         <row r="148">
           <cell r="A148">
-            <v>101010</v>
+            <v>100921</v>
           </cell>
           <cell r="B148" t="str">
-            <v>エウロス</v>
+            <v>プロミネンス</v>
           </cell>
         </row>
         <row r="149">
           <cell r="A149">
-            <v>101020</v>
+            <v>101010</v>
           </cell>
           <cell r="B149" t="str">
-            <v>ボレアス</v>
+            <v>エウロス</v>
           </cell>
         </row>
         <row r="150">
           <cell r="A150">
-            <v>101110</v>
+            <v>101020</v>
           </cell>
           <cell r="B150" t="str">
-            <v>アバランシュ</v>
+            <v>ボレアス</v>
           </cell>
         </row>
         <row r="151">
           <cell r="A151">
-            <v>101120</v>
+            <v>101110</v>
           </cell>
           <cell r="B151" t="str">
-            <v>ブリザードコフィン</v>
+            <v>アバランシュ</v>
           </cell>
         </row>
         <row r="152">
           <cell r="A152">
-            <v>110110</v>
+            <v>101120</v>
           </cell>
           <cell r="B152" t="str">
-            <v>ウィビングヒストリー</v>
+            <v>ブリザードコフィン</v>
           </cell>
         </row>
         <row r="153">
           <cell r="A153">
-            <v>110120</v>
+            <v>110110</v>
           </cell>
           <cell r="B153" t="str">
-            <v>アンライバルド</v>
+            <v>ウィビングヒストリー</v>
           </cell>
         </row>
         <row r="154">
           <cell r="A154">
-            <v>200110</v>
+            <v>110120</v>
           </cell>
           <cell r="B154" t="str">
-            <v>スリータイムス</v>
+            <v>アンライバルド</v>
           </cell>
         </row>
         <row r="155">
           <cell r="A155">
-            <v>200120</v>
+            <v>200110</v>
           </cell>
           <cell r="B155" t="str">
-            <v>アングリークライ</v>
+            <v>スリータイムス</v>
           </cell>
         </row>
         <row r="156">
           <cell r="A156">
-            <v>200210</v>
+            <v>200120</v>
           </cell>
           <cell r="B156" t="str">
-            <v>マイトレインフォース</v>
+            <v>アングリークライ</v>
           </cell>
         </row>
         <row r="157">
           <cell r="A157">
-            <v>200220</v>
+            <v>200210</v>
           </cell>
           <cell r="B157" t="str">
-            <v>カタストロフィ</v>
+            <v>マイトレインフォース</v>
           </cell>
         </row>
         <row r="158">
           <cell r="A158">
-            <v>200230</v>
+            <v>200220</v>
           </cell>
           <cell r="B158" t="str">
-            <v>悪魔(ベリト)</v>
+            <v>カタストロフィ</v>
           </cell>
         </row>
         <row r="159">
           <cell r="A159">
-            <v>200310</v>
+            <v>200230</v>
           </cell>
           <cell r="B159" t="str">
-            <v>プルガシオン</v>
+            <v>悪魔(ベリト)</v>
           </cell>
         </row>
         <row r="160">
           <cell r="A160">
-            <v>200320</v>
+            <v>200310</v>
           </cell>
           <cell r="B160" t="str">
-            <v>プリエステス</v>
+            <v>プルガシオン</v>
           </cell>
         </row>
         <row r="161">
           <cell r="A161">
-            <v>200330</v>
+            <v>200320</v>
           </cell>
           <cell r="B161" t="str">
-            <v>悪魔(パイモン)</v>
+            <v>プリエステス</v>
           </cell>
         </row>
         <row r="162">
           <cell r="A162">
-            <v>200410</v>
+            <v>200330</v>
           </cell>
           <cell r="B162" t="str">
-            <v>コウソクテンショウ</v>
+            <v>悪魔(パイモン)</v>
           </cell>
         </row>
         <row r="163">
           <cell r="A163">
-            <v>200411</v>
+            <v>200410</v>
           </cell>
           <cell r="B163" t="str">
             <v>コウソクテンショウ</v>
@@ -2421,1191 +2421,1191 @@
         </row>
         <row r="164">
           <cell r="A164">
-            <v>200420</v>
+            <v>200411</v>
           </cell>
           <cell r="B164" t="str">
-            <v>アンチバフ</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="165">
           <cell r="A165">
-            <v>200430</v>
+            <v>200420</v>
           </cell>
           <cell r="B165" t="str">
-            <v>悪魔(アンドラス)</v>
+            <v>アンチバフ</v>
           </cell>
         </row>
         <row r="166">
           <cell r="A166">
-            <v>200510</v>
+            <v>200430</v>
           </cell>
           <cell r="B166" t="str">
-            <v>カウントダウン</v>
+            <v>悪魔(アンドラス)</v>
           </cell>
         </row>
         <row r="167">
           <cell r="A167">
-            <v>200520</v>
+            <v>200510</v>
           </cell>
           <cell r="B167" t="str">
-            <v>グラウンドゼロ</v>
+            <v>カウントダウン</v>
           </cell>
         </row>
         <row r="168">
           <cell r="A168">
-            <v>200530</v>
+            <v>200520</v>
           </cell>
           <cell r="B168" t="str">
-            <v>悪魔(ビフロンス)</v>
+            <v>グラウンドゼロ</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169">
-            <v>201010</v>
+            <v>200530</v>
           </cell>
           <cell r="B169" t="str">
-            <v>カオスペイン</v>
+            <v>悪魔(ビフロンス)</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170">
-            <v>201020</v>
+            <v>201010</v>
           </cell>
           <cell r="B170" t="str">
-            <v>フォールンワン</v>
+            <v>カオスペイン</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171">
-            <v>201030</v>
+            <v>201020</v>
           </cell>
           <cell r="B171" t="str">
-            <v>アンリマユ</v>
+            <v>フォールンワン</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172">
-            <v>300010</v>
+            <v>201030</v>
           </cell>
           <cell r="B172" t="str">
-            <v>ライフブースト</v>
+            <v>アンリマユ</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173">
-            <v>300020</v>
+            <v>300010</v>
           </cell>
           <cell r="B173" t="str">
-            <v>スピリットチャージ</v>
+            <v>ライフブースト</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174">
-            <v>300030</v>
+            <v>300020</v>
           </cell>
           <cell r="B174" t="str">
-            <v>フォースライズ</v>
+            <v>スピリットチャージ</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175">
-            <v>300040</v>
+            <v>300030</v>
           </cell>
           <cell r="B175" t="str">
-            <v>ディフェンスオーラ</v>
+            <v>フォースライズ</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176">
-            <v>300050</v>
+            <v>300040</v>
           </cell>
           <cell r="B176" t="str">
-            <v>ラピッドムーブ</v>
+            <v>ディフェンスオーラ</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177">
-            <v>300130</v>
+            <v>300050</v>
           </cell>
           <cell r="B177" t="str">
-            <v>アタックブレイク</v>
+            <v>ラピッドムーブ</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178">
-            <v>300140</v>
+            <v>300130</v>
           </cell>
           <cell r="B178" t="str">
-            <v>シールドバニッシュ</v>
+            <v>アタックブレイク</v>
           </cell>
         </row>
         <row r="179">
           <cell r="A179">
-            <v>300210</v>
+            <v>300140</v>
           </cell>
           <cell r="B179" t="str">
-            <v>エーテルリチャージ</v>
+            <v>シールドバニッシュ</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180">
-            <v>300220</v>
+            <v>300210</v>
           </cell>
           <cell r="B180" t="str">
-            <v>リカバリーエンハンス</v>
+            <v>エーテルリチャージ</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181">
-            <v>300230</v>
+            <v>300220</v>
           </cell>
           <cell r="B181" t="str">
-            <v>ヴェンジェンス</v>
+            <v>リカバリーエンハンス</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182">
-            <v>301010</v>
+            <v>300230</v>
           </cell>
           <cell r="B182" t="str">
-            <v>ディケイドリセット</v>
+            <v>ヴェンジェンス</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183">
-            <v>301020</v>
+            <v>301010</v>
           </cell>
           <cell r="B183" t="str">
-            <v>ウォーリアーブラッド</v>
+            <v>ディケイドリセット</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184">
-            <v>301030</v>
+            <v>301020</v>
           </cell>
           <cell r="B184" t="str">
-            <v>トライアングルガード</v>
+            <v>ウォーリアーブラッド</v>
           </cell>
         </row>
         <row r="185">
           <cell r="A185">
-            <v>301040</v>
+            <v>301030</v>
           </cell>
           <cell r="B185" t="str">
-            <v>セーフティバリア</v>
+            <v>トライアングルガード</v>
           </cell>
         </row>
         <row r="186">
           <cell r="A186">
-            <v>301050</v>
+            <v>301040</v>
           </cell>
           <cell r="B186" t="str">
-            <v>ヒロインズハイ</v>
+            <v>セーフティバリア</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187">
-            <v>301060</v>
+            <v>301050</v>
           </cell>
           <cell r="B187" t="str">
-            <v>セカンドステージ</v>
+            <v>ヒロインズハイ</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188">
-            <v>301070</v>
+            <v>301060</v>
           </cell>
           <cell r="B188" t="str">
-            <v>ハイヒットポイント</v>
+            <v>セカンドステージ</v>
           </cell>
         </row>
         <row r="189">
           <cell r="A189">
-            <v>301080</v>
+            <v>301070</v>
           </cell>
           <cell r="B189" t="str">
-            <v>セプタブラスト</v>
+            <v>ハイヒットポイント</v>
           </cell>
         </row>
         <row r="190">
           <cell r="A190">
-            <v>301090</v>
+            <v>301080</v>
           </cell>
           <cell r="B190" t="str">
-            <v>イニシャルブロッカー</v>
+            <v>セプタブラスト</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191">
-            <v>301100</v>
+            <v>301090</v>
           </cell>
           <cell r="B191" t="str">
-            <v>ファーストテイク</v>
+            <v>イニシャルブロッカー</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192">
-            <v>310010</v>
+            <v>301100</v>
           </cell>
           <cell r="B192" t="str">
-            <v>妖精の祈り</v>
+            <v>ファーストテイク</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193">
-            <v>310020</v>
+            <v>310010</v>
           </cell>
           <cell r="B193" t="str">
-            <v>月のかけら</v>
+            <v>妖精の祈り</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194">
-            <v>310030</v>
+            <v>310020</v>
           </cell>
           <cell r="B194" t="str">
-            <v>商売の才覚書</v>
+            <v>月のかけら</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195">
-            <v>310040</v>
+            <v>310030</v>
           </cell>
           <cell r="B195" t="str">
-            <v>メビウスの砂時計</v>
+            <v>商売の才覚書</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196">
-            <v>310050</v>
+            <v>310040</v>
           </cell>
           <cell r="B196" t="str">
-            <v>先陣の心得</v>
+            <v>メビウスの砂時計</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197">
-            <v>310060</v>
+            <v>310050</v>
           </cell>
           <cell r="B197" t="str">
-            <v>ヒスイの勾玉</v>
+            <v>先陣の心得</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198">
-            <v>310070</v>
+            <v>310060</v>
           </cell>
           <cell r="B198" t="str">
-            <v>英傑の盾</v>
+            <v>ヒスイの勾玉</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199">
-            <v>310080</v>
+            <v>310070</v>
           </cell>
           <cell r="B199" t="str">
-            <v>鷹の目</v>
+            <v>英傑の盾</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200">
-            <v>310130</v>
+            <v>310080</v>
           </cell>
           <cell r="B200" t="str">
-            <v>ヒールユニット</v>
+            <v>鷹の目</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201">
-            <v>320010</v>
+            <v>310130</v>
           </cell>
           <cell r="B201" t="str">
-            <v>訓練所Lv1</v>
+            <v>ヒールユニット</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202">
-            <v>320011</v>
+            <v>320010</v>
           </cell>
           <cell r="B202" t="str">
-            <v>訓練所Lv2</v>
+            <v>訓練所Lv1</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203">
-            <v>320012</v>
+            <v>320011</v>
           </cell>
           <cell r="B203" t="str">
-            <v>訓練所Lv3</v>
+            <v>訓練所Lv2</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204">
-            <v>320020</v>
+            <v>320012</v>
           </cell>
           <cell r="B204" t="str">
-            <v>研究施設Lv1</v>
+            <v>訓練所Lv3</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205">
-            <v>320021</v>
+            <v>320020</v>
           </cell>
           <cell r="B205" t="str">
-            <v>研究施設Lv2</v>
+            <v>研究施設Lv1</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206">
-            <v>320022</v>
+            <v>320021</v>
           </cell>
           <cell r="B206" t="str">
-            <v>研究施設Lv3</v>
+            <v>研究施設Lv2</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207">
-            <v>320030</v>
+            <v>320022</v>
           </cell>
           <cell r="B207" t="str">
-            <v>資料館Lv1</v>
+            <v>研究施設Lv3</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208">
-            <v>320031</v>
+            <v>320030</v>
           </cell>
           <cell r="B208" t="str">
-            <v>資料館Lv2</v>
+            <v>資料館Lv1</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209">
-            <v>320032</v>
+            <v>320031</v>
           </cell>
           <cell r="B209" t="str">
-            <v>資料館Lv3</v>
+            <v>資料館Lv2</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210">
-            <v>320040</v>
+            <v>320032</v>
           </cell>
           <cell r="B210" t="str">
-            <v>潜伏技術Lv1</v>
+            <v>資料館Lv3</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211">
-            <v>321010</v>
+            <v>320040</v>
           </cell>
           <cell r="B211" t="str">
-            <v>炎の祭壇</v>
+            <v>潜伏技術Lv1</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212">
-            <v>321020</v>
+            <v>321010</v>
           </cell>
           <cell r="B212" t="str">
-            <v>稲妻の祭壇</v>
+            <v>炎の祭壇</v>
           </cell>
         </row>
         <row r="213">
           <cell r="A213">
-            <v>321030</v>
+            <v>321020</v>
           </cell>
           <cell r="B213" t="str">
-            <v>蒼の祭壇</v>
+            <v>稲妻の祭壇</v>
           </cell>
         </row>
         <row r="214">
           <cell r="A214">
-            <v>321040</v>
+            <v>321030</v>
           </cell>
           <cell r="B214" t="str">
-            <v>光の祭壇</v>
+            <v>蒼の祭壇</v>
           </cell>
         </row>
         <row r="215">
           <cell r="A215">
-            <v>321050</v>
+            <v>321040</v>
           </cell>
           <cell r="B215" t="str">
-            <v>月の祭壇</v>
+            <v>光の祭壇</v>
           </cell>
         </row>
         <row r="216">
           <cell r="A216">
-            <v>322010</v>
+            <v>321050</v>
           </cell>
           <cell r="B216" t="str">
-            <v>食糧庫Lv1</v>
+            <v>月の祭壇</v>
           </cell>
         </row>
         <row r="217">
           <cell r="A217">
-            <v>322020</v>
+            <v>322010</v>
           </cell>
           <cell r="B217" t="str">
-            <v>攻撃技術Lv1</v>
+            <v>食糧庫Lv1</v>
           </cell>
         </row>
         <row r="218">
           <cell r="A218">
-            <v>322030</v>
+            <v>322020</v>
           </cell>
           <cell r="B218" t="str">
-            <v>防御技術Lv1</v>
+            <v>攻撃技術Lv1</v>
           </cell>
         </row>
         <row r="219">
           <cell r="A219">
-            <v>322040</v>
+            <v>322030</v>
           </cell>
           <cell r="B219" t="str">
-            <v>詠唱技術Lv1</v>
+            <v>防御技術Lv1</v>
           </cell>
         </row>
         <row r="220">
           <cell r="A220">
-            <v>401010</v>
+            <v>322040</v>
           </cell>
           <cell r="B220" t="str">
-            <v>ファイアボール+</v>
+            <v>詠唱技術Lv1</v>
           </cell>
         </row>
         <row r="221">
           <cell r="A221">
-            <v>401020</v>
+            <v>401010</v>
           </cell>
           <cell r="B221" t="str">
-            <v>バーンストーム+</v>
+            <v>ファイアボール+</v>
           </cell>
         </row>
         <row r="222">
           <cell r="A222">
-            <v>401030</v>
+            <v>401020</v>
           </cell>
           <cell r="B222" t="str">
-            <v>ヒートスタンプ+</v>
+            <v>バーンストーム+</v>
           </cell>
         </row>
         <row r="223">
           <cell r="A223">
-            <v>401040</v>
+            <v>401030</v>
           </cell>
           <cell r="B223" t="str">
-            <v>ソードアダプト+</v>
+            <v>ヒートスタンプ+</v>
           </cell>
         </row>
         <row r="224">
           <cell r="A224">
-            <v>401050</v>
+            <v>401040</v>
           </cell>
           <cell r="B224" t="str">
-            <v>フレイムレイン+</v>
+            <v>ソードアダプト+</v>
           </cell>
         </row>
         <row r="225">
           <cell r="A225">
-            <v>401060</v>
+            <v>401050</v>
           </cell>
           <cell r="B225" t="str">
-            <v>イクスティンクション+</v>
+            <v>フレイムレイン+</v>
           </cell>
         </row>
         <row r="226">
           <cell r="A226">
-            <v>401070</v>
+            <v>401060</v>
           </cell>
           <cell r="B226" t="str">
-            <v>バーニングソウル+</v>
+            <v>イクスティンクション+</v>
           </cell>
         </row>
         <row r="227">
           <cell r="A227">
-            <v>401080</v>
+            <v>401070</v>
           </cell>
           <cell r="B227" t="str">
-            <v>レイジングバウンサー+</v>
+            <v>バーニングソウル+</v>
           </cell>
         </row>
         <row r="228">
           <cell r="A228">
-            <v>402010</v>
+            <v>401080</v>
           </cell>
           <cell r="B228" t="str">
-            <v>ディスチャージ+</v>
+            <v>レイジングバウンサー+</v>
           </cell>
         </row>
         <row r="229">
           <cell r="A229">
-            <v>402020</v>
+            <v>402010</v>
           </cell>
           <cell r="B229" t="str">
-            <v>イベイドコード+</v>
+            <v>ディスチャージ+</v>
           </cell>
         </row>
         <row r="230">
           <cell r="A230">
-            <v>402030</v>
+            <v>402020</v>
           </cell>
           <cell r="B230" t="str">
-            <v>ショックインパルス+</v>
+            <v>イベイドコード+</v>
           </cell>
         </row>
         <row r="231">
           <cell r="A231">
-            <v>402040</v>
+            <v>402030</v>
           </cell>
           <cell r="B231" t="str">
-            <v>トラストチェイン+</v>
+            <v>ショックインパルス+</v>
           </cell>
         </row>
         <row r="232">
           <cell r="A232">
-            <v>402050</v>
+            <v>402040</v>
           </cell>
           <cell r="B232" t="str">
-            <v>スペルバニシング+</v>
+            <v>トラストチェイン+</v>
           </cell>
         </row>
         <row r="233">
           <cell r="A233">
-            <v>402060</v>
+            <v>402050</v>
           </cell>
           <cell r="B233" t="str">
-            <v>アーテニーストライク+</v>
+            <v>スペルバニシング+</v>
           </cell>
         </row>
         <row r="234">
           <cell r="A234">
-            <v>402070</v>
+            <v>402060</v>
           </cell>
           <cell r="B234" t="str">
-            <v>コンセントレイト+</v>
+            <v>アーテニーストライク+</v>
           </cell>
         </row>
         <row r="235">
           <cell r="A235">
-            <v>402080</v>
+            <v>402070</v>
           </cell>
           <cell r="B235" t="str">
-            <v>ディレイマジック+</v>
+            <v>コンセントレイト+</v>
           </cell>
         </row>
         <row r="236">
           <cell r="A236">
-            <v>403010</v>
+            <v>402080</v>
           </cell>
           <cell r="B236" t="str">
-            <v>アイスブレイド+</v>
+            <v>ディレイマジック+</v>
           </cell>
         </row>
         <row r="237">
           <cell r="A237">
-            <v>403020</v>
+            <v>403010</v>
           </cell>
           <cell r="B237" t="str">
-            <v>カウンターオーラ+</v>
+            <v>アイスブレイド+</v>
           </cell>
         </row>
         <row r="238">
           <cell r="A238">
-            <v>403030</v>
+            <v>403020</v>
           </cell>
           <cell r="B238" t="str">
-            <v>ラインプロテクト+</v>
+            <v>カウンターオーラ+</v>
           </cell>
         </row>
         <row r="239">
           <cell r="A239">
-            <v>403040</v>
+            <v>403030</v>
           </cell>
           <cell r="B239" t="str">
-            <v>エスコートソール+</v>
+            <v>ラインプロテクト+</v>
           </cell>
         </row>
         <row r="240">
           <cell r="A240">
-            <v>403050</v>
+            <v>403040</v>
           </cell>
           <cell r="B240" t="str">
-            <v>ディープフリーズ+</v>
+            <v>エスコートソール+</v>
           </cell>
         </row>
         <row r="241">
           <cell r="A241">
-            <v>403060</v>
+            <v>403050</v>
           </cell>
           <cell r="B241" t="str">
-            <v>バブルブロウ+</v>
+            <v>ディープフリーズ+</v>
           </cell>
         </row>
         <row r="242">
           <cell r="A242">
-            <v>403070</v>
+            <v>403060</v>
           </cell>
           <cell r="B242" t="str">
-            <v>アクアミラージュ+</v>
+            <v>バブルブロウ+</v>
           </cell>
         </row>
         <row r="243">
           <cell r="A243">
-            <v>403080</v>
+            <v>403070</v>
           </cell>
           <cell r="B243" t="str">
-            <v>フロストシールド+</v>
+            <v>アクアミラージュ+</v>
           </cell>
         </row>
         <row r="244">
           <cell r="A244">
-            <v>404010</v>
+            <v>403080</v>
           </cell>
           <cell r="B244" t="str">
-            <v>セイントレーザー+</v>
+            <v>フロストシールド+</v>
           </cell>
         </row>
         <row r="245">
           <cell r="A245">
-            <v>404020</v>
+            <v>404010</v>
           </cell>
           <cell r="B245" t="str">
-            <v>ペネトレイト+</v>
+            <v>セイントレーザー+</v>
           </cell>
         </row>
         <row r="246">
           <cell r="A246">
-            <v>404030</v>
+            <v>404020</v>
           </cell>
           <cell r="B246" t="str">
-            <v>ヒーリング+</v>
+            <v>ペネトレイト+</v>
           </cell>
         </row>
         <row r="247">
           <cell r="A247">
-            <v>404040</v>
+            <v>404030</v>
           </cell>
           <cell r="B247" t="str">
-            <v>リザイアフォトン+</v>
+            <v>ヒーリング+</v>
           </cell>
         </row>
         <row r="248">
           <cell r="A248">
-            <v>404050</v>
+            <v>404040</v>
           </cell>
           <cell r="B248" t="str">
-            <v>べネディクション+</v>
+            <v>リザイアフォトン+</v>
           </cell>
         </row>
         <row r="249">
           <cell r="A249">
-            <v>404060</v>
+            <v>404050</v>
           </cell>
           <cell r="B249" t="str">
-            <v>ホーリーグレイス+</v>
+            <v>べネディクション+</v>
           </cell>
         </row>
         <row r="250">
           <cell r="A250">
-            <v>404070</v>
+            <v>404060</v>
           </cell>
           <cell r="B250" t="str">
-            <v>キュアエール+</v>
+            <v>ホーリーグレイス+</v>
           </cell>
         </row>
         <row r="251">
           <cell r="A251">
-            <v>404080</v>
+            <v>404070</v>
           </cell>
           <cell r="B251" t="str">
-            <v>ラインバリア+</v>
+            <v>キュアエール+</v>
           </cell>
         </row>
         <row r="252">
           <cell r="A252">
-            <v>405010</v>
+            <v>404080</v>
           </cell>
           <cell r="B252" t="str">
-            <v>ダークプリズン+</v>
+            <v>ラインバリア+</v>
           </cell>
         </row>
         <row r="253">
           <cell r="A253">
-            <v>405020</v>
+            <v>405010</v>
           </cell>
           <cell r="B253" t="str">
-            <v>ユーサネイジア+</v>
+            <v>ダークプリズン+</v>
           </cell>
         </row>
         <row r="254">
           <cell r="A254">
-            <v>405030</v>
+            <v>405020</v>
           </cell>
           <cell r="B254" t="str">
-            <v>ドレインヒール+</v>
+            <v>ユーサネイジア+</v>
           </cell>
         </row>
         <row r="255">
           <cell r="A255">
-            <v>405040</v>
+            <v>405030</v>
           </cell>
           <cell r="B255" t="str">
-            <v>アビサルデスペア+</v>
+            <v>ドレインヒール+</v>
           </cell>
         </row>
         <row r="256">
           <cell r="A256">
-            <v>405050</v>
+            <v>405040</v>
           </cell>
           <cell r="B256" t="str">
-            <v>ディプラヴィティ+</v>
+            <v>アビサルデスペア+</v>
           </cell>
         </row>
         <row r="257">
           <cell r="A257">
-            <v>405060</v>
+            <v>405050</v>
           </cell>
           <cell r="B257" t="str">
-            <v>ダークネス+</v>
+            <v>ディプラヴィティ+</v>
           </cell>
         </row>
         <row r="258">
           <cell r="A258">
-            <v>405070</v>
+            <v>405060</v>
           </cell>
           <cell r="B258" t="str">
-            <v>シェイディークラウド+</v>
+            <v>ダークネス+</v>
           </cell>
         </row>
         <row r="259">
           <cell r="A259">
-            <v>405080</v>
+            <v>405070</v>
           </cell>
           <cell r="B259" t="str">
-            <v>ポイズンブロウ+</v>
+            <v>シェイディークラウド+</v>
           </cell>
         </row>
         <row r="260">
           <cell r="A260">
-            <v>411010</v>
+            <v>405080</v>
           </cell>
           <cell r="B260" t="str">
-            <v>ウルフソウル+</v>
+            <v>ポイズンブロウ+</v>
           </cell>
         </row>
         <row r="261">
           <cell r="A261">
-            <v>411020</v>
+            <v>411010</v>
           </cell>
           <cell r="B261" t="str">
-            <v>プリディカメント+</v>
+            <v>ウルフソウル+</v>
           </cell>
         </row>
         <row r="262">
           <cell r="A262">
-            <v>411030</v>
+            <v>411020</v>
           </cell>
           <cell r="B262" t="str">
-            <v>アサルトシフト+</v>
+            <v>プリディカメント+</v>
           </cell>
         </row>
         <row r="263">
           <cell r="A263">
-            <v>411040</v>
+            <v>411030</v>
           </cell>
           <cell r="B263" t="str">
-            <v>アクティブギフト+</v>
+            <v>アサルトシフト+</v>
           </cell>
         </row>
         <row r="264">
           <cell r="A264">
-            <v>411050</v>
+            <v>411040</v>
           </cell>
           <cell r="B264" t="str">
-            <v>イグナイテッド+</v>
+            <v>アクティブギフト+</v>
           </cell>
         </row>
         <row r="265">
           <cell r="A265">
-            <v>411060</v>
+            <v>411050</v>
           </cell>
           <cell r="B265" t="str">
-            <v>ライジングファイア+</v>
+            <v>イグナイテッド+</v>
           </cell>
         </row>
         <row r="266">
           <cell r="A266">
-            <v>411070</v>
+            <v>411060</v>
           </cell>
           <cell r="B266" t="str">
-            <v>ルージュバック+</v>
+            <v>ライジングファイア+</v>
           </cell>
         </row>
         <row r="267">
           <cell r="A267">
-            <v>411080</v>
+            <v>411070</v>
           </cell>
           <cell r="B267" t="str">
-            <v>パワーエール+</v>
+            <v>ルージュバック+</v>
           </cell>
         </row>
         <row r="268">
           <cell r="A268">
-            <v>411090</v>
+            <v>411080</v>
           </cell>
           <cell r="B268" t="str">
-            <v>スレイプニル+</v>
+            <v>パワーエール+</v>
           </cell>
         </row>
         <row r="269">
           <cell r="A269">
-            <v>412010</v>
+            <v>411090</v>
           </cell>
           <cell r="B269" t="str">
-            <v>エクステンション+</v>
+            <v>スレイプニル+</v>
           </cell>
         </row>
         <row r="270">
           <cell r="A270">
-            <v>412020</v>
+            <v>412010</v>
           </cell>
           <cell r="B270" t="str">
-            <v>ヘブンリーラック+</v>
+            <v>エクステンション+</v>
           </cell>
         </row>
         <row r="271">
           <cell r="A271">
-            <v>412030</v>
+            <v>412020</v>
           </cell>
           <cell r="B271" t="str">
-            <v>スウィフトカレント+</v>
+            <v>ヘブンリーラック+</v>
           </cell>
         </row>
         <row r="272">
           <cell r="A272">
-            <v>412040</v>
+            <v>412030</v>
           </cell>
           <cell r="B272" t="str">
-            <v>イヴェイドオール+</v>
+            <v>スウィフトカレント+</v>
           </cell>
         </row>
         <row r="273">
           <cell r="A273">
-            <v>412050</v>
+            <v>412040</v>
           </cell>
           <cell r="B273" t="str">
-            <v>クイックムーブ+</v>
+            <v>イヴェイドオール+</v>
           </cell>
         </row>
         <row r="274">
           <cell r="A274">
-            <v>412060</v>
+            <v>412050</v>
           </cell>
           <cell r="B274" t="str">
-            <v>チェイスマジック+</v>
+            <v>クイックムーブ+</v>
           </cell>
         </row>
         <row r="275">
           <cell r="A275">
-            <v>412070</v>
+            <v>412060</v>
           </cell>
           <cell r="B275" t="str">
-            <v>ソーサリーコネクト+</v>
+            <v>チェイスマジック+</v>
           </cell>
         </row>
         <row r="276">
           <cell r="A276">
-            <v>412080</v>
+            <v>412070</v>
           </cell>
           <cell r="B276" t="str">
-            <v>ウィンドライズ+</v>
+            <v>ソーサリーコネクト+</v>
           </cell>
         </row>
         <row r="277">
           <cell r="A277">
-            <v>412090</v>
+            <v>412080</v>
           </cell>
           <cell r="B277" t="str">
-            <v>アウトオブオーダー+</v>
+            <v>ウィンドライズ+</v>
           </cell>
         </row>
         <row r="278">
           <cell r="A278">
-            <v>413010</v>
+            <v>412090</v>
           </cell>
           <cell r="B278" t="str">
-            <v>アーマーコード+</v>
+            <v>アウトオブオーダー+</v>
           </cell>
         </row>
         <row r="279">
           <cell r="A279">
-            <v>413020</v>
+            <v>413010</v>
           </cell>
           <cell r="B279" t="str">
-            <v>クイックバリア+</v>
+            <v>アーマーコード+</v>
           </cell>
         </row>
         <row r="280">
           <cell r="A280">
-            <v>413030</v>
+            <v>413020</v>
           </cell>
           <cell r="B280" t="str">
-            <v>クイックキュア+</v>
+            <v>クイックバリア+</v>
           </cell>
         </row>
         <row r="281">
           <cell r="A281">
-            <v>413040</v>
+            <v>413030</v>
           </cell>
           <cell r="B281" t="str">
-            <v>セルフシールド+</v>
+            <v>クイックキュア+</v>
           </cell>
         </row>
         <row r="282">
           <cell r="A282">
-            <v>413050</v>
+            <v>413040</v>
           </cell>
           <cell r="B282" t="str">
-            <v>パッシブジャミング+</v>
+            <v>セルフシールド+</v>
           </cell>
         </row>
         <row r="283">
           <cell r="A283">
-            <v>413060</v>
+            <v>413050</v>
           </cell>
           <cell r="B283" t="str">
-            <v>サプライカバー+</v>
+            <v>パッシブジャミング+</v>
           </cell>
         </row>
         <row r="284">
           <cell r="A284">
-            <v>413070</v>
+            <v>413060</v>
           </cell>
           <cell r="B284" t="str">
-            <v>アシッドラッシュ+</v>
+            <v>サプライカバー+</v>
           </cell>
         </row>
         <row r="285">
           <cell r="A285">
-            <v>413080</v>
+            <v>413070</v>
           </cell>
           <cell r="B285" t="str">
-            <v>ライフスティール+</v>
+            <v>アシッドラッシュ+</v>
           </cell>
         </row>
         <row r="286">
           <cell r="A286">
-            <v>413090</v>
+            <v>413080</v>
           </cell>
           <cell r="B286" t="str">
-            <v>アイスセイバー+</v>
+            <v>ライフスティール+</v>
           </cell>
         </row>
         <row r="287">
           <cell r="A287">
-            <v>414010</v>
+            <v>413090</v>
           </cell>
           <cell r="B287" t="str">
-            <v>ディバインシールド+</v>
+            <v>アイスセイバー+</v>
           </cell>
         </row>
         <row r="288">
           <cell r="A288">
-            <v>414020</v>
+            <v>414010</v>
           </cell>
           <cell r="B288" t="str">
-            <v>ライフディバイド+</v>
+            <v>ディバインシールド+</v>
           </cell>
         </row>
         <row r="289">
           <cell r="A289">
-            <v>414030</v>
+            <v>414020</v>
           </cell>
           <cell r="B289" t="str">
-            <v>エイミングスコープ+</v>
+            <v>ライフディバイド+</v>
           </cell>
         </row>
         <row r="290">
           <cell r="A290">
-            <v>414040</v>
+            <v>414030</v>
           </cell>
           <cell r="B290" t="str">
-            <v>リジェネレーション+</v>
+            <v>エイミングスコープ+</v>
           </cell>
         </row>
         <row r="291">
           <cell r="A291">
-            <v>414050</v>
+            <v>414040</v>
           </cell>
           <cell r="B291" t="str">
-            <v>ホープフルアイリス+</v>
+            <v>リジェネレーション+</v>
           </cell>
         </row>
         <row r="292">
           <cell r="A292">
-            <v>414060</v>
+            <v>414050</v>
           </cell>
           <cell r="B292" t="str">
-            <v>パッシブサプライ+</v>
+            <v>ホープフルアイリス+</v>
           </cell>
         </row>
         <row r="293">
           <cell r="A293">
-            <v>414070</v>
+            <v>414060</v>
           </cell>
           <cell r="B293" t="str">
-            <v>ホーミングクルセイド+</v>
+            <v>パッシブサプライ+</v>
           </cell>
         </row>
         <row r="294">
           <cell r="A294">
-            <v>414080</v>
+            <v>414070</v>
           </cell>
           <cell r="B294" t="str">
-            <v>クイックヒール+</v>
+            <v>ホーミングクルセイド+</v>
           </cell>
         </row>
         <row r="295">
           <cell r="A295">
-            <v>414090</v>
+            <v>414080</v>
           </cell>
           <cell r="B295" t="str">
-            <v>リレイズ+</v>
+            <v>クイックヒール+</v>
           </cell>
         </row>
         <row r="296">
           <cell r="A296">
-            <v>415010</v>
+            <v>414090</v>
           </cell>
           <cell r="B296" t="str">
-            <v>イーグルアイ+</v>
+            <v>リレイズ+</v>
           </cell>
         </row>
         <row r="297">
           <cell r="A297">
-            <v>415020</v>
+            <v>415010</v>
           </cell>
           <cell r="B297" t="str">
-            <v>ネヴァーエンド+</v>
+            <v>イーグルアイ+</v>
           </cell>
         </row>
         <row r="298">
           <cell r="A298">
-            <v>415030</v>
+            <v>415020</v>
           </cell>
           <cell r="B298" t="str">
-            <v>グレイブアクト+</v>
+            <v>ネヴァーエンド+</v>
           </cell>
         </row>
         <row r="299">
           <cell r="A299">
-            <v>415040</v>
+            <v>415030</v>
           </cell>
           <cell r="B299" t="str">
-            <v>スカルグラッジ+</v>
+            <v>グレイブアクト+</v>
           </cell>
         </row>
         <row r="300">
           <cell r="A300">
-            <v>415050</v>
+            <v>415040</v>
           </cell>
           <cell r="B300" t="str">
-            <v>ネガティブドレイン+</v>
+            <v>スカルグラッジ+</v>
           </cell>
         </row>
         <row r="301">
           <cell r="A301">
-            <v>415060</v>
+            <v>415050</v>
           </cell>
           <cell r="B301" t="str">
-            <v>アンデッドペイン+</v>
+            <v>ネガティブドレイン+</v>
           </cell>
         </row>
         <row r="302">
           <cell r="A302">
-            <v>415070</v>
+            <v>415060</v>
           </cell>
           <cell r="B302" t="str">
-            <v>ジャックポッド+</v>
+            <v>アンデッドペイン+</v>
           </cell>
         </row>
         <row r="303">
           <cell r="A303">
-            <v>415080</v>
+            <v>415070</v>
           </cell>
           <cell r="B303" t="str">
-            <v>ヒールハント+</v>
+            <v>ジャックポッド+</v>
           </cell>
         </row>
         <row r="304">
           <cell r="A304">
-            <v>415090</v>
+            <v>415080</v>
           </cell>
           <cell r="B304" t="str">
-            <v>クイックカース+</v>
+            <v>ヒールハント+</v>
           </cell>
         </row>
         <row r="305">
           <cell r="A305">
-            <v>501010</v>
+            <v>415090</v>
           </cell>
           <cell r="B305" t="str">
-            <v>ATK+2</v>
+            <v>クイックカース+</v>
           </cell>
         </row>
         <row r="306">
           <cell r="A306">
-            <v>501020</v>
+            <v>501010</v>
           </cell>
           <cell r="B306" t="str">
-            <v>火傷耐性+25%</v>
+            <v>ATK+2</v>
           </cell>
         </row>
         <row r="307">
           <cell r="A307">
-            <v>501030</v>
+            <v>501020</v>
           </cell>
           <cell r="B307" t="str">
-            <v>ATK+2</v>
+            <v>火傷耐性+25%</v>
           </cell>
         </row>
         <row r="308">
           <cell r="A308">
-            <v>501040</v>
+            <v>501030</v>
           </cell>
           <cell r="B308" t="str">
-            <v>ATK+4</v>
+            <v>ATK+2</v>
           </cell>
         </row>
         <row r="309">
           <cell r="A309">
-            <v>501041</v>
+            <v>501040</v>
           </cell>
           <cell r="B309" t="str">
-            <v>会心率+10%</v>
+            <v>ATK+4</v>
           </cell>
         </row>
         <row r="310">
           <cell r="A310">
-            <v>502010</v>
+            <v>501041</v>
           </cell>
           <cell r="B310" t="str">
-            <v>回避率+5%</v>
+            <v>会心率+10%</v>
           </cell>
         </row>
         <row r="311">
           <cell r="A311">
-            <v>502020</v>
+            <v>502010</v>
           </cell>
           <cell r="B311" t="str">
-            <v>SPD+1</v>
+            <v>回避率+5%</v>
           </cell>
         </row>
         <row r="312">
           <cell r="A312">
-            <v>502030</v>
+            <v>502020</v>
           </cell>
           <cell r="B312" t="str">
             <v>SPD+1</v>
@@ -3613,31 +3613,31 @@
         </row>
         <row r="313">
           <cell r="A313">
-            <v>502040</v>
+            <v>502030</v>
           </cell>
           <cell r="B313" t="str">
-            <v>SPD+2</v>
+            <v>SPD+1</v>
           </cell>
         </row>
         <row r="314">
           <cell r="A314">
-            <v>502041</v>
+            <v>502040</v>
           </cell>
           <cell r="B314" t="str">
-            <v>回避率+15%</v>
+            <v>SPD+2</v>
           </cell>
         </row>
         <row r="315">
           <cell r="A315">
-            <v>503010</v>
+            <v>502041</v>
           </cell>
           <cell r="B315" t="str">
-            <v>DEF+2</v>
+            <v>回避率+15%</v>
           </cell>
         </row>
         <row r="316">
           <cell r="A316">
-            <v>503020</v>
+            <v>503010</v>
           </cell>
           <cell r="B316" t="str">
             <v>DEF+2</v>
@@ -3645,7 +3645,7 @@
         </row>
         <row r="317">
           <cell r="A317">
-            <v>503030</v>
+            <v>503020</v>
           </cell>
           <cell r="B317" t="str">
             <v>DEF+2</v>
@@ -3653,31 +3653,31 @@
         </row>
         <row r="318">
           <cell r="A318">
-            <v>503040</v>
+            <v>503030</v>
           </cell>
           <cell r="B318" t="str">
-            <v>DEF+4</v>
+            <v>DEF+2</v>
           </cell>
         </row>
         <row r="319">
           <cell r="A319">
-            <v>503041</v>
+            <v>503040</v>
           </cell>
           <cell r="B319" t="str">
-            <v>HP回復効果+20%</v>
+            <v>DEF+4</v>
           </cell>
         </row>
         <row r="320">
           <cell r="A320">
-            <v>504010</v>
+            <v>503041</v>
           </cell>
           <cell r="B320" t="str">
-            <v>最大HP+4</v>
+            <v>HP回復効果+20%</v>
           </cell>
         </row>
         <row r="321">
           <cell r="A321">
-            <v>504020</v>
+            <v>504010</v>
           </cell>
           <cell r="B321" t="str">
             <v>最大HP+4</v>
@@ -3685,65 +3685,105 @@
         </row>
         <row r="322">
           <cell r="A322">
-            <v>504030</v>
+            <v>504020</v>
           </cell>
           <cell r="B322" t="str">
-            <v>命中率+5%</v>
+            <v>最大HP+4</v>
           </cell>
         </row>
         <row r="323">
           <cell r="A323">
-            <v>504040</v>
+            <v>504030</v>
           </cell>
           <cell r="B323" t="str">
-            <v>最大HP+10</v>
+            <v>命中率+5%</v>
           </cell>
         </row>
         <row r="324">
           <cell r="A324">
-            <v>505010</v>
+            <v>504040</v>
           </cell>
           <cell r="B324" t="str">
-            <v>会心率+5%</v>
+            <v>最大HP+10</v>
           </cell>
         </row>
         <row r="325">
           <cell r="A325">
-            <v>505020</v>
+            <v>505010</v>
           </cell>
           <cell r="B325" t="str">
-            <v>SPD+1</v>
+            <v>会心率+5%</v>
           </cell>
         </row>
         <row r="326">
           <cell r="A326">
-            <v>505030</v>
+            <v>505020</v>
           </cell>
           <cell r="B326" t="str">
-            <v>回避率+5%</v>
+            <v>SPD+1</v>
           </cell>
         </row>
         <row r="327">
           <cell r="A327">
-            <v>505040</v>
+            <v>505030</v>
           </cell>
           <cell r="B327" t="str">
-            <v>暗闇無効</v>
+            <v>回避率+5%</v>
           </cell>
         </row>
         <row r="328">
           <cell r="A328">
-            <v>506010</v>
+            <v>505040</v>
           </cell>
           <cell r="B328" t="str">
-            <v>獲得Exp+30%</v>
+            <v>暗闇無効</v>
           </cell>
         </row>
         <row r="329">
           <cell r="A329">
-            <v>506020</v>
+            <v>506010</v>
           </cell>
           <cell r="B329" t="str">
+            <v>最大HP+3</v>
+          </cell>
+        </row>
+        <row r="330">
+          <cell r="A330">
+            <v>506011</v>
+          </cell>
+          <cell r="B330" t="str">
+            <v>ATK+1</v>
+          </cell>
+        </row>
+        <row r="331">
+          <cell r="A331">
+            <v>506012</v>
+          </cell>
+          <cell r="B331" t="str">
+            <v>DEF+1</v>
+          </cell>
+        </row>
+        <row r="332">
+          <cell r="A332">
+            <v>506013</v>
+          </cell>
+          <cell r="B332" t="str">
+            <v>SPD+1</v>
+          </cell>
+        </row>
+        <row r="333">
+          <cell r="A333">
+            <v>507010</v>
+          </cell>
+          <cell r="B333" t="str">
+            <v>獲得Exp+30%</v>
+          </cell>
+        </row>
+        <row r="334">
+          <cell r="A334">
+            <v>507020</v>
+          </cell>
+          <cell r="B334" t="str">
             <v>ATK⇔DEF交換</v>
           </cell>
         </row>
@@ -6175,7 +6215,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G220"/>
+  <dimension ref="A1:G223"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="16.7272727272727" customWidth="1"/>
@@ -8057,17 +8097,17 @@
         <v>101</v>
       </c>
       <c r="B79">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="C79" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B79,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>バーンストーム</v>
       </c>
       <c r="D79">
         <v>1</v>
       </c>
       <c r="E79">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F79">
         <v>5061</v>
@@ -8081,17 +8121,17 @@
         <v>101</v>
       </c>
       <c r="B80">
-        <v>200110</v>
+        <v>1010</v>
       </c>
       <c r="C80" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B80,[1]TextData!A:A))</f>
-        <v>スリータイムス</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D80">
         <v>1</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -8105,17 +8145,17 @@
         <v>101</v>
       </c>
       <c r="B81">
-        <v>200120</v>
+        <v>11020</v>
       </c>
       <c r="C81" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B81,[1]TextData!A:A))</f>
-        <v>アングリークライ</v>
+        <v>プリディカメント</v>
       </c>
       <c r="D81">
         <v>1</v>
       </c>
       <c r="E81">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -8126,20 +8166,20 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B82">
-        <v>5010</v>
+        <v>11080</v>
       </c>
       <c r="C82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B82,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>パワーエール</v>
       </c>
       <c r="D82">
         <v>1</v>
       </c>
       <c r="E82">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -8150,23 +8190,23 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B83">
-        <v>5020</v>
+        <v>200110</v>
       </c>
       <c r="C83" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B83,[1]TextData!A:A))</f>
-        <v>ユーサネイジア</v>
+        <v>スリータイムス</v>
       </c>
       <c r="D83">
         <v>1</v>
       </c>
       <c r="E83">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F83">
-        <v>1013</v>
+        <v>0</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8174,20 +8214,20 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B84">
-        <v>15050</v>
+        <v>200120</v>
       </c>
       <c r="C84" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B84,[1]TextData!A:A))</f>
-        <v>ネガティブドレイン</v>
+        <v>アングリークライ</v>
       </c>
       <c r="D84">
         <v>1</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -8201,17 +8241,17 @@
         <v>102</v>
       </c>
       <c r="B85">
-        <v>200210</v>
+        <v>5010</v>
       </c>
       <c r="C85" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B85,[1]TextData!A:A))</f>
-        <v>マイトレインフォース</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="D85">
         <v>1</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -8225,20 +8265,20 @@
         <v>102</v>
       </c>
       <c r="B86">
-        <v>200220</v>
+        <v>5020</v>
       </c>
       <c r="C86" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B86,[1]TextData!A:A))</f>
-        <v>カタストロフィ</v>
+        <v>ユーサネイジア</v>
       </c>
       <c r="D86">
         <v>1</v>
       </c>
       <c r="E86">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>1013</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8249,11 +8289,11 @@
         <v>102</v>
       </c>
       <c r="B87">
-        <v>200230</v>
+        <v>15050</v>
       </c>
       <c r="C87" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B87,[1]TextData!A:A))</f>
-        <v>悪魔(ベリト)</v>
+        <v>ネガティブドレイン</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -8270,20 +8310,20 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B88">
-        <v>4010</v>
+        <v>200210</v>
       </c>
       <c r="C88" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B88,[1]TextData!A:A))</f>
-        <v>セイントレーザー</v>
+        <v>マイトレインフォース</v>
       </c>
       <c r="D88">
         <v>1</v>
       </c>
       <c r="E88">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -8294,23 +8334,23 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B89">
-        <v>4030</v>
+        <v>200220</v>
       </c>
       <c r="C89" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B89,[1]TextData!A:A))</f>
-        <v>ヒーリング</v>
+        <v>カタストロフィ</v>
       </c>
       <c r="D89">
         <v>1</v>
       </c>
       <c r="E89">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F89">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8318,14 +8358,14 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B90">
-        <v>14080</v>
+        <v>200230</v>
       </c>
       <c r="C90" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B90,[1]TextData!A:A))</f>
-        <v>クイックヒール</v>
+        <v>悪魔(ベリト)</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -8334,7 +8374,7 @@
         <v>0</v>
       </c>
       <c r="F90">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8345,17 +8385,17 @@
         <v>103</v>
       </c>
       <c r="B91">
-        <v>200310</v>
+        <v>4010</v>
       </c>
       <c r="C91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B91,[1]TextData!A:A))</f>
-        <v>プルガシオン</v>
+        <v>セイントレーザー</v>
       </c>
       <c r="D91">
         <v>1</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -8369,20 +8409,20 @@
         <v>103</v>
       </c>
       <c r="B92">
-        <v>200320</v>
+        <v>4030</v>
       </c>
       <c r="C92" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B92,[1]TextData!A:A))</f>
-        <v>プリエステス</v>
+        <v>ヒーリング</v>
       </c>
       <c r="D92">
         <v>1</v>
       </c>
       <c r="E92">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F92">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8393,11 +8433,11 @@
         <v>103</v>
       </c>
       <c r="B93">
-        <v>200330</v>
+        <v>14080</v>
       </c>
       <c r="C93" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B93,[1]TextData!A:A))</f>
-        <v>悪魔(パイモン)</v>
+        <v>クイックヒール</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -8406,7 +8446,7 @@
         <v>0</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8414,20 +8454,20 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B94">
-        <v>2010</v>
+        <v>200310</v>
       </c>
       <c r="C94" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B94,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>プルガシオン</v>
       </c>
       <c r="D94">
         <v>1</v>
       </c>
       <c r="E94">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -8438,20 +8478,20 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B95">
-        <v>200410</v>
+        <v>200320</v>
       </c>
       <c r="C95" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B95,[1]TextData!A:A))</f>
-        <v>コウソクテンショウ</v>
+        <v>プリエステス</v>
       </c>
       <c r="D95">
         <v>1</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -8462,14 +8502,14 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B96">
-        <v>200420</v>
+        <v>200330</v>
       </c>
       <c r="C96" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B96,[1]TextData!A:A))</f>
-        <v>アンチバフ</v>
+        <v>悪魔(パイモン)</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -8478,7 +8518,7 @@
         <v>0</v>
       </c>
       <c r="F96">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -8489,17 +8529,17 @@
         <v>104</v>
       </c>
       <c r="B97">
-        <v>200430</v>
+        <v>2010</v>
       </c>
       <c r="C97" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B97,[1]TextData!A:A))</f>
-        <v>悪魔(アンドラス)</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D97">
         <v>1</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -8510,20 +8550,20 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B98">
-        <v>3010</v>
+        <v>200410</v>
       </c>
       <c r="C98" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B98,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>コウソクテンショウ</v>
       </c>
       <c r="D98">
         <v>1</v>
       </c>
       <c r="E98">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -8534,23 +8574,23 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B99">
-        <v>3070</v>
+        <v>200420</v>
       </c>
       <c r="C99" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B99,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>アンチバフ</v>
       </c>
       <c r="D99">
         <v>1</v>
       </c>
       <c r="E99">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F99">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -8558,14 +8598,14 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B100">
-        <v>200510</v>
+        <v>200430</v>
       </c>
       <c r="C100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B100,[1]TextData!A:A))</f>
-        <v>カウントダウン</v>
+        <v>悪魔(アンドラス)</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -8585,17 +8625,17 @@
         <v>105</v>
       </c>
       <c r="B101">
-        <v>200520</v>
+        <v>3010</v>
       </c>
       <c r="C101" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B101,[1]TextData!A:A))</f>
-        <v>グラウンドゼロ</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D101">
         <v>1</v>
       </c>
       <c r="E101">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -8609,17 +8649,17 @@
         <v>105</v>
       </c>
       <c r="B102">
-        <v>200530</v>
+        <v>3070</v>
       </c>
       <c r="C102" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B102,[1]TextData!A:A))</f>
-        <v>悪魔(ビフロンス)</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D102">
         <v>1</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -8633,11 +8673,11 @@
         <v>105</v>
       </c>
       <c r="B103">
-        <v>403070</v>
+        <v>200510</v>
       </c>
       <c r="C103" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B103,[1]TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>カウントダウン</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -8654,20 +8694,20 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="B104">
-        <v>5010</v>
+        <v>200520</v>
       </c>
       <c r="C104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B104,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>グラウンドゼロ</v>
       </c>
       <c r="D104">
         <v>1</v>
       </c>
       <c r="E104">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -8678,20 +8718,20 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="B105">
-        <v>5020</v>
+        <v>200530</v>
       </c>
       <c r="C105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B105,[1]TextData!A:A))</f>
-        <v>ユーサネイジア</v>
+        <v>悪魔(ビフロンス)</v>
       </c>
       <c r="D105">
         <v>1</v>
       </c>
       <c r="E105">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -8702,23 +8742,23 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="B106">
-        <v>3070</v>
+        <v>403070</v>
       </c>
       <c r="C106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B106,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="D106">
         <v>1</v>
       </c>
       <c r="E106">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F106">
-        <v>9110</v>
+        <v>0</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -8729,17 +8769,17 @@
         <v>201</v>
       </c>
       <c r="B107">
-        <v>403070</v>
+        <v>5010</v>
       </c>
       <c r="C107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B107,[1]TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="D107">
         <v>1</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -8753,20 +8793,20 @@
         <v>201</v>
       </c>
       <c r="B108">
-        <v>201010</v>
+        <v>5020</v>
       </c>
       <c r="C108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B108,[1]TextData!A:A))</f>
-        <v>カオスペイン</v>
+        <v>ユーサネイジア</v>
       </c>
       <c r="D108">
         <v>1</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F108">
-        <v>5080</v>
+        <v>0</v>
       </c>
       <c r="G108">
         <v>0</v>
@@ -8777,20 +8817,20 @@
         <v>201</v>
       </c>
       <c r="B109">
-        <v>201020</v>
+        <v>3070</v>
       </c>
       <c r="C109" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B109,[1]TextData!A:A))</f>
-        <v>フォールンワン</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D109">
         <v>1</v>
       </c>
       <c r="E109">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>9110</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -8801,11 +8841,11 @@
         <v>201</v>
       </c>
       <c r="B110">
-        <v>201030</v>
+        <v>403070</v>
       </c>
       <c r="C110" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B110,[1]TextData!A:A))</f>
-        <v>アンリマユ</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -8825,11 +8865,11 @@
         <v>201</v>
       </c>
       <c r="B111">
-        <v>405010</v>
+        <v>201010</v>
       </c>
       <c r="C111" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B111,[1]TextData!A:A))</f>
-        <v>ダークプリズン+</v>
+        <v>カオスペイン</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -8838,7 +8878,7 @@
         <v>0</v>
       </c>
       <c r="F111">
-        <v>0</v>
+        <v>5080</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -8849,17 +8889,17 @@
         <v>201</v>
       </c>
       <c r="B112">
-        <v>405020</v>
+        <v>201020</v>
       </c>
       <c r="C112" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B112,[1]TextData!A:A))</f>
-        <v>ユーサネイジア+</v>
+        <v>フォールンワン</v>
       </c>
       <c r="D112">
         <v>1</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="F112">
         <v>0</v>
@@ -8873,11 +8913,11 @@
         <v>201</v>
       </c>
       <c r="B113">
-        <v>12010</v>
+        <v>201030</v>
       </c>
       <c r="C113" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B113,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>アンリマユ</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -8894,23 +8934,23 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="B114">
-        <v>1010</v>
+        <v>405010</v>
       </c>
       <c r="C114" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B114,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>ダークプリズン+</v>
       </c>
       <c r="D114">
         <v>1</v>
       </c>
       <c r="E114">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F114">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G114">
         <v>0</v>
@@ -8918,23 +8958,23 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="B115">
-        <v>1060</v>
+        <v>405020</v>
       </c>
       <c r="C115" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B115,[1]TextData!A:A))</f>
-        <v>イクスティンクション</v>
+        <v>ユーサネイジア+</v>
       </c>
       <c r="D115">
         <v>1</v>
       </c>
       <c r="E115">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F115">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -8942,14 +8982,14 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="B116">
-        <v>100110</v>
+        <v>12010</v>
       </c>
       <c r="C116" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B116,[1]TextData!A:A))</f>
-        <v>ソーイングアームド</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -8969,20 +9009,20 @@
         <v>1001</v>
       </c>
       <c r="B117">
-        <v>100120</v>
+        <v>1010</v>
       </c>
       <c r="C117" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B117,[1]TextData!A:A))</f>
-        <v>エターナルロンド</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D117">
         <v>1</v>
       </c>
       <c r="E117">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F117">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -8993,20 +9033,20 @@
         <v>1001</v>
       </c>
       <c r="B118">
-        <v>11060</v>
+        <v>1060</v>
       </c>
       <c r="C118" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B118,[1]TextData!A:A))</f>
-        <v>ライジングファイア</v>
+        <v>イクスティンクション</v>
       </c>
       <c r="D118">
         <v>1</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -9017,11 +9057,11 @@
         <v>1001</v>
       </c>
       <c r="B119">
-        <v>14010</v>
+        <v>100110</v>
       </c>
       <c r="C119" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B119,[1]TextData!A:A))</f>
-        <v>ディバインシールド</v>
+        <v>ソーイングアームド</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -9041,17 +9081,17 @@
         <v>1001</v>
       </c>
       <c r="B120">
-        <v>12010</v>
+        <v>100120</v>
       </c>
       <c r="C120" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B120,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>エターナルロンド</v>
       </c>
       <c r="D120">
         <v>1</v>
       </c>
       <c r="E120">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F120">
         <v>0</v>
@@ -9065,11 +9105,11 @@
         <v>1001</v>
       </c>
       <c r="B121">
-        <v>12060</v>
+        <v>11060</v>
       </c>
       <c r="C121" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B121,[1]TextData!A:A))</f>
-        <v>チェイスマジック</v>
+        <v>ライジングファイア</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -9086,23 +9126,23 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B122">
-        <v>2010</v>
+        <v>14010</v>
       </c>
       <c r="C122" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B122,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>ディバインシールド</v>
       </c>
       <c r="D122">
         <v>1</v>
       </c>
       <c r="E122">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F122">
-        <v>5060</v>
+        <v>0</v>
       </c>
       <c r="G122">
         <v>0</v>
@@ -9110,10 +9150,10 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B123">
-        <v>2070</v>
+        <v>12010</v>
       </c>
       <c r="C123" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B123,[1]TextData!A:A))</f>
@@ -9123,7 +9163,7 @@
         <v>1</v>
       </c>
       <c r="E123">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F123">
         <v>0</v>
@@ -9134,14 +9174,14 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B124">
-        <v>100210</v>
+        <v>12060</v>
       </c>
       <c r="C124" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B124,[1]TextData!A:A))</f>
-        <v>アブソリュートパリィ</v>
+        <v>チェイスマジック</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -9161,23 +9201,23 @@
         <v>1002</v>
       </c>
       <c r="B125">
-        <v>100220</v>
+        <v>2010</v>
       </c>
       <c r="C125" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B125,[1]TextData!A:A))</f>
-        <v>レヴェリー</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D125">
         <v>1</v>
       </c>
       <c r="E125">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F125">
-        <v>14211</v>
+        <v>5060</v>
       </c>
       <c r="G125">
-        <v>5060</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -9185,17 +9225,17 @@
         <v>1002</v>
       </c>
       <c r="B126">
-        <v>402070</v>
+        <v>2070</v>
       </c>
       <c r="C126" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B126,[1]TextData!A:A))</f>
-        <v>コンセントレイト+</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D126">
         <v>1</v>
       </c>
       <c r="E126">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F126">
         <v>0</v>
@@ -9209,11 +9249,11 @@
         <v>1002</v>
       </c>
       <c r="B127">
-        <v>12080</v>
+        <v>100210</v>
       </c>
       <c r="C127" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B127,[1]TextData!A:A))</f>
-        <v>ウィンドライズ</v>
+        <v>アブソリュートパリィ</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -9233,23 +9273,23 @@
         <v>1002</v>
       </c>
       <c r="B128">
-        <v>12040</v>
+        <v>100220</v>
       </c>
       <c r="C128" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B128,[1]TextData!A:A))</f>
-        <v>イヴェイドオール</v>
+        <v>レヴェリー</v>
       </c>
       <c r="D128">
         <v>1</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F128">
-        <v>0</v>
+        <v>14211</v>
       </c>
       <c r="G128">
-        <v>0</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -9257,11 +9297,11 @@
         <v>1002</v>
       </c>
       <c r="B129">
-        <v>12050</v>
+        <v>402070</v>
       </c>
       <c r="C129" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B129,[1]TextData!A:A))</f>
-        <v>クイックムーブ</v>
+        <v>コンセントレイト+</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -9281,11 +9321,11 @@
         <v>1002</v>
       </c>
       <c r="B130">
-        <v>12010</v>
+        <v>12080</v>
       </c>
       <c r="C130" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B130,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>ウィンドライズ</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -9302,20 +9342,20 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B131">
-        <v>3010</v>
+        <v>12040</v>
       </c>
       <c r="C131" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B131,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>イヴェイドオール</v>
       </c>
       <c r="D131">
         <v>1</v>
       </c>
       <c r="E131">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F131">
         <v>0</v>
@@ -9326,23 +9366,23 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B132">
-        <v>3020</v>
+        <v>12050</v>
       </c>
       <c r="C132" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B132,[1]TextData!A:A))</f>
-        <v>カウンターオーラ</v>
+        <v>クイックムーブ</v>
       </c>
       <c r="D132">
         <v>1</v>
       </c>
       <c r="E132">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F132">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G132">
         <v>0</v>
@@ -9350,14 +9390,14 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B133">
-        <v>100310</v>
+        <v>12010</v>
       </c>
       <c r="C133" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B133,[1]TextData!A:A))</f>
-        <v>セイクリッドバリア</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -9377,20 +9417,20 @@
         <v>1003</v>
       </c>
       <c r="B134">
-        <v>100320</v>
+        <v>3010</v>
       </c>
       <c r="C134" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B134,[1]TextData!A:A))</f>
-        <v>リベンジニードル</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D134">
         <v>1</v>
       </c>
       <c r="E134">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F134">
-        <v>14214</v>
+        <v>0</v>
       </c>
       <c r="G134">
         <v>0</v>
@@ -9401,20 +9441,20 @@
         <v>1003</v>
       </c>
       <c r="B135">
-        <v>403020</v>
+        <v>3020</v>
       </c>
       <c r="C135" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B135,[1]TextData!A:A))</f>
-        <v>カウンターオーラ+</v>
+        <v>カウンターオーラ</v>
       </c>
       <c r="D135">
         <v>1</v>
       </c>
       <c r="E135">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F135">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G135">
         <v>0</v>
@@ -9425,11 +9465,11 @@
         <v>1003</v>
       </c>
       <c r="B136">
-        <v>403010</v>
+        <v>100310</v>
       </c>
       <c r="C136" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B136,[1]TextData!A:A))</f>
-        <v>アイスブレイド+</v>
+        <v>セイクリッドバリア</v>
       </c>
       <c r="D136">
         <v>1</v>
@@ -9449,20 +9489,20 @@
         <v>1003</v>
       </c>
       <c r="B137">
-        <v>13020</v>
+        <v>100320</v>
       </c>
       <c r="C137" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B137,[1]TextData!A:A))</f>
-        <v>クイックバリア</v>
+        <v>リベンジニードル</v>
       </c>
       <c r="D137">
         <v>1</v>
       </c>
       <c r="E137">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F137">
-        <v>0</v>
+        <v>14214</v>
       </c>
       <c r="G137">
         <v>0</v>
@@ -9473,11 +9513,11 @@
         <v>1003</v>
       </c>
       <c r="B138">
-        <v>13080</v>
+        <v>403020</v>
       </c>
       <c r="C138" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B138,[1]TextData!A:A))</f>
-        <v>ライフスティール</v>
+        <v>カウンターオーラ+</v>
       </c>
       <c r="D138">
         <v>1</v>
@@ -9497,11 +9537,11 @@
         <v>1003</v>
       </c>
       <c r="B139">
-        <v>14050</v>
+        <v>403010</v>
       </c>
       <c r="C139" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B139,[1]TextData!A:A))</f>
-        <v>ホープフルアイリス</v>
+        <v>アイスブレイド+</v>
       </c>
       <c r="D139">
         <v>1</v>
@@ -9518,20 +9558,20 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B140">
-        <v>4010</v>
+        <v>13020</v>
       </c>
       <c r="C140" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B140,[1]TextData!A:A))</f>
-        <v>セイントレーザー</v>
+        <v>クイックバリア</v>
       </c>
       <c r="D140">
         <v>1</v>
       </c>
       <c r="E140">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F140">
         <v>0</v>
@@ -9542,23 +9582,23 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B141">
-        <v>4030</v>
+        <v>13080</v>
       </c>
       <c r="C141" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B141,[1]TextData!A:A))</f>
-        <v>ヒーリング</v>
+        <v>ライフスティール</v>
       </c>
       <c r="D141">
         <v>1</v>
       </c>
       <c r="E141">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F141">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -9566,14 +9606,14 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B142">
-        <v>100410</v>
+        <v>14050</v>
       </c>
       <c r="C142" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B142,[1]TextData!A:A))</f>
-        <v>アバンデンス</v>
+        <v>ホープフルアイリス</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -9593,17 +9633,17 @@
         <v>1004</v>
       </c>
       <c r="B143">
-        <v>100420</v>
+        <v>4010</v>
       </c>
       <c r="C143" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B143,[1]TextData!A:A))</f>
-        <v>ハーヴェスト</v>
+        <v>セイントレーザー</v>
       </c>
       <c r="D143">
         <v>1</v>
       </c>
       <c r="E143">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F143">
         <v>0</v>
@@ -9617,20 +9657,20 @@
         <v>1004</v>
       </c>
       <c r="B144">
-        <v>404030</v>
+        <v>4030</v>
       </c>
       <c r="C144" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B144,[1]TextData!A:A))</f>
-        <v>ヒーリング+</v>
+        <v>ヒーリング</v>
       </c>
       <c r="D144">
         <v>1</v>
       </c>
       <c r="E144">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F144">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="G144">
         <v>0</v>
@@ -9641,11 +9681,11 @@
         <v>1004</v>
       </c>
       <c r="B145">
-        <v>14080</v>
+        <v>100410</v>
       </c>
       <c r="C145" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B145,[1]TextData!A:A))</f>
-        <v>クイックヒール</v>
+        <v>アバンデンス</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -9665,20 +9705,20 @@
         <v>1004</v>
       </c>
       <c r="B146">
-        <v>14010</v>
+        <v>100420</v>
       </c>
       <c r="C146" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B146,[1]TextData!A:A))</f>
-        <v>ディバインシールド</v>
+        <v>ハーヴェスト</v>
       </c>
       <c r="D146">
         <v>1</v>
       </c>
       <c r="E146">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F146">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G146">
         <v>0</v>
@@ -9689,11 +9729,11 @@
         <v>1004</v>
       </c>
       <c r="B147">
-        <v>14040</v>
+        <v>404030</v>
       </c>
       <c r="C147" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B147,[1]TextData!A:A))</f>
-        <v>リジェネレーション</v>
+        <v>ヒーリング+</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -9713,11 +9753,11 @@
         <v>1004</v>
       </c>
       <c r="B148">
-        <v>14090</v>
+        <v>14080</v>
       </c>
       <c r="C148" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B148,[1]TextData!A:A))</f>
-        <v>リレイズ</v>
+        <v>クイックヒール</v>
       </c>
       <c r="D148">
         <v>1</v>
@@ -9734,23 +9774,23 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B149">
-        <v>5010</v>
+        <v>14010</v>
       </c>
       <c r="C149" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B149,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>ディバインシールド</v>
       </c>
       <c r="D149">
         <v>1</v>
       </c>
       <c r="E149">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G149">
         <v>0</v>
@@ -9758,23 +9798,23 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B150">
-        <v>5070</v>
+        <v>14040</v>
       </c>
       <c r="C150" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B150,[1]TextData!A:A))</f>
-        <v>シェイディークラウド</v>
+        <v>リジェネレーション</v>
       </c>
       <c r="D150">
         <v>1</v>
       </c>
       <c r="E150">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F150">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G150">
         <v>0</v>
@@ -9782,14 +9822,14 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B151">
-        <v>100510</v>
+        <v>14090</v>
       </c>
       <c r="C151" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B151,[1]TextData!A:A))</f>
-        <v>カースドブレイク</v>
+        <v>リレイズ</v>
       </c>
       <c r="D151">
         <v>1</v>
@@ -9809,17 +9849,17 @@
         <v>1005</v>
       </c>
       <c r="B152">
-        <v>100520</v>
+        <v>5010</v>
       </c>
       <c r="C152" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B152,[1]TextData!A:A))</f>
-        <v>ムーンライトレイ</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="D152">
         <v>1</v>
       </c>
       <c r="E152">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F152">
         <v>0</v>
@@ -9833,20 +9873,20 @@
         <v>1005</v>
       </c>
       <c r="B153">
-        <v>15090</v>
+        <v>5070</v>
       </c>
       <c r="C153" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B153,[1]TextData!A:A))</f>
-        <v>クイックカース</v>
+        <v>シェイディークラウド</v>
       </c>
       <c r="D153">
         <v>1</v>
       </c>
       <c r="E153">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F153">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G153">
         <v>0</v>
@@ -9857,11 +9897,11 @@
         <v>1005</v>
       </c>
       <c r="B154">
-        <v>405070</v>
+        <v>100510</v>
       </c>
       <c r="C154" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B154,[1]TextData!A:A))</f>
-        <v>シェイディークラウド+</v>
+        <v>カースドブレイク</v>
       </c>
       <c r="D154">
         <v>1</v>
@@ -9881,17 +9921,17 @@
         <v>1005</v>
       </c>
       <c r="B155">
-        <v>15080</v>
+        <v>100520</v>
       </c>
       <c r="C155" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B155,[1]TextData!A:A))</f>
-        <v>ヒールハント</v>
+        <v>ムーンライトレイ</v>
       </c>
       <c r="D155">
         <v>1</v>
       </c>
       <c r="E155">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F155">
         <v>0</v>
@@ -9905,11 +9945,11 @@
         <v>1005</v>
       </c>
       <c r="B156">
-        <v>405010</v>
+        <v>15090</v>
       </c>
       <c r="C156" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B156,[1]TextData!A:A))</f>
-        <v>ダークプリズン+</v>
+        <v>クイックカース</v>
       </c>
       <c r="D156">
         <v>1</v>
@@ -9929,11 +9969,11 @@
         <v>1005</v>
       </c>
       <c r="B157">
-        <v>415090</v>
+        <v>405070</v>
       </c>
       <c r="C157" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B157,[1]TextData!A:A))</f>
-        <v>クイックカース+</v>
+        <v>シェイディークラウド+</v>
       </c>
       <c r="D157">
         <v>1</v>
@@ -9950,20 +9990,20 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B158">
-        <v>1010</v>
+        <v>15080</v>
       </c>
       <c r="C158" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B158,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>ヒールハント</v>
       </c>
       <c r="D158">
         <v>1</v>
       </c>
       <c r="E158">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -9974,47 +10014,47 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B159">
-        <v>1030</v>
+        <v>405010</v>
       </c>
       <c r="C159" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B159,[1]TextData!A:A))</f>
-        <v>ヒートスタンプ</v>
+        <v>ダークプリズン+</v>
       </c>
       <c r="D159">
         <v>1</v>
       </c>
       <c r="E159">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F159">
-        <v>9120</v>
+        <v>0</v>
       </c>
       <c r="G159">
-        <v>1023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:7">
       <c r="A160">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B160">
-        <v>1070</v>
+        <v>415090</v>
       </c>
       <c r="C160" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B160,[1]TextData!A:A))</f>
-        <v>バーニングソウル</v>
+        <v>クイックカース+</v>
       </c>
       <c r="D160">
         <v>1</v>
       </c>
       <c r="E160">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F160">
-        <v>6322</v>
+        <v>0</v>
       </c>
       <c r="G160">
         <v>0</v>
@@ -10025,17 +10065,17 @@
         <v>1006</v>
       </c>
       <c r="B161">
-        <v>100610</v>
+        <v>1010</v>
       </c>
       <c r="C161" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B161,[1]TextData!A:A))</f>
-        <v>サンフレイム</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D161">
         <v>1</v>
       </c>
       <c r="E161">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F161">
         <v>0</v>
@@ -10049,23 +10089,23 @@
         <v>1006</v>
       </c>
       <c r="B162">
-        <v>100620</v>
+        <v>1030</v>
       </c>
       <c r="C162" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B162,[1]TextData!A:A))</f>
-        <v>フレイムタン</v>
+        <v>ヒートスタンプ</v>
       </c>
       <c r="D162">
         <v>1</v>
       </c>
       <c r="E162">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F162">
-        <v>0</v>
+        <v>9120</v>
       </c>
       <c r="G162">
-        <v>0</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -10073,20 +10113,20 @@
         <v>1006</v>
       </c>
       <c r="B163">
-        <v>11040</v>
+        <v>1070</v>
       </c>
       <c r="C163" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B163,[1]TextData!A:A))</f>
-        <v>アクティブギフト</v>
+        <v>バーニングソウル</v>
       </c>
       <c r="D163">
         <v>1</v>
       </c>
       <c r="E163">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F163">
-        <v>5042</v>
+        <v>6322</v>
       </c>
       <c r="G163">
         <v>0</v>
@@ -10097,11 +10137,11 @@
         <v>1006</v>
       </c>
       <c r="B164">
-        <v>401030</v>
+        <v>100610</v>
       </c>
       <c r="C164" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B164,[1]TextData!A:A))</f>
-        <v>ヒートスタンプ+</v>
+        <v>サンフレイム</v>
       </c>
       <c r="D164">
         <v>1</v>
@@ -10121,17 +10161,17 @@
         <v>1006</v>
       </c>
       <c r="B165">
-        <v>411040</v>
+        <v>100620</v>
       </c>
       <c r="C165" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B165,[1]TextData!A:A))</f>
-        <v>アクティブギフト+</v>
+        <v>フレイムタン</v>
       </c>
       <c r="D165">
         <v>1</v>
       </c>
       <c r="E165">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F165">
         <v>0</v>
@@ -10145,11 +10185,11 @@
         <v>1006</v>
       </c>
       <c r="B166">
-        <v>13040</v>
+        <v>11040</v>
       </c>
       <c r="C166" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B166,[1]TextData!A:A))</f>
-        <v>セルフシールド</v>
+        <v>アクティブギフト</v>
       </c>
       <c r="D166">
         <v>1</v>
@@ -10158,7 +10198,7 @@
         <v>0</v>
       </c>
       <c r="F166">
-        <v>0</v>
+        <v>5042</v>
       </c>
       <c r="G166">
         <v>0</v>
@@ -10166,20 +10206,20 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B167">
-        <v>2010</v>
+        <v>401030</v>
       </c>
       <c r="C167" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B167,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>ヒートスタンプ+</v>
       </c>
       <c r="D167">
         <v>1</v>
       </c>
       <c r="E167">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F167">
         <v>0</v>
@@ -10190,23 +10230,23 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B168">
-        <v>2040</v>
+        <v>411040</v>
       </c>
       <c r="C168" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B168,[1]TextData!A:A))</f>
-        <v>トラストチェイン</v>
+        <v>アクティブギフト+</v>
       </c>
       <c r="D168">
         <v>1</v>
       </c>
       <c r="E168">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F168">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G168">
         <v>0</v>
@@ -10214,14 +10254,14 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B169">
-        <v>100710</v>
+        <v>13040</v>
       </c>
       <c r="C169" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B169,[1]TextData!A:A))</f>
-        <v>ライズザフラッグ</v>
+        <v>セルフシールド</v>
       </c>
       <c r="D169">
         <v>1</v>
@@ -10241,17 +10281,17 @@
         <v>1007</v>
       </c>
       <c r="B170">
-        <v>100720</v>
+        <v>2010</v>
       </c>
       <c r="C170" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B170,[1]TextData!A:A))</f>
-        <v>オーバーリミット</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D170">
         <v>1</v>
       </c>
       <c r="E170">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F170">
         <v>0</v>
@@ -10265,20 +10305,20 @@
         <v>1007</v>
       </c>
       <c r="B171">
-        <v>12090</v>
+        <v>2040</v>
       </c>
       <c r="C171" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B171,[1]TextData!A:A))</f>
-        <v>アウトオブオーダー</v>
+        <v>トラストチェイン</v>
       </c>
       <c r="D171">
         <v>1</v>
       </c>
       <c r="E171">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F171">
-        <v>5042</v>
+        <v>1023</v>
       </c>
       <c r="G171">
         <v>0</v>
@@ -10289,11 +10329,11 @@
         <v>1007</v>
       </c>
       <c r="B172">
-        <v>412090</v>
+        <v>100710</v>
       </c>
       <c r="C172" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B172,[1]TextData!A:A))</f>
-        <v>アウトオブオーダー+</v>
+        <v>ライズザフラッグ</v>
       </c>
       <c r="D172">
         <v>1</v>
@@ -10313,17 +10353,17 @@
         <v>1007</v>
       </c>
       <c r="B173">
-        <v>12050</v>
+        <v>100720</v>
       </c>
       <c r="C173" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B173,[1]TextData!A:A))</f>
-        <v>クイックムーブ</v>
+        <v>オーバーリミット</v>
       </c>
       <c r="D173">
         <v>1</v>
       </c>
       <c r="E173">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F173">
         <v>0</v>
@@ -10337,11 +10377,11 @@
         <v>1007</v>
       </c>
       <c r="B174">
-        <v>12070</v>
+        <v>12090</v>
       </c>
       <c r="C174" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B174,[1]TextData!A:A))</f>
-        <v>ソーサリーコネクト</v>
+        <v>アウトオブオーダー</v>
       </c>
       <c r="D174">
         <v>1</v>
@@ -10350,7 +10390,7 @@
         <v>0</v>
       </c>
       <c r="F174">
-        <v>0</v>
+        <v>5042</v>
       </c>
       <c r="G174">
         <v>0</v>
@@ -10361,11 +10401,11 @@
         <v>1007</v>
       </c>
       <c r="B175">
-        <v>14030</v>
+        <v>412090</v>
       </c>
       <c r="C175" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B175,[1]TextData!A:A))</f>
-        <v>エイミングスコープ</v>
+        <v>アウトオブオーダー+</v>
       </c>
       <c r="D175">
         <v>1</v>
@@ -10382,20 +10422,20 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B176">
-        <v>3010</v>
+        <v>12050</v>
       </c>
       <c r="C176" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B176,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>クイックムーブ</v>
       </c>
       <c r="D176">
         <v>1</v>
       </c>
       <c r="E176">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F176">
         <v>0</v>
@@ -10406,20 +10446,20 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B177">
-        <v>3070</v>
+        <v>12070</v>
       </c>
       <c r="C177" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B177,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>ソーサリーコネクト</v>
       </c>
       <c r="D177">
         <v>1</v>
       </c>
       <c r="E177">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F177">
         <v>0</v>
@@ -10430,14 +10470,14 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B178">
-        <v>100810</v>
+        <v>14030</v>
       </c>
       <c r="C178" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B178,[1]TextData!A:A))</f>
-        <v>テンパランス</v>
+        <v>エイミングスコープ</v>
       </c>
       <c r="D178">
         <v>1</v>
@@ -10457,17 +10497,17 @@
         <v>1008</v>
       </c>
       <c r="B179">
-        <v>100820</v>
+        <v>3010</v>
       </c>
       <c r="C179" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B179,[1]TextData!A:A))</f>
-        <v>シエルクルセイダー</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D179">
         <v>1</v>
       </c>
       <c r="E179">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F179">
         <v>0</v>
@@ -10481,20 +10521,20 @@
         <v>1008</v>
       </c>
       <c r="B180">
-        <v>13060</v>
+        <v>3070</v>
       </c>
       <c r="C180" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B180,[1]TextData!A:A))</f>
-        <v>サプライカバー</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D180">
         <v>1</v>
       </c>
       <c r="E180">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F180">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G180">
         <v>0</v>
@@ -10505,11 +10545,11 @@
         <v>1008</v>
       </c>
       <c r="B181">
-        <v>403070</v>
+        <v>100810</v>
       </c>
       <c r="C181" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B181,[1]TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>テンパランス</v>
       </c>
       <c r="D181">
         <v>1</v>
@@ -10529,17 +10569,17 @@
         <v>1008</v>
       </c>
       <c r="B182">
-        <v>13010</v>
+        <v>100820</v>
       </c>
       <c r="C182" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B182,[1]TextData!A:A))</f>
-        <v>アーマーコード</v>
+        <v>シエルクルセイダー</v>
       </c>
       <c r="D182">
         <v>1</v>
       </c>
       <c r="E182">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F182">
         <v>0</v>
@@ -10553,11 +10593,11 @@
         <v>1008</v>
       </c>
       <c r="B183">
-        <v>13020</v>
+        <v>13060</v>
       </c>
       <c r="C183" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B183,[1]TextData!A:A))</f>
-        <v>クイックバリア</v>
+        <v>サプライカバー</v>
       </c>
       <c r="D183">
         <v>1</v>
@@ -10566,7 +10606,7 @@
         <v>0</v>
       </c>
       <c r="F183">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G183">
         <v>0</v>
@@ -10577,11 +10617,11 @@
         <v>1008</v>
       </c>
       <c r="B184">
-        <v>13040</v>
+        <v>403070</v>
       </c>
       <c r="C184" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B184,[1]TextData!A:A))</f>
-        <v>セルフシールド</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="D184">
         <v>1</v>
@@ -10598,20 +10638,20 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B185">
-        <v>1010</v>
+        <v>13010</v>
       </c>
       <c r="C185" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B185,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>アーマーコード</v>
       </c>
       <c r="D185">
         <v>1</v>
       </c>
       <c r="E185">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F185">
         <v>0</v>
@@ -10622,23 +10662,23 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B186">
-        <v>1050</v>
+        <v>13020</v>
       </c>
       <c r="C186" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B186,[1]TextData!A:A))</f>
-        <v>フレイムレイン</v>
+        <v>クイックバリア</v>
       </c>
       <c r="D186">
         <v>1</v>
       </c>
       <c r="E186">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F186">
-        <v>1151</v>
+        <v>0</v>
       </c>
       <c r="G186">
         <v>0</v>
@@ -10646,14 +10686,14 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B187">
-        <v>100910</v>
+        <v>13040</v>
       </c>
       <c r="C187" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B187,[1]TextData!A:A))</f>
-        <v>バーニングカウンター</v>
+        <v>セルフシールド</v>
       </c>
       <c r="D187">
         <v>1</v>
@@ -10673,17 +10713,17 @@
         <v>1009</v>
       </c>
       <c r="B188">
-        <v>100920</v>
+        <v>1010</v>
       </c>
       <c r="C188" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B188,[1]TextData!A:A))</f>
-        <v>プロミネンス</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D188">
         <v>1</v>
       </c>
       <c r="E188">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F188">
         <v>0</v>
@@ -10697,20 +10737,20 @@
         <v>1009</v>
       </c>
       <c r="B189">
-        <v>11070</v>
+        <v>1050</v>
       </c>
       <c r="C189" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B189,[1]TextData!A:A))</f>
-        <v>ルージュバック</v>
+        <v>フレイムレイン</v>
       </c>
       <c r="D189">
         <v>1</v>
       </c>
       <c r="E189">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F189">
-        <v>0</v>
+        <v>1151</v>
       </c>
       <c r="G189">
         <v>0</v>
@@ -10721,11 +10761,11 @@
         <v>1009</v>
       </c>
       <c r="B190">
-        <v>401050</v>
+        <v>100910</v>
       </c>
       <c r="C190" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B190,[1]TextData!A:A))</f>
-        <v>フレイムレイン+</v>
+        <v>バーニングカウンター</v>
       </c>
       <c r="D190">
         <v>1</v>
@@ -10745,17 +10785,17 @@
         <v>1009</v>
       </c>
       <c r="B191">
-        <v>11030</v>
+        <v>100920</v>
       </c>
       <c r="C191" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B191,[1]TextData!A:A))</f>
-        <v>アサルトシフト</v>
+        <v>プロミネンス</v>
       </c>
       <c r="D191">
         <v>1</v>
       </c>
       <c r="E191">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F191">
         <v>0</v>
@@ -10769,11 +10809,11 @@
         <v>1009</v>
       </c>
       <c r="B192">
-        <v>11020</v>
+        <v>11070</v>
       </c>
       <c r="C192" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B192,[1]TextData!A:A))</f>
-        <v>プリディカメント</v>
+        <v>ルージュバック</v>
       </c>
       <c r="D192">
         <v>1</v>
@@ -10793,11 +10833,11 @@
         <v>1009</v>
       </c>
       <c r="B193">
-        <v>15040</v>
+        <v>401050</v>
       </c>
       <c r="C193" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B193,[1]TextData!A:A))</f>
-        <v>スカルグラッジ</v>
+        <v>フレイムレイン+</v>
       </c>
       <c r="D193">
         <v>1</v>
@@ -10814,20 +10854,20 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B194">
-        <v>2010</v>
+        <v>11030</v>
       </c>
       <c r="C194" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B194,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>アサルトシフト</v>
       </c>
       <c r="D194">
         <v>1</v>
       </c>
       <c r="E194">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F194">
         <v>0</v>
@@ -10838,23 +10878,23 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B195">
-        <v>2030</v>
+        <v>11020</v>
       </c>
       <c r="C195" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B195,[1]TextData!A:A))</f>
-        <v>ショックインパルス</v>
+        <v>プリディカメント</v>
       </c>
       <c r="D195">
         <v>1</v>
       </c>
       <c r="E195">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F195">
-        <v>14215</v>
+        <v>0</v>
       </c>
       <c r="G195">
         <v>0</v>
@@ -10862,14 +10902,14 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B196">
-        <v>101010</v>
+        <v>15040</v>
       </c>
       <c r="C196" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B196,[1]TextData!A:A))</f>
-        <v>エウロス</v>
+        <v>スカルグラッジ</v>
       </c>
       <c r="D196">
         <v>1</v>
@@ -10889,17 +10929,17 @@
         <v>1010</v>
       </c>
       <c r="B197">
-        <v>101020</v>
+        <v>2010</v>
       </c>
       <c r="C197" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B197,[1]TextData!A:A))</f>
-        <v>ボレアス</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D197">
         <v>1</v>
       </c>
       <c r="E197">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F197">
         <v>0</v>
@@ -10913,20 +10953,20 @@
         <v>1010</v>
       </c>
       <c r="B198">
-        <v>12010</v>
+        <v>2030</v>
       </c>
       <c r="C198" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B198,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>ショックインパルス</v>
       </c>
       <c r="D198">
         <v>1</v>
       </c>
       <c r="E198">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F198">
-        <v>0</v>
+        <v>14215</v>
       </c>
       <c r="G198">
         <v>0</v>
@@ -10937,11 +10977,11 @@
         <v>1010</v>
       </c>
       <c r="B199">
-        <v>402030</v>
+        <v>101010</v>
       </c>
       <c r="C199" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B199,[1]TextData!A:A))</f>
-        <v>ショックインパルス+</v>
+        <v>エウロス</v>
       </c>
       <c r="D199">
         <v>1</v>
@@ -10961,17 +11001,17 @@
         <v>1010</v>
       </c>
       <c r="B200">
-        <v>12020</v>
+        <v>101020</v>
       </c>
       <c r="C200" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B200,[1]TextData!A:A))</f>
-        <v>ヘブンリーラック</v>
+        <v>ボレアス</v>
       </c>
       <c r="D200">
         <v>1</v>
       </c>
       <c r="E200">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F200">
         <v>0</v>
@@ -10985,11 +11025,11 @@
         <v>1010</v>
       </c>
       <c r="B201">
-        <v>12030</v>
+        <v>12010</v>
       </c>
       <c r="C201" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B201,[1]TextData!A:A))</f>
-        <v>スウィフトカレント</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D201">
         <v>1</v>
@@ -11009,11 +11049,11 @@
         <v>1010</v>
       </c>
       <c r="B202">
-        <v>15070</v>
+        <v>402030</v>
       </c>
       <c r="C202" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B202,[1]TextData!A:A))</f>
-        <v>ジャックポッド</v>
+        <v>ショックインパルス+</v>
       </c>
       <c r="D202">
         <v>1</v>
@@ -11030,20 +11070,20 @@
     </row>
     <row r="203" spans="1:7">
       <c r="A203">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B203">
-        <v>3010</v>
+        <v>12020</v>
       </c>
       <c r="C203" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B203,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>ヘブンリーラック</v>
       </c>
       <c r="D203">
         <v>1</v>
       </c>
       <c r="E203">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F203">
         <v>0</v>
@@ -11054,20 +11094,20 @@
     </row>
     <row r="204" spans="1:7">
       <c r="A204">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B204">
-        <v>3050</v>
+        <v>12030</v>
       </c>
       <c r="C204" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B204,[1]TextData!A:A))</f>
-        <v>ディープフリーズ</v>
+        <v>スウィフトカレント</v>
       </c>
       <c r="D204">
         <v>1</v>
       </c>
       <c r="E204">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F204">
         <v>0</v>
@@ -11078,14 +11118,14 @@
     </row>
     <row r="205" spans="1:7">
       <c r="A205">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B205">
-        <v>101110</v>
+        <v>15070</v>
       </c>
       <c r="C205" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B205,[1]TextData!A:A))</f>
-        <v>アバランシュ</v>
+        <v>ジャックポッド</v>
       </c>
       <c r="D205">
         <v>1</v>
@@ -11105,17 +11145,17 @@
         <v>1011</v>
       </c>
       <c r="B206">
-        <v>101120</v>
+        <v>3010</v>
       </c>
       <c r="C206" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B206,[1]TextData!A:A))</f>
-        <v>ブリザードコフィン</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D206">
         <v>1</v>
       </c>
       <c r="E206">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F206">
         <v>0</v>
@@ -11129,17 +11169,17 @@
         <v>1011</v>
       </c>
       <c r="B207">
-        <v>13090</v>
+        <v>3050</v>
       </c>
       <c r="C207" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B207,[1]TextData!A:A))</f>
-        <v>アイスセイバー</v>
+        <v>ディープフリーズ</v>
       </c>
       <c r="D207">
         <v>1</v>
       </c>
       <c r="E207">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F207">
         <v>0</v>
@@ -11153,11 +11193,11 @@
         <v>1011</v>
       </c>
       <c r="B208">
-        <v>403050</v>
+        <v>101110</v>
       </c>
       <c r="C208" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B208,[1]TextData!A:A))</f>
-        <v>ディープフリーズ+</v>
+        <v>アバランシュ</v>
       </c>
       <c r="D208">
         <v>1</v>
@@ -11177,17 +11217,17 @@
         <v>1011</v>
       </c>
       <c r="B209">
-        <v>13050</v>
+        <v>101120</v>
       </c>
       <c r="C209" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B209,[1]TextData!A:A))</f>
-        <v>パッシブジャミング</v>
+        <v>ブリザードコフィン</v>
       </c>
       <c r="D209">
         <v>1</v>
       </c>
       <c r="E209">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F209">
         <v>0</v>
@@ -11201,11 +11241,11 @@
         <v>1011</v>
       </c>
       <c r="B210">
-        <v>13070</v>
+        <v>13090</v>
       </c>
       <c r="C210" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B210,[1]TextData!A:A))</f>
-        <v>アシッドラッシュ</v>
+        <v>アイスセイバー</v>
       </c>
       <c r="D210">
         <v>1</v>
@@ -11225,11 +11265,11 @@
         <v>1011</v>
       </c>
       <c r="B211">
-        <v>14070</v>
+        <v>403050</v>
       </c>
       <c r="C211" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B211,[1]TextData!A:A))</f>
-        <v>ホーミングクルセイド</v>
+        <v>ディープフリーズ+</v>
       </c>
       <c r="D211">
         <v>1</v>
@@ -11246,20 +11286,20 @@
     </row>
     <row r="212" spans="1:7">
       <c r="A212">
-        <v>1101</v>
+        <v>1011</v>
       </c>
       <c r="B212">
-        <v>3010</v>
+        <v>13050</v>
       </c>
       <c r="C212" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B212,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>パッシブジャミング</v>
       </c>
       <c r="D212">
         <v>1</v>
       </c>
       <c r="E212">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F212">
         <v>0</v>
@@ -11270,20 +11310,20 @@
     </row>
     <row r="213" spans="1:7">
       <c r="A213">
-        <v>1101</v>
+        <v>1011</v>
       </c>
       <c r="B213">
-        <v>3070</v>
+        <v>13070</v>
       </c>
       <c r="C213" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B213,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>アシッドラッシュ</v>
       </c>
       <c r="D213">
         <v>1</v>
       </c>
       <c r="E213">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F213">
         <v>0</v>
@@ -11294,14 +11334,14 @@
     </row>
     <row r="214" spans="1:7">
       <c r="A214">
-        <v>1101</v>
+        <v>1011</v>
       </c>
       <c r="B214">
-        <v>110110</v>
+        <v>14070</v>
       </c>
       <c r="C214" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B214,[1]TextData!A:A))</f>
-        <v>ウィビングヒストリー</v>
+        <v>ホーミングクルセイド</v>
       </c>
       <c r="D214">
         <v>1</v>
@@ -11321,17 +11361,17 @@
         <v>1101</v>
       </c>
       <c r="B215">
-        <v>110120</v>
+        <v>3010</v>
       </c>
       <c r="C215" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B215,[1]TextData!A:A))</f>
-        <v>アンライバルド</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D215">
         <v>1</v>
       </c>
       <c r="E215">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F215">
         <v>0</v>
@@ -11345,17 +11385,17 @@
         <v>1101</v>
       </c>
       <c r="B216">
-        <v>13100</v>
+        <v>3070</v>
       </c>
       <c r="C216" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B216,[1]TextData!A:A))</f>
-        <v>ルミナスカバー</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D216">
         <v>1</v>
       </c>
       <c r="E216">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F216">
         <v>0</v>
@@ -11369,11 +11409,11 @@
         <v>1101</v>
       </c>
       <c r="B217">
-        <v>403050</v>
+        <v>110110</v>
       </c>
       <c r="C217" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B217,[1]TextData!A:A))</f>
-        <v>ディープフリーズ+</v>
+        <v>ウィビングヒストリー</v>
       </c>
       <c r="D217">
         <v>1</v>
@@ -11393,17 +11433,17 @@
         <v>1101</v>
       </c>
       <c r="B218">
-        <v>13050</v>
+        <v>110120</v>
       </c>
       <c r="C218" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B218,[1]TextData!A:A))</f>
-        <v>パッシブジャミング</v>
+        <v>アンライバルド</v>
       </c>
       <c r="D218">
         <v>1</v>
       </c>
       <c r="E218">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F218">
         <v>0</v>
@@ -11417,11 +11457,11 @@
         <v>1101</v>
       </c>
       <c r="B219">
-        <v>13070</v>
+        <v>13100</v>
       </c>
       <c r="C219" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B219,[1]TextData!A:A))</f>
-        <v>アシッドラッシュ</v>
+        <v>ルミナスカバー</v>
       </c>
       <c r="D219">
         <v>1</v>
@@ -11441,22 +11481,94 @@
         <v>1101</v>
       </c>
       <c r="B220">
-        <v>14070</v>
+        <v>403050</v>
       </c>
       <c r="C220" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B220,[1]TextData!A:A))</f>
+        <v>ディープフリーズ+</v>
+      </c>
+      <c r="D220">
+        <v>1</v>
+      </c>
+      <c r="E220">
+        <v>0</v>
+      </c>
+      <c r="F220">
+        <v>0</v>
+      </c>
+      <c r="G220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7">
+      <c r="A221">
+        <v>1101</v>
+      </c>
+      <c r="B221">
+        <v>13050</v>
+      </c>
+      <c r="C221" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B221,[1]TextData!A:A))</f>
+        <v>パッシブジャミング</v>
+      </c>
+      <c r="D221">
+        <v>1</v>
+      </c>
+      <c r="E221">
+        <v>0</v>
+      </c>
+      <c r="F221">
+        <v>0</v>
+      </c>
+      <c r="G221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7">
+      <c r="A222">
+        <v>1101</v>
+      </c>
+      <c r="B222">
+        <v>13070</v>
+      </c>
+      <c r="C222" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B222,[1]TextData!A:A))</f>
+        <v>アシッドラッシュ</v>
+      </c>
+      <c r="D222">
+        <v>1</v>
+      </c>
+      <c r="E222">
+        <v>0</v>
+      </c>
+      <c r="F222">
+        <v>0</v>
+      </c>
+      <c r="G222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7">
+      <c r="A223">
+        <v>1101</v>
+      </c>
+      <c r="B223">
+        <v>14070</v>
+      </c>
+      <c r="C223" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B223,[1]TextData!A:A))</f>
         <v>ホーミングクルセイド</v>
       </c>
-      <c r="D220">
-        <v>1</v>
-      </c>
-      <c r="E220">
-        <v>0</v>
-      </c>
-      <c r="F220">
-        <v>0</v>
-      </c>
-      <c r="G220">
+      <c r="D223">
+        <v>1</v>
+      </c>
+      <c r="E223">
+        <v>0</v>
+      </c>
+      <c r="F223">
+        <v>0</v>
+      </c>
+      <c r="G223">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="129">
   <si>
     <t>Id</t>
   </si>
@@ -155,7 +155,7 @@
     <t>Bifrons</t>
   </si>
   <si>
-    <t>Cyaegha</t>
+    <t>Dragon_Saint1</t>
   </si>
   <si>
     <t>Actor0001</t>
@@ -320,22 +320,25 @@
     <t>ビヤーキー</t>
   </si>
   <si>
+    <t>ファフニール</t>
+  </si>
+  <si>
+    <t>ザガン</t>
+  </si>
+  <si>
+    <t>アスタロト</t>
+  </si>
+  <si>
+    <t>デカラビア</t>
+  </si>
+  <si>
+    <t>インドラ</t>
+  </si>
+  <si>
+    <t>ズルワーン</t>
+  </si>
+  <si>
     <t>アンリマユ</t>
-  </si>
-  <si>
-    <t>ザガン</t>
-  </si>
-  <si>
-    <t>アスタロト</t>
-  </si>
-  <si>
-    <t>デカラビア</t>
-  </si>
-  <si>
-    <t>インドラ</t>
-  </si>
-  <si>
-    <t>ズルワーン</t>
   </si>
   <si>
     <t>デビルドラゴン</t>
@@ -413,9 +416,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -433,17 +436,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -451,9 +452,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -466,50 +467,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -517,32 +474,16 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -562,18 +503,80 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -586,7 +589,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -598,7 +619,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -610,25 +643,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -640,7 +667,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -652,19 +691,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -676,61 +727,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -748,25 +757,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -789,27 +792,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -830,17 +816,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -860,20 +840,43 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -885,145 +888,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5399,7 +5402,7 @@
         <v>44</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E23">
         <v>100</v>
@@ -6215,7 +6218,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G223"/>
+  <dimension ref="A1:G216"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="16.7272727272727" customWidth="1"/>
@@ -8838,23 +8841,23 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="B110">
-        <v>403070</v>
+        <v>1010</v>
       </c>
       <c r="C110" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B110,[1]TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D110">
         <v>1</v>
       </c>
       <c r="E110">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F110">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -8862,23 +8865,23 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="B111">
-        <v>201010</v>
+        <v>1060</v>
       </c>
       <c r="C111" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B111,[1]TextData!A:A))</f>
-        <v>カオスペイン</v>
+        <v>イクスティンクション</v>
       </c>
       <c r="D111">
         <v>1</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F111">
-        <v>5080</v>
+        <v>5061</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -8886,20 +8889,20 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="B112">
-        <v>201020</v>
+        <v>100110</v>
       </c>
       <c r="C112" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B112,[1]TextData!A:A))</f>
-        <v>フォールンワン</v>
+        <v>ソーイングアームド</v>
       </c>
       <c r="D112">
         <v>1</v>
       </c>
       <c r="E112">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="F112">
         <v>0</v>
@@ -8910,20 +8913,20 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="B113">
-        <v>201030</v>
+        <v>100120</v>
       </c>
       <c r="C113" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B113,[1]TextData!A:A))</f>
-        <v>アンリマユ</v>
+        <v>エターナルロンド</v>
       </c>
       <c r="D113">
         <v>1</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -8934,14 +8937,14 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="B114">
-        <v>405010</v>
+        <v>11060</v>
       </c>
       <c r="C114" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B114,[1]TextData!A:A))</f>
-        <v>ダークプリズン+</v>
+        <v>ライジングファイア</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -8958,14 +8961,14 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="B115">
-        <v>405020</v>
+        <v>14010</v>
       </c>
       <c r="C115" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B115,[1]TextData!A:A))</f>
-        <v>ユーサネイジア+</v>
+        <v>ディバインシールド</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -8982,7 +8985,7 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="B116">
         <v>12010</v>
@@ -9009,20 +9012,20 @@
         <v>1001</v>
       </c>
       <c r="B117">
-        <v>1010</v>
+        <v>12060</v>
       </c>
       <c r="C117" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B117,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>チェイスマジック</v>
       </c>
       <c r="D117">
         <v>1</v>
       </c>
       <c r="E117">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F117">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -9030,23 +9033,23 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B118">
-        <v>1060</v>
+        <v>2010</v>
       </c>
       <c r="C118" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B118,[1]TextData!A:A))</f>
-        <v>イクスティンクション</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D118">
         <v>1</v>
       </c>
       <c r="E118">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F118">
-        <v>5061</v>
+        <v>5060</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -9054,20 +9057,20 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B119">
-        <v>100110</v>
+        <v>2070</v>
       </c>
       <c r="C119" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B119,[1]TextData!A:A))</f>
-        <v>ソーイングアームド</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D119">
         <v>1</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F119">
         <v>0</v>
@@ -9078,20 +9081,20 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B120">
-        <v>100120</v>
+        <v>100210</v>
       </c>
       <c r="C120" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B120,[1]TextData!A:A))</f>
-        <v>エターナルロンド</v>
+        <v>アブソリュートパリィ</v>
       </c>
       <c r="D120">
         <v>1</v>
       </c>
       <c r="E120">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F120">
         <v>0</v>
@@ -9102,38 +9105,38 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B121">
-        <v>11060</v>
+        <v>100220</v>
       </c>
       <c r="C121" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B121,[1]TextData!A:A))</f>
-        <v>ライジングファイア</v>
+        <v>レヴェリー</v>
       </c>
       <c r="D121">
         <v>1</v>
       </c>
       <c r="E121">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>14211</v>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B122">
-        <v>14010</v>
+        <v>402070</v>
       </c>
       <c r="C122" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B122,[1]TextData!A:A))</f>
-        <v>ディバインシールド</v>
+        <v>コンセントレイト+</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -9150,14 +9153,14 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B123">
-        <v>12010</v>
+        <v>12080</v>
       </c>
       <c r="C123" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B123,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>ウィンドライズ</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -9174,14 +9177,14 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B124">
-        <v>12060</v>
+        <v>12040</v>
       </c>
       <c r="C124" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B124,[1]TextData!A:A))</f>
-        <v>チェイスマジック</v>
+        <v>イヴェイドオール</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -9201,20 +9204,20 @@
         <v>1002</v>
       </c>
       <c r="B125">
-        <v>2010</v>
+        <v>12050</v>
       </c>
       <c r="C125" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B125,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>クイックムーブ</v>
       </c>
       <c r="D125">
         <v>1</v>
       </c>
       <c r="E125">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F125">
-        <v>5060</v>
+        <v>0</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -9225,7 +9228,7 @@
         <v>1002</v>
       </c>
       <c r="B126">
-        <v>2070</v>
+        <v>12010</v>
       </c>
       <c r="C126" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B126,[1]TextData!A:A))</f>
@@ -9235,7 +9238,7 @@
         <v>1</v>
       </c>
       <c r="E126">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F126">
         <v>0</v>
@@ -9246,20 +9249,20 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B127">
-        <v>100210</v>
+        <v>3010</v>
       </c>
       <c r="C127" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B127,[1]TextData!A:A))</f>
-        <v>アブソリュートパリィ</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D127">
         <v>1</v>
       </c>
       <c r="E127">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F127">
         <v>0</v>
@@ -9270,38 +9273,38 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B128">
-        <v>100220</v>
+        <v>3020</v>
       </c>
       <c r="C128" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B128,[1]TextData!A:A))</f>
-        <v>レヴェリー</v>
+        <v>カウンターオーラ</v>
       </c>
       <c r="D128">
         <v>1</v>
       </c>
       <c r="E128">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F128">
-        <v>14211</v>
+        <v>1023</v>
       </c>
       <c r="G128">
-        <v>5060</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B129">
-        <v>402070</v>
+        <v>100310</v>
       </c>
       <c r="C129" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B129,[1]TextData!A:A))</f>
-        <v>コンセントレイト+</v>
+        <v>セイクリッドバリア</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -9318,23 +9321,23 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B130">
-        <v>12080</v>
+        <v>100320</v>
       </c>
       <c r="C130" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B130,[1]TextData!A:A))</f>
-        <v>ウィンドライズ</v>
+        <v>リベンジニードル</v>
       </c>
       <c r="D130">
         <v>1</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F130">
-        <v>0</v>
+        <v>14214</v>
       </c>
       <c r="G130">
         <v>0</v>
@@ -9342,14 +9345,14 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B131">
-        <v>12040</v>
+        <v>403020</v>
       </c>
       <c r="C131" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B131,[1]TextData!A:A))</f>
-        <v>イヴェイドオール</v>
+        <v>カウンターオーラ+</v>
       </c>
       <c r="D131">
         <v>1</v>
@@ -9366,14 +9369,14 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B132">
-        <v>12050</v>
+        <v>403010</v>
       </c>
       <c r="C132" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B132,[1]TextData!A:A))</f>
-        <v>クイックムーブ</v>
+        <v>アイスブレイド+</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -9390,14 +9393,14 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B133">
-        <v>12010</v>
+        <v>13020</v>
       </c>
       <c r="C133" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B133,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>クイックバリア</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -9417,17 +9420,17 @@
         <v>1003</v>
       </c>
       <c r="B134">
-        <v>3010</v>
+        <v>13080</v>
       </c>
       <c r="C134" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B134,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>ライフスティール</v>
       </c>
       <c r="D134">
         <v>1</v>
       </c>
       <c r="E134">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -9441,20 +9444,20 @@
         <v>1003</v>
       </c>
       <c r="B135">
-        <v>3020</v>
+        <v>14050</v>
       </c>
       <c r="C135" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B135,[1]TextData!A:A))</f>
-        <v>カウンターオーラ</v>
+        <v>ホープフルアイリス</v>
       </c>
       <c r="D135">
         <v>1</v>
       </c>
       <c r="E135">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F135">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G135">
         <v>0</v>
@@ -9462,20 +9465,20 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B136">
-        <v>100310</v>
+        <v>4010</v>
       </c>
       <c r="C136" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B136,[1]TextData!A:A))</f>
-        <v>セイクリッドバリア</v>
+        <v>セイントレーザー</v>
       </c>
       <c r="D136">
         <v>1</v>
       </c>
       <c r="E136">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -9486,23 +9489,23 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B137">
-        <v>100320</v>
+        <v>4030</v>
       </c>
       <c r="C137" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B137,[1]TextData!A:A))</f>
-        <v>リベンジニードル</v>
+        <v>ヒーリング</v>
       </c>
       <c r="D137">
         <v>1</v>
       </c>
       <c r="E137">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F137">
-        <v>14214</v>
+        <v>1033</v>
       </c>
       <c r="G137">
         <v>0</v>
@@ -9510,14 +9513,14 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B138">
-        <v>403020</v>
+        <v>100410</v>
       </c>
       <c r="C138" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B138,[1]TextData!A:A))</f>
-        <v>カウンターオーラ+</v>
+        <v>アバンデンス</v>
       </c>
       <c r="D138">
         <v>1</v>
@@ -9534,20 +9537,20 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B139">
-        <v>403010</v>
+        <v>100420</v>
       </c>
       <c r="C139" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B139,[1]TextData!A:A))</f>
-        <v>アイスブレイド+</v>
+        <v>ハーヴェスト</v>
       </c>
       <c r="D139">
         <v>1</v>
       </c>
       <c r="E139">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -9558,14 +9561,14 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B140">
-        <v>13020</v>
+        <v>404030</v>
       </c>
       <c r="C140" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B140,[1]TextData!A:A))</f>
-        <v>クイックバリア</v>
+        <v>ヒーリング+</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -9582,14 +9585,14 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B141">
-        <v>13080</v>
+        <v>14080</v>
       </c>
       <c r="C141" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B141,[1]TextData!A:A))</f>
-        <v>ライフスティール</v>
+        <v>クイックヒール</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -9606,14 +9609,14 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B142">
-        <v>14050</v>
+        <v>14010</v>
       </c>
       <c r="C142" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B142,[1]TextData!A:A))</f>
-        <v>ホープフルアイリス</v>
+        <v>ディバインシールド</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -9622,7 +9625,7 @@
         <v>0</v>
       </c>
       <c r="F142">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G142">
         <v>0</v>
@@ -9633,17 +9636,17 @@
         <v>1004</v>
       </c>
       <c r="B143">
-        <v>4010</v>
+        <v>14040</v>
       </c>
       <c r="C143" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B143,[1]TextData!A:A))</f>
-        <v>セイントレーザー</v>
+        <v>リジェネレーション</v>
       </c>
       <c r="D143">
         <v>1</v>
       </c>
       <c r="E143">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F143">
         <v>0</v>
@@ -9657,20 +9660,20 @@
         <v>1004</v>
       </c>
       <c r="B144">
-        <v>4030</v>
+        <v>14090</v>
       </c>
       <c r="C144" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B144,[1]TextData!A:A))</f>
-        <v>ヒーリング</v>
+        <v>リレイズ</v>
       </c>
       <c r="D144">
         <v>1</v>
       </c>
       <c r="E144">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F144">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="G144">
         <v>0</v>
@@ -9678,20 +9681,20 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B145">
-        <v>100410</v>
+        <v>5010</v>
       </c>
       <c r="C145" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B145,[1]TextData!A:A))</f>
-        <v>アバンデンス</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="D145">
         <v>1</v>
       </c>
       <c r="E145">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F145">
         <v>0</v>
@@ -9702,23 +9705,23 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B146">
-        <v>100420</v>
+        <v>5070</v>
       </c>
       <c r="C146" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B146,[1]TextData!A:A))</f>
-        <v>ハーヴェスト</v>
+        <v>シェイディークラウド</v>
       </c>
       <c r="D146">
         <v>1</v>
       </c>
       <c r="E146">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F146">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G146">
         <v>0</v>
@@ -9726,14 +9729,14 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B147">
-        <v>404030</v>
+        <v>100510</v>
       </c>
       <c r="C147" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B147,[1]TextData!A:A))</f>
-        <v>ヒーリング+</v>
+        <v>カースドブレイク</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -9750,20 +9753,20 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B148">
-        <v>14080</v>
+        <v>100520</v>
       </c>
       <c r="C148" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B148,[1]TextData!A:A))</f>
-        <v>クイックヒール</v>
+        <v>ムーンライトレイ</v>
       </c>
       <c r="D148">
         <v>1</v>
       </c>
       <c r="E148">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F148">
         <v>0</v>
@@ -9774,14 +9777,14 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B149">
-        <v>14010</v>
+        <v>15090</v>
       </c>
       <c r="C149" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B149,[1]TextData!A:A))</f>
-        <v>ディバインシールド</v>
+        <v>クイックカース</v>
       </c>
       <c r="D149">
         <v>1</v>
@@ -9790,7 +9793,7 @@
         <v>0</v>
       </c>
       <c r="F149">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G149">
         <v>0</v>
@@ -9798,14 +9801,14 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B150">
-        <v>14040</v>
+        <v>405070</v>
       </c>
       <c r="C150" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B150,[1]TextData!A:A))</f>
-        <v>リジェネレーション</v>
+        <v>シェイディークラウド+</v>
       </c>
       <c r="D150">
         <v>1</v>
@@ -9822,14 +9825,14 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B151">
-        <v>14090</v>
+        <v>15080</v>
       </c>
       <c r="C151" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B151,[1]TextData!A:A))</f>
-        <v>リレイズ</v>
+        <v>ヒールハント</v>
       </c>
       <c r="D151">
         <v>1</v>
@@ -9849,17 +9852,17 @@
         <v>1005</v>
       </c>
       <c r="B152">
-        <v>5010</v>
+        <v>405010</v>
       </c>
       <c r="C152" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B152,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>ダークプリズン+</v>
       </c>
       <c r="D152">
         <v>1</v>
       </c>
       <c r="E152">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F152">
         <v>0</v>
@@ -9873,20 +9876,20 @@
         <v>1005</v>
       </c>
       <c r="B153">
-        <v>5070</v>
+        <v>415090</v>
       </c>
       <c r="C153" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B153,[1]TextData!A:A))</f>
-        <v>シェイディークラウド</v>
+        <v>クイックカース+</v>
       </c>
       <c r="D153">
         <v>1</v>
       </c>
       <c r="E153">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F153">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G153">
         <v>0</v>
@@ -9894,20 +9897,20 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B154">
-        <v>100510</v>
+        <v>1010</v>
       </c>
       <c r="C154" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B154,[1]TextData!A:A))</f>
-        <v>カースドブレイク</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D154">
         <v>1</v>
       </c>
       <c r="E154">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -9918,47 +9921,47 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B155">
-        <v>100520</v>
+        <v>1030</v>
       </c>
       <c r="C155" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B155,[1]TextData!A:A))</f>
-        <v>ムーンライトレイ</v>
+        <v>ヒートスタンプ</v>
       </c>
       <c r="D155">
         <v>1</v>
       </c>
       <c r="E155">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F155">
-        <v>0</v>
+        <v>9120</v>
       </c>
       <c r="G155">
-        <v>0</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="156" spans="1:7">
       <c r="A156">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B156">
-        <v>15090</v>
+        <v>1070</v>
       </c>
       <c r="C156" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B156,[1]TextData!A:A))</f>
-        <v>クイックカース</v>
+        <v>バーニングソウル</v>
       </c>
       <c r="D156">
         <v>1</v>
       </c>
       <c r="E156">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F156">
-        <v>0</v>
+        <v>6322</v>
       </c>
       <c r="G156">
         <v>0</v>
@@ -9966,14 +9969,14 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B157">
-        <v>405070</v>
+        <v>100610</v>
       </c>
       <c r="C157" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B157,[1]TextData!A:A))</f>
-        <v>シェイディークラウド+</v>
+        <v>サンフレイム</v>
       </c>
       <c r="D157">
         <v>1</v>
@@ -9990,20 +9993,20 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B158">
-        <v>15080</v>
+        <v>100620</v>
       </c>
       <c r="C158" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B158,[1]TextData!A:A))</f>
-        <v>ヒールハント</v>
+        <v>フレイムタン</v>
       </c>
       <c r="D158">
         <v>1</v>
       </c>
       <c r="E158">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -10014,14 +10017,14 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B159">
-        <v>405010</v>
+        <v>11040</v>
       </c>
       <c r="C159" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B159,[1]TextData!A:A))</f>
-        <v>ダークプリズン+</v>
+        <v>アクティブギフト</v>
       </c>
       <c r="D159">
         <v>1</v>
@@ -10030,7 +10033,7 @@
         <v>0</v>
       </c>
       <c r="F159">
-        <v>0</v>
+        <v>5042</v>
       </c>
       <c r="G159">
         <v>0</v>
@@ -10038,14 +10041,14 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B160">
-        <v>415090</v>
+        <v>401030</v>
       </c>
       <c r="C160" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B160,[1]TextData!A:A))</f>
-        <v>クイックカース+</v>
+        <v>ヒートスタンプ+</v>
       </c>
       <c r="D160">
         <v>1</v>
@@ -10065,17 +10068,17 @@
         <v>1006</v>
       </c>
       <c r="B161">
-        <v>1010</v>
+        <v>411040</v>
       </c>
       <c r="C161" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B161,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>アクティブギフト+</v>
       </c>
       <c r="D161">
         <v>1</v>
       </c>
       <c r="E161">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F161">
         <v>0</v>
@@ -10089,44 +10092,44 @@
         <v>1006</v>
       </c>
       <c r="B162">
-        <v>1030</v>
+        <v>13040</v>
       </c>
       <c r="C162" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B162,[1]TextData!A:A))</f>
-        <v>ヒートスタンプ</v>
+        <v>セルフシールド</v>
       </c>
       <c r="D162">
         <v>1</v>
       </c>
       <c r="E162">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F162">
-        <v>9120</v>
+        <v>0</v>
       </c>
       <c r="G162">
-        <v>1023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B163">
-        <v>1070</v>
+        <v>2010</v>
       </c>
       <c r="C163" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B163,[1]TextData!A:A))</f>
-        <v>バーニングソウル</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D163">
         <v>1</v>
       </c>
       <c r="E163">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F163">
-        <v>6322</v>
+        <v>0</v>
       </c>
       <c r="G163">
         <v>0</v>
@@ -10134,23 +10137,23 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B164">
-        <v>100610</v>
+        <v>2040</v>
       </c>
       <c r="C164" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B164,[1]TextData!A:A))</f>
-        <v>サンフレイム</v>
+        <v>トラストチェイン</v>
       </c>
       <c r="D164">
         <v>1</v>
       </c>
       <c r="E164">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F164">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G164">
         <v>0</v>
@@ -10158,20 +10161,20 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B165">
-        <v>100620</v>
+        <v>100710</v>
       </c>
       <c r="C165" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B165,[1]TextData!A:A))</f>
-        <v>フレイムタン</v>
+        <v>ライズザフラッグ</v>
       </c>
       <c r="D165">
         <v>1</v>
       </c>
       <c r="E165">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F165">
         <v>0</v>
@@ -10182,23 +10185,23 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B166">
-        <v>11040</v>
+        <v>100720</v>
       </c>
       <c r="C166" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B166,[1]TextData!A:A))</f>
-        <v>アクティブギフト</v>
+        <v>オーバーリミット</v>
       </c>
       <c r="D166">
         <v>1</v>
       </c>
       <c r="E166">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F166">
-        <v>5042</v>
+        <v>0</v>
       </c>
       <c r="G166">
         <v>0</v>
@@ -10206,14 +10209,14 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B167">
-        <v>401030</v>
+        <v>12090</v>
       </c>
       <c r="C167" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B167,[1]TextData!A:A))</f>
-        <v>ヒートスタンプ+</v>
+        <v>アウトオブオーダー</v>
       </c>
       <c r="D167">
         <v>1</v>
@@ -10222,7 +10225,7 @@
         <v>0</v>
       </c>
       <c r="F167">
-        <v>0</v>
+        <v>5042</v>
       </c>
       <c r="G167">
         <v>0</v>
@@ -10230,14 +10233,14 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B168">
-        <v>411040</v>
+        <v>412090</v>
       </c>
       <c r="C168" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B168,[1]TextData!A:A))</f>
-        <v>アクティブギフト+</v>
+        <v>アウトオブオーダー+</v>
       </c>
       <c r="D168">
         <v>1</v>
@@ -10254,14 +10257,14 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B169">
-        <v>13040</v>
+        <v>12050</v>
       </c>
       <c r="C169" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B169,[1]TextData!A:A))</f>
-        <v>セルフシールド</v>
+        <v>クイックムーブ</v>
       </c>
       <c r="D169">
         <v>1</v>
@@ -10281,17 +10284,17 @@
         <v>1007</v>
       </c>
       <c r="B170">
-        <v>2010</v>
+        <v>12070</v>
       </c>
       <c r="C170" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B170,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>ソーサリーコネクト</v>
       </c>
       <c r="D170">
         <v>1</v>
       </c>
       <c r="E170">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F170">
         <v>0</v>
@@ -10305,20 +10308,20 @@
         <v>1007</v>
       </c>
       <c r="B171">
-        <v>2040</v>
+        <v>14030</v>
       </c>
       <c r="C171" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B171,[1]TextData!A:A))</f>
-        <v>トラストチェイン</v>
+        <v>エイミングスコープ</v>
       </c>
       <c r="D171">
         <v>1</v>
       </c>
       <c r="E171">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F171">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G171">
         <v>0</v>
@@ -10326,20 +10329,20 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B172">
-        <v>100710</v>
+        <v>3010</v>
       </c>
       <c r="C172" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B172,[1]TextData!A:A))</f>
-        <v>ライズザフラッグ</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D172">
         <v>1</v>
       </c>
       <c r="E172">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F172">
         <v>0</v>
@@ -10350,20 +10353,20 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B173">
-        <v>100720</v>
+        <v>3070</v>
       </c>
       <c r="C173" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B173,[1]TextData!A:A))</f>
-        <v>オーバーリミット</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D173">
         <v>1</v>
       </c>
       <c r="E173">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F173">
         <v>0</v>
@@ -10374,14 +10377,14 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B174">
-        <v>12090</v>
+        <v>100810</v>
       </c>
       <c r="C174" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B174,[1]TextData!A:A))</f>
-        <v>アウトオブオーダー</v>
+        <v>テンパランス</v>
       </c>
       <c r="D174">
         <v>1</v>
@@ -10390,7 +10393,7 @@
         <v>0</v>
       </c>
       <c r="F174">
-        <v>5042</v>
+        <v>0</v>
       </c>
       <c r="G174">
         <v>0</v>
@@ -10398,20 +10401,20 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B175">
-        <v>412090</v>
+        <v>100820</v>
       </c>
       <c r="C175" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B175,[1]TextData!A:A))</f>
-        <v>アウトオブオーダー+</v>
+        <v>シエルクルセイダー</v>
       </c>
       <c r="D175">
         <v>1</v>
       </c>
       <c r="E175">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -10422,14 +10425,14 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B176">
-        <v>12050</v>
+        <v>13060</v>
       </c>
       <c r="C176" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B176,[1]TextData!A:A))</f>
-        <v>クイックムーブ</v>
+        <v>サプライカバー</v>
       </c>
       <c r="D176">
         <v>1</v>
@@ -10438,7 +10441,7 @@
         <v>0</v>
       </c>
       <c r="F176">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G176">
         <v>0</v>
@@ -10446,14 +10449,14 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B177">
-        <v>12070</v>
+        <v>403070</v>
       </c>
       <c r="C177" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B177,[1]TextData!A:A))</f>
-        <v>ソーサリーコネクト</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="D177">
         <v>1</v>
@@ -10470,14 +10473,14 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B178">
-        <v>14030</v>
+        <v>13010</v>
       </c>
       <c r="C178" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B178,[1]TextData!A:A))</f>
-        <v>エイミングスコープ</v>
+        <v>アーマーコード</v>
       </c>
       <c r="D178">
         <v>1</v>
@@ -10497,17 +10500,17 @@
         <v>1008</v>
       </c>
       <c r="B179">
-        <v>3010</v>
+        <v>13020</v>
       </c>
       <c r="C179" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B179,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>クイックバリア</v>
       </c>
       <c r="D179">
         <v>1</v>
       </c>
       <c r="E179">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F179">
         <v>0</v>
@@ -10521,17 +10524,17 @@
         <v>1008</v>
       </c>
       <c r="B180">
-        <v>3070</v>
+        <v>13040</v>
       </c>
       <c r="C180" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B180,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>セルフシールド</v>
       </c>
       <c r="D180">
         <v>1</v>
       </c>
       <c r="E180">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F180">
         <v>0</v>
@@ -10542,20 +10545,20 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B181">
-        <v>100810</v>
+        <v>1010</v>
       </c>
       <c r="C181" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B181,[1]TextData!A:A))</f>
-        <v>テンパランス</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D181">
         <v>1</v>
       </c>
       <c r="E181">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F181">
         <v>0</v>
@@ -10566,23 +10569,23 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B182">
-        <v>100820</v>
+        <v>1050</v>
       </c>
       <c r="C182" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B182,[1]TextData!A:A))</f>
-        <v>シエルクルセイダー</v>
+        <v>フレイムレイン</v>
       </c>
       <c r="D182">
         <v>1</v>
       </c>
       <c r="E182">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F182">
-        <v>0</v>
+        <v>1151</v>
       </c>
       <c r="G182">
         <v>0</v>
@@ -10590,14 +10593,14 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B183">
-        <v>13060</v>
+        <v>100910</v>
       </c>
       <c r="C183" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B183,[1]TextData!A:A))</f>
-        <v>サプライカバー</v>
+        <v>バーニングカウンター</v>
       </c>
       <c r="D183">
         <v>1</v>
@@ -10606,7 +10609,7 @@
         <v>0</v>
       </c>
       <c r="F183">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G183">
         <v>0</v>
@@ -10614,20 +10617,20 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B184">
-        <v>403070</v>
+        <v>100920</v>
       </c>
       <c r="C184" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B184,[1]TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>プロミネンス</v>
       </c>
       <c r="D184">
         <v>1</v>
       </c>
       <c r="E184">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F184">
         <v>0</v>
@@ -10638,14 +10641,14 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B185">
-        <v>13010</v>
+        <v>11070</v>
       </c>
       <c r="C185" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B185,[1]TextData!A:A))</f>
-        <v>アーマーコード</v>
+        <v>ルージュバック</v>
       </c>
       <c r="D185">
         <v>1</v>
@@ -10662,14 +10665,14 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B186">
-        <v>13020</v>
+        <v>401050</v>
       </c>
       <c r="C186" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B186,[1]TextData!A:A))</f>
-        <v>クイックバリア</v>
+        <v>フレイムレイン+</v>
       </c>
       <c r="D186">
         <v>1</v>
@@ -10686,14 +10689,14 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B187">
-        <v>13040</v>
+        <v>11030</v>
       </c>
       <c r="C187" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B187,[1]TextData!A:A))</f>
-        <v>セルフシールド</v>
+        <v>アサルトシフト</v>
       </c>
       <c r="D187">
         <v>1</v>
@@ -10713,17 +10716,17 @@
         <v>1009</v>
       </c>
       <c r="B188">
-        <v>1010</v>
+        <v>11020</v>
       </c>
       <c r="C188" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B188,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>プリディカメント</v>
       </c>
       <c r="D188">
         <v>1</v>
       </c>
       <c r="E188">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F188">
         <v>0</v>
@@ -10737,20 +10740,20 @@
         <v>1009</v>
       </c>
       <c r="B189">
-        <v>1050</v>
+        <v>15040</v>
       </c>
       <c r="C189" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B189,[1]TextData!A:A))</f>
-        <v>フレイムレイン</v>
+        <v>スカルグラッジ</v>
       </c>
       <c r="D189">
         <v>1</v>
       </c>
       <c r="E189">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F189">
-        <v>1151</v>
+        <v>0</v>
       </c>
       <c r="G189">
         <v>0</v>
@@ -10758,20 +10761,20 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B190">
-        <v>100910</v>
+        <v>2010</v>
       </c>
       <c r="C190" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B190,[1]TextData!A:A))</f>
-        <v>バーニングカウンター</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D190">
         <v>1</v>
       </c>
       <c r="E190">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F190">
         <v>0</v>
@@ -10782,23 +10785,23 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B191">
-        <v>100920</v>
+        <v>2030</v>
       </c>
       <c r="C191" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B191,[1]TextData!A:A))</f>
-        <v>プロミネンス</v>
+        <v>ショックインパルス</v>
       </c>
       <c r="D191">
         <v>1</v>
       </c>
       <c r="E191">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F191">
-        <v>0</v>
+        <v>14215</v>
       </c>
       <c r="G191">
         <v>0</v>
@@ -10806,14 +10809,14 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B192">
-        <v>11070</v>
+        <v>101010</v>
       </c>
       <c r="C192" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B192,[1]TextData!A:A))</f>
-        <v>ルージュバック</v>
+        <v>エウロス</v>
       </c>
       <c r="D192">
         <v>1</v>
@@ -10830,20 +10833,20 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B193">
-        <v>401050</v>
+        <v>101020</v>
       </c>
       <c r="C193" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B193,[1]TextData!A:A))</f>
-        <v>フレイムレイン+</v>
+        <v>ボレアス</v>
       </c>
       <c r="D193">
         <v>1</v>
       </c>
       <c r="E193">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F193">
         <v>0</v>
@@ -10854,14 +10857,14 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B194">
-        <v>11030</v>
+        <v>12010</v>
       </c>
       <c r="C194" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B194,[1]TextData!A:A))</f>
-        <v>アサルトシフト</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D194">
         <v>1</v>
@@ -10878,14 +10881,14 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B195">
-        <v>11020</v>
+        <v>402030</v>
       </c>
       <c r="C195" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B195,[1]TextData!A:A))</f>
-        <v>プリディカメント</v>
+        <v>ショックインパルス+</v>
       </c>
       <c r="D195">
         <v>1</v>
@@ -10902,14 +10905,14 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B196">
-        <v>15040</v>
+        <v>12020</v>
       </c>
       <c r="C196" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B196,[1]TextData!A:A))</f>
-        <v>スカルグラッジ</v>
+        <v>ヘブンリーラック</v>
       </c>
       <c r="D196">
         <v>1</v>
@@ -10929,17 +10932,17 @@
         <v>1010</v>
       </c>
       <c r="B197">
-        <v>2010</v>
+        <v>12030</v>
       </c>
       <c r="C197" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B197,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>スウィフトカレント</v>
       </c>
       <c r="D197">
         <v>1</v>
       </c>
       <c r="E197">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F197">
         <v>0</v>
@@ -10953,20 +10956,20 @@
         <v>1010</v>
       </c>
       <c r="B198">
-        <v>2030</v>
+        <v>15070</v>
       </c>
       <c r="C198" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B198,[1]TextData!A:A))</f>
-        <v>ショックインパルス</v>
+        <v>ジャックポッド</v>
       </c>
       <c r="D198">
         <v>1</v>
       </c>
       <c r="E198">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F198">
-        <v>14215</v>
+        <v>0</v>
       </c>
       <c r="G198">
         <v>0</v>
@@ -10974,20 +10977,20 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B199">
-        <v>101010</v>
+        <v>3010</v>
       </c>
       <c r="C199" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B199,[1]TextData!A:A))</f>
-        <v>エウロス</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D199">
         <v>1</v>
       </c>
       <c r="E199">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F199">
         <v>0</v>
@@ -10998,20 +11001,20 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B200">
-        <v>101020</v>
+        <v>3050</v>
       </c>
       <c r="C200" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B200,[1]TextData!A:A))</f>
-        <v>ボレアス</v>
+        <v>ディープフリーズ</v>
       </c>
       <c r="D200">
         <v>1</v>
       </c>
       <c r="E200">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F200">
         <v>0</v>
@@ -11022,14 +11025,14 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B201">
-        <v>12010</v>
+        <v>101110</v>
       </c>
       <c r="C201" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B201,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>アバランシュ</v>
       </c>
       <c r="D201">
         <v>1</v>
@@ -11046,20 +11049,20 @@
     </row>
     <row r="202" spans="1:7">
       <c r="A202">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B202">
-        <v>402030</v>
+        <v>101120</v>
       </c>
       <c r="C202" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B202,[1]TextData!A:A))</f>
-        <v>ショックインパルス+</v>
+        <v>ブリザードコフィン</v>
       </c>
       <c r="D202">
         <v>1</v>
       </c>
       <c r="E202">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F202">
         <v>0</v>
@@ -11070,14 +11073,14 @@
     </row>
     <row r="203" spans="1:7">
       <c r="A203">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B203">
-        <v>12020</v>
+        <v>13090</v>
       </c>
       <c r="C203" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B203,[1]TextData!A:A))</f>
-        <v>ヘブンリーラック</v>
+        <v>アイスセイバー</v>
       </c>
       <c r="D203">
         <v>1</v>
@@ -11094,14 +11097,14 @@
     </row>
     <row r="204" spans="1:7">
       <c r="A204">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B204">
-        <v>12030</v>
+        <v>403050</v>
       </c>
       <c r="C204" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B204,[1]TextData!A:A))</f>
-        <v>スウィフトカレント</v>
+        <v>ディープフリーズ+</v>
       </c>
       <c r="D204">
         <v>1</v>
@@ -11118,14 +11121,14 @@
     </row>
     <row r="205" spans="1:7">
       <c r="A205">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B205">
-        <v>15070</v>
+        <v>13050</v>
       </c>
       <c r="C205" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B205,[1]TextData!A:A))</f>
-        <v>ジャックポッド</v>
+        <v>パッシブジャミング</v>
       </c>
       <c r="D205">
         <v>1</v>
@@ -11145,17 +11148,17 @@
         <v>1011</v>
       </c>
       <c r="B206">
-        <v>3010</v>
+        <v>13070</v>
       </c>
       <c r="C206" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B206,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>アシッドラッシュ</v>
       </c>
       <c r="D206">
         <v>1</v>
       </c>
       <c r="E206">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F206">
         <v>0</v>
@@ -11169,17 +11172,17 @@
         <v>1011</v>
       </c>
       <c r="B207">
-        <v>3050</v>
+        <v>14070</v>
       </c>
       <c r="C207" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B207,[1]TextData!A:A))</f>
-        <v>ディープフリーズ</v>
+        <v>ホーミングクルセイド</v>
       </c>
       <c r="D207">
         <v>1</v>
       </c>
       <c r="E207">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F207">
         <v>0</v>
@@ -11190,20 +11193,20 @@
     </row>
     <row r="208" spans="1:7">
       <c r="A208">
-        <v>1011</v>
+        <v>1101</v>
       </c>
       <c r="B208">
-        <v>101110</v>
+        <v>3010</v>
       </c>
       <c r="C208" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B208,[1]TextData!A:A))</f>
-        <v>アバランシュ</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D208">
         <v>1</v>
       </c>
       <c r="E208">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F208">
         <v>0</v>
@@ -11214,20 +11217,20 @@
     </row>
     <row r="209" spans="1:7">
       <c r="A209">
-        <v>1011</v>
+        <v>1101</v>
       </c>
       <c r="B209">
-        <v>101120</v>
+        <v>3070</v>
       </c>
       <c r="C209" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B209,[1]TextData!A:A))</f>
-        <v>ブリザードコフィン</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D209">
         <v>1</v>
       </c>
       <c r="E209">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F209">
         <v>0</v>
@@ -11238,14 +11241,14 @@
     </row>
     <row r="210" spans="1:7">
       <c r="A210">
-        <v>1011</v>
+        <v>1101</v>
       </c>
       <c r="B210">
-        <v>13090</v>
+        <v>110110</v>
       </c>
       <c r="C210" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B210,[1]TextData!A:A))</f>
-        <v>アイスセイバー</v>
+        <v>ウィビングヒストリー</v>
       </c>
       <c r="D210">
         <v>1</v>
@@ -11262,20 +11265,20 @@
     </row>
     <row r="211" spans="1:7">
       <c r="A211">
-        <v>1011</v>
+        <v>1101</v>
       </c>
       <c r="B211">
-        <v>403050</v>
+        <v>110120</v>
       </c>
       <c r="C211" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B211,[1]TextData!A:A))</f>
-        <v>ディープフリーズ+</v>
+        <v>アンライバルド</v>
       </c>
       <c r="D211">
         <v>1</v>
       </c>
       <c r="E211">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F211">
         <v>0</v>
@@ -11286,14 +11289,14 @@
     </row>
     <row r="212" spans="1:7">
       <c r="A212">
-        <v>1011</v>
+        <v>1101</v>
       </c>
       <c r="B212">
-        <v>13050</v>
+        <v>13100</v>
       </c>
       <c r="C212" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B212,[1]TextData!A:A))</f>
-        <v>パッシブジャミング</v>
+        <v>ルミナスカバー</v>
       </c>
       <c r="D212">
         <v>1</v>
@@ -11310,14 +11313,14 @@
     </row>
     <row r="213" spans="1:7">
       <c r="A213">
-        <v>1011</v>
+        <v>1101</v>
       </c>
       <c r="B213">
-        <v>13070</v>
+        <v>403050</v>
       </c>
       <c r="C213" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B213,[1]TextData!A:A))</f>
-        <v>アシッドラッシュ</v>
+        <v>ディープフリーズ+</v>
       </c>
       <c r="D213">
         <v>1</v>
@@ -11334,14 +11337,14 @@
     </row>
     <row r="214" spans="1:7">
       <c r="A214">
-        <v>1011</v>
+        <v>1101</v>
       </c>
       <c r="B214">
-        <v>14070</v>
+        <v>13050</v>
       </c>
       <c r="C214" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B214,[1]TextData!A:A))</f>
-        <v>ホーミングクルセイド</v>
+        <v>パッシブジャミング</v>
       </c>
       <c r="D214">
         <v>1</v>
@@ -11361,17 +11364,17 @@
         <v>1101</v>
       </c>
       <c r="B215">
-        <v>3010</v>
+        <v>13070</v>
       </c>
       <c r="C215" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B215,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>アシッドラッシュ</v>
       </c>
       <c r="D215">
         <v>1</v>
       </c>
       <c r="E215">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F215">
         <v>0</v>
@@ -11385,190 +11388,22 @@
         <v>1101</v>
       </c>
       <c r="B216">
-        <v>3070</v>
+        <v>14070</v>
       </c>
       <c r="C216" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B216,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>ホーミングクルセイド</v>
       </c>
       <c r="D216">
         <v>1</v>
       </c>
       <c r="E216">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F216">
         <v>0</v>
       </c>
       <c r="G216">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7">
-      <c r="A217">
-        <v>1101</v>
-      </c>
-      <c r="B217">
-        <v>110110</v>
-      </c>
-      <c r="C217" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B217,[1]TextData!A:A))</f>
-        <v>ウィビングヒストリー</v>
-      </c>
-      <c r="D217">
-        <v>1</v>
-      </c>
-      <c r="E217">
-        <v>0</v>
-      </c>
-      <c r="F217">
-        <v>0</v>
-      </c>
-      <c r="G217">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7">
-      <c r="A218">
-        <v>1101</v>
-      </c>
-      <c r="B218">
-        <v>110120</v>
-      </c>
-      <c r="C218" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B218,[1]TextData!A:A))</f>
-        <v>アンライバルド</v>
-      </c>
-      <c r="D218">
-        <v>1</v>
-      </c>
-      <c r="E218">
-        <v>200</v>
-      </c>
-      <c r="F218">
-        <v>0</v>
-      </c>
-      <c r="G218">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7">
-      <c r="A219">
-        <v>1101</v>
-      </c>
-      <c r="B219">
-        <v>13100</v>
-      </c>
-      <c r="C219" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B219,[1]TextData!A:A))</f>
-        <v>ルミナスカバー</v>
-      </c>
-      <c r="D219">
-        <v>1</v>
-      </c>
-      <c r="E219">
-        <v>0</v>
-      </c>
-      <c r="F219">
-        <v>0</v>
-      </c>
-      <c r="G219">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7">
-      <c r="A220">
-        <v>1101</v>
-      </c>
-      <c r="B220">
-        <v>403050</v>
-      </c>
-      <c r="C220" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B220,[1]TextData!A:A))</f>
-        <v>ディープフリーズ+</v>
-      </c>
-      <c r="D220">
-        <v>1</v>
-      </c>
-      <c r="E220">
-        <v>0</v>
-      </c>
-      <c r="F220">
-        <v>0</v>
-      </c>
-      <c r="G220">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7">
-      <c r="A221">
-        <v>1101</v>
-      </c>
-      <c r="B221">
-        <v>13050</v>
-      </c>
-      <c r="C221" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B221,[1]TextData!A:A))</f>
-        <v>パッシブジャミング</v>
-      </c>
-      <c r="D221">
-        <v>1</v>
-      </c>
-      <c r="E221">
-        <v>0</v>
-      </c>
-      <c r="F221">
-        <v>0</v>
-      </c>
-      <c r="G221">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7">
-      <c r="A222">
-        <v>1101</v>
-      </c>
-      <c r="B222">
-        <v>13070</v>
-      </c>
-      <c r="C222" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B222,[1]TextData!A:A))</f>
-        <v>アシッドラッシュ</v>
-      </c>
-      <c r="D222">
-        <v>1</v>
-      </c>
-      <c r="E222">
-        <v>0</v>
-      </c>
-      <c r="F222">
-        <v>0</v>
-      </c>
-      <c r="G222">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7">
-      <c r="A223">
-        <v>1101</v>
-      </c>
-      <c r="B223">
-        <v>14070</v>
-      </c>
-      <c r="C223" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B223,[1]TextData!A:A))</f>
-        <v>ホーミングクルセイド</v>
-      </c>
-      <c r="D223">
-        <v>1</v>
-      </c>
-      <c r="E223">
-        <v>0</v>
-      </c>
-      <c r="F223">
-        <v>0</v>
-      </c>
-      <c r="G223">
         <v>0</v>
       </c>
     </row>
@@ -12120,7 +11955,7 @@
         <v>207</v>
       </c>
       <c r="B31" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -12128,7 +11963,7 @@
         <v>301</v>
       </c>
       <c r="B32" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -12136,7 +11971,7 @@
         <v>1001</v>
       </c>
       <c r="B33" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -12144,7 +11979,7 @@
         <v>1002</v>
       </c>
       <c r="B34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -12152,7 +11987,7 @@
         <v>1003</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -12160,7 +11995,7 @@
         <v>1004</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -12168,7 +12003,7 @@
         <v>1005</v>
       </c>
       <c r="B37" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -12176,7 +12011,7 @@
         <v>1006</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -12184,7 +12019,7 @@
         <v>1007</v>
       </c>
       <c r="B39" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -12192,7 +12027,7 @@
         <v>1008</v>
       </c>
       <c r="B40" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -12200,7 +12035,7 @@
         <v>1009</v>
       </c>
       <c r="B41" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -12208,7 +12043,7 @@
         <v>1010</v>
       </c>
       <c r="B42" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -12216,7 +12051,7 @@
         <v>1011</v>
       </c>
       <c r="B43" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -12224,7 +12059,7 @@
         <v>1101</v>
       </c>
       <c r="B44" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -12232,7 +12067,7 @@
         <v>1102</v>
       </c>
       <c r="B45" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -12249,7 +12084,7 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="2:3">
@@ -12257,7 +12092,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="2:3">
@@ -12265,7 +12100,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="2:3">
@@ -12273,7 +12108,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="2:3">
@@ -12281,7 +12116,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="2:3">
@@ -12289,7 +12124,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="2:3">
@@ -12297,7 +12132,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="2:3">
@@ -12305,7 +12140,7 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="2:3">
@@ -12313,7 +12148,7 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -436,15 +436,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -459,15 +476,23 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -482,8 +507,16 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -497,7 +530,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -505,46 +545,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -557,19 +565,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -589,7 +589,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -601,121 +673,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -733,7 +703,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -745,19 +733,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -769,7 +763,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -780,48 +780,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -836,6 +794,39 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -866,17 +857,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -888,7 +888,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -897,136 +897,136 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2352,1231 +2352,1231 @@
         </row>
         <row r="155">
           <cell r="A155">
-            <v>200110</v>
+            <v>110210</v>
           </cell>
           <cell r="B155" t="str">
-            <v>スリータイムス</v>
+            <v>リベリオンスピリッツ</v>
           </cell>
         </row>
         <row r="156">
           <cell r="A156">
-            <v>200120</v>
+            <v>110220</v>
           </cell>
           <cell r="B156" t="str">
-            <v>アングリークライ</v>
+            <v>ファイナリティアビス</v>
           </cell>
         </row>
         <row r="157">
           <cell r="A157">
-            <v>200210</v>
+            <v>200110</v>
           </cell>
           <cell r="B157" t="str">
-            <v>マイトレインフォース</v>
+            <v>スリータイムス</v>
           </cell>
         </row>
         <row r="158">
           <cell r="A158">
-            <v>200220</v>
+            <v>200120</v>
           </cell>
           <cell r="B158" t="str">
-            <v>カタストロフィ</v>
+            <v>アングリークライ</v>
           </cell>
         </row>
         <row r="159">
           <cell r="A159">
-            <v>200230</v>
+            <v>200210</v>
           </cell>
           <cell r="B159" t="str">
-            <v>悪魔(ベリト)</v>
+            <v>マイトレインフォース</v>
           </cell>
         </row>
         <row r="160">
           <cell r="A160">
-            <v>200310</v>
+            <v>200220</v>
           </cell>
           <cell r="B160" t="str">
-            <v>プルガシオン</v>
+            <v>カタストロフィ</v>
           </cell>
         </row>
         <row r="161">
           <cell r="A161">
-            <v>200320</v>
+            <v>200230</v>
           </cell>
           <cell r="B161" t="str">
-            <v>プリエステス</v>
+            <v>悪魔(ベリト)</v>
           </cell>
         </row>
         <row r="162">
           <cell r="A162">
-            <v>200330</v>
+            <v>200310</v>
           </cell>
           <cell r="B162" t="str">
-            <v>悪魔(パイモン)</v>
+            <v>プルガシオン</v>
           </cell>
         </row>
         <row r="163">
           <cell r="A163">
-            <v>200410</v>
+            <v>200320</v>
           </cell>
           <cell r="B163" t="str">
-            <v>コウソクテンショウ</v>
+            <v>プリエステス</v>
           </cell>
         </row>
         <row r="164">
           <cell r="A164">
-            <v>200411</v>
+            <v>200330</v>
           </cell>
           <cell r="B164" t="str">
-            <v>コウソクテンショウ</v>
+            <v>悪魔(パイモン)</v>
           </cell>
         </row>
         <row r="165">
           <cell r="A165">
-            <v>200420</v>
+            <v>200410</v>
           </cell>
           <cell r="B165" t="str">
-            <v>アンチバフ</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="166">
           <cell r="A166">
-            <v>200430</v>
+            <v>200411</v>
           </cell>
           <cell r="B166" t="str">
-            <v>悪魔(アンドラス)</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="167">
           <cell r="A167">
-            <v>200510</v>
+            <v>200420</v>
           </cell>
           <cell r="B167" t="str">
-            <v>カウントダウン</v>
+            <v>アンチバフ</v>
           </cell>
         </row>
         <row r="168">
           <cell r="A168">
-            <v>200520</v>
+            <v>200430</v>
           </cell>
           <cell r="B168" t="str">
-            <v>グラウンドゼロ</v>
+            <v>悪魔(アンドラス)</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169">
-            <v>200530</v>
+            <v>200510</v>
           </cell>
           <cell r="B169" t="str">
-            <v>悪魔(ビフロンス)</v>
+            <v>カウントダウン</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170">
-            <v>201010</v>
+            <v>200520</v>
           </cell>
           <cell r="B170" t="str">
-            <v>カオスペイン</v>
+            <v>グラウンドゼロ</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171">
-            <v>201020</v>
+            <v>200530</v>
           </cell>
           <cell r="B171" t="str">
-            <v>フォールンワン</v>
+            <v>悪魔(ビフロンス)</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172">
-            <v>201030</v>
+            <v>201010</v>
           </cell>
           <cell r="B172" t="str">
-            <v>アンリマユ</v>
+            <v>カオスペイン</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173">
-            <v>300010</v>
+            <v>201020</v>
           </cell>
           <cell r="B173" t="str">
-            <v>ライフブースト</v>
+            <v>フォールンワン</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174">
-            <v>300020</v>
+            <v>201030</v>
           </cell>
           <cell r="B174" t="str">
-            <v>スピリットチャージ</v>
+            <v>アンリマユ</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175">
-            <v>300030</v>
+            <v>300010</v>
           </cell>
           <cell r="B175" t="str">
-            <v>フォースライズ</v>
+            <v>ライフブースト</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176">
-            <v>300040</v>
+            <v>300020</v>
           </cell>
           <cell r="B176" t="str">
-            <v>ディフェンスオーラ</v>
+            <v>スピリットチャージ</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177">
-            <v>300050</v>
+            <v>300030</v>
           </cell>
           <cell r="B177" t="str">
-            <v>ラピッドムーブ</v>
+            <v>フォースライズ</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178">
-            <v>300130</v>
+            <v>300040</v>
           </cell>
           <cell r="B178" t="str">
-            <v>アタックブレイク</v>
+            <v>ディフェンスオーラ</v>
           </cell>
         </row>
         <row r="179">
           <cell r="A179">
-            <v>300140</v>
+            <v>300050</v>
           </cell>
           <cell r="B179" t="str">
-            <v>シールドバニッシュ</v>
+            <v>ラピッドムーブ</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180">
-            <v>300210</v>
+            <v>300130</v>
           </cell>
           <cell r="B180" t="str">
-            <v>エーテルリチャージ</v>
+            <v>アタックブレイク</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181">
-            <v>300220</v>
+            <v>300140</v>
           </cell>
           <cell r="B181" t="str">
-            <v>リカバリーエンハンス</v>
+            <v>シールドバニッシュ</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182">
-            <v>300230</v>
+            <v>300210</v>
           </cell>
           <cell r="B182" t="str">
-            <v>ヴェンジェンス</v>
+            <v>エーテルリチャージ</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183">
-            <v>301010</v>
+            <v>300220</v>
           </cell>
           <cell r="B183" t="str">
-            <v>ディケイドリセット</v>
+            <v>リカバリーエンハンス</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184">
-            <v>301020</v>
+            <v>300230</v>
           </cell>
           <cell r="B184" t="str">
-            <v>ウォーリアーブラッド</v>
+            <v>ヴェンジェンス</v>
           </cell>
         </row>
         <row r="185">
           <cell r="A185">
-            <v>301030</v>
+            <v>301010</v>
           </cell>
           <cell r="B185" t="str">
-            <v>トライアングルガード</v>
+            <v>ディケイドリセット</v>
           </cell>
         </row>
         <row r="186">
           <cell r="A186">
-            <v>301040</v>
+            <v>301020</v>
           </cell>
           <cell r="B186" t="str">
-            <v>セーフティバリア</v>
+            <v>ウォーリアーブラッド</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187">
-            <v>301050</v>
+            <v>301030</v>
           </cell>
           <cell r="B187" t="str">
-            <v>ヒロインズハイ</v>
+            <v>トライアングルガード</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188">
-            <v>301060</v>
+            <v>301040</v>
           </cell>
           <cell r="B188" t="str">
-            <v>セカンドステージ</v>
+            <v>セーフティバリア</v>
           </cell>
         </row>
         <row r="189">
           <cell r="A189">
-            <v>301070</v>
+            <v>301050</v>
           </cell>
           <cell r="B189" t="str">
-            <v>ハイヒットポイント</v>
+            <v>ヒロインズハイ</v>
           </cell>
         </row>
         <row r="190">
           <cell r="A190">
-            <v>301080</v>
+            <v>301060</v>
           </cell>
           <cell r="B190" t="str">
-            <v>セプタブラスト</v>
+            <v>セカンドステージ</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191">
-            <v>301090</v>
+            <v>301070</v>
           </cell>
           <cell r="B191" t="str">
-            <v>イニシャルブロッカー</v>
+            <v>ハイヒットポイント</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192">
-            <v>301100</v>
+            <v>301080</v>
           </cell>
           <cell r="B192" t="str">
-            <v>ファーストテイク</v>
+            <v>セプタブラスト</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193">
-            <v>310010</v>
+            <v>301090</v>
           </cell>
           <cell r="B193" t="str">
-            <v>妖精の祈り</v>
+            <v>イニシャルブロッカー</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194">
-            <v>310020</v>
+            <v>301100</v>
           </cell>
           <cell r="B194" t="str">
-            <v>月のかけら</v>
+            <v>ファーストテイク</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195">
-            <v>310030</v>
+            <v>310010</v>
           </cell>
           <cell r="B195" t="str">
-            <v>商売の才覚書</v>
+            <v>妖精の祈り</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196">
-            <v>310040</v>
+            <v>310020</v>
           </cell>
           <cell r="B196" t="str">
-            <v>メビウスの砂時計</v>
+            <v>月のかけら</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197">
-            <v>310050</v>
+            <v>310030</v>
           </cell>
           <cell r="B197" t="str">
-            <v>先陣の心得</v>
+            <v>商売の才覚書</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198">
-            <v>310060</v>
+            <v>310040</v>
           </cell>
           <cell r="B198" t="str">
-            <v>ヒスイの勾玉</v>
+            <v>メビウスの砂時計</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199">
-            <v>310070</v>
+            <v>310050</v>
           </cell>
           <cell r="B199" t="str">
-            <v>英傑の盾</v>
+            <v>先陣の心得</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200">
-            <v>310080</v>
+            <v>310060</v>
           </cell>
           <cell r="B200" t="str">
-            <v>鷹の目</v>
+            <v>ヒスイの勾玉</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201">
-            <v>310130</v>
+            <v>310070</v>
           </cell>
           <cell r="B201" t="str">
-            <v>ヒールユニット</v>
+            <v>英傑の盾</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202">
-            <v>320010</v>
+            <v>310080</v>
           </cell>
           <cell r="B202" t="str">
-            <v>訓練所Lv1</v>
+            <v>鷹の目</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203">
-            <v>320011</v>
+            <v>310130</v>
           </cell>
           <cell r="B203" t="str">
-            <v>訓練所Lv2</v>
+            <v>ヒールユニット</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204">
-            <v>320012</v>
+            <v>320010</v>
           </cell>
           <cell r="B204" t="str">
-            <v>訓練所Lv3</v>
+            <v>訓練所Lv1</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205">
-            <v>320020</v>
+            <v>320011</v>
           </cell>
           <cell r="B205" t="str">
-            <v>研究施設Lv1</v>
+            <v>訓練所Lv2</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206">
-            <v>320021</v>
+            <v>320012</v>
           </cell>
           <cell r="B206" t="str">
-            <v>研究施設Lv2</v>
+            <v>訓練所Lv3</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207">
-            <v>320022</v>
+            <v>320020</v>
           </cell>
           <cell r="B207" t="str">
-            <v>研究施設Lv3</v>
+            <v>研究施設Lv1</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208">
-            <v>320030</v>
+            <v>320021</v>
           </cell>
           <cell r="B208" t="str">
-            <v>資料館Lv1</v>
+            <v>研究施設Lv2</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209">
-            <v>320031</v>
+            <v>320022</v>
           </cell>
           <cell r="B209" t="str">
-            <v>資料館Lv2</v>
+            <v>研究施設Lv3</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210">
-            <v>320032</v>
+            <v>320030</v>
           </cell>
           <cell r="B210" t="str">
-            <v>資料館Lv3</v>
+            <v>資料館Lv1</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211">
-            <v>320040</v>
+            <v>320031</v>
           </cell>
           <cell r="B211" t="str">
-            <v>潜伏技術Lv1</v>
+            <v>資料館Lv2</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212">
-            <v>321010</v>
+            <v>320032</v>
           </cell>
           <cell r="B212" t="str">
-            <v>炎の祭壇</v>
+            <v>資料館Lv3</v>
           </cell>
         </row>
         <row r="213">
           <cell r="A213">
-            <v>321020</v>
+            <v>320040</v>
           </cell>
           <cell r="B213" t="str">
-            <v>稲妻の祭壇</v>
+            <v>潜伏技術Lv1</v>
           </cell>
         </row>
         <row r="214">
           <cell r="A214">
-            <v>321030</v>
+            <v>321010</v>
           </cell>
           <cell r="B214" t="str">
-            <v>蒼の祭壇</v>
+            <v>炎の祭壇</v>
           </cell>
         </row>
         <row r="215">
           <cell r="A215">
-            <v>321040</v>
+            <v>321020</v>
           </cell>
           <cell r="B215" t="str">
-            <v>光の祭壇</v>
+            <v>稲妻の祭壇</v>
           </cell>
         </row>
         <row r="216">
           <cell r="A216">
-            <v>321050</v>
+            <v>321030</v>
           </cell>
           <cell r="B216" t="str">
-            <v>月の祭壇</v>
+            <v>蒼の祭壇</v>
           </cell>
         </row>
         <row r="217">
           <cell r="A217">
-            <v>322010</v>
+            <v>321040</v>
           </cell>
           <cell r="B217" t="str">
-            <v>食糧庫Lv1</v>
+            <v>光の祭壇</v>
           </cell>
         </row>
         <row r="218">
           <cell r="A218">
-            <v>322020</v>
+            <v>321050</v>
           </cell>
           <cell r="B218" t="str">
-            <v>攻撃技術Lv1</v>
+            <v>月の祭壇</v>
           </cell>
         </row>
         <row r="219">
           <cell r="A219">
-            <v>322030</v>
+            <v>322010</v>
           </cell>
           <cell r="B219" t="str">
-            <v>防御技術Lv1</v>
+            <v>食糧庫Lv1</v>
           </cell>
         </row>
         <row r="220">
           <cell r="A220">
-            <v>322040</v>
+            <v>322020</v>
           </cell>
           <cell r="B220" t="str">
-            <v>詠唱技術Lv1</v>
+            <v>攻撃技術Lv1</v>
           </cell>
         </row>
         <row r="221">
           <cell r="A221">
-            <v>401010</v>
+            <v>322030</v>
           </cell>
           <cell r="B221" t="str">
-            <v>ファイアボール+</v>
+            <v>防御技術Lv1</v>
           </cell>
         </row>
         <row r="222">
           <cell r="A222">
-            <v>401020</v>
+            <v>322040</v>
           </cell>
           <cell r="B222" t="str">
-            <v>バーンストーム+</v>
+            <v>詠唱技術Lv1</v>
           </cell>
         </row>
         <row r="223">
           <cell r="A223">
-            <v>401030</v>
+            <v>401010</v>
           </cell>
           <cell r="B223" t="str">
-            <v>ヒートスタンプ+</v>
+            <v>ファイアボール+</v>
           </cell>
         </row>
         <row r="224">
           <cell r="A224">
-            <v>401040</v>
+            <v>401020</v>
           </cell>
           <cell r="B224" t="str">
-            <v>ソードアダプト+</v>
+            <v>バーンストーム+</v>
           </cell>
         </row>
         <row r="225">
           <cell r="A225">
-            <v>401050</v>
+            <v>401030</v>
           </cell>
           <cell r="B225" t="str">
-            <v>フレイムレイン+</v>
+            <v>ヒートスタンプ+</v>
           </cell>
         </row>
         <row r="226">
           <cell r="A226">
-            <v>401060</v>
+            <v>401040</v>
           </cell>
           <cell r="B226" t="str">
-            <v>イクスティンクション+</v>
+            <v>ソードアダプト+</v>
           </cell>
         </row>
         <row r="227">
           <cell r="A227">
-            <v>401070</v>
+            <v>401050</v>
           </cell>
           <cell r="B227" t="str">
-            <v>バーニングソウル+</v>
+            <v>フレイムレイン+</v>
           </cell>
         </row>
         <row r="228">
           <cell r="A228">
-            <v>401080</v>
+            <v>401060</v>
           </cell>
           <cell r="B228" t="str">
-            <v>レイジングバウンサー+</v>
+            <v>イクスティンクション+</v>
           </cell>
         </row>
         <row r="229">
           <cell r="A229">
-            <v>402010</v>
+            <v>401070</v>
           </cell>
           <cell r="B229" t="str">
-            <v>ディスチャージ+</v>
+            <v>バーニングソウル+</v>
           </cell>
         </row>
         <row r="230">
           <cell r="A230">
-            <v>402020</v>
+            <v>401080</v>
           </cell>
           <cell r="B230" t="str">
-            <v>イベイドコード+</v>
+            <v>レイジングバウンサー+</v>
           </cell>
         </row>
         <row r="231">
           <cell r="A231">
-            <v>402030</v>
+            <v>402010</v>
           </cell>
           <cell r="B231" t="str">
-            <v>ショックインパルス+</v>
+            <v>ディスチャージ+</v>
           </cell>
         </row>
         <row r="232">
           <cell r="A232">
-            <v>402040</v>
+            <v>402020</v>
           </cell>
           <cell r="B232" t="str">
-            <v>トラストチェイン+</v>
+            <v>イベイドコード+</v>
           </cell>
         </row>
         <row r="233">
           <cell r="A233">
-            <v>402050</v>
+            <v>402030</v>
           </cell>
           <cell r="B233" t="str">
-            <v>スペルバニシング+</v>
+            <v>ショックインパルス+</v>
           </cell>
         </row>
         <row r="234">
           <cell r="A234">
-            <v>402060</v>
+            <v>402040</v>
           </cell>
           <cell r="B234" t="str">
-            <v>アーテニーストライク+</v>
+            <v>トラストチェイン+</v>
           </cell>
         </row>
         <row r="235">
           <cell r="A235">
-            <v>402070</v>
+            <v>402050</v>
           </cell>
           <cell r="B235" t="str">
-            <v>コンセントレイト+</v>
+            <v>スペルバニシング+</v>
           </cell>
         </row>
         <row r="236">
           <cell r="A236">
-            <v>402080</v>
+            <v>402060</v>
           </cell>
           <cell r="B236" t="str">
-            <v>ディレイマジック+</v>
+            <v>アーテニーストライク+</v>
           </cell>
         </row>
         <row r="237">
           <cell r="A237">
-            <v>403010</v>
+            <v>402070</v>
           </cell>
           <cell r="B237" t="str">
-            <v>アイスブレイド+</v>
+            <v>コンセントレイト+</v>
           </cell>
         </row>
         <row r="238">
           <cell r="A238">
-            <v>403020</v>
+            <v>402080</v>
           </cell>
           <cell r="B238" t="str">
-            <v>カウンターオーラ+</v>
+            <v>ディレイマジック+</v>
           </cell>
         </row>
         <row r="239">
           <cell r="A239">
-            <v>403030</v>
+            <v>403010</v>
           </cell>
           <cell r="B239" t="str">
-            <v>ラインプロテクト+</v>
+            <v>アイスブレイド+</v>
           </cell>
         </row>
         <row r="240">
           <cell r="A240">
-            <v>403040</v>
+            <v>403020</v>
           </cell>
           <cell r="B240" t="str">
-            <v>エスコートソール+</v>
+            <v>カウンターオーラ+</v>
           </cell>
         </row>
         <row r="241">
           <cell r="A241">
-            <v>403050</v>
+            <v>403030</v>
           </cell>
           <cell r="B241" t="str">
-            <v>ディープフリーズ+</v>
+            <v>ラインプロテクト+</v>
           </cell>
         </row>
         <row r="242">
           <cell r="A242">
-            <v>403060</v>
+            <v>403040</v>
           </cell>
           <cell r="B242" t="str">
-            <v>バブルブロウ+</v>
+            <v>エスコートソール+</v>
           </cell>
         </row>
         <row r="243">
           <cell r="A243">
-            <v>403070</v>
+            <v>403050</v>
           </cell>
           <cell r="B243" t="str">
-            <v>アクアミラージュ+</v>
+            <v>ディープフリーズ+</v>
           </cell>
         </row>
         <row r="244">
           <cell r="A244">
-            <v>403080</v>
+            <v>403060</v>
           </cell>
           <cell r="B244" t="str">
-            <v>フロストシールド+</v>
+            <v>バブルブロウ+</v>
           </cell>
         </row>
         <row r="245">
           <cell r="A245">
-            <v>404010</v>
+            <v>403070</v>
           </cell>
           <cell r="B245" t="str">
-            <v>セイントレーザー+</v>
+            <v>アクアミラージュ+</v>
           </cell>
         </row>
         <row r="246">
           <cell r="A246">
-            <v>404020</v>
+            <v>403080</v>
           </cell>
           <cell r="B246" t="str">
-            <v>ペネトレイト+</v>
+            <v>フロストシールド+</v>
           </cell>
         </row>
         <row r="247">
           <cell r="A247">
-            <v>404030</v>
+            <v>404010</v>
           </cell>
           <cell r="B247" t="str">
-            <v>ヒーリング+</v>
+            <v>セイントレーザー+</v>
           </cell>
         </row>
         <row r="248">
           <cell r="A248">
-            <v>404040</v>
+            <v>404020</v>
           </cell>
           <cell r="B248" t="str">
-            <v>リザイアフォトン+</v>
+            <v>ペネトレイト+</v>
           </cell>
         </row>
         <row r="249">
           <cell r="A249">
-            <v>404050</v>
+            <v>404030</v>
           </cell>
           <cell r="B249" t="str">
-            <v>べネディクション+</v>
+            <v>ヒーリング+</v>
           </cell>
         </row>
         <row r="250">
           <cell r="A250">
-            <v>404060</v>
+            <v>404040</v>
           </cell>
           <cell r="B250" t="str">
-            <v>ホーリーグレイス+</v>
+            <v>リザイアフォトン+</v>
           </cell>
         </row>
         <row r="251">
           <cell r="A251">
-            <v>404070</v>
+            <v>404050</v>
           </cell>
           <cell r="B251" t="str">
-            <v>キュアエール+</v>
+            <v>べネディクション+</v>
           </cell>
         </row>
         <row r="252">
           <cell r="A252">
-            <v>404080</v>
+            <v>404060</v>
           </cell>
           <cell r="B252" t="str">
-            <v>ラインバリア+</v>
+            <v>ホーリーグレイス+</v>
           </cell>
         </row>
         <row r="253">
           <cell r="A253">
-            <v>405010</v>
+            <v>404070</v>
           </cell>
           <cell r="B253" t="str">
-            <v>ダークプリズン+</v>
+            <v>キュアエール+</v>
           </cell>
         </row>
         <row r="254">
           <cell r="A254">
-            <v>405020</v>
+            <v>404080</v>
           </cell>
           <cell r="B254" t="str">
-            <v>ユーサネイジア+</v>
+            <v>ラインバリア+</v>
           </cell>
         </row>
         <row r="255">
           <cell r="A255">
-            <v>405030</v>
+            <v>405010</v>
           </cell>
           <cell r="B255" t="str">
-            <v>ドレインヒール+</v>
+            <v>ダークプリズン+</v>
           </cell>
         </row>
         <row r="256">
           <cell r="A256">
-            <v>405040</v>
+            <v>405020</v>
           </cell>
           <cell r="B256" t="str">
-            <v>アビサルデスペア+</v>
+            <v>ユーサネイジア+</v>
           </cell>
         </row>
         <row r="257">
           <cell r="A257">
-            <v>405050</v>
+            <v>405030</v>
           </cell>
           <cell r="B257" t="str">
-            <v>ディプラヴィティ+</v>
+            <v>ドレインヒール+</v>
           </cell>
         </row>
         <row r="258">
           <cell r="A258">
-            <v>405060</v>
+            <v>405040</v>
           </cell>
           <cell r="B258" t="str">
-            <v>ダークネス+</v>
+            <v>アビサルデスペア+</v>
           </cell>
         </row>
         <row r="259">
           <cell r="A259">
-            <v>405070</v>
+            <v>405050</v>
           </cell>
           <cell r="B259" t="str">
-            <v>シェイディークラウド+</v>
+            <v>ディプラヴィティ+</v>
           </cell>
         </row>
         <row r="260">
           <cell r="A260">
-            <v>405080</v>
+            <v>405060</v>
           </cell>
           <cell r="B260" t="str">
-            <v>ポイズンブロウ+</v>
+            <v>ダークネス+</v>
           </cell>
         </row>
         <row r="261">
           <cell r="A261">
-            <v>411010</v>
+            <v>405070</v>
           </cell>
           <cell r="B261" t="str">
-            <v>ウルフソウル+</v>
+            <v>シェイディークラウド+</v>
           </cell>
         </row>
         <row r="262">
           <cell r="A262">
-            <v>411020</v>
+            <v>405080</v>
           </cell>
           <cell r="B262" t="str">
-            <v>プリディカメント+</v>
+            <v>ポイズンブロウ+</v>
           </cell>
         </row>
         <row r="263">
           <cell r="A263">
-            <v>411030</v>
+            <v>411010</v>
           </cell>
           <cell r="B263" t="str">
-            <v>アサルトシフト+</v>
+            <v>ウルフソウル+</v>
           </cell>
         </row>
         <row r="264">
           <cell r="A264">
-            <v>411040</v>
+            <v>411020</v>
           </cell>
           <cell r="B264" t="str">
-            <v>アクティブギフト+</v>
+            <v>プリディカメント+</v>
           </cell>
         </row>
         <row r="265">
           <cell r="A265">
-            <v>411050</v>
+            <v>411030</v>
           </cell>
           <cell r="B265" t="str">
-            <v>イグナイテッド+</v>
+            <v>アサルトシフト+</v>
           </cell>
         </row>
         <row r="266">
           <cell r="A266">
-            <v>411060</v>
+            <v>411040</v>
           </cell>
           <cell r="B266" t="str">
-            <v>ライジングファイア+</v>
+            <v>アクティブギフト+</v>
           </cell>
         </row>
         <row r="267">
           <cell r="A267">
-            <v>411070</v>
+            <v>411050</v>
           </cell>
           <cell r="B267" t="str">
-            <v>ルージュバック+</v>
+            <v>イグナイテッド+</v>
           </cell>
         </row>
         <row r="268">
           <cell r="A268">
-            <v>411080</v>
+            <v>411060</v>
           </cell>
           <cell r="B268" t="str">
-            <v>パワーエール+</v>
+            <v>ライジングファイア+</v>
           </cell>
         </row>
         <row r="269">
           <cell r="A269">
-            <v>411090</v>
+            <v>411070</v>
           </cell>
           <cell r="B269" t="str">
-            <v>スレイプニル+</v>
+            <v>ルージュバック+</v>
           </cell>
         </row>
         <row r="270">
           <cell r="A270">
-            <v>412010</v>
+            <v>411080</v>
           </cell>
           <cell r="B270" t="str">
-            <v>エクステンション+</v>
+            <v>パワーエール+</v>
           </cell>
         </row>
         <row r="271">
           <cell r="A271">
-            <v>412020</v>
+            <v>411090</v>
           </cell>
           <cell r="B271" t="str">
-            <v>ヘブンリーラック+</v>
+            <v>スレイプニル+</v>
           </cell>
         </row>
         <row r="272">
           <cell r="A272">
-            <v>412030</v>
+            <v>412010</v>
           </cell>
           <cell r="B272" t="str">
-            <v>スウィフトカレント+</v>
+            <v>エクステンション+</v>
           </cell>
         </row>
         <row r="273">
           <cell r="A273">
-            <v>412040</v>
+            <v>412020</v>
           </cell>
           <cell r="B273" t="str">
-            <v>イヴェイドオール+</v>
+            <v>ヘブンリーラック+</v>
           </cell>
         </row>
         <row r="274">
           <cell r="A274">
-            <v>412050</v>
+            <v>412030</v>
           </cell>
           <cell r="B274" t="str">
-            <v>クイックムーブ+</v>
+            <v>スウィフトカレント+</v>
           </cell>
         </row>
         <row r="275">
           <cell r="A275">
-            <v>412060</v>
+            <v>412040</v>
           </cell>
           <cell r="B275" t="str">
-            <v>チェイスマジック+</v>
+            <v>イヴェイドオール+</v>
           </cell>
         </row>
         <row r="276">
           <cell r="A276">
-            <v>412070</v>
+            <v>412050</v>
           </cell>
           <cell r="B276" t="str">
-            <v>ソーサリーコネクト+</v>
+            <v>クイックムーブ+</v>
           </cell>
         </row>
         <row r="277">
           <cell r="A277">
-            <v>412080</v>
+            <v>412060</v>
           </cell>
           <cell r="B277" t="str">
-            <v>ウィンドライズ+</v>
+            <v>チェイスマジック+</v>
           </cell>
         </row>
         <row r="278">
           <cell r="A278">
-            <v>412090</v>
+            <v>412070</v>
           </cell>
           <cell r="B278" t="str">
-            <v>アウトオブオーダー+</v>
+            <v>ソーサリーコネクト+</v>
           </cell>
         </row>
         <row r="279">
           <cell r="A279">
-            <v>413010</v>
+            <v>412080</v>
           </cell>
           <cell r="B279" t="str">
-            <v>アーマーコード+</v>
+            <v>ウィンドライズ+</v>
           </cell>
         </row>
         <row r="280">
           <cell r="A280">
-            <v>413020</v>
+            <v>412090</v>
           </cell>
           <cell r="B280" t="str">
-            <v>クイックバリア+</v>
+            <v>アウトオブオーダー+</v>
           </cell>
         </row>
         <row r="281">
           <cell r="A281">
-            <v>413030</v>
+            <v>413010</v>
           </cell>
           <cell r="B281" t="str">
-            <v>クイックキュア+</v>
+            <v>アーマーコード+</v>
           </cell>
         </row>
         <row r="282">
           <cell r="A282">
-            <v>413040</v>
+            <v>413020</v>
           </cell>
           <cell r="B282" t="str">
-            <v>セルフシールド+</v>
+            <v>クイックバリア+</v>
           </cell>
         </row>
         <row r="283">
           <cell r="A283">
-            <v>413050</v>
+            <v>413030</v>
           </cell>
           <cell r="B283" t="str">
-            <v>パッシブジャミング+</v>
+            <v>クイックキュア+</v>
           </cell>
         </row>
         <row r="284">
           <cell r="A284">
-            <v>413060</v>
+            <v>413040</v>
           </cell>
           <cell r="B284" t="str">
-            <v>サプライカバー+</v>
+            <v>セルフシールド+</v>
           </cell>
         </row>
         <row r="285">
           <cell r="A285">
-            <v>413070</v>
+            <v>413050</v>
           </cell>
           <cell r="B285" t="str">
-            <v>アシッドラッシュ+</v>
+            <v>パッシブジャミング+</v>
           </cell>
         </row>
         <row r="286">
           <cell r="A286">
-            <v>413080</v>
+            <v>413060</v>
           </cell>
           <cell r="B286" t="str">
-            <v>ライフスティール+</v>
+            <v>サプライカバー+</v>
           </cell>
         </row>
         <row r="287">
           <cell r="A287">
-            <v>413090</v>
+            <v>413070</v>
           </cell>
           <cell r="B287" t="str">
-            <v>アイスセイバー+</v>
+            <v>アシッドラッシュ+</v>
           </cell>
         </row>
         <row r="288">
           <cell r="A288">
-            <v>414010</v>
+            <v>413080</v>
           </cell>
           <cell r="B288" t="str">
-            <v>ディバインシールド+</v>
+            <v>ライフスティール+</v>
           </cell>
         </row>
         <row r="289">
           <cell r="A289">
-            <v>414020</v>
+            <v>413090</v>
           </cell>
           <cell r="B289" t="str">
-            <v>ライフディバイド+</v>
+            <v>アイスセイバー+</v>
           </cell>
         </row>
         <row r="290">
           <cell r="A290">
-            <v>414030</v>
+            <v>414010</v>
           </cell>
           <cell r="B290" t="str">
-            <v>エイミングスコープ+</v>
+            <v>ディバインシールド+</v>
           </cell>
         </row>
         <row r="291">
           <cell r="A291">
-            <v>414040</v>
+            <v>414020</v>
           </cell>
           <cell r="B291" t="str">
-            <v>リジェネレーション+</v>
+            <v>ライフディバイド+</v>
           </cell>
         </row>
         <row r="292">
           <cell r="A292">
-            <v>414050</v>
+            <v>414030</v>
           </cell>
           <cell r="B292" t="str">
-            <v>ホープフルアイリス+</v>
+            <v>エイミングスコープ+</v>
           </cell>
         </row>
         <row r="293">
           <cell r="A293">
-            <v>414060</v>
+            <v>414040</v>
           </cell>
           <cell r="B293" t="str">
-            <v>パッシブサプライ+</v>
+            <v>リジェネレーション+</v>
           </cell>
         </row>
         <row r="294">
           <cell r="A294">
-            <v>414070</v>
+            <v>414050</v>
           </cell>
           <cell r="B294" t="str">
-            <v>ホーミングクルセイド+</v>
+            <v>ホープフルアイリス+</v>
           </cell>
         </row>
         <row r="295">
           <cell r="A295">
-            <v>414080</v>
+            <v>414060</v>
           </cell>
           <cell r="B295" t="str">
-            <v>クイックヒール+</v>
+            <v>パッシブサプライ+</v>
           </cell>
         </row>
         <row r="296">
           <cell r="A296">
-            <v>414090</v>
+            <v>414070</v>
           </cell>
           <cell r="B296" t="str">
-            <v>リレイズ+</v>
+            <v>ホーミングクルセイド+</v>
           </cell>
         </row>
         <row r="297">
           <cell r="A297">
-            <v>415010</v>
+            <v>414080</v>
           </cell>
           <cell r="B297" t="str">
-            <v>イーグルアイ+</v>
+            <v>クイックヒール+</v>
           </cell>
         </row>
         <row r="298">
           <cell r="A298">
-            <v>415020</v>
+            <v>414090</v>
           </cell>
           <cell r="B298" t="str">
-            <v>ネヴァーエンド+</v>
+            <v>リレイズ+</v>
           </cell>
         </row>
         <row r="299">
           <cell r="A299">
-            <v>415030</v>
+            <v>415010</v>
           </cell>
           <cell r="B299" t="str">
-            <v>グレイブアクト+</v>
+            <v>イーグルアイ+</v>
           </cell>
         </row>
         <row r="300">
           <cell r="A300">
-            <v>415040</v>
+            <v>415020</v>
           </cell>
           <cell r="B300" t="str">
-            <v>スカルグラッジ+</v>
+            <v>ネヴァーエンド+</v>
           </cell>
         </row>
         <row r="301">
           <cell r="A301">
-            <v>415050</v>
+            <v>415030</v>
           </cell>
           <cell r="B301" t="str">
-            <v>ネガティブドレイン+</v>
+            <v>グレイブアクト+</v>
           </cell>
         </row>
         <row r="302">
           <cell r="A302">
-            <v>415060</v>
+            <v>415040</v>
           </cell>
           <cell r="B302" t="str">
-            <v>アンデッドペイン+</v>
+            <v>スカルグラッジ+</v>
           </cell>
         </row>
         <row r="303">
           <cell r="A303">
-            <v>415070</v>
+            <v>415050</v>
           </cell>
           <cell r="B303" t="str">
-            <v>ジャックポッド+</v>
+            <v>ネガティブドレイン+</v>
           </cell>
         </row>
         <row r="304">
           <cell r="A304">
-            <v>415080</v>
+            <v>415060</v>
           </cell>
           <cell r="B304" t="str">
-            <v>ヒールハント+</v>
+            <v>アンデッドペイン+</v>
           </cell>
         </row>
         <row r="305">
           <cell r="A305">
-            <v>415090</v>
+            <v>415070</v>
           </cell>
           <cell r="B305" t="str">
-            <v>クイックカース+</v>
+            <v>ジャックポッド+</v>
           </cell>
         </row>
         <row r="306">
           <cell r="A306">
-            <v>501010</v>
+            <v>415080</v>
           </cell>
           <cell r="B306" t="str">
-            <v>ATK+2</v>
+            <v>ヒールハント+</v>
           </cell>
         </row>
         <row r="307">
           <cell r="A307">
-            <v>501020</v>
+            <v>415090</v>
           </cell>
           <cell r="B307" t="str">
-            <v>火傷耐性+25%</v>
+            <v>クイックカース+</v>
           </cell>
         </row>
         <row r="308">
           <cell r="A308">
-            <v>501030</v>
+            <v>501010</v>
           </cell>
           <cell r="B308" t="str">
             <v>ATK+2</v>
@@ -3584,79 +3584,79 @@
         </row>
         <row r="309">
           <cell r="A309">
-            <v>501040</v>
+            <v>501020</v>
           </cell>
           <cell r="B309" t="str">
-            <v>ATK+4</v>
+            <v>火傷耐性+25%</v>
           </cell>
         </row>
         <row r="310">
           <cell r="A310">
-            <v>501041</v>
+            <v>501030</v>
           </cell>
           <cell r="B310" t="str">
-            <v>会心率+10%</v>
+            <v>ATK+2</v>
           </cell>
         </row>
         <row r="311">
           <cell r="A311">
-            <v>502010</v>
+            <v>501040</v>
           </cell>
           <cell r="B311" t="str">
-            <v>回避率+5%</v>
+            <v>ATK+4</v>
           </cell>
         </row>
         <row r="312">
           <cell r="A312">
-            <v>502020</v>
+            <v>501041</v>
           </cell>
           <cell r="B312" t="str">
-            <v>SPD+1</v>
+            <v>会心率+10%</v>
           </cell>
         </row>
         <row r="313">
           <cell r="A313">
-            <v>502030</v>
+            <v>502010</v>
           </cell>
           <cell r="B313" t="str">
-            <v>SPD+1</v>
+            <v>回避率+5%</v>
           </cell>
         </row>
         <row r="314">
           <cell r="A314">
-            <v>502040</v>
+            <v>502020</v>
           </cell>
           <cell r="B314" t="str">
-            <v>SPD+2</v>
+            <v>SPD+1</v>
           </cell>
         </row>
         <row r="315">
           <cell r="A315">
-            <v>502041</v>
+            <v>502030</v>
           </cell>
           <cell r="B315" t="str">
-            <v>回避率+15%</v>
+            <v>SPD+1</v>
           </cell>
         </row>
         <row r="316">
           <cell r="A316">
-            <v>503010</v>
+            <v>502040</v>
           </cell>
           <cell r="B316" t="str">
-            <v>DEF+2</v>
+            <v>SPD+2</v>
           </cell>
         </row>
         <row r="317">
           <cell r="A317">
-            <v>503020</v>
+            <v>502041</v>
           </cell>
           <cell r="B317" t="str">
-            <v>DEF+2</v>
+            <v>回避率+15%</v>
           </cell>
         </row>
         <row r="318">
           <cell r="A318">
-            <v>503030</v>
+            <v>503010</v>
           </cell>
           <cell r="B318" t="str">
             <v>DEF+2</v>
@@ -3664,129 +3664,145 @@
         </row>
         <row r="319">
           <cell r="A319">
-            <v>503040</v>
+            <v>503020</v>
           </cell>
           <cell r="B319" t="str">
-            <v>DEF+4</v>
+            <v>DEF+2</v>
           </cell>
         </row>
         <row r="320">
           <cell r="A320">
-            <v>503041</v>
+            <v>503030</v>
           </cell>
           <cell r="B320" t="str">
-            <v>HP回復効果+20%</v>
+            <v>DEF+2</v>
           </cell>
         </row>
         <row r="321">
           <cell r="A321">
-            <v>504010</v>
+            <v>503040</v>
           </cell>
           <cell r="B321" t="str">
-            <v>最大HP+4</v>
+            <v>DEF+4</v>
           </cell>
         </row>
         <row r="322">
           <cell r="A322">
-            <v>504020</v>
+            <v>503041</v>
           </cell>
           <cell r="B322" t="str">
-            <v>最大HP+4</v>
+            <v>HP回復効果+20%</v>
           </cell>
         </row>
         <row r="323">
           <cell r="A323">
-            <v>504030</v>
+            <v>504010</v>
           </cell>
           <cell r="B323" t="str">
-            <v>命中率+5%</v>
+            <v>最大HP+4</v>
           </cell>
         </row>
         <row r="324">
           <cell r="A324">
-            <v>504040</v>
+            <v>504020</v>
           </cell>
           <cell r="B324" t="str">
-            <v>最大HP+10</v>
+            <v>最大HP+4</v>
           </cell>
         </row>
         <row r="325">
           <cell r="A325">
-            <v>505010</v>
+            <v>504030</v>
           </cell>
           <cell r="B325" t="str">
-            <v>会心率+5%</v>
+            <v>命中率+5%</v>
           </cell>
         </row>
         <row r="326">
           <cell r="A326">
-            <v>505020</v>
+            <v>504040</v>
           </cell>
           <cell r="B326" t="str">
-            <v>SPD+1</v>
+            <v>最大HP+10</v>
           </cell>
         </row>
         <row r="327">
           <cell r="A327">
-            <v>505030</v>
+            <v>505010</v>
           </cell>
           <cell r="B327" t="str">
-            <v>回避率+5%</v>
+            <v>会心率+5%</v>
           </cell>
         </row>
         <row r="328">
           <cell r="A328">
-            <v>505040</v>
+            <v>505020</v>
           </cell>
           <cell r="B328" t="str">
-            <v>暗闇無効</v>
+            <v>SPD+1</v>
           </cell>
         </row>
         <row r="329">
           <cell r="A329">
-            <v>506010</v>
+            <v>505030</v>
           </cell>
           <cell r="B329" t="str">
-            <v>最大HP+3</v>
+            <v>回避率+5%</v>
           </cell>
         </row>
         <row r="330">
           <cell r="A330">
-            <v>506011</v>
+            <v>505040</v>
           </cell>
           <cell r="B330" t="str">
-            <v>ATK+1</v>
+            <v>暗闇無効</v>
           </cell>
         </row>
         <row r="331">
           <cell r="A331">
-            <v>506012</v>
+            <v>506010</v>
           </cell>
           <cell r="B331" t="str">
-            <v>DEF+1</v>
+            <v>最大HP+3</v>
           </cell>
         </row>
         <row r="332">
           <cell r="A332">
-            <v>506013</v>
+            <v>506011</v>
           </cell>
           <cell r="B332" t="str">
-            <v>SPD+1</v>
+            <v>ATK+1</v>
           </cell>
         </row>
         <row r="333">
           <cell r="A333">
-            <v>507010</v>
+            <v>506012</v>
           </cell>
           <cell r="B333" t="str">
-            <v>獲得Exp+30%</v>
+            <v>DEF+1</v>
           </cell>
         </row>
         <row r="334">
           <cell r="A334">
+            <v>506013</v>
+          </cell>
+          <cell r="B334" t="str">
+            <v>SPD+1</v>
+          </cell>
+        </row>
+        <row r="335">
+          <cell r="A335">
+            <v>507010</v>
+          </cell>
+          <cell r="B335" t="str">
+            <v>獲得Exp+30%</v>
+          </cell>
+        </row>
+        <row r="336">
+          <cell r="A336">
             <v>507020</v>
           </cell>
-          <cell r="B334" t="str">
+          <cell r="B336" t="str">
             <v>ATK⇔DEF交換</v>
           </cell>
         </row>
@@ -6218,7 +6234,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G216"/>
+  <dimension ref="A1:G214"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="16.7272727272727" customWidth="1"/>
@@ -8772,11 +8788,11 @@
         <v>201</v>
       </c>
       <c r="B107">
-        <v>5010</v>
+        <v>4010</v>
       </c>
       <c r="C107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B107,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>セイントレーザー</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -8793,23 +8809,23 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="B108">
-        <v>5020</v>
+        <v>1010</v>
       </c>
       <c r="C108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B108,[1]TextData!A:A))</f>
-        <v>ユーサネイジア</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D108">
         <v>1</v>
       </c>
       <c r="E108">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F108">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G108">
         <v>0</v>
@@ -8817,14 +8833,14 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="B109">
-        <v>3070</v>
+        <v>1060</v>
       </c>
       <c r="C109" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B109,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>イクスティンクション</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -8833,7 +8849,7 @@
         <v>150</v>
       </c>
       <c r="F109">
-        <v>9110</v>
+        <v>5061</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -8844,20 +8860,20 @@
         <v>1001</v>
       </c>
       <c r="B110">
-        <v>1010</v>
+        <v>100110</v>
       </c>
       <c r="C110" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B110,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>ソーイングアームド</v>
       </c>
       <c r="D110">
         <v>1</v>
       </c>
       <c r="E110">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F110">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -8868,20 +8884,20 @@
         <v>1001</v>
       </c>
       <c r="B111">
-        <v>1060</v>
+        <v>100120</v>
       </c>
       <c r="C111" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B111,[1]TextData!A:A))</f>
-        <v>イクスティンクション</v>
+        <v>エターナルロンド</v>
       </c>
       <c r="D111">
         <v>1</v>
       </c>
       <c r="E111">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F111">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -8892,11 +8908,11 @@
         <v>1001</v>
       </c>
       <c r="B112">
-        <v>100110</v>
+        <v>11060</v>
       </c>
       <c r="C112" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B112,[1]TextData!A:A))</f>
-        <v>ソーイングアームド</v>
+        <v>ライジングファイア</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -8916,17 +8932,17 @@
         <v>1001</v>
       </c>
       <c r="B113">
-        <v>100120</v>
+        <v>14010</v>
       </c>
       <c r="C113" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B113,[1]TextData!A:A))</f>
-        <v>エターナルロンド</v>
+        <v>ディバインシールド</v>
       </c>
       <c r="D113">
         <v>1</v>
       </c>
       <c r="E113">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -8940,11 +8956,11 @@
         <v>1001</v>
       </c>
       <c r="B114">
-        <v>11060</v>
+        <v>12010</v>
       </c>
       <c r="C114" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B114,[1]TextData!A:A))</f>
-        <v>ライジングファイア</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -8964,11 +8980,11 @@
         <v>1001</v>
       </c>
       <c r="B115">
-        <v>14010</v>
+        <v>12060</v>
       </c>
       <c r="C115" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B115,[1]TextData!A:A))</f>
-        <v>ディバインシールド</v>
+        <v>チェイスマジック</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -8985,23 +9001,23 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B116">
-        <v>12010</v>
+        <v>2010</v>
       </c>
       <c r="C116" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B116,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D116">
         <v>1</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F116">
-        <v>0</v>
+        <v>5060</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -9009,20 +9025,20 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B117">
-        <v>12060</v>
+        <v>2070</v>
       </c>
       <c r="C117" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B117,[1]TextData!A:A))</f>
-        <v>チェイスマジック</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D117">
         <v>1</v>
       </c>
       <c r="E117">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F117">
         <v>0</v>
@@ -9036,20 +9052,20 @@
         <v>1002</v>
       </c>
       <c r="B118">
-        <v>2010</v>
+        <v>100210</v>
       </c>
       <c r="C118" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B118,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>アブソリュートパリィ</v>
       </c>
       <c r="D118">
         <v>1</v>
       </c>
       <c r="E118">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F118">
-        <v>5060</v>
+        <v>0</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -9060,23 +9076,23 @@
         <v>1002</v>
       </c>
       <c r="B119">
-        <v>2070</v>
+        <v>100220</v>
       </c>
       <c r="C119" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B119,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>レヴェリー</v>
       </c>
       <c r="D119">
         <v>1</v>
       </c>
       <c r="E119">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>14211</v>
       </c>
       <c r="G119">
-        <v>0</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -9084,11 +9100,11 @@
         <v>1002</v>
       </c>
       <c r="B120">
-        <v>100210</v>
+        <v>402070</v>
       </c>
       <c r="C120" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B120,[1]TextData!A:A))</f>
-        <v>アブソリュートパリィ</v>
+        <v>コンセントレイト+</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -9108,23 +9124,23 @@
         <v>1002</v>
       </c>
       <c r="B121">
-        <v>100220</v>
+        <v>12080</v>
       </c>
       <c r="C121" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B121,[1]TextData!A:A))</f>
-        <v>レヴェリー</v>
+        <v>ウィンドライズ</v>
       </c>
       <c r="D121">
         <v>1</v>
       </c>
       <c r="E121">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F121">
-        <v>14211</v>
+        <v>0</v>
       </c>
       <c r="G121">
-        <v>5060</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -9132,11 +9148,11 @@
         <v>1002</v>
       </c>
       <c r="B122">
-        <v>402070</v>
+        <v>12040</v>
       </c>
       <c r="C122" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B122,[1]TextData!A:A))</f>
-        <v>コンセントレイト+</v>
+        <v>イヴェイドオール</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -9156,11 +9172,11 @@
         <v>1002</v>
       </c>
       <c r="B123">
-        <v>12080</v>
+        <v>12050</v>
       </c>
       <c r="C123" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B123,[1]TextData!A:A))</f>
-        <v>ウィンドライズ</v>
+        <v>クイックムーブ</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -9180,11 +9196,11 @@
         <v>1002</v>
       </c>
       <c r="B124">
-        <v>12040</v>
+        <v>12010</v>
       </c>
       <c r="C124" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B124,[1]TextData!A:A))</f>
-        <v>イヴェイドオール</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -9201,20 +9217,20 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B125">
-        <v>12050</v>
+        <v>3010</v>
       </c>
       <c r="C125" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B125,[1]TextData!A:A))</f>
-        <v>クイックムーブ</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D125">
         <v>1</v>
       </c>
       <c r="E125">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F125">
         <v>0</v>
@@ -9225,23 +9241,23 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B126">
-        <v>12010</v>
+        <v>3020</v>
       </c>
       <c r="C126" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B126,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>カウンターオーラ</v>
       </c>
       <c r="D126">
         <v>1</v>
       </c>
       <c r="E126">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F126">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G126">
         <v>0</v>
@@ -9252,17 +9268,17 @@
         <v>1003</v>
       </c>
       <c r="B127">
-        <v>3010</v>
+        <v>100310</v>
       </c>
       <c r="C127" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B127,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>セイクリッドバリア</v>
       </c>
       <c r="D127">
         <v>1</v>
       </c>
       <c r="E127">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F127">
         <v>0</v>
@@ -9276,20 +9292,20 @@
         <v>1003</v>
       </c>
       <c r="B128">
-        <v>3020</v>
+        <v>100320</v>
       </c>
       <c r="C128" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B128,[1]TextData!A:A))</f>
-        <v>カウンターオーラ</v>
+        <v>リベンジニードル</v>
       </c>
       <c r="D128">
         <v>1</v>
       </c>
       <c r="E128">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F128">
-        <v>1023</v>
+        <v>14214</v>
       </c>
       <c r="G128">
         <v>0</v>
@@ -9300,11 +9316,11 @@
         <v>1003</v>
       </c>
       <c r="B129">
-        <v>100310</v>
+        <v>403020</v>
       </c>
       <c r="C129" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B129,[1]TextData!A:A))</f>
-        <v>セイクリッドバリア</v>
+        <v>カウンターオーラ+</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -9324,20 +9340,20 @@
         <v>1003</v>
       </c>
       <c r="B130">
-        <v>100320</v>
+        <v>403010</v>
       </c>
       <c r="C130" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B130,[1]TextData!A:A))</f>
-        <v>リベンジニードル</v>
+        <v>アイスブレイド+</v>
       </c>
       <c r="D130">
         <v>1</v>
       </c>
       <c r="E130">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F130">
-        <v>14214</v>
+        <v>0</v>
       </c>
       <c r="G130">
         <v>0</v>
@@ -9348,11 +9364,11 @@
         <v>1003</v>
       </c>
       <c r="B131">
-        <v>403020</v>
+        <v>13020</v>
       </c>
       <c r="C131" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B131,[1]TextData!A:A))</f>
-        <v>カウンターオーラ+</v>
+        <v>クイックバリア</v>
       </c>
       <c r="D131">
         <v>1</v>
@@ -9372,11 +9388,11 @@
         <v>1003</v>
       </c>
       <c r="B132">
-        <v>403010</v>
+        <v>13080</v>
       </c>
       <c r="C132" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B132,[1]TextData!A:A))</f>
-        <v>アイスブレイド+</v>
+        <v>ライフスティール</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -9396,11 +9412,11 @@
         <v>1003</v>
       </c>
       <c r="B133">
-        <v>13020</v>
+        <v>14050</v>
       </c>
       <c r="C133" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B133,[1]TextData!A:A))</f>
-        <v>クイックバリア</v>
+        <v>ホープフルアイリス</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -9417,20 +9433,20 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B134">
-        <v>13080</v>
+        <v>4010</v>
       </c>
       <c r="C134" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B134,[1]TextData!A:A))</f>
-        <v>ライフスティール</v>
+        <v>セイントレーザー</v>
       </c>
       <c r="D134">
         <v>1</v>
       </c>
       <c r="E134">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -9441,23 +9457,23 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B135">
-        <v>14050</v>
+        <v>4030</v>
       </c>
       <c r="C135" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B135,[1]TextData!A:A))</f>
-        <v>ホープフルアイリス</v>
+        <v>ヒーリング</v>
       </c>
       <c r="D135">
         <v>1</v>
       </c>
       <c r="E135">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F135">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="G135">
         <v>0</v>
@@ -9468,17 +9484,17 @@
         <v>1004</v>
       </c>
       <c r="B136">
-        <v>4010</v>
+        <v>100410</v>
       </c>
       <c r="C136" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B136,[1]TextData!A:A))</f>
-        <v>セイントレーザー</v>
+        <v>アバンデンス</v>
       </c>
       <c r="D136">
         <v>1</v>
       </c>
       <c r="E136">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -9492,20 +9508,20 @@
         <v>1004</v>
       </c>
       <c r="B137">
-        <v>4030</v>
+        <v>100420</v>
       </c>
       <c r="C137" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B137,[1]TextData!A:A))</f>
-        <v>ヒーリング</v>
+        <v>ハーヴェスト</v>
       </c>
       <c r="D137">
         <v>1</v>
       </c>
       <c r="E137">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F137">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="G137">
         <v>0</v>
@@ -9516,11 +9532,11 @@
         <v>1004</v>
       </c>
       <c r="B138">
-        <v>100410</v>
+        <v>404030</v>
       </c>
       <c r="C138" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B138,[1]TextData!A:A))</f>
-        <v>アバンデンス</v>
+        <v>ヒーリング+</v>
       </c>
       <c r="D138">
         <v>1</v>
@@ -9540,17 +9556,17 @@
         <v>1004</v>
       </c>
       <c r="B139">
-        <v>100420</v>
+        <v>14080</v>
       </c>
       <c r="C139" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B139,[1]TextData!A:A))</f>
-        <v>ハーヴェスト</v>
+        <v>クイックヒール</v>
       </c>
       <c r="D139">
         <v>1</v>
       </c>
       <c r="E139">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -9564,11 +9580,11 @@
         <v>1004</v>
       </c>
       <c r="B140">
-        <v>404030</v>
+        <v>14010</v>
       </c>
       <c r="C140" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B140,[1]TextData!A:A))</f>
-        <v>ヒーリング+</v>
+        <v>ディバインシールド</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -9577,7 +9593,7 @@
         <v>0</v>
       </c>
       <c r="F140">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G140">
         <v>0</v>
@@ -9588,11 +9604,11 @@
         <v>1004</v>
       </c>
       <c r="B141">
-        <v>14080</v>
+        <v>14040</v>
       </c>
       <c r="C141" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B141,[1]TextData!A:A))</f>
-        <v>クイックヒール</v>
+        <v>リジェネレーション</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -9612,11 +9628,11 @@
         <v>1004</v>
       </c>
       <c r="B142">
-        <v>14010</v>
+        <v>14090</v>
       </c>
       <c r="C142" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B142,[1]TextData!A:A))</f>
-        <v>ディバインシールド</v>
+        <v>リレイズ</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -9625,7 +9641,7 @@
         <v>0</v>
       </c>
       <c r="F142">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G142">
         <v>0</v>
@@ -9633,20 +9649,20 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B143">
-        <v>14040</v>
+        <v>5010</v>
       </c>
       <c r="C143" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B143,[1]TextData!A:A))</f>
-        <v>リジェネレーション</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="D143">
         <v>1</v>
       </c>
       <c r="E143">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F143">
         <v>0</v>
@@ -9657,23 +9673,23 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B144">
-        <v>14090</v>
+        <v>5070</v>
       </c>
       <c r="C144" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B144,[1]TextData!A:A))</f>
-        <v>リレイズ</v>
+        <v>シェイディークラウド</v>
       </c>
       <c r="D144">
         <v>1</v>
       </c>
       <c r="E144">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F144">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G144">
         <v>0</v>
@@ -9684,17 +9700,17 @@
         <v>1005</v>
       </c>
       <c r="B145">
-        <v>5010</v>
+        <v>100510</v>
       </c>
       <c r="C145" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B145,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>カースドブレイク</v>
       </c>
       <c r="D145">
         <v>1</v>
       </c>
       <c r="E145">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F145">
         <v>0</v>
@@ -9708,20 +9724,20 @@
         <v>1005</v>
       </c>
       <c r="B146">
-        <v>5070</v>
+        <v>100520</v>
       </c>
       <c r="C146" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B146,[1]TextData!A:A))</f>
-        <v>シェイディークラウド</v>
+        <v>ムーンライトレイ</v>
       </c>
       <c r="D146">
         <v>1</v>
       </c>
       <c r="E146">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F146">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G146">
         <v>0</v>
@@ -9732,11 +9748,11 @@
         <v>1005</v>
       </c>
       <c r="B147">
-        <v>100510</v>
+        <v>15090</v>
       </c>
       <c r="C147" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B147,[1]TextData!A:A))</f>
-        <v>カースドブレイク</v>
+        <v>クイックカース</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -9756,17 +9772,17 @@
         <v>1005</v>
       </c>
       <c r="B148">
-        <v>100520</v>
+        <v>405070</v>
       </c>
       <c r="C148" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B148,[1]TextData!A:A))</f>
-        <v>ムーンライトレイ</v>
+        <v>シェイディークラウド+</v>
       </c>
       <c r="D148">
         <v>1</v>
       </c>
       <c r="E148">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F148">
         <v>0</v>
@@ -9780,11 +9796,11 @@
         <v>1005</v>
       </c>
       <c r="B149">
-        <v>15090</v>
+        <v>15080</v>
       </c>
       <c r="C149" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B149,[1]TextData!A:A))</f>
-        <v>クイックカース</v>
+        <v>ヒールハント</v>
       </c>
       <c r="D149">
         <v>1</v>
@@ -9804,11 +9820,11 @@
         <v>1005</v>
       </c>
       <c r="B150">
-        <v>405070</v>
+        <v>405010</v>
       </c>
       <c r="C150" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B150,[1]TextData!A:A))</f>
-        <v>シェイディークラウド+</v>
+        <v>ダークプリズン+</v>
       </c>
       <c r="D150">
         <v>1</v>
@@ -9828,11 +9844,11 @@
         <v>1005</v>
       </c>
       <c r="B151">
-        <v>15080</v>
+        <v>415090</v>
       </c>
       <c r="C151" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B151,[1]TextData!A:A))</f>
-        <v>ヒールハント</v>
+        <v>クイックカース+</v>
       </c>
       <c r="D151">
         <v>1</v>
@@ -9849,20 +9865,20 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B152">
-        <v>405010</v>
+        <v>1010</v>
       </c>
       <c r="C152" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B152,[1]TextData!A:A))</f>
-        <v>ダークプリズン+</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D152">
         <v>1</v>
       </c>
       <c r="E152">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F152">
         <v>0</v>
@@ -9873,26 +9889,26 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B153">
-        <v>415090</v>
+        <v>1030</v>
       </c>
       <c r="C153" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B153,[1]TextData!A:A))</f>
-        <v>クイックカース+</v>
+        <v>ヒートスタンプ</v>
       </c>
       <c r="D153">
         <v>1</v>
       </c>
       <c r="E153">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F153">
-        <v>0</v>
+        <v>9120</v>
       </c>
       <c r="G153">
-        <v>0</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -9900,20 +9916,20 @@
         <v>1006</v>
       </c>
       <c r="B154">
-        <v>1010</v>
+        <v>1070</v>
       </c>
       <c r="C154" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B154,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>バーニングソウル</v>
       </c>
       <c r="D154">
         <v>1</v>
       </c>
       <c r="E154">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F154">
-        <v>0</v>
+        <v>6322</v>
       </c>
       <c r="G154">
         <v>0</v>
@@ -9924,23 +9940,23 @@
         <v>1006</v>
       </c>
       <c r="B155">
-        <v>1030</v>
+        <v>100610</v>
       </c>
       <c r="C155" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B155,[1]TextData!A:A))</f>
-        <v>ヒートスタンプ</v>
+        <v>サンフレイム</v>
       </c>
       <c r="D155">
         <v>1</v>
       </c>
       <c r="E155">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F155">
-        <v>9120</v>
+        <v>0</v>
       </c>
       <c r="G155">
-        <v>1023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -9948,20 +9964,20 @@
         <v>1006</v>
       </c>
       <c r="B156">
-        <v>1070</v>
+        <v>100620</v>
       </c>
       <c r="C156" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B156,[1]TextData!A:A))</f>
-        <v>バーニングソウル</v>
+        <v>フレイムタン</v>
       </c>
       <c r="D156">
         <v>1</v>
       </c>
       <c r="E156">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F156">
-        <v>6322</v>
+        <v>0</v>
       </c>
       <c r="G156">
         <v>0</v>
@@ -9972,11 +9988,11 @@
         <v>1006</v>
       </c>
       <c r="B157">
-        <v>100610</v>
+        <v>11040</v>
       </c>
       <c r="C157" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B157,[1]TextData!A:A))</f>
-        <v>サンフレイム</v>
+        <v>アクティブギフト</v>
       </c>
       <c r="D157">
         <v>1</v>
@@ -9985,7 +10001,7 @@
         <v>0</v>
       </c>
       <c r="F157">
-        <v>0</v>
+        <v>5042</v>
       </c>
       <c r="G157">
         <v>0</v>
@@ -9996,17 +10012,17 @@
         <v>1006</v>
       </c>
       <c r="B158">
-        <v>100620</v>
+        <v>401030</v>
       </c>
       <c r="C158" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B158,[1]TextData!A:A))</f>
-        <v>フレイムタン</v>
+        <v>ヒートスタンプ+</v>
       </c>
       <c r="D158">
         <v>1</v>
       </c>
       <c r="E158">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -10020,11 +10036,11 @@
         <v>1006</v>
       </c>
       <c r="B159">
-        <v>11040</v>
+        <v>411040</v>
       </c>
       <c r="C159" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B159,[1]TextData!A:A))</f>
-        <v>アクティブギフト</v>
+        <v>アクティブギフト+</v>
       </c>
       <c r="D159">
         <v>1</v>
@@ -10033,7 +10049,7 @@
         <v>0</v>
       </c>
       <c r="F159">
-        <v>5042</v>
+        <v>0</v>
       </c>
       <c r="G159">
         <v>0</v>
@@ -10044,11 +10060,11 @@
         <v>1006</v>
       </c>
       <c r="B160">
-        <v>401030</v>
+        <v>13040</v>
       </c>
       <c r="C160" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B160,[1]TextData!A:A))</f>
-        <v>ヒートスタンプ+</v>
+        <v>セルフシールド</v>
       </c>
       <c r="D160">
         <v>1</v>
@@ -10065,20 +10081,20 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B161">
-        <v>411040</v>
+        <v>2010</v>
       </c>
       <c r="C161" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B161,[1]TextData!A:A))</f>
-        <v>アクティブギフト+</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D161">
         <v>1</v>
       </c>
       <c r="E161">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F161">
         <v>0</v>
@@ -10089,23 +10105,23 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B162">
-        <v>13040</v>
+        <v>2040</v>
       </c>
       <c r="C162" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B162,[1]TextData!A:A))</f>
-        <v>セルフシールド</v>
+        <v>トラストチェイン</v>
       </c>
       <c r="D162">
         <v>1</v>
       </c>
       <c r="E162">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F162">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G162">
         <v>0</v>
@@ -10116,17 +10132,17 @@
         <v>1007</v>
       </c>
       <c r="B163">
-        <v>2010</v>
+        <v>100710</v>
       </c>
       <c r="C163" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B163,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>ライズザフラッグ</v>
       </c>
       <c r="D163">
         <v>1</v>
       </c>
       <c r="E163">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F163">
         <v>0</v>
@@ -10140,20 +10156,20 @@
         <v>1007</v>
       </c>
       <c r="B164">
-        <v>2040</v>
+        <v>100720</v>
       </c>
       <c r="C164" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B164,[1]TextData!A:A))</f>
-        <v>トラストチェイン</v>
+        <v>オーバーリミット</v>
       </c>
       <c r="D164">
         <v>1</v>
       </c>
       <c r="E164">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F164">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G164">
         <v>0</v>
@@ -10164,11 +10180,11 @@
         <v>1007</v>
       </c>
       <c r="B165">
-        <v>100710</v>
+        <v>12090</v>
       </c>
       <c r="C165" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B165,[1]TextData!A:A))</f>
-        <v>ライズザフラッグ</v>
+        <v>アウトオブオーダー</v>
       </c>
       <c r="D165">
         <v>1</v>
@@ -10177,7 +10193,7 @@
         <v>0</v>
       </c>
       <c r="F165">
-        <v>0</v>
+        <v>5042</v>
       </c>
       <c r="G165">
         <v>0</v>
@@ -10188,17 +10204,17 @@
         <v>1007</v>
       </c>
       <c r="B166">
-        <v>100720</v>
+        <v>412090</v>
       </c>
       <c r="C166" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B166,[1]TextData!A:A))</f>
-        <v>オーバーリミット</v>
+        <v>アウトオブオーダー+</v>
       </c>
       <c r="D166">
         <v>1</v>
       </c>
       <c r="E166">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F166">
         <v>0</v>
@@ -10212,11 +10228,11 @@
         <v>1007</v>
       </c>
       <c r="B167">
-        <v>12090</v>
+        <v>12050</v>
       </c>
       <c r="C167" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B167,[1]TextData!A:A))</f>
-        <v>アウトオブオーダー</v>
+        <v>クイックムーブ</v>
       </c>
       <c r="D167">
         <v>1</v>
@@ -10225,7 +10241,7 @@
         <v>0</v>
       </c>
       <c r="F167">
-        <v>5042</v>
+        <v>0</v>
       </c>
       <c r="G167">
         <v>0</v>
@@ -10236,11 +10252,11 @@
         <v>1007</v>
       </c>
       <c r="B168">
-        <v>412090</v>
+        <v>12070</v>
       </c>
       <c r="C168" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B168,[1]TextData!A:A))</f>
-        <v>アウトオブオーダー+</v>
+        <v>ソーサリーコネクト</v>
       </c>
       <c r="D168">
         <v>1</v>
@@ -10260,11 +10276,11 @@
         <v>1007</v>
       </c>
       <c r="B169">
-        <v>12050</v>
+        <v>14030</v>
       </c>
       <c r="C169" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B169,[1]TextData!A:A))</f>
-        <v>クイックムーブ</v>
+        <v>エイミングスコープ</v>
       </c>
       <c r="D169">
         <v>1</v>
@@ -10281,20 +10297,20 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B170">
-        <v>12070</v>
+        <v>3010</v>
       </c>
       <c r="C170" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B170,[1]TextData!A:A))</f>
-        <v>ソーサリーコネクト</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D170">
         <v>1</v>
       </c>
       <c r="E170">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F170">
         <v>0</v>
@@ -10305,20 +10321,20 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B171">
-        <v>14030</v>
+        <v>3070</v>
       </c>
       <c r="C171" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B171,[1]TextData!A:A))</f>
-        <v>エイミングスコープ</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D171">
         <v>1</v>
       </c>
       <c r="E171">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F171">
         <v>0</v>
@@ -10332,17 +10348,17 @@
         <v>1008</v>
       </c>
       <c r="B172">
-        <v>3010</v>
+        <v>100810</v>
       </c>
       <c r="C172" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B172,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>テンパランス</v>
       </c>
       <c r="D172">
         <v>1</v>
       </c>
       <c r="E172">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F172">
         <v>0</v>
@@ -10356,17 +10372,17 @@
         <v>1008</v>
       </c>
       <c r="B173">
-        <v>3070</v>
+        <v>100820</v>
       </c>
       <c r="C173" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B173,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>シエルクルセイダー</v>
       </c>
       <c r="D173">
         <v>1</v>
       </c>
       <c r="E173">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F173">
         <v>0</v>
@@ -10380,11 +10396,11 @@
         <v>1008</v>
       </c>
       <c r="B174">
-        <v>100810</v>
+        <v>13060</v>
       </c>
       <c r="C174" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B174,[1]TextData!A:A))</f>
-        <v>テンパランス</v>
+        <v>サプライカバー</v>
       </c>
       <c r="D174">
         <v>1</v>
@@ -10393,7 +10409,7 @@
         <v>0</v>
       </c>
       <c r="F174">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G174">
         <v>0</v>
@@ -10404,17 +10420,17 @@
         <v>1008</v>
       </c>
       <c r="B175">
-        <v>100820</v>
+        <v>403070</v>
       </c>
       <c r="C175" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B175,[1]TextData!A:A))</f>
-        <v>シエルクルセイダー</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="D175">
         <v>1</v>
       </c>
       <c r="E175">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -10428,11 +10444,11 @@
         <v>1008</v>
       </c>
       <c r="B176">
-        <v>13060</v>
+        <v>13010</v>
       </c>
       <c r="C176" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B176,[1]TextData!A:A))</f>
-        <v>サプライカバー</v>
+        <v>アーマーコード</v>
       </c>
       <c r="D176">
         <v>1</v>
@@ -10441,7 +10457,7 @@
         <v>0</v>
       </c>
       <c r="F176">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G176">
         <v>0</v>
@@ -10452,11 +10468,11 @@
         <v>1008</v>
       </c>
       <c r="B177">
-        <v>403070</v>
+        <v>13020</v>
       </c>
       <c r="C177" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B177,[1]TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>クイックバリア</v>
       </c>
       <c r="D177">
         <v>1</v>
@@ -10476,11 +10492,11 @@
         <v>1008</v>
       </c>
       <c r="B178">
-        <v>13010</v>
+        <v>13040</v>
       </c>
       <c r="C178" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B178,[1]TextData!A:A))</f>
-        <v>アーマーコード</v>
+        <v>セルフシールド</v>
       </c>
       <c r="D178">
         <v>1</v>
@@ -10497,20 +10513,20 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B179">
-        <v>13020</v>
+        <v>1010</v>
       </c>
       <c r="C179" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B179,[1]TextData!A:A))</f>
-        <v>クイックバリア</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D179">
         <v>1</v>
       </c>
       <c r="E179">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F179">
         <v>0</v>
@@ -10521,23 +10537,23 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B180">
-        <v>13040</v>
+        <v>1050</v>
       </c>
       <c r="C180" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B180,[1]TextData!A:A))</f>
-        <v>セルフシールド</v>
+        <v>フレイムレイン</v>
       </c>
       <c r="D180">
         <v>1</v>
       </c>
       <c r="E180">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F180">
-        <v>0</v>
+        <v>1151</v>
       </c>
       <c r="G180">
         <v>0</v>
@@ -10548,17 +10564,17 @@
         <v>1009</v>
       </c>
       <c r="B181">
-        <v>1010</v>
+        <v>100910</v>
       </c>
       <c r="C181" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B181,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>バーニングカウンター</v>
       </c>
       <c r="D181">
         <v>1</v>
       </c>
       <c r="E181">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F181">
         <v>0</v>
@@ -10572,20 +10588,20 @@
         <v>1009</v>
       </c>
       <c r="B182">
-        <v>1050</v>
+        <v>100920</v>
       </c>
       <c r="C182" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B182,[1]TextData!A:A))</f>
-        <v>フレイムレイン</v>
+        <v>プロミネンス</v>
       </c>
       <c r="D182">
         <v>1</v>
       </c>
       <c r="E182">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F182">
-        <v>1151</v>
+        <v>0</v>
       </c>
       <c r="G182">
         <v>0</v>
@@ -10596,11 +10612,11 @@
         <v>1009</v>
       </c>
       <c r="B183">
-        <v>100910</v>
+        <v>11070</v>
       </c>
       <c r="C183" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B183,[1]TextData!A:A))</f>
-        <v>バーニングカウンター</v>
+        <v>ルージュバック</v>
       </c>
       <c r="D183">
         <v>1</v>
@@ -10620,17 +10636,17 @@
         <v>1009</v>
       </c>
       <c r="B184">
-        <v>100920</v>
+        <v>401050</v>
       </c>
       <c r="C184" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B184,[1]TextData!A:A))</f>
-        <v>プロミネンス</v>
+        <v>フレイムレイン+</v>
       </c>
       <c r="D184">
         <v>1</v>
       </c>
       <c r="E184">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F184">
         <v>0</v>
@@ -10644,11 +10660,11 @@
         <v>1009</v>
       </c>
       <c r="B185">
-        <v>11070</v>
+        <v>11030</v>
       </c>
       <c r="C185" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B185,[1]TextData!A:A))</f>
-        <v>ルージュバック</v>
+        <v>アサルトシフト</v>
       </c>
       <c r="D185">
         <v>1</v>
@@ -10668,11 +10684,11 @@
         <v>1009</v>
       </c>
       <c r="B186">
-        <v>401050</v>
+        <v>11020</v>
       </c>
       <c r="C186" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B186,[1]TextData!A:A))</f>
-        <v>フレイムレイン+</v>
+        <v>プリディカメント</v>
       </c>
       <c r="D186">
         <v>1</v>
@@ -10692,11 +10708,11 @@
         <v>1009</v>
       </c>
       <c r="B187">
-        <v>11030</v>
+        <v>15040</v>
       </c>
       <c r="C187" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B187,[1]TextData!A:A))</f>
-        <v>アサルトシフト</v>
+        <v>スカルグラッジ</v>
       </c>
       <c r="D187">
         <v>1</v>
@@ -10713,20 +10729,20 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B188">
-        <v>11020</v>
+        <v>2010</v>
       </c>
       <c r="C188" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B188,[1]TextData!A:A))</f>
-        <v>プリディカメント</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D188">
         <v>1</v>
       </c>
       <c r="E188">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F188">
         <v>0</v>
@@ -10737,23 +10753,23 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B189">
-        <v>15040</v>
+        <v>2030</v>
       </c>
       <c r="C189" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B189,[1]TextData!A:A))</f>
-        <v>スカルグラッジ</v>
+        <v>ショックインパルス</v>
       </c>
       <c r="D189">
         <v>1</v>
       </c>
       <c r="E189">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F189">
-        <v>0</v>
+        <v>14215</v>
       </c>
       <c r="G189">
         <v>0</v>
@@ -10764,17 +10780,17 @@
         <v>1010</v>
       </c>
       <c r="B190">
-        <v>2010</v>
+        <v>101010</v>
       </c>
       <c r="C190" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B190,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>エウロス</v>
       </c>
       <c r="D190">
         <v>1</v>
       </c>
       <c r="E190">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F190">
         <v>0</v>
@@ -10788,20 +10804,20 @@
         <v>1010</v>
       </c>
       <c r="B191">
-        <v>2030</v>
+        <v>101020</v>
       </c>
       <c r="C191" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B191,[1]TextData!A:A))</f>
-        <v>ショックインパルス</v>
+        <v>ボレアス</v>
       </c>
       <c r="D191">
         <v>1</v>
       </c>
       <c r="E191">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F191">
-        <v>14215</v>
+        <v>0</v>
       </c>
       <c r="G191">
         <v>0</v>
@@ -10812,11 +10828,11 @@
         <v>1010</v>
       </c>
       <c r="B192">
-        <v>101010</v>
+        <v>12010</v>
       </c>
       <c r="C192" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B192,[1]TextData!A:A))</f>
-        <v>エウロス</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D192">
         <v>1</v>
@@ -10836,17 +10852,17 @@
         <v>1010</v>
       </c>
       <c r="B193">
-        <v>101020</v>
+        <v>402030</v>
       </c>
       <c r="C193" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B193,[1]TextData!A:A))</f>
-        <v>ボレアス</v>
+        <v>ショックインパルス+</v>
       </c>
       <c r="D193">
         <v>1</v>
       </c>
       <c r="E193">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F193">
         <v>0</v>
@@ -10860,11 +10876,11 @@
         <v>1010</v>
       </c>
       <c r="B194">
-        <v>12010</v>
+        <v>12020</v>
       </c>
       <c r="C194" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B194,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>ヘブンリーラック</v>
       </c>
       <c r="D194">
         <v>1</v>
@@ -10884,11 +10900,11 @@
         <v>1010</v>
       </c>
       <c r="B195">
-        <v>402030</v>
+        <v>12030</v>
       </c>
       <c r="C195" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B195,[1]TextData!A:A))</f>
-        <v>ショックインパルス+</v>
+        <v>スウィフトカレント</v>
       </c>
       <c r="D195">
         <v>1</v>
@@ -10908,11 +10924,11 @@
         <v>1010</v>
       </c>
       <c r="B196">
-        <v>12020</v>
+        <v>15070</v>
       </c>
       <c r="C196" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B196,[1]TextData!A:A))</f>
-        <v>ヘブンリーラック</v>
+        <v>ジャックポッド</v>
       </c>
       <c r="D196">
         <v>1</v>
@@ -10929,20 +10945,20 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B197">
-        <v>12030</v>
+        <v>3010</v>
       </c>
       <c r="C197" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B197,[1]TextData!A:A))</f>
-        <v>スウィフトカレント</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D197">
         <v>1</v>
       </c>
       <c r="E197">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F197">
         <v>0</v>
@@ -10953,20 +10969,20 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B198">
-        <v>15070</v>
+        <v>3050</v>
       </c>
       <c r="C198" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B198,[1]TextData!A:A))</f>
-        <v>ジャックポッド</v>
+        <v>ディープフリーズ</v>
       </c>
       <c r="D198">
         <v>1</v>
       </c>
       <c r="E198">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F198">
         <v>0</v>
@@ -10980,17 +10996,17 @@
         <v>1011</v>
       </c>
       <c r="B199">
-        <v>3010</v>
+        <v>101110</v>
       </c>
       <c r="C199" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B199,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>アバランシュ</v>
       </c>
       <c r="D199">
         <v>1</v>
       </c>
       <c r="E199">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F199">
         <v>0</v>
@@ -11004,17 +11020,17 @@
         <v>1011</v>
       </c>
       <c r="B200">
-        <v>3050</v>
+        <v>101120</v>
       </c>
       <c r="C200" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B200,[1]TextData!A:A))</f>
-        <v>ディープフリーズ</v>
+        <v>ブリザードコフィン</v>
       </c>
       <c r="D200">
         <v>1</v>
       </c>
       <c r="E200">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F200">
         <v>0</v>
@@ -11028,11 +11044,11 @@
         <v>1011</v>
       </c>
       <c r="B201">
-        <v>101110</v>
+        <v>13090</v>
       </c>
       <c r="C201" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B201,[1]TextData!A:A))</f>
-        <v>アバランシュ</v>
+        <v>アイスセイバー</v>
       </c>
       <c r="D201">
         <v>1</v>
@@ -11052,17 +11068,17 @@
         <v>1011</v>
       </c>
       <c r="B202">
-        <v>101120</v>
+        <v>403050</v>
       </c>
       <c r="C202" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B202,[1]TextData!A:A))</f>
-        <v>ブリザードコフィン</v>
+        <v>ディープフリーズ+</v>
       </c>
       <c r="D202">
         <v>1</v>
       </c>
       <c r="E202">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F202">
         <v>0</v>
@@ -11076,11 +11092,11 @@
         <v>1011</v>
       </c>
       <c r="B203">
-        <v>13090</v>
+        <v>13050</v>
       </c>
       <c r="C203" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B203,[1]TextData!A:A))</f>
-        <v>アイスセイバー</v>
+        <v>パッシブジャミング</v>
       </c>
       <c r="D203">
         <v>1</v>
@@ -11100,11 +11116,11 @@
         <v>1011</v>
       </c>
       <c r="B204">
-        <v>403050</v>
+        <v>13070</v>
       </c>
       <c r="C204" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B204,[1]TextData!A:A))</f>
-        <v>ディープフリーズ+</v>
+        <v>アシッドラッシュ</v>
       </c>
       <c r="D204">
         <v>1</v>
@@ -11124,11 +11140,11 @@
         <v>1011</v>
       </c>
       <c r="B205">
-        <v>13050</v>
+        <v>14070</v>
       </c>
       <c r="C205" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B205,[1]TextData!A:A))</f>
-        <v>パッシブジャミング</v>
+        <v>ホーミングクルセイド</v>
       </c>
       <c r="D205">
         <v>1</v>
@@ -11145,20 +11161,20 @@
     </row>
     <row r="206" spans="1:7">
       <c r="A206">
-        <v>1011</v>
+        <v>1101</v>
       </c>
       <c r="B206">
-        <v>13070</v>
+        <v>3010</v>
       </c>
       <c r="C206" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B206,[1]TextData!A:A))</f>
-        <v>アシッドラッシュ</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D206">
         <v>1</v>
       </c>
       <c r="E206">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F206">
         <v>0</v>
@@ -11169,20 +11185,20 @@
     </row>
     <row r="207" spans="1:7">
       <c r="A207">
-        <v>1011</v>
+        <v>1101</v>
       </c>
       <c r="B207">
-        <v>14070</v>
+        <v>3070</v>
       </c>
       <c r="C207" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B207,[1]TextData!A:A))</f>
-        <v>ホーミングクルセイド</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D207">
         <v>1</v>
       </c>
       <c r="E207">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F207">
         <v>0</v>
@@ -11196,17 +11212,17 @@
         <v>1101</v>
       </c>
       <c r="B208">
-        <v>3010</v>
+        <v>110110</v>
       </c>
       <c r="C208" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B208,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>ウィビングヒストリー</v>
       </c>
       <c r="D208">
         <v>1</v>
       </c>
       <c r="E208">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F208">
         <v>0</v>
@@ -11220,17 +11236,17 @@
         <v>1101</v>
       </c>
       <c r="B209">
-        <v>3070</v>
+        <v>110120</v>
       </c>
       <c r="C209" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B209,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>アンライバルド</v>
       </c>
       <c r="D209">
         <v>1</v>
       </c>
       <c r="E209">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F209">
         <v>0</v>
@@ -11244,11 +11260,11 @@
         <v>1101</v>
       </c>
       <c r="B210">
-        <v>110110</v>
+        <v>13100</v>
       </c>
       <c r="C210" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B210,[1]TextData!A:A))</f>
-        <v>ウィビングヒストリー</v>
+        <v>ルミナスカバー</v>
       </c>
       <c r="D210">
         <v>1</v>
@@ -11268,17 +11284,17 @@
         <v>1101</v>
       </c>
       <c r="B211">
-        <v>110120</v>
+        <v>403050</v>
       </c>
       <c r="C211" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B211,[1]TextData!A:A))</f>
-        <v>アンライバルド</v>
+        <v>ディープフリーズ+</v>
       </c>
       <c r="D211">
         <v>1</v>
       </c>
       <c r="E211">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F211">
         <v>0</v>
@@ -11292,11 +11308,11 @@
         <v>1101</v>
       </c>
       <c r="B212">
-        <v>13100</v>
+        <v>13050</v>
       </c>
       <c r="C212" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B212,[1]TextData!A:A))</f>
-        <v>ルミナスカバー</v>
+        <v>パッシブジャミング</v>
       </c>
       <c r="D212">
         <v>1</v>
@@ -11316,11 +11332,11 @@
         <v>1101</v>
       </c>
       <c r="B213">
-        <v>403050</v>
+        <v>13070</v>
       </c>
       <c r="C213" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B213,[1]TextData!A:A))</f>
-        <v>ディープフリーズ+</v>
+        <v>アシッドラッシュ</v>
       </c>
       <c r="D213">
         <v>1</v>
@@ -11340,11 +11356,11 @@
         <v>1101</v>
       </c>
       <c r="B214">
-        <v>13050</v>
+        <v>14070</v>
       </c>
       <c r="C214" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B214,[1]TextData!A:A))</f>
-        <v>パッシブジャミング</v>
+        <v>ホーミングクルセイド</v>
       </c>
       <c r="D214">
         <v>1</v>
@@ -11356,54 +11372,6 @@
         <v>0</v>
       </c>
       <c r="G214">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215" spans="1:7">
-      <c r="A215">
-        <v>1101</v>
-      </c>
-      <c r="B215">
-        <v>13070</v>
-      </c>
-      <c r="C215" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B215,[1]TextData!A:A))</f>
-        <v>アシッドラッシュ</v>
-      </c>
-      <c r="D215">
-        <v>1</v>
-      </c>
-      <c r="E215">
-        <v>0</v>
-      </c>
-      <c r="F215">
-        <v>0</v>
-      </c>
-      <c r="G215">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7">
-      <c r="A216">
-        <v>1101</v>
-      </c>
-      <c r="B216">
-        <v>14070</v>
-      </c>
-      <c r="C216" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B216,[1]TextData!A:A))</f>
-        <v>ホーミングクルセイド</v>
-      </c>
-      <c r="D216">
-        <v>1</v>
-      </c>
-      <c r="E216">
-        <v>0</v>
-      </c>
-      <c r="F216">
-        <v>0</v>
-      </c>
-      <c r="G216">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="144">
   <si>
     <t>Id</t>
   </si>
@@ -83,58 +83,103 @@
     <t>氷</t>
   </si>
   <si>
+    <t>ファイター</t>
+  </si>
+  <si>
     <t>Cursed</t>
   </si>
   <si>
     <t>闇</t>
   </si>
   <si>
+    <t>シーフ</t>
+  </si>
+  <si>
     <t>Bee</t>
   </si>
   <si>
     <t>雷</t>
   </si>
   <si>
+    <t>ソードマン</t>
+  </si>
+  <si>
     <t>Wolf</t>
   </si>
   <si>
     <t>炎</t>
   </si>
   <si>
+    <t>ハスカール</t>
+  </si>
+  <si>
     <t>Crow</t>
   </si>
   <si>
+    <t>ハンター</t>
+  </si>
+  <si>
     <t>NY_CJ_monster_010_3</t>
   </si>
   <si>
+    <t>ウィザード</t>
+  </si>
+  <si>
     <t>Seacher</t>
   </si>
   <si>
+    <t>ホワイトナイト</t>
+  </si>
+  <si>
     <t>Shiled</t>
   </si>
   <si>
+    <t>ホブリタイ</t>
+  </si>
+  <si>
     <t>Dryad</t>
   </si>
   <si>
+    <t>ウィッチ</t>
+  </si>
+  <si>
     <t>Scorpion</t>
   </si>
   <si>
+    <t>ソルジャー</t>
+  </si>
+  <si>
     <t>Squid</t>
   </si>
   <si>
+    <t>グリフォンナイト</t>
+  </si>
+  <si>
     <t>Creeper</t>
   </si>
   <si>
+    <t>シャーマン</t>
+  </si>
+  <si>
     <t>Imp</t>
   </si>
   <si>
     <t>白</t>
   </si>
   <si>
+    <t>クレリック</t>
+  </si>
+  <si>
     <t>Armor</t>
   </si>
   <si>
+    <t>グラディエイター</t>
+  </si>
+  <si>
     <t>Sword</t>
+  </si>
+  <si>
+    <t>マーセナリー</t>
   </si>
   <si>
     <t>Orga</t>
@@ -417,8 +462,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -436,48 +481,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -491,37 +496,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -530,14 +505,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -545,14 +513,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -579,6 +547,83 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -589,7 +634,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -601,25 +658,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -637,13 +688,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -661,43 +760,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -709,13 +790,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -727,49 +814,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -783,17 +828,28 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -813,46 +869,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -880,6 +907,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -888,145 +933,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" ap